--- a/data/IEG.MI.xlsx
+++ b/data/IEG.MI.xlsx
@@ -42669,6 +42669,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1840">
+      <c r="A1840" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1840" t="n">
+        <v>10250</v>
+      </c>
+      <c r="C1840" t="n">
+        <v>17.1499996185303</v>
+      </c>
+      <c r="D1840" t="n">
+        <v>16.2999992370605</v>
+      </c>
+      <c r="E1840" t="n">
+        <v>16.8999996185303</v>
+      </c>
+      <c r="F1840" t="n">
+        <v>16.3999996185303</v>
+      </c>
+      <c r="G1840" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IEG.MI.xlsx
+++ b/data/IEG.MI.xlsx
@@ -42692,6 +42692,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1841">
+      <c r="A1841" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1841" t="n">
+        <v>8822</v>
+      </c>
+      <c r="C1841" t="n">
+        <v>16.4500007629395</v>
+      </c>
+      <c r="D1841" t="n">
+        <v>16.2999992370605</v>
+      </c>
+      <c r="E1841" t="n">
+        <v>16.3999996185303</v>
+      </c>
+      <c r="F1841" t="n">
+        <v>16.4500007629395</v>
+      </c>
+      <c r="G1841" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IEG.MI.xlsx
+++ b/data/IEG.MI.xlsx
@@ -42715,6 +42715,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1842">
+      <c r="A1842" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1842" t="n">
+        <v>23240</v>
+      </c>
+      <c r="C1842" t="n">
+        <v>16.8999996185303</v>
+      </c>
+      <c r="D1842" t="n">
+        <v>16.2999992370605</v>
+      </c>
+      <c r="E1842" t="n">
+        <v>16.4500007629395</v>
+      </c>
+      <c r="F1842" t="n">
+        <v>16.6000003814697</v>
+      </c>
+      <c r="G1842" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IEG.MI.xlsx
+++ b/data/IEG.MI.xlsx
@@ -42738,6 +42738,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1843">
+      <c r="A1843" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1843" t="n">
+        <v>51316</v>
+      </c>
+      <c r="C1843" t="n">
+        <v>17.7000007629395</v>
+      </c>
+      <c r="D1843" t="n">
+        <v>16.5499992370605</v>
+      </c>
+      <c r="E1843" t="n">
+        <v>16.6000003814697</v>
+      </c>
+      <c r="F1843" t="n">
+        <v>16.8999996185303</v>
+      </c>
+      <c r="G1843" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IEG.MI.xlsx
+++ b/data/IEG.MI.xlsx
@@ -42579,22 +42579,22 @@
     </row>
     <row r="1836">
       <c r="A1836" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1836" t="n">
-        <v>1402</v>
+        <v>4461</v>
       </c>
       <c r="C1836" t="n">
-        <v>15.6999998092651</v>
+        <v>15.5500001907349</v>
       </c>
       <c r="D1836" t="n">
+        <v>15.1000003814697</v>
+      </c>
+      <c r="E1836" t="n">
         <v>15.3500003814697</v>
       </c>
-      <c r="E1836" t="n">
-        <v>15.6999998092651</v>
-      </c>
       <c r="F1836" t="n">
-        <v>15.5</v>
+        <v>15.3000001907349</v>
       </c>
       <c r="G1836" t="s">
         <v>7</v>
@@ -42602,22 +42602,22 @@
     </row>
     <row r="1837">
       <c r="A1837" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1837" t="n">
-        <v>15763</v>
+        <v>1402</v>
       </c>
       <c r="C1837" t="n">
-        <v>16</v>
+        <v>15.6999998092651</v>
       </c>
       <c r="D1837" t="n">
-        <v>15.3999996185303</v>
+        <v>15.3500003814697</v>
       </c>
       <c r="E1837" t="n">
+        <v>15.6999998092651</v>
+      </c>
+      <c r="F1837" t="n">
         <v>15.5</v>
-      </c>
-      <c r="F1837" t="n">
-        <v>16</v>
       </c>
       <c r="G1837" t="s">
         <v>7</v>
@@ -42625,22 +42625,22 @@
     </row>
     <row r="1838">
       <c r="A1838" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1838" t="n">
-        <v>8576</v>
+        <v>15763</v>
       </c>
       <c r="C1838" t="n">
-        <v>16.6499996185303</v>
+        <v>16</v>
       </c>
       <c r="D1838" t="n">
+        <v>15.3999996185303</v>
+      </c>
+      <c r="E1838" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="F1838" t="n">
         <v>16</v>
-      </c>
-      <c r="E1838" t="n">
-        <v>16</v>
-      </c>
-      <c r="F1838" t="n">
-        <v>16.3999996185303</v>
       </c>
       <c r="G1838" t="s">
         <v>7</v>
@@ -42648,22 +42648,22 @@
     </row>
     <row r="1839">
       <c r="A1839" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1839" t="n">
-        <v>14342</v>
+        <v>8576</v>
       </c>
       <c r="C1839" t="n">
-        <v>17.2999992370605</v>
+        <v>16.6499996185303</v>
       </c>
       <c r="D1839" t="n">
-        <v>16.5499992370605</v>
+        <v>16</v>
       </c>
       <c r="E1839" t="n">
-        <v>16.5499992370605</v>
+        <v>16</v>
       </c>
       <c r="F1839" t="n">
-        <v>16.9500007629395</v>
+        <v>16.3999996185303</v>
       </c>
       <c r="G1839" t="s">
         <v>7</v>
@@ -42671,22 +42671,22 @@
     </row>
     <row r="1840">
       <c r="A1840" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1840" t="n">
-        <v>10250</v>
+        <v>14342</v>
       </c>
       <c r="C1840" t="n">
-        <v>17.1499996185303</v>
+        <v>17.2999992370605</v>
       </c>
       <c r="D1840" t="n">
-        <v>16.2999992370605</v>
+        <v>16.5499992370605</v>
       </c>
       <c r="E1840" t="n">
-        <v>16.8999996185303</v>
+        <v>16.5499992370605</v>
       </c>
       <c r="F1840" t="n">
-        <v>16.3999996185303</v>
+        <v>16.9500007629395</v>
       </c>
       <c r="G1840" t="s">
         <v>7</v>
@@ -42694,22 +42694,22 @@
     </row>
     <row r="1841">
       <c r="A1841" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1841" t="n">
-        <v>8822</v>
+        <v>10250</v>
       </c>
       <c r="C1841" t="n">
-        <v>16.4500007629395</v>
+        <v>17.1499996185303</v>
       </c>
       <c r="D1841" t="n">
         <v>16.2999992370605</v>
       </c>
       <c r="E1841" t="n">
+        <v>16.8999996185303</v>
+      </c>
+      <c r="F1841" t="n">
         <v>16.3999996185303</v>
-      </c>
-      <c r="F1841" t="n">
-        <v>16.4500007629395</v>
       </c>
       <c r="G1841" t="s">
         <v>7</v>
@@ -42717,22 +42717,22 @@
     </row>
     <row r="1842">
       <c r="A1842" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1842" t="n">
-        <v>23240</v>
+        <v>8822</v>
       </c>
       <c r="C1842" t="n">
-        <v>16.8999996185303</v>
+        <v>16.4500007629395</v>
       </c>
       <c r="D1842" t="n">
         <v>16.2999992370605</v>
       </c>
       <c r="E1842" t="n">
+        <v>16.3999996185303</v>
+      </c>
+      <c r="F1842" t="n">
         <v>16.4500007629395</v>
-      </c>
-      <c r="F1842" t="n">
-        <v>16.6000003814697</v>
       </c>
       <c r="G1842" t="s">
         <v>7</v>
@@ -42740,24 +42740,47 @@
     </row>
     <row r="1843">
       <c r="A1843" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1843" t="n">
-        <v>51316</v>
+        <v>23240</v>
       </c>
       <c r="C1843" t="n">
-        <v>17.7000007629395</v>
+        <v>16.8999996185303</v>
       </c>
       <c r="D1843" t="n">
+        <v>16.2999992370605</v>
+      </c>
+      <c r="E1843" t="n">
+        <v>16.4500007629395</v>
+      </c>
+      <c r="F1843" t="n">
+        <v>16.6000003814697</v>
+      </c>
+      <c r="G1843" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1844">
+      <c r="A1844" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1844" t="n">
+        <v>12533</v>
+      </c>
+      <c r="C1844" t="n">
+        <v>17.5499992370605</v>
+      </c>
+      <c r="D1844" t="n">
         <v>16.5499992370605</v>
       </c>
-      <c r="E1843" t="n">
+      <c r="E1844" t="n">
+        <v>17.2999992370605</v>
+      </c>
+      <c r="F1844" t="n">
         <v>16.6000003814697</v>
       </c>
-      <c r="F1843" t="n">
-        <v>16.8999996185303</v>
-      </c>
-      <c r="G1843" t="s">
+      <c r="G1844" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IEG.MI.xlsx
+++ b/data/IEG.MI.xlsx
@@ -48371,6 +48371,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1847">
+      <c r="A1847" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1847" t="n">
+        <v>9425</v>
+      </c>
+      <c r="C1847" t="n">
+        <v>16.6499996185303</v>
+      </c>
+      <c r="D1847" t="n">
+        <v>16.2999992370605</v>
+      </c>
+      <c r="E1847" t="n">
+        <v>16.3999996185303</v>
+      </c>
+      <c r="F1847" t="n">
+        <v>16.3999996185303</v>
+      </c>
+      <c r="G1847" t="n">
+        <v>16.3999996185303</v>
+      </c>
+      <c r="H1847" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IEG.MI.xlsx
+++ b/data/IEG.MI.xlsx
@@ -473,7 +473,7 @@
         <v>3.73099994659424</v>
       </c>
       <c r="G4" t="n">
-        <v>3.48258662223816</v>
+        <v>3.48258686065674</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G5" t="n">
-        <v>3.52832412719727</v>
+        <v>3.52832436561584</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G7" t="n">
-        <v>3.45365071296692</v>
+        <v>3.4536509513855</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>3.40697979927063</v>
+        <v>3.40698003768921</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G10" t="n">
-        <v>3.45365071296692</v>
+        <v>3.4536509513855</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G11" t="n">
-        <v>3.45365071296692</v>
+        <v>3.4536509513855</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G17" t="n">
-        <v>3.47231936454773</v>
+        <v>3.47231912612915</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G18" t="n">
-        <v>3.67767143249512</v>
+        <v>3.67767119407654</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G19" t="n">
-        <v>3.69634008407593</v>
+        <v>3.69633984565735</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G24" t="n">
-        <v>3.85502123832703</v>
+        <v>3.85502099990845</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G25" t="n">
-        <v>3.81768465042114</v>
+        <v>3.81768441200256</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G26" t="n">
-        <v>3.91102623939514</v>
+        <v>3.91102647781372</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G27" t="n">
-        <v>3.98569989204407</v>
+        <v>3.98569941520691</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G31" t="n">
-        <v>4.03237056732178</v>
+        <v>4.03237104415894</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G32" t="n">
-        <v>3.93902826309204</v>
+        <v>3.9390287399292</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>4.01370239257812</v>
+        <v>4.01370191574097</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G34" t="n">
-        <v>4.01370239257812</v>
+        <v>4.01370191574097</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>3.92036032676697</v>
+        <v>3.92036008834839</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G44" t="n">
-        <v>3.92036032676697</v>
+        <v>3.92036008834839</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G45" t="n">
-        <v>3.91102623939514</v>
+        <v>3.91102647781372</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G46" t="n">
-        <v>3.92036032676697</v>
+        <v>3.92036008834839</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G47" t="n">
-        <v>3.85502123832703</v>
+        <v>3.85502099990845</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G48" t="n">
-        <v>3.84568667411804</v>
+        <v>3.8456871509552</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G49" t="n">
-        <v>3.91102623939514</v>
+        <v>3.91102647781372</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G50" t="n">
-        <v>3.92036032676697</v>
+        <v>3.92036008834839</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G56" t="n">
-        <v>3.40697979927063</v>
+        <v>3.40698003768921</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G57" t="n">
-        <v>3.45365071296692</v>
+        <v>3.4536509513855</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G58" t="n">
-        <v>3.45365071296692</v>
+        <v>3.4536509513855</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G59" t="n">
-        <v>3.48165345191956</v>
+        <v>3.48165369033813</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G60" t="n">
-        <v>3.47231936454773</v>
+        <v>3.47231912612915</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G61" t="n">
-        <v>3.48165345191956</v>
+        <v>3.48165369033813</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G64" t="n">
-        <v>3.56566119194031</v>
+        <v>3.56566095352173</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G68" t="n">
-        <v>3.69634008407593</v>
+        <v>3.69633984565735</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G79" t="n">
-        <v>3.56566119194031</v>
+        <v>3.56566095352173</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G85" t="n">
-        <v>3.56566119194031</v>
+        <v>3.56566095352173</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>3.57499504089355</v>
+        <v>3.57499527931213</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G96" t="n">
-        <v>3.67767143249512</v>
+        <v>3.67767119407654</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>3.69634008407593</v>
+        <v>3.69633984565735</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G101" t="n">
-        <v>3.69634008407593</v>
+        <v>3.69633984565735</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G106" t="n">
-        <v>3.79901599884033</v>
+        <v>3.79901623725891</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G108" t="n">
-        <v>3.81768465042114</v>
+        <v>3.81768441200256</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G110" t="n">
-        <v>3.81768465042114</v>
+        <v>3.81768441200256</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>3.75234484672546</v>
+        <v>3.75234508514404</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G121" t="n">
-        <v>3.79901599884033</v>
+        <v>3.79901623725891</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G122" t="n">
-        <v>3.86435532569885</v>
+        <v>3.86435508728027</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G123" t="n">
-        <v>3.85502123832703</v>
+        <v>3.85502099990845</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G124" t="n">
-        <v>3.86435532569885</v>
+        <v>3.86435508728027</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G130" t="n">
-        <v>3.74301099777222</v>
+        <v>3.74301075935364</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G132" t="n">
-        <v>3.84568667411804</v>
+        <v>3.8456871509552</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G133" t="n">
-        <v>3.87368941307068</v>
+        <v>3.87368965148926</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G135" t="n">
-        <v>3.92036032676697</v>
+        <v>3.92036008834839</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G136" t="n">
-        <v>3.92036032676697</v>
+        <v>3.92036008834839</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G138" t="n">
-        <v>3.92036032676697</v>
+        <v>3.92036008834839</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G139" t="n">
-        <v>3.87368941307068</v>
+        <v>3.87368965148926</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G140" t="n">
-        <v>3.93902826309204</v>
+        <v>3.9390287399292</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G144" t="n">
-        <v>3.93902826309204</v>
+        <v>3.9390287399292</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G146" t="n">
-        <v>3.87368941307068</v>
+        <v>3.87368965148926</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G149" t="n">
-        <v>4.0417046546936</v>
+        <v>4.04170513153076</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G150" t="n">
-        <v>4.22838878631592</v>
+        <v>4.22838926315308</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G152" t="n">
-        <v>4.27505970001221</v>
+        <v>4.27505922317505</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G154" t="n">
-        <v>4.35906744003296</v>
+        <v>4.35906791687012</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G160" t="n">
-        <v>4.23772287368774</v>
+        <v>4.23772239685059</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G161" t="n">
-        <v>4.17238330841064</v>
+        <v>4.17238283157349</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G170" t="n">
-        <v>4.13504648208618</v>
+        <v>4.13504695892334</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G171" t="n">
-        <v>4.15371561050415</v>
+        <v>4.15371513366699</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G179" t="n">
-        <v>3.45365071296692</v>
+        <v>3.4536509513855</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G180" t="n">
-        <v>3.56566119194031</v>
+        <v>3.56566095352173</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G181" t="n">
-        <v>3.51899027824402</v>
+        <v>3.51899003982544</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14562249183655</v>
+        <v>3.14562225341797</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G185" t="n">
-        <v>3.08961725234985</v>
+        <v>3.08961749076843</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G186" t="n">
-        <v>2.92160224914551</v>
+        <v>2.92160201072693</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G206" t="n">
-        <v>2.95893859863281</v>
+        <v>2.95893883705139</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G208" t="n">
-        <v>2.91226744651794</v>
+        <v>2.91226768493652</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G209" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G213" t="n">
-        <v>2.65091013908386</v>
+        <v>2.65091037750244</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G214" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G220" t="n">
-        <v>2.85626244544983</v>
+        <v>2.85626268386841</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G225" t="n">
-        <v>2.73491787910461</v>
+        <v>2.73491811752319</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G227" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G232" t="n">
-        <v>2.65091013908386</v>
+        <v>2.65091037750244</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G234" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G236" t="n">
-        <v>2.753586769104</v>
+        <v>2.75358653068542</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G238" t="n">
-        <v>2.85626244544983</v>
+        <v>2.85626268386841</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G239" t="n">
-        <v>2.85626244544983</v>
+        <v>2.85626268386841</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G246" t="n">
-        <v>3.01494383811951</v>
+        <v>3.01494359970093</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G247" t="n">
-        <v>2.91226744651794</v>
+        <v>2.91226768493652</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G266" t="n">
-        <v>2.62290787696838</v>
+        <v>2.6229076385498</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G267" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G270" t="n">
-        <v>2.62290787696838</v>
+        <v>2.6229076385498</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G273" t="n">
-        <v>2.52956604957581</v>
+        <v>2.52956581115723</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G280" t="n">
-        <v>2.52956604957581</v>
+        <v>2.52956581115723</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G281" t="n">
-        <v>2.47356081008911</v>
+        <v>2.47356104850769</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G282" t="n">
-        <v>2.48289513587952</v>
+        <v>2.48289489746094</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G290" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G291" t="n">
-        <v>2.62290787696838</v>
+        <v>2.6229076385498</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G297" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G298" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G301" t="n">
-        <v>2.47356081008911</v>
+        <v>2.47356104850769</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G302" t="n">
-        <v>2.47356081008911</v>
+        <v>2.47356104850769</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G310" t="n">
-        <v>2.47356081008911</v>
+        <v>2.47356104850769</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G311" t="n">
-        <v>2.48289513587952</v>
+        <v>2.48289489746094</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G312" t="n">
-        <v>2.48289513587952</v>
+        <v>2.48289489746094</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G313" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G324" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G325" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G326" t="n">
-        <v>2.36155033111572</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G334" t="n">
-        <v>2.24020576477051</v>
+        <v>2.24020600318909</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G337" t="n">
-        <v>2.24020576477051</v>
+        <v>2.24020600318909</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>2.19353485107422</v>
+        <v>2.1935350894928</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.25</v>
       </c>
       <c r="G340" t="n">
-        <v>2.10019302368164</v>
+        <v>2.10019326210022</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.25</v>
       </c>
       <c r="G341" t="n">
-        <v>2.10019302368164</v>
+        <v>2.10019326210022</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G344" t="n">
-        <v>1.92284333705902</v>
+        <v>1.9228435754776</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G345" t="n">
-        <v>1.87617242336273</v>
+        <v>1.87617254257202</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G348" t="n">
-        <v>1.76416206359863</v>
+        <v>1.76416218280792</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G351" t="n">
-        <v>1.57747840881348</v>
+        <v>1.57747852802277</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G352" t="n">
-        <v>1.5308073759079</v>
+        <v>1.53080725669861</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G353" t="n">
-        <v>1.50747191905975</v>
+        <v>1.50747179985046</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G359" t="n">
-        <v>1.58681261539459</v>
+        <v>1.5868124961853</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G360" t="n">
-        <v>1.54947578907013</v>
+        <v>1.54947566986084</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G361" t="n">
-        <v>1.66148614883423</v>
+        <v>1.66148602962494</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G363" t="n">
-        <v>1.84817004203796</v>
+        <v>1.84816992282867</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.25</v>
       </c>
       <c r="G368" t="n">
-        <v>2.10019302368164</v>
+        <v>2.10019326210022</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G376" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G378" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G381" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G384" t="n">
-        <v>2.36155033111572</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G394" t="n">
-        <v>2.47356081008911</v>
+        <v>2.47356104850769</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G402" t="n">
-        <v>2.21220350265503</v>
+        <v>2.21220326423645</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.25</v>
       </c>
       <c r="G405" t="n">
-        <v>2.10019302368164</v>
+        <v>2.10019326210022</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G407" t="n">
-        <v>2.19353485107422</v>
+        <v>2.1935350894928</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G415" t="n">
-        <v>2.18420076370239</v>
+        <v>2.18420052528381</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G430" t="n">
-        <v>2.2588746547699</v>
+        <v>2.25887441635132</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G431" t="n">
-        <v>2.2588746547699</v>
+        <v>2.25887441635132</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G433" t="n">
-        <v>2.2588746547699</v>
+        <v>2.25887441635132</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G434" t="n">
-        <v>2.24020576477051</v>
+        <v>2.24020600318909</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G448" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G453" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G454" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G460" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G461" t="n">
-        <v>2.73491787910461</v>
+        <v>2.73491811752319</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G470" t="n">
-        <v>3.35097455978394</v>
+        <v>3.35097479820251</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G475" t="n">
-        <v>3.22962999343872</v>
+        <v>3.2296302318573</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>3.17362523078918</v>
+        <v>3.17362499237061</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G481" t="n">
-        <v>3.14562249183655</v>
+        <v>3.14562225341797</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G482" t="n">
-        <v>3.08961725234985</v>
+        <v>3.08961749076843</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G483" t="n">
-        <v>3.12695407867432</v>
+        <v>3.12695384025574</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G485" t="n">
-        <v>3.15495681762695</v>
+        <v>3.15495705604553</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G486" t="n">
-        <v>3.17362523078918</v>
+        <v>3.17362499237061</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G493" t="n">
-        <v>3.04294633865356</v>
+        <v>3.04294657707214</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G501" t="n">
-        <v>3.0616147518158</v>
+        <v>3.06161451339722</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G502" t="n">
-        <v>3.09895157814026</v>
+        <v>3.09895133972168</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G505" t="n">
-        <v>3.0056095123291</v>
+        <v>3.00560975074768</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G506" t="n">
-        <v>2.95893859863281</v>
+        <v>2.95893883705139</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G509" t="n">
-        <v>2.9682731628418</v>
+        <v>2.96827292442322</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G510" t="n">
-        <v>3.0056095123291</v>
+        <v>3.00560975074768</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G512" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G518" t="n">
-        <v>2.73491787910461</v>
+        <v>2.73491811752319</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G521" t="n">
-        <v>2.753586769104</v>
+        <v>2.75358653068542</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G522" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G531" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G535" t="n">
-        <v>2.53890013694763</v>
+        <v>2.53890037536621</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G536" t="n">
-        <v>2.52956604957581</v>
+        <v>2.52956581115723</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G538" t="n">
-        <v>2.62290787696838</v>
+        <v>2.6229076385498</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G539" t="n">
-        <v>2.62290787696838</v>
+        <v>2.6229076385498</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G540" t="n">
-        <v>2.62290787696838</v>
+        <v>2.6229076385498</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G541" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G542" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G549" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G553" t="n">
-        <v>2.65091013908386</v>
+        <v>2.65091037750244</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G555" t="n">
-        <v>2.753586769104</v>
+        <v>2.75358653068542</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G558" t="n">
-        <v>2.65091013908386</v>
+        <v>2.65091037750244</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G559" t="n">
-        <v>2.65091013908386</v>
+        <v>2.65091037750244</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G598" t="n">
-        <v>2.753586769104</v>
+        <v>2.75358653068542</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G600" t="n">
-        <v>2.753586769104</v>
+        <v>2.75358653068542</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G601" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G602" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G603" t="n">
-        <v>2.73491787910461</v>
+        <v>2.73491811752319</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G604" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G622" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G624" t="n">
-        <v>2.47356081008911</v>
+        <v>2.47356104850769</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G625" t="n">
-        <v>2.48289513587952</v>
+        <v>2.48289489746094</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G627" t="n">
-        <v>2.48289513587952</v>
+        <v>2.48289489746094</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G628" t="n">
-        <v>2.47356081008911</v>
+        <v>2.47356104850769</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G630" t="n">
-        <v>2.52956604957581</v>
+        <v>2.52956581115723</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G634" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G635" t="n">
-        <v>2.65091013908386</v>
+        <v>2.65091037750244</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G637" t="n">
-        <v>2.53890013694763</v>
+        <v>2.53890037536621</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G638" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G639" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G642" t="n">
-        <v>2.47356081008911</v>
+        <v>2.47356104850769</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G648" t="n">
-        <v>2.53890013694763</v>
+        <v>2.53890037536621</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G649" t="n">
-        <v>2.53890013694763</v>
+        <v>2.53890037536621</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G652" t="n">
-        <v>2.52956604957581</v>
+        <v>2.52956581115723</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G653" t="n">
-        <v>2.52956604957581</v>
+        <v>2.52956581115723</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G655" t="n">
-        <v>2.47356081008911</v>
+        <v>2.47356104850769</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>2.52956604957581</v>
+        <v>2.52956581115723</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G657" t="n">
-        <v>2.53890013694763</v>
+        <v>2.53890037536621</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G662" t="n">
-        <v>2.53890013694763</v>
+        <v>2.53890037536621</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G665" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G670" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G671" t="n">
-        <v>2.52956604957581</v>
+        <v>2.52956581115723</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G674" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G675" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G677" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G681" t="n">
-        <v>2.53890013694763</v>
+        <v>2.53890037536621</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G685" t="n">
-        <v>2.65091013908386</v>
+        <v>2.65091037750244</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G686" t="n">
-        <v>2.48289513587952</v>
+        <v>2.48289489746094</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G693" t="n">
-        <v>2.14686393737793</v>
+        <v>2.14686417579651</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G694" t="n">
-        <v>2.21220350265503</v>
+        <v>2.21220326423645</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G705" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G706" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G713" t="n">
-        <v>2.36155033111572</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G734" t="n">
-        <v>2.36155033111572</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G736" t="n">
-        <v>2.24020576477051</v>
+        <v>2.24020600318909</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G737" t="n">
-        <v>2.21220350265503</v>
+        <v>2.21220326423645</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G738" t="n">
-        <v>2.18420076370239</v>
+        <v>2.18420052528381</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G740" t="n">
-        <v>2.19353485107422</v>
+        <v>2.1935350894928</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G746" t="n">
-        <v>2.14686393737793</v>
+        <v>2.14686417579651</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G751" t="n">
-        <v>2.14686393737793</v>
+        <v>2.14686417579651</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G752" t="n">
-        <v>2.14686393737793</v>
+        <v>2.14686417579651</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G753" t="n">
-        <v>2.14686393737793</v>
+        <v>2.14686417579651</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G755" t="n">
-        <v>2.11886143684387</v>
+        <v>2.11886119842529</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G756" t="n">
-        <v>2.1375298500061</v>
+        <v>2.13752961158752</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G758" t="n">
-        <v>2.24020576477051</v>
+        <v>2.24020600318909</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G761" t="n">
-        <v>2.11886143684387</v>
+        <v>2.11886119842529</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G766" t="n">
-        <v>2.11886143684387</v>
+        <v>2.11886119842529</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G767" t="n">
-        <v>2.14686393737793</v>
+        <v>2.14686417579651</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G768" t="n">
-        <v>2.14686393737793</v>
+        <v>2.14686417579651</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G773" t="n">
-        <v>2.19353485107422</v>
+        <v>2.1935350894928</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G774" t="n">
-        <v>2.14686393737793</v>
+        <v>2.14686417579651</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G776" t="n">
-        <v>2.14686393737793</v>
+        <v>2.14686417579651</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G777" t="n">
-        <v>2.00685119628906</v>
+        <v>2.00685095787048</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G778" t="n">
-        <v>2.01618528366089</v>
+        <v>2.01618552207947</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G779" t="n">
-        <v>2.01618528366089</v>
+        <v>2.01618552207947</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G782" t="n">
-        <v>1.96018016338348</v>
+        <v>1.96018004417419</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G787" t="n">
-        <v>1.76416206359863</v>
+        <v>1.76416218280792</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G794" t="n">
-        <v>1.87617242336273</v>
+        <v>1.87617254257202</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G795" t="n">
-        <v>1.84817004203796</v>
+        <v>1.84816992282867</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G810" t="n">
-        <v>1.83883571624756</v>
+        <v>1.83883559703827</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G811" t="n">
-        <v>1.83883571624756</v>
+        <v>1.83883559703827</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G818" t="n">
-        <v>1.92284333705902</v>
+        <v>1.9228435754776</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G831" t="n">
-        <v>1.84817004203796</v>
+        <v>1.84816992282867</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G854" t="n">
-        <v>1.92284333705902</v>
+        <v>1.9228435754776</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G857" t="n">
-        <v>1.92284333705902</v>
+        <v>1.9228435754776</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G859" t="n">
-        <v>1.87617242336273</v>
+        <v>1.87617254257202</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G864" t="n">
-        <v>1.84817004203796</v>
+        <v>1.84816992282867</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G872" t="n">
-        <v>1.92284333705902</v>
+        <v>1.9228435754776</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G877" t="n">
-        <v>1.92284333705902</v>
+        <v>1.9228435754776</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G878" t="n">
-        <v>1.92284333705902</v>
+        <v>1.9228435754776</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G895" t="n">
-        <v>1.92284333705902</v>
+        <v>1.9228435754776</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G899" t="n">
-        <v>2.21220350265503</v>
+        <v>2.21220326423645</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G901" t="n">
-        <v>2.2588746547699</v>
+        <v>2.25887441635132</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G907" t="n">
-        <v>2.2588746547699</v>
+        <v>2.25887441635132</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G919" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G925" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G927" t="n">
-        <v>2.36155033111572</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G935" t="n">
-        <v>2.21220350265503</v>
+        <v>2.21220326423645</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G937" t="n">
-        <v>2.24020576477051</v>
+        <v>2.24020600318909</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G955" t="n">
-        <v>2.36155033111572</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G957" t="n">
-        <v>2.36155033111572</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G981" t="n">
-        <v>2.36155033111572</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G984" t="n">
-        <v>2.36155033111572</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1002" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1009" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1011" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1052" t="n">
-        <v>2.36155033111572</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1071" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1072" t="n">
-        <v>2.65091013908386</v>
+        <v>2.65091037750244</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1087" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1089" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1090" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1092" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.62290787696838</v>
+        <v>2.6229076385498</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1096" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1097" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1098" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1100" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1101" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1102" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1103" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1106" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1108" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1109" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1110" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1112" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1113" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1114" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1115" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1126" t="n">
-        <v>2.753586769104</v>
+        <v>2.75358653068542</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1143" t="n">
-        <v>2.85626244544983</v>
+        <v>2.85626268386841</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1148" t="n">
-        <v>2.91226744651794</v>
+        <v>2.91226768493652</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1149" t="n">
-        <v>2.92160224914551</v>
+        <v>2.92160201072693</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1154" t="n">
-        <v>2.85626244544983</v>
+        <v>2.85626268386841</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1158" t="n">
-        <v>2.91226744651794</v>
+        <v>2.91226768493652</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1163" t="n">
-        <v>2.9682731628418</v>
+        <v>2.96827292442322</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.13628816604614</v>
+        <v>3.13628840446472</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.18295907974243</v>
+        <v>3.18295931816101</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.18295907974243</v>
+        <v>3.18295931816101</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.22962999343872</v>
+        <v>3.2296302318573</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1178" t="n">
-        <v>3.79901599884033</v>
+        <v>3.79901623725891</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1185" t="n">
-        <v>4.94712162017822</v>
+        <v>4.94712209701538</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1186" t="n">
-        <v>4.85377931594849</v>
+        <v>4.85377979278564</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1189" t="n">
-        <v>4.51774930953979</v>
+        <v>4.51774883270264</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1197" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1198" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1200" t="n">
-        <v>4.51774930953979</v>
+        <v>4.51774883270264</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1201" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1208" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1209" t="n">
-        <v>4.42440700531006</v>
+        <v>4.4244065284729</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1214" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1215" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1218" t="n">
-        <v>4.45240926742554</v>
+        <v>4.4524097442627</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1219" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1220" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1221" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1222" t="n">
-        <v>4.42440700531006</v>
+        <v>4.4244065284729</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1223" t="n">
-        <v>4.38706970214844</v>
+        <v>4.3870701789856</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1225" t="n">
-        <v>4.36840152740479</v>
+        <v>4.36840105056763</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1227" t="n">
-        <v>4.38706970214844</v>
+        <v>4.3870701789856</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1229" t="n">
-        <v>4.38706970214844</v>
+        <v>4.3870701789856</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1231" t="n">
-        <v>4.38706970214844</v>
+        <v>4.3870701789856</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1232" t="n">
-        <v>4.38706970214844</v>
+        <v>4.3870701789856</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1233" t="n">
-        <v>4.38706970214844</v>
+        <v>4.3870701789856</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1235" t="n">
-        <v>4.38706970214844</v>
+        <v>4.3870701789856</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1236" t="n">
-        <v>4.38706970214844</v>
+        <v>4.3870701789856</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1237" t="n">
-        <v>4.38706970214844</v>
+        <v>4.3870701789856</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1238" t="n">
-        <v>4.38706970214844</v>
+        <v>4.3870701789856</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1239" t="n">
-        <v>4.38706970214844</v>
+        <v>4.3870701789856</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1240" t="n">
-        <v>4.45240926742554</v>
+        <v>4.4524097442627</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1241" t="n">
-        <v>4.42440700531006</v>
+        <v>4.4244065284729</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1244" t="n">
-        <v>4.38706970214844</v>
+        <v>4.3870701789856</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>4.75</v>
       </c>
       <c r="G1246" t="n">
-        <v>4.43374109268188</v>
+        <v>4.43374061584473</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1251" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -48394,6 +48394,32 @@
         <v>16.3999996185303</v>
       </c>
       <c r="H1847" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1848">
+      <c r="A1848" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1848" t="n">
+        <v>5416</v>
+      </c>
+      <c r="C1848" t="n">
+        <v>16.5499992370605</v>
+      </c>
+      <c r="D1848" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="E1848" t="n">
+        <v>16.5499992370605</v>
+      </c>
+      <c r="F1848" t="n">
+        <v>16.4500007629395</v>
+      </c>
+      <c r="G1848" t="n">
+        <v>16.4500007629395</v>
+      </c>
+      <c r="H1848" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IEG.MI.xlsx
+++ b/data/IEG.MI.xlsx
@@ -473,7 +473,7 @@
         <v>3.73099994659424</v>
       </c>
       <c r="G4" t="n">
-        <v>3.48258686065674</v>
+        <v>3.48258662223816</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G5" t="n">
-        <v>3.52832436561584</v>
+        <v>3.52832412719727</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G7" t="n">
-        <v>3.4536509513855</v>
+        <v>3.45365071296692</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>3.40698003768921</v>
+        <v>3.40697979927063</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G10" t="n">
-        <v>3.4536509513855</v>
+        <v>3.45365071296692</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G11" t="n">
-        <v>3.4536509513855</v>
+        <v>3.45365071296692</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G17" t="n">
-        <v>3.47231912612915</v>
+        <v>3.47231936454773</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G18" t="n">
-        <v>3.67767119407654</v>
+        <v>3.67767143249512</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G19" t="n">
-        <v>3.69633984565735</v>
+        <v>3.69634008407593</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G24" t="n">
-        <v>3.85502099990845</v>
+        <v>3.85502123832703</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G25" t="n">
-        <v>3.81768441200256</v>
+        <v>3.81768465042114</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G26" t="n">
-        <v>3.91102647781372</v>
+        <v>3.91102623939514</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G27" t="n">
-        <v>3.98569941520691</v>
+        <v>3.98569989204407</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G31" t="n">
-        <v>4.03237104415894</v>
+        <v>4.03237056732178</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G32" t="n">
-        <v>3.9390287399292</v>
+        <v>3.93902826309204</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>4.01370191574097</v>
+        <v>4.01370239257812</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G34" t="n">
-        <v>4.01370191574097</v>
+        <v>4.01370239257812</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>3.92036008834839</v>
+        <v>3.92036032676697</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G44" t="n">
-        <v>3.92036008834839</v>
+        <v>3.92036032676697</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G45" t="n">
-        <v>3.91102647781372</v>
+        <v>3.91102623939514</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G46" t="n">
-        <v>3.92036008834839</v>
+        <v>3.92036032676697</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G47" t="n">
-        <v>3.85502099990845</v>
+        <v>3.85502123832703</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G48" t="n">
-        <v>3.8456871509552</v>
+        <v>3.84568667411804</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G49" t="n">
-        <v>3.91102647781372</v>
+        <v>3.91102623939514</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G50" t="n">
-        <v>3.92036008834839</v>
+        <v>3.92036032676697</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G56" t="n">
-        <v>3.40698003768921</v>
+        <v>3.40697979927063</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G57" t="n">
-        <v>3.4536509513855</v>
+        <v>3.45365071296692</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G58" t="n">
-        <v>3.4536509513855</v>
+        <v>3.45365071296692</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G59" t="n">
-        <v>3.48165369033813</v>
+        <v>3.48165345191956</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G60" t="n">
-        <v>3.47231912612915</v>
+        <v>3.47231936454773</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G61" t="n">
-        <v>3.48165369033813</v>
+        <v>3.48165345191956</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G64" t="n">
-        <v>3.56566095352173</v>
+        <v>3.56566119194031</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G68" t="n">
-        <v>3.69633984565735</v>
+        <v>3.69634008407593</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G79" t="n">
-        <v>3.56566095352173</v>
+        <v>3.56566119194031</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G85" t="n">
-        <v>3.56566095352173</v>
+        <v>3.56566119194031</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>3.57499527931213</v>
+        <v>3.57499504089355</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G96" t="n">
-        <v>3.67767119407654</v>
+        <v>3.67767143249512</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>3.69633984565735</v>
+        <v>3.69634008407593</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G101" t="n">
-        <v>3.69633984565735</v>
+        <v>3.69634008407593</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G106" t="n">
-        <v>3.79901623725891</v>
+        <v>3.79901599884033</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G108" t="n">
-        <v>3.81768441200256</v>
+        <v>3.81768465042114</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G110" t="n">
-        <v>3.81768441200256</v>
+        <v>3.81768465042114</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>3.75234508514404</v>
+        <v>3.75234484672546</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G121" t="n">
-        <v>3.79901623725891</v>
+        <v>3.79901599884033</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G122" t="n">
-        <v>3.86435508728027</v>
+        <v>3.86435532569885</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G123" t="n">
-        <v>3.85502099990845</v>
+        <v>3.85502123832703</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G124" t="n">
-        <v>3.86435508728027</v>
+        <v>3.86435532569885</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G130" t="n">
-        <v>3.74301075935364</v>
+        <v>3.74301099777222</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G132" t="n">
-        <v>3.8456871509552</v>
+        <v>3.84568667411804</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G133" t="n">
-        <v>3.87368965148926</v>
+        <v>3.87368941307068</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G135" t="n">
-        <v>3.92036008834839</v>
+        <v>3.92036032676697</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G136" t="n">
-        <v>3.92036008834839</v>
+        <v>3.92036032676697</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G138" t="n">
-        <v>3.92036008834839</v>
+        <v>3.92036032676697</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G139" t="n">
-        <v>3.87368965148926</v>
+        <v>3.87368941307068</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G140" t="n">
-        <v>3.9390287399292</v>
+        <v>3.93902826309204</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G144" t="n">
-        <v>3.9390287399292</v>
+        <v>3.93902826309204</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G146" t="n">
-        <v>3.87368965148926</v>
+        <v>3.87368941307068</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G149" t="n">
-        <v>4.04170513153076</v>
+        <v>4.0417046546936</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G150" t="n">
-        <v>4.22838926315308</v>
+        <v>4.22838878631592</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G152" t="n">
-        <v>4.27505922317505</v>
+        <v>4.27505970001221</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G154" t="n">
-        <v>4.35906791687012</v>
+        <v>4.35906744003296</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G160" t="n">
-        <v>4.23772239685059</v>
+        <v>4.23772287368774</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G161" t="n">
-        <v>4.17238283157349</v>
+        <v>4.17238330841064</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G170" t="n">
-        <v>4.13504695892334</v>
+        <v>4.13504648208618</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G171" t="n">
-        <v>4.15371513366699</v>
+        <v>4.15371561050415</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G179" t="n">
-        <v>3.4536509513855</v>
+        <v>3.45365071296692</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G180" t="n">
-        <v>3.56566095352173</v>
+        <v>3.56566119194031</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G181" t="n">
-        <v>3.51899003982544</v>
+        <v>3.51899027824402</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14562225341797</v>
+        <v>3.14562249183655</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G185" t="n">
-        <v>3.08961749076843</v>
+        <v>3.08961725234985</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G186" t="n">
-        <v>2.92160201072693</v>
+        <v>2.92160224914551</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G206" t="n">
-        <v>2.95893883705139</v>
+        <v>2.95893859863281</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G208" t="n">
-        <v>2.91226768493652</v>
+        <v>2.91226744651794</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G209" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G213" t="n">
-        <v>2.65091037750244</v>
+        <v>2.65091013908386</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G214" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G220" t="n">
-        <v>2.85626268386841</v>
+        <v>2.85626244544983</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G225" t="n">
-        <v>2.73491811752319</v>
+        <v>2.73491787910461</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G227" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G232" t="n">
-        <v>2.65091037750244</v>
+        <v>2.65091013908386</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G234" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G236" t="n">
-        <v>2.75358653068542</v>
+        <v>2.753586769104</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G238" t="n">
-        <v>2.85626268386841</v>
+        <v>2.85626244544983</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G239" t="n">
-        <v>2.85626268386841</v>
+        <v>2.85626244544983</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G246" t="n">
-        <v>3.01494359970093</v>
+        <v>3.01494383811951</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G247" t="n">
-        <v>2.91226768493652</v>
+        <v>2.91226744651794</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G266" t="n">
-        <v>2.6229076385498</v>
+        <v>2.62290787696838</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G267" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G270" t="n">
-        <v>2.6229076385498</v>
+        <v>2.62290787696838</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G273" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G280" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G281" t="n">
-        <v>2.47356104850769</v>
+        <v>2.47356081008911</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G282" t="n">
-        <v>2.48289489746094</v>
+        <v>2.48289513587952</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G290" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G291" t="n">
-        <v>2.6229076385498</v>
+        <v>2.62290787696838</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G297" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G298" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G301" t="n">
-        <v>2.47356104850769</v>
+        <v>2.47356081008911</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G302" t="n">
-        <v>2.47356104850769</v>
+        <v>2.47356081008911</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G310" t="n">
-        <v>2.47356104850769</v>
+        <v>2.47356081008911</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G311" t="n">
-        <v>2.48289489746094</v>
+        <v>2.48289513587952</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G312" t="n">
-        <v>2.48289489746094</v>
+        <v>2.48289513587952</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G313" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G324" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G325" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G326" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G334" t="n">
-        <v>2.24020600318909</v>
+        <v>2.24020576477051</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G337" t="n">
-        <v>2.24020600318909</v>
+        <v>2.24020576477051</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>2.1935350894928</v>
+        <v>2.19353485107422</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.25</v>
       </c>
       <c r="G340" t="n">
-        <v>2.10019326210022</v>
+        <v>2.10019302368164</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.25</v>
       </c>
       <c r="G341" t="n">
-        <v>2.10019326210022</v>
+        <v>2.10019302368164</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G344" t="n">
-        <v>1.9228435754776</v>
+        <v>1.92284333705902</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G345" t="n">
-        <v>1.87617254257202</v>
+        <v>1.87617242336273</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G348" t="n">
-        <v>1.76416218280792</v>
+        <v>1.76416206359863</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G351" t="n">
-        <v>1.57747852802277</v>
+        <v>1.57747840881348</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G352" t="n">
-        <v>1.53080725669861</v>
+        <v>1.5308073759079</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G353" t="n">
-        <v>1.50747179985046</v>
+        <v>1.50747191905975</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G359" t="n">
-        <v>1.5868124961853</v>
+        <v>1.58681261539459</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G360" t="n">
-        <v>1.54947566986084</v>
+        <v>1.54947578907013</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G361" t="n">
-        <v>1.66148602962494</v>
+        <v>1.66148614883423</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G363" t="n">
-        <v>1.84816992282867</v>
+        <v>1.84817004203796</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.25</v>
       </c>
       <c r="G368" t="n">
-        <v>2.10019326210022</v>
+        <v>2.10019302368164</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G376" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G378" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G381" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G384" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G394" t="n">
-        <v>2.47356104850769</v>
+        <v>2.47356081008911</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G402" t="n">
-        <v>2.21220326423645</v>
+        <v>2.21220350265503</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.25</v>
       </c>
       <c r="G405" t="n">
-        <v>2.10019326210022</v>
+        <v>2.10019302368164</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G407" t="n">
-        <v>2.1935350894928</v>
+        <v>2.19353485107422</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G415" t="n">
-        <v>2.18420052528381</v>
+        <v>2.18420076370239</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G430" t="n">
-        <v>2.25887441635132</v>
+        <v>2.2588746547699</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G431" t="n">
-        <v>2.25887441635132</v>
+        <v>2.2588746547699</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G433" t="n">
-        <v>2.25887441635132</v>
+        <v>2.2588746547699</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G434" t="n">
-        <v>2.24020600318909</v>
+        <v>2.24020576477051</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G448" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G453" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G454" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G460" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G461" t="n">
-        <v>2.73491811752319</v>
+        <v>2.73491787910461</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G470" t="n">
-        <v>3.35097479820251</v>
+        <v>3.35097455978394</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G475" t="n">
-        <v>3.2296302318573</v>
+        <v>3.22962999343872</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>3.17362499237061</v>
+        <v>3.17362523078918</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G481" t="n">
-        <v>3.14562225341797</v>
+        <v>3.14562249183655</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G482" t="n">
-        <v>3.08961749076843</v>
+        <v>3.08961725234985</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G483" t="n">
-        <v>3.12695384025574</v>
+        <v>3.12695407867432</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G485" t="n">
-        <v>3.15495705604553</v>
+        <v>3.15495681762695</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G486" t="n">
-        <v>3.17362499237061</v>
+        <v>3.17362523078918</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G493" t="n">
-        <v>3.04294657707214</v>
+        <v>3.04294633865356</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G501" t="n">
-        <v>3.06161451339722</v>
+        <v>3.0616147518158</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G502" t="n">
-        <v>3.09895133972168</v>
+        <v>3.09895157814026</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G505" t="n">
-        <v>3.00560975074768</v>
+        <v>3.0056095123291</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G506" t="n">
-        <v>2.95893883705139</v>
+        <v>2.95893859863281</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G509" t="n">
-        <v>2.96827292442322</v>
+        <v>2.9682731628418</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G510" t="n">
-        <v>3.00560975074768</v>
+        <v>3.0056095123291</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G512" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G518" t="n">
-        <v>2.73491811752319</v>
+        <v>2.73491787910461</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G521" t="n">
-        <v>2.75358653068542</v>
+        <v>2.753586769104</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G522" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G531" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G535" t="n">
-        <v>2.53890037536621</v>
+        <v>2.53890013694763</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G536" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G538" t="n">
-        <v>2.6229076385498</v>
+        <v>2.62290787696838</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G539" t="n">
-        <v>2.6229076385498</v>
+        <v>2.62290787696838</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G540" t="n">
-        <v>2.6229076385498</v>
+        <v>2.62290787696838</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G541" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G542" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G549" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G553" t="n">
-        <v>2.65091037750244</v>
+        <v>2.65091013908386</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G555" t="n">
-        <v>2.75358653068542</v>
+        <v>2.753586769104</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G558" t="n">
-        <v>2.65091037750244</v>
+        <v>2.65091013908386</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G559" t="n">
-        <v>2.65091037750244</v>
+        <v>2.65091013908386</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G598" t="n">
-        <v>2.75358653068542</v>
+        <v>2.753586769104</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G600" t="n">
-        <v>2.75358653068542</v>
+        <v>2.753586769104</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G601" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G602" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G603" t="n">
-        <v>2.73491811752319</v>
+        <v>2.73491787910461</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G604" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G622" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G624" t="n">
-        <v>2.47356104850769</v>
+        <v>2.47356081008911</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G625" t="n">
-        <v>2.48289489746094</v>
+        <v>2.48289513587952</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G627" t="n">
-        <v>2.48289489746094</v>
+        <v>2.48289513587952</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G628" t="n">
-        <v>2.47356104850769</v>
+        <v>2.47356081008911</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G630" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G634" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G635" t="n">
-        <v>2.65091037750244</v>
+        <v>2.65091013908386</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G637" t="n">
-        <v>2.53890037536621</v>
+        <v>2.53890013694763</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G638" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G639" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G642" t="n">
-        <v>2.47356104850769</v>
+        <v>2.47356081008911</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G648" t="n">
-        <v>2.53890037536621</v>
+        <v>2.53890013694763</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G649" t="n">
-        <v>2.53890037536621</v>
+        <v>2.53890013694763</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G652" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G653" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G655" t="n">
-        <v>2.47356104850769</v>
+        <v>2.47356081008911</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G657" t="n">
-        <v>2.53890037536621</v>
+        <v>2.53890013694763</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G662" t="n">
-        <v>2.53890037536621</v>
+        <v>2.53890013694763</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G665" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G670" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G671" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G674" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G675" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G677" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G681" t="n">
-        <v>2.53890037536621</v>
+        <v>2.53890013694763</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G685" t="n">
-        <v>2.65091037750244</v>
+        <v>2.65091013908386</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G686" t="n">
-        <v>2.48289489746094</v>
+        <v>2.48289513587952</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G693" t="n">
-        <v>2.14686417579651</v>
+        <v>2.14686393737793</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G694" t="n">
-        <v>2.21220326423645</v>
+        <v>2.21220350265503</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G705" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G706" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G713" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G734" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G736" t="n">
-        <v>2.24020600318909</v>
+        <v>2.24020576477051</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G737" t="n">
-        <v>2.21220326423645</v>
+        <v>2.21220350265503</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G738" t="n">
-        <v>2.18420052528381</v>
+        <v>2.18420076370239</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G740" t="n">
-        <v>2.1935350894928</v>
+        <v>2.19353485107422</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G746" t="n">
-        <v>2.14686417579651</v>
+        <v>2.14686393737793</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G751" t="n">
-        <v>2.14686417579651</v>
+        <v>2.14686393737793</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G752" t="n">
-        <v>2.14686417579651</v>
+        <v>2.14686393737793</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G753" t="n">
-        <v>2.14686417579651</v>
+        <v>2.14686393737793</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G755" t="n">
-        <v>2.11886119842529</v>
+        <v>2.11886143684387</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G756" t="n">
-        <v>2.13752961158752</v>
+        <v>2.1375298500061</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G758" t="n">
-        <v>2.24020600318909</v>
+        <v>2.24020576477051</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G761" t="n">
-        <v>2.11886119842529</v>
+        <v>2.11886143684387</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G766" t="n">
-        <v>2.11886119842529</v>
+        <v>2.11886143684387</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G767" t="n">
-        <v>2.14686417579651</v>
+        <v>2.14686393737793</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G768" t="n">
-        <v>2.14686417579651</v>
+        <v>2.14686393737793</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G773" t="n">
-        <v>2.1935350894928</v>
+        <v>2.19353485107422</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G774" t="n">
-        <v>2.14686417579651</v>
+        <v>2.14686393737793</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G776" t="n">
-        <v>2.14686417579651</v>
+        <v>2.14686393737793</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G777" t="n">
-        <v>2.00685095787048</v>
+        <v>2.00685119628906</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G778" t="n">
-        <v>2.01618552207947</v>
+        <v>2.01618528366089</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G779" t="n">
-        <v>2.01618552207947</v>
+        <v>2.01618528366089</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G782" t="n">
-        <v>1.96018004417419</v>
+        <v>1.96018016338348</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G787" t="n">
-        <v>1.76416218280792</v>
+        <v>1.76416206359863</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G794" t="n">
-        <v>1.87617254257202</v>
+        <v>1.87617242336273</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G795" t="n">
-        <v>1.84816992282867</v>
+        <v>1.84817004203796</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G810" t="n">
-        <v>1.83883559703827</v>
+        <v>1.83883571624756</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G811" t="n">
-        <v>1.83883559703827</v>
+        <v>1.83883571624756</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G818" t="n">
-        <v>1.9228435754776</v>
+        <v>1.92284333705902</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G831" t="n">
-        <v>1.84816992282867</v>
+        <v>1.84817004203796</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G854" t="n">
-        <v>1.9228435754776</v>
+        <v>1.92284333705902</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G857" t="n">
-        <v>1.9228435754776</v>
+        <v>1.92284333705902</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G859" t="n">
-        <v>1.87617254257202</v>
+        <v>1.87617242336273</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G864" t="n">
-        <v>1.84816992282867</v>
+        <v>1.84817004203796</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G872" t="n">
-        <v>1.9228435754776</v>
+        <v>1.92284333705902</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G877" t="n">
-        <v>1.9228435754776</v>
+        <v>1.92284333705902</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G878" t="n">
-        <v>1.9228435754776</v>
+        <v>1.92284333705902</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G895" t="n">
-        <v>1.9228435754776</v>
+        <v>1.92284333705902</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G899" t="n">
-        <v>2.21220326423645</v>
+        <v>2.21220350265503</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G901" t="n">
-        <v>2.25887441635132</v>
+        <v>2.2588746547699</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G907" t="n">
-        <v>2.25887441635132</v>
+        <v>2.2588746547699</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G919" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G925" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G927" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G935" t="n">
-        <v>2.21220326423645</v>
+        <v>2.21220350265503</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G937" t="n">
-        <v>2.24020600318909</v>
+        <v>2.24020576477051</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G955" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G957" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G981" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G984" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1002" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1009" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1011" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1052" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1071" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1072" t="n">
-        <v>2.65091037750244</v>
+        <v>2.65091013908386</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1087" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1089" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1090" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1092" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.6229076385498</v>
+        <v>2.62290787696838</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1096" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1097" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1098" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1100" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1101" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1102" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1103" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1106" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1108" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1109" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1110" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1112" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1113" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1114" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1115" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1126" t="n">
-        <v>2.75358653068542</v>
+        <v>2.753586769104</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1143" t="n">
-        <v>2.85626268386841</v>
+        <v>2.85626244544983</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1148" t="n">
-        <v>2.91226768493652</v>
+        <v>2.91226744651794</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1149" t="n">
-        <v>2.92160201072693</v>
+        <v>2.92160224914551</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1154" t="n">
-        <v>2.85626268386841</v>
+        <v>2.85626244544983</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1158" t="n">
-        <v>2.91226768493652</v>
+        <v>2.91226744651794</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1163" t="n">
-        <v>2.96827292442322</v>
+        <v>2.9682731628418</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.13628840446472</v>
+        <v>3.13628816604614</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.18295931816101</v>
+        <v>3.18295907974243</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.18295931816101</v>
+        <v>3.18295907974243</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.2296302318573</v>
+        <v>3.22962999343872</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1178" t="n">
-        <v>3.79901623725891</v>
+        <v>3.79901599884033</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1185" t="n">
-        <v>4.94712209701538</v>
+        <v>4.94712162017822</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1186" t="n">
-        <v>4.85377979278564</v>
+        <v>4.85377931594849</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1189" t="n">
-        <v>4.51774883270264</v>
+        <v>4.51774930953979</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1197" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1198" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1200" t="n">
-        <v>4.51774883270264</v>
+        <v>4.51774930953979</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1201" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1208" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1209" t="n">
-        <v>4.4244065284729</v>
+        <v>4.42440700531006</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1214" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1215" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1218" t="n">
-        <v>4.4524097442627</v>
+        <v>4.45240926742554</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1219" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1220" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1221" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1222" t="n">
-        <v>4.4244065284729</v>
+        <v>4.42440700531006</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1223" t="n">
-        <v>4.3870701789856</v>
+        <v>4.38706970214844</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1225" t="n">
-        <v>4.36840105056763</v>
+        <v>4.36840152740479</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1227" t="n">
-        <v>4.3870701789856</v>
+        <v>4.38706970214844</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1229" t="n">
-        <v>4.3870701789856</v>
+        <v>4.38706970214844</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1231" t="n">
-        <v>4.3870701789856</v>
+        <v>4.38706970214844</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1232" t="n">
-        <v>4.3870701789856</v>
+        <v>4.38706970214844</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1233" t="n">
-        <v>4.3870701789856</v>
+        <v>4.38706970214844</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1235" t="n">
-        <v>4.3870701789856</v>
+        <v>4.38706970214844</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1236" t="n">
-        <v>4.3870701789856</v>
+        <v>4.38706970214844</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1237" t="n">
-        <v>4.3870701789856</v>
+        <v>4.38706970214844</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1238" t="n">
-        <v>4.3870701789856</v>
+        <v>4.38706970214844</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1239" t="n">
-        <v>4.3870701789856</v>
+        <v>4.38706970214844</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1240" t="n">
-        <v>4.4524097442627</v>
+        <v>4.45240926742554</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1241" t="n">
-        <v>4.4244065284729</v>
+        <v>4.42440700531006</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1244" t="n">
-        <v>4.3870701789856</v>
+        <v>4.38706970214844</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>4.75</v>
       </c>
       <c r="G1246" t="n">
-        <v>4.43374061584473</v>
+        <v>4.43374109268188</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1251" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -48420,6 +48420,32 @@
         <v>16.4500007629395</v>
       </c>
       <c r="H1848" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1849">
+      <c r="A1849" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1849" t="n">
+        <v>28354</v>
+      </c>
+      <c r="C1849" t="n">
+        <v>16.7000007629395</v>
+      </c>
+      <c r="D1849" t="n">
+        <v>16.2000007629395</v>
+      </c>
+      <c r="E1849" t="n">
+        <v>16.2999992370605</v>
+      </c>
+      <c r="F1849" t="n">
+        <v>16.6499996185303</v>
+      </c>
+      <c r="G1849" t="n">
+        <v>16.6499996185303</v>
+      </c>
+      <c r="H1849" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IEG.MI.xlsx
+++ b/data/IEG.MI.xlsx
@@ -447,7 +447,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G3" t="n">
-        <v>3.49098753929138</v>
+        <v>3.49098777770996</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.69749999046326</v>
       </c>
       <c r="G6" t="n">
-        <v>3.45131707191467</v>
+        <v>3.45131731033325</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.64050006866455</v>
       </c>
       <c r="G13" t="n">
-        <v>3.39811229705811</v>
+        <v>3.39811253547668</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G14" t="n">
-        <v>3.31363773345947</v>
+        <v>3.31363797187805</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G16" t="n">
-        <v>3.36030864715576</v>
+        <v>3.36030888557434</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G17" t="n">
-        <v>3.47231936454773</v>
+        <v>3.47231912612915</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G20" t="n">
-        <v>3.78034782409668</v>
+        <v>3.7803475856781</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G21" t="n">
-        <v>3.80834984779358</v>
+        <v>3.80835008621216</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G22" t="n">
-        <v>3.78034782409668</v>
+        <v>3.7803475856781</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G26" t="n">
-        <v>3.91102623939514</v>
+        <v>3.91102600097656</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G28" t="n">
-        <v>3.95769667625427</v>
+        <v>3.95769715309143</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G29" t="n">
-        <v>3.97636604309082</v>
+        <v>3.97636580467224</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G30" t="n">
-        <v>4.05103874206543</v>
+        <v>4.05103921890259</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G32" t="n">
-        <v>3.93902826309204</v>
+        <v>3.93902850151062</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>4.01370239257812</v>
+        <v>4.01370286941528</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G34" t="n">
-        <v>4.01370239257812</v>
+        <v>4.01370286941528</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G35" t="n">
-        <v>3.99503421783447</v>
+        <v>3.99503397941589</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G36" t="n">
-        <v>3.99503421783447</v>
+        <v>3.99503397941589</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G37" t="n">
-        <v>3.99503421783447</v>
+        <v>3.99503397941589</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G38" t="n">
-        <v>3.95769667625427</v>
+        <v>3.95769715309143</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G41" t="n">
-        <v>3.95769667625427</v>
+        <v>3.95769715309143</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G42" t="n">
-        <v>3.95769667625427</v>
+        <v>3.95769715309143</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>3.92036032676697</v>
+        <v>3.92036008834839</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G44" t="n">
-        <v>3.92036032676697</v>
+        <v>3.92036008834839</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G45" t="n">
-        <v>3.91102623939514</v>
+        <v>3.91102600097656</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G46" t="n">
-        <v>3.92036032676697</v>
+        <v>3.92036008834839</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G49" t="n">
-        <v>3.91102623939514</v>
+        <v>3.91102600097656</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G50" t="n">
-        <v>3.92036032676697</v>
+        <v>3.92036008834839</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G60" t="n">
-        <v>3.47231936454773</v>
+        <v>3.47231912612915</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G63" t="n">
-        <v>3.60299777984619</v>
+        <v>3.60299754142761</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G70" t="n">
-        <v>3.60299777984619</v>
+        <v>3.60299754142761</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>3.54699277877808</v>
+        <v>3.54699301719666</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G76" t="n">
-        <v>3.54699277877808</v>
+        <v>3.54699301719666</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>3.54699277877808</v>
+        <v>3.54699301719666</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G78" t="n">
-        <v>3.621666431427</v>
+        <v>3.62166666984558</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G83" t="n">
-        <v>3.61233186721802</v>
+        <v>3.6123321056366</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G84" t="n">
-        <v>3.61233186721802</v>
+        <v>3.6123321056366</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G88" t="n">
-        <v>3.621666431427</v>
+        <v>3.62166666984558</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G91" t="n">
-        <v>3.61233186721802</v>
+        <v>3.6123321056366</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G92" t="n">
-        <v>3.54699277877808</v>
+        <v>3.54699301719666</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G94" t="n">
-        <v>3.621666431427</v>
+        <v>3.62166666984558</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G105" t="n">
-        <v>3.64966893196106</v>
+        <v>3.64966869354248</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>3.80834984779358</v>
+        <v>3.80835008621216</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G112" t="n">
-        <v>3.80834984779358</v>
+        <v>3.80835008621216</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G116" t="n">
-        <v>3.76167917251587</v>
+        <v>3.76167941093445</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>3.78034782409668</v>
+        <v>3.7803475856781</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G122" t="n">
-        <v>3.86435532569885</v>
+        <v>3.86435508728027</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G124" t="n">
-        <v>3.86435532569885</v>
+        <v>3.86435508728027</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G126" t="n">
-        <v>3.80834984779358</v>
+        <v>3.80835008621216</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G129" t="n">
-        <v>3.78034782409668</v>
+        <v>3.7803475856781</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G130" t="n">
-        <v>3.74301099777222</v>
+        <v>3.7430112361908</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G133" t="n">
-        <v>3.87368941307068</v>
+        <v>3.87368965148926</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G135" t="n">
-        <v>3.92036032676697</v>
+        <v>3.92036008834839</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G136" t="n">
-        <v>3.92036032676697</v>
+        <v>3.92036008834839</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G138" t="n">
-        <v>3.92036032676697</v>
+        <v>3.92036008834839</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G139" t="n">
-        <v>3.87368941307068</v>
+        <v>3.87368965148926</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G140" t="n">
-        <v>3.93902826309204</v>
+        <v>3.93902850151062</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G144" t="n">
-        <v>3.93902826309204</v>
+        <v>3.93902850151062</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G145" t="n">
-        <v>3.89235782623291</v>
+        <v>3.89235806465149</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G146" t="n">
-        <v>3.87368941307068</v>
+        <v>3.87368965148926</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G148" t="n">
-        <v>3.95769667625427</v>
+        <v>3.95769715309143</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G150" t="n">
-        <v>4.22838878631592</v>
+        <v>4.22838926315308</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G155" t="n">
-        <v>4.40573787689209</v>
+        <v>4.40573835372925</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G157" t="n">
-        <v>4.40573787689209</v>
+        <v>4.40573835372925</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G159" t="n">
-        <v>4.19105195999146</v>
+        <v>4.1910514831543</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G162" t="n">
-        <v>4.14438056945801</v>
+        <v>4.14438104629517</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G164" t="n">
-        <v>4.0697078704834</v>
+        <v>4.06970739364624</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G165" t="n">
-        <v>4.1070442199707</v>
+        <v>4.10704469680786</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>4.05103874206543</v>
+        <v>4.05103921890259</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G169" t="n">
-        <v>4.14438056945801</v>
+        <v>4.14438104629517</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G170" t="n">
-        <v>4.13504648208618</v>
+        <v>4.13504695892334</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G171" t="n">
-        <v>4.15371561050415</v>
+        <v>4.15371513366699</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G173" t="n">
-        <v>4.06037330627441</v>
+        <v>4.06037282943726</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G175" t="n">
-        <v>3.49098753929138</v>
+        <v>3.49098777770996</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G177" t="n">
-        <v>3.64966893196106</v>
+        <v>3.64966869354248</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14562249183655</v>
+        <v>3.14562225341797</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G185" t="n">
-        <v>3.08961725234985</v>
+        <v>3.08961749076843</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G186" t="n">
-        <v>2.92160224914551</v>
+        <v>2.92160201072693</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G188" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G189" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G190" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G191" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G192" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G198" t="n">
-        <v>2.45489239692688</v>
+        <v>2.45489263534546</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>2.5</v>
       </c>
       <c r="G199" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G200" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>2.5</v>
       </c>
       <c r="G202" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G203" t="n">
-        <v>2.34288215637207</v>
+        <v>2.34288191795349</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G204" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G206" t="n">
-        <v>2.95893859863281</v>
+        <v>2.95893883705139</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G208" t="n">
-        <v>2.91226744651794</v>
+        <v>2.91226768493652</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>2.76292061805725</v>
+        <v>2.76292085647583</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G213" t="n">
-        <v>2.65091013908386</v>
+        <v>2.65091037750244</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G218" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G225" t="n">
-        <v>2.73491787910461</v>
+        <v>2.73491811752319</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G230" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G232" t="n">
-        <v>2.65091013908386</v>
+        <v>2.65091037750244</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>2.76292061805725</v>
+        <v>2.76292085647583</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G235" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G236" t="n">
-        <v>2.753586769104</v>
+        <v>2.75358653068542</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G240" t="n">
-        <v>2.82825994491577</v>
+        <v>2.82826018333435</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G245" t="n">
-        <v>2.82825994491577</v>
+        <v>2.82826018333435</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G247" t="n">
-        <v>2.91226744651794</v>
+        <v>2.91226768493652</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G251" t="n">
-        <v>2.78158903121948</v>
+        <v>2.78158926963806</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G253" t="n">
-        <v>2.82825994491577</v>
+        <v>2.82826018333435</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G254" t="n">
-        <v>2.82825994491577</v>
+        <v>2.82826018333435</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G257" t="n">
-        <v>2.78158903121948</v>
+        <v>2.78158926963806</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G266" t="n">
-        <v>2.62290787696838</v>
+        <v>2.6229076385498</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G267" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G270" t="n">
-        <v>2.62290787696838</v>
+        <v>2.6229076385498</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G271" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G274" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G275" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G276" t="n">
-        <v>2.49222922325134</v>
+        <v>2.49222898483276</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G277" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G278" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G279" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.5</v>
       </c>
       <c r="G289" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G290" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G291" t="n">
-        <v>2.62290787696838</v>
+        <v>2.6229076385498</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G293" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G294" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G303" t="n">
-        <v>2.49222922325134</v>
+        <v>2.49222898483276</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G304" t="n">
-        <v>2.49222922325134</v>
+        <v>2.49222898483276</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G305" t="n">
-        <v>2.49222922325134</v>
+        <v>2.49222898483276</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G309" t="n">
-        <v>2.45489239692688</v>
+        <v>2.45489263534546</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G326" t="n">
-        <v>2.36155033111572</v>
+        <v>2.36155009269714</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.5</v>
       </c>
       <c r="G328" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.5</v>
       </c>
       <c r="G333" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G343" t="n">
-        <v>1.98818302154541</v>
+        <v>1.98818290233612</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G350" t="n">
-        <v>1.68015432357788</v>
+        <v>1.68015444278717</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G358" t="n">
-        <v>1.5354745388031</v>
+        <v>1.53547441959381</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G361" t="n">
-        <v>1.66148614883423</v>
+        <v>1.66148602962494</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G366" t="n">
-        <v>2.02551937103271</v>
+        <v>2.02551960945129</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G377" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G378" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G384" t="n">
-        <v>2.36155033111572</v>
+        <v>2.36155009269714</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G385" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.5</v>
       </c>
       <c r="G386" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G390" t="n">
-        <v>2.49222922325134</v>
+        <v>2.49222898483276</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G392" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G399" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G400" t="n">
-        <v>2.20286893844604</v>
+        <v>2.20286917686462</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G401" t="n">
-        <v>2.072190284729</v>
+        <v>2.07219052314758</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G402" t="n">
-        <v>2.21220350265503</v>
+        <v>2.21220326423645</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G403" t="n">
-        <v>2.17486667633057</v>
+        <v>2.17486643791199</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G404" t="n">
-        <v>2.17486667633057</v>
+        <v>2.17486643791199</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G406" t="n">
-        <v>2.05352210998535</v>
+        <v>2.05352234840393</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G408" t="n">
-        <v>2.20286893844604</v>
+        <v>2.20286917686462</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G410" t="n">
-        <v>2.05352210998535</v>
+        <v>2.05352234840393</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G411" t="n">
-        <v>2.05352210998535</v>
+        <v>2.05352234840393</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G412" t="n">
-        <v>2.05352210998535</v>
+        <v>2.05352234840393</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G413" t="n">
-        <v>2.05352210998535</v>
+        <v>2.05352234840393</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G421" t="n">
-        <v>2.34288215637207</v>
+        <v>2.34288191795349</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G424" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G435" t="n">
-        <v>2.24954009056091</v>
+        <v>2.24954032897949</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G437" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>2.5</v>
       </c>
       <c r="G440" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>2.5</v>
       </c>
       <c r="G442" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G444" t="n">
-        <v>2.24954009056091</v>
+        <v>2.24954032897949</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G450" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G461" t="n">
-        <v>2.73491787910461</v>
+        <v>2.73491811752319</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>3.25</v>
       </c>
       <c r="G465" t="n">
-        <v>3.03361201286316</v>
+        <v>3.03361225128174</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>3.25</v>
       </c>
       <c r="G467" t="n">
-        <v>3.03361201286316</v>
+        <v>3.03361225128174</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>3.25</v>
       </c>
       <c r="G469" t="n">
-        <v>3.03361201286316</v>
+        <v>3.03361225128174</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G471" t="n">
-        <v>3.27630114555359</v>
+        <v>3.27630090713501</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G473" t="n">
-        <v>3.33230638504028</v>
+        <v>3.3323061466217</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G475" t="n">
-        <v>3.22962999343872</v>
+        <v>3.2296302318573</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G479" t="n">
-        <v>3.16429090499878</v>
+        <v>3.16429114341736</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G480" t="n">
-        <v>3.20162796974182</v>
+        <v>3.20162773132324</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G481" t="n">
-        <v>3.14562249183655</v>
+        <v>3.14562225341797</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G482" t="n">
-        <v>3.08961725234985</v>
+        <v>3.08961749076843</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G488" t="n">
-        <v>3.16429090499878</v>
+        <v>3.16429114341736</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G498" t="n">
-        <v>3.0709490776062</v>
+        <v>3.07094883918762</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>3.25</v>
       </c>
       <c r="G503" t="n">
-        <v>3.03361201286316</v>
+        <v>3.03361225128174</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G506" t="n">
-        <v>2.95893859863281</v>
+        <v>2.95893883705139</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G509" t="n">
-        <v>2.9682731628418</v>
+        <v>2.96827292442322</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G511" t="n">
-        <v>2.7442524433136</v>
+        <v>2.74425220489502</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G514" t="n">
-        <v>2.78158903121948</v>
+        <v>2.78158926963806</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G516" t="n">
-        <v>2.7442524433136</v>
+        <v>2.74425220489502</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G518" t="n">
-        <v>2.73491787910461</v>
+        <v>2.73491811752319</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G519" t="n">
-        <v>2.7442524433136</v>
+        <v>2.74425220489502</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G520" t="n">
-        <v>2.7442524433136</v>
+        <v>2.74425220489502</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G521" t="n">
-        <v>2.753586769104</v>
+        <v>2.75358653068542</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G528" t="n">
-        <v>2.49222922325134</v>
+        <v>2.49222898483276</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G530" t="n">
-        <v>2.49222922325134</v>
+        <v>2.49222898483276</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G533" t="n">
-        <v>2.45489239692688</v>
+        <v>2.45489263534546</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G534" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G535" t="n">
-        <v>2.53890013694763</v>
+        <v>2.53889989852905</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G538" t="n">
-        <v>2.62290787696838</v>
+        <v>2.6229076385498</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G539" t="n">
-        <v>2.62290787696838</v>
+        <v>2.6229076385498</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G540" t="n">
-        <v>2.62290787696838</v>
+        <v>2.6229076385498</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G541" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G553" t="n">
-        <v>2.65091013908386</v>
+        <v>2.65091037750244</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G555" t="n">
-        <v>2.753586769104</v>
+        <v>2.75358653068542</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G558" t="n">
-        <v>2.65091013908386</v>
+        <v>2.65091037750244</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G559" t="n">
-        <v>2.65091013908386</v>
+        <v>2.65091037750244</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G561" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G565" t="n">
-        <v>2.78158903121948</v>
+        <v>2.78158926963806</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G566" t="n">
-        <v>2.86559653282166</v>
+        <v>2.86559677124023</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G568" t="n">
-        <v>2.78158903121948</v>
+        <v>2.78158926963806</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G571" t="n">
-        <v>2.82825994491577</v>
+        <v>2.82826018333435</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G576" t="n">
-        <v>2.7442524433136</v>
+        <v>2.74425220489502</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G577" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G578" t="n">
-        <v>2.82825994491577</v>
+        <v>2.82826018333435</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G579" t="n">
-        <v>2.78158903121948</v>
+        <v>2.78158926963806</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G583" t="n">
-        <v>2.76292061805725</v>
+        <v>2.76292085647583</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G584" t="n">
-        <v>2.78158903121948</v>
+        <v>2.78158926963806</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G585" t="n">
-        <v>2.78158903121948</v>
+        <v>2.78158926963806</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G589" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G594" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G598" t="n">
-        <v>2.753586769104</v>
+        <v>2.75358653068542</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G599" t="n">
-        <v>2.7442524433136</v>
+        <v>2.74425220489502</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G600" t="n">
-        <v>2.753586769104</v>
+        <v>2.75358653068542</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G603" t="n">
-        <v>2.73491787910461</v>
+        <v>2.73491811752319</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G607" t="n">
-        <v>2.7442524433136</v>
+        <v>2.74425220489502</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G608" t="n">
-        <v>2.78158903121948</v>
+        <v>2.78158926963806</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G609" t="n">
-        <v>2.76292061805725</v>
+        <v>2.76292085647583</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G611" t="n">
-        <v>2.82825994491577</v>
+        <v>2.82826018333435</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G613" t="n">
-        <v>2.82825994491577</v>
+        <v>2.82826018333435</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G615" t="n">
-        <v>2.78158903121948</v>
+        <v>2.78158926963806</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G620" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G621" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G629" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G634" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G635" t="n">
-        <v>2.65091013908386</v>
+        <v>2.65091037750244</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G637" t="n">
-        <v>2.53890013694763</v>
+        <v>2.53889989852905</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G639" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G640" t="n">
-        <v>2.49222922325134</v>
+        <v>2.49222898483276</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G646" t="n">
-        <v>2.49222922325134</v>
+        <v>2.49222898483276</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G647" t="n">
-        <v>2.49222922325134</v>
+        <v>2.49222898483276</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G648" t="n">
-        <v>2.53890013694763</v>
+        <v>2.53889989852905</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G649" t="n">
-        <v>2.53890013694763</v>
+        <v>2.53889989852905</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G657" t="n">
-        <v>2.53890013694763</v>
+        <v>2.53889989852905</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G658" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G662" t="n">
-        <v>2.53890013694763</v>
+        <v>2.53889989852905</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G669" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G670" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G677" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G679" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G681" t="n">
-        <v>2.53890013694763</v>
+        <v>2.53889989852905</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G685" t="n">
-        <v>2.65091013908386</v>
+        <v>2.65091037750244</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G689" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G694" t="n">
-        <v>2.21220350265503</v>
+        <v>2.21220326423645</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>2.5</v>
       </c>
       <c r="G699" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G703" t="n">
-        <v>2.34288215637207</v>
+        <v>2.34288191795349</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G704" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G711" t="n">
-        <v>2.38955307006836</v>
+        <v>2.38955283164978</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G713" t="n">
-        <v>2.36155033111572</v>
+        <v>2.36155009269714</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>2.5</v>
       </c>
       <c r="G721" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G731" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G732" t="n">
-        <v>2.49222922325134</v>
+        <v>2.49222898483276</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G733" t="n">
-        <v>2.38955307006836</v>
+        <v>2.38955283164978</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G734" t="n">
-        <v>2.36155033111572</v>
+        <v>2.36155009269714</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G737" t="n">
-        <v>2.21220350265503</v>
+        <v>2.21220326423645</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G745" t="n">
-        <v>2.20286893844604</v>
+        <v>2.20286917686462</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G747" t="n">
-        <v>2.10952734947205</v>
+        <v>2.10952711105347</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G750" t="n">
-        <v>2.10952734947205</v>
+        <v>2.10952711105347</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G754" t="n">
-        <v>2.10952734947205</v>
+        <v>2.10952711105347</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G757" t="n">
-        <v>2.15619802474976</v>
+        <v>2.15619826316833</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G759" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G760" t="n">
-        <v>2.15619802474976</v>
+        <v>2.15619826316833</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G762" t="n">
-        <v>2.16553235054016</v>
+        <v>2.16553211212158</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G763" t="n">
-        <v>2.15619802474976</v>
+        <v>2.15619826316833</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G764" t="n">
-        <v>2.10952734947205</v>
+        <v>2.10952711105347</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G765" t="n">
-        <v>2.10952734947205</v>
+        <v>2.10952711105347</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G772" t="n">
-        <v>2.16553235054016</v>
+        <v>2.16553211212158</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G777" t="n">
-        <v>2.00685119628906</v>
+        <v>2.00685143470764</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G780" t="n">
-        <v>1.99751710891724</v>
+        <v>1.99751698970795</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G781" t="n">
-        <v>2.02551937103271</v>
+        <v>2.02551960945129</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G782" t="n">
-        <v>1.96018016338348</v>
+        <v>1.96018004417419</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G783" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417504310608</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>2</v>
       </c>
       <c r="G785" t="n">
-        <v>1.86683833599091</v>
+        <v>1.86683821678162</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>2</v>
       </c>
       <c r="G786" t="n">
-        <v>1.86683833599091</v>
+        <v>1.86683821678162</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G789" t="n">
-        <v>1.74549376964569</v>
+        <v>1.74549388885498</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>2</v>
       </c>
       <c r="G797" t="n">
-        <v>1.86683833599091</v>
+        <v>1.86683821678162</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>2</v>
       </c>
       <c r="G798" t="n">
-        <v>1.86683833599091</v>
+        <v>1.86683821678162</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>2</v>
       </c>
       <c r="G799" t="n">
-        <v>1.86683833599091</v>
+        <v>1.86683821678162</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>2</v>
       </c>
       <c r="G801" t="n">
-        <v>1.86683833599091</v>
+        <v>1.86683821678162</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>2</v>
       </c>
       <c r="G802" t="n">
-        <v>1.86683833599091</v>
+        <v>1.86683821678162</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>2</v>
       </c>
       <c r="G803" t="n">
-        <v>1.86683833599091</v>
+        <v>1.86683821678162</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417504310608</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G814" t="n">
-        <v>1.98818302154541</v>
+        <v>1.98818290233612</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G815" t="n">
-        <v>1.98818302154541</v>
+        <v>1.98818290233612</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G816" t="n">
-        <v>1.97884833812714</v>
+        <v>1.97884857654572</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G823" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417504310608</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G824" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417504310608</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>2</v>
       </c>
       <c r="G825" t="n">
-        <v>1.86683833599091</v>
+        <v>1.86683821678162</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G826" t="n">
-        <v>2.02551937103271</v>
+        <v>2.02551960945129</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G827" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417504310608</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G829" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417504310608</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>2</v>
       </c>
       <c r="G830" t="n">
-        <v>1.86683833599091</v>
+        <v>1.86683821678162</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G834" t="n">
-        <v>1.8108332157135</v>
+        <v>1.81083333492279</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G843" t="n">
-        <v>1.8108332157135</v>
+        <v>1.81083333492279</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>1.875</v>
       </c>
       <c r="G844" t="n">
-        <v>1.75016093254089</v>
+        <v>1.7501608133316</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G845" t="n">
-        <v>1.74549376964569</v>
+        <v>1.74549388885498</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G846" t="n">
-        <v>1.74549376964569</v>
+        <v>1.74549388885498</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G847" t="n">
-        <v>1.74549376964569</v>
+        <v>1.74549388885498</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G848" t="n">
-        <v>1.74549376964569</v>
+        <v>1.74549388885498</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G849" t="n">
-        <v>1.8108332157135</v>
+        <v>1.81083333492279</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G850" t="n">
-        <v>1.74549376964569</v>
+        <v>1.74549388885498</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>2</v>
       </c>
       <c r="G856" t="n">
-        <v>1.86683833599091</v>
+        <v>1.86683821678162</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G858" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417504310608</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G860" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417504310608</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>2</v>
       </c>
       <c r="G865" t="n">
-        <v>1.86683833599091</v>
+        <v>1.86683821678162</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>2</v>
       </c>
       <c r="G866" t="n">
-        <v>1.86683833599091</v>
+        <v>1.86683821678162</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>2</v>
       </c>
       <c r="G867" t="n">
-        <v>1.86683833599091</v>
+        <v>1.86683821678162</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G870" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417504310608</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>2</v>
       </c>
       <c r="G876" t="n">
-        <v>1.86683833599091</v>
+        <v>1.86683821678162</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417504310608</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G893" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417504310608</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G898" t="n">
-        <v>2.20286893844604</v>
+        <v>2.20286917686462</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G899" t="n">
-        <v>2.21220350265503</v>
+        <v>2.21220326423645</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G902" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G903" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G910" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G911" t="n">
-        <v>2.34288215637207</v>
+        <v>2.34288191795349</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G912" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G915" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G926" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G927" t="n">
-        <v>2.36155033111572</v>
+        <v>2.36155009269714</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>2.5</v>
       </c>
       <c r="G928" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G929" t="n">
-        <v>2.38955307006836</v>
+        <v>2.38955283164978</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G931" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G934" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G935" t="n">
-        <v>2.21220350265503</v>
+        <v>2.21220326423645</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G936" t="n">
-        <v>2.20286893844604</v>
+        <v>2.20286917686462</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G938" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>2.5</v>
       </c>
       <c r="G940" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>2.5</v>
       </c>
       <c r="G941" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>2.5</v>
       </c>
       <c r="G944" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>2.5</v>
       </c>
       <c r="G946" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G947" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G953" t="n">
-        <v>2.34288215637207</v>
+        <v>2.34288191795349</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G955" t="n">
-        <v>2.36155033111572</v>
+        <v>2.36155009269714</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G957" t="n">
-        <v>2.36155033111572</v>
+        <v>2.36155009269714</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>2.5</v>
       </c>
       <c r="G958" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>2.5</v>
       </c>
       <c r="G959" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>2.5</v>
       </c>
       <c r="G963" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G967" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G968" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G970" t="n">
-        <v>2.38955307006836</v>
+        <v>2.38955283164978</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G971" t="n">
-        <v>2.38955307006836</v>
+        <v>2.38955283164978</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G972" t="n">
-        <v>2.38955307006836</v>
+        <v>2.38955283164978</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G976" t="n">
-        <v>2.38955307006836</v>
+        <v>2.38955283164978</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G980" t="n">
-        <v>2.38955307006836</v>
+        <v>2.38955283164978</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G981" t="n">
-        <v>2.36155033111572</v>
+        <v>2.36155009269714</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G982" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G983" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G984" t="n">
-        <v>2.36155033111572</v>
+        <v>2.36155009269714</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G985" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G986" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G987" t="n">
-        <v>2.34288215637207</v>
+        <v>2.34288191795349</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>2.5</v>
       </c>
       <c r="G988" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>2.5</v>
       </c>
       <c r="G991" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>2.5</v>
       </c>
       <c r="G994" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G995" t="n">
-        <v>2.34288215637207</v>
+        <v>2.34288191795349</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>2.5</v>
       </c>
       <c r="G996" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G997" t="n">
-        <v>2.34288215637207</v>
+        <v>2.34288191795349</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>2.5</v>
       </c>
       <c r="G998" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>2.5</v>
       </c>
       <c r="G999" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>2.5</v>
       </c>
       <c r="G1000" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1001" t="n">
-        <v>2.38955307006836</v>
+        <v>2.38955283164978</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1003" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1004" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1007" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1008" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>2.5</v>
       </c>
       <c r="G1010" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1012" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1013" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1014" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1015" t="n">
-        <v>2.38955307006836</v>
+        <v>2.38955283164978</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1016" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1017" t="n">
-        <v>2.34288215637207</v>
+        <v>2.34288191795349</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1018" t="n">
-        <v>2.34288215637207</v>
+        <v>2.34288191795349</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1019" t="n">
-        <v>2.34288215637207</v>
+        <v>2.34288191795349</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1020" t="n">
-        <v>2.34288215637207</v>
+        <v>2.34288191795349</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1021" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>2.5</v>
       </c>
       <c r="G1022" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>2.5</v>
       </c>
       <c r="G1023" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>2.5</v>
       </c>
       <c r="G1025" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>2.5</v>
       </c>
       <c r="G1026" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>2.5</v>
       </c>
       <c r="G1027" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>2.5</v>
       </c>
       <c r="G1028" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>2.5</v>
       </c>
       <c r="G1029" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>2.5</v>
       </c>
       <c r="G1034" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1038" t="n">
-        <v>2.34288215637207</v>
+        <v>2.34288191795349</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1039" t="n">
-        <v>2.34288215637207</v>
+        <v>2.34288191795349</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>2.5</v>
       </c>
       <c r="G1040" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1041" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1042" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>2.5</v>
       </c>
       <c r="G1045" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1046" t="n">
-        <v>2.34288215637207</v>
+        <v>2.34288191795349</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>2.5</v>
       </c>
       <c r="G1051" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1052" t="n">
-        <v>2.36155033111572</v>
+        <v>2.36155009269714</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1053" t="n">
-        <v>2.34288215637207</v>
+        <v>2.34288191795349</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1054" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1055" t="n">
-        <v>2.38955307006836</v>
+        <v>2.38955283164978</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1057" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1058" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1059" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1060" t="n">
-        <v>2.38955307006836</v>
+        <v>2.38955283164978</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1072" t="n">
-        <v>2.65091013908386</v>
+        <v>2.65091037750244</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1081" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1082" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1083" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1086" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1087" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1089" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1090" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1092" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.62290787696838</v>
+        <v>2.6229076385498</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1096" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1097" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1098" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1099" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1100" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1101" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1102" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1103" t="n">
-        <v>2.58557081222534</v>
+        <v>2.58557105064392</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1121" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1122" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1123" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1124" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1126" t="n">
-        <v>2.753586769104</v>
+        <v>2.75358653068542</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1140" t="n">
-        <v>2.82825994491577</v>
+        <v>2.82826018333435</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1148" t="n">
-        <v>2.91226744651794</v>
+        <v>2.91226768493652</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1149" t="n">
-        <v>2.92160224914551</v>
+        <v>2.92160201072693</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1158" t="n">
-        <v>2.91226744651794</v>
+        <v>2.91226768493652</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1163" t="n">
-        <v>2.9682731628418</v>
+        <v>2.96827292442322</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.20162796974182</v>
+        <v>3.20162773132324</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.18295907974243</v>
+        <v>3.18295931816101</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.18295907974243</v>
+        <v>3.18295931816101</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.22962999343872</v>
+        <v>3.2296302318573</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.31363773345947</v>
+        <v>3.31363797187805</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.44431662559509</v>
+        <v>3.44431686401367</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1183" t="n">
-        <v>4.76043748855591</v>
+        <v>4.76043796539307</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G1187" t="n">
-        <v>4.63909292221069</v>
+        <v>4.63909339904785</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>5</v>
       </c>
       <c r="G1205" t="n">
-        <v>4.66709566116333</v>
+        <v>4.66709613800049</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1209" t="n">
-        <v>4.42440700531006</v>
+        <v>4.4244065284729</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1216" t="n">
-        <v>4.48974609375</v>
+        <v>4.48974657058716</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1217" t="n">
-        <v>4.48974609375</v>
+        <v>4.48974657058716</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1218" t="n">
-        <v>4.45240926742554</v>
+        <v>4.45240879058838</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1222" t="n">
-        <v>4.42440700531006</v>
+        <v>4.4244065284729</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1224" t="n">
-        <v>4.37773561477661</v>
+        <v>4.37773609161377</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1226" t="n">
-        <v>4.37773561477661</v>
+        <v>4.37773609161377</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1228" t="n">
-        <v>4.34973335266113</v>
+        <v>4.34973287582397</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1240" t="n">
-        <v>4.45240926742554</v>
+        <v>4.45240879058838</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1241" t="n">
-        <v>4.42440700531006</v>
+        <v>4.4244065284729</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.40573787689209</v>
+        <v>4.40573835372925</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1250" t="n">
-        <v>4.40573787689209</v>
+        <v>4.40573835372925</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1253" t="n">
-        <v>4.76043748855591</v>
+        <v>4.76043796539307</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1274" t="n">
-        <v>4.99078130722046</v>
+        <v>4.9907808303833</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1275" t="n">
-        <v>5.02917146682739</v>
+        <v>5.02917194366455</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1278" t="n">
-        <v>5.48985958099365</v>
+        <v>5.48985910415649</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1283" t="n">
-        <v>5.83537483215332</v>
+        <v>5.83537530899048</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1285" t="n">
-        <v>6.39203929901123</v>
+        <v>6.39203882217407</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1289" t="n">
-        <v>6.46882009506226</v>
+        <v>6.46882057189941</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G1293" t="n">
-        <v>6.1808910369873</v>
+        <v>6.18089056015015</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1294" t="n">
-        <v>6.12330532073975</v>
+        <v>6.12330484390259</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1296" t="n">
-        <v>6.39203929901123</v>
+        <v>6.39203882217407</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1297" t="n">
-        <v>6.48801612854004</v>
+        <v>6.48801565170288</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1298" t="n">
-        <v>6.48801612854004</v>
+        <v>6.48801565170288</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1303" t="n">
-        <v>6.48801612854004</v>
+        <v>6.48801565170288</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1311" t="n">
-        <v>5.93135118484497</v>
+        <v>5.93135166168213</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1313" t="n">
-        <v>5.93135118484497</v>
+        <v>5.93135166168213</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1316" t="n">
-        <v>5.93135118484497</v>
+        <v>5.93135166168213</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1330" t="n">
-        <v>5.68181276321411</v>
+        <v>5.68181228637695</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1333" t="n">
-        <v>5.66261720657349</v>
+        <v>5.66261768341064</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.56664085388184</v>
+        <v>5.56664133071899</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1335" t="n">
-        <v>5.48985958099365</v>
+        <v>5.48985910415649</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1337" t="n">
-        <v>5.56664085388184</v>
+        <v>5.56664133071899</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1338" t="n">
-        <v>5.56664085388184</v>
+        <v>5.56664133071899</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1341" t="n">
-        <v>5.66261720657349</v>
+        <v>5.66261768341064</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1342" t="n">
-        <v>5.66261720657349</v>
+        <v>5.66261768341064</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1346" t="n">
-        <v>5.56664085388184</v>
+        <v>5.56664133071899</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1350" t="n">
-        <v>5.93135118484497</v>
+        <v>5.93135166168213</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1351" t="n">
-        <v>5.93135118484497</v>
+        <v>5.93135166168213</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1352" t="n">
-        <v>5.93135118484497</v>
+        <v>5.93135166168213</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1353" t="n">
-        <v>6.12330532073975</v>
+        <v>6.12330484390259</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1356" t="n">
-        <v>5.87376546859741</v>
+        <v>5.87376594543457</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1363" t="n">
-        <v>5.96974182128906</v>
+        <v>5.96974229812622</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1367" t="n">
-        <v>5.96974182128906</v>
+        <v>5.96974229812622</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1368" t="n">
-        <v>5.83537483215332</v>
+        <v>5.83537530899048</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1370" t="n">
-        <v>5.96974182128906</v>
+        <v>5.96974229812622</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1371" t="n">
-        <v>5.87376546859741</v>
+        <v>5.87376594543457</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1373" t="n">
-        <v>6.08491468429565</v>
+        <v>6.0849142074585</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1375" t="n">
-        <v>5.87376546859741</v>
+        <v>5.87376594543457</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1384" t="n">
-        <v>5.87376546859741</v>
+        <v>5.87376594543457</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1385" t="n">
-        <v>5.96974182128906</v>
+        <v>5.96974229812622</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1386" t="n">
-        <v>5.96974182128906</v>
+        <v>5.96974229812622</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1387" t="n">
-        <v>5.96974182128906</v>
+        <v>5.96974229812622</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1388" t="n">
-        <v>5.93135118484497</v>
+        <v>5.93135166168213</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1390" t="n">
-        <v>5.93135118484497</v>
+        <v>5.93135166168213</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1392" t="n">
-        <v>5.93135118484497</v>
+        <v>5.93135166168213</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1393" t="n">
-        <v>5.87376546859741</v>
+        <v>5.87376594543457</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1404" t="n">
-        <v>6.08491468429565</v>
+        <v>6.0849142074585</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1406" t="n">
-        <v>6.12330532073975</v>
+        <v>6.12330484390259</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1417" t="n">
-        <v>7.02548503875732</v>
+        <v>7.02548456192017</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1430" t="n">
-        <v>7.02548503875732</v>
+        <v>7.02548456192017</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1432" t="n">
-        <v>7.02548503875732</v>
+        <v>7.02548456192017</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1440" t="n">
-        <v>7.06387519836426</v>
+        <v>7.06387567520142</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G1442" t="n">
-        <v>7.12146139144897</v>
+        <v>7.12146091461182</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1446" t="n">
-        <v>7.06387519836426</v>
+        <v>7.06387567520142</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1448" t="n">
-        <v>7.06387519836426</v>
+        <v>7.06387567520142</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1449" t="n">
-        <v>6.91031265258789</v>
+        <v>6.91031217575073</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1450" t="n">
-        <v>7.02548503875732</v>
+        <v>7.02548456192017</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1454" t="n">
-        <v>7.06387519836426</v>
+        <v>7.06387567520142</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1459" t="n">
-        <v>6.91031265258789</v>
+        <v>6.91031217575073</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1461" t="n">
-        <v>6.91031265258789</v>
+        <v>6.91031217575073</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1462" t="n">
-        <v>7.06387519836426</v>
+        <v>7.06387567520142</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1466" t="n">
-        <v>7.02548503875732</v>
+        <v>7.02548456192017</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1476" t="n">
-        <v>6.91031265258789</v>
+        <v>6.91031217575073</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1477" t="n">
-        <v>6.89111757278442</v>
+        <v>6.89111709594727</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1479" t="n">
-        <v>6.91031265258789</v>
+        <v>6.91031217575073</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1480" t="n">
-        <v>6.77594518661499</v>
+        <v>6.77594566345215</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1481" t="n">
-        <v>6.98709440231323</v>
+        <v>6.98709392547607</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1482" t="n">
-        <v>6.89111757278442</v>
+        <v>6.89111709594727</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G1484" t="n">
-        <v>6.79514026641846</v>
+        <v>6.79514074325562</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1485" t="n">
-        <v>6.81433629989624</v>
+        <v>6.81433582305908</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1486" t="n">
-        <v>6.91031265258789</v>
+        <v>6.91031217575073</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1487" t="n">
-        <v>6.91031265258789</v>
+        <v>6.91031217575073</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1488" t="n">
-        <v>6.98709440231323</v>
+        <v>6.98709392547607</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1495" t="n">
-        <v>7.29421901702881</v>
+        <v>7.29421854019165</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1496" t="n">
-        <v>7.42858552932739</v>
+        <v>7.42858600616455</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1498" t="n">
-        <v>7.54375791549683</v>
+        <v>7.54375839233398</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -48446,6 +48446,32 @@
         <v>16.6499996185303</v>
       </c>
       <c r="H1849" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1850">
+      <c r="A1850" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1850" t="n">
+        <v>9156</v>
+      </c>
+      <c r="C1850" t="n">
+        <v>17.1000003814697</v>
+      </c>
+      <c r="D1850" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="E1850" t="n">
+        <v>16.6000003814697</v>
+      </c>
+      <c r="F1850" t="n">
+        <v>17.1499996185303</v>
+      </c>
+      <c r="G1850" t="n">
+        <v>17.1499996185303</v>
+      </c>
+      <c r="H1850" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IEG.MI.xlsx
+++ b/data/IEG.MI.xlsx
@@ -447,7 +447,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G3" t="n">
-        <v>3.49098777770996</v>
+        <v>3.49098753929138</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.73099994659424</v>
       </c>
       <c r="G4" t="n">
-        <v>3.48258662223816</v>
+        <v>3.48258686065674</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G5" t="n">
-        <v>3.52832412719727</v>
+        <v>3.52832436561584</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G7" t="n">
-        <v>3.45365071296692</v>
+        <v>3.4536509513855</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>3.40697979927063</v>
+        <v>3.40698003768921</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.67050004005432</v>
       </c>
       <c r="G9" t="n">
-        <v>3.42611503601074</v>
+        <v>3.42611479759216</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G10" t="n">
-        <v>3.45365071296692</v>
+        <v>3.4536509513855</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G11" t="n">
-        <v>3.45365071296692</v>
+        <v>3.4536509513855</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G12" t="n">
-        <v>3.43498253822327</v>
+        <v>3.43498277664185</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G14" t="n">
-        <v>3.31363797187805</v>
+        <v>3.31363773345947</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G15" t="n">
-        <v>3.42564821243286</v>
+        <v>3.42564845085144</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G16" t="n">
-        <v>3.36030888557434</v>
+        <v>3.36030864715576</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G19" t="n">
-        <v>3.69634008407593</v>
+        <v>3.69633960723877</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G20" t="n">
-        <v>3.7803475856781</v>
+        <v>3.78034782409668</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G21" t="n">
-        <v>3.80835008621216</v>
+        <v>3.80835032463074</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G22" t="n">
-        <v>3.7803475856781</v>
+        <v>3.78034782409668</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G24" t="n">
-        <v>3.85502123832703</v>
+        <v>3.85502099990845</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G25" t="n">
-        <v>3.81768465042114</v>
+        <v>3.81768441200256</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G26" t="n">
-        <v>3.91102600097656</v>
+        <v>3.91102623939514</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G28" t="n">
-        <v>3.95769715309143</v>
+        <v>3.95769739151001</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G29" t="n">
-        <v>3.97636580467224</v>
+        <v>3.97636556625366</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G30" t="n">
-        <v>4.05103921890259</v>
+        <v>4.05103969573975</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G31" t="n">
-        <v>4.03237056732178</v>
+        <v>4.03237104415894</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G32" t="n">
-        <v>3.93902850151062</v>
+        <v>3.9390287399292</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G38" t="n">
-        <v>3.95769715309143</v>
+        <v>3.95769739151001</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G39" t="n">
-        <v>3.88302326202393</v>
+        <v>3.8830235004425</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G40" t="n">
-        <v>3.88302326202393</v>
+        <v>3.8830235004425</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G41" t="n">
-        <v>3.95769715309143</v>
+        <v>3.95769739151001</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G42" t="n">
-        <v>3.95769715309143</v>
+        <v>3.95769739151001</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G45" t="n">
-        <v>3.91102600097656</v>
+        <v>3.91102623939514</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G47" t="n">
-        <v>3.85502123832703</v>
+        <v>3.85502099990845</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G49" t="n">
-        <v>3.91102600097656</v>
+        <v>3.91102623939514</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G51" t="n">
-        <v>3.64033484458923</v>
+        <v>3.64033460617065</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G52" t="n">
-        <v>3.59366369247437</v>
+        <v>3.59366345405579</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G53" t="n">
-        <v>3.63100051879883</v>
+        <v>3.63100075721741</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G54" t="n">
-        <v>3.53765845298767</v>
+        <v>3.53765869140625</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G55" t="n">
-        <v>3.42564821243286</v>
+        <v>3.42564845085144</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G56" t="n">
-        <v>3.40697979927063</v>
+        <v>3.40698003768921</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G57" t="n">
-        <v>3.45365071296692</v>
+        <v>3.4536509513855</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G58" t="n">
-        <v>3.45365071296692</v>
+        <v>3.4536509513855</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>3.59366369247437</v>
+        <v>3.59366345405579</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G63" t="n">
-        <v>3.60299754142761</v>
+        <v>3.60299777984619</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G64" t="n">
-        <v>3.56566119194031</v>
+        <v>3.56566095352173</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G65" t="n">
-        <v>3.58432936668396</v>
+        <v>3.58432960510254</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G66" t="n">
-        <v>3.59366369247437</v>
+        <v>3.59366345405579</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G68" t="n">
-        <v>3.69634008407593</v>
+        <v>3.69633960723877</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G70" t="n">
-        <v>3.60299754142761</v>
+        <v>3.60299777984619</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G71" t="n">
-        <v>3.59366369247437</v>
+        <v>3.59366345405579</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G72" t="n">
-        <v>3.53765845298767</v>
+        <v>3.53765869140625</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G73" t="n">
-        <v>3.53765845298767</v>
+        <v>3.53765869140625</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G74" t="n">
-        <v>3.53765845298767</v>
+        <v>3.53765869140625</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>3.54699301719666</v>
+        <v>3.5469925403595</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G76" t="n">
-        <v>3.54699301719666</v>
+        <v>3.5469925403595</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>3.54699301719666</v>
+        <v>3.5469925403595</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G78" t="n">
-        <v>3.62166666984558</v>
+        <v>3.621666431427</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G79" t="n">
-        <v>3.56566119194031</v>
+        <v>3.56566095352173</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G80" t="n">
-        <v>3.59366369247437</v>
+        <v>3.59366345405579</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G81" t="n">
-        <v>3.59366369247437</v>
+        <v>3.59366345405579</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G82" t="n">
-        <v>3.59366369247437</v>
+        <v>3.59366345405579</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G85" t="n">
-        <v>3.56566119194031</v>
+        <v>3.56566095352173</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>3.57499504089355</v>
+        <v>3.57499527931213</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G87" t="n">
-        <v>3.63100051879883</v>
+        <v>3.63100075721741</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G88" t="n">
-        <v>3.62166666984558</v>
+        <v>3.621666431427</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>3.59366369247437</v>
+        <v>3.59366345405579</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G92" t="n">
-        <v>3.54699301719666</v>
+        <v>3.5469925403595</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G93" t="n">
-        <v>3.58432936668396</v>
+        <v>3.58432960510254</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G94" t="n">
-        <v>3.62166666984558</v>
+        <v>3.621666431427</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>3.69634008407593</v>
+        <v>3.69633960723877</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G101" t="n">
-        <v>3.69634008407593</v>
+        <v>3.69633960723877</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G102" t="n">
-        <v>3.64033484458923</v>
+        <v>3.64033460617065</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G103" t="n">
-        <v>3.64033484458923</v>
+        <v>3.64033460617065</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>3.64033484458923</v>
+        <v>3.64033460617065</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G108" t="n">
-        <v>3.81768465042114</v>
+        <v>3.81768441200256</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G110" t="n">
-        <v>3.81768465042114</v>
+        <v>3.81768441200256</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>3.80835008621216</v>
+        <v>3.80835032463074</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G112" t="n">
-        <v>3.80835008621216</v>
+        <v>3.80835032463074</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>3.7803475856781</v>
+        <v>3.78034782409668</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G122" t="n">
-        <v>3.86435508728027</v>
+        <v>3.86435484886169</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G123" t="n">
-        <v>3.85502123832703</v>
+        <v>3.85502099990845</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G124" t="n">
-        <v>3.86435508728027</v>
+        <v>3.86435484886169</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G126" t="n">
-        <v>3.80835008621216</v>
+        <v>3.80835032463074</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G129" t="n">
-        <v>3.7803475856781</v>
+        <v>3.78034782409668</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G130" t="n">
-        <v>3.7430112361908</v>
+        <v>3.74301099777222</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G137" t="n">
-        <v>3.92969465255737</v>
+        <v>3.92969489097595</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G140" t="n">
-        <v>3.93902850151062</v>
+        <v>3.9390287399292</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G144" t="n">
-        <v>3.93902850151062</v>
+        <v>3.9390287399292</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G145" t="n">
-        <v>3.89235806465149</v>
+        <v>3.89235758781433</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G148" t="n">
-        <v>3.95769715309143</v>
+        <v>3.95769739151001</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G149" t="n">
-        <v>4.0417046546936</v>
+        <v>4.04170513153076</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G151" t="n">
-        <v>4.25639152526855</v>
+        <v>4.2563910484314</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G154" t="n">
-        <v>4.35906744003296</v>
+        <v>4.3590669631958</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G156" t="n">
-        <v>4.46174383163452</v>
+        <v>4.46174335479736</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G158" t="n">
-        <v>4.26572561264038</v>
+        <v>4.26572513580322</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G159" t="n">
-        <v>4.1910514831543</v>
+        <v>4.19105195999146</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G163" t="n">
-        <v>4.16304969787598</v>
+        <v>4.16304922103882</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G164" t="n">
-        <v>4.06970739364624</v>
+        <v>4.0697078704834</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G165" t="n">
-        <v>4.10704469680786</v>
+        <v>4.1070442199707</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G166" t="n">
-        <v>4.16304969787598</v>
+        <v>4.16304922103882</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G167" t="n">
-        <v>4.12571287155151</v>
+        <v>4.12571239471436</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>4.05103921890259</v>
+        <v>4.05103969573975</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G172" t="n">
-        <v>4.28439426422119</v>
+        <v>4.28439378738403</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G174" t="n">
-        <v>3.59366369247437</v>
+        <v>3.59366345405579</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G175" t="n">
-        <v>3.49098777770996</v>
+        <v>3.49098753929138</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G179" t="n">
-        <v>3.45365071296692</v>
+        <v>3.4536509513855</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G180" t="n">
-        <v>3.56566119194031</v>
+        <v>3.56566095352173</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G181" t="n">
-        <v>3.51899027824402</v>
+        <v>3.51899003982544</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14562225341797</v>
+        <v>3.14562249183655</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G198" t="n">
-        <v>2.45489263534546</v>
+        <v>2.45489239692688</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>2.5</v>
       </c>
       <c r="G199" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G201" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>2.5</v>
       </c>
       <c r="G202" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G203" t="n">
-        <v>2.34288191795349</v>
+        <v>2.34288215637207</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G204" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G206" t="n">
-        <v>2.95893883705139</v>
+        <v>2.95893859863281</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G211" t="n">
-        <v>2.77225494384766</v>
+        <v>2.77225470542908</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>2.76292085647583</v>
+        <v>2.76292037963867</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G220" t="n">
-        <v>2.85626244544983</v>
+        <v>2.85626268386841</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G225" t="n">
-        <v>2.73491811752319</v>
+        <v>2.73491835594177</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G230" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>2.76292085647583</v>
+        <v>2.76292037963867</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G235" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G238" t="n">
-        <v>2.85626244544983</v>
+        <v>2.85626268386841</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G239" t="n">
-        <v>2.85626244544983</v>
+        <v>2.85626268386841</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G240" t="n">
-        <v>2.82826018333435</v>
+        <v>2.82825994491577</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G245" t="n">
-        <v>2.82826018333435</v>
+        <v>2.82825994491577</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G248" t="n">
-        <v>2.97760725021362</v>
+        <v>2.97760701179504</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G249" t="n">
-        <v>2.88426494598389</v>
+        <v>2.88426518440247</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G251" t="n">
-        <v>2.78158926963806</v>
+        <v>2.78158903121948</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G253" t="n">
-        <v>2.82826018333435</v>
+        <v>2.82825994491577</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G254" t="n">
-        <v>2.82826018333435</v>
+        <v>2.82825994491577</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G257" t="n">
-        <v>2.78158926963806</v>
+        <v>2.78158903121948</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G267" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G268" t="n">
-        <v>2.63224196434021</v>
+        <v>2.63224172592163</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G271" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G273" t="n">
-        <v>2.52956604957581</v>
+        <v>2.52956581115723</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G276" t="n">
-        <v>2.49222898483276</v>
+        <v>2.49222922325134</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G280" t="n">
-        <v>2.52956604957581</v>
+        <v>2.52956581115723</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G282" t="n">
-        <v>2.48289513587952</v>
+        <v>2.48289489746094</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G284" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G285" t="n">
-        <v>2.40822148323059</v>
+        <v>2.40822124481201</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G286" t="n">
-        <v>2.40822148323059</v>
+        <v>2.40822124481201</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.5</v>
       </c>
       <c r="G289" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G290" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G293" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G294" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G295" t="n">
-        <v>2.54823422431946</v>
+        <v>2.54823446273804</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G297" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G298" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G303" t="n">
-        <v>2.49222898483276</v>
+        <v>2.49222922325134</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G304" t="n">
-        <v>2.49222898483276</v>
+        <v>2.49222922325134</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G305" t="n">
-        <v>2.49222898483276</v>
+        <v>2.49222922325134</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G307" t="n">
-        <v>2.50156331062317</v>
+        <v>2.50156354904175</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G308" t="n">
-        <v>2.46422648429871</v>
+        <v>2.46422672271729</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G309" t="n">
-        <v>2.45489263534546</v>
+        <v>2.45489239692688</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G311" t="n">
-        <v>2.48289513587952</v>
+        <v>2.48289489746094</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G312" t="n">
-        <v>2.48289513587952</v>
+        <v>2.48289489746094</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G313" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G315" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G316" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G319" t="n">
-        <v>2.40822148323059</v>
+        <v>2.40822124481201</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G320" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G321" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G324" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G325" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G326" t="n">
-        <v>2.36155009269714</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.5</v>
       </c>
       <c r="G328" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G329" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G330" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G331" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G332" t="n">
-        <v>2.27754282951355</v>
+        <v>2.27754259109497</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.5</v>
       </c>
       <c r="G333" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G334" t="n">
-        <v>2.24020576477051</v>
+        <v>2.24020600318909</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G336" t="n">
-        <v>2.26820850372314</v>
+        <v>2.26820874214172</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G337" t="n">
-        <v>2.24020576477051</v>
+        <v>2.24020600318909</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G339" t="n">
-        <v>2.12819576263428</v>
+        <v>2.1281955242157</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>2.06285643577576</v>
+        <v>2.06285619735718</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G343" t="n">
-        <v>1.98818290233612</v>
+        <v>1.98818278312683</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G348" t="n">
-        <v>1.76416206359863</v>
+        <v>1.76416218280792</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G350" t="n">
-        <v>1.68015444278717</v>
+        <v>1.68015432357788</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G351" t="n">
-        <v>1.57747840881348</v>
+        <v>1.57747828960419</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G358" t="n">
-        <v>1.53547441959381</v>
+        <v>1.5354745388031</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G363" t="n">
-        <v>1.84817004203796</v>
+        <v>1.84816980361938</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G365" t="n">
-        <v>1.94151163101196</v>
+        <v>1.94151175022125</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G366" t="n">
-        <v>2.02551960945129</v>
+        <v>2.02551984786987</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G367" t="n">
-        <v>2.06285643577576</v>
+        <v>2.06285619735718</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G369" t="n">
-        <v>2.12819576263428</v>
+        <v>2.1281955242157</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G372" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G373" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G374" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G376" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G377" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G378" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G381" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G382" t="n">
-        <v>2.50156331062317</v>
+        <v>2.50156354904175</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G383" t="n">
-        <v>2.40822148323059</v>
+        <v>2.40822124481201</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G384" t="n">
-        <v>2.36155009269714</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G385" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.5</v>
       </c>
       <c r="G386" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G387" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G390" t="n">
-        <v>2.49222898483276</v>
+        <v>2.49222922325134</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G393" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G396" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G397" t="n">
-        <v>2.27754282951355</v>
+        <v>2.27754259109497</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G402" t="n">
-        <v>2.21220326423645</v>
+        <v>2.21220350265503</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G403" t="n">
-        <v>2.17486643791199</v>
+        <v>2.17486667633057</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G404" t="n">
-        <v>2.17486643791199</v>
+        <v>2.17486667633057</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G406" t="n">
-        <v>2.05352234840393</v>
+        <v>2.05352210998535</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G410" t="n">
-        <v>2.05352234840393</v>
+        <v>2.05352210998535</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G411" t="n">
-        <v>2.05352234840393</v>
+        <v>2.05352210998535</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G412" t="n">
-        <v>2.05352234840393</v>
+        <v>2.05352210998535</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G413" t="n">
-        <v>2.05352234840393</v>
+        <v>2.05352210998535</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G414" t="n">
-        <v>2.08152484893799</v>
+        <v>2.08152461051941</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G417" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G418" t="n">
-        <v>2.40822148323059</v>
+        <v>2.40822124481201</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G419" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G421" t="n">
-        <v>2.34288191795349</v>
+        <v>2.34288215637207</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G422" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G426" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G427" t="n">
-        <v>2.26820850372314</v>
+        <v>2.26820874214172</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G428" t="n">
-        <v>2.27754282951355</v>
+        <v>2.27754259109497</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G429" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G430" t="n">
-        <v>2.2588746547699</v>
+        <v>2.25887441635132</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G431" t="n">
-        <v>2.2588746547699</v>
+        <v>2.25887441635132</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G432" t="n">
-        <v>2.27754282951355</v>
+        <v>2.27754259109497</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G433" t="n">
-        <v>2.2588746547699</v>
+        <v>2.25887441635132</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G434" t="n">
-        <v>2.24020576477051</v>
+        <v>2.24020600318909</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G435" t="n">
-        <v>2.24954032897949</v>
+        <v>2.24954009056091</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G436" t="n">
-        <v>2.27754282951355</v>
+        <v>2.27754259109497</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G438" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G439" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>2.5</v>
       </c>
       <c r="G440" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G441" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>2.5</v>
       </c>
       <c r="G442" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G443" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G444" t="n">
-        <v>2.24954032897949</v>
+        <v>2.24954009056091</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G445" t="n">
-        <v>2.23087191581726</v>
+        <v>2.23087167739868</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G446" t="n">
-        <v>2.23087191581726</v>
+        <v>2.23087167739868</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G447" t="n">
-        <v>2.27754282951355</v>
+        <v>2.27754259109497</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G448" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G461" t="n">
-        <v>2.73491811752319</v>
+        <v>2.73491835594177</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G468" t="n">
-        <v>3.08028292655945</v>
+        <v>3.08028316497803</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G471" t="n">
-        <v>3.27630090713501</v>
+        <v>3.27630138397217</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G477" t="n">
-        <v>3.11761999130249</v>
+        <v>3.11761975288391</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G479" t="n">
-        <v>3.16429114341736</v>
+        <v>3.16429090499878</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G481" t="n">
-        <v>3.14562225341797</v>
+        <v>3.14562249183655</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G483" t="n">
-        <v>3.12695407867432</v>
+        <v>3.12695384025574</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G485" t="n">
-        <v>3.15495681762695</v>
+        <v>3.15495657920837</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G488" t="n">
-        <v>3.16429114341736</v>
+        <v>3.16429090499878</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G489" t="n">
-        <v>3.11761999130249</v>
+        <v>3.11761975288391</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G490" t="n">
-        <v>3.08028292655945</v>
+        <v>3.08028316497803</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G492" t="n">
-        <v>2.97760725021362</v>
+        <v>2.97760701179504</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G493" t="n">
-        <v>3.04294633865356</v>
+        <v>3.04294657707214</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G496" t="n">
-        <v>3.08028292655945</v>
+        <v>3.08028316497803</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G497" t="n">
-        <v>3.08028292655945</v>
+        <v>3.08028316497803</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G498" t="n">
-        <v>3.07094883918762</v>
+        <v>3.0709490776062</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G499" t="n">
-        <v>3.11761999130249</v>
+        <v>3.11761975288391</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G500" t="n">
-        <v>3.11761999130249</v>
+        <v>3.11761975288391</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G504" t="n">
-        <v>3.02427816390991</v>
+        <v>3.02427792549133</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G506" t="n">
-        <v>2.95893883705139</v>
+        <v>2.95893859863281</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G511" t="n">
-        <v>2.74425220489502</v>
+        <v>2.7442524433136</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G514" t="n">
-        <v>2.78158926963806</v>
+        <v>2.78158903121948</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G516" t="n">
-        <v>2.74425220489502</v>
+        <v>2.7442524433136</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G518" t="n">
-        <v>2.73491811752319</v>
+        <v>2.73491835594177</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G519" t="n">
-        <v>2.74425220489502</v>
+        <v>2.7442524433136</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G520" t="n">
-        <v>2.74425220489502</v>
+        <v>2.7442524433136</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G524" t="n">
-        <v>2.63224196434021</v>
+        <v>2.63224172592163</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G528" t="n">
-        <v>2.49222898483276</v>
+        <v>2.49222922325134</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G529" t="n">
-        <v>2.46422648429871</v>
+        <v>2.46422672271729</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G530" t="n">
-        <v>2.49222898483276</v>
+        <v>2.49222922325134</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G531" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G532" t="n">
-        <v>2.46422648429871</v>
+        <v>2.46422672271729</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G533" t="n">
-        <v>2.45489263534546</v>
+        <v>2.45489239692688</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G535" t="n">
-        <v>2.53889989852905</v>
+        <v>2.53890013694763</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G536" t="n">
-        <v>2.52956604957581</v>
+        <v>2.52956581115723</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G541" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G542" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G543" t="n">
-        <v>2.63224196434021</v>
+        <v>2.63224172592163</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G544" t="n">
-        <v>2.54823422431946</v>
+        <v>2.54823446273804</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G556" t="n">
-        <v>2.77225494384766</v>
+        <v>2.77225470542908</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G557" t="n">
-        <v>2.77225494384766</v>
+        <v>2.77225470542908</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G565" t="n">
-        <v>2.78158926963806</v>
+        <v>2.78158903121948</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G566" t="n">
-        <v>2.86559677124023</v>
+        <v>2.86559653282166</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G568" t="n">
-        <v>2.78158926963806</v>
+        <v>2.78158903121948</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G570" t="n">
-        <v>2.77225494384766</v>
+        <v>2.77225470542908</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G571" t="n">
-        <v>2.82826018333435</v>
+        <v>2.82825994491577</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G576" t="n">
-        <v>2.74425220489502</v>
+        <v>2.7442524433136</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G578" t="n">
-        <v>2.82826018333435</v>
+        <v>2.82825994491577</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G579" t="n">
-        <v>2.78158926963806</v>
+        <v>2.78158903121948</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G581" t="n">
-        <v>2.77225494384766</v>
+        <v>2.77225470542908</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G583" t="n">
-        <v>2.76292085647583</v>
+        <v>2.76292037963867</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G584" t="n">
-        <v>2.78158926963806</v>
+        <v>2.78158903121948</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G585" t="n">
-        <v>2.78158926963806</v>
+        <v>2.78158903121948</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G591" t="n">
-        <v>2.77225494384766</v>
+        <v>2.77225470542908</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G592" t="n">
-        <v>2.77225494384766</v>
+        <v>2.77225470542908</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G596" t="n">
-        <v>2.77225494384766</v>
+        <v>2.77225470542908</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G599" t="n">
-        <v>2.74425220489502</v>
+        <v>2.7442524433136</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G603" t="n">
-        <v>2.73491811752319</v>
+        <v>2.73491835594177</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G607" t="n">
-        <v>2.74425220489502</v>
+        <v>2.7442524433136</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G608" t="n">
-        <v>2.78158926963806</v>
+        <v>2.78158903121948</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G609" t="n">
-        <v>2.76292085647583</v>
+        <v>2.76292037963867</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G610" t="n">
-        <v>2.77225494384766</v>
+        <v>2.77225470542908</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G611" t="n">
-        <v>2.82826018333435</v>
+        <v>2.82825994491577</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G613" t="n">
-        <v>2.82826018333435</v>
+        <v>2.82825994491577</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G614" t="n">
-        <v>2.77225494384766</v>
+        <v>2.77225470542908</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G615" t="n">
-        <v>2.78158926963806</v>
+        <v>2.78158903121948</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G620" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G621" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G622" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G625" t="n">
-        <v>2.48289513587952</v>
+        <v>2.48289489746094</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G626" t="n">
-        <v>2.50156331062317</v>
+        <v>2.50156354904175</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G627" t="n">
-        <v>2.48289513587952</v>
+        <v>2.48289489746094</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G630" t="n">
-        <v>2.52956604957581</v>
+        <v>2.52956581115723</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G634" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G637" t="n">
-        <v>2.53889989852905</v>
+        <v>2.53890013694763</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G638" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G639" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G640" t="n">
-        <v>2.49222898483276</v>
+        <v>2.49222922325134</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G644" t="n">
-        <v>2.50156331062317</v>
+        <v>2.50156354904175</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G645" t="n">
-        <v>2.40822148323059</v>
+        <v>2.40822124481201</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G646" t="n">
-        <v>2.49222898483276</v>
+        <v>2.49222922325134</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G647" t="n">
-        <v>2.49222898483276</v>
+        <v>2.49222922325134</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G648" t="n">
-        <v>2.53889989852905</v>
+        <v>2.53890013694763</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G649" t="n">
-        <v>2.53889989852905</v>
+        <v>2.53890013694763</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G651" t="n">
-        <v>2.54823422431946</v>
+        <v>2.54823446273804</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G652" t="n">
-        <v>2.52956604957581</v>
+        <v>2.52956581115723</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G653" t="n">
-        <v>2.52956604957581</v>
+        <v>2.52956581115723</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G654" t="n">
-        <v>2.50156331062317</v>
+        <v>2.50156354904175</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>2.52956604957581</v>
+        <v>2.52956581115723</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G657" t="n">
-        <v>2.53889989852905</v>
+        <v>2.53890013694763</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G658" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G662" t="n">
-        <v>2.53889989852905</v>
+        <v>2.53890013694763</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G665" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G669" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G670" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G671" t="n">
-        <v>2.52956604957581</v>
+        <v>2.52956581115723</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G674" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G675" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G677" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G681" t="n">
-        <v>2.53889989852905</v>
+        <v>2.53890013694763</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G686" t="n">
-        <v>2.48289513587952</v>
+        <v>2.48289489746094</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G688" t="n">
-        <v>2.50156331062317</v>
+        <v>2.50156354904175</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G694" t="n">
-        <v>2.21220326423645</v>
+        <v>2.21220350265503</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G695" t="n">
-        <v>2.23087191581726</v>
+        <v>2.23087167739868</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G697" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G698" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>2.5</v>
       </c>
       <c r="G699" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G700" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G701" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G702" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G703" t="n">
-        <v>2.34288191795349</v>
+        <v>2.34288215637207</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G704" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G705" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G706" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G708" t="n">
-        <v>2.40822148323059</v>
+        <v>2.40822124481201</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G711" t="n">
-        <v>2.38955283164978</v>
+        <v>2.38955307006836</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G713" t="n">
-        <v>2.36155009269714</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G714" t="n">
-        <v>2.40822148323059</v>
+        <v>2.40822124481201</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G720" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>2.5</v>
       </c>
       <c r="G721" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G722" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G724" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G725" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G726" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G727" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G728" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G730" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G731" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G732" t="n">
-        <v>2.49222898483276</v>
+        <v>2.49222922325134</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G733" t="n">
-        <v>2.38955283164978</v>
+        <v>2.38955307006836</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G734" t="n">
-        <v>2.36155009269714</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G736" t="n">
-        <v>2.24020576477051</v>
+        <v>2.24020600318909</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G737" t="n">
-        <v>2.21220326423645</v>
+        <v>2.21220350265503</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G739" t="n">
-        <v>2.23087191581726</v>
+        <v>2.23087167739868</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G742" t="n">
-        <v>2.23087191581726</v>
+        <v>2.23087167739868</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G747" t="n">
-        <v>2.10952711105347</v>
+        <v>2.10952734947205</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G748" t="n">
-        <v>2.12819576263428</v>
+        <v>2.1281955242157</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G749" t="n">
-        <v>2.12819576263428</v>
+        <v>2.1281955242157</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G750" t="n">
-        <v>2.10952711105347</v>
+        <v>2.10952734947205</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G754" t="n">
-        <v>2.10952711105347</v>
+        <v>2.10952734947205</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G758" t="n">
-        <v>2.24020576477051</v>
+        <v>2.24020600318909</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G762" t="n">
-        <v>2.16553211212158</v>
+        <v>2.16553235054016</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G764" t="n">
-        <v>2.10952711105347</v>
+        <v>2.10952734947205</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G765" t="n">
-        <v>2.10952711105347</v>
+        <v>2.10952734947205</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G769" t="n">
-        <v>2.08152484893799</v>
+        <v>2.08152461051941</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G770" t="n">
-        <v>2.08152484893799</v>
+        <v>2.08152461051941</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G772" t="n">
-        <v>2.16553211212158</v>
+        <v>2.16553235054016</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G778" t="n">
-        <v>2.01618528366089</v>
+        <v>2.01618552207947</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G779" t="n">
-        <v>2.01618528366089</v>
+        <v>2.01618552207947</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G781" t="n">
-        <v>2.02551960945129</v>
+        <v>2.02551984786987</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G783" t="n">
-        <v>1.90417504310608</v>
+        <v>1.90417516231537</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>2</v>
       </c>
       <c r="G785" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>2</v>
       </c>
       <c r="G786" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G787" t="n">
-        <v>1.76416206359863</v>
+        <v>1.76416218280792</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G788" t="n">
-        <v>1.76882922649384</v>
+        <v>1.76882934570312</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G789" t="n">
-        <v>1.74549388885498</v>
+        <v>1.74549376964569</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G793" t="n">
-        <v>1.79216468334198</v>
+        <v>1.79216480255127</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G795" t="n">
-        <v>1.84817004203796</v>
+        <v>1.84816980361938</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>2</v>
       </c>
       <c r="G797" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>2</v>
       </c>
       <c r="G798" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>2</v>
       </c>
       <c r="G799" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G800" t="n">
-        <v>1.82016742229462</v>
+        <v>1.82016730308533</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>2</v>
       </c>
       <c r="G801" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>2</v>
       </c>
       <c r="G802" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>2</v>
       </c>
       <c r="G803" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>1.90417504310608</v>
+        <v>1.90417516231537</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G807" t="n">
-        <v>1.88550662994385</v>
+        <v>1.88550674915314</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G814" t="n">
-        <v>1.98818290233612</v>
+        <v>1.98818278312683</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G815" t="n">
-        <v>1.98818290233612</v>
+        <v>1.98818278312683</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G816" t="n">
-        <v>1.97884857654572</v>
+        <v>1.978848695755</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G819" t="n">
-        <v>1.94151163101196</v>
+        <v>1.94151175022125</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G823" t="n">
-        <v>1.90417504310608</v>
+        <v>1.90417516231537</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G824" t="n">
-        <v>1.90417504310608</v>
+        <v>1.90417516231537</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>2</v>
       </c>
       <c r="G825" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G826" t="n">
-        <v>2.02551960945129</v>
+        <v>2.02551984786987</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G827" t="n">
-        <v>1.90417504310608</v>
+        <v>1.90417516231537</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G828" t="n">
-        <v>1.88550662994385</v>
+        <v>1.88550674915314</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G829" t="n">
-        <v>1.90417504310608</v>
+        <v>1.90417516231537</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>2</v>
       </c>
       <c r="G830" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G831" t="n">
-        <v>1.84817004203796</v>
+        <v>1.84816980361938</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G833" t="n">
-        <v>1.88550662994385</v>
+        <v>1.88550674915314</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G834" t="n">
-        <v>1.81083333492279</v>
+        <v>1.8108332157135</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G838" t="n">
-        <v>1.82016742229462</v>
+        <v>1.82016730308533</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G842" t="n">
-        <v>1.79216468334198</v>
+        <v>1.79216480255127</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G843" t="n">
-        <v>1.81083333492279</v>
+        <v>1.8108332157135</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G845" t="n">
-        <v>1.74549388885498</v>
+        <v>1.74549376964569</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G846" t="n">
-        <v>1.74549388885498</v>
+        <v>1.74549376964569</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G847" t="n">
-        <v>1.74549388885498</v>
+        <v>1.74549376964569</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G848" t="n">
-        <v>1.74549388885498</v>
+        <v>1.74549376964569</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G849" t="n">
-        <v>1.81083333492279</v>
+        <v>1.8108332157135</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G850" t="n">
-        <v>1.74549388885498</v>
+        <v>1.74549376964569</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G851" t="n">
-        <v>1.79216468334198</v>
+        <v>1.79216480255127</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G853" t="n">
-        <v>1.82016742229462</v>
+        <v>1.82016730308533</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>2</v>
       </c>
       <c r="G856" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G858" t="n">
-        <v>1.90417504310608</v>
+        <v>1.90417516231537</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G860" t="n">
-        <v>1.90417504310608</v>
+        <v>1.90417516231537</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G864" t="n">
-        <v>1.84817004203796</v>
+        <v>1.84816980361938</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>2</v>
       </c>
       <c r="G865" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>2</v>
       </c>
       <c r="G866" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>2</v>
       </c>
       <c r="G867" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G869" t="n">
-        <v>1.88550662994385</v>
+        <v>1.88550674915314</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G870" t="n">
-        <v>1.90417504310608</v>
+        <v>1.90417516231537</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G871" t="n">
-        <v>1.94151163101196</v>
+        <v>1.94151175022125</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G875" t="n">
-        <v>1.88550662994385</v>
+        <v>1.88550674915314</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>2</v>
       </c>
       <c r="G876" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G882" t="n">
-        <v>1.94151163101196</v>
+        <v>1.94151175022125</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G883" t="n">
-        <v>1.94151163101196</v>
+        <v>1.94151175022125</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>1.90417504310608</v>
+        <v>1.90417516231537</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G887" t="n">
-        <v>1.94151163101196</v>
+        <v>1.94151175022125</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G888" t="n">
-        <v>1.94151163101196</v>
+        <v>1.94151175022125</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G891" t="n">
-        <v>1.94151163101196</v>
+        <v>1.94151175022125</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G893" t="n">
-        <v>1.90417504310608</v>
+        <v>1.90417516231537</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G899" t="n">
-        <v>2.21220326423645</v>
+        <v>2.21220350265503</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G900" t="n">
-        <v>2.23087191581726</v>
+        <v>2.23087167739868</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G901" t="n">
-        <v>2.2588746547699</v>
+        <v>2.25887441635132</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G905" t="n">
-        <v>2.23087191581726</v>
+        <v>2.23087167739868</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G906" t="n">
-        <v>2.23087191581726</v>
+        <v>2.23087167739868</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G907" t="n">
-        <v>2.2588746547699</v>
+        <v>2.25887441635132</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G908" t="n">
-        <v>2.23087191581726</v>
+        <v>2.23087167739868</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G909" t="n">
-        <v>2.27754282951355</v>
+        <v>2.27754259109497</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G911" t="n">
-        <v>2.34288191795349</v>
+        <v>2.34288215637207</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G912" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G915" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G917" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G919" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G921" t="n">
-        <v>2.40822148323059</v>
+        <v>2.40822124481201</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G922" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G923" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G924" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G925" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G926" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G927" t="n">
-        <v>2.36155009269714</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>2.5</v>
       </c>
       <c r="G928" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G929" t="n">
-        <v>2.38955283164978</v>
+        <v>2.38955307006836</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G930" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G931" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G935" t="n">
-        <v>2.21220326423645</v>
+        <v>2.21220350265503</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G937" t="n">
-        <v>2.24020576477051</v>
+        <v>2.24020600318909</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G939" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>2.5</v>
       </c>
       <c r="G940" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>2.5</v>
       </c>
       <c r="G941" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G942" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G943" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>2.5</v>
       </c>
       <c r="G944" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>2.5</v>
       </c>
       <c r="G946" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G947" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G948" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G950" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G951" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G953" t="n">
-        <v>2.34288191795349</v>
+        <v>2.34288215637207</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G955" t="n">
-        <v>2.36155009269714</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G956" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G957" t="n">
-        <v>2.36155009269714</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>2.5</v>
       </c>
       <c r="G958" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>2.5</v>
       </c>
       <c r="G959" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G960" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G962" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>2.5</v>
       </c>
       <c r="G963" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G965" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G966" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G967" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G968" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G970" t="n">
-        <v>2.38955283164978</v>
+        <v>2.38955307006836</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G971" t="n">
-        <v>2.38955283164978</v>
+        <v>2.38955307006836</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G972" t="n">
-        <v>2.38955283164978</v>
+        <v>2.38955307006836</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G975" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G976" t="n">
-        <v>2.38955283164978</v>
+        <v>2.38955307006836</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G977" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G978" t="n">
-        <v>2.40822148323059</v>
+        <v>2.40822124481201</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G980" t="n">
-        <v>2.38955283164978</v>
+        <v>2.38955307006836</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G981" t="n">
-        <v>2.36155009269714</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G982" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G983" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G984" t="n">
-        <v>2.36155009269714</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G985" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G986" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G987" t="n">
-        <v>2.34288191795349</v>
+        <v>2.34288215637207</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>2.5</v>
       </c>
       <c r="G988" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>2.5</v>
       </c>
       <c r="G991" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>2.5</v>
       </c>
       <c r="G994" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G995" t="n">
-        <v>2.34288191795349</v>
+        <v>2.34288215637207</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>2.5</v>
       </c>
       <c r="G996" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G997" t="n">
-        <v>2.34288191795349</v>
+        <v>2.34288215637207</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>2.5</v>
       </c>
       <c r="G998" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>2.5</v>
       </c>
       <c r="G999" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>2.5</v>
       </c>
       <c r="G1000" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1001" t="n">
-        <v>2.38955283164978</v>
+        <v>2.38955307006836</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1002" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1003" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1004" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1005" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.40822148323059</v>
+        <v>2.40822124481201</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1007" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1008" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1009" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>2.5</v>
       </c>
       <c r="G1010" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1011" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1012" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1013" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1014" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1015" t="n">
-        <v>2.38955283164978</v>
+        <v>2.38955307006836</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1016" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1017" t="n">
-        <v>2.34288191795349</v>
+        <v>2.34288215637207</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1018" t="n">
-        <v>2.34288191795349</v>
+        <v>2.34288215637207</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1019" t="n">
-        <v>2.34288191795349</v>
+        <v>2.34288215637207</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1020" t="n">
-        <v>2.34288191795349</v>
+        <v>2.34288215637207</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>2.5</v>
       </c>
       <c r="G1022" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>2.5</v>
       </c>
       <c r="G1023" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1024" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>2.5</v>
       </c>
       <c r="G1025" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>2.5</v>
       </c>
       <c r="G1026" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>2.5</v>
       </c>
       <c r="G1027" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>2.5</v>
       </c>
       <c r="G1028" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>2.5</v>
       </c>
       <c r="G1029" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1030" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1031" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1032" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1033" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>2.5</v>
       </c>
       <c r="G1034" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1036" t="n">
-        <v>2.40822148323059</v>
+        <v>2.40822124481201</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1038" t="n">
-        <v>2.34288191795349</v>
+        <v>2.34288215637207</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1039" t="n">
-        <v>2.34288191795349</v>
+        <v>2.34288215637207</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>2.5</v>
       </c>
       <c r="G1040" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1043" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1044" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>2.5</v>
       </c>
       <c r="G1045" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1046" t="n">
-        <v>2.34288191795349</v>
+        <v>2.34288215637207</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>2.5</v>
       </c>
       <c r="G1051" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1052" t="n">
-        <v>2.36155009269714</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1053" t="n">
-        <v>2.34288191795349</v>
+        <v>2.34288215637207</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1054" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1055" t="n">
-        <v>2.38955283164978</v>
+        <v>2.38955307006836</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1057" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1058" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1059" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1060" t="n">
-        <v>2.38955283164978</v>
+        <v>2.38955307006836</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1061" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1063" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1064" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1065" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1081" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1082" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1083" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1086" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1087" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1089" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1090" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1092" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1096" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1097" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1098" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1099" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1100" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1101" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1102" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1103" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1106" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1108" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1109" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1110" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1112" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1113" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1114" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1115" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1120" t="n">
-        <v>2.63224196434021</v>
+        <v>2.63224172592163</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1121" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1122" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1123" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1124" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1140" t="n">
-        <v>2.82826018333435</v>
+        <v>2.82825994491577</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1143" t="n">
-        <v>2.85626244544983</v>
+        <v>2.85626268386841</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1154" t="n">
-        <v>2.85626244544983</v>
+        <v>2.85626268386841</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1161" t="n">
-        <v>2.88426494598389</v>
+        <v>2.88426518440247</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.28563547134399</v>
+        <v>3.28563523292542</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.31363797187805</v>
+        <v>3.31363773345947</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1180" t="n">
-        <v>4.0043683052063</v>
+        <v>4.00436782836914</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1181" t="n">
-        <v>4.26572561264038</v>
+        <v>4.26572513580322</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1182" t="n">
-        <v>4.46174383163452</v>
+        <v>4.46174335479736</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1183" t="n">
-        <v>4.76043796539307</v>
+        <v>4.76043748855591</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1186" t="n">
-        <v>4.85377931594849</v>
+        <v>4.85377883911133</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G1187" t="n">
-        <v>4.63909339904785</v>
+        <v>4.63909292221069</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1189" t="n">
-        <v>4.51774930953979</v>
+        <v>4.51774883270264</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1191" t="n">
-        <v>4.50841426849365</v>
+        <v>4.50841474533081</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1193" t="n">
-        <v>4.46174383163452</v>
+        <v>4.46174335479736</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1195" t="n">
-        <v>4.46174383163452</v>
+        <v>4.46174335479736</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1197" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1198" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1200" t="n">
-        <v>4.51774930953979</v>
+        <v>4.51774883270264</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1201" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>5</v>
       </c>
       <c r="G1205" t="n">
-        <v>4.66709613800049</v>
+        <v>4.66709566116333</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1208" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1209" t="n">
-        <v>4.4244065284729</v>
+        <v>4.42440700531006</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1211" t="n">
-        <v>4.46174383163452</v>
+        <v>4.46174335479736</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1212" t="n">
-        <v>4.50841426849365</v>
+        <v>4.50841474533081</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1214" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1215" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1216" t="n">
-        <v>4.48974657058716</v>
+        <v>4.48974609375</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1217" t="n">
-        <v>4.48974657058716</v>
+        <v>4.48974609375</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1218" t="n">
-        <v>4.45240879058838</v>
+        <v>4.45240926742554</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1219" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1220" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1221" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1222" t="n">
-        <v>4.4244065284729</v>
+        <v>4.42440700531006</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1224" t="n">
-        <v>4.37773609161377</v>
+        <v>4.37773561477661</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1226" t="n">
-        <v>4.37773609161377</v>
+        <v>4.37773561477661</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1228" t="n">
-        <v>4.34973287582397</v>
+        <v>4.34973335266113</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1240" t="n">
-        <v>4.45240879058838</v>
+        <v>4.45240926742554</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1241" t="n">
-        <v>4.4244065284729</v>
+        <v>4.42440700531006</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1251" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1252" t="n">
-        <v>4.53641700744629</v>
+        <v>4.53641748428345</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1253" t="n">
-        <v>4.76043796539307</v>
+        <v>4.76043748855591</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -48524,6 +48524,32 @@
         <v>17</v>
       </c>
       <c r="H1852" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1853">
+      <c r="A1853" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1853" t="n">
+        <v>16301</v>
+      </c>
+      <c r="C1853" t="n">
+        <v>17.0499992370605</v>
+      </c>
+      <c r="D1853" t="n">
+        <v>16.6499996185303</v>
+      </c>
+      <c r="E1853" t="n">
+        <v>16.9500007629395</v>
+      </c>
+      <c r="F1853" t="n">
+        <v>17</v>
+      </c>
+      <c r="G1853" t="n">
+        <v>17</v>
+      </c>
+      <c r="H1853" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IEG.MI.xlsx
+++ b/data/IEG.MI.xlsx
@@ -43048,13 +43048,36 @@
         <v>16.1000003814697</v>
       </c>
       <c r="D1856" t="n">
-        <v>15.25</v>
+        <v>15.1499996185303</v>
       </c>
       <c r="E1856" t="n">
         <v>15.75</v>
       </c>
-      <c r="F1856"/>
+      <c r="F1856" t="n">
+        <v>15.1499996185303</v>
+      </c>
       <c r="G1856" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1857">
+      <c r="A1857" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1857" t="n">
+        <v>29593</v>
+      </c>
+      <c r="C1857" t="n">
+        <v>15.8000001907349</v>
+      </c>
+      <c r="D1857" t="n">
+        <v>15.3999996185303</v>
+      </c>
+      <c r="E1857" t="n">
+        <v>15.8000001907349</v>
+      </c>
+      <c r="F1857"/>
+      <c r="G1857" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IEG.MI.xlsx
+++ b/data/IEG.MI.xlsx
@@ -43076,8 +43076,31 @@
       <c r="E1857" t="n">
         <v>15.8000001907349</v>
       </c>
-      <c r="F1857"/>
+      <c r="F1857" t="n">
+        <v>15.6000003814697</v>
+      </c>
       <c r="G1857" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1858">
+      <c r="A1858" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1858" t="n">
+        <v>207315</v>
+      </c>
+      <c r="C1858" t="n">
+        <v>13.8000001907349</v>
+      </c>
+      <c r="D1858" t="n">
+        <v>13.1499996185303</v>
+      </c>
+      <c r="E1858" t="n">
+        <v>13.4499998092651</v>
+      </c>
+      <c r="F1858"/>
+      <c r="G1858" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IEG.MI.xlsx
+++ b/data/IEG.MI.xlsx
@@ -43099,8 +43099,31 @@
       <c r="E1858" t="n">
         <v>13.4499998092651</v>
       </c>
-      <c r="F1858"/>
+      <c r="F1858" t="n">
+        <v>13.6000003814697</v>
+      </c>
       <c r="G1858" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1859">
+      <c r="A1859" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1859" t="n">
+        <v>71499</v>
+      </c>
+      <c r="C1859" t="n">
+        <v>13.9499998092651</v>
+      </c>
+      <c r="D1859" t="n">
+        <v>13.3500003814697</v>
+      </c>
+      <c r="E1859" t="n">
+        <v>13.3999996185303</v>
+      </c>
+      <c r="F1859"/>
+      <c r="G1859" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IEG.MI.xlsx
+++ b/data/IEG.MI.xlsx
@@ -43122,8 +43122,31 @@
       <c r="E1859" t="n">
         <v>13.3999996185303</v>
       </c>
-      <c r="F1859"/>
+      <c r="F1859" t="n">
+        <v>13.6999998092651</v>
+      </c>
       <c r="G1859" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1860">
+      <c r="A1860" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1860" t="n">
+        <v>62813</v>
+      </c>
+      <c r="C1860" t="n">
+        <v>14.3000001907349</v>
+      </c>
+      <c r="D1860" t="n">
+        <v>13.6000003814697</v>
+      </c>
+      <c r="E1860" t="n">
+        <v>13.8999996185303</v>
+      </c>
+      <c r="F1860"/>
+      <c r="G1860" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IEG.MI.xlsx
+++ b/data/IEG.MI.xlsx
@@ -43152,6 +43152,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1861">
+      <c r="A1861" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1861" t="n">
+        <v>26923</v>
+      </c>
+      <c r="C1861" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="D1861" t="n">
+        <v>14.1000003814697</v>
+      </c>
+      <c r="E1861" t="n">
+        <v>14.1000003814697</v>
+      </c>
+      <c r="F1861" t="n">
+        <v>14.4499998092651</v>
+      </c>
+      <c r="G1861" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IEG.MI.xlsx
+++ b/data/IEG.MI.xlsx
@@ -473,7 +473,7 @@
         <v>3.73099994659424</v>
       </c>
       <c r="G4" t="n">
-        <v>3.48258686065674</v>
+        <v>3.48258662223816</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G5" t="n">
-        <v>3.52832436561584</v>
+        <v>3.52832412719727</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.69749999046326</v>
       </c>
       <c r="G6" t="n">
-        <v>3.45131731033325</v>
+        <v>3.45131707191467</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G7" t="n">
-        <v>3.4536509513855</v>
+        <v>3.45365071296692</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>3.40698003768921</v>
+        <v>3.40697979927063</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.67050004005432</v>
       </c>
       <c r="G9" t="n">
-        <v>3.42611479759216</v>
+        <v>3.42611503601074</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G10" t="n">
-        <v>3.4536509513855</v>
+        <v>3.45365071296692</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G11" t="n">
-        <v>3.4536509513855</v>
+        <v>3.45365071296692</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G12" t="n">
-        <v>3.43498277664185</v>
+        <v>3.43498253822327</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.64050006866455</v>
       </c>
       <c r="G13" t="n">
-        <v>3.39811253547668</v>
+        <v>3.39811229705811</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G15" t="n">
-        <v>3.42564845085144</v>
+        <v>3.42564821243286</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G17" t="n">
-        <v>3.47231912612915</v>
+        <v>3.47231936454773</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G19" t="n">
-        <v>3.69633960723877</v>
+        <v>3.69634008407593</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G21" t="n">
-        <v>3.80835032463074</v>
+        <v>3.80834984779358</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G24" t="n">
-        <v>3.85502099990845</v>
+        <v>3.85502123832703</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G25" t="n">
-        <v>3.81768441200256</v>
+        <v>3.81768465042114</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G28" t="n">
-        <v>3.95769739151001</v>
+        <v>3.95769667625427</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G29" t="n">
-        <v>3.97636556625366</v>
+        <v>3.97636604309082</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G30" t="n">
-        <v>4.05103969573975</v>
+        <v>4.05103874206543</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G31" t="n">
-        <v>4.03237104415894</v>
+        <v>4.03237056732178</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G32" t="n">
-        <v>3.9390287399292</v>
+        <v>3.93902826309204</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>4.01370286941528</v>
+        <v>4.01370239257812</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G34" t="n">
-        <v>4.01370286941528</v>
+        <v>4.01370239257812</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G35" t="n">
-        <v>3.99503397941589</v>
+        <v>3.99503421783447</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G36" t="n">
-        <v>3.99503397941589</v>
+        <v>3.99503421783447</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G37" t="n">
-        <v>3.99503397941589</v>
+        <v>3.99503421783447</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G38" t="n">
-        <v>3.95769739151001</v>
+        <v>3.95769667625427</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G39" t="n">
-        <v>3.8830235004425</v>
+        <v>3.88302326202393</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G40" t="n">
-        <v>3.8830235004425</v>
+        <v>3.88302326202393</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G41" t="n">
-        <v>3.95769739151001</v>
+        <v>3.95769667625427</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G42" t="n">
-        <v>3.95769739151001</v>
+        <v>3.95769667625427</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>3.92036008834839</v>
+        <v>3.92036032676697</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G44" t="n">
-        <v>3.92036008834839</v>
+        <v>3.92036032676697</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G46" t="n">
-        <v>3.92036008834839</v>
+        <v>3.92036032676697</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G47" t="n">
-        <v>3.85502099990845</v>
+        <v>3.85502123832703</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G50" t="n">
-        <v>3.92036008834839</v>
+        <v>3.92036032676697</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G51" t="n">
-        <v>3.64033460617065</v>
+        <v>3.64033484458923</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G52" t="n">
-        <v>3.59366345405579</v>
+        <v>3.59366369247437</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G53" t="n">
-        <v>3.63100075721741</v>
+        <v>3.63100051879883</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G54" t="n">
-        <v>3.53765869140625</v>
+        <v>3.53765845298767</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G55" t="n">
-        <v>3.42564845085144</v>
+        <v>3.42564821243286</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G56" t="n">
-        <v>3.40698003768921</v>
+        <v>3.40697979927063</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G57" t="n">
-        <v>3.4536509513855</v>
+        <v>3.45365071296692</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G58" t="n">
-        <v>3.4536509513855</v>
+        <v>3.45365071296692</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G60" t="n">
-        <v>3.47231912612915</v>
+        <v>3.47231936454773</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>3.59366345405579</v>
+        <v>3.59366369247437</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G64" t="n">
-        <v>3.56566095352173</v>
+        <v>3.56566119194031</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G65" t="n">
-        <v>3.58432960510254</v>
+        <v>3.58432936668396</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G66" t="n">
-        <v>3.59366345405579</v>
+        <v>3.59366369247437</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G68" t="n">
-        <v>3.69633960723877</v>
+        <v>3.69634008407593</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G71" t="n">
-        <v>3.59366345405579</v>
+        <v>3.59366369247437</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G72" t="n">
-        <v>3.53765869140625</v>
+        <v>3.53765845298767</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G73" t="n">
-        <v>3.53765869140625</v>
+        <v>3.53765845298767</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G74" t="n">
-        <v>3.53765869140625</v>
+        <v>3.53765845298767</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>3.5469925403595</v>
+        <v>3.54699277877808</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G76" t="n">
-        <v>3.5469925403595</v>
+        <v>3.54699277877808</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>3.5469925403595</v>
+        <v>3.54699277877808</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G79" t="n">
-        <v>3.56566095352173</v>
+        <v>3.56566119194031</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G80" t="n">
-        <v>3.59366345405579</v>
+        <v>3.59366369247437</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G81" t="n">
-        <v>3.59366345405579</v>
+        <v>3.59366369247437</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G82" t="n">
-        <v>3.59366345405579</v>
+        <v>3.59366369247437</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G83" t="n">
-        <v>3.6123321056366</v>
+        <v>3.61233186721802</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G84" t="n">
-        <v>3.6123321056366</v>
+        <v>3.61233186721802</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G85" t="n">
-        <v>3.56566095352173</v>
+        <v>3.56566119194031</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>3.57499527931213</v>
+        <v>3.57499504089355</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G87" t="n">
-        <v>3.63100075721741</v>
+        <v>3.63100051879883</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>3.59366345405579</v>
+        <v>3.59366369247437</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G91" t="n">
-        <v>3.6123321056366</v>
+        <v>3.61233186721802</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G92" t="n">
-        <v>3.5469925403595</v>
+        <v>3.54699277877808</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G93" t="n">
-        <v>3.58432960510254</v>
+        <v>3.58432936668396</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>3.69633960723877</v>
+        <v>3.69634008407593</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G101" t="n">
-        <v>3.69633960723877</v>
+        <v>3.69634008407593</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G102" t="n">
-        <v>3.64033460617065</v>
+        <v>3.64033484458923</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G103" t="n">
-        <v>3.64033460617065</v>
+        <v>3.64033484458923</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>3.64033460617065</v>
+        <v>3.64033484458923</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G105" t="n">
-        <v>3.64966869354248</v>
+        <v>3.64966893196106</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G108" t="n">
-        <v>3.81768441200256</v>
+        <v>3.81768465042114</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G110" t="n">
-        <v>3.81768441200256</v>
+        <v>3.81768465042114</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>3.80835032463074</v>
+        <v>3.80834984779358</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G112" t="n">
-        <v>3.80835032463074</v>
+        <v>3.80834984779358</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G116" t="n">
-        <v>3.76167941093445</v>
+        <v>3.76167917251587</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G122" t="n">
-        <v>3.86435484886169</v>
+        <v>3.86435532569885</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G123" t="n">
-        <v>3.85502099990845</v>
+        <v>3.85502123832703</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G124" t="n">
-        <v>3.86435484886169</v>
+        <v>3.86435532569885</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G126" t="n">
-        <v>3.80835032463074</v>
+        <v>3.80834984779358</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G133" t="n">
-        <v>3.87368965148926</v>
+        <v>3.87368941307068</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G135" t="n">
-        <v>3.92036008834839</v>
+        <v>3.92036032676697</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G136" t="n">
-        <v>3.92036008834839</v>
+        <v>3.92036032676697</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G137" t="n">
-        <v>3.92969489097595</v>
+        <v>3.92969465255737</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G138" t="n">
-        <v>3.92036008834839</v>
+        <v>3.92036032676697</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G139" t="n">
-        <v>3.87368965148926</v>
+        <v>3.87368941307068</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G140" t="n">
-        <v>3.9390287399292</v>
+        <v>3.93902826309204</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G144" t="n">
-        <v>3.9390287399292</v>
+        <v>3.93902826309204</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G145" t="n">
-        <v>3.89235758781433</v>
+        <v>3.89235782623291</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G146" t="n">
-        <v>3.87368965148926</v>
+        <v>3.87368941307068</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G148" t="n">
-        <v>3.95769739151001</v>
+        <v>3.95769667625427</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G149" t="n">
-        <v>4.04170513153076</v>
+        <v>4.0417046546936</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G150" t="n">
-        <v>4.22838926315308</v>
+        <v>4.22838878631592</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G151" t="n">
-        <v>4.2563910484314</v>
+        <v>4.25639152526855</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G154" t="n">
-        <v>4.3590669631958</v>
+        <v>4.35906744003296</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G155" t="n">
-        <v>4.40573835372925</v>
+        <v>4.40573787689209</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G156" t="n">
-        <v>4.46174335479736</v>
+        <v>4.46174383163452</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G157" t="n">
-        <v>4.40573835372925</v>
+        <v>4.40573787689209</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G158" t="n">
-        <v>4.26572513580322</v>
+        <v>4.26572561264038</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G162" t="n">
-        <v>4.14438104629517</v>
+        <v>4.14438056945801</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G163" t="n">
-        <v>4.16304922103882</v>
+        <v>4.16304969787598</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G166" t="n">
-        <v>4.16304922103882</v>
+        <v>4.16304969787598</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G167" t="n">
-        <v>4.12571239471436</v>
+        <v>4.12571287155151</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>4.05103969573975</v>
+        <v>4.05103874206543</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G169" t="n">
-        <v>4.14438104629517</v>
+        <v>4.14438056945801</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G170" t="n">
-        <v>4.13504695892334</v>
+        <v>4.13504648208618</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G171" t="n">
-        <v>4.15371513366699</v>
+        <v>4.15371561050415</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G172" t="n">
-        <v>4.28439378738403</v>
+        <v>4.28439426422119</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G173" t="n">
-        <v>4.06037282943726</v>
+        <v>4.06037330627441</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G174" t="n">
-        <v>3.59366345405579</v>
+        <v>3.59366369247437</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G177" t="n">
-        <v>3.64966869354248</v>
+        <v>3.64966893196106</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G179" t="n">
-        <v>3.4536509513855</v>
+        <v>3.45365071296692</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G180" t="n">
-        <v>3.56566095352173</v>
+        <v>3.56566119194031</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G181" t="n">
-        <v>3.51899003982544</v>
+        <v>3.51899027824402</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G185" t="n">
-        <v>3.08961749076843</v>
+        <v>3.08961725234985</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G186" t="n">
-        <v>2.92160201072693</v>
+        <v>2.92160224914551</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G188" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G189" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G190" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G191" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G192" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G200" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G201" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G208" t="n">
-        <v>2.91226768493652</v>
+        <v>2.91226744651794</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G211" t="n">
-        <v>2.77225470542908</v>
+        <v>2.77225494384766</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>2.76292037963867</v>
+        <v>2.76292061805725</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G213" t="n">
-        <v>2.65091037750244</v>
+        <v>2.65091013908386</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G218" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G220" t="n">
-        <v>2.85626268386841</v>
+        <v>2.85626244544983</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G225" t="n">
-        <v>2.73491835594177</v>
+        <v>2.73491787910461</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G232" t="n">
-        <v>2.65091037750244</v>
+        <v>2.65091013908386</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>2.76292037963867</v>
+        <v>2.76292061805725</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G236" t="n">
-        <v>2.75358653068542</v>
+        <v>2.753586769104</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G238" t="n">
-        <v>2.85626268386841</v>
+        <v>2.85626244544983</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G239" t="n">
-        <v>2.85626268386841</v>
+        <v>2.85626244544983</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G247" t="n">
-        <v>2.91226768493652</v>
+        <v>2.91226744651794</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G248" t="n">
-        <v>2.97760701179504</v>
+        <v>2.97760725021362</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G249" t="n">
-        <v>2.88426518440247</v>
+        <v>2.88426494598389</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G266" t="n">
-        <v>2.6229076385498</v>
+        <v>2.62290787696838</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G268" t="n">
-        <v>2.63224172592163</v>
+        <v>2.63224196434021</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G270" t="n">
-        <v>2.6229076385498</v>
+        <v>2.62290787696838</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G273" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G274" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G275" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G277" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G278" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G279" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G280" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G282" t="n">
-        <v>2.48289489746094</v>
+        <v>2.48289513587952</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G284" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G285" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G286" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G291" t="n">
-        <v>2.6229076385498</v>
+        <v>2.62290787696838</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G295" t="n">
-        <v>2.54823446273804</v>
+        <v>2.54823422431946</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G297" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G298" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G307" t="n">
-        <v>2.50156354904175</v>
+        <v>2.50156331062317</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G308" t="n">
-        <v>2.46422672271729</v>
+        <v>2.46422648429871</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G311" t="n">
-        <v>2.48289489746094</v>
+        <v>2.48289513587952</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G312" t="n">
-        <v>2.48289489746094</v>
+        <v>2.48289513587952</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G313" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G315" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G316" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G319" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G320" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G321" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G324" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G325" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G326" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G329" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G330" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G331" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G332" t="n">
-        <v>2.27754259109497</v>
+        <v>2.27754282951355</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G334" t="n">
-        <v>2.24020600318909</v>
+        <v>2.24020576477051</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G336" t="n">
-        <v>2.26820874214172</v>
+        <v>2.26820850372314</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G337" t="n">
-        <v>2.24020600318909</v>
+        <v>2.24020576477051</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G339" t="n">
-        <v>2.1281955242157</v>
+        <v>2.12819576263428</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>2.06285619735718</v>
+        <v>2.06285643577576</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G343" t="n">
-        <v>1.98818278312683</v>
+        <v>1.98818302154541</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G348" t="n">
-        <v>1.76416218280792</v>
+        <v>1.76416206359863</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G351" t="n">
-        <v>1.57747828960419</v>
+        <v>1.57747840881348</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G361" t="n">
-        <v>1.66148602962494</v>
+        <v>1.66148614883423</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G363" t="n">
-        <v>1.84816980361938</v>
+        <v>1.84817004203796</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G365" t="n">
-        <v>1.94151175022125</v>
+        <v>1.94151163101196</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G366" t="n">
-        <v>2.02551984786987</v>
+        <v>2.02551937103271</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G367" t="n">
-        <v>2.06285619735718</v>
+        <v>2.06285643577576</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G369" t="n">
-        <v>2.1281955242157</v>
+        <v>2.12819576263428</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G372" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G373" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G374" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G376" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G381" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G382" t="n">
-        <v>2.50156354904175</v>
+        <v>2.50156331062317</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G383" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G384" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G387" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G392" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G393" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G396" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G397" t="n">
-        <v>2.27754259109497</v>
+        <v>2.27754282951355</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G399" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G400" t="n">
-        <v>2.20286917686462</v>
+        <v>2.20286893844604</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G401" t="n">
-        <v>2.07219052314758</v>
+        <v>2.072190284729</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G408" t="n">
-        <v>2.20286917686462</v>
+        <v>2.20286893844604</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G414" t="n">
-        <v>2.08152461051941</v>
+        <v>2.08152484893799</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G417" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G418" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G419" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G422" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G424" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G426" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G427" t="n">
-        <v>2.26820874214172</v>
+        <v>2.26820850372314</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G428" t="n">
-        <v>2.27754259109497</v>
+        <v>2.27754282951355</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G429" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G430" t="n">
-        <v>2.25887441635132</v>
+        <v>2.2588746547699</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G431" t="n">
-        <v>2.25887441635132</v>
+        <v>2.2588746547699</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G432" t="n">
-        <v>2.27754259109497</v>
+        <v>2.27754282951355</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G433" t="n">
-        <v>2.25887441635132</v>
+        <v>2.2588746547699</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G434" t="n">
-        <v>2.24020600318909</v>
+        <v>2.24020576477051</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G436" t="n">
-        <v>2.27754259109497</v>
+        <v>2.27754282951355</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G437" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G438" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G439" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G441" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G443" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G445" t="n">
-        <v>2.23087167739868</v>
+        <v>2.23087191581726</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G446" t="n">
-        <v>2.23087167739868</v>
+        <v>2.23087191581726</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G447" t="n">
-        <v>2.27754259109497</v>
+        <v>2.27754282951355</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G448" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G450" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G461" t="n">
-        <v>2.73491835594177</v>
+        <v>2.73491787910461</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>3.25</v>
       </c>
       <c r="G465" t="n">
-        <v>3.03361225128174</v>
+        <v>3.03361201286316</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>3.25</v>
       </c>
       <c r="G467" t="n">
-        <v>3.03361225128174</v>
+        <v>3.03361201286316</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G468" t="n">
-        <v>3.08028316497803</v>
+        <v>3.08028292655945</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>3.25</v>
       </c>
       <c r="G469" t="n">
-        <v>3.03361225128174</v>
+        <v>3.03361201286316</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G471" t="n">
-        <v>3.27630138397217</v>
+        <v>3.27630114555359</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G473" t="n">
-        <v>3.3323061466217</v>
+        <v>3.33230638504028</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G475" t="n">
-        <v>3.2296302318573</v>
+        <v>3.22962999343872</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G477" t="n">
-        <v>3.11761975288391</v>
+        <v>3.11761999130249</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G480" t="n">
-        <v>3.20162773132324</v>
+        <v>3.20162796974182</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G482" t="n">
-        <v>3.08961749076843</v>
+        <v>3.08961725234985</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G483" t="n">
-        <v>3.12695384025574</v>
+        <v>3.12695407867432</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G485" t="n">
-        <v>3.15495657920837</v>
+        <v>3.15495681762695</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G489" t="n">
-        <v>3.11761975288391</v>
+        <v>3.11761999130249</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G490" t="n">
-        <v>3.08028316497803</v>
+        <v>3.08028292655945</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G492" t="n">
-        <v>2.97760701179504</v>
+        <v>2.97760725021362</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G493" t="n">
-        <v>3.04294657707214</v>
+        <v>3.04294633865356</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G496" t="n">
-        <v>3.08028316497803</v>
+        <v>3.08028292655945</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G497" t="n">
-        <v>3.08028316497803</v>
+        <v>3.08028292655945</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G499" t="n">
-        <v>3.11761975288391</v>
+        <v>3.11761999130249</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G500" t="n">
-        <v>3.11761975288391</v>
+        <v>3.11761999130249</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>3.25</v>
       </c>
       <c r="G503" t="n">
-        <v>3.03361225128174</v>
+        <v>3.03361201286316</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G504" t="n">
-        <v>3.02427792549133</v>
+        <v>3.02427816390991</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G509" t="n">
-        <v>2.96827292442322</v>
+        <v>2.9682731628418</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G518" t="n">
-        <v>2.73491835594177</v>
+        <v>2.73491787910461</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G521" t="n">
-        <v>2.75358653068542</v>
+        <v>2.753586769104</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G524" t="n">
-        <v>2.63224172592163</v>
+        <v>2.63224196434021</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G529" t="n">
-        <v>2.46422672271729</v>
+        <v>2.46422648429871</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G531" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G532" t="n">
-        <v>2.46422672271729</v>
+        <v>2.46422648429871</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G534" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G536" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G538" t="n">
-        <v>2.6229076385498</v>
+        <v>2.62290787696838</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G539" t="n">
-        <v>2.6229076385498</v>
+        <v>2.62290787696838</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G540" t="n">
-        <v>2.6229076385498</v>
+        <v>2.62290787696838</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G542" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G543" t="n">
-        <v>2.63224172592163</v>
+        <v>2.63224196434021</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G544" t="n">
-        <v>2.54823446273804</v>
+        <v>2.54823422431946</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G553" t="n">
-        <v>2.65091037750244</v>
+        <v>2.65091013908386</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G555" t="n">
-        <v>2.75358653068542</v>
+        <v>2.753586769104</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G556" t="n">
-        <v>2.77225470542908</v>
+        <v>2.77225494384766</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G557" t="n">
-        <v>2.77225470542908</v>
+        <v>2.77225494384766</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G558" t="n">
-        <v>2.65091037750244</v>
+        <v>2.65091013908386</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G559" t="n">
-        <v>2.65091037750244</v>
+        <v>2.65091013908386</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G561" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G570" t="n">
-        <v>2.77225470542908</v>
+        <v>2.77225494384766</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G577" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G581" t="n">
-        <v>2.77225470542908</v>
+        <v>2.77225494384766</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G583" t="n">
-        <v>2.76292037963867</v>
+        <v>2.76292061805725</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G589" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G591" t="n">
-        <v>2.77225470542908</v>
+        <v>2.77225494384766</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G592" t="n">
-        <v>2.77225470542908</v>
+        <v>2.77225494384766</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G594" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G596" t="n">
-        <v>2.77225470542908</v>
+        <v>2.77225494384766</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G598" t="n">
-        <v>2.75358653068542</v>
+        <v>2.753586769104</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G600" t="n">
-        <v>2.75358653068542</v>
+        <v>2.753586769104</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G603" t="n">
-        <v>2.73491835594177</v>
+        <v>2.73491787910461</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G609" t="n">
-        <v>2.76292037963867</v>
+        <v>2.76292061805725</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G610" t="n">
-        <v>2.77225470542908</v>
+        <v>2.77225494384766</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G614" t="n">
-        <v>2.77225470542908</v>
+        <v>2.77225494384766</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G622" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G625" t="n">
-        <v>2.48289489746094</v>
+        <v>2.48289513587952</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G626" t="n">
-        <v>2.50156354904175</v>
+        <v>2.50156331062317</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G627" t="n">
-        <v>2.48289489746094</v>
+        <v>2.48289513587952</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G629" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G630" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G635" t="n">
-        <v>2.65091037750244</v>
+        <v>2.65091013908386</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G638" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G644" t="n">
-        <v>2.50156354904175</v>
+        <v>2.50156331062317</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G645" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G651" t="n">
-        <v>2.54823446273804</v>
+        <v>2.54823422431946</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G652" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G653" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G654" t="n">
-        <v>2.50156354904175</v>
+        <v>2.50156331062317</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G665" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G671" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G674" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G675" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G679" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G685" t="n">
-        <v>2.65091037750244</v>
+        <v>2.65091013908386</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G686" t="n">
-        <v>2.48289489746094</v>
+        <v>2.48289513587952</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G688" t="n">
-        <v>2.50156354904175</v>
+        <v>2.50156331062317</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G689" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G695" t="n">
-        <v>2.23087167739868</v>
+        <v>2.23087191581726</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G697" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G698" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G700" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G701" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G702" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G705" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G706" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G708" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G713" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G714" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G720" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G722" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G724" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G725" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G726" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G727" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G728" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G730" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G734" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G736" t="n">
-        <v>2.24020600318909</v>
+        <v>2.24020576477051</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G739" t="n">
-        <v>2.23087167739868</v>
+        <v>2.23087191581726</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G742" t="n">
-        <v>2.23087167739868</v>
+        <v>2.23087191581726</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G745" t="n">
-        <v>2.20286917686462</v>
+        <v>2.20286893844604</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G748" t="n">
-        <v>2.1281955242157</v>
+        <v>2.12819576263428</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G749" t="n">
-        <v>2.1281955242157</v>
+        <v>2.12819576263428</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G757" t="n">
-        <v>2.15619826316833</v>
+        <v>2.15619802474976</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G758" t="n">
-        <v>2.24020600318909</v>
+        <v>2.24020576477051</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G759" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G760" t="n">
-        <v>2.15619826316833</v>
+        <v>2.15619802474976</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G763" t="n">
-        <v>2.15619826316833</v>
+        <v>2.15619802474976</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G769" t="n">
-        <v>2.08152461051941</v>
+        <v>2.08152484893799</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G770" t="n">
-        <v>2.08152461051941</v>
+        <v>2.08152484893799</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G777" t="n">
-        <v>2.00685143470764</v>
+        <v>2.00685119628906</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G778" t="n">
-        <v>2.01618552207947</v>
+        <v>2.01618528366089</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G779" t="n">
-        <v>2.01618552207947</v>
+        <v>2.01618528366089</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G780" t="n">
-        <v>1.99751698970795</v>
+        <v>1.99751710891724</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G781" t="n">
-        <v>2.02551984786987</v>
+        <v>2.02551937103271</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G782" t="n">
-        <v>1.96018004417419</v>
+        <v>1.96018016338348</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G783" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G787" t="n">
-        <v>1.76416218280792</v>
+        <v>1.76416206359863</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G788" t="n">
-        <v>1.76882934570312</v>
+        <v>1.76882922649384</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G793" t="n">
-        <v>1.79216480255127</v>
+        <v>1.79216468334198</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G795" t="n">
-        <v>1.84816980361938</v>
+        <v>1.84817004203796</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G800" t="n">
-        <v>1.82016730308533</v>
+        <v>1.82016742229462</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G807" t="n">
-        <v>1.88550674915314</v>
+        <v>1.88550662994385</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G814" t="n">
-        <v>1.98818278312683</v>
+        <v>1.98818302154541</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G815" t="n">
-        <v>1.98818278312683</v>
+        <v>1.98818302154541</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G816" t="n">
-        <v>1.978848695755</v>
+        <v>1.97884833812714</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G819" t="n">
-        <v>1.94151175022125</v>
+        <v>1.94151163101196</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G823" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G824" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G826" t="n">
-        <v>2.02551984786987</v>
+        <v>2.02551937103271</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G827" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G828" t="n">
-        <v>1.88550674915314</v>
+        <v>1.88550662994385</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G829" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G831" t="n">
-        <v>1.84816980361938</v>
+        <v>1.84817004203796</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G833" t="n">
-        <v>1.88550674915314</v>
+        <v>1.88550662994385</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G838" t="n">
-        <v>1.82016730308533</v>
+        <v>1.82016742229462</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G842" t="n">
-        <v>1.79216480255127</v>
+        <v>1.79216468334198</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>1.875</v>
       </c>
       <c r="G844" t="n">
-        <v>1.7501608133316</v>
+        <v>1.75016093254089</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G851" t="n">
-        <v>1.79216480255127</v>
+        <v>1.79216468334198</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G853" t="n">
-        <v>1.82016730308533</v>
+        <v>1.82016742229462</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G858" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G860" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G864" t="n">
-        <v>1.84816980361938</v>
+        <v>1.84817004203796</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G869" t="n">
-        <v>1.88550674915314</v>
+        <v>1.88550662994385</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G870" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G871" t="n">
-        <v>1.94151175022125</v>
+        <v>1.94151163101196</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G875" t="n">
-        <v>1.88550674915314</v>
+        <v>1.88550662994385</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G882" t="n">
-        <v>1.94151175022125</v>
+        <v>1.94151163101196</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G883" t="n">
-        <v>1.94151175022125</v>
+        <v>1.94151163101196</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G887" t="n">
-        <v>1.94151175022125</v>
+        <v>1.94151163101196</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G888" t="n">
-        <v>1.94151175022125</v>
+        <v>1.94151163101196</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G891" t="n">
-        <v>1.94151175022125</v>
+        <v>1.94151163101196</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G893" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G898" t="n">
-        <v>2.20286917686462</v>
+        <v>2.20286893844604</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G900" t="n">
-        <v>2.23087167739868</v>
+        <v>2.23087191581726</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G901" t="n">
-        <v>2.25887441635132</v>
+        <v>2.2588746547699</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G902" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G903" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G905" t="n">
-        <v>2.23087167739868</v>
+        <v>2.23087191581726</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G906" t="n">
-        <v>2.23087167739868</v>
+        <v>2.23087191581726</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G907" t="n">
-        <v>2.25887441635132</v>
+        <v>2.2588746547699</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G908" t="n">
-        <v>2.23087167739868</v>
+        <v>2.23087191581726</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G909" t="n">
-        <v>2.27754259109497</v>
+        <v>2.27754282951355</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G910" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G917" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G919" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G921" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G922" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G923" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G924" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G925" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G927" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G930" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G934" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G936" t="n">
-        <v>2.20286917686462</v>
+        <v>2.20286893844604</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G937" t="n">
-        <v>2.24020600318909</v>
+        <v>2.24020576477051</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G938" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G939" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G942" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G943" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G948" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G950" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G951" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G955" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G956" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G957" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G960" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G962" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G965" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G966" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G975" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G977" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G978" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G981" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G984" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1002" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1005" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1009" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1011" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1021" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1024" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1030" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1031" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1032" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1033" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1036" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1041" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1042" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1043" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1044" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1052" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1061" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1063" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1064" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1065" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1072" t="n">
-        <v>2.65091037750244</v>
+        <v>2.65091013908386</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.6229076385498</v>
+        <v>2.62290787696838</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1106" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1108" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1109" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1110" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1112" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1113" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1114" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1115" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1120" t="n">
-        <v>2.63224172592163</v>
+        <v>2.63224196434021</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1126" t="n">
-        <v>2.75358653068542</v>
+        <v>2.753586769104</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1143" t="n">
-        <v>2.85626268386841</v>
+        <v>2.85626244544983</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1148" t="n">
-        <v>2.91226768493652</v>
+        <v>2.91226744651794</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1149" t="n">
-        <v>2.92160201072693</v>
+        <v>2.92160224914551</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1154" t="n">
-        <v>2.85626268386841</v>
+        <v>2.85626244544983</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1158" t="n">
-        <v>2.91226768493652</v>
+        <v>2.91226744651794</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1161" t="n">
-        <v>2.88426518440247</v>
+        <v>2.88426494598389</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1163" t="n">
-        <v>2.96827292442322</v>
+        <v>2.9682731628418</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.20162773132324</v>
+        <v>3.20162796974182</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.18295931816101</v>
+        <v>3.18295907974243</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.18295931816101</v>
+        <v>3.18295907974243</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.2296302318573</v>
+        <v>3.22962999343872</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.28563523292542</v>
+        <v>3.28563547134399</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.44431686401367</v>
+        <v>3.44431662559509</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1180" t="n">
-        <v>4.00436782836914</v>
+        <v>4.0043683052063</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1181" t="n">
-        <v>4.26572513580322</v>
+        <v>4.26572561264038</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1182" t="n">
-        <v>4.46174335479736</v>
+        <v>4.46174383163452</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1186" t="n">
-        <v>4.85377883911133</v>
+        <v>4.85377931594849</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1189" t="n">
-        <v>4.51774883270264</v>
+        <v>4.51774930953979</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1191" t="n">
-        <v>4.50841474533081</v>
+        <v>4.50841426849365</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1193" t="n">
-        <v>4.46174335479736</v>
+        <v>4.46174383163452</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1195" t="n">
-        <v>4.46174335479736</v>
+        <v>4.46174383163452</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1197" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1198" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1200" t="n">
-        <v>4.51774883270264</v>
+        <v>4.51774930953979</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1201" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1208" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1211" t="n">
-        <v>4.46174335479736</v>
+        <v>4.46174383163452</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1212" t="n">
-        <v>4.50841474533081</v>
+        <v>4.50841426849365</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1214" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1215" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1219" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1220" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1221" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.40573835372925</v>
+        <v>4.40573787689209</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1250" t="n">
-        <v>4.40573835372925</v>
+        <v>4.40573787689209</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1251" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1252" t="n">
-        <v>4.53641748428345</v>
+        <v>4.53641700744629</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1274" t="n">
-        <v>4.9907808303833</v>
+        <v>4.99078130722046</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1275" t="n">
-        <v>5.02917194366455</v>
+        <v>5.02917146682739</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1278" t="n">
-        <v>5.48985910415649</v>
+        <v>5.48985958099365</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1283" t="n">
-        <v>5.83537530899048</v>
+        <v>5.83537483215332</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1285" t="n">
-        <v>6.39203882217407</v>
+        <v>6.39203929901123</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1289" t="n">
-        <v>6.46882057189941</v>
+        <v>6.46882009506226</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G1293" t="n">
-        <v>6.18089056015015</v>
+        <v>6.1808910369873</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1294" t="n">
-        <v>6.12330484390259</v>
+        <v>6.12330532073975</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1296" t="n">
-        <v>6.39203882217407</v>
+        <v>6.39203929901123</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1297" t="n">
-        <v>6.48801565170288</v>
+        <v>6.48801612854004</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1298" t="n">
-        <v>6.48801565170288</v>
+        <v>6.48801612854004</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1303" t="n">
-        <v>6.48801565170288</v>
+        <v>6.48801612854004</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1311" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1313" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1316" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1330" t="n">
-        <v>5.68181228637695</v>
+        <v>5.68181276321411</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1333" t="n">
-        <v>5.66261768341064</v>
+        <v>5.66261720657349</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.56664133071899</v>
+        <v>5.56664085388184</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1335" t="n">
-        <v>5.48985910415649</v>
+        <v>5.48985958099365</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1337" t="n">
-        <v>5.56664133071899</v>
+        <v>5.56664085388184</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1338" t="n">
-        <v>5.56664133071899</v>
+        <v>5.56664085388184</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1341" t="n">
-        <v>5.66261768341064</v>
+        <v>5.66261720657349</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1342" t="n">
-        <v>5.66261768341064</v>
+        <v>5.66261720657349</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1346" t="n">
-        <v>5.56664133071899</v>
+        <v>5.56664085388184</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1350" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1351" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1352" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1353" t="n">
-        <v>6.12330484390259</v>
+        <v>6.12330532073975</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1356" t="n">
-        <v>5.87376594543457</v>
+        <v>5.87376546859741</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1363" t="n">
-        <v>5.96974229812622</v>
+        <v>5.96974182128906</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1367" t="n">
-        <v>5.96974229812622</v>
+        <v>5.96974182128906</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1368" t="n">
-        <v>5.83537530899048</v>
+        <v>5.83537483215332</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1370" t="n">
-        <v>5.96974229812622</v>
+        <v>5.96974182128906</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1371" t="n">
-        <v>5.87376594543457</v>
+        <v>5.87376546859741</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1373" t="n">
-        <v>6.0849142074585</v>
+        <v>6.08491468429565</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1375" t="n">
-        <v>5.87376594543457</v>
+        <v>5.87376546859741</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1384" t="n">
-        <v>5.87376594543457</v>
+        <v>5.87376546859741</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1385" t="n">
-        <v>5.96974229812622</v>
+        <v>5.96974182128906</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1386" t="n">
-        <v>5.96974229812622</v>
+        <v>5.96974182128906</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1387" t="n">
-        <v>5.96974229812622</v>
+        <v>5.96974182128906</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1388" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1390" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1392" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1393" t="n">
-        <v>5.87376594543457</v>
+        <v>5.87376546859741</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1404" t="n">
-        <v>6.0849142074585</v>
+        <v>6.08491468429565</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1406" t="n">
-        <v>6.12330484390259</v>
+        <v>6.12330532073975</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1417" t="n">
-        <v>7.02548456192017</v>
+        <v>7.02548503875732</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1430" t="n">
-        <v>7.02548456192017</v>
+        <v>7.02548503875732</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1432" t="n">
-        <v>7.02548456192017</v>
+        <v>7.02548503875732</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1440" t="n">
-        <v>7.06387567520142</v>
+        <v>7.06387519836426</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G1442" t="n">
-        <v>7.12146091461182</v>
+        <v>7.12146139144897</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1446" t="n">
-        <v>7.06387567520142</v>
+        <v>7.06387519836426</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1448" t="n">
-        <v>7.06387567520142</v>
+        <v>7.06387519836426</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1449" t="n">
-        <v>6.91031217575073</v>
+        <v>6.91031265258789</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1450" t="n">
-        <v>7.02548456192017</v>
+        <v>7.02548503875732</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1454" t="n">
-        <v>7.06387567520142</v>
+        <v>7.06387519836426</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1459" t="n">
-        <v>6.91031217575073</v>
+        <v>6.91031265258789</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1461" t="n">
-        <v>6.91031217575073</v>
+        <v>6.91031265258789</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1462" t="n">
-        <v>7.06387567520142</v>
+        <v>7.06387519836426</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1466" t="n">
-        <v>7.02548456192017</v>
+        <v>7.02548503875732</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1476" t="n">
-        <v>6.91031217575073</v>
+        <v>6.91031265258789</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1477" t="n">
-        <v>6.89111709594727</v>
+        <v>6.89111757278442</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1479" t="n">
-        <v>6.91031217575073</v>
+        <v>6.91031265258789</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1480" t="n">
-        <v>6.77594566345215</v>
+        <v>6.77594518661499</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1481" t="n">
-        <v>6.98709392547607</v>
+        <v>6.98709440231323</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1482" t="n">
-        <v>6.89111709594727</v>
+        <v>6.89111757278442</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G1484" t="n">
-        <v>6.79514074325562</v>
+        <v>6.79514026641846</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1485" t="n">
-        <v>6.81433582305908</v>
+        <v>6.81433629989624</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1486" t="n">
-        <v>6.91031217575073</v>
+        <v>6.91031265258789</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1487" t="n">
-        <v>6.91031217575073</v>
+        <v>6.91031265258789</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1488" t="n">
-        <v>6.98709392547607</v>
+        <v>6.98709440231323</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1495" t="n">
-        <v>7.29421854019165</v>
+        <v>7.29421901702881</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1496" t="n">
-        <v>7.42858600616455</v>
+        <v>7.42858552932739</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1498" t="n">
-        <v>7.54375839233398</v>
+        <v>7.54375791549683</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -48810,6 +48810,32 @@
         <v>14.25</v>
       </c>
       <c r="H1863" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1864">
+      <c r="A1864" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1864" t="n">
+        <v>13917</v>
+      </c>
+      <c r="C1864" t="n">
+        <v>14.3999996185303</v>
+      </c>
+      <c r="D1864" t="n">
+        <v>13.8000001907349</v>
+      </c>
+      <c r="E1864" t="n">
+        <v>14.3999996185303</v>
+      </c>
+      <c r="F1864" t="n">
+        <v>13.9499998092651</v>
+      </c>
+      <c r="G1864" t="n">
+        <v>13.9499998092651</v>
+      </c>
+      <c r="H1864" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IEG.MI.xlsx
+++ b/data/IEG.MI.xlsx
@@ -48839,6 +48839,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1865">
+      <c r="A1865" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1865" t="n">
+        <v>3703</v>
+      </c>
+      <c r="C1865" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="D1865" t="n">
+        <v>13.8000001907349</v>
+      </c>
+      <c r="E1865" t="n">
+        <v>13.8000001907349</v>
+      </c>
+      <c r="F1865" t="n">
+        <v>14.1999998092651</v>
+      </c>
+      <c r="G1865" t="n">
+        <v>14.1999998092651</v>
+      </c>
+      <c r="H1865" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IEG.MI.xlsx
+++ b/data/IEG.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.70549988746643</v>
       </c>
       <c r="G2" t="n">
-        <v>3.45878434181213</v>
+        <v>3.45878458023071</v>
       </c>
       <c r="H2" t="n">
         <v>138225</v>
@@ -485,7 +485,7 @@
         <v>3.73099994659424</v>
       </c>
       <c r="G4" t="n">
-        <v>3.48258662223816</v>
+        <v>3.48258686065674</v>
       </c>
       <c r="H4" t="n">
         <v>132269</v>
@@ -543,7 +543,7 @@
         <v>3.69749999046326</v>
       </c>
       <c r="G6" t="n">
-        <v>3.45131731033325</v>
+        <v>3.45131707191467</v>
       </c>
       <c r="H6" t="n">
         <v>5051</v>
@@ -775,7 +775,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G14" t="n">
-        <v>3.31363797187805</v>
+        <v>3.31363773345947</v>
       </c>
       <c r="H14" t="n">
         <v>25612</v>
@@ -804,7 +804,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G15" t="n">
-        <v>3.42564845085144</v>
+        <v>3.42564821243286</v>
       </c>
       <c r="H15" t="n">
         <v>10175</v>
@@ -833,7 +833,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G16" t="n">
-        <v>3.36030888557434</v>
+        <v>3.36030864715576</v>
       </c>
       <c r="H16" t="n">
         <v>51650</v>
@@ -891,7 +891,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G18" t="n">
-        <v>3.67767143249512</v>
+        <v>3.67767119407654</v>
       </c>
       <c r="H18" t="n">
         <v>96799</v>
@@ -949,7 +949,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G20" t="n">
-        <v>3.7803475856781</v>
+        <v>3.78034782409668</v>
       </c>
       <c r="H20" t="n">
         <v>59862</v>
@@ -978,7 +978,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G21" t="n">
-        <v>3.80835032463074</v>
+        <v>3.80834984779358</v>
       </c>
       <c r="H21" t="n">
         <v>29979</v>
@@ -1007,7 +1007,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G22" t="n">
-        <v>3.7803475856781</v>
+        <v>3.78034782409668</v>
       </c>
       <c r="H22" t="n">
         <v>4670</v>
@@ -1094,7 +1094,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G25" t="n">
-        <v>3.81768465042114</v>
+        <v>3.81768441200256</v>
       </c>
       <c r="H25" t="n">
         <v>4963</v>
@@ -1123,7 +1123,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G26" t="n">
-        <v>3.91102600097656</v>
+        <v>3.91102647781372</v>
       </c>
       <c r="H26" t="n">
         <v>12441</v>
@@ -1152,7 +1152,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G27" t="n">
-        <v>3.98569989204407</v>
+        <v>3.98569941520691</v>
       </c>
       <c r="H27" t="n">
         <v>15090</v>
@@ -1181,7 +1181,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G28" t="n">
-        <v>3.95769715309143</v>
+        <v>3.95769667625427</v>
       </c>
       <c r="H28" t="n">
         <v>6052</v>
@@ -1210,7 +1210,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G29" t="n">
-        <v>3.97636580467224</v>
+        <v>3.97636604309082</v>
       </c>
       <c r="H29" t="n">
         <v>2457</v>
@@ -1239,7 +1239,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G30" t="n">
-        <v>4.05103921890259</v>
+        <v>4.05103874206543</v>
       </c>
       <c r="H30" t="n">
         <v>10363</v>
@@ -1268,7 +1268,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G31" t="n">
-        <v>4.03237056732178</v>
+        <v>4.03237104415894</v>
       </c>
       <c r="H31" t="n">
         <v>17060</v>
@@ -1297,7 +1297,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G32" t="n">
-        <v>3.93902850151062</v>
+        <v>3.9390287399292</v>
       </c>
       <c r="H32" t="n">
         <v>6284</v>
@@ -1326,7 +1326,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>4.01370286941528</v>
+        <v>4.01370191574097</v>
       </c>
       <c r="H33" t="n">
         <v>4871</v>
@@ -1355,7 +1355,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G34" t="n">
-        <v>4.01370286941528</v>
+        <v>4.01370191574097</v>
       </c>
       <c r="H34" t="n">
         <v>114</v>
@@ -1384,7 +1384,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G35" t="n">
-        <v>3.99503397941589</v>
+        <v>3.99503421783447</v>
       </c>
       <c r="H35" t="n">
         <v>922</v>
@@ -1413,7 +1413,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G36" t="n">
-        <v>3.99503397941589</v>
+        <v>3.99503421783447</v>
       </c>
       <c r="H36" t="n">
         <v>300</v>
@@ -1442,7 +1442,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G37" t="n">
-        <v>3.99503397941589</v>
+        <v>3.99503421783447</v>
       </c>
       <c r="H37" t="n">
         <v>4226</v>
@@ -1471,7 +1471,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G38" t="n">
-        <v>3.95769715309143</v>
+        <v>3.95769667625427</v>
       </c>
       <c r="H38" t="n">
         <v>4960</v>
@@ -1500,7 +1500,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G39" t="n">
-        <v>3.8830235004425</v>
+        <v>3.88302326202393</v>
       </c>
       <c r="H39" t="n">
         <v>592</v>
@@ -1529,7 +1529,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G40" t="n">
-        <v>3.8830235004425</v>
+        <v>3.88302326202393</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1558,7 +1558,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G41" t="n">
-        <v>3.95769715309143</v>
+        <v>3.95769667625427</v>
       </c>
       <c r="H41" t="n">
         <v>225</v>
@@ -1587,7 +1587,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G42" t="n">
-        <v>3.95769715309143</v>
+        <v>3.95769667625427</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G45" t="n">
-        <v>3.91102600097656</v>
+        <v>3.91102647781372</v>
       </c>
       <c r="H45" t="n">
         <v>115</v>
@@ -1761,7 +1761,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G48" t="n">
-        <v>3.84568667411804</v>
+        <v>3.8456871509552</v>
       </c>
       <c r="H48" t="n">
         <v>600</v>
@@ -1790,7 +1790,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G49" t="n">
-        <v>3.91102600097656</v>
+        <v>3.91102647781372</v>
       </c>
       <c r="H49" t="n">
         <v>400</v>
@@ -1877,7 +1877,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G52" t="n">
-        <v>3.59366345405579</v>
+        <v>3.59366369247437</v>
       </c>
       <c r="H52" t="n">
         <v>66112</v>
@@ -1964,7 +1964,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G55" t="n">
-        <v>3.42564845085144</v>
+        <v>3.42564821243286</v>
       </c>
       <c r="H55" t="n">
         <v>62162</v>
@@ -2167,7 +2167,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>3.59366345405579</v>
+        <v>3.59366369247437</v>
       </c>
       <c r="H62" t="n">
         <v>6367</v>
@@ -2283,7 +2283,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G66" t="n">
-        <v>3.59366345405579</v>
+        <v>3.59366369247437</v>
       </c>
       <c r="H66" t="n">
         <v>2000</v>
@@ -2428,7 +2428,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G71" t="n">
-        <v>3.59366345405579</v>
+        <v>3.59366369247437</v>
       </c>
       <c r="H71" t="n">
         <v>700</v>
@@ -2689,7 +2689,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G80" t="n">
-        <v>3.59366345405579</v>
+        <v>3.59366369247437</v>
       </c>
       <c r="H80" t="n">
         <v>320</v>
@@ -2718,7 +2718,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G81" t="n">
-        <v>3.59366345405579</v>
+        <v>3.59366369247437</v>
       </c>
       <c r="H81" t="n">
         <v>11</v>
@@ -2747,7 +2747,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G82" t="n">
-        <v>3.59366345405579</v>
+        <v>3.59366369247437</v>
       </c>
       <c r="H82" t="n">
         <v>659</v>
@@ -2776,7 +2776,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G83" t="n">
-        <v>3.6123321056366</v>
+        <v>3.61233186721802</v>
       </c>
       <c r="H83" t="n">
         <v>505</v>
@@ -2805,7 +2805,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G84" t="n">
-        <v>3.6123321056366</v>
+        <v>3.61233186721802</v>
       </c>
       <c r="H84" t="n">
         <v>10</v>
@@ -2950,7 +2950,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>3.59366345405579</v>
+        <v>3.59366369247437</v>
       </c>
       <c r="H89" t="n">
         <v>19</v>
@@ -3008,7 +3008,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G91" t="n">
-        <v>3.6123321056366</v>
+        <v>3.61233186721802</v>
       </c>
       <c r="H91" t="n">
         <v>5</v>
@@ -3153,7 +3153,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G96" t="n">
-        <v>3.67767143249512</v>
+        <v>3.67767119407654</v>
       </c>
       <c r="H96" t="n">
         <v>9735</v>
@@ -3443,7 +3443,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G106" t="n">
-        <v>3.79901576042175</v>
+        <v>3.79901623725891</v>
       </c>
       <c r="H106" t="n">
         <v>10585</v>
@@ -3501,7 +3501,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G108" t="n">
-        <v>3.81768465042114</v>
+        <v>3.81768441200256</v>
       </c>
       <c r="H108" t="n">
         <v>7940</v>
@@ -3559,7 +3559,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G110" t="n">
-        <v>3.81768465042114</v>
+        <v>3.81768441200256</v>
       </c>
       <c r="H110" t="n">
         <v>41689</v>
@@ -3588,7 +3588,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>3.80835032463074</v>
+        <v>3.80834984779358</v>
       </c>
       <c r="H111" t="n">
         <v>19699</v>
@@ -3617,7 +3617,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G112" t="n">
-        <v>3.80835032463074</v>
+        <v>3.80834984779358</v>
       </c>
       <c r="H112" t="n">
         <v>17603</v>
@@ -3733,7 +3733,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G116" t="n">
-        <v>3.76167941093445</v>
+        <v>3.76167917251587</v>
       </c>
       <c r="H116" t="n">
         <v>40346</v>
@@ -3762,7 +3762,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>3.75234484672546</v>
+        <v>3.75234508514404</v>
       </c>
       <c r="H117" t="n">
         <v>7599</v>
@@ -3820,7 +3820,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G119" t="n">
-        <v>3.83635306358337</v>
+        <v>3.83635282516479</v>
       </c>
       <c r="H119" t="n">
         <v>11424</v>
@@ -3849,7 +3849,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>3.7803475856781</v>
+        <v>3.78034782409668</v>
       </c>
       <c r="H120" t="n">
         <v>12037</v>
@@ -3878,7 +3878,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G121" t="n">
-        <v>3.79901576042175</v>
+        <v>3.79901623725891</v>
       </c>
       <c r="H121" t="n">
         <v>12025</v>
@@ -3907,7 +3907,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G122" t="n">
-        <v>3.86435484886169</v>
+        <v>3.86435508728027</v>
       </c>
       <c r="H122" t="n">
         <v>44816</v>
@@ -3965,7 +3965,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G124" t="n">
-        <v>3.86435484886169</v>
+        <v>3.86435508728027</v>
       </c>
       <c r="H124" t="n">
         <v>15805</v>
@@ -4023,7 +4023,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G126" t="n">
-        <v>3.80835032463074</v>
+        <v>3.80834984779358</v>
       </c>
       <c r="H126" t="n">
         <v>1562</v>
@@ -4110,7 +4110,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G129" t="n">
-        <v>3.7803475856781</v>
+        <v>3.78034782409668</v>
       </c>
       <c r="H129" t="n">
         <v>535</v>
@@ -4139,7 +4139,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G130" t="n">
-        <v>3.7430112361908</v>
+        <v>3.74301075935364</v>
       </c>
       <c r="H130" t="n">
         <v>76762</v>
@@ -4197,7 +4197,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G132" t="n">
-        <v>3.84568667411804</v>
+        <v>3.8456871509552</v>
       </c>
       <c r="H132" t="n">
         <v>2547</v>
@@ -4429,7 +4429,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G140" t="n">
-        <v>3.93902850151062</v>
+        <v>3.9390287399292</v>
       </c>
       <c r="H140" t="n">
         <v>3505</v>
@@ -4545,7 +4545,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G144" t="n">
-        <v>3.93902850151062</v>
+        <v>3.9390287399292</v>
       </c>
       <c r="H144" t="n">
         <v>3005</v>
@@ -4661,7 +4661,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G148" t="n">
-        <v>3.95769715309143</v>
+        <v>3.95769667625427</v>
       </c>
       <c r="H148" t="n">
         <v>228432</v>
@@ -4777,7 +4777,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G152" t="n">
-        <v>4.27505970001221</v>
+        <v>4.27505922317505</v>
       </c>
       <c r="H152" t="n">
         <v>10712</v>
@@ -4835,7 +4835,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G154" t="n">
-        <v>4.35906744003296</v>
+        <v>4.35906791687012</v>
       </c>
       <c r="H154" t="n">
         <v>15474</v>
@@ -4864,7 +4864,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G155" t="n">
-        <v>4.40573835372925</v>
+        <v>4.40573787689209</v>
       </c>
       <c r="H155" t="n">
         <v>10834</v>
@@ -4893,7 +4893,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G156" t="n">
-        <v>4.46174335479736</v>
+        <v>4.46174383163452</v>
       </c>
       <c r="H156" t="n">
         <v>4570</v>
@@ -4922,7 +4922,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G157" t="n">
-        <v>4.40573835372925</v>
+        <v>4.40573787689209</v>
       </c>
       <c r="H157" t="n">
         <v>4479</v>
@@ -5009,7 +5009,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G160" t="n">
-        <v>4.23772287368774</v>
+        <v>4.23772239685059</v>
       </c>
       <c r="H160" t="n">
         <v>1012</v>
@@ -5038,7 +5038,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G161" t="n">
-        <v>4.17238330841064</v>
+        <v>4.17238283157349</v>
       </c>
       <c r="H161" t="n">
         <v>1389</v>
@@ -5067,7 +5067,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G162" t="n">
-        <v>4.14438104629517</v>
+        <v>4.14438056945801</v>
       </c>
       <c r="H162" t="n">
         <v>5657</v>
@@ -5154,7 +5154,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G165" t="n">
-        <v>4.10704469680786</v>
+        <v>4.1070442199707</v>
       </c>
       <c r="H165" t="n">
         <v>765</v>
@@ -5212,7 +5212,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G167" t="n">
-        <v>4.12571239471436</v>
+        <v>4.12571287155151</v>
       </c>
       <c r="H167" t="n">
         <v>1585</v>
@@ -5241,7 +5241,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>4.05103921890259</v>
+        <v>4.05103874206543</v>
       </c>
       <c r="H168" t="n">
         <v>499</v>
@@ -5270,7 +5270,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G169" t="n">
-        <v>4.14438104629517</v>
+        <v>4.14438056945801</v>
       </c>
       <c r="H169" t="n">
         <v>4433</v>
@@ -5328,7 +5328,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G171" t="n">
-        <v>4.15371465682983</v>
+        <v>4.15371513366699</v>
       </c>
       <c r="H171" t="n">
         <v>3578</v>
@@ -5386,7 +5386,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G173" t="n">
-        <v>4.06037282943726</v>
+        <v>4.06037330627441</v>
       </c>
       <c r="H173" t="n">
         <v>6766</v>
@@ -5415,7 +5415,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G174" t="n">
-        <v>3.59366345405579</v>
+        <v>3.59366369247437</v>
       </c>
       <c r="H174" t="n">
         <v>11092</v>
@@ -5647,7 +5647,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G182" t="n">
-        <v>3.3883113861084</v>
+        <v>3.38831162452698</v>
       </c>
       <c r="H182" t="n">
         <v>4453</v>
@@ -5705,7 +5705,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14562249183655</v>
+        <v>3.14562225341797</v>
       </c>
       <c r="H184" t="n">
         <v>4305</v>
@@ -5821,7 +5821,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G188" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H188" t="n">
         <v>6941</v>
@@ -5850,7 +5850,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G189" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G190" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H190" t="n">
         <v>500</v>
@@ -5908,7 +5908,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G191" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -5937,7 +5937,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G192" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -6169,7 +6169,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G200" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H200" t="n">
         <v>925</v>
@@ -6198,7 +6198,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G201" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H201" t="n">
         <v>93</v>
@@ -6430,7 +6430,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G209" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H209" t="n">
         <v>865</v>
@@ -6575,7 +6575,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G214" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H214" t="n">
         <v>7441</v>
@@ -6691,7 +6691,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G218" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H218" t="n">
         <v>488</v>
@@ -6894,7 +6894,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G225" t="n">
-        <v>2.73491835594177</v>
+        <v>2.73491811752319</v>
       </c>
       <c r="H225" t="n">
         <v>823</v>
@@ -6952,7 +6952,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G227" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H227" t="n">
         <v>6933</v>
@@ -6981,7 +6981,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G228" t="n">
-        <v>2.68824696540833</v>
+        <v>2.6882472038269</v>
       </c>
       <c r="H228" t="n">
         <v>942</v>
@@ -7010,7 +7010,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G229" t="n">
-        <v>2.68824696540833</v>
+        <v>2.6882472038269</v>
       </c>
       <c r="H229" t="n">
         <v>5</v>
@@ -7155,7 +7155,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G234" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H234" t="n">
         <v>252</v>
@@ -7329,7 +7329,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G240" t="n">
-        <v>2.82826018333435</v>
+        <v>2.82825994491577</v>
       </c>
       <c r="H240" t="n">
         <v>950</v>
@@ -7474,7 +7474,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G245" t="n">
-        <v>2.82826018333435</v>
+        <v>2.82825994491577</v>
       </c>
       <c r="H245" t="n">
         <v>1750</v>
@@ -7503,7 +7503,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G246" t="n">
-        <v>3.01494383811951</v>
+        <v>3.01494359970093</v>
       </c>
       <c r="H246" t="n">
         <v>3050</v>
@@ -7561,7 +7561,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G248" t="n">
-        <v>2.97760701179504</v>
+        <v>2.97760725021362</v>
       </c>
       <c r="H248" t="n">
         <v>6756</v>
@@ -7648,7 +7648,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G251" t="n">
-        <v>2.78158926963806</v>
+        <v>2.78158903121948</v>
       </c>
       <c r="H251" t="n">
         <v>411</v>
@@ -7706,7 +7706,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G253" t="n">
-        <v>2.82826018333435</v>
+        <v>2.82825994491577</v>
       </c>
       <c r="H253" t="n">
         <v>19598</v>
@@ -7735,7 +7735,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G254" t="n">
-        <v>2.82826018333435</v>
+        <v>2.82825994491577</v>
       </c>
       <c r="H254" t="n">
         <v>2500</v>
@@ -7822,7 +7822,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G257" t="n">
-        <v>2.78158926963806</v>
+        <v>2.78158903121948</v>
       </c>
       <c r="H257" t="n">
         <v>9597</v>
@@ -8315,7 +8315,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G274" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H274" t="n">
         <v>12686</v>
@@ -8344,7 +8344,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G275" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H275" t="n">
         <v>3412</v>
@@ -8402,7 +8402,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G277" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H277" t="n">
         <v>689</v>
@@ -8431,7 +8431,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G278" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H278" t="n">
         <v>0</v>
@@ -8460,7 +8460,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G279" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H279" t="n">
         <v>1890</v>
@@ -8518,7 +8518,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G281" t="n">
-        <v>2.47356081008911</v>
+        <v>2.47356104850769</v>
       </c>
       <c r="H281" t="n">
         <v>1069</v>
@@ -8605,7 +8605,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G284" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H284" t="n">
         <v>550</v>
@@ -8634,7 +8634,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G285" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H285" t="n">
         <v>437</v>
@@ -8663,7 +8663,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G286" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H286" t="n">
         <v>155</v>
@@ -8721,7 +8721,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G288" t="n">
-        <v>2.35221600532532</v>
+        <v>2.3522162437439</v>
       </c>
       <c r="H288" t="n">
         <v>1176</v>
@@ -8982,7 +8982,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G297" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H297" t="n">
         <v>238</v>
@@ -9011,7 +9011,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G298" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H298" t="n">
         <v>0</v>
@@ -9098,7 +9098,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G301" t="n">
-        <v>2.47356081008911</v>
+        <v>2.47356104850769</v>
       </c>
       <c r="H301" t="n">
         <v>9559</v>
@@ -9127,7 +9127,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G302" t="n">
-        <v>2.47356081008911</v>
+        <v>2.47356104850769</v>
       </c>
       <c r="H302" t="n">
         <v>2820</v>
@@ -9301,7 +9301,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G308" t="n">
-        <v>2.46422672271729</v>
+        <v>2.46422648429871</v>
       </c>
       <c r="H308" t="n">
         <v>982</v>
@@ -9359,7 +9359,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G310" t="n">
-        <v>2.47356081008911</v>
+        <v>2.47356104850769</v>
       </c>
       <c r="H310" t="n">
         <v>1449</v>
@@ -9446,7 +9446,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G313" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H313" t="n">
         <v>350</v>
@@ -9504,7 +9504,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G315" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H315" t="n">
         <v>500</v>
@@ -9533,7 +9533,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G316" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H316" t="n">
         <v>2033</v>
@@ -9562,7 +9562,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G317" t="n">
-        <v>2.35221600532532</v>
+        <v>2.3522162437439</v>
       </c>
       <c r="H317" t="n">
         <v>5</v>
@@ -9591,7 +9591,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G318" t="n">
-        <v>2.35221600532532</v>
+        <v>2.3522162437439</v>
       </c>
       <c r="H318" t="n">
         <v>5</v>
@@ -9620,7 +9620,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G319" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H319" t="n">
         <v>50</v>
@@ -9649,7 +9649,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G320" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H320" t="n">
         <v>110</v>
@@ -9736,7 +9736,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G323" t="n">
-        <v>2.30554509162903</v>
+        <v>2.30554533004761</v>
       </c>
       <c r="H323" t="n">
         <v>2155</v>
@@ -9765,7 +9765,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G324" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H324" t="n">
         <v>1280</v>
@@ -9794,7 +9794,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G325" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G326" t="n">
-        <v>2.36155033111572</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H326" t="n">
         <v>4022</v>
@@ -9852,7 +9852,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H327" t="n">
         <v>7005</v>
@@ -9910,7 +9910,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G329" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H329" t="n">
         <v>2690</v>
@@ -9939,7 +9939,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G330" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -9968,7 +9968,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G331" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -10084,7 +10084,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G335" t="n">
-        <v>2.30554509162903</v>
+        <v>2.30554533004761</v>
       </c>
       <c r="H335" t="n">
         <v>15682</v>
@@ -10113,7 +10113,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G336" t="n">
-        <v>2.26820874214172</v>
+        <v>2.26820850372314</v>
       </c>
       <c r="H336" t="n">
         <v>12996</v>
@@ -10171,7 +10171,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>2.19353485107422</v>
+        <v>2.1935350894928</v>
       </c>
       <c r="H338" t="n">
         <v>17797</v>
@@ -10229,7 +10229,7 @@
         <v>2.25</v>
       </c>
       <c r="G340" t="n">
-        <v>2.10019302368164</v>
+        <v>2.10019326210022</v>
       </c>
       <c r="H340" t="n">
         <v>17080</v>
@@ -10258,7 +10258,7 @@
         <v>2.25</v>
       </c>
       <c r="G341" t="n">
-        <v>2.10019302368164</v>
+        <v>2.10019326210022</v>
       </c>
       <c r="H341" t="n">
         <v>6035</v>
@@ -10287,7 +10287,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>2.06285619735718</v>
+        <v>2.06285643577576</v>
       </c>
       <c r="H342" t="n">
         <v>15756</v>
@@ -10316,7 +10316,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G343" t="n">
-        <v>1.98818290233612</v>
+        <v>1.98818302154541</v>
       </c>
       <c r="H343" t="n">
         <v>9524</v>
@@ -10345,7 +10345,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G344" t="n">
-        <v>1.92284333705902</v>
+        <v>1.9228435754776</v>
       </c>
       <c r="H344" t="n">
         <v>5020</v>
@@ -10374,7 +10374,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G345" t="n">
-        <v>1.87617242336273</v>
+        <v>1.87617254257202</v>
       </c>
       <c r="H345" t="n">
         <v>10119</v>
@@ -10490,7 +10490,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G349" t="n">
-        <v>1.6941556930542</v>
+        <v>1.69415581226349</v>
       </c>
       <c r="H349" t="n">
         <v>7852</v>
@@ -10519,7 +10519,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G350" t="n">
-        <v>1.68015444278717</v>
+        <v>1.68015432357788</v>
       </c>
       <c r="H350" t="n">
         <v>3654</v>
@@ -10548,7 +10548,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G351" t="n">
-        <v>1.57747840881348</v>
+        <v>1.57747852802277</v>
       </c>
       <c r="H351" t="n">
         <v>44141</v>
@@ -10577,7 +10577,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G352" t="n">
-        <v>1.5308073759079</v>
+        <v>1.53080725669861</v>
       </c>
       <c r="H352" t="n">
         <v>32342</v>
@@ -10606,7 +10606,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G353" t="n">
-        <v>1.50747191905975</v>
+        <v>1.50747179985046</v>
       </c>
       <c r="H353" t="n">
         <v>17138</v>
@@ -10780,7 +10780,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G359" t="n">
-        <v>1.58681261539459</v>
+        <v>1.5868124961853</v>
       </c>
       <c r="H359" t="n">
         <v>162717</v>
@@ -10954,7 +10954,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G365" t="n">
-        <v>1.94151175022125</v>
+        <v>1.94151163101196</v>
       </c>
       <c r="H365" t="n">
         <v>38866</v>
@@ -10983,7 +10983,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G366" t="n">
-        <v>2.02551960945129</v>
+        <v>2.02551937103271</v>
       </c>
       <c r="H366" t="n">
         <v>41167</v>
@@ -11012,7 +11012,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G367" t="n">
-        <v>2.06285619735718</v>
+        <v>2.06285643577576</v>
       </c>
       <c r="H367" t="n">
         <v>65581</v>
@@ -11041,7 +11041,7 @@
         <v>2.25</v>
       </c>
       <c r="G368" t="n">
-        <v>2.10019302368164</v>
+        <v>2.10019326210022</v>
       </c>
       <c r="H368" t="n">
         <v>40808</v>
@@ -11157,7 +11157,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G372" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H372" t="n">
         <v>100574</v>
@@ -11186,7 +11186,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G373" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H373" t="n">
         <v>50734</v>
@@ -11215,7 +11215,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G374" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H374" t="n">
         <v>32104</v>
@@ -11273,7 +11273,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G376" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H376" t="n">
         <v>260524</v>
@@ -11360,7 +11360,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G379" t="n">
-        <v>2.55756831169128</v>
+        <v>2.55756855010986</v>
       </c>
       <c r="H379" t="n">
         <v>77697</v>
@@ -11418,7 +11418,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G381" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H381" t="n">
         <v>13489</v>
@@ -11476,7 +11476,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G383" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H383" t="n">
         <v>19181</v>
@@ -11505,7 +11505,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G384" t="n">
-        <v>2.36155033111572</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H384" t="n">
         <v>46528</v>
@@ -11592,7 +11592,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G387" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H387" t="n">
         <v>20692</v>
@@ -11621,7 +11621,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G388" t="n">
-        <v>2.30554509162903</v>
+        <v>2.30554533004761</v>
       </c>
       <c r="H388" t="n">
         <v>7571</v>
@@ -11650,7 +11650,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G389" t="n">
-        <v>2.35221600532532</v>
+        <v>2.3522162437439</v>
       </c>
       <c r="H389" t="n">
         <v>11526</v>
@@ -11737,7 +11737,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G392" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H392" t="n">
         <v>78496</v>
@@ -11766,7 +11766,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G393" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H393" t="n">
         <v>2710</v>
@@ -11795,7 +11795,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G394" t="n">
-        <v>2.47356081008911</v>
+        <v>2.47356104850769</v>
       </c>
       <c r="H394" t="n">
         <v>21034</v>
@@ -11853,7 +11853,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G396" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H396" t="n">
         <v>3361</v>
@@ -11911,7 +11911,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H398" t="n">
         <v>4671</v>
@@ -11940,7 +11940,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G399" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H399" t="n">
         <v>20075</v>
@@ -11969,7 +11969,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G400" t="n">
-        <v>2.20286917686462</v>
+        <v>2.20286893844604</v>
       </c>
       <c r="H400" t="n">
         <v>35084</v>
@@ -11998,7 +11998,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G401" t="n">
-        <v>2.07219052314758</v>
+        <v>2.072190284729</v>
       </c>
       <c r="H401" t="n">
         <v>51398</v>
@@ -12056,7 +12056,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G403" t="n">
-        <v>2.17486643791199</v>
+        <v>2.17486667633057</v>
       </c>
       <c r="H403" t="n">
         <v>18632</v>
@@ -12085,7 +12085,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G404" t="n">
-        <v>2.17486643791199</v>
+        <v>2.17486667633057</v>
       </c>
       <c r="H404" t="n">
         <v>10603</v>
@@ -12114,7 +12114,7 @@
         <v>2.25</v>
       </c>
       <c r="G405" t="n">
-        <v>2.10019302368164</v>
+        <v>2.10019326210022</v>
       </c>
       <c r="H405" t="n">
         <v>50986</v>
@@ -12143,7 +12143,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G406" t="n">
-        <v>2.05352234840393</v>
+        <v>2.05352210998535</v>
       </c>
       <c r="H406" t="n">
         <v>51628</v>
@@ -12172,7 +12172,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G407" t="n">
-        <v>2.19353485107422</v>
+        <v>2.1935350894928</v>
       </c>
       <c r="H407" t="n">
         <v>30243</v>
@@ -12201,7 +12201,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G408" t="n">
-        <v>2.20286917686462</v>
+        <v>2.20286893844604</v>
       </c>
       <c r="H408" t="n">
         <v>20357</v>
@@ -12259,7 +12259,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G410" t="n">
-        <v>2.05352234840393</v>
+        <v>2.05352210998535</v>
       </c>
       <c r="H410" t="n">
         <v>55928</v>
@@ -12288,7 +12288,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G411" t="n">
-        <v>2.05352234840393</v>
+        <v>2.05352210998535</v>
       </c>
       <c r="H411" t="n">
         <v>27870</v>
@@ -12317,7 +12317,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G412" t="n">
-        <v>2.05352234840393</v>
+        <v>2.05352210998535</v>
       </c>
       <c r="H412" t="n">
         <v>10965</v>
@@ -12346,7 +12346,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G413" t="n">
-        <v>2.05352234840393</v>
+        <v>2.05352210998535</v>
       </c>
       <c r="H413" t="n">
         <v>6880</v>
@@ -12404,7 +12404,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G415" t="n">
-        <v>2.18420076370239</v>
+        <v>2.18420052528381</v>
       </c>
       <c r="H415" t="n">
         <v>21434</v>
@@ -12462,7 +12462,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G417" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H417" t="n">
         <v>112741</v>
@@ -12491,7 +12491,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G418" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H418" t="n">
         <v>31183</v>
@@ -12636,7 +12636,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G423" t="n">
-        <v>2.30554509162903</v>
+        <v>2.30554533004761</v>
       </c>
       <c r="H423" t="n">
         <v>13773</v>
@@ -12665,7 +12665,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G424" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H424" t="n">
         <v>4139</v>
@@ -12694,7 +12694,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G425" t="n">
-        <v>2.30554509162903</v>
+        <v>2.30554533004761</v>
       </c>
       <c r="H425" t="n">
         <v>12103</v>
@@ -12723,7 +12723,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G426" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H426" t="n">
         <v>6863</v>
@@ -12752,7 +12752,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G427" t="n">
-        <v>2.26820874214172</v>
+        <v>2.26820850372314</v>
       </c>
       <c r="H427" t="n">
         <v>8209</v>
@@ -12810,7 +12810,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G429" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H429" t="n">
         <v>17663</v>
@@ -12984,7 +12984,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G435" t="n">
-        <v>2.24954032897949</v>
+        <v>2.24954009056091</v>
       </c>
       <c r="H435" t="n">
         <v>1950</v>
@@ -13042,7 +13042,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G437" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H437" t="n">
         <v>10145</v>
@@ -13216,7 +13216,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G443" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H443" t="n">
         <v>10240</v>
@@ -13245,7 +13245,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G444" t="n">
-        <v>2.24954032897949</v>
+        <v>2.24954009056091</v>
       </c>
       <c r="H444" t="n">
         <v>11540</v>
@@ -13274,7 +13274,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G445" t="n">
-        <v>2.23087167739868</v>
+        <v>2.23087191581726</v>
       </c>
       <c r="H445" t="n">
         <v>29277</v>
@@ -13303,7 +13303,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G446" t="n">
-        <v>2.23087167739868</v>
+        <v>2.23087191581726</v>
       </c>
       <c r="H446" t="n">
         <v>37961</v>
@@ -13361,7 +13361,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G448" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H448" t="n">
         <v>75506</v>
@@ -13390,7 +13390,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G449" t="n">
-        <v>2.44555830955505</v>
+        <v>2.44555807113647</v>
       </c>
       <c r="H449" t="n">
         <v>23869</v>
@@ -13419,7 +13419,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G450" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H450" t="n">
         <v>45849</v>
@@ -13506,7 +13506,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G453" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H453" t="n">
         <v>35893</v>
@@ -13535,7 +13535,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G454" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H454" t="n">
         <v>25836</v>
@@ -13709,7 +13709,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G460" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H460" t="n">
         <v>44981</v>
@@ -13738,7 +13738,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G461" t="n">
-        <v>2.73491835594177</v>
+        <v>2.73491811752319</v>
       </c>
       <c r="H461" t="n">
         <v>18508</v>
@@ -13854,7 +13854,7 @@
         <v>3.25</v>
       </c>
       <c r="G465" t="n">
-        <v>3.03361225128174</v>
+        <v>3.03361201286316</v>
       </c>
       <c r="H465" t="n">
         <v>83242</v>
@@ -13883,7 +13883,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G466" t="n">
-        <v>3.05228042602539</v>
+        <v>3.05228066444397</v>
       </c>
       <c r="H466" t="n">
         <v>208563</v>
@@ -13912,7 +13912,7 @@
         <v>3.25</v>
       </c>
       <c r="G467" t="n">
-        <v>3.03361225128174</v>
+        <v>3.03361201286316</v>
       </c>
       <c r="H467" t="n">
         <v>62595</v>
@@ -13970,7 +13970,7 @@
         <v>3.25</v>
       </c>
       <c r="G469" t="n">
-        <v>3.03361225128174</v>
+        <v>3.03361201286316</v>
       </c>
       <c r="H469" t="n">
         <v>22979</v>
@@ -14086,7 +14086,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G473" t="n">
-        <v>3.3323061466217</v>
+        <v>3.33230638504028</v>
       </c>
       <c r="H473" t="n">
         <v>14421</v>
@@ -14115,7 +14115,7 @@
         <v>3.5</v>
       </c>
       <c r="G474" t="n">
-        <v>3.26696681976318</v>
+        <v>3.26696705818176</v>
       </c>
       <c r="H474" t="n">
         <v>42504</v>
@@ -14173,7 +14173,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>3.17362523078918</v>
+        <v>3.17362499237061</v>
       </c>
       <c r="H476" t="n">
         <v>25140</v>
@@ -14260,7 +14260,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G479" t="n">
-        <v>3.16429114341736</v>
+        <v>3.16429090499878</v>
       </c>
       <c r="H479" t="n">
         <v>22442</v>
@@ -14289,7 +14289,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G480" t="n">
-        <v>3.20162773132324</v>
+        <v>3.20162796974182</v>
       </c>
       <c r="H480" t="n">
         <v>55118</v>
@@ -14318,7 +14318,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G481" t="n">
-        <v>3.14562249183655</v>
+        <v>3.14562225341797</v>
       </c>
       <c r="H481" t="n">
         <v>17292</v>
@@ -14434,7 +14434,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G485" t="n">
-        <v>3.15495681762695</v>
+        <v>3.15495705604553</v>
       </c>
       <c r="H485" t="n">
         <v>12813</v>
@@ -14463,7 +14463,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G486" t="n">
-        <v>3.17362523078918</v>
+        <v>3.17362499237061</v>
       </c>
       <c r="H486" t="n">
         <v>33087</v>
@@ -14521,7 +14521,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G488" t="n">
-        <v>3.16429114341736</v>
+        <v>3.16429090499878</v>
       </c>
       <c r="H488" t="n">
         <v>32411</v>
@@ -14637,7 +14637,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G492" t="n">
-        <v>2.97760701179504</v>
+        <v>2.97760725021362</v>
       </c>
       <c r="H492" t="n">
         <v>12648</v>
@@ -14898,7 +14898,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G501" t="n">
-        <v>3.0616147518158</v>
+        <v>3.06161451339722</v>
       </c>
       <c r="H501" t="n">
         <v>13910</v>
@@ -14956,7 +14956,7 @@
         <v>3.25</v>
       </c>
       <c r="G503" t="n">
-        <v>3.03361225128174</v>
+        <v>3.03361201286316</v>
       </c>
       <c r="H503" t="n">
         <v>5248</v>
@@ -15014,7 +15014,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G505" t="n">
-        <v>3.0056095123291</v>
+        <v>3.00560975074768</v>
       </c>
       <c r="H505" t="n">
         <v>10540</v>
@@ -15130,7 +15130,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G509" t="n">
-        <v>2.9682731628418</v>
+        <v>2.96827292442322</v>
       </c>
       <c r="H509" t="n">
         <v>5868</v>
@@ -15159,7 +15159,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G510" t="n">
-        <v>3.0056095123291</v>
+        <v>3.00560975074768</v>
       </c>
       <c r="H510" t="n">
         <v>10066</v>
@@ -15188,7 +15188,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G511" t="n">
-        <v>2.74425220489502</v>
+        <v>2.7442524433136</v>
       </c>
       <c r="H511" t="n">
         <v>47993</v>
@@ -15217,7 +15217,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G512" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H512" t="n">
         <v>87951</v>
@@ -15275,7 +15275,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G514" t="n">
-        <v>2.78158926963806</v>
+        <v>2.78158903121948</v>
       </c>
       <c r="H514" t="n">
         <v>5508</v>
@@ -15333,7 +15333,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G516" t="n">
-        <v>2.74425220489502</v>
+        <v>2.7442524433136</v>
       </c>
       <c r="H516" t="n">
         <v>7255</v>
@@ -15391,7 +15391,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G518" t="n">
-        <v>2.73491835594177</v>
+        <v>2.73491811752319</v>
       </c>
       <c r="H518" t="n">
         <v>15415</v>
@@ -15420,7 +15420,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G519" t="n">
-        <v>2.74425220489502</v>
+        <v>2.7442524433136</v>
       </c>
       <c r="H519" t="n">
         <v>22223</v>
@@ -15449,7 +15449,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G520" t="n">
-        <v>2.74425220489502</v>
+        <v>2.7442524433136</v>
       </c>
       <c r="H520" t="n">
         <v>5309</v>
@@ -15507,7 +15507,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G522" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H522" t="n">
         <v>18120</v>
@@ -15652,7 +15652,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G527" t="n">
-        <v>2.55756831169128</v>
+        <v>2.55756855010986</v>
       </c>
       <c r="H527" t="n">
         <v>18295</v>
@@ -15710,7 +15710,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G529" t="n">
-        <v>2.46422672271729</v>
+        <v>2.46422648429871</v>
       </c>
       <c r="H529" t="n">
         <v>31873</v>
@@ -15768,7 +15768,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G531" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H531" t="n">
         <v>29110</v>
@@ -15797,7 +15797,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G532" t="n">
-        <v>2.46422672271729</v>
+        <v>2.46422648429871</v>
       </c>
       <c r="H532" t="n">
         <v>14070</v>
@@ -15855,7 +15855,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G534" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H534" t="n">
         <v>58949</v>
@@ -15884,7 +15884,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G535" t="n">
-        <v>2.53890013694763</v>
+        <v>2.53890037536621</v>
       </c>
       <c r="H535" t="n">
         <v>31474</v>
@@ -15942,7 +15942,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G537" t="n">
-        <v>2.55756831169128</v>
+        <v>2.55756855010986</v>
       </c>
       <c r="H537" t="n">
         <v>10130</v>
@@ -16087,7 +16087,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G542" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H542" t="n">
         <v>34564</v>
@@ -16174,7 +16174,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G545" t="n">
-        <v>2.68824696540833</v>
+        <v>2.6882472038269</v>
       </c>
       <c r="H545" t="n">
         <v>33684</v>
@@ -16290,7 +16290,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G549" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H549" t="n">
         <v>9940</v>
@@ -16348,7 +16348,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G551" t="n">
-        <v>2.68824696540833</v>
+        <v>2.6882472038269</v>
       </c>
       <c r="H551" t="n">
         <v>21133</v>
@@ -16638,7 +16638,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G561" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H561" t="n">
         <v>55511</v>
@@ -16754,7 +16754,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G565" t="n">
-        <v>2.78158926963806</v>
+        <v>2.78158903121948</v>
       </c>
       <c r="H565" t="n">
         <v>5626</v>
@@ -16841,7 +16841,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G568" t="n">
-        <v>2.78158926963806</v>
+        <v>2.78158903121948</v>
       </c>
       <c r="H568" t="n">
         <v>6622</v>
@@ -16928,7 +16928,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G571" t="n">
-        <v>2.82826018333435</v>
+        <v>2.82825994491577</v>
       </c>
       <c r="H571" t="n">
         <v>2855</v>
@@ -17073,7 +17073,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G576" t="n">
-        <v>2.74425220489502</v>
+        <v>2.7442524433136</v>
       </c>
       <c r="H576" t="n">
         <v>4135</v>
@@ -17102,7 +17102,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G577" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H577" t="n">
         <v>5655</v>
@@ -17131,7 +17131,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G578" t="n">
-        <v>2.82826018333435</v>
+        <v>2.82825994491577</v>
       </c>
       <c r="H578" t="n">
         <v>6954</v>
@@ -17160,7 +17160,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G579" t="n">
-        <v>2.78158926963806</v>
+        <v>2.78158903121948</v>
       </c>
       <c r="H579" t="n">
         <v>2133</v>
@@ -17305,7 +17305,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G584" t="n">
-        <v>2.78158926963806</v>
+        <v>2.78158903121948</v>
       </c>
       <c r="H584" t="n">
         <v>6045</v>
@@ -17334,7 +17334,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G585" t="n">
-        <v>2.78158926963806</v>
+        <v>2.78158903121948</v>
       </c>
       <c r="H585" t="n">
         <v>1601</v>
@@ -17450,7 +17450,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G589" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H589" t="n">
         <v>5281</v>
@@ -17595,7 +17595,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G594" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H594" t="n">
         <v>3352</v>
@@ -17740,7 +17740,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G599" t="n">
-        <v>2.74425220489502</v>
+        <v>2.7442524433136</v>
       </c>
       <c r="H599" t="n">
         <v>13898</v>
@@ -17798,7 +17798,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G601" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H601" t="n">
         <v>11543</v>
@@ -17827,7 +17827,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G602" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H602" t="n">
         <v>22041</v>
@@ -17856,7 +17856,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G603" t="n">
-        <v>2.73491835594177</v>
+        <v>2.73491811752319</v>
       </c>
       <c r="H603" t="n">
         <v>6297</v>
@@ -17885,7 +17885,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G604" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H604" t="n">
         <v>5168</v>
@@ -17914,7 +17914,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G605" t="n">
-        <v>2.68824696540833</v>
+        <v>2.6882472038269</v>
       </c>
       <c r="H605" t="n">
         <v>2829</v>
@@ -17943,7 +17943,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H606" t="n">
         <v>1325</v>
@@ -17972,7 +17972,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G607" t="n">
-        <v>2.74425220489502</v>
+        <v>2.7442524433136</v>
       </c>
       <c r="H607" t="n">
         <v>1800</v>
@@ -18001,7 +18001,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G608" t="n">
-        <v>2.78158926963806</v>
+        <v>2.78158903121948</v>
       </c>
       <c r="H608" t="n">
         <v>7882</v>
@@ -18088,7 +18088,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G611" t="n">
-        <v>2.82826018333435</v>
+        <v>2.82825994491577</v>
       </c>
       <c r="H611" t="n">
         <v>2800</v>
@@ -18146,7 +18146,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G613" t="n">
-        <v>2.82826018333435</v>
+        <v>2.82825994491577</v>
       </c>
       <c r="H613" t="n">
         <v>7360</v>
@@ -18204,7 +18204,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G615" t="n">
-        <v>2.78158926963806</v>
+        <v>2.78158903121948</v>
       </c>
       <c r="H615" t="n">
         <v>21813</v>
@@ -18407,7 +18407,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G622" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H622" t="n">
         <v>9853</v>
@@ -18465,7 +18465,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G624" t="n">
-        <v>2.47356081008911</v>
+        <v>2.47356104850769</v>
       </c>
       <c r="H624" t="n">
         <v>17921</v>
@@ -18581,7 +18581,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G628" t="n">
-        <v>2.47356081008911</v>
+        <v>2.47356104850769</v>
       </c>
       <c r="H628" t="n">
         <v>7127</v>
@@ -18610,7 +18610,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G629" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H629" t="n">
         <v>9381</v>
@@ -18842,7 +18842,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G637" t="n">
-        <v>2.53890013694763</v>
+        <v>2.53890037536621</v>
       </c>
       <c r="H637" t="n">
         <v>7036</v>
@@ -18871,7 +18871,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G638" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H638" t="n">
         <v>10004</v>
@@ -18987,7 +18987,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G642" t="n">
-        <v>2.47356081008911</v>
+        <v>2.47356104850769</v>
       </c>
       <c r="H642" t="n">
         <v>25000</v>
@@ -19016,7 +19016,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G643" t="n">
-        <v>2.44555830955505</v>
+        <v>2.44555807113647</v>
       </c>
       <c r="H643" t="n">
         <v>4300</v>
@@ -19074,7 +19074,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G645" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H645" t="n">
         <v>26536</v>
@@ -19161,7 +19161,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G648" t="n">
-        <v>2.53890013694763</v>
+        <v>2.53890037536621</v>
       </c>
       <c r="H648" t="n">
         <v>20795</v>
@@ -19190,7 +19190,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G649" t="n">
-        <v>2.53890013694763</v>
+        <v>2.53890037536621</v>
       </c>
       <c r="H649" t="n">
         <v>26026</v>
@@ -19219,7 +19219,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G650" t="n">
-        <v>2.55756831169128</v>
+        <v>2.55756855010986</v>
       </c>
       <c r="H650" t="n">
         <v>3999</v>
@@ -19364,7 +19364,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G655" t="n">
-        <v>2.47356081008911</v>
+        <v>2.47356104850769</v>
       </c>
       <c r="H655" t="n">
         <v>1680</v>
@@ -19422,7 +19422,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G657" t="n">
-        <v>2.53890013694763</v>
+        <v>2.53890037536621</v>
       </c>
       <c r="H657" t="n">
         <v>8536</v>
@@ -19509,7 +19509,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G660" t="n">
-        <v>2.55756831169128</v>
+        <v>2.55756855010986</v>
       </c>
       <c r="H660" t="n">
         <v>5009</v>
@@ -19567,7 +19567,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G662" t="n">
-        <v>2.53890013694763</v>
+        <v>2.53890037536621</v>
       </c>
       <c r="H662" t="n">
         <v>18926</v>
@@ -19625,7 +19625,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G664" t="n">
-        <v>2.55756831169128</v>
+        <v>2.55756855010986</v>
       </c>
       <c r="H664" t="n">
         <v>2957</v>
@@ -19654,7 +19654,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G665" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H665" t="n">
         <v>1580</v>
@@ -19915,7 +19915,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G674" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H674" t="n">
         <v>1004</v>
@@ -19944,7 +19944,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G675" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H675" t="n">
         <v>0</v>
@@ -20031,7 +20031,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G678" t="n">
-        <v>2.55756831169128</v>
+        <v>2.55756855010986</v>
       </c>
       <c r="H678" t="n">
         <v>1348</v>
@@ -20060,7 +20060,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G679" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H679" t="n">
         <v>6131</v>
@@ -20089,7 +20089,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G680" t="n">
-        <v>2.55756831169128</v>
+        <v>2.55756855010986</v>
       </c>
       <c r="H680" t="n">
         <v>6365</v>
@@ -20118,7 +20118,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G681" t="n">
-        <v>2.53890013694763</v>
+        <v>2.53890037536621</v>
       </c>
       <c r="H681" t="n">
         <v>1200</v>
@@ -20350,7 +20350,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G689" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H689" t="n">
         <v>6459</v>
@@ -20379,7 +20379,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G690" t="n">
-        <v>2.30554509162903</v>
+        <v>2.30554533004761</v>
       </c>
       <c r="H690" t="n">
         <v>15886</v>
@@ -20466,7 +20466,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G693" t="n">
-        <v>2.14686393737793</v>
+        <v>2.14686417579651</v>
       </c>
       <c r="H693" t="n">
         <v>5992</v>
@@ -20524,7 +20524,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G695" t="n">
-        <v>2.23087167739868</v>
+        <v>2.23087191581726</v>
       </c>
       <c r="H695" t="n">
         <v>25461</v>
@@ -20553,7 +20553,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G696" t="n">
-        <v>2.30554509162903</v>
+        <v>2.30554533004761</v>
       </c>
       <c r="H696" t="n">
         <v>8721</v>
@@ -20611,7 +20611,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G698" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H698" t="n">
         <v>4617</v>
@@ -20669,7 +20669,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G700" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H700" t="n">
         <v>10078</v>
@@ -20814,7 +20814,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G705" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H705" t="n">
         <v>7231</v>
@@ -20843,7 +20843,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G706" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H706" t="n">
         <v>16794</v>
@@ -20872,7 +20872,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G707" t="n">
-        <v>2.44555830955505</v>
+        <v>2.44555807113647</v>
       </c>
       <c r="H707" t="n">
         <v>8593</v>
@@ -20901,7 +20901,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G708" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H708" t="n">
         <v>11650</v>
@@ -20930,7 +20930,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G709" t="n">
-        <v>2.44555830955505</v>
+        <v>2.44555807113647</v>
       </c>
       <c r="H709" t="n">
         <v>3150</v>
@@ -21046,7 +21046,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G713" t="n">
-        <v>2.36155033111572</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H713" t="n">
         <v>5601</v>
@@ -21075,7 +21075,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G714" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H714" t="n">
         <v>3865</v>
@@ -21104,7 +21104,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G715" t="n">
-        <v>2.35221600532532</v>
+        <v>2.3522162437439</v>
       </c>
       <c r="H715" t="n">
         <v>10111</v>
@@ -21133,7 +21133,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G716" t="n">
-        <v>2.35221600532532</v>
+        <v>2.3522162437439</v>
       </c>
       <c r="H716" t="n">
         <v>0</v>
@@ -21162,7 +21162,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G717" t="n">
-        <v>2.35221600532532</v>
+        <v>2.3522162437439</v>
       </c>
       <c r="H717" t="n">
         <v>6146</v>
@@ -21191,7 +21191,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G718" t="n">
-        <v>2.35221600532532</v>
+        <v>2.3522162437439</v>
       </c>
       <c r="H718" t="n">
         <v>0</v>
@@ -21220,7 +21220,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G719" t="n">
-        <v>2.35221600532532</v>
+        <v>2.3522162437439</v>
       </c>
       <c r="H719" t="n">
         <v>610</v>
@@ -21249,7 +21249,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G720" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H720" t="n">
         <v>2110</v>
@@ -21307,7 +21307,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G722" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H722" t="n">
         <v>20</v>
@@ -21336,7 +21336,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G723" t="n">
-        <v>2.35221600532532</v>
+        <v>2.3522162437439</v>
       </c>
       <c r="H723" t="n">
         <v>585</v>
@@ -21365,7 +21365,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G724" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H724" t="n">
         <v>3000</v>
@@ -21394,7 +21394,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G725" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H725" t="n">
         <v>2583</v>
@@ -21423,7 +21423,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G726" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H726" t="n">
         <v>2</v>
@@ -21452,7 +21452,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G727" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H727" t="n">
         <v>4770</v>
@@ -21481,7 +21481,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G728" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H728" t="n">
         <v>6795</v>
@@ -21539,7 +21539,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G730" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H730" t="n">
         <v>9829</v>
@@ -21655,7 +21655,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G734" t="n">
-        <v>2.36155033111572</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H734" t="n">
         <v>59751</v>
@@ -21771,7 +21771,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G738" t="n">
-        <v>2.18420076370239</v>
+        <v>2.18420052528381</v>
       </c>
       <c r="H738" t="n">
         <v>10750</v>
@@ -21800,7 +21800,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G739" t="n">
-        <v>2.23087167739868</v>
+        <v>2.23087191581726</v>
       </c>
       <c r="H739" t="n">
         <v>4337</v>
@@ -21829,7 +21829,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G740" t="n">
-        <v>2.19353485107422</v>
+        <v>2.1935350894928</v>
       </c>
       <c r="H740" t="n">
         <v>5880</v>
@@ -21887,7 +21887,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G742" t="n">
-        <v>2.23087167739868</v>
+        <v>2.23087191581726</v>
       </c>
       <c r="H742" t="n">
         <v>6415</v>
@@ -21974,7 +21974,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G745" t="n">
-        <v>2.20286917686462</v>
+        <v>2.20286893844604</v>
       </c>
       <c r="H745" t="n">
         <v>3400</v>
@@ -22003,7 +22003,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G746" t="n">
-        <v>2.14686393737793</v>
+        <v>2.14686417579651</v>
       </c>
       <c r="H746" t="n">
         <v>11917</v>
@@ -22032,7 +22032,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G747" t="n">
-        <v>2.10952711105347</v>
+        <v>2.10952734947205</v>
       </c>
       <c r="H747" t="n">
         <v>5878</v>
@@ -22119,7 +22119,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G750" t="n">
-        <v>2.10952711105347</v>
+        <v>2.10952734947205</v>
       </c>
       <c r="H750" t="n">
         <v>3015</v>
@@ -22148,7 +22148,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G751" t="n">
-        <v>2.14686393737793</v>
+        <v>2.14686417579651</v>
       </c>
       <c r="H751" t="n">
         <v>4774</v>
@@ -22177,7 +22177,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G752" t="n">
-        <v>2.14686393737793</v>
+        <v>2.14686417579651</v>
       </c>
       <c r="H752" t="n">
         <v>0</v>
@@ -22206,7 +22206,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G753" t="n">
-        <v>2.14686393737793</v>
+        <v>2.14686417579651</v>
       </c>
       <c r="H753" t="n">
         <v>1518</v>
@@ -22235,7 +22235,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G754" t="n">
-        <v>2.10952711105347</v>
+        <v>2.10952734947205</v>
       </c>
       <c r="H754" t="n">
         <v>332</v>
@@ -22264,7 +22264,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G755" t="n">
-        <v>2.11886143684387</v>
+        <v>2.11886119842529</v>
       </c>
       <c r="H755" t="n">
         <v>2015</v>
@@ -22293,7 +22293,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G756" t="n">
-        <v>2.1375298500061</v>
+        <v>2.13752961158752</v>
       </c>
       <c r="H756" t="n">
         <v>759</v>
@@ -22322,7 +22322,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G757" t="n">
-        <v>2.15619826316833</v>
+        <v>2.15619802474976</v>
       </c>
       <c r="H757" t="n">
         <v>5</v>
@@ -22380,7 +22380,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G759" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H759" t="n">
         <v>6674</v>
@@ -22409,7 +22409,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G760" t="n">
-        <v>2.15619826316833</v>
+        <v>2.15619802474976</v>
       </c>
       <c r="H760" t="n">
         <v>9288</v>
@@ -22438,7 +22438,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G761" t="n">
-        <v>2.11886143684387</v>
+        <v>2.11886119842529</v>
       </c>
       <c r="H761" t="n">
         <v>3433</v>
@@ -22467,7 +22467,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G762" t="n">
-        <v>2.16553211212158</v>
+        <v>2.16553235054016</v>
       </c>
       <c r="H762" t="n">
         <v>710</v>
@@ -22496,7 +22496,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G763" t="n">
-        <v>2.15619826316833</v>
+        <v>2.15619802474976</v>
       </c>
       <c r="H763" t="n">
         <v>74</v>
@@ -22525,7 +22525,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G764" t="n">
-        <v>2.10952711105347</v>
+        <v>2.10952734947205</v>
       </c>
       <c r="H764" t="n">
         <v>2010</v>
@@ -22554,7 +22554,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G765" t="n">
-        <v>2.10952711105347</v>
+        <v>2.10952734947205</v>
       </c>
       <c r="H765" t="n">
         <v>0</v>
@@ -22583,7 +22583,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G766" t="n">
-        <v>2.11886143684387</v>
+        <v>2.11886119842529</v>
       </c>
       <c r="H766" t="n">
         <v>155</v>
@@ -22612,7 +22612,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G767" t="n">
-        <v>2.14686393737793</v>
+        <v>2.14686417579651</v>
       </c>
       <c r="H767" t="n">
         <v>1300</v>
@@ -22641,7 +22641,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G768" t="n">
-        <v>2.14686393737793</v>
+        <v>2.14686417579651</v>
       </c>
       <c r="H768" t="n">
         <v>0</v>
@@ -22728,7 +22728,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G771" t="n">
-        <v>2.30554509162903</v>
+        <v>2.30554533004761</v>
       </c>
       <c r="H771" t="n">
         <v>7755</v>
@@ -22757,7 +22757,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G772" t="n">
-        <v>2.16553211212158</v>
+        <v>2.16553235054016</v>
       </c>
       <c r="H772" t="n">
         <v>1743</v>
@@ -22786,7 +22786,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G773" t="n">
-        <v>2.19353485107422</v>
+        <v>2.1935350894928</v>
       </c>
       <c r="H773" t="n">
         <v>499</v>
@@ -22815,7 +22815,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G774" t="n">
-        <v>2.14686393737793</v>
+        <v>2.14686417579651</v>
       </c>
       <c r="H774" t="n">
         <v>1537</v>
@@ -22873,7 +22873,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G776" t="n">
-        <v>2.14686393737793</v>
+        <v>2.14686417579651</v>
       </c>
       <c r="H776" t="n">
         <v>8020</v>
@@ -22902,7 +22902,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G777" t="n">
-        <v>2.00685143470764</v>
+        <v>2.00685095787048</v>
       </c>
       <c r="H777" t="n">
         <v>6782</v>
@@ -22931,7 +22931,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G778" t="n">
-        <v>2.01618528366089</v>
+        <v>2.01618552207947</v>
       </c>
       <c r="H778" t="n">
         <v>3662</v>
@@ -22960,7 +22960,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G779" t="n">
-        <v>2.01618528366089</v>
+        <v>2.01618552207947</v>
       </c>
       <c r="H779" t="n">
         <v>5386</v>
@@ -22989,7 +22989,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G780" t="n">
-        <v>1.99751698970795</v>
+        <v>1.99751710891724</v>
       </c>
       <c r="H780" t="n">
         <v>923</v>
@@ -23018,7 +23018,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G781" t="n">
-        <v>2.02551960945129</v>
+        <v>2.02551937103271</v>
       </c>
       <c r="H781" t="n">
         <v>2701</v>
@@ -23076,7 +23076,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G783" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H783" t="n">
         <v>16989</v>
@@ -23134,7 +23134,7 @@
         <v>2</v>
       </c>
       <c r="G785" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H785" t="n">
         <v>17005</v>
@@ -23163,7 +23163,7 @@
         <v>2</v>
       </c>
       <c r="G786" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H786" t="n">
         <v>10000</v>
@@ -23308,7 +23308,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G791" t="n">
-        <v>1.73149240016937</v>
+        <v>1.73149251937866</v>
       </c>
       <c r="H791" t="n">
         <v>13284</v>
@@ -23337,7 +23337,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G792" t="n">
-        <v>1.6941556930542</v>
+        <v>1.69415581226349</v>
       </c>
       <c r="H792" t="n">
         <v>8371</v>
@@ -23395,7 +23395,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G794" t="n">
-        <v>1.87617242336273</v>
+        <v>1.87617254257202</v>
       </c>
       <c r="H794" t="n">
         <v>9697</v>
@@ -23482,7 +23482,7 @@
         <v>2</v>
       </c>
       <c r="G797" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H797" t="n">
         <v>1805</v>
@@ -23511,7 +23511,7 @@
         <v>2</v>
       </c>
       <c r="G798" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H798" t="n">
         <v>1028</v>
@@ -23540,7 +23540,7 @@
         <v>2</v>
       </c>
       <c r="G799" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H799" t="n">
         <v>0</v>
@@ -23598,7 +23598,7 @@
         <v>2</v>
       </c>
       <c r="G801" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H801" t="n">
         <v>170</v>
@@ -23627,7 +23627,7 @@
         <v>2</v>
       </c>
       <c r="G802" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H802" t="n">
         <v>0</v>
@@ -23656,7 +23656,7 @@
         <v>2</v>
       </c>
       <c r="G803" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H803" t="n">
         <v>3200</v>
@@ -23743,7 +23743,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H806" t="n">
         <v>2225</v>
@@ -23772,7 +23772,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G807" t="n">
-        <v>1.88550674915314</v>
+        <v>1.88550662994385</v>
       </c>
       <c r="H807" t="n">
         <v>530</v>
@@ -23859,7 +23859,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G810" t="n">
-        <v>1.83883571624756</v>
+        <v>1.83883559703827</v>
       </c>
       <c r="H810" t="n">
         <v>2520</v>
@@ -23888,7 +23888,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G811" t="n">
-        <v>1.83883571624756</v>
+        <v>1.83883559703827</v>
       </c>
       <c r="H811" t="n">
         <v>626</v>
@@ -23975,7 +23975,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G814" t="n">
-        <v>1.98818290233612</v>
+        <v>1.98818302154541</v>
       </c>
       <c r="H814" t="n">
         <v>5130</v>
@@ -24004,7 +24004,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G815" t="n">
-        <v>1.98818290233612</v>
+        <v>1.98818302154541</v>
       </c>
       <c r="H815" t="n">
         <v>13633</v>
@@ -24033,7 +24033,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G816" t="n">
-        <v>1.97884857654572</v>
+        <v>1.97884833812714</v>
       </c>
       <c r="H816" t="n">
         <v>18908</v>
@@ -24091,7 +24091,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G818" t="n">
-        <v>1.92284333705902</v>
+        <v>1.9228435754776</v>
       </c>
       <c r="H818" t="n">
         <v>3832</v>
@@ -24120,7 +24120,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G819" t="n">
-        <v>1.94151175022125</v>
+        <v>1.94151163101196</v>
       </c>
       <c r="H819" t="n">
         <v>4235</v>
@@ -24236,7 +24236,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G823" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H823" t="n">
         <v>2258</v>
@@ -24265,7 +24265,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G824" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H824" t="n">
         <v>0</v>
@@ -24294,7 +24294,7 @@
         <v>2</v>
       </c>
       <c r="G825" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H825" t="n">
         <v>1433</v>
@@ -24323,7 +24323,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G826" t="n">
-        <v>2.02551960945129</v>
+        <v>2.02551937103271</v>
       </c>
       <c r="H826" t="n">
         <v>12498</v>
@@ -24352,7 +24352,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G827" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H827" t="n">
         <v>15383</v>
@@ -24381,7 +24381,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G828" t="n">
-        <v>1.88550674915314</v>
+        <v>1.88550662994385</v>
       </c>
       <c r="H828" t="n">
         <v>2410</v>
@@ -24410,7 +24410,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G829" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H829" t="n">
         <v>4980</v>
@@ -24439,7 +24439,7 @@
         <v>2</v>
       </c>
       <c r="G830" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H830" t="n">
         <v>5204</v>
@@ -24526,7 +24526,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G833" t="n">
-        <v>1.88550674915314</v>
+        <v>1.88550662994385</v>
       </c>
       <c r="H833" t="n">
         <v>500</v>
@@ -25135,7 +25135,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G854" t="n">
-        <v>1.92284333705902</v>
+        <v>1.9228435754776</v>
       </c>
       <c r="H854" t="n">
         <v>3818</v>
@@ -25193,7 +25193,7 @@
         <v>2</v>
       </c>
       <c r="G856" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H856" t="n">
         <v>1249</v>
@@ -25222,7 +25222,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G857" t="n">
-        <v>1.92284333705902</v>
+        <v>1.9228435754776</v>
       </c>
       <c r="H857" t="n">
         <v>1847</v>
@@ -25251,7 +25251,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G858" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H858" t="n">
         <v>1659</v>
@@ -25280,7 +25280,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G859" t="n">
-        <v>1.87617242336273</v>
+        <v>1.87617254257202</v>
       </c>
       <c r="H859" t="n">
         <v>1005</v>
@@ -25309,7 +25309,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G860" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H860" t="n">
         <v>5149</v>
@@ -25454,7 +25454,7 @@
         <v>2</v>
       </c>
       <c r="G865" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H865" t="n">
         <v>3350</v>
@@ -25483,7 +25483,7 @@
         <v>2</v>
       </c>
       <c r="G866" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H866" t="n">
         <v>1000</v>
@@ -25512,7 +25512,7 @@
         <v>2</v>
       </c>
       <c r="G867" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H867" t="n">
         <v>0</v>
@@ -25570,7 +25570,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G869" t="n">
-        <v>1.88550674915314</v>
+        <v>1.88550662994385</v>
       </c>
       <c r="H869" t="n">
         <v>4311</v>
@@ -25599,7 +25599,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G870" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H870" t="n">
         <v>5440</v>
@@ -25628,7 +25628,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G871" t="n">
-        <v>1.94151175022125</v>
+        <v>1.94151163101196</v>
       </c>
       <c r="H871" t="n">
         <v>830</v>
@@ -25657,7 +25657,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G872" t="n">
-        <v>1.92284333705902</v>
+        <v>1.9228435754776</v>
       </c>
       <c r="H872" t="n">
         <v>1350</v>
@@ -25744,7 +25744,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G875" t="n">
-        <v>1.88550674915314</v>
+        <v>1.88550662994385</v>
       </c>
       <c r="H875" t="n">
         <v>7617</v>
@@ -25773,7 +25773,7 @@
         <v>2</v>
       </c>
       <c r="G876" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H876" t="n">
         <v>2503</v>
@@ -25802,7 +25802,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G877" t="n">
-        <v>1.92284333705902</v>
+        <v>1.9228435754776</v>
       </c>
       <c r="H877" t="n">
         <v>1605</v>
@@ -25831,7 +25831,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G878" t="n">
-        <v>1.92284333705902</v>
+        <v>1.9228435754776</v>
       </c>
       <c r="H878" t="n">
         <v>4340</v>
@@ -25947,7 +25947,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G882" t="n">
-        <v>1.94151175022125</v>
+        <v>1.94151163101196</v>
       </c>
       <c r="H882" t="n">
         <v>5000</v>
@@ -25976,7 +25976,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G883" t="n">
-        <v>1.94151175022125</v>
+        <v>1.94151163101196</v>
       </c>
       <c r="H883" t="n">
         <v>1500</v>
@@ -26034,7 +26034,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H885" t="n">
         <v>6104</v>
@@ -26092,7 +26092,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G887" t="n">
-        <v>1.94151175022125</v>
+        <v>1.94151163101196</v>
       </c>
       <c r="H887" t="n">
         <v>3600</v>
@@ -26121,7 +26121,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G888" t="n">
-        <v>1.94151175022125</v>
+        <v>1.94151163101196</v>
       </c>
       <c r="H888" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G891" t="n">
-        <v>1.94151175022125</v>
+        <v>1.94151163101196</v>
       </c>
       <c r="H891" t="n">
         <v>3305</v>
@@ -26266,7 +26266,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G893" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H893" t="n">
         <v>2300</v>
@@ -26324,7 +26324,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G895" t="n">
-        <v>1.92284333705902</v>
+        <v>1.9228435754776</v>
       </c>
       <c r="H895" t="n">
         <v>1000</v>
@@ -26411,7 +26411,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G898" t="n">
-        <v>2.20286917686462</v>
+        <v>2.20286893844604</v>
       </c>
       <c r="H898" t="n">
         <v>36211</v>
@@ -26469,7 +26469,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G900" t="n">
-        <v>2.23087167739868</v>
+        <v>2.23087191581726</v>
       </c>
       <c r="H900" t="n">
         <v>18041</v>
@@ -26527,7 +26527,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G902" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H902" t="n">
         <v>9996</v>
@@ -26556,7 +26556,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G903" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H903" t="n">
         <v>12989</v>
@@ -26585,7 +26585,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G904" t="n">
-        <v>2.30554509162903</v>
+        <v>2.30554533004761</v>
       </c>
       <c r="H904" t="n">
         <v>7011</v>
@@ -26614,7 +26614,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G905" t="n">
-        <v>2.23087167739868</v>
+        <v>2.23087191581726</v>
       </c>
       <c r="H905" t="n">
         <v>12451</v>
@@ -26643,7 +26643,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G906" t="n">
-        <v>2.23087167739868</v>
+        <v>2.23087191581726</v>
       </c>
       <c r="H906" t="n">
         <v>1897</v>
@@ -26701,7 +26701,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G908" t="n">
-        <v>2.23087167739868</v>
+        <v>2.23087191581726</v>
       </c>
       <c r="H908" t="n">
         <v>1500</v>
@@ -26759,7 +26759,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G910" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H910" t="n">
         <v>2850</v>
@@ -26875,7 +26875,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G914" t="n">
-        <v>2.35221600532532</v>
+        <v>2.3522162437439</v>
       </c>
       <c r="H914" t="n">
         <v>8833</v>
@@ -26962,7 +26962,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G917" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H917" t="n">
         <v>3029</v>
@@ -27020,7 +27020,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G919" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H919" t="n">
         <v>3027</v>
@@ -27078,7 +27078,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G921" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H921" t="n">
         <v>2800</v>
@@ -27107,7 +27107,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G922" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H922" t="n">
         <v>2840</v>
@@ -27136,7 +27136,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G923" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H923" t="n">
         <v>2275</v>
@@ -27165,7 +27165,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G924" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H924" t="n">
         <v>2811</v>
@@ -27194,7 +27194,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G925" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H925" t="n">
         <v>10000</v>
@@ -27252,7 +27252,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G927" t="n">
-        <v>2.36155033111572</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H927" t="n">
         <v>13666</v>
@@ -27339,7 +27339,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G930" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H930" t="n">
         <v>2560</v>
@@ -27397,7 +27397,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G932" t="n">
-        <v>2.35221600532532</v>
+        <v>2.3522162437439</v>
       </c>
       <c r="H932" t="n">
         <v>2295</v>
@@ -27426,7 +27426,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G933" t="n">
-        <v>2.35221600532532</v>
+        <v>2.3522162437439</v>
       </c>
       <c r="H933" t="n">
         <v>1955</v>
@@ -27455,7 +27455,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G934" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H934" t="n">
         <v>18035</v>
@@ -27513,7 +27513,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G936" t="n">
-        <v>2.20286917686462</v>
+        <v>2.20286893844604</v>
       </c>
       <c r="H936" t="n">
         <v>6398</v>
@@ -27571,7 +27571,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G938" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H938" t="n">
         <v>36604</v>
@@ -27600,7 +27600,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G939" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H939" t="n">
         <v>14446</v>
@@ -27774,7 +27774,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G945" t="n">
-        <v>2.35221600532532</v>
+        <v>2.3522162437439</v>
       </c>
       <c r="H945" t="n">
         <v>14242</v>
@@ -27861,7 +27861,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G948" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H948" t="n">
         <v>2000</v>
@@ -27919,7 +27919,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G950" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H950" t="n">
         <v>2715</v>
@@ -27948,7 +27948,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G951" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H951" t="n">
         <v>3000</v>
@@ -27977,7 +27977,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G952" t="n">
-        <v>2.35221600532532</v>
+        <v>2.3522162437439</v>
       </c>
       <c r="H952" t="n">
         <v>3300</v>
@@ -28035,7 +28035,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G954" t="n">
-        <v>2.35221600532532</v>
+        <v>2.3522162437439</v>
       </c>
       <c r="H954" t="n">
         <v>3875</v>
@@ -28064,7 +28064,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G955" t="n">
-        <v>2.36155033111572</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H955" t="n">
         <v>1000</v>
@@ -28093,7 +28093,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G956" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H956" t="n">
         <v>4601</v>
@@ -28122,7 +28122,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G957" t="n">
-        <v>2.36155033111572</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H957" t="n">
         <v>2000</v>
@@ -28209,7 +28209,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G960" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H960" t="n">
         <v>8263</v>
@@ -28238,7 +28238,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G961" t="n">
-        <v>2.35221600532532</v>
+        <v>2.3522162437439</v>
       </c>
       <c r="H961" t="n">
         <v>2030</v>
@@ -28267,7 +28267,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G962" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H962" t="n">
         <v>1000</v>
@@ -28354,7 +28354,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G965" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H965" t="n">
         <v>21</v>
@@ -28383,7 +28383,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G966" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H966" t="n">
         <v>6028</v>
@@ -28470,7 +28470,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G969" t="n">
-        <v>2.35221600532532</v>
+        <v>2.3522162437439</v>
       </c>
       <c r="H969" t="n">
         <v>4462</v>
@@ -28586,7 +28586,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G973" t="n">
-        <v>2.35221600532532</v>
+        <v>2.3522162437439</v>
       </c>
       <c r="H973" t="n">
         <v>10250</v>
@@ -28644,7 +28644,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G975" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H975" t="n">
         <v>5517</v>
@@ -28702,7 +28702,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G977" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H977" t="n">
         <v>2500</v>
@@ -28731,7 +28731,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G978" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H978" t="n">
         <v>4636</v>
@@ -28818,7 +28818,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G981" t="n">
-        <v>2.36155033111572</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H981" t="n">
         <v>3499</v>
@@ -28905,7 +28905,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G984" t="n">
-        <v>2.36155033111572</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H984" t="n">
         <v>1677</v>
@@ -29079,7 +29079,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G990" t="n">
-        <v>2.35221600532532</v>
+        <v>2.3522162437439</v>
       </c>
       <c r="H990" t="n">
         <v>450</v>
@@ -29137,7 +29137,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G992" t="n">
-        <v>2.35221600532532</v>
+        <v>2.3522162437439</v>
       </c>
       <c r="H992" t="n">
         <v>7531</v>
@@ -29166,7 +29166,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G993" t="n">
-        <v>2.35221600532532</v>
+        <v>2.3522162437439</v>
       </c>
       <c r="H993" t="n">
         <v>0</v>
@@ -29427,7 +29427,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1002" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H1002" t="n">
         <v>3900</v>
@@ -29514,7 +29514,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1005" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H1005" t="n">
         <v>642</v>
@@ -29543,7 +29543,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H1006" t="n">
         <v>2020</v>
@@ -29630,7 +29630,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1009" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H1009" t="n">
         <v>1826</v>
@@ -29688,7 +29688,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1011" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H1011" t="n">
         <v>3388</v>
@@ -29978,7 +29978,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1021" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H1021" t="n">
         <v>942</v>
@@ -30065,7 +30065,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1024" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H1024" t="n">
         <v>1010</v>
@@ -30268,7 +30268,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1031" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H1031" t="n">
         <v>2233</v>
@@ -30297,7 +30297,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1032" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H1032" t="n">
         <v>200</v>
@@ -30326,7 +30326,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1033" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H1033" t="n">
         <v>939</v>
@@ -30384,7 +30384,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1035" t="n">
-        <v>2.35221600532532</v>
+        <v>2.3522162437439</v>
       </c>
       <c r="H1035" t="n">
         <v>970</v>
@@ -30413,7 +30413,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1036" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H1036" t="n">
         <v>1101</v>
@@ -30442,7 +30442,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1037" t="n">
-        <v>2.35221600532532</v>
+        <v>2.3522162437439</v>
       </c>
       <c r="H1037" t="n">
         <v>1000</v>
@@ -30558,7 +30558,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1041" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H1041" t="n">
         <v>15334</v>
@@ -30587,7 +30587,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1042" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H1042" t="n">
         <v>548</v>
@@ -30732,7 +30732,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1047" t="n">
-        <v>2.35221600532532</v>
+        <v>2.3522162437439</v>
       </c>
       <c r="H1047" t="n">
         <v>626</v>
@@ -30761,7 +30761,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1048" t="n">
-        <v>2.30554509162903</v>
+        <v>2.30554533004761</v>
       </c>
       <c r="H1048" t="n">
         <v>2360</v>
@@ -30790,7 +30790,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1049" t="n">
-        <v>2.30554509162903</v>
+        <v>2.30554533004761</v>
       </c>
       <c r="H1049" t="n">
         <v>25973</v>
@@ -30819,7 +30819,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1050" t="n">
-        <v>2.30554509162903</v>
+        <v>2.30554533004761</v>
       </c>
       <c r="H1050" t="n">
         <v>0</v>
@@ -30877,7 +30877,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1052" t="n">
-        <v>2.36155033111572</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H1052" t="n">
         <v>6417</v>
@@ -31138,7 +31138,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1061" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H1061" t="n">
         <v>6</v>
@@ -31196,7 +31196,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1063" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H1063" t="n">
         <v>2460</v>
@@ -31225,7 +31225,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1064" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H1064" t="n">
         <v>0</v>
@@ -31254,7 +31254,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1065" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H1065" t="n">
         <v>7276</v>
@@ -31283,7 +31283,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H1066" t="n">
         <v>5691</v>
@@ -31312,7 +31312,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H1067" t="n">
         <v>400</v>
@@ -31370,7 +31370,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1069" t="n">
-        <v>2.44555830955505</v>
+        <v>2.44555807113647</v>
       </c>
       <c r="H1069" t="n">
         <v>1500</v>
@@ -31399,7 +31399,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1070" t="n">
-        <v>2.44555830955505</v>
+        <v>2.44555807113647</v>
       </c>
       <c r="H1070" t="n">
         <v>11000</v>
@@ -31428,7 +31428,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1071" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H1071" t="n">
         <v>53618</v>
@@ -32124,7 +32124,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1095" t="n">
         <v>2654</v>
@@ -32385,7 +32385,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1104" t="n">
-        <v>2.55756831169128</v>
+        <v>2.55756855010986</v>
       </c>
       <c r="H1104" t="n">
         <v>1500</v>
@@ -32443,7 +32443,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1106" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1106" t="n">
         <v>200</v>
@@ -32472,7 +32472,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1107" t="n">
-        <v>2.55756831169128</v>
+        <v>2.55756855010986</v>
       </c>
       <c r="H1107" t="n">
         <v>1250</v>
@@ -32501,7 +32501,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1108" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1108" t="n">
         <v>1000</v>
@@ -32530,7 +32530,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1109" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1109" t="n">
         <v>1587</v>
@@ -32559,7 +32559,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1110" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1110" t="n">
         <v>2194</v>
@@ -32617,7 +32617,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1112" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1112" t="n">
         <v>3440</v>
@@ -32646,7 +32646,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1113" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1113" t="n">
         <v>0</v>
@@ -32675,7 +32675,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1114" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1114" t="n">
         <v>3456</v>
@@ -32704,7 +32704,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1115" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1115" t="n">
         <v>0</v>
@@ -33429,7 +33429,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1140" t="n">
-        <v>2.82826018333435</v>
+        <v>2.82825994491577</v>
       </c>
       <c r="H1140" t="n">
         <v>9200</v>
@@ -34096,7 +34096,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1163" t="n">
-        <v>2.9682731628418</v>
+        <v>2.96827292442322</v>
       </c>
       <c r="H1163" t="n">
         <v>21970</v>
@@ -34183,7 +34183,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.13628816604614</v>
+        <v>3.13628840446472</v>
       </c>
       <c r="H1166" t="n">
         <v>15387</v>
@@ -34212,7 +34212,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.20162773132324</v>
+        <v>3.20162796974182</v>
       </c>
       <c r="H1167" t="n">
         <v>24299</v>
@@ -34357,7 +34357,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.30430388450623</v>
+        <v>3.30430364608765</v>
       </c>
       <c r="H1172" t="n">
         <v>21171</v>
@@ -34386,7 +34386,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.34164023399353</v>
+        <v>3.34164047241211</v>
       </c>
       <c r="H1173" t="n">
         <v>13961</v>
@@ -34415,7 +34415,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.31363797187805</v>
+        <v>3.31363773345947</v>
       </c>
       <c r="H1174" t="n">
         <v>34347</v>
@@ -34531,7 +34531,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1178" t="n">
-        <v>3.79901576042175</v>
+        <v>3.79901623725891</v>
       </c>
       <c r="H1178" t="n">
         <v>19529</v>
@@ -34589,7 +34589,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1180" t="n">
-        <v>4.00436782836914</v>
+        <v>4.0043683052063</v>
       </c>
       <c r="H1180" t="n">
         <v>86548</v>
@@ -34647,7 +34647,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1182" t="n">
-        <v>4.46174335479736</v>
+        <v>4.46174383163452</v>
       </c>
       <c r="H1182" t="n">
         <v>47140</v>
@@ -34734,7 +34734,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1185" t="n">
-        <v>4.94712162017822</v>
+        <v>4.94712209701538</v>
       </c>
       <c r="H1185" t="n">
         <v>36680</v>
@@ -34763,7 +34763,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1186" t="n">
-        <v>4.85377883911133</v>
+        <v>4.85377979278564</v>
       </c>
       <c r="H1186" t="n">
         <v>39631</v>
@@ -34908,7 +34908,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1191" t="n">
-        <v>4.50841474533081</v>
+        <v>4.50841426849365</v>
       </c>
       <c r="H1191" t="n">
         <v>16999</v>
@@ -34966,7 +34966,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1193" t="n">
-        <v>4.46174335479736</v>
+        <v>4.46174383163452</v>
       </c>
       <c r="H1193" t="n">
         <v>24861</v>
@@ -35024,7 +35024,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1195" t="n">
-        <v>4.46174335479736</v>
+        <v>4.46174383163452</v>
       </c>
       <c r="H1195" t="n">
         <v>12604</v>
@@ -35343,7 +35343,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1206" t="n">
-        <v>4.58308744430542</v>
+        <v>4.58308792114258</v>
       </c>
       <c r="H1206" t="n">
         <v>12504</v>
@@ -35488,7 +35488,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1211" t="n">
-        <v>4.46174335479736</v>
+        <v>4.46174383163452</v>
       </c>
       <c r="H1211" t="n">
         <v>10557</v>
@@ -35517,7 +35517,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1212" t="n">
-        <v>4.50841474533081</v>
+        <v>4.50841426849365</v>
       </c>
       <c r="H1212" t="n">
         <v>8520</v>
@@ -35691,7 +35691,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1218" t="n">
-        <v>4.45240926742554</v>
+        <v>4.4524097442627</v>
       </c>
       <c r="H1218" t="n">
         <v>17443</v>
@@ -35836,7 +35836,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1223" t="n">
-        <v>4.38706970214844</v>
+        <v>4.3870701789856</v>
       </c>
       <c r="H1223" t="n">
         <v>2203</v>
@@ -35865,7 +35865,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1224" t="n">
-        <v>4.37773609161377</v>
+        <v>4.37773561477661</v>
       </c>
       <c r="H1224" t="n">
         <v>6752</v>
@@ -35894,7 +35894,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1225" t="n">
-        <v>4.36840152740479</v>
+        <v>4.36840105056763</v>
       </c>
       <c r="H1225" t="n">
         <v>12461</v>
@@ -35923,7 +35923,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1226" t="n">
-        <v>4.37773609161377</v>
+        <v>4.37773561477661</v>
       </c>
       <c r="H1226" t="n">
         <v>1614</v>
@@ -35952,7 +35952,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1227" t="n">
-        <v>4.38706970214844</v>
+        <v>4.3870701789856</v>
       </c>
       <c r="H1227" t="n">
         <v>11176</v>
@@ -35981,7 +35981,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1228" t="n">
-        <v>4.34973287582397</v>
+        <v>4.34973335266113</v>
       </c>
       <c r="H1228" t="n">
         <v>766</v>
@@ -36010,7 +36010,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1229" t="n">
-        <v>4.38706970214844</v>
+        <v>4.3870701789856</v>
       </c>
       <c r="H1229" t="n">
         <v>3628</v>
@@ -36068,7 +36068,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1231" t="n">
-        <v>4.38706970214844</v>
+        <v>4.3870701789856</v>
       </c>
       <c r="H1231" t="n">
         <v>12136</v>
@@ -36097,7 +36097,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1232" t="n">
-        <v>4.38706970214844</v>
+        <v>4.3870701789856</v>
       </c>
       <c r="H1232" t="n">
         <v>8849</v>
@@ -36126,7 +36126,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1233" t="n">
-        <v>4.38706970214844</v>
+        <v>4.3870701789856</v>
       </c>
       <c r="H1233" t="n">
         <v>8218</v>
@@ -36184,7 +36184,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1235" t="n">
-        <v>4.38706970214844</v>
+        <v>4.3870701789856</v>
       </c>
       <c r="H1235" t="n">
         <v>3700</v>
@@ -36213,7 +36213,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1236" t="n">
-        <v>4.38706970214844</v>
+        <v>4.3870701789856</v>
       </c>
       <c r="H1236" t="n">
         <v>9129</v>
@@ -36242,7 +36242,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1237" t="n">
-        <v>4.38706970214844</v>
+        <v>4.3870701789856</v>
       </c>
       <c r="H1237" t="n">
         <v>3361</v>
@@ -36271,7 +36271,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1238" t="n">
-        <v>4.38706970214844</v>
+        <v>4.3870701789856</v>
       </c>
       <c r="H1238" t="n">
         <v>3927</v>
@@ -36300,7 +36300,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1239" t="n">
-        <v>4.38706970214844</v>
+        <v>4.3870701789856</v>
       </c>
       <c r="H1239" t="n">
         <v>2020</v>
@@ -36329,7 +36329,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1240" t="n">
-        <v>4.45240926742554</v>
+        <v>4.4524097442627</v>
       </c>
       <c r="H1240" t="n">
         <v>7982</v>
@@ -36445,7 +36445,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1244" t="n">
-        <v>4.38706970214844</v>
+        <v>4.3870701789856</v>
       </c>
       <c r="H1244" t="n">
         <v>10595</v>
@@ -36474,7 +36474,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.40573835372925</v>
+        <v>4.40573787689209</v>
       </c>
       <c r="H1245" t="n">
         <v>1123</v>
@@ -36503,7 +36503,7 @@
         <v>4.75</v>
       </c>
       <c r="G1246" t="n">
-        <v>4.43374109268188</v>
+        <v>4.43374061584473</v>
       </c>
       <c r="H1246" t="n">
         <v>2543</v>
@@ -36619,7 +36619,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1250" t="n">
-        <v>4.40573835372925</v>
+        <v>4.40573787689209</v>
       </c>
       <c r="H1250" t="n">
         <v>2487</v>
@@ -36677,7 +36677,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1252" t="n">
-        <v>4.53641748428345</v>
+        <v>4.53641700744629</v>
       </c>
       <c r="H1252" t="n">
         <v>10852</v>
@@ -37315,7 +37315,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1274" t="n">
-        <v>4.9907808303833</v>
+        <v>4.99078130722046</v>
       </c>
       <c r="H1274" t="n">
         <v>24772</v>
@@ -37344,7 +37344,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1275" t="n">
-        <v>5.02917194366455</v>
+        <v>5.02917146682739</v>
       </c>
       <c r="H1275" t="n">
         <v>31385</v>
@@ -37431,7 +37431,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1278" t="n">
-        <v>5.48985910415649</v>
+        <v>5.48985958099365</v>
       </c>
       <c r="H1278" t="n">
         <v>70084</v>
@@ -37576,7 +37576,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1283" t="n">
-        <v>5.83537530899048</v>
+        <v>5.83537483215332</v>
       </c>
       <c r="H1283" t="n">
         <v>8786</v>
@@ -37634,7 +37634,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1285" t="n">
-        <v>6.39203882217407</v>
+        <v>6.39203929901123</v>
       </c>
       <c r="H1285" t="n">
         <v>35361</v>
@@ -37750,7 +37750,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1289" t="n">
-        <v>6.46882057189941</v>
+        <v>6.46882009506226</v>
       </c>
       <c r="H1289" t="n">
         <v>13104</v>
@@ -37866,7 +37866,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G1293" t="n">
-        <v>6.18089056015015</v>
+        <v>6.1808910369873</v>
       </c>
       <c r="H1293" t="n">
         <v>21462</v>
@@ -37895,7 +37895,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1294" t="n">
-        <v>6.12330484390259</v>
+        <v>6.12330532073975</v>
       </c>
       <c r="H1294" t="n">
         <v>21748</v>
@@ -37953,7 +37953,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1296" t="n">
-        <v>6.39203882217407</v>
+        <v>6.39203929901123</v>
       </c>
       <c r="H1296" t="n">
         <v>15861</v>
@@ -37982,7 +37982,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1297" t="n">
-        <v>6.48801565170288</v>
+        <v>6.48801612854004</v>
       </c>
       <c r="H1297" t="n">
         <v>2374</v>
@@ -38011,7 +38011,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1298" t="n">
-        <v>6.48801565170288</v>
+        <v>6.48801612854004</v>
       </c>
       <c r="H1298" t="n">
         <v>9827</v>
@@ -38156,7 +38156,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1303" t="n">
-        <v>6.48801565170288</v>
+        <v>6.48801612854004</v>
       </c>
       <c r="H1303" t="n">
         <v>11171</v>
@@ -38388,7 +38388,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1311" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1311" t="n">
         <v>18885</v>
@@ -38446,7 +38446,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1313" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1313" t="n">
         <v>34147</v>
@@ -38533,7 +38533,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1316" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1316" t="n">
         <v>10376</v>
@@ -38939,7 +38939,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1330" t="n">
-        <v>5.68181228637695</v>
+        <v>5.68181276321411</v>
       </c>
       <c r="H1330" t="n">
         <v>4010</v>
@@ -39026,7 +39026,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1333" t="n">
-        <v>5.66261768341064</v>
+        <v>5.66261720657349</v>
       </c>
       <c r="H1333" t="n">
         <v>3167</v>
@@ -39055,7 +39055,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.56664133071899</v>
+        <v>5.56664085388184</v>
       </c>
       <c r="H1334" t="n">
         <v>13673</v>
@@ -39084,7 +39084,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1335" t="n">
-        <v>5.48985910415649</v>
+        <v>5.48985958099365</v>
       </c>
       <c r="H1335" t="n">
         <v>2565</v>
@@ -39142,7 +39142,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1337" t="n">
-        <v>5.56664133071899</v>
+        <v>5.56664085388184</v>
       </c>
       <c r="H1337" t="n">
         <v>2917</v>
@@ -39171,7 +39171,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1338" t="n">
-        <v>5.56664133071899</v>
+        <v>5.56664085388184</v>
       </c>
       <c r="H1338" t="n">
         <v>1312</v>
@@ -39258,7 +39258,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1341" t="n">
-        <v>5.66261768341064</v>
+        <v>5.66261720657349</v>
       </c>
       <c r="H1341" t="n">
         <v>1605</v>
@@ -39287,7 +39287,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1342" t="n">
-        <v>5.66261768341064</v>
+        <v>5.66261720657349</v>
       </c>
       <c r="H1342" t="n">
         <v>3220</v>
@@ -39403,7 +39403,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1346" t="n">
-        <v>5.56664133071899</v>
+        <v>5.56664085388184</v>
       </c>
       <c r="H1346" t="n">
         <v>2814</v>
@@ -39519,7 +39519,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1350" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1350" t="n">
         <v>11182</v>
@@ -39548,7 +39548,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1351" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1351" t="n">
         <v>17082</v>
@@ -39577,7 +39577,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1352" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1352" t="n">
         <v>5027</v>
@@ -39606,7 +39606,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1353" t="n">
-        <v>6.12330484390259</v>
+        <v>6.12330532073975</v>
       </c>
       <c r="H1353" t="n">
         <v>15567</v>
@@ -39693,7 +39693,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1356" t="n">
-        <v>5.87376594543457</v>
+        <v>5.87376546859741</v>
       </c>
       <c r="H1356" t="n">
         <v>18468</v>
@@ -39896,7 +39896,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1363" t="n">
-        <v>5.96974229812622</v>
+        <v>5.96974182128906</v>
       </c>
       <c r="H1363" t="n">
         <v>14927</v>
@@ -40012,7 +40012,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1367" t="n">
-        <v>5.96974229812622</v>
+        <v>5.96974182128906</v>
       </c>
       <c r="H1367" t="n">
         <v>5383</v>
@@ -40041,7 +40041,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1368" t="n">
-        <v>5.83537530899048</v>
+        <v>5.83537483215332</v>
       </c>
       <c r="H1368" t="n">
         <v>3207</v>
@@ -40099,7 +40099,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1370" t="n">
-        <v>5.96974229812622</v>
+        <v>5.96974182128906</v>
       </c>
       <c r="H1370" t="n">
         <v>2420</v>
@@ -40128,7 +40128,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1371" t="n">
-        <v>5.87376594543457</v>
+        <v>5.87376546859741</v>
       </c>
       <c r="H1371" t="n">
         <v>5952</v>
@@ -40186,7 +40186,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1373" t="n">
-        <v>6.0849142074585</v>
+        <v>6.08491468429565</v>
       </c>
       <c r="H1373" t="n">
         <v>4048</v>
@@ -40244,7 +40244,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1375" t="n">
-        <v>5.87376594543457</v>
+        <v>5.87376546859741</v>
       </c>
       <c r="H1375" t="n">
         <v>6216</v>
@@ -40505,7 +40505,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1384" t="n">
-        <v>5.87376594543457</v>
+        <v>5.87376546859741</v>
       </c>
       <c r="H1384" t="n">
         <v>8532</v>
@@ -40534,7 +40534,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1385" t="n">
-        <v>5.96974229812622</v>
+        <v>5.96974182128906</v>
       </c>
       <c r="H1385" t="n">
         <v>4804</v>
@@ -40563,7 +40563,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1386" t="n">
-        <v>5.96974229812622</v>
+        <v>5.96974182128906</v>
       </c>
       <c r="H1386" t="n">
         <v>51315</v>
@@ -40592,7 +40592,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1387" t="n">
-        <v>5.96974229812622</v>
+        <v>5.96974182128906</v>
       </c>
       <c r="H1387" t="n">
         <v>3086</v>
@@ -40621,7 +40621,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1388" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1388" t="n">
         <v>5083</v>
@@ -40679,7 +40679,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1390" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1390" t="n">
         <v>3425</v>
@@ -40737,7 +40737,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1392" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1392" t="n">
         <v>2371</v>
@@ -40766,7 +40766,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1393" t="n">
-        <v>5.87376594543457</v>
+        <v>5.87376546859741</v>
       </c>
       <c r="H1393" t="n">
         <v>4474</v>
@@ -41085,7 +41085,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1404" t="n">
-        <v>6.0849142074585</v>
+        <v>6.08491468429565</v>
       </c>
       <c r="H1404" t="n">
         <v>18941</v>
@@ -41143,7 +41143,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1406" t="n">
-        <v>6.12330484390259</v>
+        <v>6.12330532073975</v>
       </c>
       <c r="H1406" t="n">
         <v>40015</v>
@@ -41462,7 +41462,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1417" t="n">
-        <v>7.02548456192017</v>
+        <v>7.02548503875732</v>
       </c>
       <c r="H1417" t="n">
         <v>6334</v>
@@ -41839,7 +41839,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1430" t="n">
-        <v>7.02548456192017</v>
+        <v>7.02548503875732</v>
       </c>
       <c r="H1430" t="n">
         <v>15354</v>
@@ -41897,7 +41897,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1432" t="n">
-        <v>7.02548456192017</v>
+        <v>7.02548503875732</v>
       </c>
       <c r="H1432" t="n">
         <v>1260</v>
@@ -42129,7 +42129,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1440" t="n">
-        <v>7.06387567520142</v>
+        <v>7.06387519836426</v>
       </c>
       <c r="H1440" t="n">
         <v>1592</v>
@@ -42187,7 +42187,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G1442" t="n">
-        <v>7.12146091461182</v>
+        <v>7.12146139144897</v>
       </c>
       <c r="H1442" t="n">
         <v>9087</v>
@@ -42303,7 +42303,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1446" t="n">
-        <v>7.06387567520142</v>
+        <v>7.06387519836426</v>
       </c>
       <c r="H1446" t="n">
         <v>10440</v>
@@ -42361,7 +42361,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1448" t="n">
-        <v>7.06387567520142</v>
+        <v>7.06387519836426</v>
       </c>
       <c r="H1448" t="n">
         <v>6369</v>
@@ -42390,7 +42390,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1449" t="n">
-        <v>6.91031217575073</v>
+        <v>6.91031265258789</v>
       </c>
       <c r="H1449" t="n">
         <v>8416</v>
@@ -42419,7 +42419,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1450" t="n">
-        <v>7.02548456192017</v>
+        <v>7.02548503875732</v>
       </c>
       <c r="H1450" t="n">
         <v>5499</v>
@@ -42535,7 +42535,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1454" t="n">
-        <v>7.06387567520142</v>
+        <v>7.06387519836426</v>
       </c>
       <c r="H1454" t="n">
         <v>2894</v>
@@ -42680,7 +42680,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1459" t="n">
-        <v>6.91031217575073</v>
+        <v>6.91031265258789</v>
       </c>
       <c r="H1459" t="n">
         <v>3121</v>
@@ -42738,7 +42738,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1461" t="n">
-        <v>6.91031217575073</v>
+        <v>6.91031265258789</v>
       </c>
       <c r="H1461" t="n">
         <v>9076</v>
@@ -42767,7 +42767,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1462" t="n">
-        <v>7.06387567520142</v>
+        <v>7.06387519836426</v>
       </c>
       <c r="H1462" t="n">
         <v>300</v>
@@ -42883,7 +42883,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1466" t="n">
-        <v>7.02548456192017</v>
+        <v>7.02548503875732</v>
       </c>
       <c r="H1466" t="n">
         <v>501</v>
@@ -43173,7 +43173,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1476" t="n">
-        <v>6.91031217575073</v>
+        <v>6.91031265258789</v>
       </c>
       <c r="H1476" t="n">
         <v>7848</v>
@@ -43202,7 +43202,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1477" t="n">
-        <v>6.89111709594727</v>
+        <v>6.89111757278442</v>
       </c>
       <c r="H1477" t="n">
         <v>12560</v>
@@ -43260,7 +43260,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1479" t="n">
-        <v>6.91031217575073</v>
+        <v>6.91031265258789</v>
       </c>
       <c r="H1479" t="n">
         <v>16205</v>
@@ -43289,7 +43289,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1480" t="n">
-        <v>6.77594566345215</v>
+        <v>6.77594518661499</v>
       </c>
       <c r="H1480" t="n">
         <v>1973</v>
@@ -43318,7 +43318,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1481" t="n">
-        <v>6.98709392547607</v>
+        <v>6.98709440231323</v>
       </c>
       <c r="H1481" t="n">
         <v>4148</v>
@@ -43347,7 +43347,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1482" t="n">
-        <v>6.89111709594727</v>
+        <v>6.89111757278442</v>
       </c>
       <c r="H1482" t="n">
         <v>144</v>
@@ -43405,7 +43405,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G1484" t="n">
-        <v>6.79514074325562</v>
+        <v>6.79514026641846</v>
       </c>
       <c r="H1484" t="n">
         <v>10530</v>
@@ -43434,7 +43434,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1485" t="n">
-        <v>6.81433582305908</v>
+        <v>6.81433629989624</v>
       </c>
       <c r="H1485" t="n">
         <v>2742</v>
@@ -43463,7 +43463,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1486" t="n">
-        <v>6.91031217575073</v>
+        <v>6.91031265258789</v>
       </c>
       <c r="H1486" t="n">
         <v>1912</v>
@@ -43492,7 +43492,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1487" t="n">
-        <v>6.91031217575073</v>
+        <v>6.91031265258789</v>
       </c>
       <c r="H1487" t="n">
         <v>6267</v>
@@ -43521,7 +43521,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1488" t="n">
-        <v>6.98709392547607</v>
+        <v>6.98709440231323</v>
       </c>
       <c r="H1488" t="n">
         <v>8301</v>
@@ -43724,7 +43724,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1495" t="n">
-        <v>7.29421854019165</v>
+        <v>7.29421901702881</v>
       </c>
       <c r="H1495" t="n">
         <v>3213</v>
@@ -43753,7 +43753,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1496" t="n">
-        <v>7.42858600616455</v>
+        <v>7.42858552932739</v>
       </c>
       <c r="H1496" t="n">
         <v>9505</v>
@@ -43811,7 +43811,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1498" t="n">
-        <v>7.54375839233398</v>
+        <v>7.54375791549683</v>
       </c>
       <c r="H1498" t="n">
         <v>2199</v>
@@ -54460,6 +54460,64 @@
         <v>3703</v>
       </c>
       <c r="I1865" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1866">
+      <c r="A1866" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1866" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1866" t="n">
+        <v>14.1999998092651</v>
+      </c>
+      <c r="D1866" t="n">
+        <v>14.4499998092651</v>
+      </c>
+      <c r="E1866" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="F1866" t="n">
+        <v>13.8999996185303</v>
+      </c>
+      <c r="G1866" t="n">
+        <v>13.8999996185303</v>
+      </c>
+      <c r="H1866" t="n">
+        <v>10732</v>
+      </c>
+      <c r="I1866" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1867">
+      <c r="A1867" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1867" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1867" t="n">
+        <v>13.8500003814697</v>
+      </c>
+      <c r="D1867" t="n">
+        <v>14.1000003814697</v>
+      </c>
+      <c r="E1867" t="n">
+        <v>13.8000001907349</v>
+      </c>
+      <c r="F1867" t="n">
+        <v>13.8000001907349</v>
+      </c>
+      <c r="G1867" t="n">
+        <v>13.8000001907349</v>
+      </c>
+      <c r="H1867" t="n">
+        <v>7702</v>
+      </c>
+      <c r="I1867" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IEG.MI.xlsx
+++ b/data/IEG.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G3" t="n">
-        <v>3.49098753929138</v>
+        <v>3.49098777770996</v>
       </c>
       <c r="H3" t="n">
         <v>29088</v>
@@ -485,7 +485,7 @@
         <v>3.73099994659424</v>
       </c>
       <c r="G4" t="n">
-        <v>3.48258686065674</v>
+        <v>3.48258662223816</v>
       </c>
       <c r="H4" t="n">
         <v>132269</v>
@@ -514,7 +514,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G5" t="n">
-        <v>3.52832436561584</v>
+        <v>3.52832412719727</v>
       </c>
       <c r="H5" t="n">
         <v>20727</v>
@@ -543,7 +543,7 @@
         <v>3.69749999046326</v>
       </c>
       <c r="G6" t="n">
-        <v>3.45131707191467</v>
+        <v>3.45131731033325</v>
       </c>
       <c r="H6" t="n">
         <v>5051</v>
@@ -572,7 +572,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G7" t="n">
-        <v>3.4536509513855</v>
+        <v>3.45365071296692</v>
       </c>
       <c r="H7" t="n">
         <v>13909</v>
@@ -601,7 +601,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>3.40698003768921</v>
+        <v>3.40697979927063</v>
       </c>
       <c r="H8" t="n">
         <v>31297</v>
@@ -659,7 +659,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G10" t="n">
-        <v>3.4536509513855</v>
+        <v>3.45365071296692</v>
       </c>
       <c r="H10" t="n">
         <v>5150</v>
@@ -688,7 +688,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G11" t="n">
-        <v>3.4536509513855</v>
+        <v>3.45365071296692</v>
       </c>
       <c r="H11" t="n">
         <v>2000</v>
@@ -746,7 +746,7 @@
         <v>3.64050006866455</v>
       </c>
       <c r="G13" t="n">
-        <v>3.39811229705811</v>
+        <v>3.39811253547668</v>
       </c>
       <c r="H13" t="n">
         <v>1311</v>
@@ -775,7 +775,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G14" t="n">
-        <v>3.31363773345947</v>
+        <v>3.31363797187805</v>
       </c>
       <c r="H14" t="n">
         <v>25612</v>
@@ -833,7 +833,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G16" t="n">
-        <v>3.36030864715576</v>
+        <v>3.36030888557434</v>
       </c>
       <c r="H16" t="n">
         <v>51650</v>
@@ -891,7 +891,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G18" t="n">
-        <v>3.67767119407654</v>
+        <v>3.67767143249512</v>
       </c>
       <c r="H18" t="n">
         <v>96799</v>
@@ -920,7 +920,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G19" t="n">
-        <v>3.69633984565735</v>
+        <v>3.69634008407593</v>
       </c>
       <c r="H19" t="n">
         <v>96525</v>
@@ -949,7 +949,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G20" t="n">
-        <v>3.78034782409668</v>
+        <v>3.7803475856781</v>
       </c>
       <c r="H20" t="n">
         <v>59862</v>
@@ -978,7 +978,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G21" t="n">
-        <v>3.80834984779358</v>
+        <v>3.80835008621216</v>
       </c>
       <c r="H21" t="n">
         <v>29979</v>
@@ -1007,7 +1007,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G22" t="n">
-        <v>3.78034782409668</v>
+        <v>3.7803475856781</v>
       </c>
       <c r="H22" t="n">
         <v>4670</v>
@@ -1065,7 +1065,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G24" t="n">
-        <v>3.85502099990845</v>
+        <v>3.85502123832703</v>
       </c>
       <c r="H24" t="n">
         <v>69970</v>
@@ -1094,7 +1094,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G25" t="n">
-        <v>3.81768441200256</v>
+        <v>3.81768465042114</v>
       </c>
       <c r="H25" t="n">
         <v>4963</v>
@@ -1123,7 +1123,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G26" t="n">
-        <v>3.91102647781372</v>
+        <v>3.91102600097656</v>
       </c>
       <c r="H26" t="n">
         <v>12441</v>
@@ -1152,7 +1152,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G27" t="n">
-        <v>3.98569941520691</v>
+        <v>3.98569989204407</v>
       </c>
       <c r="H27" t="n">
         <v>15090</v>
@@ -1181,7 +1181,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G28" t="n">
-        <v>3.95769667625427</v>
+        <v>3.95769715309143</v>
       </c>
       <c r="H28" t="n">
         <v>6052</v>
@@ -1210,7 +1210,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G29" t="n">
-        <v>3.97636604309082</v>
+        <v>3.97636580467224</v>
       </c>
       <c r="H29" t="n">
         <v>2457</v>
@@ -1239,7 +1239,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G30" t="n">
-        <v>4.05103874206543</v>
+        <v>4.05103921890259</v>
       </c>
       <c r="H30" t="n">
         <v>10363</v>
@@ -1268,7 +1268,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G31" t="n">
-        <v>4.03237104415894</v>
+        <v>4.03237056732178</v>
       </c>
       <c r="H31" t="n">
         <v>17060</v>
@@ -1297,7 +1297,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G32" t="n">
-        <v>3.9390287399292</v>
+        <v>3.93902850151062</v>
       </c>
       <c r="H32" t="n">
         <v>6284</v>
@@ -1326,7 +1326,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>4.01370191574097</v>
+        <v>4.01370286941528</v>
       </c>
       <c r="H33" t="n">
         <v>4871</v>
@@ -1355,7 +1355,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G34" t="n">
-        <v>4.01370191574097</v>
+        <v>4.01370286941528</v>
       </c>
       <c r="H34" t="n">
         <v>114</v>
@@ -1384,7 +1384,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G35" t="n">
-        <v>3.99503421783447</v>
+        <v>3.99503397941589</v>
       </c>
       <c r="H35" t="n">
         <v>922</v>
@@ -1413,7 +1413,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G36" t="n">
-        <v>3.99503421783447</v>
+        <v>3.99503397941589</v>
       </c>
       <c r="H36" t="n">
         <v>300</v>
@@ -1442,7 +1442,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G37" t="n">
-        <v>3.99503421783447</v>
+        <v>3.99503397941589</v>
       </c>
       <c r="H37" t="n">
         <v>4226</v>
@@ -1471,7 +1471,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G38" t="n">
-        <v>3.95769667625427</v>
+        <v>3.95769715309143</v>
       </c>
       <c r="H38" t="n">
         <v>4960</v>
@@ -1558,7 +1558,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G41" t="n">
-        <v>3.95769667625427</v>
+        <v>3.95769715309143</v>
       </c>
       <c r="H41" t="n">
         <v>225</v>
@@ -1587,7 +1587,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G42" t="n">
-        <v>3.95769667625427</v>
+        <v>3.95769715309143</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G45" t="n">
-        <v>3.91102647781372</v>
+        <v>3.91102600097656</v>
       </c>
       <c r="H45" t="n">
         <v>115</v>
@@ -1732,7 +1732,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G47" t="n">
-        <v>3.85502099990845</v>
+        <v>3.85502123832703</v>
       </c>
       <c r="H47" t="n">
         <v>125</v>
@@ -1761,7 +1761,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G48" t="n">
-        <v>3.8456871509552</v>
+        <v>3.84568667411804</v>
       </c>
       <c r="H48" t="n">
         <v>600</v>
@@ -1790,7 +1790,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G49" t="n">
-        <v>3.91102647781372</v>
+        <v>3.91102600097656</v>
       </c>
       <c r="H49" t="n">
         <v>400</v>
@@ -1993,7 +1993,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G56" t="n">
-        <v>3.40698003768921</v>
+        <v>3.40697979927063</v>
       </c>
       <c r="H56" t="n">
         <v>6594</v>
@@ -2022,7 +2022,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G57" t="n">
-        <v>3.4536509513855</v>
+        <v>3.45365071296692</v>
       </c>
       <c r="H57" t="n">
         <v>73464</v>
@@ -2051,7 +2051,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G58" t="n">
-        <v>3.4536509513855</v>
+        <v>3.45365071296692</v>
       </c>
       <c r="H58" t="n">
         <v>35821</v>
@@ -2080,7 +2080,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G59" t="n">
-        <v>3.48165369033813</v>
+        <v>3.48165345191956</v>
       </c>
       <c r="H59" t="n">
         <v>10667</v>
@@ -2138,7 +2138,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G61" t="n">
-        <v>3.48165369033813</v>
+        <v>3.48165345191956</v>
       </c>
       <c r="H61" t="n">
         <v>851</v>
@@ -2196,7 +2196,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G63" t="n">
-        <v>3.60299777984619</v>
+        <v>3.60299754142761</v>
       </c>
       <c r="H63" t="n">
         <v>2685</v>
@@ -2225,7 +2225,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G64" t="n">
-        <v>3.56566095352173</v>
+        <v>3.56566119194031</v>
       </c>
       <c r="H64" t="n">
         <v>333</v>
@@ -2341,7 +2341,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G68" t="n">
-        <v>3.69633984565735</v>
+        <v>3.69634008407593</v>
       </c>
       <c r="H68" t="n">
         <v>6933</v>
@@ -2399,7 +2399,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G70" t="n">
-        <v>3.60299777984619</v>
+        <v>3.60299754142761</v>
       </c>
       <c r="H70" t="n">
         <v>1400</v>
@@ -2544,7 +2544,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>3.54699277877808</v>
+        <v>3.54699301719666</v>
       </c>
       <c r="H75" t="n">
         <v>550</v>
@@ -2573,7 +2573,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G76" t="n">
-        <v>3.54699277877808</v>
+        <v>3.54699301719666</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>3.54699277877808</v>
+        <v>3.54699301719666</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -2631,7 +2631,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G78" t="n">
-        <v>3.621666431427</v>
+        <v>3.62166666984558</v>
       </c>
       <c r="H78" t="n">
         <v>400</v>
@@ -2660,7 +2660,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G79" t="n">
-        <v>3.56566095352173</v>
+        <v>3.56566119194031</v>
       </c>
       <c r="H79" t="n">
         <v>505</v>
@@ -2776,7 +2776,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G83" t="n">
-        <v>3.61233186721802</v>
+        <v>3.6123321056366</v>
       </c>
       <c r="H83" t="n">
         <v>505</v>
@@ -2805,7 +2805,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G84" t="n">
-        <v>3.61233186721802</v>
+        <v>3.6123321056366</v>
       </c>
       <c r="H84" t="n">
         <v>10</v>
@@ -2834,7 +2834,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G85" t="n">
-        <v>3.56566095352173</v>
+        <v>3.56566119194031</v>
       </c>
       <c r="H85" t="n">
         <v>7252</v>
@@ -2863,7 +2863,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>3.57499527931213</v>
+        <v>3.57499504089355</v>
       </c>
       <c r="H86" t="n">
         <v>6205</v>
@@ -2921,7 +2921,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G88" t="n">
-        <v>3.621666431427</v>
+        <v>3.62166666984558</v>
       </c>
       <c r="H88" t="n">
         <v>1010</v>
@@ -3008,7 +3008,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G91" t="n">
-        <v>3.61233186721802</v>
+        <v>3.6123321056366</v>
       </c>
       <c r="H91" t="n">
         <v>5</v>
@@ -3037,7 +3037,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G92" t="n">
-        <v>3.54699277877808</v>
+        <v>3.54699301719666</v>
       </c>
       <c r="H92" t="n">
         <v>495</v>
@@ -3095,7 +3095,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G94" t="n">
-        <v>3.621666431427</v>
+        <v>3.62166666984558</v>
       </c>
       <c r="H94" t="n">
         <v>2005</v>
@@ -3153,7 +3153,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G96" t="n">
-        <v>3.67767119407654</v>
+        <v>3.67767143249512</v>
       </c>
       <c r="H96" t="n">
         <v>9735</v>
@@ -3269,7 +3269,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>3.69633984565735</v>
+        <v>3.69634008407593</v>
       </c>
       <c r="H100" t="n">
         <v>5164</v>
@@ -3298,7 +3298,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G101" t="n">
-        <v>3.69633984565735</v>
+        <v>3.69634008407593</v>
       </c>
       <c r="H101" t="n">
         <v>1750</v>
@@ -3414,7 +3414,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G105" t="n">
-        <v>3.64966893196106</v>
+        <v>3.64966869354248</v>
       </c>
       <c r="H105" t="n">
         <v>1680</v>
@@ -3443,7 +3443,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G106" t="n">
-        <v>3.79901623725891</v>
+        <v>3.79901599884033</v>
       </c>
       <c r="H106" t="n">
         <v>10585</v>
@@ -3501,7 +3501,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G108" t="n">
-        <v>3.81768441200256</v>
+        <v>3.81768465042114</v>
       </c>
       <c r="H108" t="n">
         <v>7940</v>
@@ -3559,7 +3559,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G110" t="n">
-        <v>3.81768441200256</v>
+        <v>3.81768465042114</v>
       </c>
       <c r="H110" t="n">
         <v>41689</v>
@@ -3588,7 +3588,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>3.80834984779358</v>
+        <v>3.80835008621216</v>
       </c>
       <c r="H111" t="n">
         <v>19699</v>
@@ -3617,7 +3617,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G112" t="n">
-        <v>3.80834984779358</v>
+        <v>3.80835008621216</v>
       </c>
       <c r="H112" t="n">
         <v>17603</v>
@@ -3733,7 +3733,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G116" t="n">
-        <v>3.76167917251587</v>
+        <v>3.76167941093445</v>
       </c>
       <c r="H116" t="n">
         <v>40346</v>
@@ -3762,7 +3762,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>3.75234508514404</v>
+        <v>3.75234484672546</v>
       </c>
       <c r="H117" t="n">
         <v>7599</v>
@@ -3849,7 +3849,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>3.78034782409668</v>
+        <v>3.7803475856781</v>
       </c>
       <c r="H120" t="n">
         <v>12037</v>
@@ -3878,7 +3878,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G121" t="n">
-        <v>3.79901623725891</v>
+        <v>3.79901599884033</v>
       </c>
       <c r="H121" t="n">
         <v>12025</v>
@@ -3936,7 +3936,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G123" t="n">
-        <v>3.85502099990845</v>
+        <v>3.85502123832703</v>
       </c>
       <c r="H123" t="n">
         <v>5193</v>
@@ -4023,7 +4023,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G126" t="n">
-        <v>3.80834984779358</v>
+        <v>3.80835008621216</v>
       </c>
       <c r="H126" t="n">
         <v>1562</v>
@@ -4110,7 +4110,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G129" t="n">
-        <v>3.78034782409668</v>
+        <v>3.7803475856781</v>
       </c>
       <c r="H129" t="n">
         <v>535</v>
@@ -4139,7 +4139,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G130" t="n">
-        <v>3.74301075935364</v>
+        <v>3.7430112361908</v>
       </c>
       <c r="H130" t="n">
         <v>76762</v>
@@ -4197,7 +4197,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G132" t="n">
-        <v>3.8456871509552</v>
+        <v>3.84568667411804</v>
       </c>
       <c r="H132" t="n">
         <v>2547</v>
@@ -4429,7 +4429,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G140" t="n">
-        <v>3.9390287399292</v>
+        <v>3.93902850151062</v>
       </c>
       <c r="H140" t="n">
         <v>3505</v>
@@ -4545,7 +4545,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G144" t="n">
-        <v>3.9390287399292</v>
+        <v>3.93902850151062</v>
       </c>
       <c r="H144" t="n">
         <v>3005</v>
@@ -4574,7 +4574,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G145" t="n">
-        <v>3.89235782623291</v>
+        <v>3.89235806465149</v>
       </c>
       <c r="H145" t="n">
         <v>14</v>
@@ -4661,7 +4661,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G148" t="n">
-        <v>3.95769667625427</v>
+        <v>3.95769715309143</v>
       </c>
       <c r="H148" t="n">
         <v>228432</v>
@@ -4690,7 +4690,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G149" t="n">
-        <v>4.04170513153076</v>
+        <v>4.0417046546936</v>
       </c>
       <c r="H149" t="n">
         <v>42576</v>
@@ -4777,7 +4777,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G152" t="n">
-        <v>4.27505922317505</v>
+        <v>4.27505970001221</v>
       </c>
       <c r="H152" t="n">
         <v>10712</v>
@@ -4835,7 +4835,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G154" t="n">
-        <v>4.35906791687012</v>
+        <v>4.35906744003296</v>
       </c>
       <c r="H154" t="n">
         <v>15474</v>
@@ -4864,7 +4864,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G155" t="n">
-        <v>4.40573787689209</v>
+        <v>4.40573835372925</v>
       </c>
       <c r="H155" t="n">
         <v>10834</v>
@@ -4922,7 +4922,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G157" t="n">
-        <v>4.40573787689209</v>
+        <v>4.40573835372925</v>
       </c>
       <c r="H157" t="n">
         <v>4479</v>
@@ -4980,7 +4980,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G159" t="n">
-        <v>4.19105195999146</v>
+        <v>4.1910514831543</v>
       </c>
       <c r="H159" t="n">
         <v>105</v>
@@ -5009,7 +5009,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G160" t="n">
-        <v>4.23772239685059</v>
+        <v>4.23772287368774</v>
       </c>
       <c r="H160" t="n">
         <v>1012</v>
@@ -5038,7 +5038,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G161" t="n">
-        <v>4.17238283157349</v>
+        <v>4.17238330841064</v>
       </c>
       <c r="H161" t="n">
         <v>1389</v>
@@ -5067,7 +5067,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G162" t="n">
-        <v>4.14438056945801</v>
+        <v>4.14438104629517</v>
       </c>
       <c r="H162" t="n">
         <v>5657</v>
@@ -5125,7 +5125,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G164" t="n">
-        <v>4.0697078704834</v>
+        <v>4.06970739364624</v>
       </c>
       <c r="H164" t="n">
         <v>8003</v>
@@ -5154,7 +5154,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G165" t="n">
-        <v>4.1070442199707</v>
+        <v>4.10704469680786</v>
       </c>
       <c r="H165" t="n">
         <v>765</v>
@@ -5241,7 +5241,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>4.05103874206543</v>
+        <v>4.05103921890259</v>
       </c>
       <c r="H168" t="n">
         <v>499</v>
@@ -5270,7 +5270,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G169" t="n">
-        <v>4.14438056945801</v>
+        <v>4.14438104629517</v>
       </c>
       <c r="H169" t="n">
         <v>4433</v>
@@ -5386,7 +5386,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G173" t="n">
-        <v>4.06037330627441</v>
+        <v>4.06037282943726</v>
       </c>
       <c r="H173" t="n">
         <v>6766</v>
@@ -5444,7 +5444,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G175" t="n">
-        <v>3.49098753929138</v>
+        <v>3.49098777770996</v>
       </c>
       <c r="H175" t="n">
         <v>5376</v>
@@ -5502,7 +5502,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G177" t="n">
-        <v>3.64966893196106</v>
+        <v>3.64966869354248</v>
       </c>
       <c r="H177" t="n">
         <v>15736</v>
@@ -5560,7 +5560,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G179" t="n">
-        <v>3.4536509513855</v>
+        <v>3.45365071296692</v>
       </c>
       <c r="H179" t="n">
         <v>1256</v>
@@ -5589,7 +5589,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G180" t="n">
-        <v>3.56566095352173</v>
+        <v>3.56566119194031</v>
       </c>
       <c r="H180" t="n">
         <v>6037</v>
@@ -5618,7 +5618,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G181" t="n">
-        <v>3.51899003982544</v>
+        <v>3.51899027824402</v>
       </c>
       <c r="H181" t="n">
         <v>1786</v>
@@ -5821,7 +5821,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G188" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H188" t="n">
         <v>6941</v>
@@ -5850,7 +5850,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G189" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G190" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H190" t="n">
         <v>500</v>
@@ -5908,7 +5908,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G191" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -5937,7 +5937,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G192" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -6111,7 +6111,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G198" t="n">
-        <v>2.45489239692688</v>
+        <v>2.45489263534546</v>
       </c>
       <c r="H198" t="n">
         <v>3279</v>
@@ -6140,7 +6140,7 @@
         <v>2.5</v>
       </c>
       <c r="G199" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H199" t="n">
         <v>300</v>
@@ -6169,7 +6169,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G200" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H200" t="n">
         <v>925</v>
@@ -6227,7 +6227,7 @@
         <v>2.5</v>
       </c>
       <c r="G202" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H202" t="n">
         <v>2588</v>
@@ -6256,7 +6256,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G203" t="n">
-        <v>2.34288215637207</v>
+        <v>2.34288191795349</v>
       </c>
       <c r="H203" t="n">
         <v>400</v>
@@ -6285,7 +6285,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G204" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H204" t="n">
         <v>3549</v>
@@ -6430,7 +6430,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G209" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H209" t="n">
         <v>865</v>
@@ -6517,7 +6517,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>2.76292061805725</v>
+        <v>2.76292085647583</v>
       </c>
       <c r="H212" t="n">
         <v>1030</v>
@@ -6575,7 +6575,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G214" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H214" t="n">
         <v>7441</v>
@@ -6691,7 +6691,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G218" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H218" t="n">
         <v>488</v>
@@ -6749,7 +6749,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G220" t="n">
-        <v>2.85626268386841</v>
+        <v>2.85626244544983</v>
       </c>
       <c r="H220" t="n">
         <v>4706</v>
@@ -6952,7 +6952,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G227" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H227" t="n">
         <v>6933</v>
@@ -7039,7 +7039,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G230" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H230" t="n">
         <v>676</v>
@@ -7126,7 +7126,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>2.76292061805725</v>
+        <v>2.76292085647583</v>
       </c>
       <c r="H233" t="n">
         <v>2100</v>
@@ -7155,7 +7155,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G234" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H234" t="n">
         <v>252</v>
@@ -7184,7 +7184,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G235" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H235" t="n">
         <v>350</v>
@@ -7271,7 +7271,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G238" t="n">
-        <v>2.85626268386841</v>
+        <v>2.85626244544983</v>
       </c>
       <c r="H238" t="n">
         <v>3815</v>
@@ -7300,7 +7300,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G239" t="n">
-        <v>2.85626268386841</v>
+        <v>2.85626244544983</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -7329,7 +7329,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G240" t="n">
-        <v>2.82825994491577</v>
+        <v>2.82826018333435</v>
       </c>
       <c r="H240" t="n">
         <v>950</v>
@@ -7474,7 +7474,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G245" t="n">
-        <v>2.82825994491577</v>
+        <v>2.82826018333435</v>
       </c>
       <c r="H245" t="n">
         <v>1750</v>
@@ -7503,7 +7503,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G246" t="n">
-        <v>3.01494359970093</v>
+        <v>3.01494383811951</v>
       </c>
       <c r="H246" t="n">
         <v>3050</v>
@@ -7648,7 +7648,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G251" t="n">
-        <v>2.78158903121948</v>
+        <v>2.78158926963806</v>
       </c>
       <c r="H251" t="n">
         <v>411</v>
@@ -7706,7 +7706,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G253" t="n">
-        <v>2.82825994491577</v>
+        <v>2.82826018333435</v>
       </c>
       <c r="H253" t="n">
         <v>19598</v>
@@ -7735,7 +7735,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G254" t="n">
-        <v>2.82825994491577</v>
+        <v>2.82826018333435</v>
       </c>
       <c r="H254" t="n">
         <v>2500</v>
@@ -7822,7 +7822,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G257" t="n">
-        <v>2.78158903121948</v>
+        <v>2.78158926963806</v>
       </c>
       <c r="H257" t="n">
         <v>9597</v>
@@ -8228,7 +8228,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G271" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H271" t="n">
         <v>110</v>
@@ -8286,7 +8286,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G273" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H273" t="n">
         <v>3807</v>
@@ -8315,7 +8315,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G274" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H274" t="n">
         <v>12686</v>
@@ -8344,7 +8344,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G275" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H275" t="n">
         <v>3412</v>
@@ -8373,7 +8373,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G276" t="n">
-        <v>2.49222922325134</v>
+        <v>2.49222898483276</v>
       </c>
       <c r="H276" t="n">
         <v>2643</v>
@@ -8402,7 +8402,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G277" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H277" t="n">
         <v>689</v>
@@ -8431,7 +8431,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G278" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H278" t="n">
         <v>0</v>
@@ -8460,7 +8460,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G279" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H279" t="n">
         <v>1890</v>
@@ -8489,7 +8489,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G280" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H280" t="n">
         <v>3085</v>
@@ -8518,7 +8518,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G281" t="n">
-        <v>2.47356104850769</v>
+        <v>2.47356081008911</v>
       </c>
       <c r="H281" t="n">
         <v>1069</v>
@@ -8547,7 +8547,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G282" t="n">
-        <v>2.48289489746094</v>
+        <v>2.48289513587952</v>
       </c>
       <c r="H282" t="n">
         <v>1691</v>
@@ -8750,7 +8750,7 @@
         <v>2.5</v>
       </c>
       <c r="G289" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H289" t="n">
         <v>5004</v>
@@ -8866,7 +8866,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G293" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H293" t="n">
         <v>3579</v>
@@ -8895,7 +8895,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G294" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H294" t="n">
         <v>2595</v>
@@ -8982,7 +8982,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G297" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H297" t="n">
         <v>238</v>
@@ -9011,7 +9011,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G298" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H298" t="n">
         <v>0</v>
@@ -9098,7 +9098,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G301" t="n">
-        <v>2.47356104850769</v>
+        <v>2.47356081008911</v>
       </c>
       <c r="H301" t="n">
         <v>9559</v>
@@ -9127,7 +9127,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G302" t="n">
-        <v>2.47356104850769</v>
+        <v>2.47356081008911</v>
       </c>
       <c r="H302" t="n">
         <v>2820</v>
@@ -9156,7 +9156,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G303" t="n">
-        <v>2.49222922325134</v>
+        <v>2.49222898483276</v>
       </c>
       <c r="H303" t="n">
         <v>782</v>
@@ -9185,7 +9185,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G304" t="n">
-        <v>2.49222922325134</v>
+        <v>2.49222898483276</v>
       </c>
       <c r="H304" t="n">
         <v>5</v>
@@ -9214,7 +9214,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G305" t="n">
-        <v>2.49222922325134</v>
+        <v>2.49222898483276</v>
       </c>
       <c r="H305" t="n">
         <v>17210</v>
@@ -9330,7 +9330,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G309" t="n">
-        <v>2.45489239692688</v>
+        <v>2.45489263534546</v>
       </c>
       <c r="H309" t="n">
         <v>16887</v>
@@ -9359,7 +9359,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G310" t="n">
-        <v>2.47356104850769</v>
+        <v>2.47356081008911</v>
       </c>
       <c r="H310" t="n">
         <v>1449</v>
@@ -9388,7 +9388,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G311" t="n">
-        <v>2.48289489746094</v>
+        <v>2.48289513587952</v>
       </c>
       <c r="H311" t="n">
         <v>204</v>
@@ -9417,7 +9417,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G312" t="n">
-        <v>2.48289489746094</v>
+        <v>2.48289513587952</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G313" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H313" t="n">
         <v>350</v>
@@ -9765,7 +9765,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G324" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H324" t="n">
         <v>1280</v>
@@ -9794,7 +9794,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G325" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G326" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155009269714</v>
       </c>
       <c r="H326" t="n">
         <v>4022</v>
@@ -9881,7 +9881,7 @@
         <v>2.5</v>
       </c>
       <c r="G328" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H328" t="n">
         <v>3490</v>
@@ -10026,7 +10026,7 @@
         <v>2.5</v>
       </c>
       <c r="G333" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H333" t="n">
         <v>7692</v>
@@ -10055,7 +10055,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G334" t="n">
-        <v>2.24020600318909</v>
+        <v>2.24020576477051</v>
       </c>
       <c r="H334" t="n">
         <v>4089</v>
@@ -10142,7 +10142,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G337" t="n">
-        <v>2.24020600318909</v>
+        <v>2.24020576477051</v>
       </c>
       <c r="H337" t="n">
         <v>15170</v>
@@ -10171,7 +10171,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>2.1935350894928</v>
+        <v>2.19353485107422</v>
       </c>
       <c r="H338" t="n">
         <v>17797</v>
@@ -10229,7 +10229,7 @@
         <v>2.25</v>
       </c>
       <c r="G340" t="n">
-        <v>2.10019326210022</v>
+        <v>2.10019302368164</v>
       </c>
       <c r="H340" t="n">
         <v>17080</v>
@@ -10258,7 +10258,7 @@
         <v>2.25</v>
       </c>
       <c r="G341" t="n">
-        <v>2.10019326210022</v>
+        <v>2.10019302368164</v>
       </c>
       <c r="H341" t="n">
         <v>6035</v>
@@ -10316,7 +10316,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G343" t="n">
-        <v>1.98818302154541</v>
+        <v>1.98818290233612</v>
       </c>
       <c r="H343" t="n">
         <v>9524</v>
@@ -10345,7 +10345,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G344" t="n">
-        <v>1.9228435754776</v>
+        <v>1.92284333705902</v>
       </c>
       <c r="H344" t="n">
         <v>5020</v>
@@ -10374,7 +10374,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G345" t="n">
-        <v>1.87617254257202</v>
+        <v>1.87617242336273</v>
       </c>
       <c r="H345" t="n">
         <v>10119</v>
@@ -10461,7 +10461,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G348" t="n">
-        <v>1.76416218280792</v>
+        <v>1.76416206359863</v>
       </c>
       <c r="H348" t="n">
         <v>3234</v>
@@ -10519,7 +10519,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G350" t="n">
-        <v>1.68015432357788</v>
+        <v>1.68015444278717</v>
       </c>
       <c r="H350" t="n">
         <v>3654</v>
@@ -10548,7 +10548,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G351" t="n">
-        <v>1.57747852802277</v>
+        <v>1.57747840881348</v>
       </c>
       <c r="H351" t="n">
         <v>44141</v>
@@ -10577,7 +10577,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G352" t="n">
-        <v>1.53080725669861</v>
+        <v>1.5308073759079</v>
       </c>
       <c r="H352" t="n">
         <v>32342</v>
@@ -10606,7 +10606,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G353" t="n">
-        <v>1.50747179985046</v>
+        <v>1.50747191905975</v>
       </c>
       <c r="H353" t="n">
         <v>17138</v>
@@ -10751,7 +10751,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G358" t="n">
-        <v>1.5354745388031</v>
+        <v>1.53547441959381</v>
       </c>
       <c r="H358" t="n">
         <v>224765</v>
@@ -10780,7 +10780,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G359" t="n">
-        <v>1.5868124961853</v>
+        <v>1.58681261539459</v>
       </c>
       <c r="H359" t="n">
         <v>162717</v>
@@ -10809,7 +10809,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G360" t="n">
-        <v>1.54947566986084</v>
+        <v>1.54947578907013</v>
       </c>
       <c r="H360" t="n">
         <v>52791</v>
@@ -10896,7 +10896,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G363" t="n">
-        <v>1.84816992282867</v>
+        <v>1.84817004203796</v>
       </c>
       <c r="H363" t="n">
         <v>74595</v>
@@ -10983,7 +10983,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G366" t="n">
-        <v>2.02551937103271</v>
+        <v>2.02551960945129</v>
       </c>
       <c r="H366" t="n">
         <v>41167</v>
@@ -11041,7 +11041,7 @@
         <v>2.25</v>
       </c>
       <c r="G368" t="n">
-        <v>2.10019326210022</v>
+        <v>2.10019302368164</v>
       </c>
       <c r="H368" t="n">
         <v>40808</v>
@@ -11273,7 +11273,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G376" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H376" t="n">
         <v>260524</v>
@@ -11302,7 +11302,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G377" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H377" t="n">
         <v>89733</v>
@@ -11418,7 +11418,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G381" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H381" t="n">
         <v>13489</v>
@@ -11505,7 +11505,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G384" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155009269714</v>
       </c>
       <c r="H384" t="n">
         <v>46528</v>
@@ -11534,7 +11534,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G385" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H385" t="n">
         <v>14657</v>
@@ -11563,7 +11563,7 @@
         <v>2.5</v>
       </c>
       <c r="G386" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H386" t="n">
         <v>14989</v>
@@ -11679,7 +11679,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G390" t="n">
-        <v>2.49222922325134</v>
+        <v>2.49222898483276</v>
       </c>
       <c r="H390" t="n">
         <v>23339</v>
@@ -11737,7 +11737,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G392" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H392" t="n">
         <v>78496</v>
@@ -11795,7 +11795,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G394" t="n">
-        <v>2.47356104850769</v>
+        <v>2.47356081008911</v>
       </c>
       <c r="H394" t="n">
         <v>21034</v>
@@ -11911,7 +11911,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H398" t="n">
         <v>4671</v>
@@ -11940,7 +11940,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G399" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H399" t="n">
         <v>20075</v>
@@ -11969,7 +11969,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G400" t="n">
-        <v>2.20286893844604</v>
+        <v>2.20286917686462</v>
       </c>
       <c r="H400" t="n">
         <v>35084</v>
@@ -11998,7 +11998,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G401" t="n">
-        <v>2.072190284729</v>
+        <v>2.07219052314758</v>
       </c>
       <c r="H401" t="n">
         <v>51398</v>
@@ -12056,7 +12056,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G403" t="n">
-        <v>2.17486667633057</v>
+        <v>2.17486643791199</v>
       </c>
       <c r="H403" t="n">
         <v>18632</v>
@@ -12085,7 +12085,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G404" t="n">
-        <v>2.17486667633057</v>
+        <v>2.17486643791199</v>
       </c>
       <c r="H404" t="n">
         <v>10603</v>
@@ -12114,7 +12114,7 @@
         <v>2.25</v>
       </c>
       <c r="G405" t="n">
-        <v>2.10019326210022</v>
+        <v>2.10019302368164</v>
       </c>
       <c r="H405" t="n">
         <v>50986</v>
@@ -12143,7 +12143,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G406" t="n">
-        <v>2.05352210998535</v>
+        <v>2.05352234840393</v>
       </c>
       <c r="H406" t="n">
         <v>51628</v>
@@ -12172,7 +12172,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G407" t="n">
-        <v>2.1935350894928</v>
+        <v>2.19353485107422</v>
       </c>
       <c r="H407" t="n">
         <v>30243</v>
@@ -12201,7 +12201,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G408" t="n">
-        <v>2.20286893844604</v>
+        <v>2.20286917686462</v>
       </c>
       <c r="H408" t="n">
         <v>20357</v>
@@ -12259,7 +12259,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G410" t="n">
-        <v>2.05352210998535</v>
+        <v>2.05352234840393</v>
       </c>
       <c r="H410" t="n">
         <v>55928</v>
@@ -12288,7 +12288,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G411" t="n">
-        <v>2.05352210998535</v>
+        <v>2.05352234840393</v>
       </c>
       <c r="H411" t="n">
         <v>27870</v>
@@ -12317,7 +12317,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G412" t="n">
-        <v>2.05352210998535</v>
+        <v>2.05352234840393</v>
       </c>
       <c r="H412" t="n">
         <v>10965</v>
@@ -12346,7 +12346,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G413" t="n">
-        <v>2.05352210998535</v>
+        <v>2.05352234840393</v>
       </c>
       <c r="H413" t="n">
         <v>6880</v>
@@ -12404,7 +12404,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G415" t="n">
-        <v>2.18420052528381</v>
+        <v>2.18420076370239</v>
       </c>
       <c r="H415" t="n">
         <v>21434</v>
@@ -12578,7 +12578,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G421" t="n">
-        <v>2.34288215637207</v>
+        <v>2.34288191795349</v>
       </c>
       <c r="H421" t="n">
         <v>34127</v>
@@ -12665,7 +12665,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G424" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H424" t="n">
         <v>4139</v>
@@ -12839,7 +12839,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G430" t="n">
-        <v>2.25887441635132</v>
+        <v>2.2588746547699</v>
       </c>
       <c r="H430" t="n">
         <v>8648</v>
@@ -12868,7 +12868,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G431" t="n">
-        <v>2.25887441635132</v>
+        <v>2.2588746547699</v>
       </c>
       <c r="H431" t="n">
         <v>10630</v>
@@ -12926,7 +12926,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G433" t="n">
-        <v>2.25887441635132</v>
+        <v>2.2588746547699</v>
       </c>
       <c r="H433" t="n">
         <v>39250</v>
@@ -12955,7 +12955,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G434" t="n">
-        <v>2.24020600318909</v>
+        <v>2.24020576477051</v>
       </c>
       <c r="H434" t="n">
         <v>3580</v>
@@ -12984,7 +12984,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G435" t="n">
-        <v>2.24954009056091</v>
+        <v>2.24954032897949</v>
       </c>
       <c r="H435" t="n">
         <v>1950</v>
@@ -13042,7 +13042,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G437" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H437" t="n">
         <v>10145</v>
@@ -13129,7 +13129,7 @@
         <v>2.5</v>
       </c>
       <c r="G440" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H440" t="n">
         <v>11714</v>
@@ -13187,7 +13187,7 @@
         <v>2.5</v>
       </c>
       <c r="G442" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H442" t="n">
         <v>13466</v>
@@ -13245,7 +13245,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G444" t="n">
-        <v>2.24954009056091</v>
+        <v>2.24954032897949</v>
       </c>
       <c r="H444" t="n">
         <v>11540</v>
@@ -13361,7 +13361,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G448" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H448" t="n">
         <v>75506</v>
@@ -13419,7 +13419,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G450" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H450" t="n">
         <v>45849</v>
@@ -13506,7 +13506,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G453" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H453" t="n">
         <v>35893</v>
@@ -13535,7 +13535,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G454" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H454" t="n">
         <v>25836</v>
@@ -13709,7 +13709,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G460" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H460" t="n">
         <v>44981</v>
@@ -13854,7 +13854,7 @@
         <v>3.25</v>
       </c>
       <c r="G465" t="n">
-        <v>3.03361201286316</v>
+        <v>3.03361225128174</v>
       </c>
       <c r="H465" t="n">
         <v>83242</v>
@@ -13912,7 +13912,7 @@
         <v>3.25</v>
       </c>
       <c r="G467" t="n">
-        <v>3.03361201286316</v>
+        <v>3.03361225128174</v>
       </c>
       <c r="H467" t="n">
         <v>62595</v>
@@ -13970,7 +13970,7 @@
         <v>3.25</v>
       </c>
       <c r="G469" t="n">
-        <v>3.03361201286316</v>
+        <v>3.03361225128174</v>
       </c>
       <c r="H469" t="n">
         <v>22979</v>
@@ -13999,7 +13999,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G470" t="n">
-        <v>3.35097479820251</v>
+        <v>3.35097455978394</v>
       </c>
       <c r="H470" t="n">
         <v>111507</v>
@@ -14028,7 +14028,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G471" t="n">
-        <v>3.27630114555359</v>
+        <v>3.27630090713501</v>
       </c>
       <c r="H471" t="n">
         <v>27454</v>
@@ -14086,7 +14086,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G473" t="n">
-        <v>3.33230638504028</v>
+        <v>3.3323061466217</v>
       </c>
       <c r="H473" t="n">
         <v>14421</v>
@@ -14173,7 +14173,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>3.17362499237061</v>
+        <v>3.17362523078918</v>
       </c>
       <c r="H476" t="n">
         <v>25140</v>
@@ -14260,7 +14260,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G479" t="n">
-        <v>3.16429090499878</v>
+        <v>3.16429114341736</v>
       </c>
       <c r="H479" t="n">
         <v>22442</v>
@@ -14289,7 +14289,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G480" t="n">
-        <v>3.20162796974182</v>
+        <v>3.20162773132324</v>
       </c>
       <c r="H480" t="n">
         <v>55118</v>
@@ -14376,7 +14376,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G483" t="n">
-        <v>3.12695384025574</v>
+        <v>3.12695407867432</v>
       </c>
       <c r="H483" t="n">
         <v>32378</v>
@@ -14434,7 +14434,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G485" t="n">
-        <v>3.15495705604553</v>
+        <v>3.15495681762695</v>
       </c>
       <c r="H485" t="n">
         <v>12813</v>
@@ -14463,7 +14463,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G486" t="n">
-        <v>3.17362499237061</v>
+        <v>3.17362523078918</v>
       </c>
       <c r="H486" t="n">
         <v>33087</v>
@@ -14521,7 +14521,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G488" t="n">
-        <v>3.16429090499878</v>
+        <v>3.16429114341736</v>
       </c>
       <c r="H488" t="n">
         <v>32411</v>
@@ -14666,7 +14666,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G493" t="n">
-        <v>3.04294657707214</v>
+        <v>3.04294633865356</v>
       </c>
       <c r="H493" t="n">
         <v>3499</v>
@@ -14811,7 +14811,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G498" t="n">
-        <v>3.0709490776062</v>
+        <v>3.07094883918762</v>
       </c>
       <c r="H498" t="n">
         <v>13299</v>
@@ -14898,7 +14898,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G501" t="n">
-        <v>3.06161451339722</v>
+        <v>3.0616147518158</v>
       </c>
       <c r="H501" t="n">
         <v>13910</v>
@@ -14927,7 +14927,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G502" t="n">
-        <v>3.09895133972168</v>
+        <v>3.09895157814026</v>
       </c>
       <c r="H502" t="n">
         <v>27956</v>
@@ -14956,7 +14956,7 @@
         <v>3.25</v>
       </c>
       <c r="G503" t="n">
-        <v>3.03361201286316</v>
+        <v>3.03361225128174</v>
       </c>
       <c r="H503" t="n">
         <v>5248</v>
@@ -15014,7 +15014,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G505" t="n">
-        <v>3.00560975074768</v>
+        <v>3.0056095123291</v>
       </c>
       <c r="H505" t="n">
         <v>10540</v>
@@ -15159,7 +15159,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G510" t="n">
-        <v>3.00560975074768</v>
+        <v>3.0056095123291</v>
       </c>
       <c r="H510" t="n">
         <v>10066</v>
@@ -15188,7 +15188,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G511" t="n">
-        <v>2.7442524433136</v>
+        <v>2.74425220489502</v>
       </c>
       <c r="H511" t="n">
         <v>47993</v>
@@ -15217,7 +15217,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G512" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H512" t="n">
         <v>87951</v>
@@ -15275,7 +15275,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G514" t="n">
-        <v>2.78158903121948</v>
+        <v>2.78158926963806</v>
       </c>
       <c r="H514" t="n">
         <v>5508</v>
@@ -15333,7 +15333,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G516" t="n">
-        <v>2.7442524433136</v>
+        <v>2.74425220489502</v>
       </c>
       <c r="H516" t="n">
         <v>7255</v>
@@ -15420,7 +15420,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G519" t="n">
-        <v>2.7442524433136</v>
+        <v>2.74425220489502</v>
       </c>
       <c r="H519" t="n">
         <v>22223</v>
@@ -15449,7 +15449,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G520" t="n">
-        <v>2.7442524433136</v>
+        <v>2.74425220489502</v>
       </c>
       <c r="H520" t="n">
         <v>5309</v>
@@ -15507,7 +15507,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G522" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H522" t="n">
         <v>18120</v>
@@ -15681,7 +15681,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G528" t="n">
-        <v>2.49222922325134</v>
+        <v>2.49222898483276</v>
       </c>
       <c r="H528" t="n">
         <v>36945</v>
@@ -15739,7 +15739,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G530" t="n">
-        <v>2.49222922325134</v>
+        <v>2.49222898483276</v>
       </c>
       <c r="H530" t="n">
         <v>44466</v>
@@ -15768,7 +15768,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G531" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H531" t="n">
         <v>29110</v>
@@ -15826,7 +15826,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G533" t="n">
-        <v>2.45489239692688</v>
+        <v>2.45489263534546</v>
       </c>
       <c r="H533" t="n">
         <v>27587</v>
@@ -15855,7 +15855,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G534" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H534" t="n">
         <v>58949</v>
@@ -15884,7 +15884,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G535" t="n">
-        <v>2.53890037536621</v>
+        <v>2.53889989852905</v>
       </c>
       <c r="H535" t="n">
         <v>31474</v>
@@ -15913,7 +15913,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G536" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H536" t="n">
         <v>18439</v>
@@ -16087,7 +16087,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G542" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H542" t="n">
         <v>34564</v>
@@ -16290,7 +16290,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G549" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H549" t="n">
         <v>9940</v>
@@ -16638,7 +16638,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G561" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H561" t="n">
         <v>55511</v>
@@ -16754,7 +16754,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G565" t="n">
-        <v>2.78158903121948</v>
+        <v>2.78158926963806</v>
       </c>
       <c r="H565" t="n">
         <v>5626</v>
@@ -16783,7 +16783,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G566" t="n">
-        <v>2.86559653282166</v>
+        <v>2.86559677124023</v>
       </c>
       <c r="H566" t="n">
         <v>4904</v>
@@ -16841,7 +16841,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G568" t="n">
-        <v>2.78158903121948</v>
+        <v>2.78158926963806</v>
       </c>
       <c r="H568" t="n">
         <v>6622</v>
@@ -16928,7 +16928,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G571" t="n">
-        <v>2.82825994491577</v>
+        <v>2.82826018333435</v>
       </c>
       <c r="H571" t="n">
         <v>2855</v>
@@ -17073,7 +17073,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G576" t="n">
-        <v>2.7442524433136</v>
+        <v>2.74425220489502</v>
       </c>
       <c r="H576" t="n">
         <v>4135</v>
@@ -17102,7 +17102,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G577" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H577" t="n">
         <v>5655</v>
@@ -17131,7 +17131,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G578" t="n">
-        <v>2.82825994491577</v>
+        <v>2.82826018333435</v>
       </c>
       <c r="H578" t="n">
         <v>6954</v>
@@ -17160,7 +17160,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G579" t="n">
-        <v>2.78158903121948</v>
+        <v>2.78158926963806</v>
       </c>
       <c r="H579" t="n">
         <v>2133</v>
@@ -17276,7 +17276,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G583" t="n">
-        <v>2.76292061805725</v>
+        <v>2.76292085647583</v>
       </c>
       <c r="H583" t="n">
         <v>1500</v>
@@ -17305,7 +17305,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G584" t="n">
-        <v>2.78158903121948</v>
+        <v>2.78158926963806</v>
       </c>
       <c r="H584" t="n">
         <v>6045</v>
@@ -17334,7 +17334,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G585" t="n">
-        <v>2.78158903121948</v>
+        <v>2.78158926963806</v>
       </c>
       <c r="H585" t="n">
         <v>1601</v>
@@ -17450,7 +17450,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G589" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H589" t="n">
         <v>5281</v>
@@ -17595,7 +17595,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G594" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H594" t="n">
         <v>3352</v>
@@ -17740,7 +17740,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G599" t="n">
-        <v>2.7442524433136</v>
+        <v>2.74425220489502</v>
       </c>
       <c r="H599" t="n">
         <v>13898</v>
@@ -17798,7 +17798,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G601" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H601" t="n">
         <v>11543</v>
@@ -17827,7 +17827,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G602" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H602" t="n">
         <v>22041</v>
@@ -17885,7 +17885,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G604" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H604" t="n">
         <v>5168</v>
@@ -17943,7 +17943,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H606" t="n">
         <v>1325</v>
@@ -17972,7 +17972,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G607" t="n">
-        <v>2.7442524433136</v>
+        <v>2.74425220489502</v>
       </c>
       <c r="H607" t="n">
         <v>1800</v>
@@ -18001,7 +18001,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G608" t="n">
-        <v>2.78158903121948</v>
+        <v>2.78158926963806</v>
       </c>
       <c r="H608" t="n">
         <v>7882</v>
@@ -18030,7 +18030,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G609" t="n">
-        <v>2.76292061805725</v>
+        <v>2.76292085647583</v>
       </c>
       <c r="H609" t="n">
         <v>13444</v>
@@ -18088,7 +18088,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G611" t="n">
-        <v>2.82825994491577</v>
+        <v>2.82826018333435</v>
       </c>
       <c r="H611" t="n">
         <v>2800</v>
@@ -18146,7 +18146,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G613" t="n">
-        <v>2.82825994491577</v>
+        <v>2.82826018333435</v>
       </c>
       <c r="H613" t="n">
         <v>7360</v>
@@ -18204,7 +18204,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G615" t="n">
-        <v>2.78158903121948</v>
+        <v>2.78158926963806</v>
       </c>
       <c r="H615" t="n">
         <v>21813</v>
@@ -18349,7 +18349,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G620" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H620" t="n">
         <v>12267</v>
@@ -18378,7 +18378,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G621" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H621" t="n">
         <v>13278</v>
@@ -18407,7 +18407,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G622" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H622" t="n">
         <v>9853</v>
@@ -18465,7 +18465,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G624" t="n">
-        <v>2.47356104850769</v>
+        <v>2.47356081008911</v>
       </c>
       <c r="H624" t="n">
         <v>17921</v>
@@ -18494,7 +18494,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G625" t="n">
-        <v>2.48289489746094</v>
+        <v>2.48289513587952</v>
       </c>
       <c r="H625" t="n">
         <v>9305</v>
@@ -18552,7 +18552,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G627" t="n">
-        <v>2.48289489746094</v>
+        <v>2.48289513587952</v>
       </c>
       <c r="H627" t="n">
         <v>3175</v>
@@ -18581,7 +18581,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G628" t="n">
-        <v>2.47356104850769</v>
+        <v>2.47356081008911</v>
       </c>
       <c r="H628" t="n">
         <v>7127</v>
@@ -18610,7 +18610,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G629" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H629" t="n">
         <v>9381</v>
@@ -18639,7 +18639,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G630" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H630" t="n">
         <v>5890</v>
@@ -18842,7 +18842,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G637" t="n">
-        <v>2.53890037536621</v>
+        <v>2.53889989852905</v>
       </c>
       <c r="H637" t="n">
         <v>7036</v>
@@ -18871,7 +18871,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G638" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H638" t="n">
         <v>10004</v>
@@ -18929,7 +18929,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G640" t="n">
-        <v>2.49222922325134</v>
+        <v>2.49222898483276</v>
       </c>
       <c r="H640" t="n">
         <v>15217</v>
@@ -18987,7 +18987,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G642" t="n">
-        <v>2.47356104850769</v>
+        <v>2.47356081008911</v>
       </c>
       <c r="H642" t="n">
         <v>25000</v>
@@ -19103,7 +19103,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G646" t="n">
-        <v>2.49222922325134</v>
+        <v>2.49222898483276</v>
       </c>
       <c r="H646" t="n">
         <v>4792</v>
@@ -19132,7 +19132,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G647" t="n">
-        <v>2.49222922325134</v>
+        <v>2.49222898483276</v>
       </c>
       <c r="H647" t="n">
         <v>6674</v>
@@ -19161,7 +19161,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G648" t="n">
-        <v>2.53890037536621</v>
+        <v>2.53889989852905</v>
       </c>
       <c r="H648" t="n">
         <v>20795</v>
@@ -19190,7 +19190,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G649" t="n">
-        <v>2.53890037536621</v>
+        <v>2.53889989852905</v>
       </c>
       <c r="H649" t="n">
         <v>26026</v>
@@ -19277,7 +19277,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G652" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H652" t="n">
         <v>6533</v>
@@ -19306,7 +19306,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G653" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H653" t="n">
         <v>6896</v>
@@ -19364,7 +19364,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G655" t="n">
-        <v>2.47356104850769</v>
+        <v>2.47356081008911</v>
       </c>
       <c r="H655" t="n">
         <v>1680</v>
@@ -19393,7 +19393,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H656" t="n">
         <v>5573</v>
@@ -19422,7 +19422,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G657" t="n">
-        <v>2.53890037536621</v>
+        <v>2.53889989852905</v>
       </c>
       <c r="H657" t="n">
         <v>8536</v>
@@ -19451,7 +19451,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G658" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H658" t="n">
         <v>24925</v>
@@ -19567,7 +19567,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G662" t="n">
-        <v>2.53890037536621</v>
+        <v>2.53889989852905</v>
       </c>
       <c r="H662" t="n">
         <v>18926</v>
@@ -19654,7 +19654,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G665" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H665" t="n">
         <v>1580</v>
@@ -19770,7 +19770,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G669" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H669" t="n">
         <v>6000</v>
@@ -19828,7 +19828,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G671" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H671" t="n">
         <v>1055</v>
@@ -19915,7 +19915,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G674" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H674" t="n">
         <v>1004</v>
@@ -19944,7 +19944,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G675" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H675" t="n">
         <v>0</v>
@@ -20060,7 +20060,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G679" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H679" t="n">
         <v>6131</v>
@@ -20118,7 +20118,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G681" t="n">
-        <v>2.53890037536621</v>
+        <v>2.53889989852905</v>
       </c>
       <c r="H681" t="n">
         <v>1200</v>
@@ -20263,7 +20263,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G686" t="n">
-        <v>2.48289489746094</v>
+        <v>2.48289513587952</v>
       </c>
       <c r="H686" t="n">
         <v>18872</v>
@@ -20350,7 +20350,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G689" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H689" t="n">
         <v>6459</v>
@@ -20466,7 +20466,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G693" t="n">
-        <v>2.14686417579651</v>
+        <v>2.14686393737793</v>
       </c>
       <c r="H693" t="n">
         <v>5992</v>
@@ -20640,7 +20640,7 @@
         <v>2.5</v>
       </c>
       <c r="G699" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H699" t="n">
         <v>12532</v>
@@ -20756,7 +20756,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G703" t="n">
-        <v>2.34288215637207</v>
+        <v>2.34288191795349</v>
       </c>
       <c r="H703" t="n">
         <v>8222</v>
@@ -20785,7 +20785,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G704" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H704" t="n">
         <v>2380</v>
@@ -20814,7 +20814,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G705" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H705" t="n">
         <v>7231</v>
@@ -20843,7 +20843,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G706" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H706" t="n">
         <v>16794</v>
@@ -20988,7 +20988,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G711" t="n">
-        <v>2.38955307006836</v>
+        <v>2.38955283164978</v>
       </c>
       <c r="H711" t="n">
         <v>5255</v>
@@ -21046,7 +21046,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G713" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155009269714</v>
       </c>
       <c r="H713" t="n">
         <v>5601</v>
@@ -21278,7 +21278,7 @@
         <v>2.5</v>
       </c>
       <c r="G721" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H721" t="n">
         <v>780</v>
@@ -21568,7 +21568,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G731" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H731" t="n">
         <v>5608</v>
@@ -21597,7 +21597,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G732" t="n">
-        <v>2.49222922325134</v>
+        <v>2.49222898483276</v>
       </c>
       <c r="H732" t="n">
         <v>14580</v>
@@ -21626,7 +21626,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G733" t="n">
-        <v>2.38955307006836</v>
+        <v>2.38955283164978</v>
       </c>
       <c r="H733" t="n">
         <v>3359</v>
@@ -21655,7 +21655,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G734" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155009269714</v>
       </c>
       <c r="H734" t="n">
         <v>59751</v>
@@ -21713,7 +21713,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G736" t="n">
-        <v>2.24020600318909</v>
+        <v>2.24020576477051</v>
       </c>
       <c r="H736" t="n">
         <v>8673</v>
@@ -21771,7 +21771,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G738" t="n">
-        <v>2.18420052528381</v>
+        <v>2.18420076370239</v>
       </c>
       <c r="H738" t="n">
         <v>10750</v>
@@ -21829,7 +21829,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G740" t="n">
-        <v>2.1935350894928</v>
+        <v>2.19353485107422</v>
       </c>
       <c r="H740" t="n">
         <v>5880</v>
@@ -21974,7 +21974,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G745" t="n">
-        <v>2.20286893844604</v>
+        <v>2.20286917686462</v>
       </c>
       <c r="H745" t="n">
         <v>3400</v>
@@ -22003,7 +22003,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G746" t="n">
-        <v>2.14686417579651</v>
+        <v>2.14686393737793</v>
       </c>
       <c r="H746" t="n">
         <v>11917</v>
@@ -22032,7 +22032,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G747" t="n">
-        <v>2.10952734947205</v>
+        <v>2.10952711105347</v>
       </c>
       <c r="H747" t="n">
         <v>5878</v>
@@ -22119,7 +22119,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G750" t="n">
-        <v>2.10952734947205</v>
+        <v>2.10952711105347</v>
       </c>
       <c r="H750" t="n">
         <v>3015</v>
@@ -22148,7 +22148,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G751" t="n">
-        <v>2.14686417579651</v>
+        <v>2.14686393737793</v>
       </c>
       <c r="H751" t="n">
         <v>4774</v>
@@ -22177,7 +22177,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G752" t="n">
-        <v>2.14686417579651</v>
+        <v>2.14686393737793</v>
       </c>
       <c r="H752" t="n">
         <v>0</v>
@@ -22206,7 +22206,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G753" t="n">
-        <v>2.14686417579651</v>
+        <v>2.14686393737793</v>
       </c>
       <c r="H753" t="n">
         <v>1518</v>
@@ -22235,7 +22235,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G754" t="n">
-        <v>2.10952734947205</v>
+        <v>2.10952711105347</v>
       </c>
       <c r="H754" t="n">
         <v>332</v>
@@ -22264,7 +22264,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G755" t="n">
-        <v>2.11886119842529</v>
+        <v>2.11886143684387</v>
       </c>
       <c r="H755" t="n">
         <v>2015</v>
@@ -22293,7 +22293,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G756" t="n">
-        <v>2.13752961158752</v>
+        <v>2.1375298500061</v>
       </c>
       <c r="H756" t="n">
         <v>759</v>
@@ -22322,7 +22322,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G757" t="n">
-        <v>2.15619802474976</v>
+        <v>2.15619826316833</v>
       </c>
       <c r="H757" t="n">
         <v>5</v>
@@ -22351,7 +22351,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G758" t="n">
-        <v>2.24020600318909</v>
+        <v>2.24020576477051</v>
       </c>
       <c r="H758" t="n">
         <v>3859</v>
@@ -22380,7 +22380,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G759" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H759" t="n">
         <v>6674</v>
@@ -22409,7 +22409,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G760" t="n">
-        <v>2.15619802474976</v>
+        <v>2.15619826316833</v>
       </c>
       <c r="H760" t="n">
         <v>9288</v>
@@ -22438,7 +22438,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G761" t="n">
-        <v>2.11886119842529</v>
+        <v>2.11886143684387</v>
       </c>
       <c r="H761" t="n">
         <v>3433</v>
@@ -22467,7 +22467,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G762" t="n">
-        <v>2.16553235054016</v>
+        <v>2.16553211212158</v>
       </c>
       <c r="H762" t="n">
         <v>710</v>
@@ -22496,7 +22496,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G763" t="n">
-        <v>2.15619802474976</v>
+        <v>2.15619826316833</v>
       </c>
       <c r="H763" t="n">
         <v>74</v>
@@ -22525,7 +22525,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G764" t="n">
-        <v>2.10952734947205</v>
+        <v>2.10952711105347</v>
       </c>
       <c r="H764" t="n">
         <v>2010</v>
@@ -22554,7 +22554,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G765" t="n">
-        <v>2.10952734947205</v>
+        <v>2.10952711105347</v>
       </c>
       <c r="H765" t="n">
         <v>0</v>
@@ -22583,7 +22583,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G766" t="n">
-        <v>2.11886119842529</v>
+        <v>2.11886143684387</v>
       </c>
       <c r="H766" t="n">
         <v>155</v>
@@ -22612,7 +22612,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G767" t="n">
-        <v>2.14686417579651</v>
+        <v>2.14686393737793</v>
       </c>
       <c r="H767" t="n">
         <v>1300</v>
@@ -22641,7 +22641,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G768" t="n">
-        <v>2.14686417579651</v>
+        <v>2.14686393737793</v>
       </c>
       <c r="H768" t="n">
         <v>0</v>
@@ -22757,7 +22757,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G772" t="n">
-        <v>2.16553235054016</v>
+        <v>2.16553211212158</v>
       </c>
       <c r="H772" t="n">
         <v>1743</v>
@@ -22786,7 +22786,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G773" t="n">
-        <v>2.1935350894928</v>
+        <v>2.19353485107422</v>
       </c>
       <c r="H773" t="n">
         <v>499</v>
@@ -22815,7 +22815,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G774" t="n">
-        <v>2.14686417579651</v>
+        <v>2.14686393737793</v>
       </c>
       <c r="H774" t="n">
         <v>1537</v>
@@ -22873,7 +22873,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G776" t="n">
-        <v>2.14686417579651</v>
+        <v>2.14686393737793</v>
       </c>
       <c r="H776" t="n">
         <v>8020</v>
@@ -22902,7 +22902,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G777" t="n">
-        <v>2.00685095787048</v>
+        <v>2.00685143470764</v>
       </c>
       <c r="H777" t="n">
         <v>6782</v>
@@ -22931,7 +22931,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G778" t="n">
-        <v>2.01618552207947</v>
+        <v>2.01618528366089</v>
       </c>
       <c r="H778" t="n">
         <v>3662</v>
@@ -22960,7 +22960,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G779" t="n">
-        <v>2.01618552207947</v>
+        <v>2.01618528366089</v>
       </c>
       <c r="H779" t="n">
         <v>5386</v>
@@ -22989,7 +22989,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G780" t="n">
-        <v>1.99751710891724</v>
+        <v>1.99751698970795</v>
       </c>
       <c r="H780" t="n">
         <v>923</v>
@@ -23018,7 +23018,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G781" t="n">
-        <v>2.02551937103271</v>
+        <v>2.02551960945129</v>
       </c>
       <c r="H781" t="n">
         <v>2701</v>
@@ -23076,7 +23076,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G783" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417504310608</v>
       </c>
       <c r="H783" t="n">
         <v>16989</v>
@@ -23134,7 +23134,7 @@
         <v>2</v>
       </c>
       <c r="G785" t="n">
-        <v>1.86683833599091</v>
+        <v>1.86683821678162</v>
       </c>
       <c r="H785" t="n">
         <v>17005</v>
@@ -23163,7 +23163,7 @@
         <v>2</v>
       </c>
       <c r="G786" t="n">
-        <v>1.86683833599091</v>
+        <v>1.86683821678162</v>
       </c>
       <c r="H786" t="n">
         <v>10000</v>
@@ -23192,7 +23192,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G787" t="n">
-        <v>1.76416218280792</v>
+        <v>1.76416206359863</v>
       </c>
       <c r="H787" t="n">
         <v>18464</v>
@@ -23250,7 +23250,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G789" t="n">
-        <v>1.74549376964569</v>
+        <v>1.74549388885498</v>
       </c>
       <c r="H789" t="n">
         <v>11205</v>
@@ -23395,7 +23395,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G794" t="n">
-        <v>1.87617254257202</v>
+        <v>1.87617242336273</v>
       </c>
       <c r="H794" t="n">
         <v>9697</v>
@@ -23424,7 +23424,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G795" t="n">
-        <v>1.84816992282867</v>
+        <v>1.84817004203796</v>
       </c>
       <c r="H795" t="n">
         <v>1870</v>
@@ -23482,7 +23482,7 @@
         <v>2</v>
       </c>
       <c r="G797" t="n">
-        <v>1.86683833599091</v>
+        <v>1.86683821678162</v>
       </c>
       <c r="H797" t="n">
         <v>1805</v>
@@ -23511,7 +23511,7 @@
         <v>2</v>
       </c>
       <c r="G798" t="n">
-        <v>1.86683833599091</v>
+        <v>1.86683821678162</v>
       </c>
       <c r="H798" t="n">
         <v>1028</v>
@@ -23540,7 +23540,7 @@
         <v>2</v>
       </c>
       <c r="G799" t="n">
-        <v>1.86683833599091</v>
+        <v>1.86683821678162</v>
       </c>
       <c r="H799" t="n">
         <v>0</v>
@@ -23598,7 +23598,7 @@
         <v>2</v>
       </c>
       <c r="G801" t="n">
-        <v>1.86683833599091</v>
+        <v>1.86683821678162</v>
       </c>
       <c r="H801" t="n">
         <v>170</v>
@@ -23627,7 +23627,7 @@
         <v>2</v>
       </c>
       <c r="G802" t="n">
-        <v>1.86683833599091</v>
+        <v>1.86683821678162</v>
       </c>
       <c r="H802" t="n">
         <v>0</v>
@@ -23656,7 +23656,7 @@
         <v>2</v>
       </c>
       <c r="G803" t="n">
-        <v>1.86683833599091</v>
+        <v>1.86683821678162</v>
       </c>
       <c r="H803" t="n">
         <v>3200</v>
@@ -23743,7 +23743,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417504310608</v>
       </c>
       <c r="H806" t="n">
         <v>2225</v>
@@ -23859,7 +23859,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G810" t="n">
-        <v>1.83883559703827</v>
+        <v>1.83883571624756</v>
       </c>
       <c r="H810" t="n">
         <v>2520</v>
@@ -23888,7 +23888,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G811" t="n">
-        <v>1.83883559703827</v>
+        <v>1.83883571624756</v>
       </c>
       <c r="H811" t="n">
         <v>626</v>
@@ -23975,7 +23975,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G814" t="n">
-        <v>1.98818302154541</v>
+        <v>1.98818290233612</v>
       </c>
       <c r="H814" t="n">
         <v>5130</v>
@@ -24004,7 +24004,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G815" t="n">
-        <v>1.98818302154541</v>
+        <v>1.98818290233612</v>
       </c>
       <c r="H815" t="n">
         <v>13633</v>
@@ -24033,7 +24033,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G816" t="n">
-        <v>1.97884833812714</v>
+        <v>1.97884857654572</v>
       </c>
       <c r="H816" t="n">
         <v>18908</v>
@@ -24091,7 +24091,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G818" t="n">
-        <v>1.9228435754776</v>
+        <v>1.92284333705902</v>
       </c>
       <c r="H818" t="n">
         <v>3832</v>
@@ -24236,7 +24236,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G823" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417504310608</v>
       </c>
       <c r="H823" t="n">
         <v>2258</v>
@@ -24265,7 +24265,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G824" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417504310608</v>
       </c>
       <c r="H824" t="n">
         <v>0</v>
@@ -24294,7 +24294,7 @@
         <v>2</v>
       </c>
       <c r="G825" t="n">
-        <v>1.86683833599091</v>
+        <v>1.86683821678162</v>
       </c>
       <c r="H825" t="n">
         <v>1433</v>
@@ -24323,7 +24323,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G826" t="n">
-        <v>2.02551937103271</v>
+        <v>2.02551960945129</v>
       </c>
       <c r="H826" t="n">
         <v>12498</v>
@@ -24352,7 +24352,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G827" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417504310608</v>
       </c>
       <c r="H827" t="n">
         <v>15383</v>
@@ -24410,7 +24410,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G829" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417504310608</v>
       </c>
       <c r="H829" t="n">
         <v>4980</v>
@@ -24439,7 +24439,7 @@
         <v>2</v>
       </c>
       <c r="G830" t="n">
-        <v>1.86683833599091</v>
+        <v>1.86683821678162</v>
       </c>
       <c r="H830" t="n">
         <v>5204</v>
@@ -24468,7 +24468,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G831" t="n">
-        <v>1.84816992282867</v>
+        <v>1.84817004203796</v>
       </c>
       <c r="H831" t="n">
         <v>1282</v>
@@ -24555,7 +24555,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G834" t="n">
-        <v>1.8108332157135</v>
+        <v>1.81083333492279</v>
       </c>
       <c r="H834" t="n">
         <v>14350</v>
@@ -24816,7 +24816,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G843" t="n">
-        <v>1.8108332157135</v>
+        <v>1.81083333492279</v>
       </c>
       <c r="H843" t="n">
         <v>34989</v>
@@ -24845,7 +24845,7 @@
         <v>1.875</v>
       </c>
       <c r="G844" t="n">
-        <v>1.75016093254089</v>
+        <v>1.7501608133316</v>
       </c>
       <c r="H844" t="n">
         <v>17976</v>
@@ -24874,7 +24874,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G845" t="n">
-        <v>1.74549376964569</v>
+        <v>1.74549388885498</v>
       </c>
       <c r="H845" t="n">
         <v>1100</v>
@@ -24903,7 +24903,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G846" t="n">
-        <v>1.74549376964569</v>
+        <v>1.74549388885498</v>
       </c>
       <c r="H846" t="n">
         <v>7263</v>
@@ -24932,7 +24932,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G847" t="n">
-        <v>1.74549376964569</v>
+        <v>1.74549388885498</v>
       </c>
       <c r="H847" t="n">
         <v>5353</v>
@@ -24961,7 +24961,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G848" t="n">
-        <v>1.74549376964569</v>
+        <v>1.74549388885498</v>
       </c>
       <c r="H848" t="n">
         <v>1200</v>
@@ -24990,7 +24990,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G849" t="n">
-        <v>1.8108332157135</v>
+        <v>1.81083333492279</v>
       </c>
       <c r="H849" t="n">
         <v>2048</v>
@@ -25019,7 +25019,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G850" t="n">
-        <v>1.74549376964569</v>
+        <v>1.74549388885498</v>
       </c>
       <c r="H850" t="n">
         <v>1200</v>
@@ -25135,7 +25135,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G854" t="n">
-        <v>1.9228435754776</v>
+        <v>1.92284333705902</v>
       </c>
       <c r="H854" t="n">
         <v>3818</v>
@@ -25193,7 +25193,7 @@
         <v>2</v>
       </c>
       <c r="G856" t="n">
-        <v>1.86683833599091</v>
+        <v>1.86683821678162</v>
       </c>
       <c r="H856" t="n">
         <v>1249</v>
@@ -25222,7 +25222,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G857" t="n">
-        <v>1.9228435754776</v>
+        <v>1.92284333705902</v>
       </c>
       <c r="H857" t="n">
         <v>1847</v>
@@ -25251,7 +25251,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G858" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417504310608</v>
       </c>
       <c r="H858" t="n">
         <v>1659</v>
@@ -25280,7 +25280,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G859" t="n">
-        <v>1.87617254257202</v>
+        <v>1.87617242336273</v>
       </c>
       <c r="H859" t="n">
         <v>1005</v>
@@ -25309,7 +25309,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G860" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417504310608</v>
       </c>
       <c r="H860" t="n">
         <v>5149</v>
@@ -25425,7 +25425,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G864" t="n">
-        <v>1.84816992282867</v>
+        <v>1.84817004203796</v>
       </c>
       <c r="H864" t="n">
         <v>1500</v>
@@ -25454,7 +25454,7 @@
         <v>2</v>
       </c>
       <c r="G865" t="n">
-        <v>1.86683833599091</v>
+        <v>1.86683821678162</v>
       </c>
       <c r="H865" t="n">
         <v>3350</v>
@@ -25483,7 +25483,7 @@
         <v>2</v>
       </c>
       <c r="G866" t="n">
-        <v>1.86683833599091</v>
+        <v>1.86683821678162</v>
       </c>
       <c r="H866" t="n">
         <v>1000</v>
@@ -25512,7 +25512,7 @@
         <v>2</v>
       </c>
       <c r="G867" t="n">
-        <v>1.86683833599091</v>
+        <v>1.86683821678162</v>
       </c>
       <c r="H867" t="n">
         <v>0</v>
@@ -25599,7 +25599,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G870" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417504310608</v>
       </c>
       <c r="H870" t="n">
         <v>5440</v>
@@ -25657,7 +25657,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G872" t="n">
-        <v>1.9228435754776</v>
+        <v>1.92284333705902</v>
       </c>
       <c r="H872" t="n">
         <v>1350</v>
@@ -25773,7 +25773,7 @@
         <v>2</v>
       </c>
       <c r="G876" t="n">
-        <v>1.86683833599091</v>
+        <v>1.86683821678162</v>
       </c>
       <c r="H876" t="n">
         <v>2503</v>
@@ -25802,7 +25802,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G877" t="n">
-        <v>1.9228435754776</v>
+        <v>1.92284333705902</v>
       </c>
       <c r="H877" t="n">
         <v>1605</v>
@@ -25831,7 +25831,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G878" t="n">
-        <v>1.9228435754776</v>
+        <v>1.92284333705902</v>
       </c>
       <c r="H878" t="n">
         <v>4340</v>
@@ -26034,7 +26034,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417504310608</v>
       </c>
       <c r="H885" t="n">
         <v>6104</v>
@@ -26266,7 +26266,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G893" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417504310608</v>
       </c>
       <c r="H893" t="n">
         <v>2300</v>
@@ -26324,7 +26324,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G895" t="n">
-        <v>1.9228435754776</v>
+        <v>1.92284333705902</v>
       </c>
       <c r="H895" t="n">
         <v>1000</v>
@@ -26411,7 +26411,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G898" t="n">
-        <v>2.20286893844604</v>
+        <v>2.20286917686462</v>
       </c>
       <c r="H898" t="n">
         <v>36211</v>
@@ -26498,7 +26498,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G901" t="n">
-        <v>2.25887441635132</v>
+        <v>2.2588746547699</v>
       </c>
       <c r="H901" t="n">
         <v>13774</v>
@@ -26527,7 +26527,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G902" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H902" t="n">
         <v>9996</v>
@@ -26556,7 +26556,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G903" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H903" t="n">
         <v>12989</v>
@@ -26672,7 +26672,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G907" t="n">
-        <v>2.25887441635132</v>
+        <v>2.2588746547699</v>
       </c>
       <c r="H907" t="n">
         <v>2583</v>
@@ -26759,7 +26759,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G910" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H910" t="n">
         <v>2850</v>
@@ -26788,7 +26788,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G911" t="n">
-        <v>2.34288215637207</v>
+        <v>2.34288191795349</v>
       </c>
       <c r="H911" t="n">
         <v>17943</v>
@@ -26817,7 +26817,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G912" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H912" t="n">
         <v>18020</v>
@@ -26904,7 +26904,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G915" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H915" t="n">
         <v>2959</v>
@@ -27020,7 +27020,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G919" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H919" t="n">
         <v>3027</v>
@@ -27194,7 +27194,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G925" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H925" t="n">
         <v>10000</v>
@@ -27223,7 +27223,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G926" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H926" t="n">
         <v>3008</v>
@@ -27252,7 +27252,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G927" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155009269714</v>
       </c>
       <c r="H927" t="n">
         <v>13666</v>
@@ -27281,7 +27281,7 @@
         <v>2.5</v>
       </c>
       <c r="G928" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H928" t="n">
         <v>5817</v>
@@ -27310,7 +27310,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G929" t="n">
-        <v>2.38955307006836</v>
+        <v>2.38955283164978</v>
       </c>
       <c r="H929" t="n">
         <v>2434</v>
@@ -27368,7 +27368,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G931" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H931" t="n">
         <v>1499</v>
@@ -27455,7 +27455,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G934" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H934" t="n">
         <v>18035</v>
@@ -27513,7 +27513,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G936" t="n">
-        <v>2.20286893844604</v>
+        <v>2.20286917686462</v>
       </c>
       <c r="H936" t="n">
         <v>6398</v>
@@ -27542,7 +27542,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G937" t="n">
-        <v>2.24020600318909</v>
+        <v>2.24020576477051</v>
       </c>
       <c r="H937" t="n">
         <v>5629</v>
@@ -27571,7 +27571,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G938" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H938" t="n">
         <v>36604</v>
@@ -27629,7 +27629,7 @@
         <v>2.5</v>
       </c>
       <c r="G940" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H940" t="n">
         <v>25694</v>
@@ -27658,7 +27658,7 @@
         <v>2.5</v>
       </c>
       <c r="G941" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H941" t="n">
         <v>21800</v>
@@ -27745,7 +27745,7 @@
         <v>2.5</v>
       </c>
       <c r="G944" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H944" t="n">
         <v>1700</v>
@@ -27803,7 +27803,7 @@
         <v>2.5</v>
       </c>
       <c r="G946" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H946" t="n">
         <v>11500</v>
@@ -27832,7 +27832,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G947" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H947" t="n">
         <v>10650</v>
@@ -28006,7 +28006,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G953" t="n">
-        <v>2.34288215637207</v>
+        <v>2.34288191795349</v>
       </c>
       <c r="H953" t="n">
         <v>8059</v>
@@ -28064,7 +28064,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G955" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155009269714</v>
       </c>
       <c r="H955" t="n">
         <v>1000</v>
@@ -28122,7 +28122,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G957" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155009269714</v>
       </c>
       <c r="H957" t="n">
         <v>2000</v>
@@ -28151,7 +28151,7 @@
         <v>2.5</v>
       </c>
       <c r="G958" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H958" t="n">
         <v>5819</v>
@@ -28180,7 +28180,7 @@
         <v>2.5</v>
       </c>
       <c r="G959" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H959" t="n">
         <v>1888</v>
@@ -28296,7 +28296,7 @@
         <v>2.5</v>
       </c>
       <c r="G963" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H963" t="n">
         <v>5469</v>
@@ -28412,7 +28412,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G967" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H967" t="n">
         <v>3005</v>
@@ -28441,7 +28441,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G968" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H968" t="n">
         <v>0</v>
@@ -28499,7 +28499,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G970" t="n">
-        <v>2.38955307006836</v>
+        <v>2.38955283164978</v>
       </c>
       <c r="H970" t="n">
         <v>1000</v>
@@ -28528,7 +28528,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G971" t="n">
-        <v>2.38955307006836</v>
+        <v>2.38955283164978</v>
       </c>
       <c r="H971" t="n">
         <v>2000</v>
@@ -28557,7 +28557,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G972" t="n">
-        <v>2.38955307006836</v>
+        <v>2.38955283164978</v>
       </c>
       <c r="H972" t="n">
         <v>1000</v>
@@ -28673,7 +28673,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G976" t="n">
-        <v>2.38955307006836</v>
+        <v>2.38955283164978</v>
       </c>
       <c r="H976" t="n">
         <v>6488</v>
@@ -28789,7 +28789,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G980" t="n">
-        <v>2.38955307006836</v>
+        <v>2.38955283164978</v>
       </c>
       <c r="H980" t="n">
         <v>1000</v>
@@ -28818,7 +28818,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G981" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155009269714</v>
       </c>
       <c r="H981" t="n">
         <v>3499</v>
@@ -28847,7 +28847,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G982" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H982" t="n">
         <v>509</v>
@@ -28876,7 +28876,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G983" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H983" t="n">
         <v>0</v>
@@ -28905,7 +28905,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G984" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155009269714</v>
       </c>
       <c r="H984" t="n">
         <v>1677</v>
@@ -28934,7 +28934,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G985" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H985" t="n">
         <v>1000</v>
@@ -28963,7 +28963,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G986" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H986" t="n">
         <v>0</v>
@@ -28992,7 +28992,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G987" t="n">
-        <v>2.34288215637207</v>
+        <v>2.34288191795349</v>
       </c>
       <c r="H987" t="n">
         <v>1228</v>
@@ -29021,7 +29021,7 @@
         <v>2.5</v>
       </c>
       <c r="G988" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H988" t="n">
         <v>1300</v>
@@ -29108,7 +29108,7 @@
         <v>2.5</v>
       </c>
       <c r="G991" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H991" t="n">
         <v>560</v>
@@ -29195,7 +29195,7 @@
         <v>2.5</v>
       </c>
       <c r="G994" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H994" t="n">
         <v>17583</v>
@@ -29224,7 +29224,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G995" t="n">
-        <v>2.34288215637207</v>
+        <v>2.34288191795349</v>
       </c>
       <c r="H995" t="n">
         <v>3329</v>
@@ -29253,7 +29253,7 @@
         <v>2.5</v>
       </c>
       <c r="G996" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H996" t="n">
         <v>1000</v>
@@ -29282,7 +29282,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G997" t="n">
-        <v>2.34288215637207</v>
+        <v>2.34288191795349</v>
       </c>
       <c r="H997" t="n">
         <v>1000</v>
@@ -29311,7 +29311,7 @@
         <v>2.5</v>
       </c>
       <c r="G998" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H998" t="n">
         <v>7811</v>
@@ -29340,7 +29340,7 @@
         <v>2.5</v>
       </c>
       <c r="G999" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H999" t="n">
         <v>5034</v>
@@ -29369,7 +29369,7 @@
         <v>2.5</v>
       </c>
       <c r="G1000" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H1000" t="n">
         <v>5333</v>
@@ -29398,7 +29398,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1001" t="n">
-        <v>2.38955307006836</v>
+        <v>2.38955283164978</v>
       </c>
       <c r="H1001" t="n">
         <v>4093</v>
@@ -29427,7 +29427,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1002" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H1002" t="n">
         <v>3900</v>
@@ -29456,7 +29456,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1003" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H1003" t="n">
         <v>4000</v>
@@ -29485,7 +29485,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1004" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H1004" t="n">
         <v>1500</v>
@@ -29572,7 +29572,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1007" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H1007" t="n">
         <v>900</v>
@@ -29601,7 +29601,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1008" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H1008" t="n">
         <v>1100</v>
@@ -29630,7 +29630,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1009" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H1009" t="n">
         <v>1826</v>
@@ -29659,7 +29659,7 @@
         <v>2.5</v>
       </c>
       <c r="G1010" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H1010" t="n">
         <v>2800</v>
@@ -29688,7 +29688,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1011" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H1011" t="n">
         <v>3388</v>
@@ -29717,7 +29717,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1012" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H1012" t="n">
         <v>10877</v>
@@ -29746,7 +29746,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1013" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H1013" t="n">
         <v>35374</v>
@@ -29775,7 +29775,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1014" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H1014" t="n">
         <v>0</v>
@@ -29804,7 +29804,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1015" t="n">
-        <v>2.38955307006836</v>
+        <v>2.38955283164978</v>
       </c>
       <c r="H1015" t="n">
         <v>27110</v>
@@ -29833,7 +29833,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1016" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H1016" t="n">
         <v>34383</v>
@@ -29862,7 +29862,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1017" t="n">
-        <v>2.34288215637207</v>
+        <v>2.34288191795349</v>
       </c>
       <c r="H1017" t="n">
         <v>10140</v>
@@ -29891,7 +29891,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1018" t="n">
-        <v>2.34288215637207</v>
+        <v>2.34288191795349</v>
       </c>
       <c r="H1018" t="n">
         <v>1200</v>
@@ -29920,7 +29920,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1019" t="n">
-        <v>2.34288215637207</v>
+        <v>2.34288191795349</v>
       </c>
       <c r="H1019" t="n">
         <v>408</v>
@@ -29949,7 +29949,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1020" t="n">
-        <v>2.34288215637207</v>
+        <v>2.34288191795349</v>
       </c>
       <c r="H1020" t="n">
         <v>250</v>
@@ -29978,7 +29978,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1021" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H1021" t="n">
         <v>942</v>
@@ -30007,7 +30007,7 @@
         <v>2.5</v>
       </c>
       <c r="G1022" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H1022" t="n">
         <v>5140</v>
@@ -30036,7 +30036,7 @@
         <v>2.5</v>
       </c>
       <c r="G1023" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H1023" t="n">
         <v>12627</v>
@@ -30094,7 +30094,7 @@
         <v>2.5</v>
       </c>
       <c r="G1025" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H1025" t="n">
         <v>1230</v>
@@ -30123,7 +30123,7 @@
         <v>2.5</v>
       </c>
       <c r="G1026" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H1026" t="n">
         <v>1559</v>
@@ -30152,7 +30152,7 @@
         <v>2.5</v>
       </c>
       <c r="G1027" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H1027" t="n">
         <v>6612</v>
@@ -30181,7 +30181,7 @@
         <v>2.5</v>
       </c>
       <c r="G1028" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H1028" t="n">
         <v>0</v>
@@ -30210,7 +30210,7 @@
         <v>2.5</v>
       </c>
       <c r="G1029" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H1029" t="n">
         <v>15470</v>
@@ -30355,7 +30355,7 @@
         <v>2.5</v>
       </c>
       <c r="G1034" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H1034" t="n">
         <v>7531</v>
@@ -30471,7 +30471,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1038" t="n">
-        <v>2.34288215637207</v>
+        <v>2.34288191795349</v>
       </c>
       <c r="H1038" t="n">
         <v>35898</v>
@@ -30500,7 +30500,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1039" t="n">
-        <v>2.34288215637207</v>
+        <v>2.34288191795349</v>
       </c>
       <c r="H1039" t="n">
         <v>10000</v>
@@ -30529,7 +30529,7 @@
         <v>2.5</v>
       </c>
       <c r="G1040" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H1040" t="n">
         <v>2030</v>
@@ -30558,7 +30558,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1041" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H1041" t="n">
         <v>15334</v>
@@ -30587,7 +30587,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1042" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H1042" t="n">
         <v>548</v>
@@ -30674,7 +30674,7 @@
         <v>2.5</v>
       </c>
       <c r="G1045" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H1045" t="n">
         <v>2500</v>
@@ -30703,7 +30703,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1046" t="n">
-        <v>2.34288215637207</v>
+        <v>2.34288191795349</v>
       </c>
       <c r="H1046" t="n">
         <v>31954</v>
@@ -30848,7 +30848,7 @@
         <v>2.5</v>
       </c>
       <c r="G1051" t="n">
-        <v>2.33354783058167</v>
+        <v>2.33354806900024</v>
       </c>
       <c r="H1051" t="n">
         <v>8205</v>
@@ -30877,7 +30877,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1052" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155009269714</v>
       </c>
       <c r="H1052" t="n">
         <v>6417</v>
@@ -30906,7 +30906,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1053" t="n">
-        <v>2.34288215637207</v>
+        <v>2.34288191795349</v>
       </c>
       <c r="H1053" t="n">
         <v>6475</v>
@@ -30935,7 +30935,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1054" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H1054" t="n">
         <v>862</v>
@@ -30964,7 +30964,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1055" t="n">
-        <v>2.38955307006836</v>
+        <v>2.38955283164978</v>
       </c>
       <c r="H1055" t="n">
         <v>5201</v>
@@ -31022,7 +31022,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1057" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H1057" t="n">
         <v>2510</v>
@@ -31051,7 +31051,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1058" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H1058" t="n">
         <v>0</v>
@@ -31080,7 +31080,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1059" t="n">
-        <v>2.38021874427795</v>
+        <v>2.38021898269653</v>
       </c>
       <c r="H1059" t="n">
         <v>1100</v>
@@ -31109,7 +31109,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1060" t="n">
-        <v>2.38955307006836</v>
+        <v>2.38955283164978</v>
       </c>
       <c r="H1060" t="n">
         <v>290</v>
@@ -31283,7 +31283,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H1066" t="n">
         <v>5691</v>
@@ -31312,7 +31312,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H1067" t="n">
         <v>400</v>
@@ -31428,7 +31428,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1071" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H1071" t="n">
         <v>53618</v>
@@ -31718,7 +31718,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1081" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H1081" t="n">
         <v>317450</v>
@@ -31747,7 +31747,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1082" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H1082" t="n">
         <v>125568</v>
@@ -31776,7 +31776,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1083" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H1083" t="n">
         <v>170449</v>
@@ -31863,7 +31863,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1086" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H1086" t="n">
         <v>1691</v>
@@ -32124,7 +32124,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1095" t="n">
         <v>2654</v>
@@ -32240,7 +32240,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1099" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H1099" t="n">
         <v>1400</v>
@@ -32443,7 +32443,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1106" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1106" t="n">
         <v>200</v>
@@ -32501,7 +32501,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1108" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1108" t="n">
         <v>1000</v>
@@ -32530,7 +32530,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1109" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1109" t="n">
         <v>1587</v>
@@ -32559,7 +32559,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1110" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1110" t="n">
         <v>2194</v>
@@ -32617,7 +32617,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1112" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1112" t="n">
         <v>3440</v>
@@ -32646,7 +32646,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1113" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1113" t="n">
         <v>0</v>
@@ -32675,7 +32675,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1114" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1114" t="n">
         <v>3456</v>
@@ -32704,7 +32704,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1115" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1115" t="n">
         <v>0</v>
@@ -32878,7 +32878,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1121" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H1121" t="n">
         <v>10111</v>
@@ -32907,7 +32907,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1122" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H1122" t="n">
         <v>0</v>
@@ -32936,7 +32936,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1123" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H1123" t="n">
         <v>8171</v>
@@ -32965,7 +32965,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1124" t="n">
-        <v>2.61357355117798</v>
+        <v>2.6135733127594</v>
       </c>
       <c r="H1124" t="n">
         <v>0</v>
@@ -33429,7 +33429,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1140" t="n">
-        <v>2.82825994491577</v>
+        <v>2.82826018333435</v>
       </c>
       <c r="H1140" t="n">
         <v>9200</v>
@@ -33516,7 +33516,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1143" t="n">
-        <v>2.85626268386841</v>
+        <v>2.85626244544983</v>
       </c>
       <c r="H1143" t="n">
         <v>15530</v>
@@ -33835,7 +33835,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1154" t="n">
-        <v>2.85626268386841</v>
+        <v>2.85626244544983</v>
       </c>
       <c r="H1154" t="n">
         <v>3063</v>
@@ -34183,7 +34183,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.13628840446472</v>
+        <v>3.13628816604614</v>
       </c>
       <c r="H1166" t="n">
         <v>15387</v>
@@ -34212,7 +34212,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.20162796974182</v>
+        <v>3.20162773132324</v>
       </c>
       <c r="H1167" t="n">
         <v>24299</v>
@@ -34415,7 +34415,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.31363773345947</v>
+        <v>3.31363797187805</v>
       </c>
       <c r="H1174" t="n">
         <v>34347</v>
@@ -34444,7 +34444,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.44431662559509</v>
+        <v>3.44431686401367</v>
       </c>
       <c r="H1175" t="n">
         <v>13251</v>
@@ -34531,7 +34531,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1178" t="n">
-        <v>3.79901623725891</v>
+        <v>3.79901599884033</v>
       </c>
       <c r="H1178" t="n">
         <v>19529</v>
@@ -34676,7 +34676,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1183" t="n">
-        <v>4.76043748855591</v>
+        <v>4.76043796539307</v>
       </c>
       <c r="H1183" t="n">
         <v>303286</v>
@@ -34734,7 +34734,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1185" t="n">
-        <v>4.94712209701538</v>
+        <v>4.94712162017822</v>
       </c>
       <c r="H1185" t="n">
         <v>36680</v>
@@ -34763,7 +34763,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1186" t="n">
-        <v>4.85377979278564</v>
+        <v>4.85377931594849</v>
       </c>
       <c r="H1186" t="n">
         <v>39631</v>
@@ -34792,7 +34792,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G1187" t="n">
-        <v>4.63909292221069</v>
+        <v>4.63909339904785</v>
       </c>
       <c r="H1187" t="n">
         <v>70233</v>
@@ -34850,7 +34850,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1189" t="n">
-        <v>4.51774883270264</v>
+        <v>4.51774930953979</v>
       </c>
       <c r="H1189" t="n">
         <v>67215</v>
@@ -35082,7 +35082,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1197" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1197" t="n">
         <v>37624</v>
@@ -35111,7 +35111,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1198" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1198" t="n">
         <v>17896</v>
@@ -35169,7 +35169,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1200" t="n">
-        <v>4.51774883270264</v>
+        <v>4.51774930953979</v>
       </c>
       <c r="H1200" t="n">
         <v>23594</v>
@@ -35198,7 +35198,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1201" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1201" t="n">
         <v>16723</v>
@@ -35314,7 +35314,7 @@
         <v>5</v>
       </c>
       <c r="G1205" t="n">
-        <v>4.66709566116333</v>
+        <v>4.66709613800049</v>
       </c>
       <c r="H1205" t="n">
         <v>37268</v>
@@ -35401,7 +35401,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1208" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1208" t="n">
         <v>10200</v>
@@ -35575,7 +35575,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1214" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1214" t="n">
         <v>5950</v>
@@ -35604,7 +35604,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1215" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1215" t="n">
         <v>6941</v>
@@ -35633,7 +35633,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1216" t="n">
-        <v>4.48974609375</v>
+        <v>4.48974657058716</v>
       </c>
       <c r="H1216" t="n">
         <v>694</v>
@@ -35662,7 +35662,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1217" t="n">
-        <v>4.48974609375</v>
+        <v>4.48974657058716</v>
       </c>
       <c r="H1217" t="n">
         <v>5620</v>
@@ -35691,7 +35691,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1218" t="n">
-        <v>4.4524097442627</v>
+        <v>4.45240879058838</v>
       </c>
       <c r="H1218" t="n">
         <v>17443</v>
@@ -35720,7 +35720,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1219" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1219" t="n">
         <v>2891</v>
@@ -35749,7 +35749,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1220" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1220" t="n">
         <v>5384</v>
@@ -35778,7 +35778,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1221" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1221" t="n">
         <v>3060</v>
@@ -35836,7 +35836,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1223" t="n">
-        <v>4.3870701789856</v>
+        <v>4.38706970214844</v>
       </c>
       <c r="H1223" t="n">
         <v>2203</v>
@@ -35865,7 +35865,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1224" t="n">
-        <v>4.37773561477661</v>
+        <v>4.37773609161377</v>
       </c>
       <c r="H1224" t="n">
         <v>6752</v>
@@ -35894,7 +35894,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1225" t="n">
-        <v>4.36840105056763</v>
+        <v>4.36840152740479</v>
       </c>
       <c r="H1225" t="n">
         <v>12461</v>
@@ -35923,7 +35923,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1226" t="n">
-        <v>4.37773561477661</v>
+        <v>4.37773609161377</v>
       </c>
       <c r="H1226" t="n">
         <v>1614</v>
@@ -35952,7 +35952,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1227" t="n">
-        <v>4.3870701789856</v>
+        <v>4.38706970214844</v>
       </c>
       <c r="H1227" t="n">
         <v>11176</v>
@@ -35981,7 +35981,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1228" t="n">
-        <v>4.34973335266113</v>
+        <v>4.34973287582397</v>
       </c>
       <c r="H1228" t="n">
         <v>766</v>
@@ -36010,7 +36010,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1229" t="n">
-        <v>4.3870701789856</v>
+        <v>4.38706970214844</v>
       </c>
       <c r="H1229" t="n">
         <v>3628</v>
@@ -36068,7 +36068,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1231" t="n">
-        <v>4.3870701789856</v>
+        <v>4.38706970214844</v>
       </c>
       <c r="H1231" t="n">
         <v>12136</v>
@@ -36097,7 +36097,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1232" t="n">
-        <v>4.3870701789856</v>
+        <v>4.38706970214844</v>
       </c>
       <c r="H1232" t="n">
         <v>8849</v>
@@ -36126,7 +36126,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1233" t="n">
-        <v>4.3870701789856</v>
+        <v>4.38706970214844</v>
       </c>
       <c r="H1233" t="n">
         <v>8218</v>
@@ -36184,7 +36184,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1235" t="n">
-        <v>4.3870701789856</v>
+        <v>4.38706970214844</v>
       </c>
       <c r="H1235" t="n">
         <v>3700</v>
@@ -36213,7 +36213,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1236" t="n">
-        <v>4.3870701789856</v>
+        <v>4.38706970214844</v>
       </c>
       <c r="H1236" t="n">
         <v>9129</v>
@@ -36242,7 +36242,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1237" t="n">
-        <v>4.3870701789856</v>
+        <v>4.38706970214844</v>
       </c>
       <c r="H1237" t="n">
         <v>3361</v>
@@ -36271,7 +36271,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1238" t="n">
-        <v>4.3870701789856</v>
+        <v>4.38706970214844</v>
       </c>
       <c r="H1238" t="n">
         <v>3927</v>
@@ -36300,7 +36300,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1239" t="n">
-        <v>4.3870701789856</v>
+        <v>4.38706970214844</v>
       </c>
       <c r="H1239" t="n">
         <v>2020</v>
@@ -36329,7 +36329,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1240" t="n">
-        <v>4.4524097442627</v>
+        <v>4.45240879058838</v>
       </c>
       <c r="H1240" t="n">
         <v>7982</v>
@@ -36445,7 +36445,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1244" t="n">
-        <v>4.3870701789856</v>
+        <v>4.38706970214844</v>
       </c>
       <c r="H1244" t="n">
         <v>10595</v>
@@ -36474,7 +36474,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.40573787689209</v>
+        <v>4.40573835372925</v>
       </c>
       <c r="H1245" t="n">
         <v>1123</v>
@@ -36503,7 +36503,7 @@
         <v>4.75</v>
       </c>
       <c r="G1246" t="n">
-        <v>4.43374061584473</v>
+        <v>4.43374109268188</v>
       </c>
       <c r="H1246" t="n">
         <v>2543</v>
@@ -36619,7 +36619,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1250" t="n">
-        <v>4.40573787689209</v>
+        <v>4.40573835372925</v>
       </c>
       <c r="H1250" t="n">
         <v>2487</v>
@@ -36648,7 +36648,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1251" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1251" t="n">
         <v>39291</v>
@@ -36706,7 +36706,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1253" t="n">
-        <v>4.76043748855591</v>
+        <v>4.76043796539307</v>
       </c>
       <c r="H1253" t="n">
         <v>29354</v>
@@ -37315,7 +37315,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1274" t="n">
-        <v>4.99078130722046</v>
+        <v>4.9907808303833</v>
       </c>
       <c r="H1274" t="n">
         <v>24772</v>
@@ -37344,7 +37344,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1275" t="n">
-        <v>5.02917146682739</v>
+        <v>5.02917194366455</v>
       </c>
       <c r="H1275" t="n">
         <v>31385</v>
@@ -37431,7 +37431,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1278" t="n">
-        <v>5.48985958099365</v>
+        <v>5.48985910415649</v>
       </c>
       <c r="H1278" t="n">
         <v>70084</v>
@@ -37576,7 +37576,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1283" t="n">
-        <v>5.83537483215332</v>
+        <v>5.83537530899048</v>
       </c>
       <c r="H1283" t="n">
         <v>8786</v>
@@ -37634,7 +37634,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1285" t="n">
-        <v>6.39203929901123</v>
+        <v>6.39203882217407</v>
       </c>
       <c r="H1285" t="n">
         <v>35361</v>
@@ -37750,7 +37750,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1289" t="n">
-        <v>6.46882009506226</v>
+        <v>6.46882057189941</v>
       </c>
       <c r="H1289" t="n">
         <v>13104</v>
@@ -37866,7 +37866,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G1293" t="n">
-        <v>6.1808910369873</v>
+        <v>6.18089056015015</v>
       </c>
       <c r="H1293" t="n">
         <v>21462</v>
@@ -37895,7 +37895,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1294" t="n">
-        <v>6.12330532073975</v>
+        <v>6.12330484390259</v>
       </c>
       <c r="H1294" t="n">
         <v>21748</v>
@@ -37953,7 +37953,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1296" t="n">
-        <v>6.39203929901123</v>
+        <v>6.39203882217407</v>
       </c>
       <c r="H1296" t="n">
         <v>15861</v>
@@ -37982,7 +37982,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1297" t="n">
-        <v>6.48801612854004</v>
+        <v>6.48801565170288</v>
       </c>
       <c r="H1297" t="n">
         <v>2374</v>
@@ -38011,7 +38011,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1298" t="n">
-        <v>6.48801612854004</v>
+        <v>6.48801565170288</v>
       </c>
       <c r="H1298" t="n">
         <v>9827</v>
@@ -38156,7 +38156,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1303" t="n">
-        <v>6.48801612854004</v>
+        <v>6.48801565170288</v>
       </c>
       <c r="H1303" t="n">
         <v>11171</v>
@@ -38388,7 +38388,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1311" t="n">
-        <v>5.93135118484497</v>
+        <v>5.93135166168213</v>
       </c>
       <c r="H1311" t="n">
         <v>18885</v>
@@ -38446,7 +38446,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1313" t="n">
-        <v>5.93135118484497</v>
+        <v>5.93135166168213</v>
       </c>
       <c r="H1313" t="n">
         <v>34147</v>
@@ -38533,7 +38533,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1316" t="n">
-        <v>5.93135118484497</v>
+        <v>5.93135166168213</v>
       </c>
       <c r="H1316" t="n">
         <v>10376</v>
@@ -38939,7 +38939,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1330" t="n">
-        <v>5.68181276321411</v>
+        <v>5.68181228637695</v>
       </c>
       <c r="H1330" t="n">
         <v>4010</v>
@@ -39026,7 +39026,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1333" t="n">
-        <v>5.66261720657349</v>
+        <v>5.66261768341064</v>
       </c>
       <c r="H1333" t="n">
         <v>3167</v>
@@ -39055,7 +39055,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.56664085388184</v>
+        <v>5.56664133071899</v>
       </c>
       <c r="H1334" t="n">
         <v>13673</v>
@@ -39084,7 +39084,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1335" t="n">
-        <v>5.48985958099365</v>
+        <v>5.48985910415649</v>
       </c>
       <c r="H1335" t="n">
         <v>2565</v>
@@ -39142,7 +39142,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1337" t="n">
-        <v>5.56664085388184</v>
+        <v>5.56664133071899</v>
       </c>
       <c r="H1337" t="n">
         <v>2917</v>
@@ -39171,7 +39171,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1338" t="n">
-        <v>5.56664085388184</v>
+        <v>5.56664133071899</v>
       </c>
       <c r="H1338" t="n">
         <v>1312</v>
@@ -39258,7 +39258,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1341" t="n">
-        <v>5.66261720657349</v>
+        <v>5.66261768341064</v>
       </c>
       <c r="H1341" t="n">
         <v>1605</v>
@@ -39287,7 +39287,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1342" t="n">
-        <v>5.66261720657349</v>
+        <v>5.66261768341064</v>
       </c>
       <c r="H1342" t="n">
         <v>3220</v>
@@ -39403,7 +39403,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1346" t="n">
-        <v>5.56664085388184</v>
+        <v>5.56664133071899</v>
       </c>
       <c r="H1346" t="n">
         <v>2814</v>
@@ -39519,7 +39519,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1350" t="n">
-        <v>5.93135118484497</v>
+        <v>5.93135166168213</v>
       </c>
       <c r="H1350" t="n">
         <v>11182</v>
@@ -39548,7 +39548,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1351" t="n">
-        <v>5.93135118484497</v>
+        <v>5.93135166168213</v>
       </c>
       <c r="H1351" t="n">
         <v>17082</v>
@@ -39577,7 +39577,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1352" t="n">
-        <v>5.93135118484497</v>
+        <v>5.93135166168213</v>
       </c>
       <c r="H1352" t="n">
         <v>5027</v>
@@ -39606,7 +39606,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1353" t="n">
-        <v>6.12330532073975</v>
+        <v>6.12330484390259</v>
       </c>
       <c r="H1353" t="n">
         <v>15567</v>
@@ -39693,7 +39693,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1356" t="n">
-        <v>5.87376546859741</v>
+        <v>5.87376594543457</v>
       </c>
       <c r="H1356" t="n">
         <v>18468</v>
@@ -39896,7 +39896,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1363" t="n">
-        <v>5.96974182128906</v>
+        <v>5.96974229812622</v>
       </c>
       <c r="H1363" t="n">
         <v>14927</v>
@@ -40012,7 +40012,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1367" t="n">
-        <v>5.96974182128906</v>
+        <v>5.96974229812622</v>
       </c>
       <c r="H1367" t="n">
         <v>5383</v>
@@ -40041,7 +40041,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1368" t="n">
-        <v>5.83537483215332</v>
+        <v>5.83537530899048</v>
       </c>
       <c r="H1368" t="n">
         <v>3207</v>
@@ -40099,7 +40099,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1370" t="n">
-        <v>5.96974182128906</v>
+        <v>5.96974229812622</v>
       </c>
       <c r="H1370" t="n">
         <v>2420</v>
@@ -40128,7 +40128,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1371" t="n">
-        <v>5.87376546859741</v>
+        <v>5.87376594543457</v>
       </c>
       <c r="H1371" t="n">
         <v>5952</v>
@@ -40186,7 +40186,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1373" t="n">
-        <v>6.08491468429565</v>
+        <v>6.0849142074585</v>
       </c>
       <c r="H1373" t="n">
         <v>4048</v>
@@ -40244,7 +40244,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1375" t="n">
-        <v>5.87376546859741</v>
+        <v>5.87376594543457</v>
       </c>
       <c r="H1375" t="n">
         <v>6216</v>
@@ -40505,7 +40505,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1384" t="n">
-        <v>5.87376546859741</v>
+        <v>5.87376594543457</v>
       </c>
       <c r="H1384" t="n">
         <v>8532</v>
@@ -40534,7 +40534,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1385" t="n">
-        <v>5.96974182128906</v>
+        <v>5.96974229812622</v>
       </c>
       <c r="H1385" t="n">
         <v>4804</v>
@@ -40563,7 +40563,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1386" t="n">
-        <v>5.96974182128906</v>
+        <v>5.96974229812622</v>
       </c>
       <c r="H1386" t="n">
         <v>51315</v>
@@ -40592,7 +40592,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1387" t="n">
-        <v>5.96974182128906</v>
+        <v>5.96974229812622</v>
       </c>
       <c r="H1387" t="n">
         <v>3086</v>
@@ -40621,7 +40621,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1388" t="n">
-        <v>5.93135118484497</v>
+        <v>5.93135166168213</v>
       </c>
       <c r="H1388" t="n">
         <v>5083</v>
@@ -40679,7 +40679,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1390" t="n">
-        <v>5.93135118484497</v>
+        <v>5.93135166168213</v>
       </c>
       <c r="H1390" t="n">
         <v>3425</v>
@@ -40737,7 +40737,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1392" t="n">
-        <v>5.93135118484497</v>
+        <v>5.93135166168213</v>
       </c>
       <c r="H1392" t="n">
         <v>2371</v>
@@ -40766,7 +40766,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1393" t="n">
-        <v>5.87376546859741</v>
+        <v>5.87376594543457</v>
       </c>
       <c r="H1393" t="n">
         <v>4474</v>
@@ -41085,7 +41085,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1404" t="n">
-        <v>6.08491468429565</v>
+        <v>6.0849142074585</v>
       </c>
       <c r="H1404" t="n">
         <v>18941</v>
@@ -41143,7 +41143,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1406" t="n">
-        <v>6.12330532073975</v>
+        <v>6.12330484390259</v>
       </c>
       <c r="H1406" t="n">
         <v>40015</v>
@@ -41462,7 +41462,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1417" t="n">
-        <v>7.02548503875732</v>
+        <v>7.02548456192017</v>
       </c>
       <c r="H1417" t="n">
         <v>6334</v>
@@ -41839,7 +41839,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1430" t="n">
-        <v>7.02548503875732</v>
+        <v>7.02548456192017</v>
       </c>
       <c r="H1430" t="n">
         <v>15354</v>
@@ -41897,7 +41897,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1432" t="n">
-        <v>7.02548503875732</v>
+        <v>7.02548456192017</v>
       </c>
       <c r="H1432" t="n">
         <v>1260</v>
@@ -42129,7 +42129,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1440" t="n">
-        <v>7.06387519836426</v>
+        <v>7.06387567520142</v>
       </c>
       <c r="H1440" t="n">
         <v>1592</v>
@@ -42187,7 +42187,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G1442" t="n">
-        <v>7.12146139144897</v>
+        <v>7.12146091461182</v>
       </c>
       <c r="H1442" t="n">
         <v>9087</v>
@@ -42303,7 +42303,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1446" t="n">
-        <v>7.06387519836426</v>
+        <v>7.06387567520142</v>
       </c>
       <c r="H1446" t="n">
         <v>10440</v>
@@ -42361,7 +42361,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1448" t="n">
-        <v>7.06387519836426</v>
+        <v>7.06387567520142</v>
       </c>
       <c r="H1448" t="n">
         <v>6369</v>
@@ -42390,7 +42390,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1449" t="n">
-        <v>6.91031265258789</v>
+        <v>6.91031217575073</v>
       </c>
       <c r="H1449" t="n">
         <v>8416</v>
@@ -42419,7 +42419,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1450" t="n">
-        <v>7.02548503875732</v>
+        <v>7.02548456192017</v>
       </c>
       <c r="H1450" t="n">
         <v>5499</v>
@@ -42535,7 +42535,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1454" t="n">
-        <v>7.06387519836426</v>
+        <v>7.06387567520142</v>
       </c>
       <c r="H1454" t="n">
         <v>2894</v>
@@ -42680,7 +42680,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1459" t="n">
-        <v>6.91031265258789</v>
+        <v>6.91031217575073</v>
       </c>
       <c r="H1459" t="n">
         <v>3121</v>
@@ -42738,7 +42738,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1461" t="n">
-        <v>6.91031265258789</v>
+        <v>6.91031217575073</v>
       </c>
       <c r="H1461" t="n">
         <v>9076</v>
@@ -42767,7 +42767,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1462" t="n">
-        <v>7.06387519836426</v>
+        <v>7.06387567520142</v>
       </c>
       <c r="H1462" t="n">
         <v>300</v>
@@ -42883,7 +42883,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1466" t="n">
-        <v>7.02548503875732</v>
+        <v>7.02548456192017</v>
       </c>
       <c r="H1466" t="n">
         <v>501</v>
@@ -43173,7 +43173,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1476" t="n">
-        <v>6.91031265258789</v>
+        <v>6.91031217575073</v>
       </c>
       <c r="H1476" t="n">
         <v>7848</v>
@@ -43202,7 +43202,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1477" t="n">
-        <v>6.89111757278442</v>
+        <v>6.89111709594727</v>
       </c>
       <c r="H1477" t="n">
         <v>12560</v>
@@ -43260,7 +43260,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1479" t="n">
-        <v>6.91031265258789</v>
+        <v>6.91031217575073</v>
       </c>
       <c r="H1479" t="n">
         <v>16205</v>
@@ -43289,7 +43289,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1480" t="n">
-        <v>6.77594518661499</v>
+        <v>6.77594566345215</v>
       </c>
       <c r="H1480" t="n">
         <v>1973</v>
@@ -43318,7 +43318,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1481" t="n">
-        <v>6.98709440231323</v>
+        <v>6.98709392547607</v>
       </c>
       <c r="H1481" t="n">
         <v>4148</v>
@@ -43347,7 +43347,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1482" t="n">
-        <v>6.89111757278442</v>
+        <v>6.89111709594727</v>
       </c>
       <c r="H1482" t="n">
         <v>144</v>
@@ -43405,7 +43405,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G1484" t="n">
-        <v>6.79514026641846</v>
+        <v>6.79514074325562</v>
       </c>
       <c r="H1484" t="n">
         <v>10530</v>
@@ -43434,7 +43434,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1485" t="n">
-        <v>6.81433629989624</v>
+        <v>6.81433582305908</v>
       </c>
       <c r="H1485" t="n">
         <v>2742</v>
@@ -43463,7 +43463,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1486" t="n">
-        <v>6.91031265258789</v>
+        <v>6.91031217575073</v>
       </c>
       <c r="H1486" t="n">
         <v>1912</v>
@@ -43492,7 +43492,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1487" t="n">
-        <v>6.91031265258789</v>
+        <v>6.91031217575073</v>
       </c>
       <c r="H1487" t="n">
         <v>6267</v>
@@ -43521,7 +43521,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1488" t="n">
-        <v>6.98709440231323</v>
+        <v>6.98709392547607</v>
       </c>
       <c r="H1488" t="n">
         <v>8301</v>
@@ -43724,7 +43724,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1495" t="n">
-        <v>7.29421901702881</v>
+        <v>7.29421854019165</v>
       </c>
       <c r="H1495" t="n">
         <v>3213</v>
@@ -43753,7 +43753,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1496" t="n">
-        <v>7.42858552932739</v>
+        <v>7.42858600616455</v>
       </c>
       <c r="H1496" t="n">
         <v>9505</v>
@@ -43811,7 +43811,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1498" t="n">
-        <v>7.54375791549683</v>
+        <v>7.54375839233398</v>
       </c>
       <c r="H1498" t="n">
         <v>2199</v>
@@ -54518,6 +54518,35 @@
         <v>7702</v>
       </c>
       <c r="I1867" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1868">
+      <c r="A1868" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1868" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1868" t="n">
+        <v>13.8500003814697</v>
+      </c>
+      <c r="D1868" t="n">
+        <v>14</v>
+      </c>
+      <c r="E1868" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="F1868" t="n">
+        <v>13.8500003814697</v>
+      </c>
+      <c r="G1868" t="n">
+        <v>13.8500003814697</v>
+      </c>
+      <c r="H1868" t="n">
+        <v>6603</v>
+      </c>
+      <c r="I1868" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IEG.MI.xlsx
+++ b/data/IEG.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G3" t="n">
-        <v>3.49098777770996</v>
+        <v>3.49098753929138</v>
       </c>
       <c r="H3" t="n">
         <v>29088</v>
@@ -485,7 +485,7 @@
         <v>3.73099994659424</v>
       </c>
       <c r="G4" t="n">
-        <v>3.48258662223816</v>
+        <v>3.48258686065674</v>
       </c>
       <c r="H4" t="n">
         <v>132269</v>
@@ -514,7 +514,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G5" t="n">
-        <v>3.52832412719727</v>
+        <v>3.52832436561584</v>
       </c>
       <c r="H5" t="n">
         <v>20727</v>
@@ -543,7 +543,7 @@
         <v>3.69749999046326</v>
       </c>
       <c r="G6" t="n">
-        <v>3.45131731033325</v>
+        <v>3.45131707191467</v>
       </c>
       <c r="H6" t="n">
         <v>5051</v>
@@ -572,7 +572,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G7" t="n">
-        <v>3.45365071296692</v>
+        <v>3.4536509513855</v>
       </c>
       <c r="H7" t="n">
         <v>13909</v>
@@ -601,7 +601,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>3.40697979927063</v>
+        <v>3.40698003768921</v>
       </c>
       <c r="H8" t="n">
         <v>31297</v>
@@ -659,7 +659,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G10" t="n">
-        <v>3.45365071296692</v>
+        <v>3.4536509513855</v>
       </c>
       <c r="H10" t="n">
         <v>5150</v>
@@ -688,7 +688,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G11" t="n">
-        <v>3.45365071296692</v>
+        <v>3.4536509513855</v>
       </c>
       <c r="H11" t="n">
         <v>2000</v>
@@ -746,7 +746,7 @@
         <v>3.64050006866455</v>
       </c>
       <c r="G13" t="n">
-        <v>3.39811253547668</v>
+        <v>3.39811229705811</v>
       </c>
       <c r="H13" t="n">
         <v>1311</v>
@@ -775,7 +775,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G14" t="n">
-        <v>3.31363797187805</v>
+        <v>3.31363773345947</v>
       </c>
       <c r="H14" t="n">
         <v>25612</v>
@@ -833,7 +833,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G16" t="n">
-        <v>3.36030888557434</v>
+        <v>3.36030864715576</v>
       </c>
       <c r="H16" t="n">
         <v>51650</v>
@@ -891,7 +891,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G18" t="n">
-        <v>3.67767143249512</v>
+        <v>3.67767119407654</v>
       </c>
       <c r="H18" t="n">
         <v>96799</v>
@@ -920,7 +920,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G19" t="n">
-        <v>3.69634008407593</v>
+        <v>3.69633984565735</v>
       </c>
       <c r="H19" t="n">
         <v>96525</v>
@@ -949,7 +949,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G20" t="n">
-        <v>3.7803475856781</v>
+        <v>3.78034782409668</v>
       </c>
       <c r="H20" t="n">
         <v>59862</v>
@@ -978,7 +978,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G21" t="n">
-        <v>3.80835008621216</v>
+        <v>3.80834984779358</v>
       </c>
       <c r="H21" t="n">
         <v>29979</v>
@@ -1007,7 +1007,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G22" t="n">
-        <v>3.7803475856781</v>
+        <v>3.78034782409668</v>
       </c>
       <c r="H22" t="n">
         <v>4670</v>
@@ -1065,7 +1065,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G24" t="n">
-        <v>3.85502123832703</v>
+        <v>3.85502099990845</v>
       </c>
       <c r="H24" t="n">
         <v>69970</v>
@@ -1094,7 +1094,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G25" t="n">
-        <v>3.81768465042114</v>
+        <v>3.81768441200256</v>
       </c>
       <c r="H25" t="n">
         <v>4963</v>
@@ -1123,7 +1123,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G26" t="n">
-        <v>3.91102600097656</v>
+        <v>3.91102647781372</v>
       </c>
       <c r="H26" t="n">
         <v>12441</v>
@@ -1152,7 +1152,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G27" t="n">
-        <v>3.98569989204407</v>
+        <v>3.98569941520691</v>
       </c>
       <c r="H27" t="n">
         <v>15090</v>
@@ -1181,7 +1181,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G28" t="n">
-        <v>3.95769715309143</v>
+        <v>3.95769667625427</v>
       </c>
       <c r="H28" t="n">
         <v>6052</v>
@@ -1210,7 +1210,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G29" t="n">
-        <v>3.97636580467224</v>
+        <v>3.97636604309082</v>
       </c>
       <c r="H29" t="n">
         <v>2457</v>
@@ -1239,7 +1239,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G30" t="n">
-        <v>4.05103921890259</v>
+        <v>4.05103874206543</v>
       </c>
       <c r="H30" t="n">
         <v>10363</v>
@@ -1268,7 +1268,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G31" t="n">
-        <v>4.03237056732178</v>
+        <v>4.03237104415894</v>
       </c>
       <c r="H31" t="n">
         <v>17060</v>
@@ -1297,7 +1297,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G32" t="n">
-        <v>3.93902850151062</v>
+        <v>3.9390287399292</v>
       </c>
       <c r="H32" t="n">
         <v>6284</v>
@@ -1326,7 +1326,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>4.01370286941528</v>
+        <v>4.01370191574097</v>
       </c>
       <c r="H33" t="n">
         <v>4871</v>
@@ -1355,7 +1355,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G34" t="n">
-        <v>4.01370286941528</v>
+        <v>4.01370191574097</v>
       </c>
       <c r="H34" t="n">
         <v>114</v>
@@ -1384,7 +1384,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G35" t="n">
-        <v>3.99503397941589</v>
+        <v>3.99503421783447</v>
       </c>
       <c r="H35" t="n">
         <v>922</v>
@@ -1413,7 +1413,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G36" t="n">
-        <v>3.99503397941589</v>
+        <v>3.99503421783447</v>
       </c>
       <c r="H36" t="n">
         <v>300</v>
@@ -1442,7 +1442,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G37" t="n">
-        <v>3.99503397941589</v>
+        <v>3.99503421783447</v>
       </c>
       <c r="H37" t="n">
         <v>4226</v>
@@ -1471,7 +1471,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G38" t="n">
-        <v>3.95769715309143</v>
+        <v>3.95769667625427</v>
       </c>
       <c r="H38" t="n">
         <v>4960</v>
@@ -1558,7 +1558,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G41" t="n">
-        <v>3.95769715309143</v>
+        <v>3.95769667625427</v>
       </c>
       <c r="H41" t="n">
         <v>225</v>
@@ -1587,7 +1587,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G42" t="n">
-        <v>3.95769715309143</v>
+        <v>3.95769667625427</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G45" t="n">
-        <v>3.91102600097656</v>
+        <v>3.91102647781372</v>
       </c>
       <c r="H45" t="n">
         <v>115</v>
@@ -1732,7 +1732,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G47" t="n">
-        <v>3.85502123832703</v>
+        <v>3.85502099990845</v>
       </c>
       <c r="H47" t="n">
         <v>125</v>
@@ -1761,7 +1761,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G48" t="n">
-        <v>3.84568667411804</v>
+        <v>3.8456871509552</v>
       </c>
       <c r="H48" t="n">
         <v>600</v>
@@ -1790,7 +1790,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G49" t="n">
-        <v>3.91102600097656</v>
+        <v>3.91102647781372</v>
       </c>
       <c r="H49" t="n">
         <v>400</v>
@@ -1993,7 +1993,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G56" t="n">
-        <v>3.40697979927063</v>
+        <v>3.40698003768921</v>
       </c>
       <c r="H56" t="n">
         <v>6594</v>
@@ -2022,7 +2022,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G57" t="n">
-        <v>3.45365071296692</v>
+        <v>3.4536509513855</v>
       </c>
       <c r="H57" t="n">
         <v>73464</v>
@@ -2051,7 +2051,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G58" t="n">
-        <v>3.45365071296692</v>
+        <v>3.4536509513855</v>
       </c>
       <c r="H58" t="n">
         <v>35821</v>
@@ -2080,7 +2080,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G59" t="n">
-        <v>3.48165345191956</v>
+        <v>3.48165369033813</v>
       </c>
       <c r="H59" t="n">
         <v>10667</v>
@@ -2138,7 +2138,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G61" t="n">
-        <v>3.48165345191956</v>
+        <v>3.48165369033813</v>
       </c>
       <c r="H61" t="n">
         <v>851</v>
@@ -2196,7 +2196,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G63" t="n">
-        <v>3.60299754142761</v>
+        <v>3.60299777984619</v>
       </c>
       <c r="H63" t="n">
         <v>2685</v>
@@ -2225,7 +2225,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G64" t="n">
-        <v>3.56566119194031</v>
+        <v>3.56566095352173</v>
       </c>
       <c r="H64" t="n">
         <v>333</v>
@@ -2341,7 +2341,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G68" t="n">
-        <v>3.69634008407593</v>
+        <v>3.69633984565735</v>
       </c>
       <c r="H68" t="n">
         <v>6933</v>
@@ -2399,7 +2399,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G70" t="n">
-        <v>3.60299754142761</v>
+        <v>3.60299777984619</v>
       </c>
       <c r="H70" t="n">
         <v>1400</v>
@@ -2544,7 +2544,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>3.54699301719666</v>
+        <v>3.54699277877808</v>
       </c>
       <c r="H75" t="n">
         <v>550</v>
@@ -2573,7 +2573,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G76" t="n">
-        <v>3.54699301719666</v>
+        <v>3.54699277877808</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>3.54699301719666</v>
+        <v>3.54699277877808</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -2631,7 +2631,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G78" t="n">
-        <v>3.62166666984558</v>
+        <v>3.621666431427</v>
       </c>
       <c r="H78" t="n">
         <v>400</v>
@@ -2660,7 +2660,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G79" t="n">
-        <v>3.56566119194031</v>
+        <v>3.56566095352173</v>
       </c>
       <c r="H79" t="n">
         <v>505</v>
@@ -2776,7 +2776,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G83" t="n">
-        <v>3.6123321056366</v>
+        <v>3.61233186721802</v>
       </c>
       <c r="H83" t="n">
         <v>505</v>
@@ -2805,7 +2805,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G84" t="n">
-        <v>3.6123321056366</v>
+        <v>3.61233186721802</v>
       </c>
       <c r="H84" t="n">
         <v>10</v>
@@ -2834,7 +2834,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G85" t="n">
-        <v>3.56566119194031</v>
+        <v>3.56566095352173</v>
       </c>
       <c r="H85" t="n">
         <v>7252</v>
@@ -2863,7 +2863,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>3.57499504089355</v>
+        <v>3.57499527931213</v>
       </c>
       <c r="H86" t="n">
         <v>6205</v>
@@ -2921,7 +2921,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G88" t="n">
-        <v>3.62166666984558</v>
+        <v>3.621666431427</v>
       </c>
       <c r="H88" t="n">
         <v>1010</v>
@@ -3008,7 +3008,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G91" t="n">
-        <v>3.6123321056366</v>
+        <v>3.61233186721802</v>
       </c>
       <c r="H91" t="n">
         <v>5</v>
@@ -3037,7 +3037,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G92" t="n">
-        <v>3.54699301719666</v>
+        <v>3.54699277877808</v>
       </c>
       <c r="H92" t="n">
         <v>495</v>
@@ -3095,7 +3095,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G94" t="n">
-        <v>3.62166666984558</v>
+        <v>3.621666431427</v>
       </c>
       <c r="H94" t="n">
         <v>2005</v>
@@ -3153,7 +3153,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G96" t="n">
-        <v>3.67767143249512</v>
+        <v>3.67767119407654</v>
       </c>
       <c r="H96" t="n">
         <v>9735</v>
@@ -3269,7 +3269,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>3.69634008407593</v>
+        <v>3.69633984565735</v>
       </c>
       <c r="H100" t="n">
         <v>5164</v>
@@ -3298,7 +3298,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G101" t="n">
-        <v>3.69634008407593</v>
+        <v>3.69633984565735</v>
       </c>
       <c r="H101" t="n">
         <v>1750</v>
@@ -3414,7 +3414,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G105" t="n">
-        <v>3.64966869354248</v>
+        <v>3.64966893196106</v>
       </c>
       <c r="H105" t="n">
         <v>1680</v>
@@ -3443,7 +3443,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G106" t="n">
-        <v>3.79901599884033</v>
+        <v>3.79901623725891</v>
       </c>
       <c r="H106" t="n">
         <v>10585</v>
@@ -3501,7 +3501,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G108" t="n">
-        <v>3.81768465042114</v>
+        <v>3.81768441200256</v>
       </c>
       <c r="H108" t="n">
         <v>7940</v>
@@ -3559,7 +3559,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G110" t="n">
-        <v>3.81768465042114</v>
+        <v>3.81768441200256</v>
       </c>
       <c r="H110" t="n">
         <v>41689</v>
@@ -3588,7 +3588,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>3.80835008621216</v>
+        <v>3.80834984779358</v>
       </c>
       <c r="H111" t="n">
         <v>19699</v>
@@ -3617,7 +3617,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G112" t="n">
-        <v>3.80835008621216</v>
+        <v>3.80834984779358</v>
       </c>
       <c r="H112" t="n">
         <v>17603</v>
@@ -3733,7 +3733,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G116" t="n">
-        <v>3.76167941093445</v>
+        <v>3.76167917251587</v>
       </c>
       <c r="H116" t="n">
         <v>40346</v>
@@ -3762,7 +3762,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>3.75234484672546</v>
+        <v>3.75234508514404</v>
       </c>
       <c r="H117" t="n">
         <v>7599</v>
@@ -3849,7 +3849,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>3.7803475856781</v>
+        <v>3.78034782409668</v>
       </c>
       <c r="H120" t="n">
         <v>12037</v>
@@ -3878,7 +3878,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G121" t="n">
-        <v>3.79901599884033</v>
+        <v>3.79901623725891</v>
       </c>
       <c r="H121" t="n">
         <v>12025</v>
@@ -3936,7 +3936,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G123" t="n">
-        <v>3.85502123832703</v>
+        <v>3.85502099990845</v>
       </c>
       <c r="H123" t="n">
         <v>5193</v>
@@ -4023,7 +4023,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G126" t="n">
-        <v>3.80835008621216</v>
+        <v>3.80834984779358</v>
       </c>
       <c r="H126" t="n">
         <v>1562</v>
@@ -4110,7 +4110,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G129" t="n">
-        <v>3.7803475856781</v>
+        <v>3.78034782409668</v>
       </c>
       <c r="H129" t="n">
         <v>535</v>
@@ -4139,7 +4139,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G130" t="n">
-        <v>3.7430112361908</v>
+        <v>3.74301075935364</v>
       </c>
       <c r="H130" t="n">
         <v>76762</v>
@@ -4197,7 +4197,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G132" t="n">
-        <v>3.84568667411804</v>
+        <v>3.8456871509552</v>
       </c>
       <c r="H132" t="n">
         <v>2547</v>
@@ -4429,7 +4429,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G140" t="n">
-        <v>3.93902850151062</v>
+        <v>3.9390287399292</v>
       </c>
       <c r="H140" t="n">
         <v>3505</v>
@@ -4545,7 +4545,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G144" t="n">
-        <v>3.93902850151062</v>
+        <v>3.9390287399292</v>
       </c>
       <c r="H144" t="n">
         <v>3005</v>
@@ -4574,7 +4574,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G145" t="n">
-        <v>3.89235806465149</v>
+        <v>3.89235782623291</v>
       </c>
       <c r="H145" t="n">
         <v>14</v>
@@ -4661,7 +4661,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G148" t="n">
-        <v>3.95769715309143</v>
+        <v>3.95769667625427</v>
       </c>
       <c r="H148" t="n">
         <v>228432</v>
@@ -4690,7 +4690,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G149" t="n">
-        <v>4.0417046546936</v>
+        <v>4.04170513153076</v>
       </c>
       <c r="H149" t="n">
         <v>42576</v>
@@ -4777,7 +4777,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G152" t="n">
-        <v>4.27505970001221</v>
+        <v>4.27505922317505</v>
       </c>
       <c r="H152" t="n">
         <v>10712</v>
@@ -4835,7 +4835,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G154" t="n">
-        <v>4.35906744003296</v>
+        <v>4.35906791687012</v>
       </c>
       <c r="H154" t="n">
         <v>15474</v>
@@ -4864,7 +4864,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G155" t="n">
-        <v>4.40573835372925</v>
+        <v>4.40573787689209</v>
       </c>
       <c r="H155" t="n">
         <v>10834</v>
@@ -4922,7 +4922,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G157" t="n">
-        <v>4.40573835372925</v>
+        <v>4.40573787689209</v>
       </c>
       <c r="H157" t="n">
         <v>4479</v>
@@ -4980,7 +4980,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G159" t="n">
-        <v>4.1910514831543</v>
+        <v>4.19105195999146</v>
       </c>
       <c r="H159" t="n">
         <v>105</v>
@@ -5009,7 +5009,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G160" t="n">
-        <v>4.23772287368774</v>
+        <v>4.23772239685059</v>
       </c>
       <c r="H160" t="n">
         <v>1012</v>
@@ -5038,7 +5038,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G161" t="n">
-        <v>4.17238330841064</v>
+        <v>4.17238283157349</v>
       </c>
       <c r="H161" t="n">
         <v>1389</v>
@@ -5067,7 +5067,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G162" t="n">
-        <v>4.14438104629517</v>
+        <v>4.14438056945801</v>
       </c>
       <c r="H162" t="n">
         <v>5657</v>
@@ -5125,7 +5125,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G164" t="n">
-        <v>4.06970739364624</v>
+        <v>4.0697078704834</v>
       </c>
       <c r="H164" t="n">
         <v>8003</v>
@@ -5154,7 +5154,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G165" t="n">
-        <v>4.10704469680786</v>
+        <v>4.1070442199707</v>
       </c>
       <c r="H165" t="n">
         <v>765</v>
@@ -5241,7 +5241,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>4.05103921890259</v>
+        <v>4.05103874206543</v>
       </c>
       <c r="H168" t="n">
         <v>499</v>
@@ -5270,7 +5270,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G169" t="n">
-        <v>4.14438104629517</v>
+        <v>4.14438056945801</v>
       </c>
       <c r="H169" t="n">
         <v>4433</v>
@@ -5386,7 +5386,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G173" t="n">
-        <v>4.06037282943726</v>
+        <v>4.06037330627441</v>
       </c>
       <c r="H173" t="n">
         <v>6766</v>
@@ -5444,7 +5444,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G175" t="n">
-        <v>3.49098777770996</v>
+        <v>3.49098753929138</v>
       </c>
       <c r="H175" t="n">
         <v>5376</v>
@@ -5502,7 +5502,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G177" t="n">
-        <v>3.64966869354248</v>
+        <v>3.64966893196106</v>
       </c>
       <c r="H177" t="n">
         <v>15736</v>
@@ -5560,7 +5560,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G179" t="n">
-        <v>3.45365071296692</v>
+        <v>3.4536509513855</v>
       </c>
       <c r="H179" t="n">
         <v>1256</v>
@@ -5589,7 +5589,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G180" t="n">
-        <v>3.56566119194031</v>
+        <v>3.56566095352173</v>
       </c>
       <c r="H180" t="n">
         <v>6037</v>
@@ -5618,7 +5618,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G181" t="n">
-        <v>3.51899027824402</v>
+        <v>3.51899003982544</v>
       </c>
       <c r="H181" t="n">
         <v>1786</v>
@@ -5821,7 +5821,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G188" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H188" t="n">
         <v>6941</v>
@@ -5850,7 +5850,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G189" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G190" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H190" t="n">
         <v>500</v>
@@ -5908,7 +5908,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G191" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -5937,7 +5937,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G192" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -6111,7 +6111,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G198" t="n">
-        <v>2.45489263534546</v>
+        <v>2.45489239692688</v>
       </c>
       <c r="H198" t="n">
         <v>3279</v>
@@ -6140,7 +6140,7 @@
         <v>2.5</v>
       </c>
       <c r="G199" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H199" t="n">
         <v>300</v>
@@ -6169,7 +6169,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G200" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H200" t="n">
         <v>925</v>
@@ -6227,7 +6227,7 @@
         <v>2.5</v>
       </c>
       <c r="G202" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H202" t="n">
         <v>2588</v>
@@ -6256,7 +6256,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G203" t="n">
-        <v>2.34288191795349</v>
+        <v>2.34288215637207</v>
       </c>
       <c r="H203" t="n">
         <v>400</v>
@@ -6285,7 +6285,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G204" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H204" t="n">
         <v>3549</v>
@@ -6430,7 +6430,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G209" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H209" t="n">
         <v>865</v>
@@ -6517,7 +6517,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>2.76292085647583</v>
+        <v>2.76292061805725</v>
       </c>
       <c r="H212" t="n">
         <v>1030</v>
@@ -6575,7 +6575,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G214" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H214" t="n">
         <v>7441</v>
@@ -6691,7 +6691,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G218" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H218" t="n">
         <v>488</v>
@@ -6749,7 +6749,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G220" t="n">
-        <v>2.85626244544983</v>
+        <v>2.85626268386841</v>
       </c>
       <c r="H220" t="n">
         <v>4706</v>
@@ -6952,7 +6952,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G227" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H227" t="n">
         <v>6933</v>
@@ -7039,7 +7039,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G230" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H230" t="n">
         <v>676</v>
@@ -7126,7 +7126,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>2.76292085647583</v>
+        <v>2.76292061805725</v>
       </c>
       <c r="H233" t="n">
         <v>2100</v>
@@ -7155,7 +7155,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G234" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H234" t="n">
         <v>252</v>
@@ -7184,7 +7184,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G235" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H235" t="n">
         <v>350</v>
@@ -7271,7 +7271,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G238" t="n">
-        <v>2.85626244544983</v>
+        <v>2.85626268386841</v>
       </c>
       <c r="H238" t="n">
         <v>3815</v>
@@ -7300,7 +7300,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G239" t="n">
-        <v>2.85626244544983</v>
+        <v>2.85626268386841</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -7329,7 +7329,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G240" t="n">
-        <v>2.82826018333435</v>
+        <v>2.82825994491577</v>
       </c>
       <c r="H240" t="n">
         <v>950</v>
@@ -7474,7 +7474,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G245" t="n">
-        <v>2.82826018333435</v>
+        <v>2.82825994491577</v>
       </c>
       <c r="H245" t="n">
         <v>1750</v>
@@ -7503,7 +7503,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G246" t="n">
-        <v>3.01494383811951</v>
+        <v>3.01494359970093</v>
       </c>
       <c r="H246" t="n">
         <v>3050</v>
@@ -7648,7 +7648,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G251" t="n">
-        <v>2.78158926963806</v>
+        <v>2.78158903121948</v>
       </c>
       <c r="H251" t="n">
         <v>411</v>
@@ -7706,7 +7706,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G253" t="n">
-        <v>2.82826018333435</v>
+        <v>2.82825994491577</v>
       </c>
       <c r="H253" t="n">
         <v>19598</v>
@@ -7735,7 +7735,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G254" t="n">
-        <v>2.82826018333435</v>
+        <v>2.82825994491577</v>
       </c>
       <c r="H254" t="n">
         <v>2500</v>
@@ -7822,7 +7822,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G257" t="n">
-        <v>2.78158926963806</v>
+        <v>2.78158903121948</v>
       </c>
       <c r="H257" t="n">
         <v>9597</v>
@@ -8228,7 +8228,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G271" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H271" t="n">
         <v>110</v>
@@ -8286,7 +8286,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G273" t="n">
-        <v>2.52956604957581</v>
+        <v>2.52956581115723</v>
       </c>
       <c r="H273" t="n">
         <v>3807</v>
@@ -8315,7 +8315,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G274" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H274" t="n">
         <v>12686</v>
@@ -8344,7 +8344,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G275" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H275" t="n">
         <v>3412</v>
@@ -8373,7 +8373,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G276" t="n">
-        <v>2.49222898483276</v>
+        <v>2.49222922325134</v>
       </c>
       <c r="H276" t="n">
         <v>2643</v>
@@ -8402,7 +8402,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G277" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H277" t="n">
         <v>689</v>
@@ -8431,7 +8431,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G278" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H278" t="n">
         <v>0</v>
@@ -8460,7 +8460,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G279" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H279" t="n">
         <v>1890</v>
@@ -8489,7 +8489,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G280" t="n">
-        <v>2.52956604957581</v>
+        <v>2.52956581115723</v>
       </c>
       <c r="H280" t="n">
         <v>3085</v>
@@ -8518,7 +8518,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G281" t="n">
-        <v>2.47356081008911</v>
+        <v>2.47356104850769</v>
       </c>
       <c r="H281" t="n">
         <v>1069</v>
@@ -8547,7 +8547,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G282" t="n">
-        <v>2.48289513587952</v>
+        <v>2.48289489746094</v>
       </c>
       <c r="H282" t="n">
         <v>1691</v>
@@ -8750,7 +8750,7 @@
         <v>2.5</v>
       </c>
       <c r="G289" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H289" t="n">
         <v>5004</v>
@@ -8866,7 +8866,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G293" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H293" t="n">
         <v>3579</v>
@@ -8895,7 +8895,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G294" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H294" t="n">
         <v>2595</v>
@@ -8982,7 +8982,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G297" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H297" t="n">
         <v>238</v>
@@ -9011,7 +9011,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G298" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H298" t="n">
         <v>0</v>
@@ -9098,7 +9098,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G301" t="n">
-        <v>2.47356081008911</v>
+        <v>2.47356104850769</v>
       </c>
       <c r="H301" t="n">
         <v>9559</v>
@@ -9127,7 +9127,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G302" t="n">
-        <v>2.47356081008911</v>
+        <v>2.47356104850769</v>
       </c>
       <c r="H302" t="n">
         <v>2820</v>
@@ -9156,7 +9156,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G303" t="n">
-        <v>2.49222898483276</v>
+        <v>2.49222922325134</v>
       </c>
       <c r="H303" t="n">
         <v>782</v>
@@ -9185,7 +9185,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G304" t="n">
-        <v>2.49222898483276</v>
+        <v>2.49222922325134</v>
       </c>
       <c r="H304" t="n">
         <v>5</v>
@@ -9214,7 +9214,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G305" t="n">
-        <v>2.49222898483276</v>
+        <v>2.49222922325134</v>
       </c>
       <c r="H305" t="n">
         <v>17210</v>
@@ -9330,7 +9330,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G309" t="n">
-        <v>2.45489263534546</v>
+        <v>2.45489239692688</v>
       </c>
       <c r="H309" t="n">
         <v>16887</v>
@@ -9359,7 +9359,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G310" t="n">
-        <v>2.47356081008911</v>
+        <v>2.47356104850769</v>
       </c>
       <c r="H310" t="n">
         <v>1449</v>
@@ -9388,7 +9388,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G311" t="n">
-        <v>2.48289513587952</v>
+        <v>2.48289489746094</v>
       </c>
       <c r="H311" t="n">
         <v>204</v>
@@ -9417,7 +9417,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G312" t="n">
-        <v>2.48289513587952</v>
+        <v>2.48289489746094</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G313" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H313" t="n">
         <v>350</v>
@@ -9765,7 +9765,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G324" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H324" t="n">
         <v>1280</v>
@@ -9794,7 +9794,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G325" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G326" t="n">
-        <v>2.36155009269714</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H326" t="n">
         <v>4022</v>
@@ -9881,7 +9881,7 @@
         <v>2.5</v>
       </c>
       <c r="G328" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H328" t="n">
         <v>3490</v>
@@ -10026,7 +10026,7 @@
         <v>2.5</v>
       </c>
       <c r="G333" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H333" t="n">
         <v>7692</v>
@@ -10055,7 +10055,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G334" t="n">
-        <v>2.24020576477051</v>
+        <v>2.24020600318909</v>
       </c>
       <c r="H334" t="n">
         <v>4089</v>
@@ -10142,7 +10142,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G337" t="n">
-        <v>2.24020576477051</v>
+        <v>2.24020600318909</v>
       </c>
       <c r="H337" t="n">
         <v>15170</v>
@@ -10171,7 +10171,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>2.19353485107422</v>
+        <v>2.1935350894928</v>
       </c>
       <c r="H338" t="n">
         <v>17797</v>
@@ -10229,7 +10229,7 @@
         <v>2.25</v>
       </c>
       <c r="G340" t="n">
-        <v>2.10019302368164</v>
+        <v>2.10019326210022</v>
       </c>
       <c r="H340" t="n">
         <v>17080</v>
@@ -10258,7 +10258,7 @@
         <v>2.25</v>
       </c>
       <c r="G341" t="n">
-        <v>2.10019302368164</v>
+        <v>2.10019326210022</v>
       </c>
       <c r="H341" t="n">
         <v>6035</v>
@@ -10316,7 +10316,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G343" t="n">
-        <v>1.98818290233612</v>
+        <v>1.98818302154541</v>
       </c>
       <c r="H343" t="n">
         <v>9524</v>
@@ -10345,7 +10345,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G344" t="n">
-        <v>1.92284333705902</v>
+        <v>1.9228435754776</v>
       </c>
       <c r="H344" t="n">
         <v>5020</v>
@@ -10374,7 +10374,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G345" t="n">
-        <v>1.87617242336273</v>
+        <v>1.87617254257202</v>
       </c>
       <c r="H345" t="n">
         <v>10119</v>
@@ -10461,7 +10461,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G348" t="n">
-        <v>1.76416206359863</v>
+        <v>1.76416218280792</v>
       </c>
       <c r="H348" t="n">
         <v>3234</v>
@@ -10519,7 +10519,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G350" t="n">
-        <v>1.68015444278717</v>
+        <v>1.68015432357788</v>
       </c>
       <c r="H350" t="n">
         <v>3654</v>
@@ -10548,7 +10548,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G351" t="n">
-        <v>1.57747840881348</v>
+        <v>1.57747852802277</v>
       </c>
       <c r="H351" t="n">
         <v>44141</v>
@@ -10577,7 +10577,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G352" t="n">
-        <v>1.5308073759079</v>
+        <v>1.53080725669861</v>
       </c>
       <c r="H352" t="n">
         <v>32342</v>
@@ -10606,7 +10606,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G353" t="n">
-        <v>1.50747191905975</v>
+        <v>1.50747179985046</v>
       </c>
       <c r="H353" t="n">
         <v>17138</v>
@@ -10751,7 +10751,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G358" t="n">
-        <v>1.53547441959381</v>
+        <v>1.5354745388031</v>
       </c>
       <c r="H358" t="n">
         <v>224765</v>
@@ -10780,7 +10780,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G359" t="n">
-        <v>1.58681261539459</v>
+        <v>1.5868124961853</v>
       </c>
       <c r="H359" t="n">
         <v>162717</v>
@@ -10809,7 +10809,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G360" t="n">
-        <v>1.54947578907013</v>
+        <v>1.54947566986084</v>
       </c>
       <c r="H360" t="n">
         <v>52791</v>
@@ -10896,7 +10896,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G363" t="n">
-        <v>1.84817004203796</v>
+        <v>1.84816992282867</v>
       </c>
       <c r="H363" t="n">
         <v>74595</v>
@@ -10983,7 +10983,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G366" t="n">
-        <v>2.02551960945129</v>
+        <v>2.02551937103271</v>
       </c>
       <c r="H366" t="n">
         <v>41167</v>
@@ -11041,7 +11041,7 @@
         <v>2.25</v>
       </c>
       <c r="G368" t="n">
-        <v>2.10019302368164</v>
+        <v>2.10019326210022</v>
       </c>
       <c r="H368" t="n">
         <v>40808</v>
@@ -11273,7 +11273,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G376" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H376" t="n">
         <v>260524</v>
@@ -11302,7 +11302,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G377" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H377" t="n">
         <v>89733</v>
@@ -11418,7 +11418,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G381" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H381" t="n">
         <v>13489</v>
@@ -11505,7 +11505,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G384" t="n">
-        <v>2.36155009269714</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H384" t="n">
         <v>46528</v>
@@ -11534,7 +11534,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G385" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H385" t="n">
         <v>14657</v>
@@ -11563,7 +11563,7 @@
         <v>2.5</v>
       </c>
       <c r="G386" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H386" t="n">
         <v>14989</v>
@@ -11679,7 +11679,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G390" t="n">
-        <v>2.49222898483276</v>
+        <v>2.49222922325134</v>
       </c>
       <c r="H390" t="n">
         <v>23339</v>
@@ -11737,7 +11737,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G392" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H392" t="n">
         <v>78496</v>
@@ -11795,7 +11795,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G394" t="n">
-        <v>2.47356081008911</v>
+        <v>2.47356104850769</v>
       </c>
       <c r="H394" t="n">
         <v>21034</v>
@@ -11911,7 +11911,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H398" t="n">
         <v>4671</v>
@@ -11940,7 +11940,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G399" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H399" t="n">
         <v>20075</v>
@@ -11969,7 +11969,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G400" t="n">
-        <v>2.20286917686462</v>
+        <v>2.20286893844604</v>
       </c>
       <c r="H400" t="n">
         <v>35084</v>
@@ -11998,7 +11998,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G401" t="n">
-        <v>2.07219052314758</v>
+        <v>2.072190284729</v>
       </c>
       <c r="H401" t="n">
         <v>51398</v>
@@ -12056,7 +12056,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G403" t="n">
-        <v>2.17486643791199</v>
+        <v>2.17486667633057</v>
       </c>
       <c r="H403" t="n">
         <v>18632</v>
@@ -12085,7 +12085,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G404" t="n">
-        <v>2.17486643791199</v>
+        <v>2.17486667633057</v>
       </c>
       <c r="H404" t="n">
         <v>10603</v>
@@ -12114,7 +12114,7 @@
         <v>2.25</v>
       </c>
       <c r="G405" t="n">
-        <v>2.10019302368164</v>
+        <v>2.10019326210022</v>
       </c>
       <c r="H405" t="n">
         <v>50986</v>
@@ -12143,7 +12143,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G406" t="n">
-        <v>2.05352234840393</v>
+        <v>2.05352210998535</v>
       </c>
       <c r="H406" t="n">
         <v>51628</v>
@@ -12172,7 +12172,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G407" t="n">
-        <v>2.19353485107422</v>
+        <v>2.1935350894928</v>
       </c>
       <c r="H407" t="n">
         <v>30243</v>
@@ -12201,7 +12201,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G408" t="n">
-        <v>2.20286917686462</v>
+        <v>2.20286893844604</v>
       </c>
       <c r="H408" t="n">
         <v>20357</v>
@@ -12259,7 +12259,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G410" t="n">
-        <v>2.05352234840393</v>
+        <v>2.05352210998535</v>
       </c>
       <c r="H410" t="n">
         <v>55928</v>
@@ -12288,7 +12288,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G411" t="n">
-        <v>2.05352234840393</v>
+        <v>2.05352210998535</v>
       </c>
       <c r="H411" t="n">
         <v>27870</v>
@@ -12317,7 +12317,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G412" t="n">
-        <v>2.05352234840393</v>
+        <v>2.05352210998535</v>
       </c>
       <c r="H412" t="n">
         <v>10965</v>
@@ -12346,7 +12346,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G413" t="n">
-        <v>2.05352234840393</v>
+        <v>2.05352210998535</v>
       </c>
       <c r="H413" t="n">
         <v>6880</v>
@@ -12404,7 +12404,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G415" t="n">
-        <v>2.18420076370239</v>
+        <v>2.18420052528381</v>
       </c>
       <c r="H415" t="n">
         <v>21434</v>
@@ -12578,7 +12578,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G421" t="n">
-        <v>2.34288191795349</v>
+        <v>2.34288215637207</v>
       </c>
       <c r="H421" t="n">
         <v>34127</v>
@@ -12665,7 +12665,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G424" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H424" t="n">
         <v>4139</v>
@@ -12839,7 +12839,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G430" t="n">
-        <v>2.2588746547699</v>
+        <v>2.25887441635132</v>
       </c>
       <c r="H430" t="n">
         <v>8648</v>
@@ -12868,7 +12868,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G431" t="n">
-        <v>2.2588746547699</v>
+        <v>2.25887441635132</v>
       </c>
       <c r="H431" t="n">
         <v>10630</v>
@@ -12926,7 +12926,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G433" t="n">
-        <v>2.2588746547699</v>
+        <v>2.25887441635132</v>
       </c>
       <c r="H433" t="n">
         <v>39250</v>
@@ -12955,7 +12955,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G434" t="n">
-        <v>2.24020576477051</v>
+        <v>2.24020600318909</v>
       </c>
       <c r="H434" t="n">
         <v>3580</v>
@@ -12984,7 +12984,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G435" t="n">
-        <v>2.24954032897949</v>
+        <v>2.24954009056091</v>
       </c>
       <c r="H435" t="n">
         <v>1950</v>
@@ -13042,7 +13042,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G437" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H437" t="n">
         <v>10145</v>
@@ -13129,7 +13129,7 @@
         <v>2.5</v>
       </c>
       <c r="G440" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H440" t="n">
         <v>11714</v>
@@ -13187,7 +13187,7 @@
         <v>2.5</v>
       </c>
       <c r="G442" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H442" t="n">
         <v>13466</v>
@@ -13245,7 +13245,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G444" t="n">
-        <v>2.24954032897949</v>
+        <v>2.24954009056091</v>
       </c>
       <c r="H444" t="n">
         <v>11540</v>
@@ -13361,7 +13361,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G448" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H448" t="n">
         <v>75506</v>
@@ -13419,7 +13419,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G450" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H450" t="n">
         <v>45849</v>
@@ -13506,7 +13506,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G453" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H453" t="n">
         <v>35893</v>
@@ -13535,7 +13535,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G454" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H454" t="n">
         <v>25836</v>
@@ -13709,7 +13709,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G460" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H460" t="n">
         <v>44981</v>
@@ -13854,7 +13854,7 @@
         <v>3.25</v>
       </c>
       <c r="G465" t="n">
-        <v>3.03361225128174</v>
+        <v>3.03361201286316</v>
       </c>
       <c r="H465" t="n">
         <v>83242</v>
@@ -13912,7 +13912,7 @@
         <v>3.25</v>
       </c>
       <c r="G467" t="n">
-        <v>3.03361225128174</v>
+        <v>3.03361201286316</v>
       </c>
       <c r="H467" t="n">
         <v>62595</v>
@@ -13970,7 +13970,7 @@
         <v>3.25</v>
       </c>
       <c r="G469" t="n">
-        <v>3.03361225128174</v>
+        <v>3.03361201286316</v>
       </c>
       <c r="H469" t="n">
         <v>22979</v>
@@ -13999,7 +13999,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G470" t="n">
-        <v>3.35097455978394</v>
+        <v>3.35097479820251</v>
       </c>
       <c r="H470" t="n">
         <v>111507</v>
@@ -14028,7 +14028,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G471" t="n">
-        <v>3.27630090713501</v>
+        <v>3.27630114555359</v>
       </c>
       <c r="H471" t="n">
         <v>27454</v>
@@ -14086,7 +14086,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G473" t="n">
-        <v>3.3323061466217</v>
+        <v>3.33230638504028</v>
       </c>
       <c r="H473" t="n">
         <v>14421</v>
@@ -14173,7 +14173,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>3.17362523078918</v>
+        <v>3.17362499237061</v>
       </c>
       <c r="H476" t="n">
         <v>25140</v>
@@ -14260,7 +14260,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G479" t="n">
-        <v>3.16429114341736</v>
+        <v>3.16429090499878</v>
       </c>
       <c r="H479" t="n">
         <v>22442</v>
@@ -14289,7 +14289,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G480" t="n">
-        <v>3.20162773132324</v>
+        <v>3.20162796974182</v>
       </c>
       <c r="H480" t="n">
         <v>55118</v>
@@ -14376,7 +14376,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G483" t="n">
-        <v>3.12695407867432</v>
+        <v>3.12695384025574</v>
       </c>
       <c r="H483" t="n">
         <v>32378</v>
@@ -14434,7 +14434,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G485" t="n">
-        <v>3.15495681762695</v>
+        <v>3.15495705604553</v>
       </c>
       <c r="H485" t="n">
         <v>12813</v>
@@ -14463,7 +14463,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G486" t="n">
-        <v>3.17362523078918</v>
+        <v>3.17362499237061</v>
       </c>
       <c r="H486" t="n">
         <v>33087</v>
@@ -14521,7 +14521,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G488" t="n">
-        <v>3.16429114341736</v>
+        <v>3.16429090499878</v>
       </c>
       <c r="H488" t="n">
         <v>32411</v>
@@ -14666,7 +14666,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G493" t="n">
-        <v>3.04294633865356</v>
+        <v>3.04294657707214</v>
       </c>
       <c r="H493" t="n">
         <v>3499</v>
@@ -14811,7 +14811,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G498" t="n">
-        <v>3.07094883918762</v>
+        <v>3.0709490776062</v>
       </c>
       <c r="H498" t="n">
         <v>13299</v>
@@ -14898,7 +14898,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G501" t="n">
-        <v>3.0616147518158</v>
+        <v>3.06161451339722</v>
       </c>
       <c r="H501" t="n">
         <v>13910</v>
@@ -14927,7 +14927,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G502" t="n">
-        <v>3.09895157814026</v>
+        <v>3.09895133972168</v>
       </c>
       <c r="H502" t="n">
         <v>27956</v>
@@ -14956,7 +14956,7 @@
         <v>3.25</v>
       </c>
       <c r="G503" t="n">
-        <v>3.03361225128174</v>
+        <v>3.03361201286316</v>
       </c>
       <c r="H503" t="n">
         <v>5248</v>
@@ -15014,7 +15014,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G505" t="n">
-        <v>3.0056095123291</v>
+        <v>3.00560975074768</v>
       </c>
       <c r="H505" t="n">
         <v>10540</v>
@@ -15159,7 +15159,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G510" t="n">
-        <v>3.0056095123291</v>
+        <v>3.00560975074768</v>
       </c>
       <c r="H510" t="n">
         <v>10066</v>
@@ -15188,7 +15188,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G511" t="n">
-        <v>2.74425220489502</v>
+        <v>2.7442524433136</v>
       </c>
       <c r="H511" t="n">
         <v>47993</v>
@@ -15217,7 +15217,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G512" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H512" t="n">
         <v>87951</v>
@@ -15275,7 +15275,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G514" t="n">
-        <v>2.78158926963806</v>
+        <v>2.78158903121948</v>
       </c>
       <c r="H514" t="n">
         <v>5508</v>
@@ -15333,7 +15333,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G516" t="n">
-        <v>2.74425220489502</v>
+        <v>2.7442524433136</v>
       </c>
       <c r="H516" t="n">
         <v>7255</v>
@@ -15420,7 +15420,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G519" t="n">
-        <v>2.74425220489502</v>
+        <v>2.7442524433136</v>
       </c>
       <c r="H519" t="n">
         <v>22223</v>
@@ -15449,7 +15449,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G520" t="n">
-        <v>2.74425220489502</v>
+        <v>2.7442524433136</v>
       </c>
       <c r="H520" t="n">
         <v>5309</v>
@@ -15507,7 +15507,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G522" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H522" t="n">
         <v>18120</v>
@@ -15681,7 +15681,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G528" t="n">
-        <v>2.49222898483276</v>
+        <v>2.49222922325134</v>
       </c>
       <c r="H528" t="n">
         <v>36945</v>
@@ -15739,7 +15739,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G530" t="n">
-        <v>2.49222898483276</v>
+        <v>2.49222922325134</v>
       </c>
       <c r="H530" t="n">
         <v>44466</v>
@@ -15768,7 +15768,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G531" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H531" t="n">
         <v>29110</v>
@@ -15826,7 +15826,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G533" t="n">
-        <v>2.45489263534546</v>
+        <v>2.45489239692688</v>
       </c>
       <c r="H533" t="n">
         <v>27587</v>
@@ -15855,7 +15855,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G534" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H534" t="n">
         <v>58949</v>
@@ -15884,7 +15884,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G535" t="n">
-        <v>2.53889989852905</v>
+        <v>2.53890037536621</v>
       </c>
       <c r="H535" t="n">
         <v>31474</v>
@@ -15913,7 +15913,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G536" t="n">
-        <v>2.52956604957581</v>
+        <v>2.52956581115723</v>
       </c>
       <c r="H536" t="n">
         <v>18439</v>
@@ -16087,7 +16087,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G542" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H542" t="n">
         <v>34564</v>
@@ -16290,7 +16290,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G549" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H549" t="n">
         <v>9940</v>
@@ -16638,7 +16638,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G561" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H561" t="n">
         <v>55511</v>
@@ -16754,7 +16754,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G565" t="n">
-        <v>2.78158926963806</v>
+        <v>2.78158903121948</v>
       </c>
       <c r="H565" t="n">
         <v>5626</v>
@@ -16783,7 +16783,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G566" t="n">
-        <v>2.86559677124023</v>
+        <v>2.86559653282166</v>
       </c>
       <c r="H566" t="n">
         <v>4904</v>
@@ -16841,7 +16841,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G568" t="n">
-        <v>2.78158926963806</v>
+        <v>2.78158903121948</v>
       </c>
       <c r="H568" t="n">
         <v>6622</v>
@@ -16928,7 +16928,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G571" t="n">
-        <v>2.82826018333435</v>
+        <v>2.82825994491577</v>
       </c>
       <c r="H571" t="n">
         <v>2855</v>
@@ -17073,7 +17073,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G576" t="n">
-        <v>2.74425220489502</v>
+        <v>2.7442524433136</v>
       </c>
       <c r="H576" t="n">
         <v>4135</v>
@@ -17102,7 +17102,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G577" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H577" t="n">
         <v>5655</v>
@@ -17131,7 +17131,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G578" t="n">
-        <v>2.82826018333435</v>
+        <v>2.82825994491577</v>
       </c>
       <c r="H578" t="n">
         <v>6954</v>
@@ -17160,7 +17160,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G579" t="n">
-        <v>2.78158926963806</v>
+        <v>2.78158903121948</v>
       </c>
       <c r="H579" t="n">
         <v>2133</v>
@@ -17276,7 +17276,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G583" t="n">
-        <v>2.76292085647583</v>
+        <v>2.76292061805725</v>
       </c>
       <c r="H583" t="n">
         <v>1500</v>
@@ -17305,7 +17305,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G584" t="n">
-        <v>2.78158926963806</v>
+        <v>2.78158903121948</v>
       </c>
       <c r="H584" t="n">
         <v>6045</v>
@@ -17334,7 +17334,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G585" t="n">
-        <v>2.78158926963806</v>
+        <v>2.78158903121948</v>
       </c>
       <c r="H585" t="n">
         <v>1601</v>
@@ -17450,7 +17450,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G589" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H589" t="n">
         <v>5281</v>
@@ -17595,7 +17595,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G594" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H594" t="n">
         <v>3352</v>
@@ -17740,7 +17740,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G599" t="n">
-        <v>2.74425220489502</v>
+        <v>2.7442524433136</v>
       </c>
       <c r="H599" t="n">
         <v>13898</v>
@@ -17798,7 +17798,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G601" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H601" t="n">
         <v>11543</v>
@@ -17827,7 +17827,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G602" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H602" t="n">
         <v>22041</v>
@@ -17885,7 +17885,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G604" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H604" t="n">
         <v>5168</v>
@@ -17943,7 +17943,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H606" t="n">
         <v>1325</v>
@@ -17972,7 +17972,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G607" t="n">
-        <v>2.74425220489502</v>
+        <v>2.7442524433136</v>
       </c>
       <c r="H607" t="n">
         <v>1800</v>
@@ -18001,7 +18001,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G608" t="n">
-        <v>2.78158926963806</v>
+        <v>2.78158903121948</v>
       </c>
       <c r="H608" t="n">
         <v>7882</v>
@@ -18030,7 +18030,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G609" t="n">
-        <v>2.76292085647583</v>
+        <v>2.76292061805725</v>
       </c>
       <c r="H609" t="n">
         <v>13444</v>
@@ -18088,7 +18088,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G611" t="n">
-        <v>2.82826018333435</v>
+        <v>2.82825994491577</v>
       </c>
       <c r="H611" t="n">
         <v>2800</v>
@@ -18146,7 +18146,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G613" t="n">
-        <v>2.82826018333435</v>
+        <v>2.82825994491577</v>
       </c>
       <c r="H613" t="n">
         <v>7360</v>
@@ -18204,7 +18204,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G615" t="n">
-        <v>2.78158926963806</v>
+        <v>2.78158903121948</v>
       </c>
       <c r="H615" t="n">
         <v>21813</v>
@@ -18349,7 +18349,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G620" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H620" t="n">
         <v>12267</v>
@@ -18378,7 +18378,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G621" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H621" t="n">
         <v>13278</v>
@@ -18407,7 +18407,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G622" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H622" t="n">
         <v>9853</v>
@@ -18465,7 +18465,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G624" t="n">
-        <v>2.47356081008911</v>
+        <v>2.47356104850769</v>
       </c>
       <c r="H624" t="n">
         <v>17921</v>
@@ -18494,7 +18494,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G625" t="n">
-        <v>2.48289513587952</v>
+        <v>2.48289489746094</v>
       </c>
       <c r="H625" t="n">
         <v>9305</v>
@@ -18552,7 +18552,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G627" t="n">
-        <v>2.48289513587952</v>
+        <v>2.48289489746094</v>
       </c>
       <c r="H627" t="n">
         <v>3175</v>
@@ -18581,7 +18581,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G628" t="n">
-        <v>2.47356081008911</v>
+        <v>2.47356104850769</v>
       </c>
       <c r="H628" t="n">
         <v>7127</v>
@@ -18610,7 +18610,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G629" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H629" t="n">
         <v>9381</v>
@@ -18639,7 +18639,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G630" t="n">
-        <v>2.52956604957581</v>
+        <v>2.52956581115723</v>
       </c>
       <c r="H630" t="n">
         <v>5890</v>
@@ -18842,7 +18842,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G637" t="n">
-        <v>2.53889989852905</v>
+        <v>2.53890037536621</v>
       </c>
       <c r="H637" t="n">
         <v>7036</v>
@@ -18871,7 +18871,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G638" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H638" t="n">
         <v>10004</v>
@@ -18929,7 +18929,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G640" t="n">
-        <v>2.49222898483276</v>
+        <v>2.49222922325134</v>
       </c>
       <c r="H640" t="n">
         <v>15217</v>
@@ -18987,7 +18987,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G642" t="n">
-        <v>2.47356081008911</v>
+        <v>2.47356104850769</v>
       </c>
       <c r="H642" t="n">
         <v>25000</v>
@@ -19103,7 +19103,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G646" t="n">
-        <v>2.49222898483276</v>
+        <v>2.49222922325134</v>
       </c>
       <c r="H646" t="n">
         <v>4792</v>
@@ -19132,7 +19132,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G647" t="n">
-        <v>2.49222898483276</v>
+        <v>2.49222922325134</v>
       </c>
       <c r="H647" t="n">
         <v>6674</v>
@@ -19161,7 +19161,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G648" t="n">
-        <v>2.53889989852905</v>
+        <v>2.53890037536621</v>
       </c>
       <c r="H648" t="n">
         <v>20795</v>
@@ -19190,7 +19190,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G649" t="n">
-        <v>2.53889989852905</v>
+        <v>2.53890037536621</v>
       </c>
       <c r="H649" t="n">
         <v>26026</v>
@@ -19277,7 +19277,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G652" t="n">
-        <v>2.52956604957581</v>
+        <v>2.52956581115723</v>
       </c>
       <c r="H652" t="n">
         <v>6533</v>
@@ -19306,7 +19306,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G653" t="n">
-        <v>2.52956604957581</v>
+        <v>2.52956581115723</v>
       </c>
       <c r="H653" t="n">
         <v>6896</v>
@@ -19364,7 +19364,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G655" t="n">
-        <v>2.47356081008911</v>
+        <v>2.47356104850769</v>
       </c>
       <c r="H655" t="n">
         <v>1680</v>
@@ -19393,7 +19393,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>2.52956604957581</v>
+        <v>2.52956581115723</v>
       </c>
       <c r="H656" t="n">
         <v>5573</v>
@@ -19422,7 +19422,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G657" t="n">
-        <v>2.53889989852905</v>
+        <v>2.53890037536621</v>
       </c>
       <c r="H657" t="n">
         <v>8536</v>
@@ -19451,7 +19451,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G658" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H658" t="n">
         <v>24925</v>
@@ -19567,7 +19567,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G662" t="n">
-        <v>2.53889989852905</v>
+        <v>2.53890037536621</v>
       </c>
       <c r="H662" t="n">
         <v>18926</v>
@@ -19654,7 +19654,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G665" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H665" t="n">
         <v>1580</v>
@@ -19770,7 +19770,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G669" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H669" t="n">
         <v>6000</v>
@@ -19828,7 +19828,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G671" t="n">
-        <v>2.52956604957581</v>
+        <v>2.52956581115723</v>
       </c>
       <c r="H671" t="n">
         <v>1055</v>
@@ -19915,7 +19915,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G674" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H674" t="n">
         <v>1004</v>
@@ -19944,7 +19944,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G675" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H675" t="n">
         <v>0</v>
@@ -20060,7 +20060,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G679" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H679" t="n">
         <v>6131</v>
@@ -20118,7 +20118,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G681" t="n">
-        <v>2.53889989852905</v>
+        <v>2.53890037536621</v>
       </c>
       <c r="H681" t="n">
         <v>1200</v>
@@ -20263,7 +20263,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G686" t="n">
-        <v>2.48289513587952</v>
+        <v>2.48289489746094</v>
       </c>
       <c r="H686" t="n">
         <v>18872</v>
@@ -20350,7 +20350,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G689" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H689" t="n">
         <v>6459</v>
@@ -20466,7 +20466,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G693" t="n">
-        <v>2.14686393737793</v>
+        <v>2.14686417579651</v>
       </c>
       <c r="H693" t="n">
         <v>5992</v>
@@ -20640,7 +20640,7 @@
         <v>2.5</v>
       </c>
       <c r="G699" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H699" t="n">
         <v>12532</v>
@@ -20756,7 +20756,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G703" t="n">
-        <v>2.34288191795349</v>
+        <v>2.34288215637207</v>
       </c>
       <c r="H703" t="n">
         <v>8222</v>
@@ -20785,7 +20785,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G704" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H704" t="n">
         <v>2380</v>
@@ -20814,7 +20814,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G705" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H705" t="n">
         <v>7231</v>
@@ -20843,7 +20843,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G706" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H706" t="n">
         <v>16794</v>
@@ -20988,7 +20988,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G711" t="n">
-        <v>2.38955283164978</v>
+        <v>2.38955307006836</v>
       </c>
       <c r="H711" t="n">
         <v>5255</v>
@@ -21046,7 +21046,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G713" t="n">
-        <v>2.36155009269714</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H713" t="n">
         <v>5601</v>
@@ -21278,7 +21278,7 @@
         <v>2.5</v>
       </c>
       <c r="G721" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H721" t="n">
         <v>780</v>
@@ -21568,7 +21568,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G731" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H731" t="n">
         <v>5608</v>
@@ -21597,7 +21597,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G732" t="n">
-        <v>2.49222898483276</v>
+        <v>2.49222922325134</v>
       </c>
       <c r="H732" t="n">
         <v>14580</v>
@@ -21626,7 +21626,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G733" t="n">
-        <v>2.38955283164978</v>
+        <v>2.38955307006836</v>
       </c>
       <c r="H733" t="n">
         <v>3359</v>
@@ -21655,7 +21655,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G734" t="n">
-        <v>2.36155009269714</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H734" t="n">
         <v>59751</v>
@@ -21713,7 +21713,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G736" t="n">
-        <v>2.24020576477051</v>
+        <v>2.24020600318909</v>
       </c>
       <c r="H736" t="n">
         <v>8673</v>
@@ -21771,7 +21771,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G738" t="n">
-        <v>2.18420076370239</v>
+        <v>2.18420052528381</v>
       </c>
       <c r="H738" t="n">
         <v>10750</v>
@@ -21829,7 +21829,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G740" t="n">
-        <v>2.19353485107422</v>
+        <v>2.1935350894928</v>
       </c>
       <c r="H740" t="n">
         <v>5880</v>
@@ -21974,7 +21974,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G745" t="n">
-        <v>2.20286917686462</v>
+        <v>2.20286893844604</v>
       </c>
       <c r="H745" t="n">
         <v>3400</v>
@@ -22003,7 +22003,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G746" t="n">
-        <v>2.14686393737793</v>
+        <v>2.14686417579651</v>
       </c>
       <c r="H746" t="n">
         <v>11917</v>
@@ -22032,7 +22032,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G747" t="n">
-        <v>2.10952711105347</v>
+        <v>2.10952734947205</v>
       </c>
       <c r="H747" t="n">
         <v>5878</v>
@@ -22119,7 +22119,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G750" t="n">
-        <v>2.10952711105347</v>
+        <v>2.10952734947205</v>
       </c>
       <c r="H750" t="n">
         <v>3015</v>
@@ -22148,7 +22148,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G751" t="n">
-        <v>2.14686393737793</v>
+        <v>2.14686417579651</v>
       </c>
       <c r="H751" t="n">
         <v>4774</v>
@@ -22177,7 +22177,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G752" t="n">
-        <v>2.14686393737793</v>
+        <v>2.14686417579651</v>
       </c>
       <c r="H752" t="n">
         <v>0</v>
@@ -22206,7 +22206,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G753" t="n">
-        <v>2.14686393737793</v>
+        <v>2.14686417579651</v>
       </c>
       <c r="H753" t="n">
         <v>1518</v>
@@ -22235,7 +22235,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G754" t="n">
-        <v>2.10952711105347</v>
+        <v>2.10952734947205</v>
       </c>
       <c r="H754" t="n">
         <v>332</v>
@@ -22264,7 +22264,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G755" t="n">
-        <v>2.11886143684387</v>
+        <v>2.11886119842529</v>
       </c>
       <c r="H755" t="n">
         <v>2015</v>
@@ -22293,7 +22293,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G756" t="n">
-        <v>2.1375298500061</v>
+        <v>2.13752961158752</v>
       </c>
       <c r="H756" t="n">
         <v>759</v>
@@ -22322,7 +22322,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G757" t="n">
-        <v>2.15619826316833</v>
+        <v>2.15619802474976</v>
       </c>
       <c r="H757" t="n">
         <v>5</v>
@@ -22351,7 +22351,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G758" t="n">
-        <v>2.24020576477051</v>
+        <v>2.24020600318909</v>
       </c>
       <c r="H758" t="n">
         <v>3859</v>
@@ -22380,7 +22380,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G759" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H759" t="n">
         <v>6674</v>
@@ -22409,7 +22409,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G760" t="n">
-        <v>2.15619826316833</v>
+        <v>2.15619802474976</v>
       </c>
       <c r="H760" t="n">
         <v>9288</v>
@@ -22438,7 +22438,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G761" t="n">
-        <v>2.11886143684387</v>
+        <v>2.11886119842529</v>
       </c>
       <c r="H761" t="n">
         <v>3433</v>
@@ -22467,7 +22467,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G762" t="n">
-        <v>2.16553211212158</v>
+        <v>2.16553235054016</v>
       </c>
       <c r="H762" t="n">
         <v>710</v>
@@ -22496,7 +22496,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G763" t="n">
-        <v>2.15619826316833</v>
+        <v>2.15619802474976</v>
       </c>
       <c r="H763" t="n">
         <v>74</v>
@@ -22525,7 +22525,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G764" t="n">
-        <v>2.10952711105347</v>
+        <v>2.10952734947205</v>
       </c>
       <c r="H764" t="n">
         <v>2010</v>
@@ -22554,7 +22554,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G765" t="n">
-        <v>2.10952711105347</v>
+        <v>2.10952734947205</v>
       </c>
       <c r="H765" t="n">
         <v>0</v>
@@ -22583,7 +22583,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G766" t="n">
-        <v>2.11886143684387</v>
+        <v>2.11886119842529</v>
       </c>
       <c r="H766" t="n">
         <v>155</v>
@@ -22612,7 +22612,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G767" t="n">
-        <v>2.14686393737793</v>
+        <v>2.14686417579651</v>
       </c>
       <c r="H767" t="n">
         <v>1300</v>
@@ -22641,7 +22641,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G768" t="n">
-        <v>2.14686393737793</v>
+        <v>2.14686417579651</v>
       </c>
       <c r="H768" t="n">
         <v>0</v>
@@ -22757,7 +22757,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G772" t="n">
-        <v>2.16553211212158</v>
+        <v>2.16553235054016</v>
       </c>
       <c r="H772" t="n">
         <v>1743</v>
@@ -22786,7 +22786,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G773" t="n">
-        <v>2.19353485107422</v>
+        <v>2.1935350894928</v>
       </c>
       <c r="H773" t="n">
         <v>499</v>
@@ -22815,7 +22815,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G774" t="n">
-        <v>2.14686393737793</v>
+        <v>2.14686417579651</v>
       </c>
       <c r="H774" t="n">
         <v>1537</v>
@@ -22873,7 +22873,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G776" t="n">
-        <v>2.14686393737793</v>
+        <v>2.14686417579651</v>
       </c>
       <c r="H776" t="n">
         <v>8020</v>
@@ -22902,7 +22902,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G777" t="n">
-        <v>2.00685143470764</v>
+        <v>2.00685095787048</v>
       </c>
       <c r="H777" t="n">
         <v>6782</v>
@@ -22931,7 +22931,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G778" t="n">
-        <v>2.01618528366089</v>
+        <v>2.01618552207947</v>
       </c>
       <c r="H778" t="n">
         <v>3662</v>
@@ -22960,7 +22960,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G779" t="n">
-        <v>2.01618528366089</v>
+        <v>2.01618552207947</v>
       </c>
       <c r="H779" t="n">
         <v>5386</v>
@@ -22989,7 +22989,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G780" t="n">
-        <v>1.99751698970795</v>
+        <v>1.99751710891724</v>
       </c>
       <c r="H780" t="n">
         <v>923</v>
@@ -23018,7 +23018,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G781" t="n">
-        <v>2.02551960945129</v>
+        <v>2.02551937103271</v>
       </c>
       <c r="H781" t="n">
         <v>2701</v>
@@ -23076,7 +23076,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G783" t="n">
-        <v>1.90417504310608</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H783" t="n">
         <v>16989</v>
@@ -23134,7 +23134,7 @@
         <v>2</v>
       </c>
       <c r="G785" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H785" t="n">
         <v>17005</v>
@@ -23163,7 +23163,7 @@
         <v>2</v>
       </c>
       <c r="G786" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H786" t="n">
         <v>10000</v>
@@ -23192,7 +23192,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G787" t="n">
-        <v>1.76416206359863</v>
+        <v>1.76416218280792</v>
       </c>
       <c r="H787" t="n">
         <v>18464</v>
@@ -23250,7 +23250,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G789" t="n">
-        <v>1.74549388885498</v>
+        <v>1.74549376964569</v>
       </c>
       <c r="H789" t="n">
         <v>11205</v>
@@ -23395,7 +23395,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G794" t="n">
-        <v>1.87617242336273</v>
+        <v>1.87617254257202</v>
       </c>
       <c r="H794" t="n">
         <v>9697</v>
@@ -23424,7 +23424,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G795" t="n">
-        <v>1.84817004203796</v>
+        <v>1.84816992282867</v>
       </c>
       <c r="H795" t="n">
         <v>1870</v>
@@ -23482,7 +23482,7 @@
         <v>2</v>
       </c>
       <c r="G797" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H797" t="n">
         <v>1805</v>
@@ -23511,7 +23511,7 @@
         <v>2</v>
       </c>
       <c r="G798" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H798" t="n">
         <v>1028</v>
@@ -23540,7 +23540,7 @@
         <v>2</v>
       </c>
       <c r="G799" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H799" t="n">
         <v>0</v>
@@ -23598,7 +23598,7 @@
         <v>2</v>
       </c>
       <c r="G801" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H801" t="n">
         <v>170</v>
@@ -23627,7 +23627,7 @@
         <v>2</v>
       </c>
       <c r="G802" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H802" t="n">
         <v>0</v>
@@ -23656,7 +23656,7 @@
         <v>2</v>
       </c>
       <c r="G803" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H803" t="n">
         <v>3200</v>
@@ -23743,7 +23743,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>1.90417504310608</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H806" t="n">
         <v>2225</v>
@@ -23859,7 +23859,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G810" t="n">
-        <v>1.83883571624756</v>
+        <v>1.83883559703827</v>
       </c>
       <c r="H810" t="n">
         <v>2520</v>
@@ -23888,7 +23888,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G811" t="n">
-        <v>1.83883571624756</v>
+        <v>1.83883559703827</v>
       </c>
       <c r="H811" t="n">
         <v>626</v>
@@ -23975,7 +23975,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G814" t="n">
-        <v>1.98818290233612</v>
+        <v>1.98818302154541</v>
       </c>
       <c r="H814" t="n">
         <v>5130</v>
@@ -24004,7 +24004,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G815" t="n">
-        <v>1.98818290233612</v>
+        <v>1.98818302154541</v>
       </c>
       <c r="H815" t="n">
         <v>13633</v>
@@ -24033,7 +24033,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G816" t="n">
-        <v>1.97884857654572</v>
+        <v>1.97884833812714</v>
       </c>
       <c r="H816" t="n">
         <v>18908</v>
@@ -24091,7 +24091,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G818" t="n">
-        <v>1.92284333705902</v>
+        <v>1.9228435754776</v>
       </c>
       <c r="H818" t="n">
         <v>3832</v>
@@ -24236,7 +24236,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G823" t="n">
-        <v>1.90417504310608</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H823" t="n">
         <v>2258</v>
@@ -24265,7 +24265,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G824" t="n">
-        <v>1.90417504310608</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H824" t="n">
         <v>0</v>
@@ -24294,7 +24294,7 @@
         <v>2</v>
       </c>
       <c r="G825" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H825" t="n">
         <v>1433</v>
@@ -24323,7 +24323,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G826" t="n">
-        <v>2.02551960945129</v>
+        <v>2.02551937103271</v>
       </c>
       <c r="H826" t="n">
         <v>12498</v>
@@ -24352,7 +24352,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G827" t="n">
-        <v>1.90417504310608</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H827" t="n">
         <v>15383</v>
@@ -24410,7 +24410,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G829" t="n">
-        <v>1.90417504310608</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H829" t="n">
         <v>4980</v>
@@ -24439,7 +24439,7 @@
         <v>2</v>
       </c>
       <c r="G830" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H830" t="n">
         <v>5204</v>
@@ -24468,7 +24468,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G831" t="n">
-        <v>1.84817004203796</v>
+        <v>1.84816992282867</v>
       </c>
       <c r="H831" t="n">
         <v>1282</v>
@@ -24555,7 +24555,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G834" t="n">
-        <v>1.81083333492279</v>
+        <v>1.8108332157135</v>
       </c>
       <c r="H834" t="n">
         <v>14350</v>
@@ -24816,7 +24816,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G843" t="n">
-        <v>1.81083333492279</v>
+        <v>1.8108332157135</v>
       </c>
       <c r="H843" t="n">
         <v>34989</v>
@@ -24845,7 +24845,7 @@
         <v>1.875</v>
       </c>
       <c r="G844" t="n">
-        <v>1.7501608133316</v>
+        <v>1.75016093254089</v>
       </c>
       <c r="H844" t="n">
         <v>17976</v>
@@ -24874,7 +24874,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G845" t="n">
-        <v>1.74549388885498</v>
+        <v>1.74549376964569</v>
       </c>
       <c r="H845" t="n">
         <v>1100</v>
@@ -24903,7 +24903,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G846" t="n">
-        <v>1.74549388885498</v>
+        <v>1.74549376964569</v>
       </c>
       <c r="H846" t="n">
         <v>7263</v>
@@ -24932,7 +24932,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G847" t="n">
-        <v>1.74549388885498</v>
+        <v>1.74549376964569</v>
       </c>
       <c r="H847" t="n">
         <v>5353</v>
@@ -24961,7 +24961,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G848" t="n">
-        <v>1.74549388885498</v>
+        <v>1.74549376964569</v>
       </c>
       <c r="H848" t="n">
         <v>1200</v>
@@ -24990,7 +24990,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G849" t="n">
-        <v>1.81083333492279</v>
+        <v>1.8108332157135</v>
       </c>
       <c r="H849" t="n">
         <v>2048</v>
@@ -25019,7 +25019,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G850" t="n">
-        <v>1.74549388885498</v>
+        <v>1.74549376964569</v>
       </c>
       <c r="H850" t="n">
         <v>1200</v>
@@ -25135,7 +25135,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G854" t="n">
-        <v>1.92284333705902</v>
+        <v>1.9228435754776</v>
       </c>
       <c r="H854" t="n">
         <v>3818</v>
@@ -25193,7 +25193,7 @@
         <v>2</v>
       </c>
       <c r="G856" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H856" t="n">
         <v>1249</v>
@@ -25222,7 +25222,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G857" t="n">
-        <v>1.92284333705902</v>
+        <v>1.9228435754776</v>
       </c>
       <c r="H857" t="n">
         <v>1847</v>
@@ -25251,7 +25251,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G858" t="n">
-        <v>1.90417504310608</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H858" t="n">
         <v>1659</v>
@@ -25280,7 +25280,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G859" t="n">
-        <v>1.87617242336273</v>
+        <v>1.87617254257202</v>
       </c>
       <c r="H859" t="n">
         <v>1005</v>
@@ -25309,7 +25309,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G860" t="n">
-        <v>1.90417504310608</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H860" t="n">
         <v>5149</v>
@@ -25425,7 +25425,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G864" t="n">
-        <v>1.84817004203796</v>
+        <v>1.84816992282867</v>
       </c>
       <c r="H864" t="n">
         <v>1500</v>
@@ -25454,7 +25454,7 @@
         <v>2</v>
       </c>
       <c r="G865" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H865" t="n">
         <v>3350</v>
@@ -25483,7 +25483,7 @@
         <v>2</v>
       </c>
       <c r="G866" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H866" t="n">
         <v>1000</v>
@@ -25512,7 +25512,7 @@
         <v>2</v>
       </c>
       <c r="G867" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H867" t="n">
         <v>0</v>
@@ -25599,7 +25599,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G870" t="n">
-        <v>1.90417504310608</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H870" t="n">
         <v>5440</v>
@@ -25657,7 +25657,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G872" t="n">
-        <v>1.92284333705902</v>
+        <v>1.9228435754776</v>
       </c>
       <c r="H872" t="n">
         <v>1350</v>
@@ -25773,7 +25773,7 @@
         <v>2</v>
       </c>
       <c r="G876" t="n">
-        <v>1.86683821678162</v>
+        <v>1.86683833599091</v>
       </c>
       <c r="H876" t="n">
         <v>2503</v>
@@ -25802,7 +25802,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G877" t="n">
-        <v>1.92284333705902</v>
+        <v>1.9228435754776</v>
       </c>
       <c r="H877" t="n">
         <v>1605</v>
@@ -25831,7 +25831,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G878" t="n">
-        <v>1.92284333705902</v>
+        <v>1.9228435754776</v>
       </c>
       <c r="H878" t="n">
         <v>4340</v>
@@ -26034,7 +26034,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>1.90417504310608</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H885" t="n">
         <v>6104</v>
@@ -26266,7 +26266,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G893" t="n">
-        <v>1.90417504310608</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H893" t="n">
         <v>2300</v>
@@ -26324,7 +26324,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G895" t="n">
-        <v>1.92284333705902</v>
+        <v>1.9228435754776</v>
       </c>
       <c r="H895" t="n">
         <v>1000</v>
@@ -26411,7 +26411,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G898" t="n">
-        <v>2.20286917686462</v>
+        <v>2.20286893844604</v>
       </c>
       <c r="H898" t="n">
         <v>36211</v>
@@ -26498,7 +26498,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G901" t="n">
-        <v>2.2588746547699</v>
+        <v>2.25887441635132</v>
       </c>
       <c r="H901" t="n">
         <v>13774</v>
@@ -26527,7 +26527,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G902" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H902" t="n">
         <v>9996</v>
@@ -26556,7 +26556,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G903" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H903" t="n">
         <v>12989</v>
@@ -26672,7 +26672,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G907" t="n">
-        <v>2.2588746547699</v>
+        <v>2.25887441635132</v>
       </c>
       <c r="H907" t="n">
         <v>2583</v>
@@ -26759,7 +26759,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G910" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H910" t="n">
         <v>2850</v>
@@ -26788,7 +26788,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G911" t="n">
-        <v>2.34288191795349</v>
+        <v>2.34288215637207</v>
       </c>
       <c r="H911" t="n">
         <v>17943</v>
@@ -26817,7 +26817,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G912" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H912" t="n">
         <v>18020</v>
@@ -26904,7 +26904,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G915" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H915" t="n">
         <v>2959</v>
@@ -27020,7 +27020,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G919" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H919" t="n">
         <v>3027</v>
@@ -27194,7 +27194,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G925" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H925" t="n">
         <v>10000</v>
@@ -27223,7 +27223,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G926" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H926" t="n">
         <v>3008</v>
@@ -27252,7 +27252,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G927" t="n">
-        <v>2.36155009269714</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H927" t="n">
         <v>13666</v>
@@ -27281,7 +27281,7 @@
         <v>2.5</v>
       </c>
       <c r="G928" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H928" t="n">
         <v>5817</v>
@@ -27310,7 +27310,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G929" t="n">
-        <v>2.38955283164978</v>
+        <v>2.38955307006836</v>
       </c>
       <c r="H929" t="n">
         <v>2434</v>
@@ -27368,7 +27368,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G931" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H931" t="n">
         <v>1499</v>
@@ -27455,7 +27455,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G934" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H934" t="n">
         <v>18035</v>
@@ -27513,7 +27513,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G936" t="n">
-        <v>2.20286917686462</v>
+        <v>2.20286893844604</v>
       </c>
       <c r="H936" t="n">
         <v>6398</v>
@@ -27542,7 +27542,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G937" t="n">
-        <v>2.24020576477051</v>
+        <v>2.24020600318909</v>
       </c>
       <c r="H937" t="n">
         <v>5629</v>
@@ -27571,7 +27571,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G938" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H938" t="n">
         <v>36604</v>
@@ -27629,7 +27629,7 @@
         <v>2.5</v>
       </c>
       <c r="G940" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H940" t="n">
         <v>25694</v>
@@ -27658,7 +27658,7 @@
         <v>2.5</v>
       </c>
       <c r="G941" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H941" t="n">
         <v>21800</v>
@@ -27745,7 +27745,7 @@
         <v>2.5</v>
       </c>
       <c r="G944" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H944" t="n">
         <v>1700</v>
@@ -27803,7 +27803,7 @@
         <v>2.5</v>
       </c>
       <c r="G946" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H946" t="n">
         <v>11500</v>
@@ -27832,7 +27832,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G947" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H947" t="n">
         <v>10650</v>
@@ -28006,7 +28006,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G953" t="n">
-        <v>2.34288191795349</v>
+        <v>2.34288215637207</v>
       </c>
       <c r="H953" t="n">
         <v>8059</v>
@@ -28064,7 +28064,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G955" t="n">
-        <v>2.36155009269714</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H955" t="n">
         <v>1000</v>
@@ -28122,7 +28122,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G957" t="n">
-        <v>2.36155009269714</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H957" t="n">
         <v>2000</v>
@@ -28151,7 +28151,7 @@
         <v>2.5</v>
       </c>
       <c r="G958" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H958" t="n">
         <v>5819</v>
@@ -28180,7 +28180,7 @@
         <v>2.5</v>
       </c>
       <c r="G959" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H959" t="n">
         <v>1888</v>
@@ -28296,7 +28296,7 @@
         <v>2.5</v>
       </c>
       <c r="G963" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H963" t="n">
         <v>5469</v>
@@ -28412,7 +28412,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G967" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H967" t="n">
         <v>3005</v>
@@ -28441,7 +28441,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G968" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H968" t="n">
         <v>0</v>
@@ -28499,7 +28499,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G970" t="n">
-        <v>2.38955283164978</v>
+        <v>2.38955307006836</v>
       </c>
       <c r="H970" t="n">
         <v>1000</v>
@@ -28528,7 +28528,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G971" t="n">
-        <v>2.38955283164978</v>
+        <v>2.38955307006836</v>
       </c>
       <c r="H971" t="n">
         <v>2000</v>
@@ -28557,7 +28557,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G972" t="n">
-        <v>2.38955283164978</v>
+        <v>2.38955307006836</v>
       </c>
       <c r="H972" t="n">
         <v>1000</v>
@@ -28673,7 +28673,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G976" t="n">
-        <v>2.38955283164978</v>
+        <v>2.38955307006836</v>
       </c>
       <c r="H976" t="n">
         <v>6488</v>
@@ -28789,7 +28789,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G980" t="n">
-        <v>2.38955283164978</v>
+        <v>2.38955307006836</v>
       </c>
       <c r="H980" t="n">
         <v>1000</v>
@@ -28818,7 +28818,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G981" t="n">
-        <v>2.36155009269714</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H981" t="n">
         <v>3499</v>
@@ -28847,7 +28847,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G982" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H982" t="n">
         <v>509</v>
@@ -28876,7 +28876,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G983" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H983" t="n">
         <v>0</v>
@@ -28905,7 +28905,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G984" t="n">
-        <v>2.36155009269714</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H984" t="n">
         <v>1677</v>
@@ -28934,7 +28934,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G985" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H985" t="n">
         <v>1000</v>
@@ -28963,7 +28963,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G986" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H986" t="n">
         <v>0</v>
@@ -28992,7 +28992,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G987" t="n">
-        <v>2.34288191795349</v>
+        <v>2.34288215637207</v>
       </c>
       <c r="H987" t="n">
         <v>1228</v>
@@ -29021,7 +29021,7 @@
         <v>2.5</v>
       </c>
       <c r="G988" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H988" t="n">
         <v>1300</v>
@@ -29108,7 +29108,7 @@
         <v>2.5</v>
       </c>
       <c r="G991" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H991" t="n">
         <v>560</v>
@@ -29195,7 +29195,7 @@
         <v>2.5</v>
       </c>
       <c r="G994" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H994" t="n">
         <v>17583</v>
@@ -29224,7 +29224,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G995" t="n">
-        <v>2.34288191795349</v>
+        <v>2.34288215637207</v>
       </c>
       <c r="H995" t="n">
         <v>3329</v>
@@ -29253,7 +29253,7 @@
         <v>2.5</v>
       </c>
       <c r="G996" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H996" t="n">
         <v>1000</v>
@@ -29282,7 +29282,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G997" t="n">
-        <v>2.34288191795349</v>
+        <v>2.34288215637207</v>
       </c>
       <c r="H997" t="n">
         <v>1000</v>
@@ -29311,7 +29311,7 @@
         <v>2.5</v>
       </c>
       <c r="G998" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H998" t="n">
         <v>7811</v>
@@ -29340,7 +29340,7 @@
         <v>2.5</v>
       </c>
       <c r="G999" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H999" t="n">
         <v>5034</v>
@@ -29369,7 +29369,7 @@
         <v>2.5</v>
       </c>
       <c r="G1000" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H1000" t="n">
         <v>5333</v>
@@ -29398,7 +29398,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1001" t="n">
-        <v>2.38955283164978</v>
+        <v>2.38955307006836</v>
       </c>
       <c r="H1001" t="n">
         <v>4093</v>
@@ -29427,7 +29427,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1002" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H1002" t="n">
         <v>3900</v>
@@ -29456,7 +29456,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1003" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H1003" t="n">
         <v>4000</v>
@@ -29485,7 +29485,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1004" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H1004" t="n">
         <v>1500</v>
@@ -29572,7 +29572,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1007" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H1007" t="n">
         <v>900</v>
@@ -29601,7 +29601,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1008" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H1008" t="n">
         <v>1100</v>
@@ -29630,7 +29630,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1009" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H1009" t="n">
         <v>1826</v>
@@ -29659,7 +29659,7 @@
         <v>2.5</v>
       </c>
       <c r="G1010" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H1010" t="n">
         <v>2800</v>
@@ -29688,7 +29688,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1011" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H1011" t="n">
         <v>3388</v>
@@ -29717,7 +29717,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1012" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H1012" t="n">
         <v>10877</v>
@@ -29746,7 +29746,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1013" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H1013" t="n">
         <v>35374</v>
@@ -29775,7 +29775,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1014" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H1014" t="n">
         <v>0</v>
@@ -29804,7 +29804,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1015" t="n">
-        <v>2.38955283164978</v>
+        <v>2.38955307006836</v>
       </c>
       <c r="H1015" t="n">
         <v>27110</v>
@@ -29833,7 +29833,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1016" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H1016" t="n">
         <v>34383</v>
@@ -29862,7 +29862,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1017" t="n">
-        <v>2.34288191795349</v>
+        <v>2.34288215637207</v>
       </c>
       <c r="H1017" t="n">
         <v>10140</v>
@@ -29891,7 +29891,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1018" t="n">
-        <v>2.34288191795349</v>
+        <v>2.34288215637207</v>
       </c>
       <c r="H1018" t="n">
         <v>1200</v>
@@ -29920,7 +29920,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1019" t="n">
-        <v>2.34288191795349</v>
+        <v>2.34288215637207</v>
       </c>
       <c r="H1019" t="n">
         <v>408</v>
@@ -29949,7 +29949,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1020" t="n">
-        <v>2.34288191795349</v>
+        <v>2.34288215637207</v>
       </c>
       <c r="H1020" t="n">
         <v>250</v>
@@ -29978,7 +29978,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1021" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H1021" t="n">
         <v>942</v>
@@ -30007,7 +30007,7 @@
         <v>2.5</v>
       </c>
       <c r="G1022" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H1022" t="n">
         <v>5140</v>
@@ -30036,7 +30036,7 @@
         <v>2.5</v>
       </c>
       <c r="G1023" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H1023" t="n">
         <v>12627</v>
@@ -30094,7 +30094,7 @@
         <v>2.5</v>
       </c>
       <c r="G1025" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H1025" t="n">
         <v>1230</v>
@@ -30123,7 +30123,7 @@
         <v>2.5</v>
       </c>
       <c r="G1026" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H1026" t="n">
         <v>1559</v>
@@ -30152,7 +30152,7 @@
         <v>2.5</v>
       </c>
       <c r="G1027" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H1027" t="n">
         <v>6612</v>
@@ -30181,7 +30181,7 @@
         <v>2.5</v>
       </c>
       <c r="G1028" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H1028" t="n">
         <v>0</v>
@@ -30210,7 +30210,7 @@
         <v>2.5</v>
       </c>
       <c r="G1029" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H1029" t="n">
         <v>15470</v>
@@ -30355,7 +30355,7 @@
         <v>2.5</v>
       </c>
       <c r="G1034" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H1034" t="n">
         <v>7531</v>
@@ -30471,7 +30471,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1038" t="n">
-        <v>2.34288191795349</v>
+        <v>2.34288215637207</v>
       </c>
       <c r="H1038" t="n">
         <v>35898</v>
@@ -30500,7 +30500,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1039" t="n">
-        <v>2.34288191795349</v>
+        <v>2.34288215637207</v>
       </c>
       <c r="H1039" t="n">
         <v>10000</v>
@@ -30529,7 +30529,7 @@
         <v>2.5</v>
       </c>
       <c r="G1040" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H1040" t="n">
         <v>2030</v>
@@ -30558,7 +30558,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1041" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H1041" t="n">
         <v>15334</v>
@@ -30587,7 +30587,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1042" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H1042" t="n">
         <v>548</v>
@@ -30674,7 +30674,7 @@
         <v>2.5</v>
       </c>
       <c r="G1045" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H1045" t="n">
         <v>2500</v>
@@ -30703,7 +30703,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1046" t="n">
-        <v>2.34288191795349</v>
+        <v>2.34288215637207</v>
       </c>
       <c r="H1046" t="n">
         <v>31954</v>
@@ -30848,7 +30848,7 @@
         <v>2.5</v>
       </c>
       <c r="G1051" t="n">
-        <v>2.33354806900024</v>
+        <v>2.33354783058167</v>
       </c>
       <c r="H1051" t="n">
         <v>8205</v>
@@ -30877,7 +30877,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1052" t="n">
-        <v>2.36155009269714</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H1052" t="n">
         <v>6417</v>
@@ -30906,7 +30906,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1053" t="n">
-        <v>2.34288191795349</v>
+        <v>2.34288215637207</v>
       </c>
       <c r="H1053" t="n">
         <v>6475</v>
@@ -30935,7 +30935,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1054" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H1054" t="n">
         <v>862</v>
@@ -30964,7 +30964,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1055" t="n">
-        <v>2.38955283164978</v>
+        <v>2.38955307006836</v>
       </c>
       <c r="H1055" t="n">
         <v>5201</v>
@@ -31022,7 +31022,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1057" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H1057" t="n">
         <v>2510</v>
@@ -31051,7 +31051,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1058" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H1058" t="n">
         <v>0</v>
@@ -31080,7 +31080,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1059" t="n">
-        <v>2.38021898269653</v>
+        <v>2.38021874427795</v>
       </c>
       <c r="H1059" t="n">
         <v>1100</v>
@@ -31109,7 +31109,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1060" t="n">
-        <v>2.38955283164978</v>
+        <v>2.38955307006836</v>
       </c>
       <c r="H1060" t="n">
         <v>290</v>
@@ -31283,7 +31283,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H1066" t="n">
         <v>5691</v>
@@ -31312,7 +31312,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688989639282</v>
       </c>
       <c r="H1067" t="n">
         <v>400</v>
@@ -31428,7 +31428,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1071" t="n">
-        <v>2.70691585540771</v>
+        <v>2.70691561698914</v>
       </c>
       <c r="H1071" t="n">
         <v>53618</v>
@@ -31718,7 +31718,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1081" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H1081" t="n">
         <v>317450</v>
@@ -31747,7 +31747,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1082" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H1082" t="n">
         <v>125568</v>
@@ -31776,7 +31776,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1083" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H1083" t="n">
         <v>170449</v>
@@ -31863,7 +31863,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1086" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H1086" t="n">
         <v>1691</v>
@@ -32124,7 +32124,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1095" t="n">
         <v>2654</v>
@@ -32240,7 +32240,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1099" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H1099" t="n">
         <v>1400</v>
@@ -32443,7 +32443,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1106" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1106" t="n">
         <v>200</v>
@@ -32501,7 +32501,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1108" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1108" t="n">
         <v>1000</v>
@@ -32530,7 +32530,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1109" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1109" t="n">
         <v>1587</v>
@@ -32559,7 +32559,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1110" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1110" t="n">
         <v>2194</v>
@@ -32617,7 +32617,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1112" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1112" t="n">
         <v>3440</v>
@@ -32646,7 +32646,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1113" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1113" t="n">
         <v>0</v>
@@ -32675,7 +32675,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1114" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1114" t="n">
         <v>3456</v>
@@ -32704,7 +32704,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1115" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1115" t="n">
         <v>0</v>
@@ -32878,7 +32878,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1121" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H1121" t="n">
         <v>10111</v>
@@ -32907,7 +32907,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1122" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H1122" t="n">
         <v>0</v>
@@ -32936,7 +32936,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1123" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H1123" t="n">
         <v>8171</v>
@@ -32965,7 +32965,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1124" t="n">
-        <v>2.6135733127594</v>
+        <v>2.61357355117798</v>
       </c>
       <c r="H1124" t="n">
         <v>0</v>
@@ -33429,7 +33429,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1140" t="n">
-        <v>2.82826018333435</v>
+        <v>2.82825994491577</v>
       </c>
       <c r="H1140" t="n">
         <v>9200</v>
@@ -33516,7 +33516,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1143" t="n">
-        <v>2.85626244544983</v>
+        <v>2.85626268386841</v>
       </c>
       <c r="H1143" t="n">
         <v>15530</v>
@@ -33835,7 +33835,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1154" t="n">
-        <v>2.85626244544983</v>
+        <v>2.85626268386841</v>
       </c>
       <c r="H1154" t="n">
         <v>3063</v>
@@ -34183,7 +34183,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.13628816604614</v>
+        <v>3.13628840446472</v>
       </c>
       <c r="H1166" t="n">
         <v>15387</v>
@@ -34212,7 +34212,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.20162773132324</v>
+        <v>3.20162796974182</v>
       </c>
       <c r="H1167" t="n">
         <v>24299</v>
@@ -34415,7 +34415,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.31363797187805</v>
+        <v>3.31363773345947</v>
       </c>
       <c r="H1174" t="n">
         <v>34347</v>
@@ -34444,7 +34444,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.44431686401367</v>
+        <v>3.44431662559509</v>
       </c>
       <c r="H1175" t="n">
         <v>13251</v>
@@ -34531,7 +34531,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1178" t="n">
-        <v>3.79901599884033</v>
+        <v>3.79901623725891</v>
       </c>
       <c r="H1178" t="n">
         <v>19529</v>
@@ -34676,7 +34676,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1183" t="n">
-        <v>4.76043796539307</v>
+        <v>4.76043748855591</v>
       </c>
       <c r="H1183" t="n">
         <v>303286</v>
@@ -34734,7 +34734,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1185" t="n">
-        <v>4.94712162017822</v>
+        <v>4.94712209701538</v>
       </c>
       <c r="H1185" t="n">
         <v>36680</v>
@@ -34763,7 +34763,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1186" t="n">
-        <v>4.85377931594849</v>
+        <v>4.85377979278564</v>
       </c>
       <c r="H1186" t="n">
         <v>39631</v>
@@ -34792,7 +34792,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G1187" t="n">
-        <v>4.63909339904785</v>
+        <v>4.63909292221069</v>
       </c>
       <c r="H1187" t="n">
         <v>70233</v>
@@ -34850,7 +34850,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1189" t="n">
-        <v>4.51774930953979</v>
+        <v>4.51774883270264</v>
       </c>
       <c r="H1189" t="n">
         <v>67215</v>
@@ -35082,7 +35082,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1197" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1197" t="n">
         <v>37624</v>
@@ -35111,7 +35111,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1198" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1198" t="n">
         <v>17896</v>
@@ -35169,7 +35169,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1200" t="n">
-        <v>4.51774930953979</v>
+        <v>4.51774883270264</v>
       </c>
       <c r="H1200" t="n">
         <v>23594</v>
@@ -35198,7 +35198,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1201" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1201" t="n">
         <v>16723</v>
@@ -35314,7 +35314,7 @@
         <v>5</v>
       </c>
       <c r="G1205" t="n">
-        <v>4.66709613800049</v>
+        <v>4.66709566116333</v>
       </c>
       <c r="H1205" t="n">
         <v>37268</v>
@@ -35401,7 +35401,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1208" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1208" t="n">
         <v>10200</v>
@@ -35575,7 +35575,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1214" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1214" t="n">
         <v>5950</v>
@@ -35604,7 +35604,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1215" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1215" t="n">
         <v>6941</v>
@@ -35633,7 +35633,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1216" t="n">
-        <v>4.48974657058716</v>
+        <v>4.48974609375</v>
       </c>
       <c r="H1216" t="n">
         <v>694</v>
@@ -35662,7 +35662,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1217" t="n">
-        <v>4.48974657058716</v>
+        <v>4.48974609375</v>
       </c>
       <c r="H1217" t="n">
         <v>5620</v>
@@ -35691,7 +35691,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1218" t="n">
-        <v>4.45240879058838</v>
+        <v>4.4524097442627</v>
       </c>
       <c r="H1218" t="n">
         <v>17443</v>
@@ -35720,7 +35720,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1219" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1219" t="n">
         <v>2891</v>
@@ -35749,7 +35749,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1220" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1220" t="n">
         <v>5384</v>
@@ -35778,7 +35778,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1221" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1221" t="n">
         <v>3060</v>
@@ -35836,7 +35836,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1223" t="n">
-        <v>4.38706970214844</v>
+        <v>4.3870701789856</v>
       </c>
       <c r="H1223" t="n">
         <v>2203</v>
@@ -35865,7 +35865,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1224" t="n">
-        <v>4.37773609161377</v>
+        <v>4.37773561477661</v>
       </c>
       <c r="H1224" t="n">
         <v>6752</v>
@@ -35894,7 +35894,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1225" t="n">
-        <v>4.36840152740479</v>
+        <v>4.36840105056763</v>
       </c>
       <c r="H1225" t="n">
         <v>12461</v>
@@ -35923,7 +35923,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1226" t="n">
-        <v>4.37773609161377</v>
+        <v>4.37773561477661</v>
       </c>
       <c r="H1226" t="n">
         <v>1614</v>
@@ -35952,7 +35952,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1227" t="n">
-        <v>4.38706970214844</v>
+        <v>4.3870701789856</v>
       </c>
       <c r="H1227" t="n">
         <v>11176</v>
@@ -35981,7 +35981,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1228" t="n">
-        <v>4.34973287582397</v>
+        <v>4.34973335266113</v>
       </c>
       <c r="H1228" t="n">
         <v>766</v>
@@ -36010,7 +36010,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1229" t="n">
-        <v>4.38706970214844</v>
+        <v>4.3870701789856</v>
       </c>
       <c r="H1229" t="n">
         <v>3628</v>
@@ -36068,7 +36068,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1231" t="n">
-        <v>4.38706970214844</v>
+        <v>4.3870701789856</v>
       </c>
       <c r="H1231" t="n">
         <v>12136</v>
@@ -36097,7 +36097,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1232" t="n">
-        <v>4.38706970214844</v>
+        <v>4.3870701789856</v>
       </c>
       <c r="H1232" t="n">
         <v>8849</v>
@@ -36126,7 +36126,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1233" t="n">
-        <v>4.38706970214844</v>
+        <v>4.3870701789856</v>
       </c>
       <c r="H1233" t="n">
         <v>8218</v>
@@ -36184,7 +36184,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1235" t="n">
-        <v>4.38706970214844</v>
+        <v>4.3870701789856</v>
       </c>
       <c r="H1235" t="n">
         <v>3700</v>
@@ -36213,7 +36213,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1236" t="n">
-        <v>4.38706970214844</v>
+        <v>4.3870701789856</v>
       </c>
       <c r="H1236" t="n">
         <v>9129</v>
@@ -36242,7 +36242,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1237" t="n">
-        <v>4.38706970214844</v>
+        <v>4.3870701789856</v>
       </c>
       <c r="H1237" t="n">
         <v>3361</v>
@@ -36271,7 +36271,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1238" t="n">
-        <v>4.38706970214844</v>
+        <v>4.3870701789856</v>
       </c>
       <c r="H1238" t="n">
         <v>3927</v>
@@ -36300,7 +36300,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1239" t="n">
-        <v>4.38706970214844</v>
+        <v>4.3870701789856</v>
       </c>
       <c r="H1239" t="n">
         <v>2020</v>
@@ -36329,7 +36329,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1240" t="n">
-        <v>4.45240879058838</v>
+        <v>4.4524097442627</v>
       </c>
       <c r="H1240" t="n">
         <v>7982</v>
@@ -36445,7 +36445,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1244" t="n">
-        <v>4.38706970214844</v>
+        <v>4.3870701789856</v>
       </c>
       <c r="H1244" t="n">
         <v>10595</v>
@@ -36474,7 +36474,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.40573835372925</v>
+        <v>4.40573787689209</v>
       </c>
       <c r="H1245" t="n">
         <v>1123</v>
@@ -36503,7 +36503,7 @@
         <v>4.75</v>
       </c>
       <c r="G1246" t="n">
-        <v>4.43374109268188</v>
+        <v>4.43374061584473</v>
       </c>
       <c r="H1246" t="n">
         <v>2543</v>
@@ -36619,7 +36619,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1250" t="n">
-        <v>4.40573835372925</v>
+        <v>4.40573787689209</v>
       </c>
       <c r="H1250" t="n">
         <v>2487</v>
@@ -36648,7 +36648,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1251" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1251" t="n">
         <v>39291</v>
@@ -36706,7 +36706,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1253" t="n">
-        <v>4.76043796539307</v>
+        <v>4.76043748855591</v>
       </c>
       <c r="H1253" t="n">
         <v>29354</v>
@@ -37315,7 +37315,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1274" t="n">
-        <v>4.9907808303833</v>
+        <v>4.99078130722046</v>
       </c>
       <c r="H1274" t="n">
         <v>24772</v>
@@ -37344,7 +37344,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1275" t="n">
-        <v>5.02917194366455</v>
+        <v>5.02917146682739</v>
       </c>
       <c r="H1275" t="n">
         <v>31385</v>
@@ -37431,7 +37431,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1278" t="n">
-        <v>5.48985910415649</v>
+        <v>5.48985958099365</v>
       </c>
       <c r="H1278" t="n">
         <v>70084</v>
@@ -37576,7 +37576,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1283" t="n">
-        <v>5.83537530899048</v>
+        <v>5.83537483215332</v>
       </c>
       <c r="H1283" t="n">
         <v>8786</v>
@@ -37634,7 +37634,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1285" t="n">
-        <v>6.39203882217407</v>
+        <v>6.39203929901123</v>
       </c>
       <c r="H1285" t="n">
         <v>35361</v>
@@ -37750,7 +37750,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1289" t="n">
-        <v>6.46882057189941</v>
+        <v>6.46882009506226</v>
       </c>
       <c r="H1289" t="n">
         <v>13104</v>
@@ -37866,7 +37866,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G1293" t="n">
-        <v>6.18089056015015</v>
+        <v>6.1808910369873</v>
       </c>
       <c r="H1293" t="n">
         <v>21462</v>
@@ -37895,7 +37895,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1294" t="n">
-        <v>6.12330484390259</v>
+        <v>6.12330532073975</v>
       </c>
       <c r="H1294" t="n">
         <v>21748</v>
@@ -37953,7 +37953,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1296" t="n">
-        <v>6.39203882217407</v>
+        <v>6.39203929901123</v>
       </c>
       <c r="H1296" t="n">
         <v>15861</v>
@@ -37982,7 +37982,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1297" t="n">
-        <v>6.48801565170288</v>
+        <v>6.48801612854004</v>
       </c>
       <c r="H1297" t="n">
         <v>2374</v>
@@ -38011,7 +38011,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1298" t="n">
-        <v>6.48801565170288</v>
+        <v>6.48801612854004</v>
       </c>
       <c r="H1298" t="n">
         <v>9827</v>
@@ -38156,7 +38156,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1303" t="n">
-        <v>6.48801565170288</v>
+        <v>6.48801612854004</v>
       </c>
       <c r="H1303" t="n">
         <v>11171</v>
@@ -38388,7 +38388,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1311" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1311" t="n">
         <v>18885</v>
@@ -38446,7 +38446,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1313" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1313" t="n">
         <v>34147</v>
@@ -38533,7 +38533,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1316" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1316" t="n">
         <v>10376</v>
@@ -38939,7 +38939,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1330" t="n">
-        <v>5.68181228637695</v>
+        <v>5.68181276321411</v>
       </c>
       <c r="H1330" t="n">
         <v>4010</v>
@@ -39026,7 +39026,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1333" t="n">
-        <v>5.66261768341064</v>
+        <v>5.66261720657349</v>
       </c>
       <c r="H1333" t="n">
         <v>3167</v>
@@ -39055,7 +39055,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.56664133071899</v>
+        <v>5.56664085388184</v>
       </c>
       <c r="H1334" t="n">
         <v>13673</v>
@@ -39084,7 +39084,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1335" t="n">
-        <v>5.48985910415649</v>
+        <v>5.48985958099365</v>
       </c>
       <c r="H1335" t="n">
         <v>2565</v>
@@ -39142,7 +39142,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1337" t="n">
-        <v>5.56664133071899</v>
+        <v>5.56664085388184</v>
       </c>
       <c r="H1337" t="n">
         <v>2917</v>
@@ -39171,7 +39171,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1338" t="n">
-        <v>5.56664133071899</v>
+        <v>5.56664085388184</v>
       </c>
       <c r="H1338" t="n">
         <v>1312</v>
@@ -39258,7 +39258,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1341" t="n">
-        <v>5.66261768341064</v>
+        <v>5.66261720657349</v>
       </c>
       <c r="H1341" t="n">
         <v>1605</v>
@@ -39287,7 +39287,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1342" t="n">
-        <v>5.66261768341064</v>
+        <v>5.66261720657349</v>
       </c>
       <c r="H1342" t="n">
         <v>3220</v>
@@ -39403,7 +39403,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1346" t="n">
-        <v>5.56664133071899</v>
+        <v>5.56664085388184</v>
       </c>
       <c r="H1346" t="n">
         <v>2814</v>
@@ -39519,7 +39519,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1350" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1350" t="n">
         <v>11182</v>
@@ -39548,7 +39548,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1351" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1351" t="n">
         <v>17082</v>
@@ -39577,7 +39577,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1352" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1352" t="n">
         <v>5027</v>
@@ -39606,7 +39606,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1353" t="n">
-        <v>6.12330484390259</v>
+        <v>6.12330532073975</v>
       </c>
       <c r="H1353" t="n">
         <v>15567</v>
@@ -39693,7 +39693,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1356" t="n">
-        <v>5.87376594543457</v>
+        <v>5.87376546859741</v>
       </c>
       <c r="H1356" t="n">
         <v>18468</v>
@@ -39896,7 +39896,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1363" t="n">
-        <v>5.96974229812622</v>
+        <v>5.96974182128906</v>
       </c>
       <c r="H1363" t="n">
         <v>14927</v>
@@ -40012,7 +40012,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1367" t="n">
-        <v>5.96974229812622</v>
+        <v>5.96974182128906</v>
       </c>
       <c r="H1367" t="n">
         <v>5383</v>
@@ -40041,7 +40041,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1368" t="n">
-        <v>5.83537530899048</v>
+        <v>5.83537483215332</v>
       </c>
       <c r="H1368" t="n">
         <v>3207</v>
@@ -40099,7 +40099,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1370" t="n">
-        <v>5.96974229812622</v>
+        <v>5.96974182128906</v>
       </c>
       <c r="H1370" t="n">
         <v>2420</v>
@@ -40128,7 +40128,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1371" t="n">
-        <v>5.87376594543457</v>
+        <v>5.87376546859741</v>
       </c>
       <c r="H1371" t="n">
         <v>5952</v>
@@ -40186,7 +40186,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1373" t="n">
-        <v>6.0849142074585</v>
+        <v>6.08491468429565</v>
       </c>
       <c r="H1373" t="n">
         <v>4048</v>
@@ -40244,7 +40244,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1375" t="n">
-        <v>5.87376594543457</v>
+        <v>5.87376546859741</v>
       </c>
       <c r="H1375" t="n">
         <v>6216</v>
@@ -40505,7 +40505,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1384" t="n">
-        <v>5.87376594543457</v>
+        <v>5.87376546859741</v>
       </c>
       <c r="H1384" t="n">
         <v>8532</v>
@@ -40534,7 +40534,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1385" t="n">
-        <v>5.96974229812622</v>
+        <v>5.96974182128906</v>
       </c>
       <c r="H1385" t="n">
         <v>4804</v>
@@ -40563,7 +40563,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1386" t="n">
-        <v>5.96974229812622</v>
+        <v>5.96974182128906</v>
       </c>
       <c r="H1386" t="n">
         <v>51315</v>
@@ -40592,7 +40592,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1387" t="n">
-        <v>5.96974229812622</v>
+        <v>5.96974182128906</v>
       </c>
       <c r="H1387" t="n">
         <v>3086</v>
@@ -40621,7 +40621,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1388" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1388" t="n">
         <v>5083</v>
@@ -40679,7 +40679,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1390" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1390" t="n">
         <v>3425</v>
@@ -40737,7 +40737,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1392" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1392" t="n">
         <v>2371</v>
@@ -40766,7 +40766,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1393" t="n">
-        <v>5.87376594543457</v>
+        <v>5.87376546859741</v>
       </c>
       <c r="H1393" t="n">
         <v>4474</v>
@@ -41085,7 +41085,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1404" t="n">
-        <v>6.0849142074585</v>
+        <v>6.08491468429565</v>
       </c>
       <c r="H1404" t="n">
         <v>18941</v>
@@ -41143,7 +41143,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1406" t="n">
-        <v>6.12330484390259</v>
+        <v>6.12330532073975</v>
       </c>
       <c r="H1406" t="n">
         <v>40015</v>
@@ -41462,7 +41462,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1417" t="n">
-        <v>7.02548456192017</v>
+        <v>7.02548503875732</v>
       </c>
       <c r="H1417" t="n">
         <v>6334</v>
@@ -41839,7 +41839,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1430" t="n">
-        <v>7.02548456192017</v>
+        <v>7.02548503875732</v>
       </c>
       <c r="H1430" t="n">
         <v>15354</v>
@@ -41897,7 +41897,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1432" t="n">
-        <v>7.02548456192017</v>
+        <v>7.02548503875732</v>
       </c>
       <c r="H1432" t="n">
         <v>1260</v>
@@ -42129,7 +42129,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1440" t="n">
-        <v>7.06387567520142</v>
+        <v>7.06387519836426</v>
       </c>
       <c r="H1440" t="n">
         <v>1592</v>
@@ -42187,7 +42187,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G1442" t="n">
-        <v>7.12146091461182</v>
+        <v>7.12146139144897</v>
       </c>
       <c r="H1442" t="n">
         <v>9087</v>
@@ -42303,7 +42303,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1446" t="n">
-        <v>7.06387567520142</v>
+        <v>7.06387519836426</v>
       </c>
       <c r="H1446" t="n">
         <v>10440</v>
@@ -42361,7 +42361,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1448" t="n">
-        <v>7.06387567520142</v>
+        <v>7.06387519836426</v>
       </c>
       <c r="H1448" t="n">
         <v>6369</v>
@@ -42390,7 +42390,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1449" t="n">
-        <v>6.91031217575073</v>
+        <v>6.91031265258789</v>
       </c>
       <c r="H1449" t="n">
         <v>8416</v>
@@ -42419,7 +42419,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1450" t="n">
-        <v>7.02548456192017</v>
+        <v>7.02548503875732</v>
       </c>
       <c r="H1450" t="n">
         <v>5499</v>
@@ -42535,7 +42535,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1454" t="n">
-        <v>7.06387567520142</v>
+        <v>7.06387519836426</v>
       </c>
       <c r="H1454" t="n">
         <v>2894</v>
@@ -42680,7 +42680,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1459" t="n">
-        <v>6.91031217575073</v>
+        <v>6.91031265258789</v>
       </c>
       <c r="H1459" t="n">
         <v>3121</v>
@@ -42738,7 +42738,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1461" t="n">
-        <v>6.91031217575073</v>
+        <v>6.91031265258789</v>
       </c>
       <c r="H1461" t="n">
         <v>9076</v>
@@ -42767,7 +42767,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1462" t="n">
-        <v>7.06387567520142</v>
+        <v>7.06387519836426</v>
       </c>
       <c r="H1462" t="n">
         <v>300</v>
@@ -42883,7 +42883,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1466" t="n">
-        <v>7.02548456192017</v>
+        <v>7.02548503875732</v>
       </c>
       <c r="H1466" t="n">
         <v>501</v>
@@ -43173,7 +43173,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1476" t="n">
-        <v>6.91031217575073</v>
+        <v>6.91031265258789</v>
       </c>
       <c r="H1476" t="n">
         <v>7848</v>
@@ -43202,7 +43202,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1477" t="n">
-        <v>6.89111709594727</v>
+        <v>6.89111757278442</v>
       </c>
       <c r="H1477" t="n">
         <v>12560</v>
@@ -43260,7 +43260,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1479" t="n">
-        <v>6.91031217575073</v>
+        <v>6.91031265258789</v>
       </c>
       <c r="H1479" t="n">
         <v>16205</v>
@@ -43289,7 +43289,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1480" t="n">
-        <v>6.77594566345215</v>
+        <v>6.77594518661499</v>
       </c>
       <c r="H1480" t="n">
         <v>1973</v>
@@ -43318,7 +43318,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1481" t="n">
-        <v>6.98709392547607</v>
+        <v>6.98709440231323</v>
       </c>
       <c r="H1481" t="n">
         <v>4148</v>
@@ -43347,7 +43347,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1482" t="n">
-        <v>6.89111709594727</v>
+        <v>6.89111757278442</v>
       </c>
       <c r="H1482" t="n">
         <v>144</v>
@@ -43405,7 +43405,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G1484" t="n">
-        <v>6.79514074325562</v>
+        <v>6.79514026641846</v>
       </c>
       <c r="H1484" t="n">
         <v>10530</v>
@@ -43434,7 +43434,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1485" t="n">
-        <v>6.81433582305908</v>
+        <v>6.81433629989624</v>
       </c>
       <c r="H1485" t="n">
         <v>2742</v>
@@ -43463,7 +43463,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1486" t="n">
-        <v>6.91031217575073</v>
+        <v>6.91031265258789</v>
       </c>
       <c r="H1486" t="n">
         <v>1912</v>
@@ -43492,7 +43492,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1487" t="n">
-        <v>6.91031217575073</v>
+        <v>6.91031265258789</v>
       </c>
       <c r="H1487" t="n">
         <v>6267</v>
@@ -43521,7 +43521,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1488" t="n">
-        <v>6.98709392547607</v>
+        <v>6.98709440231323</v>
       </c>
       <c r="H1488" t="n">
         <v>8301</v>
@@ -43724,7 +43724,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1495" t="n">
-        <v>7.29421854019165</v>
+        <v>7.29421901702881</v>
       </c>
       <c r="H1495" t="n">
         <v>3213</v>
@@ -43753,7 +43753,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1496" t="n">
-        <v>7.42858600616455</v>
+        <v>7.42858552932739</v>
       </c>
       <c r="H1496" t="n">
         <v>9505</v>
@@ -43811,7 +43811,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1498" t="n">
-        <v>7.54375839233398</v>
+        <v>7.54375791549683</v>
       </c>
       <c r="H1498" t="n">
         <v>2199</v>
@@ -54547,6 +54547,35 @@
         <v>6603</v>
       </c>
       <c r="I1868" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1869">
+      <c r="A1869" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1869" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1869" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="D1869" t="n">
+        <v>14.1999998092651</v>
+      </c>
+      <c r="E1869" t="n">
+        <v>13.4499998092651</v>
+      </c>
+      <c r="F1869" t="n">
+        <v>13.4499998092651</v>
+      </c>
+      <c r="G1869" t="n">
+        <v>13.4499998092651</v>
+      </c>
+      <c r="H1869" t="n">
+        <v>13935</v>
+      </c>
+      <c r="I1869" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IEG.MI.xlsx
+++ b/data/IEG.MI.xlsx
@@ -54579,6 +54579,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1870">
+      <c r="A1870" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1870" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1870" t="n">
+        <v>13.9499998092651</v>
+      </c>
+      <c r="D1870" t="n">
+        <v>14</v>
+      </c>
+      <c r="E1870" t="n">
+        <v>13.8000001907349</v>
+      </c>
+      <c r="F1870" t="n">
+        <v>14</v>
+      </c>
+      <c r="G1870" t="n">
+        <v>14</v>
+      </c>
+      <c r="H1870" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I1870" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IEG.MI.xlsx
+++ b/data/IEG.MI.xlsx
@@ -543,7 +543,7 @@
         <v>3.69749999046326</v>
       </c>
       <c r="G6" t="n">
-        <v>3.45131707191467</v>
+        <v>3.45131731033325</v>
       </c>
       <c r="H6" t="n">
         <v>5051</v>
@@ -630,7 +630,7 @@
         <v>3.67050004005432</v>
       </c>
       <c r="G9" t="n">
-        <v>3.42611503601074</v>
+        <v>3.42611479759216</v>
       </c>
       <c r="H9" t="n">
         <v>132</v>
@@ -717,7 +717,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G12" t="n">
-        <v>3.43498253822327</v>
+        <v>3.43498277664185</v>
       </c>
       <c r="H12" t="n">
         <v>3250</v>
@@ -746,7 +746,7 @@
         <v>3.64050006866455</v>
       </c>
       <c r="G13" t="n">
-        <v>3.39811229705811</v>
+        <v>3.39811253547668</v>
       </c>
       <c r="H13" t="n">
         <v>1311</v>
@@ -804,7 +804,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G15" t="n">
-        <v>3.42564821243286</v>
+        <v>3.42564845085144</v>
       </c>
       <c r="H15" t="n">
         <v>10175</v>
@@ -891,7 +891,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G18" t="n">
-        <v>3.67767119407654</v>
+        <v>3.67767143249512</v>
       </c>
       <c r="H18" t="n">
         <v>96799</v>
@@ -920,7 +920,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G19" t="n">
-        <v>3.69633984565735</v>
+        <v>3.69633960723877</v>
       </c>
       <c r="H19" t="n">
         <v>96525</v>
@@ -978,7 +978,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G21" t="n">
-        <v>3.80834984779358</v>
+        <v>3.80835032463074</v>
       </c>
       <c r="H21" t="n">
         <v>29979</v>
@@ -1123,7 +1123,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G26" t="n">
-        <v>3.91102647781372</v>
+        <v>3.91102623939514</v>
       </c>
       <c r="H26" t="n">
         <v>12441</v>
@@ -1152,7 +1152,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G27" t="n">
-        <v>3.98569941520691</v>
+        <v>3.98569989204407</v>
       </c>
       <c r="H27" t="n">
         <v>15090</v>
@@ -1181,7 +1181,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G28" t="n">
-        <v>3.95769667625427</v>
+        <v>3.95769739151001</v>
       </c>
       <c r="H28" t="n">
         <v>6052</v>
@@ -1210,7 +1210,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G29" t="n">
-        <v>3.97636604309082</v>
+        <v>3.97636556625366</v>
       </c>
       <c r="H29" t="n">
         <v>2457</v>
@@ -1239,7 +1239,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G30" t="n">
-        <v>4.05103874206543</v>
+        <v>4.05103969573975</v>
       </c>
       <c r="H30" t="n">
         <v>10363</v>
@@ -1326,7 +1326,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>4.01370191574097</v>
+        <v>4.01370286941528</v>
       </c>
       <c r="H33" t="n">
         <v>4871</v>
@@ -1355,7 +1355,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G34" t="n">
-        <v>4.01370191574097</v>
+        <v>4.01370286941528</v>
       </c>
       <c r="H34" t="n">
         <v>114</v>
@@ -1384,7 +1384,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G35" t="n">
-        <v>3.99503421783447</v>
+        <v>3.99503397941589</v>
       </c>
       <c r="H35" t="n">
         <v>922</v>
@@ -1413,7 +1413,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G36" t="n">
-        <v>3.99503421783447</v>
+        <v>3.99503397941589</v>
       </c>
       <c r="H36" t="n">
         <v>300</v>
@@ -1442,7 +1442,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G37" t="n">
-        <v>3.99503421783447</v>
+        <v>3.99503397941589</v>
       </c>
       <c r="H37" t="n">
         <v>4226</v>
@@ -1471,7 +1471,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G38" t="n">
-        <v>3.95769667625427</v>
+        <v>3.95769739151001</v>
       </c>
       <c r="H38" t="n">
         <v>4960</v>
@@ -1500,7 +1500,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G39" t="n">
-        <v>3.88302326202393</v>
+        <v>3.8830235004425</v>
       </c>
       <c r="H39" t="n">
         <v>592</v>
@@ -1529,7 +1529,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G40" t="n">
-        <v>3.88302326202393</v>
+        <v>3.8830235004425</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1558,7 +1558,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G41" t="n">
-        <v>3.95769667625427</v>
+        <v>3.95769739151001</v>
       </c>
       <c r="H41" t="n">
         <v>225</v>
@@ -1587,7 +1587,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G42" t="n">
-        <v>3.95769667625427</v>
+        <v>3.95769739151001</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G45" t="n">
-        <v>3.91102647781372</v>
+        <v>3.91102623939514</v>
       </c>
       <c r="H45" t="n">
         <v>115</v>
@@ -1761,7 +1761,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G48" t="n">
-        <v>3.8456871509552</v>
+        <v>3.84568667411804</v>
       </c>
       <c r="H48" t="n">
         <v>600</v>
@@ -1790,7 +1790,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G49" t="n">
-        <v>3.91102647781372</v>
+        <v>3.91102623939514</v>
       </c>
       <c r="H49" t="n">
         <v>400</v>
@@ -1848,7 +1848,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G51" t="n">
-        <v>3.64033484458923</v>
+        <v>3.64033460617065</v>
       </c>
       <c r="H51" t="n">
         <v>168018</v>
@@ -1877,7 +1877,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G52" t="n">
-        <v>3.59366369247437</v>
+        <v>3.59366345405579</v>
       </c>
       <c r="H52" t="n">
         <v>66112</v>
@@ -1906,7 +1906,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G53" t="n">
-        <v>3.63100051879883</v>
+        <v>3.63100075721741</v>
       </c>
       <c r="H53" t="n">
         <v>23073</v>
@@ -1935,7 +1935,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G54" t="n">
-        <v>3.53765845298767</v>
+        <v>3.53765869140625</v>
       </c>
       <c r="H54" t="n">
         <v>154944</v>
@@ -1964,7 +1964,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G55" t="n">
-        <v>3.42564821243286</v>
+        <v>3.42564845085144</v>
       </c>
       <c r="H55" t="n">
         <v>62162</v>
@@ -2080,7 +2080,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G59" t="n">
-        <v>3.48165369033813</v>
+        <v>3.48165345191956</v>
       </c>
       <c r="H59" t="n">
         <v>10667</v>
@@ -2138,7 +2138,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G61" t="n">
-        <v>3.48165369033813</v>
+        <v>3.48165345191956</v>
       </c>
       <c r="H61" t="n">
         <v>851</v>
@@ -2167,7 +2167,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>3.59366369247437</v>
+        <v>3.59366345405579</v>
       </c>
       <c r="H62" t="n">
         <v>6367</v>
@@ -2254,7 +2254,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G65" t="n">
-        <v>3.58432936668396</v>
+        <v>3.58432960510254</v>
       </c>
       <c r="H65" t="n">
         <v>6062</v>
@@ -2283,7 +2283,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G66" t="n">
-        <v>3.59366369247437</v>
+        <v>3.59366345405579</v>
       </c>
       <c r="H66" t="n">
         <v>2000</v>
@@ -2341,7 +2341,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G68" t="n">
-        <v>3.69633984565735</v>
+        <v>3.69633960723877</v>
       </c>
       <c r="H68" t="n">
         <v>6933</v>
@@ -2428,7 +2428,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G71" t="n">
-        <v>3.59366369247437</v>
+        <v>3.59366345405579</v>
       </c>
       <c r="H71" t="n">
         <v>700</v>
@@ -2457,7 +2457,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G72" t="n">
-        <v>3.53765845298767</v>
+        <v>3.53765869140625</v>
       </c>
       <c r="H72" t="n">
         <v>3200</v>
@@ -2486,7 +2486,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G73" t="n">
-        <v>3.53765845298767</v>
+        <v>3.53765869140625</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G74" t="n">
-        <v>3.53765845298767</v>
+        <v>3.53765869140625</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>3.54699277877808</v>
+        <v>3.5469925403595</v>
       </c>
       <c r="H75" t="n">
         <v>550</v>
@@ -2573,7 +2573,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G76" t="n">
-        <v>3.54699277877808</v>
+        <v>3.5469925403595</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>3.54699277877808</v>
+        <v>3.5469925403595</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -2689,7 +2689,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G80" t="n">
-        <v>3.59366369247437</v>
+        <v>3.59366345405579</v>
       </c>
       <c r="H80" t="n">
         <v>320</v>
@@ -2718,7 +2718,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G81" t="n">
-        <v>3.59366369247437</v>
+        <v>3.59366345405579</v>
       </c>
       <c r="H81" t="n">
         <v>11</v>
@@ -2747,7 +2747,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G82" t="n">
-        <v>3.59366369247437</v>
+        <v>3.59366345405579</v>
       </c>
       <c r="H82" t="n">
         <v>659</v>
@@ -2776,7 +2776,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G83" t="n">
-        <v>3.61233186721802</v>
+        <v>3.6123321056366</v>
       </c>
       <c r="H83" t="n">
         <v>505</v>
@@ -2805,7 +2805,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G84" t="n">
-        <v>3.61233186721802</v>
+        <v>3.6123321056366</v>
       </c>
       <c r="H84" t="n">
         <v>10</v>
@@ -2892,7 +2892,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G87" t="n">
-        <v>3.63100051879883</v>
+        <v>3.63100075721741</v>
       </c>
       <c r="H87" t="n">
         <v>3367</v>
@@ -2950,7 +2950,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>3.59366369247437</v>
+        <v>3.59366345405579</v>
       </c>
       <c r="H89" t="n">
         <v>19</v>
@@ -3008,7 +3008,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G91" t="n">
-        <v>3.61233186721802</v>
+        <v>3.6123321056366</v>
       </c>
       <c r="H91" t="n">
         <v>5</v>
@@ -3037,7 +3037,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G92" t="n">
-        <v>3.54699277877808</v>
+        <v>3.5469925403595</v>
       </c>
       <c r="H92" t="n">
         <v>495</v>
@@ -3066,7 +3066,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G93" t="n">
-        <v>3.58432936668396</v>
+        <v>3.58432960510254</v>
       </c>
       <c r="H93" t="n">
         <v>410</v>
@@ -3153,7 +3153,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G96" t="n">
-        <v>3.67767119407654</v>
+        <v>3.67767143249512</v>
       </c>
       <c r="H96" t="n">
         <v>9735</v>
@@ -3269,7 +3269,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>3.69633984565735</v>
+        <v>3.69633960723877</v>
       </c>
       <c r="H100" t="n">
         <v>5164</v>
@@ -3298,7 +3298,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G101" t="n">
-        <v>3.69633984565735</v>
+        <v>3.69633960723877</v>
       </c>
       <c r="H101" t="n">
         <v>1750</v>
@@ -3327,7 +3327,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G102" t="n">
-        <v>3.64033484458923</v>
+        <v>3.64033460617065</v>
       </c>
       <c r="H102" t="n">
         <v>9855</v>
@@ -3356,7 +3356,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G103" t="n">
-        <v>3.64033484458923</v>
+        <v>3.64033460617065</v>
       </c>
       <c r="H103" t="n">
         <v>40000</v>
@@ -3385,7 +3385,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>3.64033484458923</v>
+        <v>3.64033460617065</v>
       </c>
       <c r="H104" t="n">
         <v>505</v>
@@ -3414,7 +3414,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G105" t="n">
-        <v>3.64966893196106</v>
+        <v>3.64966869354248</v>
       </c>
       <c r="H105" t="n">
         <v>1680</v>
@@ -3443,7 +3443,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G106" t="n">
-        <v>3.79901623725891</v>
+        <v>3.79901599884033</v>
       </c>
       <c r="H106" t="n">
         <v>10585</v>
@@ -3588,7 +3588,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>3.80834984779358</v>
+        <v>3.80835032463074</v>
       </c>
       <c r="H111" t="n">
         <v>19699</v>
@@ -3617,7 +3617,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G112" t="n">
-        <v>3.80834984779358</v>
+        <v>3.80835032463074</v>
       </c>
       <c r="H112" t="n">
         <v>17603</v>
@@ -3733,7 +3733,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G116" t="n">
-        <v>3.76167917251587</v>
+        <v>3.76167941093445</v>
       </c>
       <c r="H116" t="n">
         <v>40346</v>
@@ -3762,7 +3762,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>3.75234508514404</v>
+        <v>3.75234484672546</v>
       </c>
       <c r="H117" t="n">
         <v>7599</v>
@@ -3878,7 +3878,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G121" t="n">
-        <v>3.79901623725891</v>
+        <v>3.79901599884033</v>
       </c>
       <c r="H121" t="n">
         <v>12025</v>
@@ -3907,7 +3907,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G122" t="n">
-        <v>3.86435508728027</v>
+        <v>3.86435484886169</v>
       </c>
       <c r="H122" t="n">
         <v>44816</v>
@@ -3965,7 +3965,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G124" t="n">
-        <v>3.86435508728027</v>
+        <v>3.86435484886169</v>
       </c>
       <c r="H124" t="n">
         <v>15805</v>
@@ -4023,7 +4023,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G126" t="n">
-        <v>3.80834984779358</v>
+        <v>3.80835032463074</v>
       </c>
       <c r="H126" t="n">
         <v>1562</v>
@@ -4139,7 +4139,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G130" t="n">
-        <v>3.74301075935364</v>
+        <v>3.74301099777222</v>
       </c>
       <c r="H130" t="n">
         <v>76762</v>
@@ -4197,7 +4197,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G132" t="n">
-        <v>3.8456871509552</v>
+        <v>3.84568667411804</v>
       </c>
       <c r="H132" t="n">
         <v>2547</v>
@@ -4342,7 +4342,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G137" t="n">
-        <v>3.92969465255737</v>
+        <v>3.92969489097595</v>
       </c>
       <c r="H137" t="n">
         <v>5529</v>
@@ -4574,7 +4574,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G145" t="n">
-        <v>3.89235782623291</v>
+        <v>3.89235758781433</v>
       </c>
       <c r="H145" t="n">
         <v>14</v>
@@ -4661,7 +4661,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G148" t="n">
-        <v>3.95769667625427</v>
+        <v>3.95769739151001</v>
       </c>
       <c r="H148" t="n">
         <v>228432</v>
@@ -4748,7 +4748,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G151" t="n">
-        <v>4.25639152526855</v>
+        <v>4.2563910484314</v>
       </c>
       <c r="H151" t="n">
         <v>8178</v>
@@ -4777,7 +4777,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G152" t="n">
-        <v>4.27505922317505</v>
+        <v>4.27505970001221</v>
       </c>
       <c r="H152" t="n">
         <v>10712</v>
@@ -4835,7 +4835,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G154" t="n">
-        <v>4.35906791687012</v>
+        <v>4.3590669631958</v>
       </c>
       <c r="H154" t="n">
         <v>15474</v>
@@ -4864,7 +4864,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G155" t="n">
-        <v>4.40573787689209</v>
+        <v>4.40573835372925</v>
       </c>
       <c r="H155" t="n">
         <v>10834</v>
@@ -4893,7 +4893,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G156" t="n">
-        <v>4.46174383163452</v>
+        <v>4.46174335479736</v>
       </c>
       <c r="H156" t="n">
         <v>4570</v>
@@ -4922,7 +4922,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G157" t="n">
-        <v>4.40573787689209</v>
+        <v>4.40573835372925</v>
       </c>
       <c r="H157" t="n">
         <v>4479</v>
@@ -4951,7 +4951,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G158" t="n">
-        <v>4.26572561264038</v>
+        <v>4.26572513580322</v>
       </c>
       <c r="H158" t="n">
         <v>10313</v>
@@ -5009,7 +5009,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G160" t="n">
-        <v>4.23772239685059</v>
+        <v>4.23772287368774</v>
       </c>
       <c r="H160" t="n">
         <v>1012</v>
@@ -5038,7 +5038,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G161" t="n">
-        <v>4.17238283157349</v>
+        <v>4.17238330841064</v>
       </c>
       <c r="H161" t="n">
         <v>1389</v>
@@ -5067,7 +5067,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G162" t="n">
-        <v>4.14438056945801</v>
+        <v>4.14438104629517</v>
       </c>
       <c r="H162" t="n">
         <v>5657</v>
@@ -5096,7 +5096,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G163" t="n">
-        <v>4.16304969787598</v>
+        <v>4.16304922103882</v>
       </c>
       <c r="H163" t="n">
         <v>656</v>
@@ -5183,7 +5183,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G166" t="n">
-        <v>4.16304969787598</v>
+        <v>4.16304922103882</v>
       </c>
       <c r="H166" t="n">
         <v>505</v>
@@ -5212,7 +5212,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G167" t="n">
-        <v>4.12571287155151</v>
+        <v>4.12571239471436</v>
       </c>
       <c r="H167" t="n">
         <v>1585</v>
@@ -5241,7 +5241,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>4.05103874206543</v>
+        <v>4.05103969573975</v>
       </c>
       <c r="H168" t="n">
         <v>499</v>
@@ -5270,7 +5270,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G169" t="n">
-        <v>4.14438056945801</v>
+        <v>4.14438104629517</v>
       </c>
       <c r="H169" t="n">
         <v>4433</v>
@@ -5357,7 +5357,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G172" t="n">
-        <v>4.28439426422119</v>
+        <v>4.28439378738403</v>
       </c>
       <c r="H172" t="n">
         <v>1482</v>
@@ -5386,7 +5386,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G173" t="n">
-        <v>4.06037330627441</v>
+        <v>4.06037282943726</v>
       </c>
       <c r="H173" t="n">
         <v>6766</v>
@@ -5415,7 +5415,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G174" t="n">
-        <v>3.59366369247437</v>
+        <v>3.59366345405579</v>
       </c>
       <c r="H174" t="n">
         <v>11092</v>
@@ -5502,7 +5502,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G177" t="n">
-        <v>3.64966893196106</v>
+        <v>3.64966869354248</v>
       </c>
       <c r="H177" t="n">
         <v>15736</v>
@@ -5705,7 +5705,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14562225341797</v>
+        <v>3.14562249183655</v>
       </c>
       <c r="H184" t="n">
         <v>4305</v>
@@ -5821,7 +5821,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G188" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H188" t="n">
         <v>6941</v>
@@ -5850,7 +5850,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G189" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G190" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H190" t="n">
         <v>500</v>
@@ -5908,7 +5908,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G191" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -5937,7 +5937,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G192" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -6169,7 +6169,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G200" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H200" t="n">
         <v>925</v>
@@ -6198,7 +6198,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G201" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H201" t="n">
         <v>93</v>
@@ -6343,7 +6343,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G206" t="n">
-        <v>2.95893883705139</v>
+        <v>2.95893859863281</v>
       </c>
       <c r="H206" t="n">
         <v>19421</v>
@@ -6430,7 +6430,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G209" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H209" t="n">
         <v>865</v>
@@ -6488,7 +6488,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G211" t="n">
-        <v>2.77225494384766</v>
+        <v>2.77225470542908</v>
       </c>
       <c r="H211" t="n">
         <v>5153</v>
@@ -6517,7 +6517,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>2.76292061805725</v>
+        <v>2.76292037963867</v>
       </c>
       <c r="H212" t="n">
         <v>1030</v>
@@ -6575,7 +6575,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G214" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H214" t="n">
         <v>7441</v>
@@ -6691,7 +6691,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G218" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H218" t="n">
         <v>488</v>
@@ -6894,7 +6894,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G225" t="n">
-        <v>2.73491811752319</v>
+        <v>2.73491835594177</v>
       </c>
       <c r="H225" t="n">
         <v>823</v>
@@ -6952,7 +6952,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G227" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H227" t="n">
         <v>6933</v>
@@ -7126,7 +7126,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>2.76292061805725</v>
+        <v>2.76292037963867</v>
       </c>
       <c r="H233" t="n">
         <v>2100</v>
@@ -7155,7 +7155,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G234" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H234" t="n">
         <v>252</v>
@@ -7503,7 +7503,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G246" t="n">
-        <v>3.01494359970093</v>
+        <v>3.01494383811951</v>
       </c>
       <c r="H246" t="n">
         <v>3050</v>
@@ -7561,7 +7561,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G248" t="n">
-        <v>2.97760725021362</v>
+        <v>2.97760701179504</v>
       </c>
       <c r="H248" t="n">
         <v>6756</v>
@@ -7590,7 +7590,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G249" t="n">
-        <v>2.88426494598389</v>
+        <v>2.88426518440247</v>
       </c>
       <c r="H249" t="n">
         <v>3107</v>
@@ -8112,7 +8112,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G267" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H267" t="n">
         <v>2620</v>
@@ -8141,7 +8141,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G268" t="n">
-        <v>2.63224196434021</v>
+        <v>2.63224172592163</v>
       </c>
       <c r="H268" t="n">
         <v>1640</v>
@@ -8315,7 +8315,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G274" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H274" t="n">
         <v>12686</v>
@@ -8344,7 +8344,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G275" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H275" t="n">
         <v>3412</v>
@@ -8402,7 +8402,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G277" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H277" t="n">
         <v>689</v>
@@ -8431,7 +8431,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G278" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H278" t="n">
         <v>0</v>
@@ -8460,7 +8460,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G279" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H279" t="n">
         <v>1890</v>
@@ -8518,7 +8518,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G281" t="n">
-        <v>2.47356104850769</v>
+        <v>2.47356081008911</v>
       </c>
       <c r="H281" t="n">
         <v>1069</v>
@@ -8605,7 +8605,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G284" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H284" t="n">
         <v>550</v>
@@ -8634,7 +8634,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G285" t="n">
-        <v>2.40822148323059</v>
+        <v>2.40822124481201</v>
       </c>
       <c r="H285" t="n">
         <v>437</v>
@@ -8663,7 +8663,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G286" t="n">
-        <v>2.40822148323059</v>
+        <v>2.40822124481201</v>
       </c>
       <c r="H286" t="n">
         <v>155</v>
@@ -8779,7 +8779,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G290" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H290" t="n">
         <v>3166</v>
@@ -8924,7 +8924,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G295" t="n">
-        <v>2.54823422431946</v>
+        <v>2.54823446273804</v>
       </c>
       <c r="H295" t="n">
         <v>1050</v>
@@ -9098,7 +9098,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G301" t="n">
-        <v>2.47356104850769</v>
+        <v>2.47356081008911</v>
       </c>
       <c r="H301" t="n">
         <v>9559</v>
@@ -9127,7 +9127,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G302" t="n">
-        <v>2.47356104850769</v>
+        <v>2.47356081008911</v>
       </c>
       <c r="H302" t="n">
         <v>2820</v>
@@ -9272,7 +9272,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G307" t="n">
-        <v>2.50156331062317</v>
+        <v>2.50156354904175</v>
       </c>
       <c r="H307" t="n">
         <v>7083</v>
@@ -9301,7 +9301,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G308" t="n">
-        <v>2.46422648429871</v>
+        <v>2.46422672271729</v>
       </c>
       <c r="H308" t="n">
         <v>982</v>
@@ -9359,7 +9359,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G310" t="n">
-        <v>2.47356104850769</v>
+        <v>2.47356081008911</v>
       </c>
       <c r="H310" t="n">
         <v>1449</v>
@@ -9446,7 +9446,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G313" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H313" t="n">
         <v>350</v>
@@ -9504,7 +9504,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G315" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H315" t="n">
         <v>500</v>
@@ -9533,7 +9533,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G316" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H316" t="n">
         <v>2033</v>
@@ -9620,7 +9620,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G319" t="n">
-        <v>2.40822148323059</v>
+        <v>2.40822124481201</v>
       </c>
       <c r="H319" t="n">
         <v>50</v>
@@ -9649,7 +9649,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G320" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H320" t="n">
         <v>110</v>
@@ -9678,7 +9678,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G321" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H321" t="n">
         <v>3920</v>
@@ -9765,7 +9765,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G324" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H324" t="n">
         <v>1280</v>
@@ -9794,7 +9794,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G325" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H327" t="n">
         <v>7005</v>
@@ -9910,7 +9910,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G329" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H329" t="n">
         <v>2690</v>
@@ -9939,7 +9939,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G330" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -9968,7 +9968,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G331" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -9997,7 +9997,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G332" t="n">
-        <v>2.27754282951355</v>
+        <v>2.27754259109497</v>
       </c>
       <c r="H332" t="n">
         <v>2310</v>
@@ -10113,7 +10113,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G336" t="n">
-        <v>2.26820850372314</v>
+        <v>2.26820874214172</v>
       </c>
       <c r="H336" t="n">
         <v>12996</v>
@@ -10171,7 +10171,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>2.1935350894928</v>
+        <v>2.19353485107422</v>
       </c>
       <c r="H338" t="n">
         <v>17797</v>
@@ -10200,7 +10200,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G339" t="n">
-        <v>2.12819576263428</v>
+        <v>2.1281955242157</v>
       </c>
       <c r="H339" t="n">
         <v>35672</v>
@@ -10229,7 +10229,7 @@
         <v>2.25</v>
       </c>
       <c r="G340" t="n">
-        <v>2.10019326210022</v>
+        <v>2.10019302368164</v>
       </c>
       <c r="H340" t="n">
         <v>17080</v>
@@ -10258,7 +10258,7 @@
         <v>2.25</v>
       </c>
       <c r="G341" t="n">
-        <v>2.10019326210022</v>
+        <v>2.10019302368164</v>
       </c>
       <c r="H341" t="n">
         <v>6035</v>
@@ -10287,7 +10287,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>2.06285643577576</v>
+        <v>2.06285619735718</v>
       </c>
       <c r="H342" t="n">
         <v>15756</v>
@@ -10316,7 +10316,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G343" t="n">
-        <v>1.98818302154541</v>
+        <v>1.98818278312683</v>
       </c>
       <c r="H343" t="n">
         <v>9524</v>
@@ -10345,7 +10345,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G344" t="n">
-        <v>1.9228435754776</v>
+        <v>1.92284333705902</v>
       </c>
       <c r="H344" t="n">
         <v>5020</v>
@@ -10374,7 +10374,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G345" t="n">
-        <v>1.87617254257202</v>
+        <v>1.87617242336273</v>
       </c>
       <c r="H345" t="n">
         <v>10119</v>
@@ -10548,7 +10548,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G351" t="n">
-        <v>1.57747852802277</v>
+        <v>1.57747828960419</v>
       </c>
       <c r="H351" t="n">
         <v>44141</v>
@@ -10577,7 +10577,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G352" t="n">
-        <v>1.53080725669861</v>
+        <v>1.5308073759079</v>
       </c>
       <c r="H352" t="n">
         <v>32342</v>
@@ -10606,7 +10606,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G353" t="n">
-        <v>1.50747179985046</v>
+        <v>1.50747191905975</v>
       </c>
       <c r="H353" t="n">
         <v>17138</v>
@@ -10780,7 +10780,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G359" t="n">
-        <v>1.5868124961853</v>
+        <v>1.58681261539459</v>
       </c>
       <c r="H359" t="n">
         <v>162717</v>
@@ -10809,7 +10809,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G360" t="n">
-        <v>1.54947566986084</v>
+        <v>1.54947578907013</v>
       </c>
       <c r="H360" t="n">
         <v>52791</v>
@@ -10896,7 +10896,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G363" t="n">
-        <v>1.84816992282867</v>
+        <v>1.84816980361938</v>
       </c>
       <c r="H363" t="n">
         <v>74595</v>
@@ -10954,7 +10954,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G365" t="n">
-        <v>1.94151163101196</v>
+        <v>1.94151175022125</v>
       </c>
       <c r="H365" t="n">
         <v>38866</v>
@@ -10983,7 +10983,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G366" t="n">
-        <v>2.02551937103271</v>
+        <v>2.02551984786987</v>
       </c>
       <c r="H366" t="n">
         <v>41167</v>
@@ -11012,7 +11012,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G367" t="n">
-        <v>2.06285643577576</v>
+        <v>2.06285619735718</v>
       </c>
       <c r="H367" t="n">
         <v>65581</v>
@@ -11041,7 +11041,7 @@
         <v>2.25</v>
       </c>
       <c r="G368" t="n">
-        <v>2.10019326210022</v>
+        <v>2.10019302368164</v>
       </c>
       <c r="H368" t="n">
         <v>40808</v>
@@ -11070,7 +11070,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G369" t="n">
-        <v>2.12819576263428</v>
+        <v>2.1281955242157</v>
       </c>
       <c r="H369" t="n">
         <v>27238</v>
@@ -11157,7 +11157,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G372" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H372" t="n">
         <v>100574</v>
@@ -11186,7 +11186,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G373" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H373" t="n">
         <v>50734</v>
@@ -11215,7 +11215,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G374" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H374" t="n">
         <v>32104</v>
@@ -11331,7 +11331,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G378" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H378" t="n">
         <v>48661</v>
@@ -11447,7 +11447,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G382" t="n">
-        <v>2.50156331062317</v>
+        <v>2.50156354904175</v>
       </c>
       <c r="H382" t="n">
         <v>22219</v>
@@ -11476,7 +11476,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G383" t="n">
-        <v>2.40822148323059</v>
+        <v>2.40822124481201</v>
       </c>
       <c r="H383" t="n">
         <v>19181</v>
@@ -11592,7 +11592,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G387" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H387" t="n">
         <v>20692</v>
@@ -11737,7 +11737,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G392" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H392" t="n">
         <v>78496</v>
@@ -11766,7 +11766,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G393" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H393" t="n">
         <v>2710</v>
@@ -11795,7 +11795,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G394" t="n">
-        <v>2.47356104850769</v>
+        <v>2.47356081008911</v>
       </c>
       <c r="H394" t="n">
         <v>21034</v>
@@ -11853,7 +11853,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G396" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H396" t="n">
         <v>3361</v>
@@ -11882,7 +11882,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G397" t="n">
-        <v>2.27754282951355</v>
+        <v>2.27754259109497</v>
       </c>
       <c r="H397" t="n">
         <v>70461</v>
@@ -11911,7 +11911,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H398" t="n">
         <v>4671</v>
@@ -11940,7 +11940,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G399" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H399" t="n">
         <v>20075</v>
@@ -11969,7 +11969,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G400" t="n">
-        <v>2.20286893844604</v>
+        <v>2.20286917686462</v>
       </c>
       <c r="H400" t="n">
         <v>35084</v>
@@ -11998,7 +11998,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G401" t="n">
-        <v>2.072190284729</v>
+        <v>2.07219052314758</v>
       </c>
       <c r="H401" t="n">
         <v>51398</v>
@@ -12027,7 +12027,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G402" t="n">
-        <v>2.21220326423645</v>
+        <v>2.21220350265503</v>
       </c>
       <c r="H402" t="n">
         <v>35407</v>
@@ -12114,7 +12114,7 @@
         <v>2.25</v>
       </c>
       <c r="G405" t="n">
-        <v>2.10019326210022</v>
+        <v>2.10019302368164</v>
       </c>
       <c r="H405" t="n">
         <v>50986</v>
@@ -12172,7 +12172,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G407" t="n">
-        <v>2.1935350894928</v>
+        <v>2.19353485107422</v>
       </c>
       <c r="H407" t="n">
         <v>30243</v>
@@ -12201,7 +12201,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G408" t="n">
-        <v>2.20286893844604</v>
+        <v>2.20286917686462</v>
       </c>
       <c r="H408" t="n">
         <v>20357</v>
@@ -12375,7 +12375,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G414" t="n">
-        <v>2.08152484893799</v>
+        <v>2.08152461051941</v>
       </c>
       <c r="H414" t="n">
         <v>6065</v>
@@ -12404,7 +12404,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G415" t="n">
-        <v>2.18420052528381</v>
+        <v>2.18420076370239</v>
       </c>
       <c r="H415" t="n">
         <v>21434</v>
@@ -12462,7 +12462,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G417" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H417" t="n">
         <v>112741</v>
@@ -12491,7 +12491,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G418" t="n">
-        <v>2.40822148323059</v>
+        <v>2.40822124481201</v>
       </c>
       <c r="H418" t="n">
         <v>31183</v>
@@ -12520,7 +12520,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G419" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H419" t="n">
         <v>24246</v>
@@ -12607,7 +12607,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G422" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H422" t="n">
         <v>15411</v>
@@ -12665,7 +12665,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G424" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H424" t="n">
         <v>4139</v>
@@ -12723,7 +12723,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G426" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H426" t="n">
         <v>6863</v>
@@ -12752,7 +12752,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G427" t="n">
-        <v>2.26820850372314</v>
+        <v>2.26820874214172</v>
       </c>
       <c r="H427" t="n">
         <v>8209</v>
@@ -12781,7 +12781,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G428" t="n">
-        <v>2.27754282951355</v>
+        <v>2.27754259109497</v>
       </c>
       <c r="H428" t="n">
         <v>8879</v>
@@ -12810,7 +12810,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G429" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H429" t="n">
         <v>17663</v>
@@ -12897,7 +12897,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G432" t="n">
-        <v>2.27754282951355</v>
+        <v>2.27754259109497</v>
       </c>
       <c r="H432" t="n">
         <v>5782</v>
@@ -13013,7 +13013,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G436" t="n">
-        <v>2.27754282951355</v>
+        <v>2.27754259109497</v>
       </c>
       <c r="H436" t="n">
         <v>3250</v>
@@ -13042,7 +13042,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G437" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H437" t="n">
         <v>10145</v>
@@ -13071,7 +13071,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G438" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H438" t="n">
         <v>40576</v>
@@ -13100,7 +13100,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G439" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H439" t="n">
         <v>6378</v>
@@ -13158,7 +13158,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G441" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H441" t="n">
         <v>4745</v>
@@ -13216,7 +13216,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G443" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H443" t="n">
         <v>10240</v>
@@ -13274,7 +13274,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G445" t="n">
-        <v>2.23087191581726</v>
+        <v>2.23087167739868</v>
       </c>
       <c r="H445" t="n">
         <v>29277</v>
@@ -13303,7 +13303,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G446" t="n">
-        <v>2.23087191581726</v>
+        <v>2.23087167739868</v>
       </c>
       <c r="H446" t="n">
         <v>37961</v>
@@ -13332,7 +13332,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G447" t="n">
-        <v>2.27754282951355</v>
+        <v>2.27754259109497</v>
       </c>
       <c r="H447" t="n">
         <v>53947</v>
@@ -13361,7 +13361,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G448" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H448" t="n">
         <v>75506</v>
@@ -13419,7 +13419,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G450" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H450" t="n">
         <v>45849</v>
@@ -13506,7 +13506,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G453" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H453" t="n">
         <v>35893</v>
@@ -13535,7 +13535,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G454" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H454" t="n">
         <v>25836</v>
@@ -13709,7 +13709,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G460" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H460" t="n">
         <v>44981</v>
@@ -13738,7 +13738,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G461" t="n">
-        <v>2.73491811752319</v>
+        <v>2.73491835594177</v>
       </c>
       <c r="H461" t="n">
         <v>18508</v>
@@ -13854,7 +13854,7 @@
         <v>3.25</v>
       </c>
       <c r="G465" t="n">
-        <v>3.03361201286316</v>
+        <v>3.03361225128174</v>
       </c>
       <c r="H465" t="n">
         <v>83242</v>
@@ -13912,7 +13912,7 @@
         <v>3.25</v>
       </c>
       <c r="G467" t="n">
-        <v>3.03361201286316</v>
+        <v>3.03361225128174</v>
       </c>
       <c r="H467" t="n">
         <v>62595</v>
@@ -13941,7 +13941,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G468" t="n">
-        <v>3.08028292655945</v>
+        <v>3.08028316497803</v>
       </c>
       <c r="H468" t="n">
         <v>39566</v>
@@ -13970,7 +13970,7 @@
         <v>3.25</v>
       </c>
       <c r="G469" t="n">
-        <v>3.03361201286316</v>
+        <v>3.03361225128174</v>
       </c>
       <c r="H469" t="n">
         <v>22979</v>
@@ -13999,7 +13999,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G470" t="n">
-        <v>3.35097479820251</v>
+        <v>3.35097455978394</v>
       </c>
       <c r="H470" t="n">
         <v>111507</v>
@@ -14028,7 +14028,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G471" t="n">
-        <v>3.27630114555359</v>
+        <v>3.27630138397217</v>
       </c>
       <c r="H471" t="n">
         <v>27454</v>
@@ -14086,7 +14086,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G473" t="n">
-        <v>3.33230638504028</v>
+        <v>3.3323061466217</v>
       </c>
       <c r="H473" t="n">
         <v>14421</v>
@@ -14173,7 +14173,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>3.17362499237061</v>
+        <v>3.17362523078918</v>
       </c>
       <c r="H476" t="n">
         <v>25140</v>
@@ -14202,7 +14202,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G477" t="n">
-        <v>3.11761999130249</v>
+        <v>3.11761975288391</v>
       </c>
       <c r="H477" t="n">
         <v>29958</v>
@@ -14289,7 +14289,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G480" t="n">
-        <v>3.20162796974182</v>
+        <v>3.20162773132324</v>
       </c>
       <c r="H480" t="n">
         <v>55118</v>
@@ -14318,7 +14318,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G481" t="n">
-        <v>3.14562225341797</v>
+        <v>3.14562249183655</v>
       </c>
       <c r="H481" t="n">
         <v>17292</v>
@@ -14434,7 +14434,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G485" t="n">
-        <v>3.15495705604553</v>
+        <v>3.15495657920837</v>
       </c>
       <c r="H485" t="n">
         <v>12813</v>
@@ -14463,7 +14463,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G486" t="n">
-        <v>3.17362499237061</v>
+        <v>3.17362523078918</v>
       </c>
       <c r="H486" t="n">
         <v>33087</v>
@@ -14550,7 +14550,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G489" t="n">
-        <v>3.11761999130249</v>
+        <v>3.11761975288391</v>
       </c>
       <c r="H489" t="n">
         <v>17075</v>
@@ -14579,7 +14579,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G490" t="n">
-        <v>3.08028292655945</v>
+        <v>3.08028316497803</v>
       </c>
       <c r="H490" t="n">
         <v>17126</v>
@@ -14637,7 +14637,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G492" t="n">
-        <v>2.97760725021362</v>
+        <v>2.97760701179504</v>
       </c>
       <c r="H492" t="n">
         <v>12648</v>
@@ -14753,7 +14753,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G496" t="n">
-        <v>3.08028292655945</v>
+        <v>3.08028316497803</v>
       </c>
       <c r="H496" t="n">
         <v>39248</v>
@@ -14782,7 +14782,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G497" t="n">
-        <v>3.08028292655945</v>
+        <v>3.08028316497803</v>
       </c>
       <c r="H497" t="n">
         <v>17788</v>
@@ -14840,7 +14840,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G499" t="n">
-        <v>3.11761999130249</v>
+        <v>3.11761975288391</v>
       </c>
       <c r="H499" t="n">
         <v>21907</v>
@@ -14869,7 +14869,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G500" t="n">
-        <v>3.11761999130249</v>
+        <v>3.11761975288391</v>
       </c>
       <c r="H500" t="n">
         <v>17501</v>
@@ -14898,7 +14898,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G501" t="n">
-        <v>3.06161451339722</v>
+        <v>3.0616147518158</v>
       </c>
       <c r="H501" t="n">
         <v>13910</v>
@@ -14927,7 +14927,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G502" t="n">
-        <v>3.09895133972168</v>
+        <v>3.09895157814026</v>
       </c>
       <c r="H502" t="n">
         <v>27956</v>
@@ -14956,7 +14956,7 @@
         <v>3.25</v>
       </c>
       <c r="G503" t="n">
-        <v>3.03361201286316</v>
+        <v>3.03361225128174</v>
       </c>
       <c r="H503" t="n">
         <v>5248</v>
@@ -14985,7 +14985,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G504" t="n">
-        <v>3.02427816390991</v>
+        <v>3.02427792549133</v>
       </c>
       <c r="H504" t="n">
         <v>20370</v>
@@ -15014,7 +15014,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G505" t="n">
-        <v>3.00560975074768</v>
+        <v>3.0056095123291</v>
       </c>
       <c r="H505" t="n">
         <v>10540</v>
@@ -15043,7 +15043,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G506" t="n">
-        <v>2.95893883705139</v>
+        <v>2.95893859863281</v>
       </c>
       <c r="H506" t="n">
         <v>1755</v>
@@ -15159,7 +15159,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G510" t="n">
-        <v>3.00560975074768</v>
+        <v>3.0056095123291</v>
       </c>
       <c r="H510" t="n">
         <v>10066</v>
@@ -15217,7 +15217,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G512" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H512" t="n">
         <v>87951</v>
@@ -15391,7 +15391,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G518" t="n">
-        <v>2.73491811752319</v>
+        <v>2.73491835594177</v>
       </c>
       <c r="H518" t="n">
         <v>15415</v>
@@ -15507,7 +15507,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G522" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H522" t="n">
         <v>18120</v>
@@ -15565,7 +15565,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G524" t="n">
-        <v>2.63224196434021</v>
+        <v>2.63224172592163</v>
       </c>
       <c r="H524" t="n">
         <v>10487</v>
@@ -15710,7 +15710,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G529" t="n">
-        <v>2.46422648429871</v>
+        <v>2.46422672271729</v>
       </c>
       <c r="H529" t="n">
         <v>31873</v>
@@ -15768,7 +15768,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G531" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H531" t="n">
         <v>29110</v>
@@ -15797,7 +15797,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G532" t="n">
-        <v>2.46422648429871</v>
+        <v>2.46422672271729</v>
       </c>
       <c r="H532" t="n">
         <v>14070</v>
@@ -15855,7 +15855,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G534" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H534" t="n">
         <v>58949</v>
@@ -15884,7 +15884,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G535" t="n">
-        <v>2.53890037536621</v>
+        <v>2.53890013694763</v>
       </c>
       <c r="H535" t="n">
         <v>31474</v>
@@ -16058,7 +16058,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G541" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H541" t="n">
         <v>13315</v>
@@ -16116,7 +16116,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G543" t="n">
-        <v>2.63224196434021</v>
+        <v>2.63224172592163</v>
       </c>
       <c r="H543" t="n">
         <v>7927</v>
@@ -16145,7 +16145,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G544" t="n">
-        <v>2.54823422431946</v>
+        <v>2.54823446273804</v>
       </c>
       <c r="H544" t="n">
         <v>22371</v>
@@ -16290,7 +16290,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G549" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H549" t="n">
         <v>9940</v>
@@ -16493,7 +16493,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G556" t="n">
-        <v>2.77225494384766</v>
+        <v>2.77225470542908</v>
       </c>
       <c r="H556" t="n">
         <v>1552</v>
@@ -16522,7 +16522,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G557" t="n">
-        <v>2.77225494384766</v>
+        <v>2.77225470542908</v>
       </c>
       <c r="H557" t="n">
         <v>7892</v>
@@ -16638,7 +16638,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G561" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H561" t="n">
         <v>55511</v>
@@ -16899,7 +16899,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G570" t="n">
-        <v>2.77225494384766</v>
+        <v>2.77225470542908</v>
       </c>
       <c r="H570" t="n">
         <v>12140</v>
@@ -17102,7 +17102,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G577" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H577" t="n">
         <v>5655</v>
@@ -17218,7 +17218,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G581" t="n">
-        <v>2.77225494384766</v>
+        <v>2.77225470542908</v>
       </c>
       <c r="H581" t="n">
         <v>1650</v>
@@ -17276,7 +17276,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G583" t="n">
-        <v>2.76292061805725</v>
+        <v>2.76292037963867</v>
       </c>
       <c r="H583" t="n">
         <v>1500</v>
@@ -17450,7 +17450,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G589" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H589" t="n">
         <v>5281</v>
@@ -17508,7 +17508,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G591" t="n">
-        <v>2.77225494384766</v>
+        <v>2.77225470542908</v>
       </c>
       <c r="H591" t="n">
         <v>2450</v>
@@ -17537,7 +17537,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G592" t="n">
-        <v>2.77225494384766</v>
+        <v>2.77225470542908</v>
       </c>
       <c r="H592" t="n">
         <v>0</v>
@@ -17595,7 +17595,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G594" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H594" t="n">
         <v>3352</v>
@@ -17653,7 +17653,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G596" t="n">
-        <v>2.77225494384766</v>
+        <v>2.77225470542908</v>
       </c>
       <c r="H596" t="n">
         <v>850</v>
@@ -17798,7 +17798,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G601" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H601" t="n">
         <v>11543</v>
@@ -17827,7 +17827,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G602" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H602" t="n">
         <v>22041</v>
@@ -17856,7 +17856,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G603" t="n">
-        <v>2.73491811752319</v>
+        <v>2.73491835594177</v>
       </c>
       <c r="H603" t="n">
         <v>6297</v>
@@ -17885,7 +17885,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G604" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H604" t="n">
         <v>5168</v>
@@ -17943,7 +17943,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H606" t="n">
         <v>1325</v>
@@ -18030,7 +18030,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G609" t="n">
-        <v>2.76292061805725</v>
+        <v>2.76292037963867</v>
       </c>
       <c r="H609" t="n">
         <v>13444</v>
@@ -18059,7 +18059,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G610" t="n">
-        <v>2.77225494384766</v>
+        <v>2.77225470542908</v>
       </c>
       <c r="H610" t="n">
         <v>4440</v>
@@ -18175,7 +18175,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G614" t="n">
-        <v>2.77225494384766</v>
+        <v>2.77225470542908</v>
       </c>
       <c r="H614" t="n">
         <v>20031</v>
@@ -18465,7 +18465,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G624" t="n">
-        <v>2.47356104850769</v>
+        <v>2.47356081008911</v>
       </c>
       <c r="H624" t="n">
         <v>17921</v>
@@ -18523,7 +18523,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G626" t="n">
-        <v>2.50156331062317</v>
+        <v>2.50156354904175</v>
       </c>
       <c r="H626" t="n">
         <v>7546</v>
@@ -18581,7 +18581,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G628" t="n">
-        <v>2.47356104850769</v>
+        <v>2.47356081008911</v>
       </c>
       <c r="H628" t="n">
         <v>7127</v>
@@ -18610,7 +18610,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G629" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H629" t="n">
         <v>9381</v>
@@ -18755,7 +18755,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G634" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H634" t="n">
         <v>2551</v>
@@ -18842,7 +18842,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G637" t="n">
-        <v>2.53890037536621</v>
+        <v>2.53890013694763</v>
       </c>
       <c r="H637" t="n">
         <v>7036</v>
@@ -18900,7 +18900,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G639" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H639" t="n">
         <v>850</v>
@@ -18987,7 +18987,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G642" t="n">
-        <v>2.47356104850769</v>
+        <v>2.47356081008911</v>
       </c>
       <c r="H642" t="n">
         <v>25000</v>
@@ -19045,7 +19045,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G644" t="n">
-        <v>2.50156331062317</v>
+        <v>2.50156354904175</v>
       </c>
       <c r="H644" t="n">
         <v>7248</v>
@@ -19074,7 +19074,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G645" t="n">
-        <v>2.40822148323059</v>
+        <v>2.40822124481201</v>
       </c>
       <c r="H645" t="n">
         <v>26536</v>
@@ -19161,7 +19161,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G648" t="n">
-        <v>2.53890037536621</v>
+        <v>2.53890013694763</v>
       </c>
       <c r="H648" t="n">
         <v>20795</v>
@@ -19190,7 +19190,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G649" t="n">
-        <v>2.53890037536621</v>
+        <v>2.53890013694763</v>
       </c>
       <c r="H649" t="n">
         <v>26026</v>
@@ -19248,7 +19248,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G651" t="n">
-        <v>2.54823422431946</v>
+        <v>2.54823446273804</v>
       </c>
       <c r="H651" t="n">
         <v>1402</v>
@@ -19335,7 +19335,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G654" t="n">
-        <v>2.50156331062317</v>
+        <v>2.50156354904175</v>
       </c>
       <c r="H654" t="n">
         <v>2900</v>
@@ -19364,7 +19364,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G655" t="n">
-        <v>2.47356104850769</v>
+        <v>2.47356081008911</v>
       </c>
       <c r="H655" t="n">
         <v>1680</v>
@@ -19422,7 +19422,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G657" t="n">
-        <v>2.53890037536621</v>
+        <v>2.53890013694763</v>
       </c>
       <c r="H657" t="n">
         <v>8536</v>
@@ -19567,7 +19567,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G662" t="n">
-        <v>2.53890037536621</v>
+        <v>2.53890013694763</v>
       </c>
       <c r="H662" t="n">
         <v>18926</v>
@@ -19799,7 +19799,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G670" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H670" t="n">
         <v>7574</v>
@@ -20002,7 +20002,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G677" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H677" t="n">
         <v>2850</v>
@@ -20060,7 +20060,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G679" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H679" t="n">
         <v>6131</v>
@@ -20118,7 +20118,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G681" t="n">
-        <v>2.53890037536621</v>
+        <v>2.53890013694763</v>
       </c>
       <c r="H681" t="n">
         <v>1200</v>
@@ -20321,7 +20321,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G688" t="n">
-        <v>2.50156331062317</v>
+        <v>2.50156354904175</v>
       </c>
       <c r="H688" t="n">
         <v>5477</v>
@@ -20350,7 +20350,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G689" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H689" t="n">
         <v>6459</v>
@@ -20466,7 +20466,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G693" t="n">
-        <v>2.14686417579651</v>
+        <v>2.14686393737793</v>
       </c>
       <c r="H693" t="n">
         <v>5992</v>
@@ -20495,7 +20495,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G694" t="n">
-        <v>2.21220326423645</v>
+        <v>2.21220350265503</v>
       </c>
       <c r="H694" t="n">
         <v>6060</v>
@@ -20524,7 +20524,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G695" t="n">
-        <v>2.23087191581726</v>
+        <v>2.23087167739868</v>
       </c>
       <c r="H695" t="n">
         <v>25461</v>
@@ -20582,7 +20582,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G697" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H697" t="n">
         <v>5477</v>
@@ -20611,7 +20611,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G698" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H698" t="n">
         <v>4617</v>
@@ -20669,7 +20669,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G700" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H700" t="n">
         <v>10078</v>
@@ -20698,7 +20698,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G701" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H701" t="n">
         <v>11679</v>
@@ -20727,7 +20727,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G702" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H702" t="n">
         <v>12282</v>
@@ -20814,7 +20814,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G705" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H705" t="n">
         <v>7231</v>
@@ -20843,7 +20843,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G706" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H706" t="n">
         <v>16794</v>
@@ -20901,7 +20901,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G708" t="n">
-        <v>2.40822148323059</v>
+        <v>2.40822124481201</v>
       </c>
       <c r="H708" t="n">
         <v>11650</v>
@@ -21075,7 +21075,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G714" t="n">
-        <v>2.40822148323059</v>
+        <v>2.40822124481201</v>
       </c>
       <c r="H714" t="n">
         <v>3865</v>
@@ -21249,7 +21249,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G720" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H720" t="n">
         <v>2110</v>
@@ -21307,7 +21307,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G722" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H722" t="n">
         <v>20</v>
@@ -21365,7 +21365,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G724" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H724" t="n">
         <v>3000</v>
@@ -21394,7 +21394,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G725" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H725" t="n">
         <v>2583</v>
@@ -21423,7 +21423,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G726" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H726" t="n">
         <v>2</v>
@@ -21452,7 +21452,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G727" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H727" t="n">
         <v>4770</v>
@@ -21481,7 +21481,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G728" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H728" t="n">
         <v>6795</v>
@@ -21539,7 +21539,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G730" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H730" t="n">
         <v>9829</v>
@@ -21742,7 +21742,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G737" t="n">
-        <v>2.21220326423645</v>
+        <v>2.21220350265503</v>
       </c>
       <c r="H737" t="n">
         <v>4770</v>
@@ -21771,7 +21771,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G738" t="n">
-        <v>2.18420052528381</v>
+        <v>2.18420076370239</v>
       </c>
       <c r="H738" t="n">
         <v>10750</v>
@@ -21800,7 +21800,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G739" t="n">
-        <v>2.23087191581726</v>
+        <v>2.23087167739868</v>
       </c>
       <c r="H739" t="n">
         <v>4337</v>
@@ -21829,7 +21829,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G740" t="n">
-        <v>2.1935350894928</v>
+        <v>2.19353485107422</v>
       </c>
       <c r="H740" t="n">
         <v>5880</v>
@@ -21887,7 +21887,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G742" t="n">
-        <v>2.23087191581726</v>
+        <v>2.23087167739868</v>
       </c>
       <c r="H742" t="n">
         <v>6415</v>
@@ -21974,7 +21974,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G745" t="n">
-        <v>2.20286893844604</v>
+        <v>2.20286917686462</v>
       </c>
       <c r="H745" t="n">
         <v>3400</v>
@@ -22003,7 +22003,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G746" t="n">
-        <v>2.14686417579651</v>
+        <v>2.14686393737793</v>
       </c>
       <c r="H746" t="n">
         <v>11917</v>
@@ -22061,7 +22061,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G748" t="n">
-        <v>2.12819576263428</v>
+        <v>2.1281955242157</v>
       </c>
       <c r="H748" t="n">
         <v>9244</v>
@@ -22090,7 +22090,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G749" t="n">
-        <v>2.12819576263428</v>
+        <v>2.1281955242157</v>
       </c>
       <c r="H749" t="n">
         <v>2187</v>
@@ -22148,7 +22148,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G751" t="n">
-        <v>2.14686417579651</v>
+        <v>2.14686393737793</v>
       </c>
       <c r="H751" t="n">
         <v>4774</v>
@@ -22177,7 +22177,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G752" t="n">
-        <v>2.14686417579651</v>
+        <v>2.14686393737793</v>
       </c>
       <c r="H752" t="n">
         <v>0</v>
@@ -22206,7 +22206,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G753" t="n">
-        <v>2.14686417579651</v>
+        <v>2.14686393737793</v>
       </c>
       <c r="H753" t="n">
         <v>1518</v>
@@ -22264,7 +22264,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G755" t="n">
-        <v>2.11886119842529</v>
+        <v>2.11886143684387</v>
       </c>
       <c r="H755" t="n">
         <v>2015</v>
@@ -22293,7 +22293,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G756" t="n">
-        <v>2.13752961158752</v>
+        <v>2.1375298500061</v>
       </c>
       <c r="H756" t="n">
         <v>759</v>
@@ -22322,7 +22322,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G757" t="n">
-        <v>2.15619802474976</v>
+        <v>2.15619826316833</v>
       </c>
       <c r="H757" t="n">
         <v>5</v>
@@ -22380,7 +22380,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G759" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H759" t="n">
         <v>6674</v>
@@ -22409,7 +22409,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G760" t="n">
-        <v>2.15619802474976</v>
+        <v>2.15619826316833</v>
       </c>
       <c r="H760" t="n">
         <v>9288</v>
@@ -22438,7 +22438,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G761" t="n">
-        <v>2.11886119842529</v>
+        <v>2.11886143684387</v>
       </c>
       <c r="H761" t="n">
         <v>3433</v>
@@ -22496,7 +22496,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G763" t="n">
-        <v>2.15619802474976</v>
+        <v>2.15619826316833</v>
       </c>
       <c r="H763" t="n">
         <v>74</v>
@@ -22583,7 +22583,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G766" t="n">
-        <v>2.11886119842529</v>
+        <v>2.11886143684387</v>
       </c>
       <c r="H766" t="n">
         <v>155</v>
@@ -22612,7 +22612,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G767" t="n">
-        <v>2.14686417579651</v>
+        <v>2.14686393737793</v>
       </c>
       <c r="H767" t="n">
         <v>1300</v>
@@ -22641,7 +22641,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G768" t="n">
-        <v>2.14686417579651</v>
+        <v>2.14686393737793</v>
       </c>
       <c r="H768" t="n">
         <v>0</v>
@@ -22670,7 +22670,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G769" t="n">
-        <v>2.08152484893799</v>
+        <v>2.08152461051941</v>
       </c>
       <c r="H769" t="n">
         <v>5355</v>
@@ -22699,7 +22699,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G770" t="n">
-        <v>2.08152484893799</v>
+        <v>2.08152461051941</v>
       </c>
       <c r="H770" t="n">
         <v>0</v>
@@ -22786,7 +22786,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G773" t="n">
-        <v>2.1935350894928</v>
+        <v>2.19353485107422</v>
       </c>
       <c r="H773" t="n">
         <v>499</v>
@@ -22815,7 +22815,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G774" t="n">
-        <v>2.14686417579651</v>
+        <v>2.14686393737793</v>
       </c>
       <c r="H774" t="n">
         <v>1537</v>
@@ -22873,7 +22873,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G776" t="n">
-        <v>2.14686417579651</v>
+        <v>2.14686393737793</v>
       </c>
       <c r="H776" t="n">
         <v>8020</v>
@@ -22902,7 +22902,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G777" t="n">
-        <v>2.00685095787048</v>
+        <v>2.00685143470764</v>
       </c>
       <c r="H777" t="n">
         <v>6782</v>
@@ -22989,7 +22989,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G780" t="n">
-        <v>1.99751710891724</v>
+        <v>1.99751698970795</v>
       </c>
       <c r="H780" t="n">
         <v>923</v>
@@ -23018,7 +23018,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G781" t="n">
-        <v>2.02551937103271</v>
+        <v>2.02551984786987</v>
       </c>
       <c r="H781" t="n">
         <v>2701</v>
@@ -23076,7 +23076,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G783" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417516231537</v>
       </c>
       <c r="H783" t="n">
         <v>16989</v>
@@ -23221,7 +23221,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G788" t="n">
-        <v>1.76882922649384</v>
+        <v>1.76882934570312</v>
       </c>
       <c r="H788" t="n">
         <v>25213</v>
@@ -23366,7 +23366,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G793" t="n">
-        <v>1.79216468334198</v>
+        <v>1.79216480255127</v>
       </c>
       <c r="H793" t="n">
         <v>26069</v>
@@ -23395,7 +23395,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G794" t="n">
-        <v>1.87617254257202</v>
+        <v>1.87617242336273</v>
       </c>
       <c r="H794" t="n">
         <v>9697</v>
@@ -23424,7 +23424,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G795" t="n">
-        <v>1.84816992282867</v>
+        <v>1.84816980361938</v>
       </c>
       <c r="H795" t="n">
         <v>1870</v>
@@ -23569,7 +23569,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G800" t="n">
-        <v>1.82016742229462</v>
+        <v>1.82016730308533</v>
       </c>
       <c r="H800" t="n">
         <v>293</v>
@@ -23743,7 +23743,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417516231537</v>
       </c>
       <c r="H806" t="n">
         <v>2225</v>
@@ -23772,7 +23772,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G807" t="n">
-        <v>1.88550662994385</v>
+        <v>1.88550674915314</v>
       </c>
       <c r="H807" t="n">
         <v>530</v>
@@ -23859,7 +23859,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G810" t="n">
-        <v>1.83883559703827</v>
+        <v>1.83883571624756</v>
       </c>
       <c r="H810" t="n">
         <v>2520</v>
@@ -23888,7 +23888,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G811" t="n">
-        <v>1.83883559703827</v>
+        <v>1.83883571624756</v>
       </c>
       <c r="H811" t="n">
         <v>626</v>
@@ -23975,7 +23975,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G814" t="n">
-        <v>1.98818302154541</v>
+        <v>1.98818278312683</v>
       </c>
       <c r="H814" t="n">
         <v>5130</v>
@@ -24004,7 +24004,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G815" t="n">
-        <v>1.98818302154541</v>
+        <v>1.98818278312683</v>
       </c>
       <c r="H815" t="n">
         <v>13633</v>
@@ -24033,7 +24033,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G816" t="n">
-        <v>1.97884833812714</v>
+        <v>1.978848695755</v>
       </c>
       <c r="H816" t="n">
         <v>18908</v>
@@ -24091,7 +24091,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G818" t="n">
-        <v>1.9228435754776</v>
+        <v>1.92284333705902</v>
       </c>
       <c r="H818" t="n">
         <v>3832</v>
@@ -24120,7 +24120,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G819" t="n">
-        <v>1.94151163101196</v>
+        <v>1.94151175022125</v>
       </c>
       <c r="H819" t="n">
         <v>4235</v>
@@ -24236,7 +24236,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G823" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417516231537</v>
       </c>
       <c r="H823" t="n">
         <v>2258</v>
@@ -24265,7 +24265,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G824" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417516231537</v>
       </c>
       <c r="H824" t="n">
         <v>0</v>
@@ -24323,7 +24323,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G826" t="n">
-        <v>2.02551937103271</v>
+        <v>2.02551984786987</v>
       </c>
       <c r="H826" t="n">
         <v>12498</v>
@@ -24352,7 +24352,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G827" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417516231537</v>
       </c>
       <c r="H827" t="n">
         <v>15383</v>
@@ -24381,7 +24381,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G828" t="n">
-        <v>1.88550662994385</v>
+        <v>1.88550674915314</v>
       </c>
       <c r="H828" t="n">
         <v>2410</v>
@@ -24410,7 +24410,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G829" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417516231537</v>
       </c>
       <c r="H829" t="n">
         <v>4980</v>
@@ -24468,7 +24468,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G831" t="n">
-        <v>1.84816992282867</v>
+        <v>1.84816980361938</v>
       </c>
       <c r="H831" t="n">
         <v>1282</v>
@@ -24526,7 +24526,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G833" t="n">
-        <v>1.88550662994385</v>
+        <v>1.88550674915314</v>
       </c>
       <c r="H833" t="n">
         <v>500</v>
@@ -24671,7 +24671,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G838" t="n">
-        <v>1.82016742229462</v>
+        <v>1.82016730308533</v>
       </c>
       <c r="H838" t="n">
         <v>2308</v>
@@ -24787,7 +24787,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G842" t="n">
-        <v>1.79216468334198</v>
+        <v>1.79216480255127</v>
       </c>
       <c r="H842" t="n">
         <v>5998</v>
@@ -24845,7 +24845,7 @@
         <v>1.875</v>
       </c>
       <c r="G844" t="n">
-        <v>1.75016093254089</v>
+        <v>1.7501608133316</v>
       </c>
       <c r="H844" t="n">
         <v>17976</v>
@@ -25048,7 +25048,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G851" t="n">
-        <v>1.79216468334198</v>
+        <v>1.79216480255127</v>
       </c>
       <c r="H851" t="n">
         <v>8829</v>
@@ -25106,7 +25106,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G853" t="n">
-        <v>1.82016742229462</v>
+        <v>1.82016730308533</v>
       </c>
       <c r="H853" t="n">
         <v>4615</v>
@@ -25135,7 +25135,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G854" t="n">
-        <v>1.9228435754776</v>
+        <v>1.92284333705902</v>
       </c>
       <c r="H854" t="n">
         <v>3818</v>
@@ -25222,7 +25222,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G857" t="n">
-        <v>1.9228435754776</v>
+        <v>1.92284333705902</v>
       </c>
       <c r="H857" t="n">
         <v>1847</v>
@@ -25251,7 +25251,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G858" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417516231537</v>
       </c>
       <c r="H858" t="n">
         <v>1659</v>
@@ -25280,7 +25280,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G859" t="n">
-        <v>1.87617254257202</v>
+        <v>1.87617242336273</v>
       </c>
       <c r="H859" t="n">
         <v>1005</v>
@@ -25309,7 +25309,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G860" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417516231537</v>
       </c>
       <c r="H860" t="n">
         <v>5149</v>
@@ -25425,7 +25425,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G864" t="n">
-        <v>1.84816992282867</v>
+        <v>1.84816980361938</v>
       </c>
       <c r="H864" t="n">
         <v>1500</v>
@@ -25570,7 +25570,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G869" t="n">
-        <v>1.88550662994385</v>
+        <v>1.88550674915314</v>
       </c>
       <c r="H869" t="n">
         <v>4311</v>
@@ -25599,7 +25599,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G870" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417516231537</v>
       </c>
       <c r="H870" t="n">
         <v>5440</v>
@@ -25628,7 +25628,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G871" t="n">
-        <v>1.94151163101196</v>
+        <v>1.94151175022125</v>
       </c>
       <c r="H871" t="n">
         <v>830</v>
@@ -25657,7 +25657,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G872" t="n">
-        <v>1.9228435754776</v>
+        <v>1.92284333705902</v>
       </c>
       <c r="H872" t="n">
         <v>1350</v>
@@ -25744,7 +25744,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G875" t="n">
-        <v>1.88550662994385</v>
+        <v>1.88550674915314</v>
       </c>
       <c r="H875" t="n">
         <v>7617</v>
@@ -25802,7 +25802,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G877" t="n">
-        <v>1.9228435754776</v>
+        <v>1.92284333705902</v>
       </c>
       <c r="H877" t="n">
         <v>1605</v>
@@ -25831,7 +25831,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G878" t="n">
-        <v>1.9228435754776</v>
+        <v>1.92284333705902</v>
       </c>
       <c r="H878" t="n">
         <v>4340</v>
@@ -25947,7 +25947,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G882" t="n">
-        <v>1.94151163101196</v>
+        <v>1.94151175022125</v>
       </c>
       <c r="H882" t="n">
         <v>5000</v>
@@ -25976,7 +25976,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G883" t="n">
-        <v>1.94151163101196</v>
+        <v>1.94151175022125</v>
       </c>
       <c r="H883" t="n">
         <v>1500</v>
@@ -26034,7 +26034,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417516231537</v>
       </c>
       <c r="H885" t="n">
         <v>6104</v>
@@ -26092,7 +26092,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G887" t="n">
-        <v>1.94151163101196</v>
+        <v>1.94151175022125</v>
       </c>
       <c r="H887" t="n">
         <v>3600</v>
@@ -26121,7 +26121,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G888" t="n">
-        <v>1.94151163101196</v>
+        <v>1.94151175022125</v>
       </c>
       <c r="H888" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G891" t="n">
-        <v>1.94151163101196</v>
+        <v>1.94151175022125</v>
       </c>
       <c r="H891" t="n">
         <v>3305</v>
@@ -26266,7 +26266,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G893" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417516231537</v>
       </c>
       <c r="H893" t="n">
         <v>2300</v>
@@ -26324,7 +26324,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G895" t="n">
-        <v>1.9228435754776</v>
+        <v>1.92284333705902</v>
       </c>
       <c r="H895" t="n">
         <v>1000</v>
@@ -26411,7 +26411,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G898" t="n">
-        <v>2.20286893844604</v>
+        <v>2.20286917686462</v>
       </c>
       <c r="H898" t="n">
         <v>36211</v>
@@ -26440,7 +26440,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G899" t="n">
-        <v>2.21220326423645</v>
+        <v>2.21220350265503</v>
       </c>
       <c r="H899" t="n">
         <v>23208</v>
@@ -26469,7 +26469,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G900" t="n">
-        <v>2.23087191581726</v>
+        <v>2.23087167739868</v>
       </c>
       <c r="H900" t="n">
         <v>18041</v>
@@ -26527,7 +26527,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G902" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H902" t="n">
         <v>9996</v>
@@ -26556,7 +26556,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G903" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H903" t="n">
         <v>12989</v>
@@ -26614,7 +26614,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G905" t="n">
-        <v>2.23087191581726</v>
+        <v>2.23087167739868</v>
       </c>
       <c r="H905" t="n">
         <v>12451</v>
@@ -26643,7 +26643,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G906" t="n">
-        <v>2.23087191581726</v>
+        <v>2.23087167739868</v>
       </c>
       <c r="H906" t="n">
         <v>1897</v>
@@ -26701,7 +26701,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G908" t="n">
-        <v>2.23087191581726</v>
+        <v>2.23087167739868</v>
       </c>
       <c r="H908" t="n">
         <v>1500</v>
@@ -26730,7 +26730,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G909" t="n">
-        <v>2.27754282951355</v>
+        <v>2.27754259109497</v>
       </c>
       <c r="H909" t="n">
         <v>4836</v>
@@ -26759,7 +26759,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G910" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H910" t="n">
         <v>2850</v>
@@ -26962,7 +26962,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G917" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H917" t="n">
         <v>3029</v>
@@ -27020,7 +27020,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G919" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H919" t="n">
         <v>3027</v>
@@ -27078,7 +27078,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G921" t="n">
-        <v>2.40822148323059</v>
+        <v>2.40822124481201</v>
       </c>
       <c r="H921" t="n">
         <v>2800</v>
@@ -27107,7 +27107,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G922" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H922" t="n">
         <v>2840</v>
@@ -27136,7 +27136,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G923" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H923" t="n">
         <v>2275</v>
@@ -27165,7 +27165,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G924" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H924" t="n">
         <v>2811</v>
@@ -27194,7 +27194,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G925" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H925" t="n">
         <v>10000</v>
@@ -27339,7 +27339,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G930" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H930" t="n">
         <v>2560</v>
@@ -27455,7 +27455,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G934" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H934" t="n">
         <v>18035</v>
@@ -27484,7 +27484,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G935" t="n">
-        <v>2.21220326423645</v>
+        <v>2.21220350265503</v>
       </c>
       <c r="H935" t="n">
         <v>17142</v>
@@ -27513,7 +27513,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G936" t="n">
-        <v>2.20286893844604</v>
+        <v>2.20286917686462</v>
       </c>
       <c r="H936" t="n">
         <v>6398</v>
@@ -27571,7 +27571,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G938" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H938" t="n">
         <v>36604</v>
@@ -27600,7 +27600,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G939" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H939" t="n">
         <v>14446</v>
@@ -27687,7 +27687,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G942" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H942" t="n">
         <v>24000</v>
@@ -27716,7 +27716,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G943" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H943" t="n">
         <v>10884</v>
@@ -27861,7 +27861,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G948" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H948" t="n">
         <v>2000</v>
@@ -27919,7 +27919,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G950" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H950" t="n">
         <v>2715</v>
@@ -27948,7 +27948,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G951" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H951" t="n">
         <v>3000</v>
@@ -28093,7 +28093,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G956" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H956" t="n">
         <v>4601</v>
@@ -28209,7 +28209,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G960" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H960" t="n">
         <v>8263</v>
@@ -28267,7 +28267,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G962" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H962" t="n">
         <v>1000</v>
@@ -28354,7 +28354,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G965" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H965" t="n">
         <v>21</v>
@@ -28383,7 +28383,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G966" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H966" t="n">
         <v>6028</v>
@@ -28644,7 +28644,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G975" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H975" t="n">
         <v>5517</v>
@@ -28702,7 +28702,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G977" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H977" t="n">
         <v>2500</v>
@@ -28731,7 +28731,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G978" t="n">
-        <v>2.40822148323059</v>
+        <v>2.40822124481201</v>
       </c>
       <c r="H978" t="n">
         <v>4636</v>
@@ -29427,7 +29427,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1002" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H1002" t="n">
         <v>3900</v>
@@ -29514,7 +29514,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1005" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H1005" t="n">
         <v>642</v>
@@ -29543,7 +29543,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.40822148323059</v>
+        <v>2.40822124481201</v>
       </c>
       <c r="H1006" t="n">
         <v>2020</v>
@@ -29630,7 +29630,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1009" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H1009" t="n">
         <v>1826</v>
@@ -29688,7 +29688,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1011" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H1011" t="n">
         <v>3388</v>
@@ -29978,7 +29978,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1021" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H1021" t="n">
         <v>942</v>
@@ -30065,7 +30065,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1024" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H1024" t="n">
         <v>1010</v>
@@ -30239,7 +30239,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1030" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H1030" t="n">
         <v>1301</v>
@@ -30268,7 +30268,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1031" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H1031" t="n">
         <v>2233</v>
@@ -30297,7 +30297,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1032" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H1032" t="n">
         <v>200</v>
@@ -30326,7 +30326,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1033" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H1033" t="n">
         <v>939</v>
@@ -30413,7 +30413,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1036" t="n">
-        <v>2.40822148323059</v>
+        <v>2.40822124481201</v>
       </c>
       <c r="H1036" t="n">
         <v>1101</v>
@@ -30558,7 +30558,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1041" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H1041" t="n">
         <v>15334</v>
@@ -30587,7 +30587,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1042" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H1042" t="n">
         <v>548</v>
@@ -30616,7 +30616,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1043" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H1043" t="n">
         <v>7200</v>
@@ -30645,7 +30645,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1044" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H1044" t="n">
         <v>0</v>
@@ -31138,7 +31138,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1061" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H1061" t="n">
         <v>6</v>
@@ -31196,7 +31196,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1063" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H1063" t="n">
         <v>2460</v>
@@ -31225,7 +31225,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1064" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H1064" t="n">
         <v>0</v>
@@ -31254,7 +31254,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1065" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H1065" t="n">
         <v>7276</v>
@@ -31283,7 +31283,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H1066" t="n">
         <v>5691</v>
@@ -31312,7 +31312,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.42688989639282</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H1067" t="n">
         <v>400</v>
@@ -31428,7 +31428,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1071" t="n">
-        <v>2.70691561698914</v>
+        <v>2.70691585540771</v>
       </c>
       <c r="H1071" t="n">
         <v>53618</v>
@@ -31892,7 +31892,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1087" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H1087" t="n">
         <v>433</v>
@@ -31950,7 +31950,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1089" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H1089" t="n">
         <v>7114</v>
@@ -31979,7 +31979,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1090" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H1090" t="n">
         <v>8078</v>
@@ -32037,7 +32037,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1092" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H1092" t="n">
         <v>5267</v>
@@ -32066,7 +32066,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H1093" t="n">
         <v>6000</v>
@@ -32153,7 +32153,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1096" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H1096" t="n">
         <v>5215</v>
@@ -32182,7 +32182,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1097" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H1097" t="n">
         <v>5388</v>
@@ -32211,7 +32211,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1098" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H1098" t="n">
         <v>0</v>
@@ -32269,7 +32269,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1100" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H1100" t="n">
         <v>8673</v>
@@ -32298,7 +32298,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1101" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H1101" t="n">
         <v>4000</v>
@@ -32327,7 +32327,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1102" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H1102" t="n">
         <v>16001</v>
@@ -32356,7 +32356,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1103" t="n">
-        <v>2.58557105064392</v>
+        <v>2.58557081222534</v>
       </c>
       <c r="H1103" t="n">
         <v>1905</v>
@@ -32849,7 +32849,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1120" t="n">
-        <v>2.63224196434021</v>
+        <v>2.63224172592163</v>
       </c>
       <c r="H1120" t="n">
         <v>3502</v>
@@ -34038,7 +34038,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1161" t="n">
-        <v>2.88426494598389</v>
+        <v>2.88426518440247</v>
       </c>
       <c r="H1161" t="n">
         <v>2639</v>
@@ -34183,7 +34183,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.13628840446472</v>
+        <v>3.13628816604614</v>
       </c>
       <c r="H1166" t="n">
         <v>15387</v>
@@ -34212,7 +34212,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.20162796974182</v>
+        <v>3.20162773132324</v>
       </c>
       <c r="H1167" t="n">
         <v>24299</v>
@@ -34328,7 +34328,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.28563547134399</v>
+        <v>3.28563523292542</v>
       </c>
       <c r="H1171" t="n">
         <v>9302</v>
@@ -34444,7 +34444,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.44431662559509</v>
+        <v>3.44431686401367</v>
       </c>
       <c r="H1175" t="n">
         <v>13251</v>
@@ -34531,7 +34531,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1178" t="n">
-        <v>3.79901623725891</v>
+        <v>3.79901599884033</v>
       </c>
       <c r="H1178" t="n">
         <v>19529</v>
@@ -34589,7 +34589,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1180" t="n">
-        <v>4.0043683052063</v>
+        <v>4.00436782836914</v>
       </c>
       <c r="H1180" t="n">
         <v>86548</v>
@@ -34618,7 +34618,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1181" t="n">
-        <v>4.26572561264038</v>
+        <v>4.26572513580322</v>
       </c>
       <c r="H1181" t="n">
         <v>61743</v>
@@ -34647,7 +34647,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1182" t="n">
-        <v>4.46174383163452</v>
+        <v>4.46174335479736</v>
       </c>
       <c r="H1182" t="n">
         <v>47140</v>
@@ -34734,7 +34734,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1185" t="n">
-        <v>4.94712209701538</v>
+        <v>4.94712162017822</v>
       </c>
       <c r="H1185" t="n">
         <v>36680</v>
@@ -34763,7 +34763,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1186" t="n">
-        <v>4.85377979278564</v>
+        <v>4.85377883911133</v>
       </c>
       <c r="H1186" t="n">
         <v>39631</v>
@@ -34908,7 +34908,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1191" t="n">
-        <v>4.50841426849365</v>
+        <v>4.50841474533081</v>
       </c>
       <c r="H1191" t="n">
         <v>16999</v>
@@ -34966,7 +34966,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1193" t="n">
-        <v>4.46174383163452</v>
+        <v>4.46174335479736</v>
       </c>
       <c r="H1193" t="n">
         <v>24861</v>
@@ -35024,7 +35024,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1195" t="n">
-        <v>4.46174383163452</v>
+        <v>4.46174335479736</v>
       </c>
       <c r="H1195" t="n">
         <v>12604</v>
@@ -35430,7 +35430,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1209" t="n">
-        <v>4.4244065284729</v>
+        <v>4.42440700531006</v>
       </c>
       <c r="H1209" t="n">
         <v>27502</v>
@@ -35488,7 +35488,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1211" t="n">
-        <v>4.46174383163452</v>
+        <v>4.46174335479736</v>
       </c>
       <c r="H1211" t="n">
         <v>10557</v>
@@ -35517,7 +35517,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1212" t="n">
-        <v>4.50841426849365</v>
+        <v>4.50841474533081</v>
       </c>
       <c r="H1212" t="n">
         <v>8520</v>
@@ -35691,7 +35691,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1218" t="n">
-        <v>4.4524097442627</v>
+        <v>4.45240926742554</v>
       </c>
       <c r="H1218" t="n">
         <v>17443</v>
@@ -35807,7 +35807,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1222" t="n">
-        <v>4.4244065284729</v>
+        <v>4.42440700531006</v>
       </c>
       <c r="H1222" t="n">
         <v>1578</v>
@@ -35836,7 +35836,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1223" t="n">
-        <v>4.3870701789856</v>
+        <v>4.38706970214844</v>
       </c>
       <c r="H1223" t="n">
         <v>2203</v>
@@ -35894,7 +35894,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1225" t="n">
-        <v>4.36840105056763</v>
+        <v>4.36840152740479</v>
       </c>
       <c r="H1225" t="n">
         <v>12461</v>
@@ -35952,7 +35952,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1227" t="n">
-        <v>4.3870701789856</v>
+        <v>4.38706970214844</v>
       </c>
       <c r="H1227" t="n">
         <v>11176</v>
@@ -36010,7 +36010,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1229" t="n">
-        <v>4.3870701789856</v>
+        <v>4.38706970214844</v>
       </c>
       <c r="H1229" t="n">
         <v>3628</v>
@@ -36068,7 +36068,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1231" t="n">
-        <v>4.3870701789856</v>
+        <v>4.38706970214844</v>
       </c>
       <c r="H1231" t="n">
         <v>12136</v>
@@ -36097,7 +36097,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1232" t="n">
-        <v>4.3870701789856</v>
+        <v>4.38706970214844</v>
       </c>
       <c r="H1232" t="n">
         <v>8849</v>
@@ -36126,7 +36126,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1233" t="n">
-        <v>4.3870701789856</v>
+        <v>4.38706970214844</v>
       </c>
       <c r="H1233" t="n">
         <v>8218</v>
@@ -36184,7 +36184,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1235" t="n">
-        <v>4.3870701789856</v>
+        <v>4.38706970214844</v>
       </c>
       <c r="H1235" t="n">
         <v>3700</v>
@@ -36213,7 +36213,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1236" t="n">
-        <v>4.3870701789856</v>
+        <v>4.38706970214844</v>
       </c>
       <c r="H1236" t="n">
         <v>9129</v>
@@ -36242,7 +36242,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1237" t="n">
-        <v>4.3870701789856</v>
+        <v>4.38706970214844</v>
       </c>
       <c r="H1237" t="n">
         <v>3361</v>
@@ -36271,7 +36271,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1238" t="n">
-        <v>4.3870701789856</v>
+        <v>4.38706970214844</v>
       </c>
       <c r="H1238" t="n">
         <v>3927</v>
@@ -36300,7 +36300,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1239" t="n">
-        <v>4.3870701789856</v>
+        <v>4.38706970214844</v>
       </c>
       <c r="H1239" t="n">
         <v>2020</v>
@@ -36329,7 +36329,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1240" t="n">
-        <v>4.4524097442627</v>
+        <v>4.45240926742554</v>
       </c>
       <c r="H1240" t="n">
         <v>7982</v>
@@ -36358,7 +36358,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1241" t="n">
-        <v>4.4244065284729</v>
+        <v>4.42440700531006</v>
       </c>
       <c r="H1241" t="n">
         <v>9666</v>
@@ -36445,7 +36445,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1244" t="n">
-        <v>4.3870701789856</v>
+        <v>4.38706970214844</v>
       </c>
       <c r="H1244" t="n">
         <v>10595</v>
@@ -36474,7 +36474,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.40573787689209</v>
+        <v>4.40573835372925</v>
       </c>
       <c r="H1245" t="n">
         <v>1123</v>
@@ -36503,7 +36503,7 @@
         <v>4.75</v>
       </c>
       <c r="G1246" t="n">
-        <v>4.43374061584473</v>
+        <v>4.43374109268188</v>
       </c>
       <c r="H1246" t="n">
         <v>2543</v>
@@ -36619,7 +36619,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1250" t="n">
-        <v>4.40573787689209</v>
+        <v>4.40573835372925</v>
       </c>
       <c r="H1250" t="n">
         <v>2487</v>
@@ -36677,7 +36677,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1252" t="n">
-        <v>4.53641700744629</v>
+        <v>4.53641748428345</v>
       </c>
       <c r="H1252" t="n">
         <v>10852</v>
@@ -37315,7 +37315,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1274" t="n">
-        <v>4.99078130722046</v>
+        <v>4.9907808303833</v>
       </c>
       <c r="H1274" t="n">
         <v>24772</v>
@@ -37344,7 +37344,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1275" t="n">
-        <v>5.02917146682739</v>
+        <v>5.02917194366455</v>
       </c>
       <c r="H1275" t="n">
         <v>31385</v>
@@ -37431,7 +37431,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1278" t="n">
-        <v>5.48985958099365</v>
+        <v>5.48985910415649</v>
       </c>
       <c r="H1278" t="n">
         <v>70084</v>
@@ -37576,7 +37576,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1283" t="n">
-        <v>5.83537483215332</v>
+        <v>5.83537530899048</v>
       </c>
       <c r="H1283" t="n">
         <v>8786</v>
@@ -37634,7 +37634,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1285" t="n">
-        <v>6.39203929901123</v>
+        <v>6.39203882217407</v>
       </c>
       <c r="H1285" t="n">
         <v>35361</v>
@@ -37750,7 +37750,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1289" t="n">
-        <v>6.46882009506226</v>
+        <v>6.46882057189941</v>
       </c>
       <c r="H1289" t="n">
         <v>13104</v>
@@ -37866,7 +37866,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G1293" t="n">
-        <v>6.1808910369873</v>
+        <v>6.18089056015015</v>
       </c>
       <c r="H1293" t="n">
         <v>21462</v>
@@ -37895,7 +37895,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1294" t="n">
-        <v>6.12330532073975</v>
+        <v>6.12330484390259</v>
       </c>
       <c r="H1294" t="n">
         <v>21748</v>
@@ -37953,7 +37953,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1296" t="n">
-        <v>6.39203929901123</v>
+        <v>6.39203882217407</v>
       </c>
       <c r="H1296" t="n">
         <v>15861</v>
@@ -37982,7 +37982,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1297" t="n">
-        <v>6.48801612854004</v>
+        <v>6.48801565170288</v>
       </c>
       <c r="H1297" t="n">
         <v>2374</v>
@@ -38011,7 +38011,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1298" t="n">
-        <v>6.48801612854004</v>
+        <v>6.48801565170288</v>
       </c>
       <c r="H1298" t="n">
         <v>9827</v>
@@ -38156,7 +38156,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1303" t="n">
-        <v>6.48801612854004</v>
+        <v>6.48801565170288</v>
       </c>
       <c r="H1303" t="n">
         <v>11171</v>
@@ -38388,7 +38388,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1311" t="n">
-        <v>5.93135118484497</v>
+        <v>5.93135166168213</v>
       </c>
       <c r="H1311" t="n">
         <v>18885</v>
@@ -38446,7 +38446,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1313" t="n">
-        <v>5.93135118484497</v>
+        <v>5.93135166168213</v>
       </c>
       <c r="H1313" t="n">
         <v>34147</v>
@@ -38533,7 +38533,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1316" t="n">
-        <v>5.93135118484497</v>
+        <v>5.93135166168213</v>
       </c>
       <c r="H1316" t="n">
         <v>10376</v>
@@ -38939,7 +38939,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1330" t="n">
-        <v>5.68181276321411</v>
+        <v>5.68181228637695</v>
       </c>
       <c r="H1330" t="n">
         <v>4010</v>
@@ -39026,7 +39026,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1333" t="n">
-        <v>5.66261720657349</v>
+        <v>5.66261768341064</v>
       </c>
       <c r="H1333" t="n">
         <v>3167</v>
@@ -39055,7 +39055,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.56664085388184</v>
+        <v>5.56664133071899</v>
       </c>
       <c r="H1334" t="n">
         <v>13673</v>
@@ -39084,7 +39084,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1335" t="n">
-        <v>5.48985958099365</v>
+        <v>5.48985910415649</v>
       </c>
       <c r="H1335" t="n">
         <v>2565</v>
@@ -39142,7 +39142,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1337" t="n">
-        <v>5.56664085388184</v>
+        <v>5.56664133071899</v>
       </c>
       <c r="H1337" t="n">
         <v>2917</v>
@@ -39171,7 +39171,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1338" t="n">
-        <v>5.56664085388184</v>
+        <v>5.56664133071899</v>
       </c>
       <c r="H1338" t="n">
         <v>1312</v>
@@ -39258,7 +39258,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1341" t="n">
-        <v>5.66261720657349</v>
+        <v>5.66261768341064</v>
       </c>
       <c r="H1341" t="n">
         <v>1605</v>
@@ -39287,7 +39287,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1342" t="n">
-        <v>5.66261720657349</v>
+        <v>5.66261768341064</v>
       </c>
       <c r="H1342" t="n">
         <v>3220</v>
@@ -39403,7 +39403,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1346" t="n">
-        <v>5.56664085388184</v>
+        <v>5.56664133071899</v>
       </c>
       <c r="H1346" t="n">
         <v>2814</v>
@@ -39519,7 +39519,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1350" t="n">
-        <v>5.93135118484497</v>
+        <v>5.93135166168213</v>
       </c>
       <c r="H1350" t="n">
         <v>11182</v>
@@ -39548,7 +39548,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1351" t="n">
-        <v>5.93135118484497</v>
+        <v>5.93135166168213</v>
       </c>
       <c r="H1351" t="n">
         <v>17082</v>
@@ -39577,7 +39577,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1352" t="n">
-        <v>5.93135118484497</v>
+        <v>5.93135166168213</v>
       </c>
       <c r="H1352" t="n">
         <v>5027</v>
@@ -39606,7 +39606,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1353" t="n">
-        <v>6.12330532073975</v>
+        <v>6.12330484390259</v>
       </c>
       <c r="H1353" t="n">
         <v>15567</v>
@@ -39693,7 +39693,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1356" t="n">
-        <v>5.87376546859741</v>
+        <v>5.87376594543457</v>
       </c>
       <c r="H1356" t="n">
         <v>18468</v>
@@ -39896,7 +39896,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1363" t="n">
-        <v>5.96974182128906</v>
+        <v>5.96974229812622</v>
       </c>
       <c r="H1363" t="n">
         <v>14927</v>
@@ -40012,7 +40012,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1367" t="n">
-        <v>5.96974182128906</v>
+        <v>5.96974229812622</v>
       </c>
       <c r="H1367" t="n">
         <v>5383</v>
@@ -40041,7 +40041,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1368" t="n">
-        <v>5.83537483215332</v>
+        <v>5.83537530899048</v>
       </c>
       <c r="H1368" t="n">
         <v>3207</v>
@@ -40099,7 +40099,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1370" t="n">
-        <v>5.96974182128906</v>
+        <v>5.96974229812622</v>
       </c>
       <c r="H1370" t="n">
         <v>2420</v>
@@ -40128,7 +40128,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1371" t="n">
-        <v>5.87376546859741</v>
+        <v>5.87376594543457</v>
       </c>
       <c r="H1371" t="n">
         <v>5952</v>
@@ -40186,7 +40186,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1373" t="n">
-        <v>6.08491468429565</v>
+        <v>6.0849142074585</v>
       </c>
       <c r="H1373" t="n">
         <v>4048</v>
@@ -40244,7 +40244,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1375" t="n">
-        <v>5.87376546859741</v>
+        <v>5.87376594543457</v>
       </c>
       <c r="H1375" t="n">
         <v>6216</v>
@@ -40505,7 +40505,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1384" t="n">
-        <v>5.87376546859741</v>
+        <v>5.87376594543457</v>
       </c>
       <c r="H1384" t="n">
         <v>8532</v>
@@ -40534,7 +40534,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1385" t="n">
-        <v>5.96974182128906</v>
+        <v>5.96974229812622</v>
       </c>
       <c r="H1385" t="n">
         <v>4804</v>
@@ -40563,7 +40563,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1386" t="n">
-        <v>5.96974182128906</v>
+        <v>5.96974229812622</v>
       </c>
       <c r="H1386" t="n">
         <v>51315</v>
@@ -40592,7 +40592,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1387" t="n">
-        <v>5.96974182128906</v>
+        <v>5.96974229812622</v>
       </c>
       <c r="H1387" t="n">
         <v>3086</v>
@@ -40621,7 +40621,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1388" t="n">
-        <v>5.93135118484497</v>
+        <v>5.93135166168213</v>
       </c>
       <c r="H1388" t="n">
         <v>5083</v>
@@ -40679,7 +40679,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1390" t="n">
-        <v>5.93135118484497</v>
+        <v>5.93135166168213</v>
       </c>
       <c r="H1390" t="n">
         <v>3425</v>
@@ -40737,7 +40737,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1392" t="n">
-        <v>5.93135118484497</v>
+        <v>5.93135166168213</v>
       </c>
       <c r="H1392" t="n">
         <v>2371</v>
@@ -40766,7 +40766,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1393" t="n">
-        <v>5.87376546859741</v>
+        <v>5.87376594543457</v>
       </c>
       <c r="H1393" t="n">
         <v>4474</v>
@@ -41085,7 +41085,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1404" t="n">
-        <v>6.08491468429565</v>
+        <v>6.0849142074585</v>
       </c>
       <c r="H1404" t="n">
         <v>18941</v>
@@ -41143,7 +41143,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1406" t="n">
-        <v>6.12330532073975</v>
+        <v>6.12330484390259</v>
       </c>
       <c r="H1406" t="n">
         <v>40015</v>
@@ -41462,7 +41462,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1417" t="n">
-        <v>7.02548503875732</v>
+        <v>7.02548456192017</v>
       </c>
       <c r="H1417" t="n">
         <v>6334</v>
@@ -41839,7 +41839,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1430" t="n">
-        <v>7.02548503875732</v>
+        <v>7.02548456192017</v>
       </c>
       <c r="H1430" t="n">
         <v>15354</v>
@@ -41897,7 +41897,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1432" t="n">
-        <v>7.02548503875732</v>
+        <v>7.02548456192017</v>
       </c>
       <c r="H1432" t="n">
         <v>1260</v>
@@ -42129,7 +42129,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1440" t="n">
-        <v>7.06387519836426</v>
+        <v>7.06387567520142</v>
       </c>
       <c r="H1440" t="n">
         <v>1592</v>
@@ -42187,7 +42187,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G1442" t="n">
-        <v>7.12146139144897</v>
+        <v>7.12146091461182</v>
       </c>
       <c r="H1442" t="n">
         <v>9087</v>
@@ -42303,7 +42303,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1446" t="n">
-        <v>7.06387519836426</v>
+        <v>7.06387567520142</v>
       </c>
       <c r="H1446" t="n">
         <v>10440</v>
@@ -42361,7 +42361,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1448" t="n">
-        <v>7.06387519836426</v>
+        <v>7.06387567520142</v>
       </c>
       <c r="H1448" t="n">
         <v>6369</v>
@@ -42390,7 +42390,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1449" t="n">
-        <v>6.91031265258789</v>
+        <v>6.91031217575073</v>
       </c>
       <c r="H1449" t="n">
         <v>8416</v>
@@ -42419,7 +42419,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1450" t="n">
-        <v>7.02548503875732</v>
+        <v>7.02548456192017</v>
       </c>
       <c r="H1450" t="n">
         <v>5499</v>
@@ -42535,7 +42535,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1454" t="n">
-        <v>7.06387519836426</v>
+        <v>7.06387567520142</v>
       </c>
       <c r="H1454" t="n">
         <v>2894</v>
@@ -42680,7 +42680,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1459" t="n">
-        <v>6.91031265258789</v>
+        <v>6.91031217575073</v>
       </c>
       <c r="H1459" t="n">
         <v>3121</v>
@@ -42738,7 +42738,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1461" t="n">
-        <v>6.91031265258789</v>
+        <v>6.91031217575073</v>
       </c>
       <c r="H1461" t="n">
         <v>9076</v>
@@ -42767,7 +42767,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1462" t="n">
-        <v>7.06387519836426</v>
+        <v>7.06387567520142</v>
       </c>
       <c r="H1462" t="n">
         <v>300</v>
@@ -42883,7 +42883,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1466" t="n">
-        <v>7.02548503875732</v>
+        <v>7.02548456192017</v>
       </c>
       <c r="H1466" t="n">
         <v>501</v>
@@ -43173,7 +43173,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1476" t="n">
-        <v>6.91031265258789</v>
+        <v>6.91031217575073</v>
       </c>
       <c r="H1476" t="n">
         <v>7848</v>
@@ -43202,7 +43202,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1477" t="n">
-        <v>6.89111757278442</v>
+        <v>6.89111709594727</v>
       </c>
       <c r="H1477" t="n">
         <v>12560</v>
@@ -43260,7 +43260,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1479" t="n">
-        <v>6.91031265258789</v>
+        <v>6.91031217575073</v>
       </c>
       <c r="H1479" t="n">
         <v>16205</v>
@@ -43289,7 +43289,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1480" t="n">
-        <v>6.77594518661499</v>
+        <v>6.77594566345215</v>
       </c>
       <c r="H1480" t="n">
         <v>1973</v>
@@ -43318,7 +43318,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1481" t="n">
-        <v>6.98709440231323</v>
+        <v>6.98709392547607</v>
       </c>
       <c r="H1481" t="n">
         <v>4148</v>
@@ -43347,7 +43347,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1482" t="n">
-        <v>6.89111757278442</v>
+        <v>6.89111709594727</v>
       </c>
       <c r="H1482" t="n">
         <v>144</v>
@@ -43405,7 +43405,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G1484" t="n">
-        <v>6.79514026641846</v>
+        <v>6.79514074325562</v>
       </c>
       <c r="H1484" t="n">
         <v>10530</v>
@@ -43434,7 +43434,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1485" t="n">
-        <v>6.81433629989624</v>
+        <v>6.81433582305908</v>
       </c>
       <c r="H1485" t="n">
         <v>2742</v>
@@ -43463,7 +43463,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1486" t="n">
-        <v>6.91031265258789</v>
+        <v>6.91031217575073</v>
       </c>
       <c r="H1486" t="n">
         <v>1912</v>
@@ -43492,7 +43492,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1487" t="n">
-        <v>6.91031265258789</v>
+        <v>6.91031217575073</v>
       </c>
       <c r="H1487" t="n">
         <v>6267</v>
@@ -43521,7 +43521,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1488" t="n">
-        <v>6.98709440231323</v>
+        <v>6.98709392547607</v>
       </c>
       <c r="H1488" t="n">
         <v>8301</v>
@@ -43724,7 +43724,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1495" t="n">
-        <v>7.29421901702881</v>
+        <v>7.29421854019165</v>
       </c>
       <c r="H1495" t="n">
         <v>3213</v>
@@ -43753,7 +43753,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1496" t="n">
-        <v>7.42858552932739</v>
+        <v>7.42858600616455</v>
       </c>
       <c r="H1496" t="n">
         <v>9505</v>
@@ -43811,7 +43811,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1498" t="n">
-        <v>7.54375791549683</v>
+        <v>7.54375839233398</v>
       </c>
       <c r="H1498" t="n">
         <v>2199</v>
@@ -54605,6 +54605,35 @@
         <v>1920</v>
       </c>
       <c r="I1870" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1871">
+      <c r="A1871" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1871" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1871" t="n">
+        <v>14</v>
+      </c>
+      <c r="D1871" t="n">
+        <v>14</v>
+      </c>
+      <c r="E1871" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="F1871" t="n">
+        <v>13.8999996185303</v>
+      </c>
+      <c r="G1871" t="n">
+        <v>13.8999996185303</v>
+      </c>
+      <c r="H1871" t="n">
+        <v>2575</v>
+      </c>
+      <c r="I1871" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IEG.MI.xlsx
+++ b/data/IEG.MI.xlsx
@@ -485,7 +485,7 @@
         <v>3.73099994659424</v>
       </c>
       <c r="G4" t="n">
-        <v>3.48258686065674</v>
+        <v>3.48258662223816</v>
       </c>
       <c r="H4" t="n">
         <v>132269</v>
@@ -514,7 +514,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G5" t="n">
-        <v>3.52832436561584</v>
+        <v>3.52832412719727</v>
       </c>
       <c r="H5" t="n">
         <v>20727</v>
@@ -543,7 +543,7 @@
         <v>3.69749999046326</v>
       </c>
       <c r="G6" t="n">
-        <v>3.45131731033325</v>
+        <v>3.45131707191467</v>
       </c>
       <c r="H6" t="n">
         <v>5051</v>
@@ -572,7 +572,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G7" t="n">
-        <v>3.4536509513855</v>
+        <v>3.45365071296692</v>
       </c>
       <c r="H7" t="n">
         <v>13909</v>
@@ -601,7 +601,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>3.40698003768921</v>
+        <v>3.40697979927063</v>
       </c>
       <c r="H8" t="n">
         <v>31297</v>
@@ -630,7 +630,7 @@
         <v>3.67050004005432</v>
       </c>
       <c r="G9" t="n">
-        <v>3.42611479759216</v>
+        <v>3.42611503601074</v>
       </c>
       <c r="H9" t="n">
         <v>132</v>
@@ -659,7 +659,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G10" t="n">
-        <v>3.4536509513855</v>
+        <v>3.45365071296692</v>
       </c>
       <c r="H10" t="n">
         <v>5150</v>
@@ -688,7 +688,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G11" t="n">
-        <v>3.4536509513855</v>
+        <v>3.45365071296692</v>
       </c>
       <c r="H11" t="n">
         <v>2000</v>
@@ -717,7 +717,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G12" t="n">
-        <v>3.43498277664185</v>
+        <v>3.43498253822327</v>
       </c>
       <c r="H12" t="n">
         <v>3250</v>
@@ -746,7 +746,7 @@
         <v>3.64050006866455</v>
       </c>
       <c r="G13" t="n">
-        <v>3.39811253547668</v>
+        <v>3.39811229705811</v>
       </c>
       <c r="H13" t="n">
         <v>1311</v>
@@ -804,7 +804,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G15" t="n">
-        <v>3.42564845085144</v>
+        <v>3.42564821243286</v>
       </c>
       <c r="H15" t="n">
         <v>10175</v>
@@ -862,7 +862,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G17" t="n">
-        <v>3.47231912612915</v>
+        <v>3.47231936454773</v>
       </c>
       <c r="H17" t="n">
         <v>86899</v>
@@ -920,7 +920,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G19" t="n">
-        <v>3.69633960723877</v>
+        <v>3.69634008407593</v>
       </c>
       <c r="H19" t="n">
         <v>96525</v>
@@ -978,7 +978,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G21" t="n">
-        <v>3.80835032463074</v>
+        <v>3.80834984779358</v>
       </c>
       <c r="H21" t="n">
         <v>29979</v>
@@ -1065,7 +1065,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G24" t="n">
-        <v>3.85502099990845</v>
+        <v>3.85502123832703</v>
       </c>
       <c r="H24" t="n">
         <v>69970</v>
@@ -1094,7 +1094,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G25" t="n">
-        <v>3.81768441200256</v>
+        <v>3.81768465042114</v>
       </c>
       <c r="H25" t="n">
         <v>4963</v>
@@ -1181,7 +1181,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G28" t="n">
-        <v>3.95769739151001</v>
+        <v>3.95769667625427</v>
       </c>
       <c r="H28" t="n">
         <v>6052</v>
@@ -1210,7 +1210,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G29" t="n">
-        <v>3.97636556625366</v>
+        <v>3.97636604309082</v>
       </c>
       <c r="H29" t="n">
         <v>2457</v>
@@ -1239,7 +1239,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G30" t="n">
-        <v>4.05103969573975</v>
+        <v>4.05103874206543</v>
       </c>
       <c r="H30" t="n">
         <v>10363</v>
@@ -1268,7 +1268,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G31" t="n">
-        <v>4.03237104415894</v>
+        <v>4.03237056732178</v>
       </c>
       <c r="H31" t="n">
         <v>17060</v>
@@ -1297,7 +1297,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G32" t="n">
-        <v>3.9390287399292</v>
+        <v>3.93902826309204</v>
       </c>
       <c r="H32" t="n">
         <v>6284</v>
@@ -1326,7 +1326,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>4.01370286941528</v>
+        <v>4.01370239257812</v>
       </c>
       <c r="H33" t="n">
         <v>4871</v>
@@ -1355,7 +1355,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G34" t="n">
-        <v>4.01370286941528</v>
+        <v>4.01370239257812</v>
       </c>
       <c r="H34" t="n">
         <v>114</v>
@@ -1384,7 +1384,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G35" t="n">
-        <v>3.99503397941589</v>
+        <v>3.99503421783447</v>
       </c>
       <c r="H35" t="n">
         <v>922</v>
@@ -1413,7 +1413,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G36" t="n">
-        <v>3.99503397941589</v>
+        <v>3.99503421783447</v>
       </c>
       <c r="H36" t="n">
         <v>300</v>
@@ -1442,7 +1442,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G37" t="n">
-        <v>3.99503397941589</v>
+        <v>3.99503421783447</v>
       </c>
       <c r="H37" t="n">
         <v>4226</v>
@@ -1471,7 +1471,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G38" t="n">
-        <v>3.95769739151001</v>
+        <v>3.95769667625427</v>
       </c>
       <c r="H38" t="n">
         <v>4960</v>
@@ -1500,7 +1500,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G39" t="n">
-        <v>3.8830235004425</v>
+        <v>3.88302326202393</v>
       </c>
       <c r="H39" t="n">
         <v>592</v>
@@ -1529,7 +1529,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G40" t="n">
-        <v>3.8830235004425</v>
+        <v>3.88302326202393</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1558,7 +1558,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G41" t="n">
-        <v>3.95769739151001</v>
+        <v>3.95769667625427</v>
       </c>
       <c r="H41" t="n">
         <v>225</v>
@@ -1587,7 +1587,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G42" t="n">
-        <v>3.95769739151001</v>
+        <v>3.95769667625427</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>3.92036008834839</v>
+        <v>3.92036032676697</v>
       </c>
       <c r="H43" t="n">
         <v>148291</v>
@@ -1645,7 +1645,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G44" t="n">
-        <v>3.92036008834839</v>
+        <v>3.92036032676697</v>
       </c>
       <c r="H44" t="n">
         <v>59672</v>
@@ -1703,7 +1703,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G46" t="n">
-        <v>3.92036008834839</v>
+        <v>3.92036032676697</v>
       </c>
       <c r="H46" t="n">
         <v>4540</v>
@@ -1732,7 +1732,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G47" t="n">
-        <v>3.85502099990845</v>
+        <v>3.85502123832703</v>
       </c>
       <c r="H47" t="n">
         <v>125</v>
@@ -1819,7 +1819,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G50" t="n">
-        <v>3.92036008834839</v>
+        <v>3.92036032676697</v>
       </c>
       <c r="H50" t="n">
         <v>3900</v>
@@ -1848,7 +1848,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G51" t="n">
-        <v>3.64033460617065</v>
+        <v>3.64033484458923</v>
       </c>
       <c r="H51" t="n">
         <v>168018</v>
@@ -1877,7 +1877,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G52" t="n">
-        <v>3.59366345405579</v>
+        <v>3.59366369247437</v>
       </c>
       <c r="H52" t="n">
         <v>66112</v>
@@ -1906,7 +1906,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G53" t="n">
-        <v>3.63100075721741</v>
+        <v>3.63100051879883</v>
       </c>
       <c r="H53" t="n">
         <v>23073</v>
@@ -1935,7 +1935,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G54" t="n">
-        <v>3.53765869140625</v>
+        <v>3.53765845298767</v>
       </c>
       <c r="H54" t="n">
         <v>154944</v>
@@ -1964,7 +1964,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G55" t="n">
-        <v>3.42564845085144</v>
+        <v>3.42564821243286</v>
       </c>
       <c r="H55" t="n">
         <v>62162</v>
@@ -1993,7 +1993,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G56" t="n">
-        <v>3.40698003768921</v>
+        <v>3.40697979927063</v>
       </c>
       <c r="H56" t="n">
         <v>6594</v>
@@ -2022,7 +2022,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G57" t="n">
-        <v>3.4536509513855</v>
+        <v>3.45365071296692</v>
       </c>
       <c r="H57" t="n">
         <v>73464</v>
@@ -2051,7 +2051,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G58" t="n">
-        <v>3.4536509513855</v>
+        <v>3.45365071296692</v>
       </c>
       <c r="H58" t="n">
         <v>35821</v>
@@ -2109,7 +2109,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G60" t="n">
-        <v>3.47231912612915</v>
+        <v>3.47231936454773</v>
       </c>
       <c r="H60" t="n">
         <v>10849</v>
@@ -2167,7 +2167,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>3.59366345405579</v>
+        <v>3.59366369247437</v>
       </c>
       <c r="H62" t="n">
         <v>6367</v>
@@ -2225,7 +2225,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G64" t="n">
-        <v>3.56566095352173</v>
+        <v>3.56566119194031</v>
       </c>
       <c r="H64" t="n">
         <v>333</v>
@@ -2254,7 +2254,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G65" t="n">
-        <v>3.58432960510254</v>
+        <v>3.58432936668396</v>
       </c>
       <c r="H65" t="n">
         <v>6062</v>
@@ -2283,7 +2283,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G66" t="n">
-        <v>3.59366345405579</v>
+        <v>3.59366369247437</v>
       </c>
       <c r="H66" t="n">
         <v>2000</v>
@@ -2341,7 +2341,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G68" t="n">
-        <v>3.69633960723877</v>
+        <v>3.69634008407593</v>
       </c>
       <c r="H68" t="n">
         <v>6933</v>
@@ -2428,7 +2428,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G71" t="n">
-        <v>3.59366345405579</v>
+        <v>3.59366369247437</v>
       </c>
       <c r="H71" t="n">
         <v>700</v>
@@ -2457,7 +2457,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G72" t="n">
-        <v>3.53765869140625</v>
+        <v>3.53765845298767</v>
       </c>
       <c r="H72" t="n">
         <v>3200</v>
@@ -2486,7 +2486,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G73" t="n">
-        <v>3.53765869140625</v>
+        <v>3.53765845298767</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G74" t="n">
-        <v>3.53765869140625</v>
+        <v>3.53765845298767</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>3.5469925403595</v>
+        <v>3.54699277877808</v>
       </c>
       <c r="H75" t="n">
         <v>550</v>
@@ -2573,7 +2573,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G76" t="n">
-        <v>3.5469925403595</v>
+        <v>3.54699277877808</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>3.5469925403595</v>
+        <v>3.54699277877808</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -2660,7 +2660,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G79" t="n">
-        <v>3.56566095352173</v>
+        <v>3.56566119194031</v>
       </c>
       <c r="H79" t="n">
         <v>505</v>
@@ -2689,7 +2689,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G80" t="n">
-        <v>3.59366345405579</v>
+        <v>3.59366369247437</v>
       </c>
       <c r="H80" t="n">
         <v>320</v>
@@ -2718,7 +2718,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G81" t="n">
-        <v>3.59366345405579</v>
+        <v>3.59366369247437</v>
       </c>
       <c r="H81" t="n">
         <v>11</v>
@@ -2747,7 +2747,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G82" t="n">
-        <v>3.59366345405579</v>
+        <v>3.59366369247437</v>
       </c>
       <c r="H82" t="n">
         <v>659</v>
@@ -2776,7 +2776,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G83" t="n">
-        <v>3.6123321056366</v>
+        <v>3.61233186721802</v>
       </c>
       <c r="H83" t="n">
         <v>505</v>
@@ -2805,7 +2805,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G84" t="n">
-        <v>3.6123321056366</v>
+        <v>3.61233186721802</v>
       </c>
       <c r="H84" t="n">
         <v>10</v>
@@ -2834,7 +2834,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G85" t="n">
-        <v>3.56566095352173</v>
+        <v>3.56566119194031</v>
       </c>
       <c r="H85" t="n">
         <v>7252</v>
@@ -2863,7 +2863,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>3.57499527931213</v>
+        <v>3.57499504089355</v>
       </c>
       <c r="H86" t="n">
         <v>6205</v>
@@ -2892,7 +2892,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G87" t="n">
-        <v>3.63100075721741</v>
+        <v>3.63100051879883</v>
       </c>
       <c r="H87" t="n">
         <v>3367</v>
@@ -2950,7 +2950,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>3.59366345405579</v>
+        <v>3.59366369247437</v>
       </c>
       <c r="H89" t="n">
         <v>19</v>
@@ -3008,7 +3008,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G91" t="n">
-        <v>3.6123321056366</v>
+        <v>3.61233186721802</v>
       </c>
       <c r="H91" t="n">
         <v>5</v>
@@ -3037,7 +3037,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G92" t="n">
-        <v>3.5469925403595</v>
+        <v>3.54699277877808</v>
       </c>
       <c r="H92" t="n">
         <v>495</v>
@@ -3066,7 +3066,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G93" t="n">
-        <v>3.58432960510254</v>
+        <v>3.58432936668396</v>
       </c>
       <c r="H93" t="n">
         <v>410</v>
@@ -3269,7 +3269,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>3.69633960723877</v>
+        <v>3.69634008407593</v>
       </c>
       <c r="H100" t="n">
         <v>5164</v>
@@ -3298,7 +3298,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G101" t="n">
-        <v>3.69633960723877</v>
+        <v>3.69634008407593</v>
       </c>
       <c r="H101" t="n">
         <v>1750</v>
@@ -3327,7 +3327,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G102" t="n">
-        <v>3.64033460617065</v>
+        <v>3.64033484458923</v>
       </c>
       <c r="H102" t="n">
         <v>9855</v>
@@ -3356,7 +3356,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G103" t="n">
-        <v>3.64033460617065</v>
+        <v>3.64033484458923</v>
       </c>
       <c r="H103" t="n">
         <v>40000</v>
@@ -3385,7 +3385,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>3.64033460617065</v>
+        <v>3.64033484458923</v>
       </c>
       <c r="H104" t="n">
         <v>505</v>
@@ -3414,7 +3414,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G105" t="n">
-        <v>3.64966869354248</v>
+        <v>3.64966893196106</v>
       </c>
       <c r="H105" t="n">
         <v>1680</v>
@@ -3501,7 +3501,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G108" t="n">
-        <v>3.81768441200256</v>
+        <v>3.81768465042114</v>
       </c>
       <c r="H108" t="n">
         <v>7940</v>
@@ -3559,7 +3559,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G110" t="n">
-        <v>3.81768441200256</v>
+        <v>3.81768465042114</v>
       </c>
       <c r="H110" t="n">
         <v>41689</v>
@@ -3588,7 +3588,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>3.80835032463074</v>
+        <v>3.80834984779358</v>
       </c>
       <c r="H111" t="n">
         <v>19699</v>
@@ -3617,7 +3617,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G112" t="n">
-        <v>3.80835032463074</v>
+        <v>3.80834984779358</v>
       </c>
       <c r="H112" t="n">
         <v>17603</v>
@@ -3733,7 +3733,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G116" t="n">
-        <v>3.76167941093445</v>
+        <v>3.76167917251587</v>
       </c>
       <c r="H116" t="n">
         <v>40346</v>
@@ -3907,7 +3907,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G122" t="n">
-        <v>3.86435484886169</v>
+        <v>3.86435532569885</v>
       </c>
       <c r="H122" t="n">
         <v>44816</v>
@@ -3936,7 +3936,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G123" t="n">
-        <v>3.85502099990845</v>
+        <v>3.85502123832703</v>
       </c>
       <c r="H123" t="n">
         <v>5193</v>
@@ -3965,7 +3965,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G124" t="n">
-        <v>3.86435484886169</v>
+        <v>3.86435532569885</v>
       </c>
       <c r="H124" t="n">
         <v>15805</v>
@@ -4023,7 +4023,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G126" t="n">
-        <v>3.80835032463074</v>
+        <v>3.80834984779358</v>
       </c>
       <c r="H126" t="n">
         <v>1562</v>
@@ -4226,7 +4226,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G133" t="n">
-        <v>3.87368965148926</v>
+        <v>3.87368941307068</v>
       </c>
       <c r="H133" t="n">
         <v>7109</v>
@@ -4284,7 +4284,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G135" t="n">
-        <v>3.92036008834839</v>
+        <v>3.92036032676697</v>
       </c>
       <c r="H135" t="n">
         <v>8125</v>
@@ -4313,7 +4313,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G136" t="n">
-        <v>3.92036008834839</v>
+        <v>3.92036032676697</v>
       </c>
       <c r="H136" t="n">
         <v>6440</v>
@@ -4342,7 +4342,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G137" t="n">
-        <v>3.92969489097595</v>
+        <v>3.92969465255737</v>
       </c>
       <c r="H137" t="n">
         <v>5529</v>
@@ -4371,7 +4371,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G138" t="n">
-        <v>3.92036008834839</v>
+        <v>3.92036032676697</v>
       </c>
       <c r="H138" t="n">
         <v>255</v>
@@ -4400,7 +4400,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G139" t="n">
-        <v>3.87368965148926</v>
+        <v>3.87368941307068</v>
       </c>
       <c r="H139" t="n">
         <v>2403</v>
@@ -4429,7 +4429,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G140" t="n">
-        <v>3.9390287399292</v>
+        <v>3.93902826309204</v>
       </c>
       <c r="H140" t="n">
         <v>3505</v>
@@ -4545,7 +4545,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G144" t="n">
-        <v>3.9390287399292</v>
+        <v>3.93902826309204</v>
       </c>
       <c r="H144" t="n">
         <v>3005</v>
@@ -4574,7 +4574,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G145" t="n">
-        <v>3.89235758781433</v>
+        <v>3.89235782623291</v>
       </c>
       <c r="H145" t="n">
         <v>14</v>
@@ -4603,7 +4603,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G146" t="n">
-        <v>3.87368965148926</v>
+        <v>3.87368941307068</v>
       </c>
       <c r="H146" t="n">
         <v>495</v>
@@ -4661,7 +4661,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G148" t="n">
-        <v>3.95769739151001</v>
+        <v>3.95769667625427</v>
       </c>
       <c r="H148" t="n">
         <v>228432</v>
@@ -4690,7 +4690,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G149" t="n">
-        <v>4.04170513153076</v>
+        <v>4.0417046546936</v>
       </c>
       <c r="H149" t="n">
         <v>42576</v>
@@ -4719,7 +4719,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G150" t="n">
-        <v>4.22838926315308</v>
+        <v>4.22838878631592</v>
       </c>
       <c r="H150" t="n">
         <v>26577</v>
@@ -4748,7 +4748,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G151" t="n">
-        <v>4.2563910484314</v>
+        <v>4.25639152526855</v>
       </c>
       <c r="H151" t="n">
         <v>8178</v>
@@ -4835,7 +4835,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G154" t="n">
-        <v>4.3590669631958</v>
+        <v>4.35906744003296</v>
       </c>
       <c r="H154" t="n">
         <v>15474</v>
@@ -4864,7 +4864,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G155" t="n">
-        <v>4.40573835372925</v>
+        <v>4.40573787689209</v>
       </c>
       <c r="H155" t="n">
         <v>10834</v>
@@ -4893,7 +4893,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G156" t="n">
-        <v>4.46174335479736</v>
+        <v>4.46174383163452</v>
       </c>
       <c r="H156" t="n">
         <v>4570</v>
@@ -4922,7 +4922,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G157" t="n">
-        <v>4.40573835372925</v>
+        <v>4.40573787689209</v>
       </c>
       <c r="H157" t="n">
         <v>4479</v>
@@ -4951,7 +4951,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G158" t="n">
-        <v>4.26572513580322</v>
+        <v>4.26572561264038</v>
       </c>
       <c r="H158" t="n">
         <v>10313</v>
@@ -5067,7 +5067,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G162" t="n">
-        <v>4.14438104629517</v>
+        <v>4.14438056945801</v>
       </c>
       <c r="H162" t="n">
         <v>5657</v>
@@ -5096,7 +5096,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G163" t="n">
-        <v>4.16304922103882</v>
+        <v>4.16304969787598</v>
       </c>
       <c r="H163" t="n">
         <v>656</v>
@@ -5183,7 +5183,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G166" t="n">
-        <v>4.16304922103882</v>
+        <v>4.16304969787598</v>
       </c>
       <c r="H166" t="n">
         <v>505</v>
@@ -5212,7 +5212,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G167" t="n">
-        <v>4.12571239471436</v>
+        <v>4.12571287155151</v>
       </c>
       <c r="H167" t="n">
         <v>1585</v>
@@ -5241,7 +5241,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>4.05103969573975</v>
+        <v>4.05103874206543</v>
       </c>
       <c r="H168" t="n">
         <v>499</v>
@@ -5270,7 +5270,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G169" t="n">
-        <v>4.14438104629517</v>
+        <v>4.14438056945801</v>
       </c>
       <c r="H169" t="n">
         <v>4433</v>
@@ -5299,7 +5299,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G170" t="n">
-        <v>4.13504695892334</v>
+        <v>4.13504648208618</v>
       </c>
       <c r="H170" t="n">
         <v>250</v>
@@ -5328,7 +5328,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G171" t="n">
-        <v>4.15371513366699</v>
+        <v>4.15371561050415</v>
       </c>
       <c r="H171" t="n">
         <v>3578</v>
@@ -5357,7 +5357,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G172" t="n">
-        <v>4.28439378738403</v>
+        <v>4.28439426422119</v>
       </c>
       <c r="H172" t="n">
         <v>1482</v>
@@ -5386,7 +5386,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G173" t="n">
-        <v>4.06037282943726</v>
+        <v>4.06037330627441</v>
       </c>
       <c r="H173" t="n">
         <v>6766</v>
@@ -5415,7 +5415,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G174" t="n">
-        <v>3.59366345405579</v>
+        <v>3.59366369247437</v>
       </c>
       <c r="H174" t="n">
         <v>11092</v>
@@ -5502,7 +5502,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G177" t="n">
-        <v>3.64966869354248</v>
+        <v>3.64966893196106</v>
       </c>
       <c r="H177" t="n">
         <v>15736</v>
@@ -5560,7 +5560,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G179" t="n">
-        <v>3.4536509513855</v>
+        <v>3.45365071296692</v>
       </c>
       <c r="H179" t="n">
         <v>1256</v>
@@ -5589,7 +5589,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G180" t="n">
-        <v>3.56566095352173</v>
+        <v>3.56566119194031</v>
       </c>
       <c r="H180" t="n">
         <v>6037</v>
@@ -5618,7 +5618,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G181" t="n">
-        <v>3.51899003982544</v>
+        <v>3.51899027824402</v>
       </c>
       <c r="H181" t="n">
         <v>1786</v>
@@ -5734,7 +5734,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G185" t="n">
-        <v>3.08961749076843</v>
+        <v>3.08961725234985</v>
       </c>
       <c r="H185" t="n">
         <v>4124</v>
@@ -5763,7 +5763,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G186" t="n">
-        <v>2.92160201072693</v>
+        <v>2.92160224914551</v>
       </c>
       <c r="H186" t="n">
         <v>2211</v>
@@ -5821,7 +5821,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G188" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H188" t="n">
         <v>6941</v>
@@ -5850,7 +5850,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G189" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G190" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H190" t="n">
         <v>500</v>
@@ -5908,7 +5908,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G191" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -5937,7 +5937,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G192" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -6169,7 +6169,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G200" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H200" t="n">
         <v>925</v>
@@ -6198,7 +6198,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G201" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H201" t="n">
         <v>93</v>
@@ -6401,7 +6401,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G208" t="n">
-        <v>2.91226768493652</v>
+        <v>2.91226744651794</v>
       </c>
       <c r="H208" t="n">
         <v>205</v>
@@ -6488,7 +6488,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G211" t="n">
-        <v>2.77225470542908</v>
+        <v>2.77225494384766</v>
       </c>
       <c r="H211" t="n">
         <v>5153</v>
@@ -6517,7 +6517,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>2.76292037963867</v>
+        <v>2.76292061805725</v>
       </c>
       <c r="H212" t="n">
         <v>1030</v>
@@ -6546,7 +6546,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G213" t="n">
-        <v>2.65091037750244</v>
+        <v>2.65091013908386</v>
       </c>
       <c r="H213" t="n">
         <v>760</v>
@@ -6691,7 +6691,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G218" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H218" t="n">
         <v>488</v>
@@ -6749,7 +6749,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G220" t="n">
-        <v>2.85626268386841</v>
+        <v>2.85626244544983</v>
       </c>
       <c r="H220" t="n">
         <v>4706</v>
@@ -6894,7 +6894,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G225" t="n">
-        <v>2.73491835594177</v>
+        <v>2.73491787910461</v>
       </c>
       <c r="H225" t="n">
         <v>823</v>
@@ -7097,7 +7097,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G232" t="n">
-        <v>2.65091037750244</v>
+        <v>2.65091013908386</v>
       </c>
       <c r="H232" t="n">
         <v>1146</v>
@@ -7126,7 +7126,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>2.76292037963867</v>
+        <v>2.76292061805725</v>
       </c>
       <c r="H233" t="n">
         <v>2100</v>
@@ -7213,7 +7213,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G236" t="n">
-        <v>2.75358653068542</v>
+        <v>2.753586769104</v>
       </c>
       <c r="H236" t="n">
         <v>2835</v>
@@ -7271,7 +7271,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G238" t="n">
-        <v>2.85626268386841</v>
+        <v>2.85626244544983</v>
       </c>
       <c r="H238" t="n">
         <v>3815</v>
@@ -7300,7 +7300,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G239" t="n">
-        <v>2.85626268386841</v>
+        <v>2.85626244544983</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G247" t="n">
-        <v>2.91226768493652</v>
+        <v>2.91226744651794</v>
       </c>
       <c r="H247" t="n">
         <v>1679</v>
@@ -7561,7 +7561,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G248" t="n">
-        <v>2.97760701179504</v>
+        <v>2.97760725021362</v>
       </c>
       <c r="H248" t="n">
         <v>6756</v>
@@ -7590,7 +7590,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G249" t="n">
-        <v>2.88426518440247</v>
+        <v>2.88426494598389</v>
       </c>
       <c r="H249" t="n">
         <v>3107</v>
@@ -8083,7 +8083,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G266" t="n">
-        <v>2.6229076385498</v>
+        <v>2.62290787696838</v>
       </c>
       <c r="H266" t="n">
         <v>2300</v>
@@ -8141,7 +8141,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G268" t="n">
-        <v>2.63224172592163</v>
+        <v>2.63224196434021</v>
       </c>
       <c r="H268" t="n">
         <v>1640</v>
@@ -8199,7 +8199,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G270" t="n">
-        <v>2.6229076385498</v>
+        <v>2.62290787696838</v>
       </c>
       <c r="H270" t="n">
         <v>626</v>
@@ -8286,7 +8286,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G273" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H273" t="n">
         <v>3807</v>
@@ -8315,7 +8315,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G274" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H274" t="n">
         <v>12686</v>
@@ -8344,7 +8344,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G275" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H275" t="n">
         <v>3412</v>
@@ -8402,7 +8402,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G277" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H277" t="n">
         <v>689</v>
@@ -8431,7 +8431,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G278" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H278" t="n">
         <v>0</v>
@@ -8460,7 +8460,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G279" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H279" t="n">
         <v>1890</v>
@@ -8489,7 +8489,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G280" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H280" t="n">
         <v>3085</v>
@@ -8547,7 +8547,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G282" t="n">
-        <v>2.48289489746094</v>
+        <v>2.48289513587952</v>
       </c>
       <c r="H282" t="n">
         <v>1691</v>
@@ -8605,7 +8605,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G284" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H284" t="n">
         <v>550</v>
@@ -8634,7 +8634,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G285" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H285" t="n">
         <v>437</v>
@@ -8663,7 +8663,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G286" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H286" t="n">
         <v>155</v>
@@ -8808,7 +8808,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G291" t="n">
-        <v>2.6229076385498</v>
+        <v>2.62290787696838</v>
       </c>
       <c r="H291" t="n">
         <v>32348</v>
@@ -8924,7 +8924,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G295" t="n">
-        <v>2.54823446273804</v>
+        <v>2.54823422431946</v>
       </c>
       <c r="H295" t="n">
         <v>1050</v>
@@ -8982,7 +8982,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G297" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H297" t="n">
         <v>238</v>
@@ -9011,7 +9011,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G298" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H298" t="n">
         <v>0</v>
@@ -9272,7 +9272,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G307" t="n">
-        <v>2.50156354904175</v>
+        <v>2.50156331062317</v>
       </c>
       <c r="H307" t="n">
         <v>7083</v>
@@ -9301,7 +9301,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G308" t="n">
-        <v>2.46422672271729</v>
+        <v>2.46422648429871</v>
       </c>
       <c r="H308" t="n">
         <v>982</v>
@@ -9388,7 +9388,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G311" t="n">
-        <v>2.48289489746094</v>
+        <v>2.48289513587952</v>
       </c>
       <c r="H311" t="n">
         <v>204</v>
@@ -9417,7 +9417,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G312" t="n">
-        <v>2.48289489746094</v>
+        <v>2.48289513587952</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G313" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H313" t="n">
         <v>350</v>
@@ -9504,7 +9504,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G315" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H315" t="n">
         <v>500</v>
@@ -9533,7 +9533,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G316" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H316" t="n">
         <v>2033</v>
@@ -9620,7 +9620,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G319" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H319" t="n">
         <v>50</v>
@@ -9649,7 +9649,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G320" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H320" t="n">
         <v>110</v>
@@ -9678,7 +9678,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G321" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H321" t="n">
         <v>3920</v>
@@ -9765,7 +9765,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G324" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H324" t="n">
         <v>1280</v>
@@ -9794,7 +9794,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G325" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G326" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H326" t="n">
         <v>4022</v>
@@ -9852,7 +9852,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H327" t="n">
         <v>7005</v>
@@ -9910,7 +9910,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G329" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H329" t="n">
         <v>2690</v>
@@ -9939,7 +9939,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G330" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -9968,7 +9968,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G331" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -9997,7 +9997,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G332" t="n">
-        <v>2.27754259109497</v>
+        <v>2.27754282951355</v>
       </c>
       <c r="H332" t="n">
         <v>2310</v>
@@ -10055,7 +10055,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G334" t="n">
-        <v>2.24020600318909</v>
+        <v>2.24020576477051</v>
       </c>
       <c r="H334" t="n">
         <v>4089</v>
@@ -10113,7 +10113,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G336" t="n">
-        <v>2.26820874214172</v>
+        <v>2.26820850372314</v>
       </c>
       <c r="H336" t="n">
         <v>12996</v>
@@ -10142,7 +10142,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G337" t="n">
-        <v>2.24020600318909</v>
+        <v>2.24020576477051</v>
       </c>
       <c r="H337" t="n">
         <v>15170</v>
@@ -10200,7 +10200,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G339" t="n">
-        <v>2.1281955242157</v>
+        <v>2.12819576263428</v>
       </c>
       <c r="H339" t="n">
         <v>35672</v>
@@ -10287,7 +10287,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>2.06285619735718</v>
+        <v>2.06285643577576</v>
       </c>
       <c r="H342" t="n">
         <v>15756</v>
@@ -10316,7 +10316,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G343" t="n">
-        <v>1.98818278312683</v>
+        <v>1.98818302154541</v>
       </c>
       <c r="H343" t="n">
         <v>9524</v>
@@ -10461,7 +10461,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G348" t="n">
-        <v>1.76416218280792</v>
+        <v>1.76416206359863</v>
       </c>
       <c r="H348" t="n">
         <v>3234</v>
@@ -10548,7 +10548,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G351" t="n">
-        <v>1.57747828960419</v>
+        <v>1.57747840881348</v>
       </c>
       <c r="H351" t="n">
         <v>44141</v>
@@ -10838,7 +10838,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G361" t="n">
-        <v>1.66148602962494</v>
+        <v>1.66148614883423</v>
       </c>
       <c r="H361" t="n">
         <v>186911</v>
@@ -10896,7 +10896,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G363" t="n">
-        <v>1.84816980361938</v>
+        <v>1.84817004203796</v>
       </c>
       <c r="H363" t="n">
         <v>74595</v>
@@ -10954,7 +10954,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G365" t="n">
-        <v>1.94151175022125</v>
+        <v>1.94151163101196</v>
       </c>
       <c r="H365" t="n">
         <v>38866</v>
@@ -10983,7 +10983,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G366" t="n">
-        <v>2.02551984786987</v>
+        <v>2.02551937103271</v>
       </c>
       <c r="H366" t="n">
         <v>41167</v>
@@ -11012,7 +11012,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G367" t="n">
-        <v>2.06285619735718</v>
+        <v>2.06285643577576</v>
       </c>
       <c r="H367" t="n">
         <v>65581</v>
@@ -11070,7 +11070,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G369" t="n">
-        <v>2.1281955242157</v>
+        <v>2.12819576263428</v>
       </c>
       <c r="H369" t="n">
         <v>27238</v>
@@ -11157,7 +11157,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G372" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H372" t="n">
         <v>100574</v>
@@ -11186,7 +11186,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G373" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H373" t="n">
         <v>50734</v>
@@ -11215,7 +11215,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G374" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H374" t="n">
         <v>32104</v>
@@ -11273,7 +11273,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G376" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H376" t="n">
         <v>260524</v>
@@ -11418,7 +11418,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G381" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H381" t="n">
         <v>13489</v>
@@ -11447,7 +11447,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G382" t="n">
-        <v>2.50156354904175</v>
+        <v>2.50156331062317</v>
       </c>
       <c r="H382" t="n">
         <v>22219</v>
@@ -11476,7 +11476,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G383" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H383" t="n">
         <v>19181</v>
@@ -11505,7 +11505,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G384" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H384" t="n">
         <v>46528</v>
@@ -11592,7 +11592,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G387" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H387" t="n">
         <v>20692</v>
@@ -11737,7 +11737,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G392" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H392" t="n">
         <v>78496</v>
@@ -11766,7 +11766,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G393" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H393" t="n">
         <v>2710</v>
@@ -11853,7 +11853,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G396" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H396" t="n">
         <v>3361</v>
@@ -11882,7 +11882,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G397" t="n">
-        <v>2.27754259109497</v>
+        <v>2.27754282951355</v>
       </c>
       <c r="H397" t="n">
         <v>70461</v>
@@ -11911,7 +11911,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H398" t="n">
         <v>4671</v>
@@ -11940,7 +11940,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G399" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H399" t="n">
         <v>20075</v>
@@ -11969,7 +11969,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G400" t="n">
-        <v>2.20286917686462</v>
+        <v>2.20286893844604</v>
       </c>
       <c r="H400" t="n">
         <v>35084</v>
@@ -11998,7 +11998,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G401" t="n">
-        <v>2.07219052314758</v>
+        <v>2.072190284729</v>
       </c>
       <c r="H401" t="n">
         <v>51398</v>
@@ -12201,7 +12201,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G408" t="n">
-        <v>2.20286917686462</v>
+        <v>2.20286893844604</v>
       </c>
       <c r="H408" t="n">
         <v>20357</v>
@@ -12375,7 +12375,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G414" t="n">
-        <v>2.08152461051941</v>
+        <v>2.08152484893799</v>
       </c>
       <c r="H414" t="n">
         <v>6065</v>
@@ -12462,7 +12462,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G417" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H417" t="n">
         <v>112741</v>
@@ -12491,7 +12491,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G418" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H418" t="n">
         <v>31183</v>
@@ -12520,7 +12520,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G419" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H419" t="n">
         <v>24246</v>
@@ -12607,7 +12607,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G422" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H422" t="n">
         <v>15411</v>
@@ -12665,7 +12665,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G424" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H424" t="n">
         <v>4139</v>
@@ -12723,7 +12723,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G426" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H426" t="n">
         <v>6863</v>
@@ -12752,7 +12752,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G427" t="n">
-        <v>2.26820874214172</v>
+        <v>2.26820850372314</v>
       </c>
       <c r="H427" t="n">
         <v>8209</v>
@@ -12781,7 +12781,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G428" t="n">
-        <v>2.27754259109497</v>
+        <v>2.27754282951355</v>
       </c>
       <c r="H428" t="n">
         <v>8879</v>
@@ -12810,7 +12810,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G429" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H429" t="n">
         <v>17663</v>
@@ -12839,7 +12839,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G430" t="n">
-        <v>2.25887441635132</v>
+        <v>2.2588746547699</v>
       </c>
       <c r="H430" t="n">
         <v>8648</v>
@@ -12868,7 +12868,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G431" t="n">
-        <v>2.25887441635132</v>
+        <v>2.2588746547699</v>
       </c>
       <c r="H431" t="n">
         <v>10630</v>
@@ -12897,7 +12897,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G432" t="n">
-        <v>2.27754259109497</v>
+        <v>2.27754282951355</v>
       </c>
       <c r="H432" t="n">
         <v>5782</v>
@@ -12926,7 +12926,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G433" t="n">
-        <v>2.25887441635132</v>
+        <v>2.2588746547699</v>
       </c>
       <c r="H433" t="n">
         <v>39250</v>
@@ -12955,7 +12955,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G434" t="n">
-        <v>2.24020600318909</v>
+        <v>2.24020576477051</v>
       </c>
       <c r="H434" t="n">
         <v>3580</v>
@@ -13013,7 +13013,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G436" t="n">
-        <v>2.27754259109497</v>
+        <v>2.27754282951355</v>
       </c>
       <c r="H436" t="n">
         <v>3250</v>
@@ -13042,7 +13042,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G437" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H437" t="n">
         <v>10145</v>
@@ -13071,7 +13071,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G438" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H438" t="n">
         <v>40576</v>
@@ -13100,7 +13100,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G439" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H439" t="n">
         <v>6378</v>
@@ -13158,7 +13158,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G441" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H441" t="n">
         <v>4745</v>
@@ -13216,7 +13216,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G443" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H443" t="n">
         <v>10240</v>
@@ -13274,7 +13274,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G445" t="n">
-        <v>2.23087167739868</v>
+        <v>2.23087191581726</v>
       </c>
       <c r="H445" t="n">
         <v>29277</v>
@@ -13303,7 +13303,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G446" t="n">
-        <v>2.23087167739868</v>
+        <v>2.23087191581726</v>
       </c>
       <c r="H446" t="n">
         <v>37961</v>
@@ -13332,7 +13332,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G447" t="n">
-        <v>2.27754259109497</v>
+        <v>2.27754282951355</v>
       </c>
       <c r="H447" t="n">
         <v>53947</v>
@@ -13361,7 +13361,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G448" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H448" t="n">
         <v>75506</v>
@@ -13419,7 +13419,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G450" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H450" t="n">
         <v>45849</v>
@@ -13738,7 +13738,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G461" t="n">
-        <v>2.73491835594177</v>
+        <v>2.73491787910461</v>
       </c>
       <c r="H461" t="n">
         <v>18508</v>
@@ -13854,7 +13854,7 @@
         <v>3.25</v>
       </c>
       <c r="G465" t="n">
-        <v>3.03361225128174</v>
+        <v>3.03361201286316</v>
       </c>
       <c r="H465" t="n">
         <v>83242</v>
@@ -13912,7 +13912,7 @@
         <v>3.25</v>
       </c>
       <c r="G467" t="n">
-        <v>3.03361225128174</v>
+        <v>3.03361201286316</v>
       </c>
       <c r="H467" t="n">
         <v>62595</v>
@@ -13941,7 +13941,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G468" t="n">
-        <v>3.08028316497803</v>
+        <v>3.08028292655945</v>
       </c>
       <c r="H468" t="n">
         <v>39566</v>
@@ -13970,7 +13970,7 @@
         <v>3.25</v>
       </c>
       <c r="G469" t="n">
-        <v>3.03361225128174</v>
+        <v>3.03361201286316</v>
       </c>
       <c r="H469" t="n">
         <v>22979</v>
@@ -14028,7 +14028,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G471" t="n">
-        <v>3.27630138397217</v>
+        <v>3.27630114555359</v>
       </c>
       <c r="H471" t="n">
         <v>27454</v>
@@ -14086,7 +14086,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G473" t="n">
-        <v>3.3323061466217</v>
+        <v>3.33230638504028</v>
       </c>
       <c r="H473" t="n">
         <v>14421</v>
@@ -14144,7 +14144,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G475" t="n">
-        <v>3.2296302318573</v>
+        <v>3.22962999343872</v>
       </c>
       <c r="H475" t="n">
         <v>13099</v>
@@ -14202,7 +14202,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G477" t="n">
-        <v>3.11761975288391</v>
+        <v>3.11761999130249</v>
       </c>
       <c r="H477" t="n">
         <v>29958</v>
@@ -14289,7 +14289,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G480" t="n">
-        <v>3.20162773132324</v>
+        <v>3.20162796974182</v>
       </c>
       <c r="H480" t="n">
         <v>55118</v>
@@ -14347,7 +14347,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G482" t="n">
-        <v>3.08961749076843</v>
+        <v>3.08961725234985</v>
       </c>
       <c r="H482" t="n">
         <v>34183</v>
@@ -14376,7 +14376,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G483" t="n">
-        <v>3.12695384025574</v>
+        <v>3.12695407867432</v>
       </c>
       <c r="H483" t="n">
         <v>32378</v>
@@ -14434,7 +14434,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G485" t="n">
-        <v>3.15495657920837</v>
+        <v>3.15495681762695</v>
       </c>
       <c r="H485" t="n">
         <v>12813</v>
@@ -14550,7 +14550,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G489" t="n">
-        <v>3.11761975288391</v>
+        <v>3.11761999130249</v>
       </c>
       <c r="H489" t="n">
         <v>17075</v>
@@ -14579,7 +14579,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G490" t="n">
-        <v>3.08028316497803</v>
+        <v>3.08028292655945</v>
       </c>
       <c r="H490" t="n">
         <v>17126</v>
@@ -14637,7 +14637,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G492" t="n">
-        <v>2.97760701179504</v>
+        <v>2.97760725021362</v>
       </c>
       <c r="H492" t="n">
         <v>12648</v>
@@ -14666,7 +14666,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G493" t="n">
-        <v>3.04294657707214</v>
+        <v>3.04294633865356</v>
       </c>
       <c r="H493" t="n">
         <v>3499</v>
@@ -14753,7 +14753,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G496" t="n">
-        <v>3.08028316497803</v>
+        <v>3.08028292655945</v>
       </c>
       <c r="H496" t="n">
         <v>39248</v>
@@ -14782,7 +14782,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G497" t="n">
-        <v>3.08028316497803</v>
+        <v>3.08028292655945</v>
       </c>
       <c r="H497" t="n">
         <v>17788</v>
@@ -14840,7 +14840,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G499" t="n">
-        <v>3.11761975288391</v>
+        <v>3.11761999130249</v>
       </c>
       <c r="H499" t="n">
         <v>21907</v>
@@ -14869,7 +14869,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G500" t="n">
-        <v>3.11761975288391</v>
+        <v>3.11761999130249</v>
       </c>
       <c r="H500" t="n">
         <v>17501</v>
@@ -14956,7 +14956,7 @@
         <v>3.25</v>
       </c>
       <c r="G503" t="n">
-        <v>3.03361225128174</v>
+        <v>3.03361201286316</v>
       </c>
       <c r="H503" t="n">
         <v>5248</v>
@@ -14985,7 +14985,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G504" t="n">
-        <v>3.02427792549133</v>
+        <v>3.02427816390991</v>
       </c>
       <c r="H504" t="n">
         <v>20370</v>
@@ -15130,7 +15130,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G509" t="n">
-        <v>2.96827292442322</v>
+        <v>2.9682731628418</v>
       </c>
       <c r="H509" t="n">
         <v>5868</v>
@@ -15391,7 +15391,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G518" t="n">
-        <v>2.73491835594177</v>
+        <v>2.73491787910461</v>
       </c>
       <c r="H518" t="n">
         <v>15415</v>
@@ -15478,7 +15478,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G521" t="n">
-        <v>2.75358653068542</v>
+        <v>2.753586769104</v>
       </c>
       <c r="H521" t="n">
         <v>5980</v>
@@ -15565,7 +15565,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G524" t="n">
-        <v>2.63224172592163</v>
+        <v>2.63224196434021</v>
       </c>
       <c r="H524" t="n">
         <v>10487</v>
@@ -15710,7 +15710,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G529" t="n">
-        <v>2.46422672271729</v>
+        <v>2.46422648429871</v>
       </c>
       <c r="H529" t="n">
         <v>31873</v>
@@ -15768,7 +15768,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G531" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H531" t="n">
         <v>29110</v>
@@ -15797,7 +15797,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G532" t="n">
-        <v>2.46422672271729</v>
+        <v>2.46422648429871</v>
       </c>
       <c r="H532" t="n">
         <v>14070</v>
@@ -15855,7 +15855,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G534" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H534" t="n">
         <v>58949</v>
@@ -15913,7 +15913,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G536" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H536" t="n">
         <v>18439</v>
@@ -15971,7 +15971,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G538" t="n">
-        <v>2.6229076385498</v>
+        <v>2.62290787696838</v>
       </c>
       <c r="H538" t="n">
         <v>65552</v>
@@ -16000,7 +16000,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G539" t="n">
-        <v>2.6229076385498</v>
+        <v>2.62290787696838</v>
       </c>
       <c r="H539" t="n">
         <v>55945</v>
@@ -16029,7 +16029,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G540" t="n">
-        <v>2.6229076385498</v>
+        <v>2.62290787696838</v>
       </c>
       <c r="H540" t="n">
         <v>32955</v>
@@ -16087,7 +16087,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G542" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H542" t="n">
         <v>34564</v>
@@ -16116,7 +16116,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G543" t="n">
-        <v>2.63224172592163</v>
+        <v>2.63224196434021</v>
       </c>
       <c r="H543" t="n">
         <v>7927</v>
@@ -16145,7 +16145,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G544" t="n">
-        <v>2.54823446273804</v>
+        <v>2.54823422431946</v>
       </c>
       <c r="H544" t="n">
         <v>22371</v>
@@ -16406,7 +16406,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G553" t="n">
-        <v>2.65091037750244</v>
+        <v>2.65091013908386</v>
       </c>
       <c r="H553" t="n">
         <v>17288</v>
@@ -16464,7 +16464,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G555" t="n">
-        <v>2.75358653068542</v>
+        <v>2.753586769104</v>
       </c>
       <c r="H555" t="n">
         <v>44001</v>
@@ -16493,7 +16493,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G556" t="n">
-        <v>2.77225470542908</v>
+        <v>2.77225494384766</v>
       </c>
       <c r="H556" t="n">
         <v>1552</v>
@@ -16522,7 +16522,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G557" t="n">
-        <v>2.77225470542908</v>
+        <v>2.77225494384766</v>
       </c>
       <c r="H557" t="n">
         <v>7892</v>
@@ -16551,7 +16551,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G558" t="n">
-        <v>2.65091037750244</v>
+        <v>2.65091013908386</v>
       </c>
       <c r="H558" t="n">
         <v>16646</v>
@@ -16580,7 +16580,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G559" t="n">
-        <v>2.65091037750244</v>
+        <v>2.65091013908386</v>
       </c>
       <c r="H559" t="n">
         <v>14560</v>
@@ -16638,7 +16638,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G561" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H561" t="n">
         <v>55511</v>
@@ -16899,7 +16899,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G570" t="n">
-        <v>2.77225470542908</v>
+        <v>2.77225494384766</v>
       </c>
       <c r="H570" t="n">
         <v>12140</v>
@@ -17102,7 +17102,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G577" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H577" t="n">
         <v>5655</v>
@@ -17218,7 +17218,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G581" t="n">
-        <v>2.77225470542908</v>
+        <v>2.77225494384766</v>
       </c>
       <c r="H581" t="n">
         <v>1650</v>
@@ -17276,7 +17276,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G583" t="n">
-        <v>2.76292037963867</v>
+        <v>2.76292061805725</v>
       </c>
       <c r="H583" t="n">
         <v>1500</v>
@@ -17450,7 +17450,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G589" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H589" t="n">
         <v>5281</v>
@@ -17508,7 +17508,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G591" t="n">
-        <v>2.77225470542908</v>
+        <v>2.77225494384766</v>
       </c>
       <c r="H591" t="n">
         <v>2450</v>
@@ -17537,7 +17537,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G592" t="n">
-        <v>2.77225470542908</v>
+        <v>2.77225494384766</v>
       </c>
       <c r="H592" t="n">
         <v>0</v>
@@ -17595,7 +17595,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G594" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H594" t="n">
         <v>3352</v>
@@ -17653,7 +17653,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G596" t="n">
-        <v>2.77225470542908</v>
+        <v>2.77225494384766</v>
       </c>
       <c r="H596" t="n">
         <v>850</v>
@@ -17711,7 +17711,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G598" t="n">
-        <v>2.75358653068542</v>
+        <v>2.753586769104</v>
       </c>
       <c r="H598" t="n">
         <v>47530</v>
@@ -17769,7 +17769,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G600" t="n">
-        <v>2.75358653068542</v>
+        <v>2.753586769104</v>
       </c>
       <c r="H600" t="n">
         <v>7623</v>
@@ -17856,7 +17856,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G603" t="n">
-        <v>2.73491835594177</v>
+        <v>2.73491787910461</v>
       </c>
       <c r="H603" t="n">
         <v>6297</v>
@@ -18030,7 +18030,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G609" t="n">
-        <v>2.76292037963867</v>
+        <v>2.76292061805725</v>
       </c>
       <c r="H609" t="n">
         <v>13444</v>
@@ -18059,7 +18059,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G610" t="n">
-        <v>2.77225470542908</v>
+        <v>2.77225494384766</v>
       </c>
       <c r="H610" t="n">
         <v>4440</v>
@@ -18175,7 +18175,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G614" t="n">
-        <v>2.77225470542908</v>
+        <v>2.77225494384766</v>
       </c>
       <c r="H614" t="n">
         <v>20031</v>
@@ -18407,7 +18407,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G622" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H622" t="n">
         <v>9853</v>
@@ -18494,7 +18494,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G625" t="n">
-        <v>2.48289489746094</v>
+        <v>2.48289513587952</v>
       </c>
       <c r="H625" t="n">
         <v>9305</v>
@@ -18523,7 +18523,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G626" t="n">
-        <v>2.50156354904175</v>
+        <v>2.50156331062317</v>
       </c>
       <c r="H626" t="n">
         <v>7546</v>
@@ -18552,7 +18552,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G627" t="n">
-        <v>2.48289489746094</v>
+        <v>2.48289513587952</v>
       </c>
       <c r="H627" t="n">
         <v>3175</v>
@@ -18610,7 +18610,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G629" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H629" t="n">
         <v>9381</v>
@@ -18639,7 +18639,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G630" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H630" t="n">
         <v>5890</v>
@@ -18784,7 +18784,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G635" t="n">
-        <v>2.65091037750244</v>
+        <v>2.65091013908386</v>
       </c>
       <c r="H635" t="n">
         <v>1700</v>
@@ -18871,7 +18871,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G638" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H638" t="n">
         <v>10004</v>
@@ -19045,7 +19045,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G644" t="n">
-        <v>2.50156354904175</v>
+        <v>2.50156331062317</v>
       </c>
       <c r="H644" t="n">
         <v>7248</v>
@@ -19074,7 +19074,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G645" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H645" t="n">
         <v>26536</v>
@@ -19248,7 +19248,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G651" t="n">
-        <v>2.54823446273804</v>
+        <v>2.54823422431946</v>
       </c>
       <c r="H651" t="n">
         <v>1402</v>
@@ -19277,7 +19277,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G652" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H652" t="n">
         <v>6533</v>
@@ -19306,7 +19306,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G653" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H653" t="n">
         <v>6896</v>
@@ -19335,7 +19335,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G654" t="n">
-        <v>2.50156354904175</v>
+        <v>2.50156331062317</v>
       </c>
       <c r="H654" t="n">
         <v>2900</v>
@@ -19393,7 +19393,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H656" t="n">
         <v>5573</v>
@@ -19654,7 +19654,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G665" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H665" t="n">
         <v>1580</v>
@@ -19828,7 +19828,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G671" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H671" t="n">
         <v>1055</v>
@@ -19915,7 +19915,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G674" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H674" t="n">
         <v>1004</v>
@@ -19944,7 +19944,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G675" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H675" t="n">
         <v>0</v>
@@ -20060,7 +20060,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G679" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H679" t="n">
         <v>6131</v>
@@ -20234,7 +20234,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G685" t="n">
-        <v>2.65091037750244</v>
+        <v>2.65091013908386</v>
       </c>
       <c r="H685" t="n">
         <v>3302</v>
@@ -20263,7 +20263,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G686" t="n">
-        <v>2.48289489746094</v>
+        <v>2.48289513587952</v>
       </c>
       <c r="H686" t="n">
         <v>18872</v>
@@ -20321,7 +20321,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G688" t="n">
-        <v>2.50156354904175</v>
+        <v>2.50156331062317</v>
       </c>
       <c r="H688" t="n">
         <v>5477</v>
@@ -20350,7 +20350,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G689" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H689" t="n">
         <v>6459</v>
@@ -20524,7 +20524,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G695" t="n">
-        <v>2.23087167739868</v>
+        <v>2.23087191581726</v>
       </c>
       <c r="H695" t="n">
         <v>25461</v>
@@ -20582,7 +20582,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G697" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H697" t="n">
         <v>5477</v>
@@ -20611,7 +20611,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G698" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H698" t="n">
         <v>4617</v>
@@ -20669,7 +20669,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G700" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H700" t="n">
         <v>10078</v>
@@ -20698,7 +20698,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G701" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H701" t="n">
         <v>11679</v>
@@ -20727,7 +20727,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G702" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H702" t="n">
         <v>12282</v>
@@ -20814,7 +20814,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G705" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H705" t="n">
         <v>7231</v>
@@ -20843,7 +20843,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G706" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H706" t="n">
         <v>16794</v>
@@ -20901,7 +20901,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G708" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H708" t="n">
         <v>11650</v>
@@ -21046,7 +21046,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G713" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H713" t="n">
         <v>5601</v>
@@ -21075,7 +21075,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G714" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H714" t="n">
         <v>3865</v>
@@ -21249,7 +21249,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G720" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H720" t="n">
         <v>2110</v>
@@ -21307,7 +21307,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G722" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H722" t="n">
         <v>20</v>
@@ -21365,7 +21365,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G724" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H724" t="n">
         <v>3000</v>
@@ -21394,7 +21394,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G725" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H725" t="n">
         <v>2583</v>
@@ -21423,7 +21423,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G726" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H726" t="n">
         <v>2</v>
@@ -21452,7 +21452,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G727" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H727" t="n">
         <v>4770</v>
@@ -21481,7 +21481,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G728" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H728" t="n">
         <v>6795</v>
@@ -21539,7 +21539,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G730" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H730" t="n">
         <v>9829</v>
@@ -21655,7 +21655,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G734" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H734" t="n">
         <v>59751</v>
@@ -21713,7 +21713,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G736" t="n">
-        <v>2.24020600318909</v>
+        <v>2.24020576477051</v>
       </c>
       <c r="H736" t="n">
         <v>8673</v>
@@ -21800,7 +21800,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G739" t="n">
-        <v>2.23087167739868</v>
+        <v>2.23087191581726</v>
       </c>
       <c r="H739" t="n">
         <v>4337</v>
@@ -21887,7 +21887,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G742" t="n">
-        <v>2.23087167739868</v>
+        <v>2.23087191581726</v>
       </c>
       <c r="H742" t="n">
         <v>6415</v>
@@ -21974,7 +21974,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G745" t="n">
-        <v>2.20286917686462</v>
+        <v>2.20286893844604</v>
       </c>
       <c r="H745" t="n">
         <v>3400</v>
@@ -22061,7 +22061,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G748" t="n">
-        <v>2.1281955242157</v>
+        <v>2.12819576263428</v>
       </c>
       <c r="H748" t="n">
         <v>9244</v>
@@ -22090,7 +22090,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G749" t="n">
-        <v>2.1281955242157</v>
+        <v>2.12819576263428</v>
       </c>
       <c r="H749" t="n">
         <v>2187</v>
@@ -22322,7 +22322,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G757" t="n">
-        <v>2.15619826316833</v>
+        <v>2.15619802474976</v>
       </c>
       <c r="H757" t="n">
         <v>5</v>
@@ -22351,7 +22351,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G758" t="n">
-        <v>2.24020600318909</v>
+        <v>2.24020576477051</v>
       </c>
       <c r="H758" t="n">
         <v>3859</v>
@@ -22380,7 +22380,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G759" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H759" t="n">
         <v>6674</v>
@@ -22409,7 +22409,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G760" t="n">
-        <v>2.15619826316833</v>
+        <v>2.15619802474976</v>
       </c>
       <c r="H760" t="n">
         <v>9288</v>
@@ -22496,7 +22496,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G763" t="n">
-        <v>2.15619826316833</v>
+        <v>2.15619802474976</v>
       </c>
       <c r="H763" t="n">
         <v>74</v>
@@ -22670,7 +22670,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G769" t="n">
-        <v>2.08152461051941</v>
+        <v>2.08152484893799</v>
       </c>
       <c r="H769" t="n">
         <v>5355</v>
@@ -22699,7 +22699,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G770" t="n">
-        <v>2.08152461051941</v>
+        <v>2.08152484893799</v>
       </c>
       <c r="H770" t="n">
         <v>0</v>
@@ -22902,7 +22902,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G777" t="n">
-        <v>2.00685143470764</v>
+        <v>2.00685119628906</v>
       </c>
       <c r="H777" t="n">
         <v>6782</v>
@@ -22931,7 +22931,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G778" t="n">
-        <v>2.01618552207947</v>
+        <v>2.01618528366089</v>
       </c>
       <c r="H778" t="n">
         <v>3662</v>
@@ -22960,7 +22960,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G779" t="n">
-        <v>2.01618552207947</v>
+        <v>2.01618528366089</v>
       </c>
       <c r="H779" t="n">
         <v>5386</v>
@@ -22989,7 +22989,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G780" t="n">
-        <v>1.99751698970795</v>
+        <v>1.99751710891724</v>
       </c>
       <c r="H780" t="n">
         <v>923</v>
@@ -23018,7 +23018,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G781" t="n">
-        <v>2.02551984786987</v>
+        <v>2.02551937103271</v>
       </c>
       <c r="H781" t="n">
         <v>2701</v>
@@ -23047,7 +23047,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G782" t="n">
-        <v>1.96018004417419</v>
+        <v>1.96018016338348</v>
       </c>
       <c r="H782" t="n">
         <v>4798</v>
@@ -23076,7 +23076,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G783" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H783" t="n">
         <v>16989</v>
@@ -23192,7 +23192,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G787" t="n">
-        <v>1.76416218280792</v>
+        <v>1.76416206359863</v>
       </c>
       <c r="H787" t="n">
         <v>18464</v>
@@ -23221,7 +23221,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G788" t="n">
-        <v>1.76882934570312</v>
+        <v>1.76882922649384</v>
       </c>
       <c r="H788" t="n">
         <v>25213</v>
@@ -23366,7 +23366,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G793" t="n">
-        <v>1.79216480255127</v>
+        <v>1.79216468334198</v>
       </c>
       <c r="H793" t="n">
         <v>26069</v>
@@ -23424,7 +23424,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G795" t="n">
-        <v>1.84816980361938</v>
+        <v>1.84817004203796</v>
       </c>
       <c r="H795" t="n">
         <v>1870</v>
@@ -23569,7 +23569,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G800" t="n">
-        <v>1.82016730308533</v>
+        <v>1.82016742229462</v>
       </c>
       <c r="H800" t="n">
         <v>293</v>
@@ -23743,7 +23743,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H806" t="n">
         <v>2225</v>
@@ -23772,7 +23772,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G807" t="n">
-        <v>1.88550674915314</v>
+        <v>1.88550662994385</v>
       </c>
       <c r="H807" t="n">
         <v>530</v>
@@ -23975,7 +23975,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G814" t="n">
-        <v>1.98818278312683</v>
+        <v>1.98818302154541</v>
       </c>
       <c r="H814" t="n">
         <v>5130</v>
@@ -24004,7 +24004,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G815" t="n">
-        <v>1.98818278312683</v>
+        <v>1.98818302154541</v>
       </c>
       <c r="H815" t="n">
         <v>13633</v>
@@ -24033,7 +24033,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G816" t="n">
-        <v>1.978848695755</v>
+        <v>1.97884833812714</v>
       </c>
       <c r="H816" t="n">
         <v>18908</v>
@@ -24120,7 +24120,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G819" t="n">
-        <v>1.94151175022125</v>
+        <v>1.94151163101196</v>
       </c>
       <c r="H819" t="n">
         <v>4235</v>
@@ -24236,7 +24236,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G823" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H823" t="n">
         <v>2258</v>
@@ -24265,7 +24265,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G824" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H824" t="n">
         <v>0</v>
@@ -24323,7 +24323,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G826" t="n">
-        <v>2.02551984786987</v>
+        <v>2.02551937103271</v>
       </c>
       <c r="H826" t="n">
         <v>12498</v>
@@ -24352,7 +24352,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G827" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H827" t="n">
         <v>15383</v>
@@ -24381,7 +24381,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G828" t="n">
-        <v>1.88550674915314</v>
+        <v>1.88550662994385</v>
       </c>
       <c r="H828" t="n">
         <v>2410</v>
@@ -24410,7 +24410,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G829" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H829" t="n">
         <v>4980</v>
@@ -24468,7 +24468,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G831" t="n">
-        <v>1.84816980361938</v>
+        <v>1.84817004203796</v>
       </c>
       <c r="H831" t="n">
         <v>1282</v>
@@ -24526,7 +24526,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G833" t="n">
-        <v>1.88550674915314</v>
+        <v>1.88550662994385</v>
       </c>
       <c r="H833" t="n">
         <v>500</v>
@@ -24671,7 +24671,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G838" t="n">
-        <v>1.82016730308533</v>
+        <v>1.82016742229462</v>
       </c>
       <c r="H838" t="n">
         <v>2308</v>
@@ -24787,7 +24787,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G842" t="n">
-        <v>1.79216480255127</v>
+        <v>1.79216468334198</v>
       </c>
       <c r="H842" t="n">
         <v>5998</v>
@@ -24845,7 +24845,7 @@
         <v>1.875</v>
       </c>
       <c r="G844" t="n">
-        <v>1.7501608133316</v>
+        <v>1.75016093254089</v>
       </c>
       <c r="H844" t="n">
         <v>17976</v>
@@ -25048,7 +25048,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G851" t="n">
-        <v>1.79216480255127</v>
+        <v>1.79216468334198</v>
       </c>
       <c r="H851" t="n">
         <v>8829</v>
@@ -25106,7 +25106,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G853" t="n">
-        <v>1.82016730308533</v>
+        <v>1.82016742229462</v>
       </c>
       <c r="H853" t="n">
         <v>4615</v>
@@ -25251,7 +25251,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G858" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H858" t="n">
         <v>1659</v>
@@ -25309,7 +25309,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G860" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H860" t="n">
         <v>5149</v>
@@ -25425,7 +25425,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G864" t="n">
-        <v>1.84816980361938</v>
+        <v>1.84817004203796</v>
       </c>
       <c r="H864" t="n">
         <v>1500</v>
@@ -25570,7 +25570,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G869" t="n">
-        <v>1.88550674915314</v>
+        <v>1.88550662994385</v>
       </c>
       <c r="H869" t="n">
         <v>4311</v>
@@ -25599,7 +25599,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G870" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H870" t="n">
         <v>5440</v>
@@ -25628,7 +25628,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G871" t="n">
-        <v>1.94151175022125</v>
+        <v>1.94151163101196</v>
       </c>
       <c r="H871" t="n">
         <v>830</v>
@@ -25744,7 +25744,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G875" t="n">
-        <v>1.88550674915314</v>
+        <v>1.88550662994385</v>
       </c>
       <c r="H875" t="n">
         <v>7617</v>
@@ -25947,7 +25947,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G882" t="n">
-        <v>1.94151175022125</v>
+        <v>1.94151163101196</v>
       </c>
       <c r="H882" t="n">
         <v>5000</v>
@@ -25976,7 +25976,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G883" t="n">
-        <v>1.94151175022125</v>
+        <v>1.94151163101196</v>
       </c>
       <c r="H883" t="n">
         <v>1500</v>
@@ -26034,7 +26034,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H885" t="n">
         <v>6104</v>
@@ -26092,7 +26092,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G887" t="n">
-        <v>1.94151175022125</v>
+        <v>1.94151163101196</v>
       </c>
       <c r="H887" t="n">
         <v>3600</v>
@@ -26121,7 +26121,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G888" t="n">
-        <v>1.94151175022125</v>
+        <v>1.94151163101196</v>
       </c>
       <c r="H888" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G891" t="n">
-        <v>1.94151175022125</v>
+        <v>1.94151163101196</v>
       </c>
       <c r="H891" t="n">
         <v>3305</v>
@@ -26266,7 +26266,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G893" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H893" t="n">
         <v>2300</v>
@@ -26411,7 +26411,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G898" t="n">
-        <v>2.20286917686462</v>
+        <v>2.20286893844604</v>
       </c>
       <c r="H898" t="n">
         <v>36211</v>
@@ -26469,7 +26469,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G900" t="n">
-        <v>2.23087167739868</v>
+        <v>2.23087191581726</v>
       </c>
       <c r="H900" t="n">
         <v>18041</v>
@@ -26498,7 +26498,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G901" t="n">
-        <v>2.25887441635132</v>
+        <v>2.2588746547699</v>
       </c>
       <c r="H901" t="n">
         <v>13774</v>
@@ -26527,7 +26527,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G902" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H902" t="n">
         <v>9996</v>
@@ -26556,7 +26556,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G903" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H903" t="n">
         <v>12989</v>
@@ -26614,7 +26614,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G905" t="n">
-        <v>2.23087167739868</v>
+        <v>2.23087191581726</v>
       </c>
       <c r="H905" t="n">
         <v>12451</v>
@@ -26643,7 +26643,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G906" t="n">
-        <v>2.23087167739868</v>
+        <v>2.23087191581726</v>
       </c>
       <c r="H906" t="n">
         <v>1897</v>
@@ -26672,7 +26672,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G907" t="n">
-        <v>2.25887441635132</v>
+        <v>2.2588746547699</v>
       </c>
       <c r="H907" t="n">
         <v>2583</v>
@@ -26701,7 +26701,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G908" t="n">
-        <v>2.23087167739868</v>
+        <v>2.23087191581726</v>
       </c>
       <c r="H908" t="n">
         <v>1500</v>
@@ -26730,7 +26730,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G909" t="n">
-        <v>2.27754259109497</v>
+        <v>2.27754282951355</v>
       </c>
       <c r="H909" t="n">
         <v>4836</v>
@@ -26759,7 +26759,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G910" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H910" t="n">
         <v>2850</v>
@@ -26962,7 +26962,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G917" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H917" t="n">
         <v>3029</v>
@@ -27020,7 +27020,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G919" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H919" t="n">
         <v>3027</v>
@@ -27078,7 +27078,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G921" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H921" t="n">
         <v>2800</v>
@@ -27107,7 +27107,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G922" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H922" t="n">
         <v>2840</v>
@@ -27136,7 +27136,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G923" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H923" t="n">
         <v>2275</v>
@@ -27165,7 +27165,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G924" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H924" t="n">
         <v>2811</v>
@@ -27194,7 +27194,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G925" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H925" t="n">
         <v>10000</v>
@@ -27252,7 +27252,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G927" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H927" t="n">
         <v>13666</v>
@@ -27339,7 +27339,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G930" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H930" t="n">
         <v>2560</v>
@@ -27455,7 +27455,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G934" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H934" t="n">
         <v>18035</v>
@@ -27513,7 +27513,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G936" t="n">
-        <v>2.20286917686462</v>
+        <v>2.20286893844604</v>
       </c>
       <c r="H936" t="n">
         <v>6398</v>
@@ -27542,7 +27542,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G937" t="n">
-        <v>2.24020600318909</v>
+        <v>2.24020576477051</v>
       </c>
       <c r="H937" t="n">
         <v>5629</v>
@@ -27571,7 +27571,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G938" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H938" t="n">
         <v>36604</v>
@@ -27600,7 +27600,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G939" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H939" t="n">
         <v>14446</v>
@@ -27687,7 +27687,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G942" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H942" t="n">
         <v>24000</v>
@@ -27716,7 +27716,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G943" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H943" t="n">
         <v>10884</v>
@@ -27861,7 +27861,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G948" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H948" t="n">
         <v>2000</v>
@@ -27919,7 +27919,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G950" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H950" t="n">
         <v>2715</v>
@@ -27948,7 +27948,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G951" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H951" t="n">
         <v>3000</v>
@@ -28064,7 +28064,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G955" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H955" t="n">
         <v>1000</v>
@@ -28093,7 +28093,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G956" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H956" t="n">
         <v>4601</v>
@@ -28122,7 +28122,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G957" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H957" t="n">
         <v>2000</v>
@@ -28209,7 +28209,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G960" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H960" t="n">
         <v>8263</v>
@@ -28267,7 +28267,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G962" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H962" t="n">
         <v>1000</v>
@@ -28354,7 +28354,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G965" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H965" t="n">
         <v>21</v>
@@ -28383,7 +28383,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G966" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H966" t="n">
         <v>6028</v>
@@ -28644,7 +28644,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G975" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H975" t="n">
         <v>5517</v>
@@ -28702,7 +28702,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G977" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H977" t="n">
         <v>2500</v>
@@ -28731,7 +28731,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G978" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H978" t="n">
         <v>4636</v>
@@ -28818,7 +28818,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G981" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H981" t="n">
         <v>3499</v>
@@ -28905,7 +28905,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G984" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H984" t="n">
         <v>1677</v>
@@ -29427,7 +29427,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1002" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H1002" t="n">
         <v>3900</v>
@@ -29514,7 +29514,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1005" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H1005" t="n">
         <v>642</v>
@@ -29543,7 +29543,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H1006" t="n">
         <v>2020</v>
@@ -29630,7 +29630,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1009" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H1009" t="n">
         <v>1826</v>
@@ -29688,7 +29688,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1011" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H1011" t="n">
         <v>3388</v>
@@ -29978,7 +29978,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1021" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H1021" t="n">
         <v>942</v>
@@ -30065,7 +30065,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1024" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H1024" t="n">
         <v>1010</v>
@@ -30239,7 +30239,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1030" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H1030" t="n">
         <v>1301</v>
@@ -30268,7 +30268,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1031" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H1031" t="n">
         <v>2233</v>
@@ -30297,7 +30297,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1032" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H1032" t="n">
         <v>200</v>
@@ -30326,7 +30326,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1033" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H1033" t="n">
         <v>939</v>
@@ -30413,7 +30413,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1036" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H1036" t="n">
         <v>1101</v>
@@ -30558,7 +30558,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1041" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H1041" t="n">
         <v>15334</v>
@@ -30587,7 +30587,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1042" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H1042" t="n">
         <v>548</v>
@@ -30616,7 +30616,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1043" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H1043" t="n">
         <v>7200</v>
@@ -30645,7 +30645,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1044" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H1044" t="n">
         <v>0</v>
@@ -30877,7 +30877,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1052" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H1052" t="n">
         <v>6417</v>
@@ -31138,7 +31138,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1061" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H1061" t="n">
         <v>6</v>
@@ -31196,7 +31196,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1063" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H1063" t="n">
         <v>2460</v>
@@ -31225,7 +31225,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1064" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H1064" t="n">
         <v>0</v>
@@ -31254,7 +31254,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1065" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H1065" t="n">
         <v>7276</v>
@@ -31283,7 +31283,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H1066" t="n">
         <v>5691</v>
@@ -31312,7 +31312,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H1067" t="n">
         <v>400</v>
@@ -31457,7 +31457,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1072" t="n">
-        <v>2.65091037750244</v>
+        <v>2.65091013908386</v>
       </c>
       <c r="H1072" t="n">
         <v>188026</v>
@@ -32095,7 +32095,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.6229076385498</v>
+        <v>2.62290787696838</v>
       </c>
       <c r="H1094" t="n">
         <v>16861</v>
@@ -32124,7 +32124,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1095" t="n">
         <v>2654</v>
@@ -32443,7 +32443,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1106" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1106" t="n">
         <v>200</v>
@@ -32501,7 +32501,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1108" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1108" t="n">
         <v>1000</v>
@@ -32530,7 +32530,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1109" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1109" t="n">
         <v>1587</v>
@@ -32559,7 +32559,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1110" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1110" t="n">
         <v>2194</v>
@@ -32617,7 +32617,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1112" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1112" t="n">
         <v>3440</v>
@@ -32646,7 +32646,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1113" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1113" t="n">
         <v>0</v>
@@ -32675,7 +32675,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1114" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1114" t="n">
         <v>3456</v>
@@ -32704,7 +32704,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1115" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1115" t="n">
         <v>0</v>
@@ -32849,7 +32849,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1120" t="n">
-        <v>2.63224172592163</v>
+        <v>2.63224196434021</v>
       </c>
       <c r="H1120" t="n">
         <v>3502</v>
@@ -33023,7 +33023,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1126" t="n">
-        <v>2.75358653068542</v>
+        <v>2.753586769104</v>
       </c>
       <c r="H1126" t="n">
         <v>11211</v>
@@ -33516,7 +33516,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1143" t="n">
-        <v>2.85626268386841</v>
+        <v>2.85626244544983</v>
       </c>
       <c r="H1143" t="n">
         <v>15530</v>
@@ -33661,7 +33661,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1148" t="n">
-        <v>2.91226768493652</v>
+        <v>2.91226744651794</v>
       </c>
       <c r="H1148" t="n">
         <v>1813</v>
@@ -33690,7 +33690,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1149" t="n">
-        <v>2.92160201072693</v>
+        <v>2.92160224914551</v>
       </c>
       <c r="H1149" t="n">
         <v>3909</v>
@@ -33835,7 +33835,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1154" t="n">
-        <v>2.85626268386841</v>
+        <v>2.85626244544983</v>
       </c>
       <c r="H1154" t="n">
         <v>3063</v>
@@ -33951,7 +33951,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1158" t="n">
-        <v>2.91226768493652</v>
+        <v>2.91226744651794</v>
       </c>
       <c r="H1158" t="n">
         <v>950</v>
@@ -34038,7 +34038,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1161" t="n">
-        <v>2.88426518440247</v>
+        <v>2.88426494598389</v>
       </c>
       <c r="H1161" t="n">
         <v>2639</v>
@@ -34096,7 +34096,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1163" t="n">
-        <v>2.96827292442322</v>
+        <v>2.9682731628418</v>
       </c>
       <c r="H1163" t="n">
         <v>21970</v>
@@ -34212,7 +34212,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.20162773132324</v>
+        <v>3.20162796974182</v>
       </c>
       <c r="H1167" t="n">
         <v>24299</v>
@@ -34241,7 +34241,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.18295931816101</v>
+        <v>3.18295907974243</v>
       </c>
       <c r="H1168" t="n">
         <v>4144</v>
@@ -34270,7 +34270,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.18295931816101</v>
+        <v>3.18295907974243</v>
       </c>
       <c r="H1169" t="n">
         <v>7563</v>
@@ -34299,7 +34299,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.2296302318573</v>
+        <v>3.22962999343872</v>
       </c>
       <c r="H1170" t="n">
         <v>8410</v>
@@ -34328,7 +34328,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.28563523292542</v>
+        <v>3.28563547134399</v>
       </c>
       <c r="H1171" t="n">
         <v>9302</v>
@@ -34444,7 +34444,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.44431686401367</v>
+        <v>3.44431662559509</v>
       </c>
       <c r="H1175" t="n">
         <v>13251</v>
@@ -34589,7 +34589,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1180" t="n">
-        <v>4.00436782836914</v>
+        <v>4.0043683052063</v>
       </c>
       <c r="H1180" t="n">
         <v>86548</v>
@@ -34618,7 +34618,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1181" t="n">
-        <v>4.26572513580322</v>
+        <v>4.26572561264038</v>
       </c>
       <c r="H1181" t="n">
         <v>61743</v>
@@ -34647,7 +34647,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1182" t="n">
-        <v>4.46174335479736</v>
+        <v>4.46174383163452</v>
       </c>
       <c r="H1182" t="n">
         <v>47140</v>
@@ -34763,7 +34763,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1186" t="n">
-        <v>4.85377883911133</v>
+        <v>4.85377931594849</v>
       </c>
       <c r="H1186" t="n">
         <v>39631</v>
@@ -34850,7 +34850,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1189" t="n">
-        <v>4.51774883270264</v>
+        <v>4.51774930953979</v>
       </c>
       <c r="H1189" t="n">
         <v>67215</v>
@@ -34908,7 +34908,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1191" t="n">
-        <v>4.50841474533081</v>
+        <v>4.50841426849365</v>
       </c>
       <c r="H1191" t="n">
         <v>16999</v>
@@ -34966,7 +34966,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1193" t="n">
-        <v>4.46174335479736</v>
+        <v>4.46174383163452</v>
       </c>
       <c r="H1193" t="n">
         <v>24861</v>
@@ -35024,7 +35024,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1195" t="n">
-        <v>4.46174335479736</v>
+        <v>4.46174383163452</v>
       </c>
       <c r="H1195" t="n">
         <v>12604</v>
@@ -35082,7 +35082,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1197" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1197" t="n">
         <v>37624</v>
@@ -35111,7 +35111,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1198" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1198" t="n">
         <v>17896</v>
@@ -35169,7 +35169,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1200" t="n">
-        <v>4.51774883270264</v>
+        <v>4.51774930953979</v>
       </c>
       <c r="H1200" t="n">
         <v>23594</v>
@@ -35198,7 +35198,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1201" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1201" t="n">
         <v>16723</v>
@@ -35401,7 +35401,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1208" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1208" t="n">
         <v>10200</v>
@@ -35488,7 +35488,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1211" t="n">
-        <v>4.46174335479736</v>
+        <v>4.46174383163452</v>
       </c>
       <c r="H1211" t="n">
         <v>10557</v>
@@ -35517,7 +35517,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1212" t="n">
-        <v>4.50841474533081</v>
+        <v>4.50841426849365</v>
       </c>
       <c r="H1212" t="n">
         <v>8520</v>
@@ -35575,7 +35575,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1214" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1214" t="n">
         <v>5950</v>
@@ -35604,7 +35604,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1215" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1215" t="n">
         <v>6941</v>
@@ -35720,7 +35720,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1219" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1219" t="n">
         <v>2891</v>
@@ -35749,7 +35749,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1220" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1220" t="n">
         <v>5384</v>
@@ -35778,7 +35778,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1221" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1221" t="n">
         <v>3060</v>
@@ -36474,7 +36474,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.40573835372925</v>
+        <v>4.40573787689209</v>
       </c>
       <c r="H1245" t="n">
         <v>1123</v>
@@ -36619,7 +36619,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1250" t="n">
-        <v>4.40573835372925</v>
+        <v>4.40573787689209</v>
       </c>
       <c r="H1250" t="n">
         <v>2487</v>
@@ -36648,7 +36648,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1251" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1251" t="n">
         <v>39291</v>
@@ -36677,7 +36677,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1252" t="n">
-        <v>4.53641748428345</v>
+        <v>4.53641700744629</v>
       </c>
       <c r="H1252" t="n">
         <v>10852</v>
@@ -37315,7 +37315,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1274" t="n">
-        <v>4.9907808303833</v>
+        <v>4.99078130722046</v>
       </c>
       <c r="H1274" t="n">
         <v>24772</v>
@@ -37344,7 +37344,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1275" t="n">
-        <v>5.02917194366455</v>
+        <v>5.02917146682739</v>
       </c>
       <c r="H1275" t="n">
         <v>31385</v>
@@ -37431,7 +37431,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1278" t="n">
-        <v>5.48985910415649</v>
+        <v>5.48985958099365</v>
       </c>
       <c r="H1278" t="n">
         <v>70084</v>
@@ -37576,7 +37576,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1283" t="n">
-        <v>5.83537530899048</v>
+        <v>5.83537483215332</v>
       </c>
       <c r="H1283" t="n">
         <v>8786</v>
@@ -37634,7 +37634,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1285" t="n">
-        <v>6.39203882217407</v>
+        <v>6.39203929901123</v>
       </c>
       <c r="H1285" t="n">
         <v>35361</v>
@@ -37750,7 +37750,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1289" t="n">
-        <v>6.46882057189941</v>
+        <v>6.46882009506226</v>
       </c>
       <c r="H1289" t="n">
         <v>13104</v>
@@ -37866,7 +37866,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G1293" t="n">
-        <v>6.18089056015015</v>
+        <v>6.1808910369873</v>
       </c>
       <c r="H1293" t="n">
         <v>21462</v>
@@ -37895,7 +37895,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1294" t="n">
-        <v>6.12330484390259</v>
+        <v>6.12330532073975</v>
       </c>
       <c r="H1294" t="n">
         <v>21748</v>
@@ -37953,7 +37953,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1296" t="n">
-        <v>6.39203882217407</v>
+        <v>6.39203929901123</v>
       </c>
       <c r="H1296" t="n">
         <v>15861</v>
@@ -37982,7 +37982,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1297" t="n">
-        <v>6.48801565170288</v>
+        <v>6.48801612854004</v>
       </c>
       <c r="H1297" t="n">
         <v>2374</v>
@@ -38011,7 +38011,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1298" t="n">
-        <v>6.48801565170288</v>
+        <v>6.48801612854004</v>
       </c>
       <c r="H1298" t="n">
         <v>9827</v>
@@ -38156,7 +38156,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1303" t="n">
-        <v>6.48801565170288</v>
+        <v>6.48801612854004</v>
       </c>
       <c r="H1303" t="n">
         <v>11171</v>
@@ -38388,7 +38388,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1311" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1311" t="n">
         <v>18885</v>
@@ -38446,7 +38446,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1313" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1313" t="n">
         <v>34147</v>
@@ -38533,7 +38533,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1316" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1316" t="n">
         <v>10376</v>
@@ -38939,7 +38939,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1330" t="n">
-        <v>5.68181228637695</v>
+        <v>5.68181276321411</v>
       </c>
       <c r="H1330" t="n">
         <v>4010</v>
@@ -39026,7 +39026,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1333" t="n">
-        <v>5.66261768341064</v>
+        <v>5.66261720657349</v>
       </c>
       <c r="H1333" t="n">
         <v>3167</v>
@@ -39055,7 +39055,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.56664133071899</v>
+        <v>5.56664085388184</v>
       </c>
       <c r="H1334" t="n">
         <v>13673</v>
@@ -39084,7 +39084,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1335" t="n">
-        <v>5.48985910415649</v>
+        <v>5.48985958099365</v>
       </c>
       <c r="H1335" t="n">
         <v>2565</v>
@@ -39142,7 +39142,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1337" t="n">
-        <v>5.56664133071899</v>
+        <v>5.56664085388184</v>
       </c>
       <c r="H1337" t="n">
         <v>2917</v>
@@ -39171,7 +39171,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1338" t="n">
-        <v>5.56664133071899</v>
+        <v>5.56664085388184</v>
       </c>
       <c r="H1338" t="n">
         <v>1312</v>
@@ -39258,7 +39258,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1341" t="n">
-        <v>5.66261768341064</v>
+        <v>5.66261720657349</v>
       </c>
       <c r="H1341" t="n">
         <v>1605</v>
@@ -39287,7 +39287,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1342" t="n">
-        <v>5.66261768341064</v>
+        <v>5.66261720657349</v>
       </c>
       <c r="H1342" t="n">
         <v>3220</v>
@@ -39403,7 +39403,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1346" t="n">
-        <v>5.56664133071899</v>
+        <v>5.56664085388184</v>
       </c>
       <c r="H1346" t="n">
         <v>2814</v>
@@ -39519,7 +39519,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1350" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1350" t="n">
         <v>11182</v>
@@ -39548,7 +39548,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1351" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1351" t="n">
         <v>17082</v>
@@ -39577,7 +39577,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1352" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1352" t="n">
         <v>5027</v>
@@ -39606,7 +39606,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1353" t="n">
-        <v>6.12330484390259</v>
+        <v>6.12330532073975</v>
       </c>
       <c r="H1353" t="n">
         <v>15567</v>
@@ -39693,7 +39693,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1356" t="n">
-        <v>5.87376594543457</v>
+        <v>5.87376546859741</v>
       </c>
       <c r="H1356" t="n">
         <v>18468</v>
@@ -39896,7 +39896,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1363" t="n">
-        <v>5.96974229812622</v>
+        <v>5.96974182128906</v>
       </c>
       <c r="H1363" t="n">
         <v>14927</v>
@@ -40012,7 +40012,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1367" t="n">
-        <v>5.96974229812622</v>
+        <v>5.96974182128906</v>
       </c>
       <c r="H1367" t="n">
         <v>5383</v>
@@ -40041,7 +40041,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1368" t="n">
-        <v>5.83537530899048</v>
+        <v>5.83537483215332</v>
       </c>
       <c r="H1368" t="n">
         <v>3207</v>
@@ -40099,7 +40099,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1370" t="n">
-        <v>5.96974229812622</v>
+        <v>5.96974182128906</v>
       </c>
       <c r="H1370" t="n">
         <v>2420</v>
@@ -40128,7 +40128,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1371" t="n">
-        <v>5.87376594543457</v>
+        <v>5.87376546859741</v>
       </c>
       <c r="H1371" t="n">
         <v>5952</v>
@@ -40186,7 +40186,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1373" t="n">
-        <v>6.0849142074585</v>
+        <v>6.08491468429565</v>
       </c>
       <c r="H1373" t="n">
         <v>4048</v>
@@ -40244,7 +40244,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1375" t="n">
-        <v>5.87376594543457</v>
+        <v>5.87376546859741</v>
       </c>
       <c r="H1375" t="n">
         <v>6216</v>
@@ -40505,7 +40505,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1384" t="n">
-        <v>5.87376594543457</v>
+        <v>5.87376546859741</v>
       </c>
       <c r="H1384" t="n">
         <v>8532</v>
@@ -40534,7 +40534,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1385" t="n">
-        <v>5.96974229812622</v>
+        <v>5.96974182128906</v>
       </c>
       <c r="H1385" t="n">
         <v>4804</v>
@@ -40563,7 +40563,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1386" t="n">
-        <v>5.96974229812622</v>
+        <v>5.96974182128906</v>
       </c>
       <c r="H1386" t="n">
         <v>51315</v>
@@ -40592,7 +40592,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1387" t="n">
-        <v>5.96974229812622</v>
+        <v>5.96974182128906</v>
       </c>
       <c r="H1387" t="n">
         <v>3086</v>
@@ -40621,7 +40621,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1388" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1388" t="n">
         <v>5083</v>
@@ -40679,7 +40679,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1390" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1390" t="n">
         <v>3425</v>
@@ -40737,7 +40737,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1392" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1392" t="n">
         <v>2371</v>
@@ -40766,7 +40766,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1393" t="n">
-        <v>5.87376594543457</v>
+        <v>5.87376546859741</v>
       </c>
       <c r="H1393" t="n">
         <v>4474</v>
@@ -41085,7 +41085,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1404" t="n">
-        <v>6.0849142074585</v>
+        <v>6.08491468429565</v>
       </c>
       <c r="H1404" t="n">
         <v>18941</v>
@@ -41143,7 +41143,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1406" t="n">
-        <v>6.12330484390259</v>
+        <v>6.12330532073975</v>
       </c>
       <c r="H1406" t="n">
         <v>40015</v>
@@ -41462,7 +41462,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1417" t="n">
-        <v>7.02548456192017</v>
+        <v>7.02548503875732</v>
       </c>
       <c r="H1417" t="n">
         <v>6334</v>
@@ -41839,7 +41839,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1430" t="n">
-        <v>7.02548456192017</v>
+        <v>7.02548503875732</v>
       </c>
       <c r="H1430" t="n">
         <v>15354</v>
@@ -41897,7 +41897,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1432" t="n">
-        <v>7.02548456192017</v>
+        <v>7.02548503875732</v>
       </c>
       <c r="H1432" t="n">
         <v>1260</v>
@@ -42129,7 +42129,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1440" t="n">
-        <v>7.06387567520142</v>
+        <v>7.06387519836426</v>
       </c>
       <c r="H1440" t="n">
         <v>1592</v>
@@ -42187,7 +42187,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G1442" t="n">
-        <v>7.12146091461182</v>
+        <v>7.12146139144897</v>
       </c>
       <c r="H1442" t="n">
         <v>9087</v>
@@ -42303,7 +42303,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1446" t="n">
-        <v>7.06387567520142</v>
+        <v>7.06387519836426</v>
       </c>
       <c r="H1446" t="n">
         <v>10440</v>
@@ -42361,7 +42361,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1448" t="n">
-        <v>7.06387567520142</v>
+        <v>7.06387519836426</v>
       </c>
       <c r="H1448" t="n">
         <v>6369</v>
@@ -42390,7 +42390,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1449" t="n">
-        <v>6.91031217575073</v>
+        <v>6.91031265258789</v>
       </c>
       <c r="H1449" t="n">
         <v>8416</v>
@@ -42419,7 +42419,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1450" t="n">
-        <v>7.02548456192017</v>
+        <v>7.02548503875732</v>
       </c>
       <c r="H1450" t="n">
         <v>5499</v>
@@ -42535,7 +42535,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1454" t="n">
-        <v>7.06387567520142</v>
+        <v>7.06387519836426</v>
       </c>
       <c r="H1454" t="n">
         <v>2894</v>
@@ -42680,7 +42680,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1459" t="n">
-        <v>6.91031217575073</v>
+        <v>6.91031265258789</v>
       </c>
       <c r="H1459" t="n">
         <v>3121</v>
@@ -42738,7 +42738,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1461" t="n">
-        <v>6.91031217575073</v>
+        <v>6.91031265258789</v>
       </c>
       <c r="H1461" t="n">
         <v>9076</v>
@@ -42767,7 +42767,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1462" t="n">
-        <v>7.06387567520142</v>
+        <v>7.06387519836426</v>
       </c>
       <c r="H1462" t="n">
         <v>300</v>
@@ -42883,7 +42883,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1466" t="n">
-        <v>7.02548456192017</v>
+        <v>7.02548503875732</v>
       </c>
       <c r="H1466" t="n">
         <v>501</v>
@@ -43173,7 +43173,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1476" t="n">
-        <v>6.91031217575073</v>
+        <v>6.91031265258789</v>
       </c>
       <c r="H1476" t="n">
         <v>7848</v>
@@ -43202,7 +43202,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1477" t="n">
-        <v>6.89111709594727</v>
+        <v>6.89111757278442</v>
       </c>
       <c r="H1477" t="n">
         <v>12560</v>
@@ -43260,7 +43260,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1479" t="n">
-        <v>6.91031217575073</v>
+        <v>6.91031265258789</v>
       </c>
       <c r="H1479" t="n">
         <v>16205</v>
@@ -43289,7 +43289,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1480" t="n">
-        <v>6.77594566345215</v>
+        <v>6.77594518661499</v>
       </c>
       <c r="H1480" t="n">
         <v>1973</v>
@@ -43318,7 +43318,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1481" t="n">
-        <v>6.98709392547607</v>
+        <v>6.98709440231323</v>
       </c>
       <c r="H1481" t="n">
         <v>4148</v>
@@ -43347,7 +43347,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1482" t="n">
-        <v>6.89111709594727</v>
+        <v>6.89111757278442</v>
       </c>
       <c r="H1482" t="n">
         <v>144</v>
@@ -43405,7 +43405,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G1484" t="n">
-        <v>6.79514074325562</v>
+        <v>6.79514026641846</v>
       </c>
       <c r="H1484" t="n">
         <v>10530</v>
@@ -43434,7 +43434,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1485" t="n">
-        <v>6.81433582305908</v>
+        <v>6.81433629989624</v>
       </c>
       <c r="H1485" t="n">
         <v>2742</v>
@@ -43463,7 +43463,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1486" t="n">
-        <v>6.91031217575073</v>
+        <v>6.91031265258789</v>
       </c>
       <c r="H1486" t="n">
         <v>1912</v>
@@ -43492,7 +43492,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1487" t="n">
-        <v>6.91031217575073</v>
+        <v>6.91031265258789</v>
       </c>
       <c r="H1487" t="n">
         <v>6267</v>
@@ -43521,7 +43521,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1488" t="n">
-        <v>6.98709392547607</v>
+        <v>6.98709440231323</v>
       </c>
       <c r="H1488" t="n">
         <v>8301</v>
@@ -43724,7 +43724,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1495" t="n">
-        <v>7.29421854019165</v>
+        <v>7.29421901702881</v>
       </c>
       <c r="H1495" t="n">
         <v>3213</v>
@@ -43753,7 +43753,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1496" t="n">
-        <v>7.42858600616455</v>
+        <v>7.42858552932739</v>
       </c>
       <c r="H1496" t="n">
         <v>9505</v>
@@ -43811,7 +43811,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1498" t="n">
-        <v>7.54375839233398</v>
+        <v>7.54375791549683</v>
       </c>
       <c r="H1498" t="n">
         <v>2199</v>
@@ -54631,9 +54631,38 @@
         <v>13.8999996185303</v>
       </c>
       <c r="H1871" t="n">
-        <v>2575</v>
+        <v>2576</v>
       </c>
       <c r="I1871" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1872">
+      <c r="A1872" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1872" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1872" t="n">
+        <v>13.6999998092651</v>
+      </c>
+      <c r="D1872" t="n">
+        <v>13.9499998092651</v>
+      </c>
+      <c r="E1872" t="n">
+        <v>13.6999998092651</v>
+      </c>
+      <c r="F1872" t="n">
+        <v>13.8500003814697</v>
+      </c>
+      <c r="G1872" t="n">
+        <v>13.8500003814697</v>
+      </c>
+      <c r="H1872" t="n">
+        <v>4893</v>
+      </c>
+      <c r="I1872" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IEG.MI.xlsx
+++ b/data/IEG.MI.xlsx
@@ -54660,9 +54660,38 @@
         <v>13.8500003814697</v>
       </c>
       <c r="H1872" t="n">
-        <v>4893</v>
+        <v>4901</v>
       </c>
       <c r="I1872" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1873">
+      <c r="A1873" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1873" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1873" t="n">
+        <v>13.9499998092651</v>
+      </c>
+      <c r="D1873" t="n">
+        <v>14.1499996185303</v>
+      </c>
+      <c r="E1873" t="n">
+        <v>13.8000001907349</v>
+      </c>
+      <c r="F1873" t="n">
+        <v>14</v>
+      </c>
+      <c r="G1873" t="n">
+        <v>14</v>
+      </c>
+      <c r="H1873" t="n">
+        <v>5613</v>
+      </c>
+      <c r="I1873" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IEG.MI.xlsx
+++ b/data/IEG.MI.xlsx
@@ -485,7 +485,7 @@
         <v>3.73099994659424</v>
       </c>
       <c r="G4" t="n">
-        <v>3.48258662223816</v>
+        <v>3.48258686065674</v>
       </c>
       <c r="H4" t="n">
         <v>132269</v>
@@ -514,7 +514,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G5" t="n">
-        <v>3.52832412719727</v>
+        <v>3.52832436561584</v>
       </c>
       <c r="H5" t="n">
         <v>20727</v>
@@ -543,7 +543,7 @@
         <v>3.69749999046326</v>
       </c>
       <c r="G6" t="n">
-        <v>3.45131707191467</v>
+        <v>3.45131731033325</v>
       </c>
       <c r="H6" t="n">
         <v>5051</v>
@@ -572,7 +572,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G7" t="n">
-        <v>3.45365071296692</v>
+        <v>3.4536509513855</v>
       </c>
       <c r="H7" t="n">
         <v>13909</v>
@@ -601,7 +601,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>3.40697979927063</v>
+        <v>3.40698003768921</v>
       </c>
       <c r="H8" t="n">
         <v>31297</v>
@@ -630,7 +630,7 @@
         <v>3.67050004005432</v>
       </c>
       <c r="G9" t="n">
-        <v>3.42611503601074</v>
+        <v>3.42611479759216</v>
       </c>
       <c r="H9" t="n">
         <v>132</v>
@@ -659,7 +659,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G10" t="n">
-        <v>3.45365071296692</v>
+        <v>3.4536509513855</v>
       </c>
       <c r="H10" t="n">
         <v>5150</v>
@@ -688,7 +688,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G11" t="n">
-        <v>3.45365071296692</v>
+        <v>3.4536509513855</v>
       </c>
       <c r="H11" t="n">
         <v>2000</v>
@@ -717,7 +717,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G12" t="n">
-        <v>3.43498253822327</v>
+        <v>3.43498277664185</v>
       </c>
       <c r="H12" t="n">
         <v>3250</v>
@@ -746,7 +746,7 @@
         <v>3.64050006866455</v>
       </c>
       <c r="G13" t="n">
-        <v>3.39811229705811</v>
+        <v>3.39811253547668</v>
       </c>
       <c r="H13" t="n">
         <v>1311</v>
@@ -804,7 +804,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G15" t="n">
-        <v>3.42564821243286</v>
+        <v>3.42564845085144</v>
       </c>
       <c r="H15" t="n">
         <v>10175</v>
@@ -862,7 +862,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G17" t="n">
-        <v>3.47231936454773</v>
+        <v>3.47231912612915</v>
       </c>
       <c r="H17" t="n">
         <v>86899</v>
@@ -920,7 +920,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G19" t="n">
-        <v>3.69634008407593</v>
+        <v>3.69633960723877</v>
       </c>
       <c r="H19" t="n">
         <v>96525</v>
@@ -978,7 +978,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G21" t="n">
-        <v>3.80834984779358</v>
+        <v>3.80835032463074</v>
       </c>
       <c r="H21" t="n">
         <v>29979</v>
@@ -1065,7 +1065,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G24" t="n">
-        <v>3.85502123832703</v>
+        <v>3.85502099990845</v>
       </c>
       <c r="H24" t="n">
         <v>69970</v>
@@ -1094,7 +1094,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G25" t="n">
-        <v>3.81768465042114</v>
+        <v>3.81768441200256</v>
       </c>
       <c r="H25" t="n">
         <v>4963</v>
@@ -1181,7 +1181,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G28" t="n">
-        <v>3.95769667625427</v>
+        <v>3.95769739151001</v>
       </c>
       <c r="H28" t="n">
         <v>6052</v>
@@ -1210,7 +1210,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G29" t="n">
-        <v>3.97636604309082</v>
+        <v>3.97636556625366</v>
       </c>
       <c r="H29" t="n">
         <v>2457</v>
@@ -1239,7 +1239,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G30" t="n">
-        <v>4.05103874206543</v>
+        <v>4.05103969573975</v>
       </c>
       <c r="H30" t="n">
         <v>10363</v>
@@ -1268,7 +1268,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G31" t="n">
-        <v>4.03237056732178</v>
+        <v>4.03237104415894</v>
       </c>
       <c r="H31" t="n">
         <v>17060</v>
@@ -1297,7 +1297,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G32" t="n">
-        <v>3.93902826309204</v>
+        <v>3.9390287399292</v>
       </c>
       <c r="H32" t="n">
         <v>6284</v>
@@ -1326,7 +1326,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>4.01370239257812</v>
+        <v>4.01370286941528</v>
       </c>
       <c r="H33" t="n">
         <v>4871</v>
@@ -1355,7 +1355,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G34" t="n">
-        <v>4.01370239257812</v>
+        <v>4.01370286941528</v>
       </c>
       <c r="H34" t="n">
         <v>114</v>
@@ -1384,7 +1384,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G35" t="n">
-        <v>3.99503421783447</v>
+        <v>3.99503397941589</v>
       </c>
       <c r="H35" t="n">
         <v>922</v>
@@ -1413,7 +1413,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G36" t="n">
-        <v>3.99503421783447</v>
+        <v>3.99503397941589</v>
       </c>
       <c r="H36" t="n">
         <v>300</v>
@@ -1442,7 +1442,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G37" t="n">
-        <v>3.99503421783447</v>
+        <v>3.99503397941589</v>
       </c>
       <c r="H37" t="n">
         <v>4226</v>
@@ -1471,7 +1471,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G38" t="n">
-        <v>3.95769667625427</v>
+        <v>3.95769739151001</v>
       </c>
       <c r="H38" t="n">
         <v>4960</v>
@@ -1500,7 +1500,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G39" t="n">
-        <v>3.88302326202393</v>
+        <v>3.8830235004425</v>
       </c>
       <c r="H39" t="n">
         <v>592</v>
@@ -1529,7 +1529,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G40" t="n">
-        <v>3.88302326202393</v>
+        <v>3.8830235004425</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1558,7 +1558,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G41" t="n">
-        <v>3.95769667625427</v>
+        <v>3.95769739151001</v>
       </c>
       <c r="H41" t="n">
         <v>225</v>
@@ -1587,7 +1587,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G42" t="n">
-        <v>3.95769667625427</v>
+        <v>3.95769739151001</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>3.92036032676697</v>
+        <v>3.92036008834839</v>
       </c>
       <c r="H43" t="n">
         <v>148291</v>
@@ -1645,7 +1645,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G44" t="n">
-        <v>3.92036032676697</v>
+        <v>3.92036008834839</v>
       </c>
       <c r="H44" t="n">
         <v>59672</v>
@@ -1703,7 +1703,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G46" t="n">
-        <v>3.92036032676697</v>
+        <v>3.92036008834839</v>
       </c>
       <c r="H46" t="n">
         <v>4540</v>
@@ -1732,7 +1732,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G47" t="n">
-        <v>3.85502123832703</v>
+        <v>3.85502099990845</v>
       </c>
       <c r="H47" t="n">
         <v>125</v>
@@ -1819,7 +1819,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G50" t="n">
-        <v>3.92036032676697</v>
+        <v>3.92036008834839</v>
       </c>
       <c r="H50" t="n">
         <v>3900</v>
@@ -1848,7 +1848,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G51" t="n">
-        <v>3.64033484458923</v>
+        <v>3.64033460617065</v>
       </c>
       <c r="H51" t="n">
         <v>168018</v>
@@ -1877,7 +1877,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G52" t="n">
-        <v>3.59366369247437</v>
+        <v>3.59366345405579</v>
       </c>
       <c r="H52" t="n">
         <v>66112</v>
@@ -1906,7 +1906,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G53" t="n">
-        <v>3.63100051879883</v>
+        <v>3.63100075721741</v>
       </c>
       <c r="H53" t="n">
         <v>23073</v>
@@ -1935,7 +1935,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G54" t="n">
-        <v>3.53765845298767</v>
+        <v>3.53765869140625</v>
       </c>
       <c r="H54" t="n">
         <v>154944</v>
@@ -1964,7 +1964,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G55" t="n">
-        <v>3.42564821243286</v>
+        <v>3.42564845085144</v>
       </c>
       <c r="H55" t="n">
         <v>62162</v>
@@ -1993,7 +1993,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G56" t="n">
-        <v>3.40697979927063</v>
+        <v>3.40698003768921</v>
       </c>
       <c r="H56" t="n">
         <v>6594</v>
@@ -2022,7 +2022,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G57" t="n">
-        <v>3.45365071296692</v>
+        <v>3.4536509513855</v>
       </c>
       <c r="H57" t="n">
         <v>73464</v>
@@ -2051,7 +2051,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G58" t="n">
-        <v>3.45365071296692</v>
+        <v>3.4536509513855</v>
       </c>
       <c r="H58" t="n">
         <v>35821</v>
@@ -2109,7 +2109,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G60" t="n">
-        <v>3.47231936454773</v>
+        <v>3.47231912612915</v>
       </c>
       <c r="H60" t="n">
         <v>10849</v>
@@ -2167,7 +2167,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>3.59366369247437</v>
+        <v>3.59366345405579</v>
       </c>
       <c r="H62" t="n">
         <v>6367</v>
@@ -2225,7 +2225,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G64" t="n">
-        <v>3.56566119194031</v>
+        <v>3.56566095352173</v>
       </c>
       <c r="H64" t="n">
         <v>333</v>
@@ -2254,7 +2254,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G65" t="n">
-        <v>3.58432936668396</v>
+        <v>3.58432960510254</v>
       </c>
       <c r="H65" t="n">
         <v>6062</v>
@@ -2283,7 +2283,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G66" t="n">
-        <v>3.59366369247437</v>
+        <v>3.59366345405579</v>
       </c>
       <c r="H66" t="n">
         <v>2000</v>
@@ -2341,7 +2341,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G68" t="n">
-        <v>3.69634008407593</v>
+        <v>3.69633960723877</v>
       </c>
       <c r="H68" t="n">
         <v>6933</v>
@@ -2428,7 +2428,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G71" t="n">
-        <v>3.59366369247437</v>
+        <v>3.59366345405579</v>
       </c>
       <c r="H71" t="n">
         <v>700</v>
@@ -2457,7 +2457,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G72" t="n">
-        <v>3.53765845298767</v>
+        <v>3.53765869140625</v>
       </c>
       <c r="H72" t="n">
         <v>3200</v>
@@ -2486,7 +2486,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G73" t="n">
-        <v>3.53765845298767</v>
+        <v>3.53765869140625</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G74" t="n">
-        <v>3.53765845298767</v>
+        <v>3.53765869140625</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>3.54699277877808</v>
+        <v>3.5469925403595</v>
       </c>
       <c r="H75" t="n">
         <v>550</v>
@@ -2573,7 +2573,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G76" t="n">
-        <v>3.54699277877808</v>
+        <v>3.5469925403595</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>3.54699277877808</v>
+        <v>3.5469925403595</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -2660,7 +2660,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G79" t="n">
-        <v>3.56566119194031</v>
+        <v>3.56566095352173</v>
       </c>
       <c r="H79" t="n">
         <v>505</v>
@@ -2689,7 +2689,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G80" t="n">
-        <v>3.59366369247437</v>
+        <v>3.59366345405579</v>
       </c>
       <c r="H80" t="n">
         <v>320</v>
@@ -2718,7 +2718,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G81" t="n">
-        <v>3.59366369247437</v>
+        <v>3.59366345405579</v>
       </c>
       <c r="H81" t="n">
         <v>11</v>
@@ -2747,7 +2747,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G82" t="n">
-        <v>3.59366369247437</v>
+        <v>3.59366345405579</v>
       </c>
       <c r="H82" t="n">
         <v>659</v>
@@ -2776,7 +2776,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G83" t="n">
-        <v>3.61233186721802</v>
+        <v>3.6123321056366</v>
       </c>
       <c r="H83" t="n">
         <v>505</v>
@@ -2805,7 +2805,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G84" t="n">
-        <v>3.61233186721802</v>
+        <v>3.6123321056366</v>
       </c>
       <c r="H84" t="n">
         <v>10</v>
@@ -2834,7 +2834,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G85" t="n">
-        <v>3.56566119194031</v>
+        <v>3.56566095352173</v>
       </c>
       <c r="H85" t="n">
         <v>7252</v>
@@ -2863,7 +2863,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>3.57499504089355</v>
+        <v>3.57499527931213</v>
       </c>
       <c r="H86" t="n">
         <v>6205</v>
@@ -2892,7 +2892,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G87" t="n">
-        <v>3.63100051879883</v>
+        <v>3.63100075721741</v>
       </c>
       <c r="H87" t="n">
         <v>3367</v>
@@ -2950,7 +2950,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>3.59366369247437</v>
+        <v>3.59366345405579</v>
       </c>
       <c r="H89" t="n">
         <v>19</v>
@@ -3008,7 +3008,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G91" t="n">
-        <v>3.61233186721802</v>
+        <v>3.6123321056366</v>
       </c>
       <c r="H91" t="n">
         <v>5</v>
@@ -3037,7 +3037,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G92" t="n">
-        <v>3.54699277877808</v>
+        <v>3.5469925403595</v>
       </c>
       <c r="H92" t="n">
         <v>495</v>
@@ -3066,7 +3066,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G93" t="n">
-        <v>3.58432936668396</v>
+        <v>3.58432960510254</v>
       </c>
       <c r="H93" t="n">
         <v>410</v>
@@ -3269,7 +3269,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>3.69634008407593</v>
+        <v>3.69633960723877</v>
       </c>
       <c r="H100" t="n">
         <v>5164</v>
@@ -3298,7 +3298,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G101" t="n">
-        <v>3.69634008407593</v>
+        <v>3.69633960723877</v>
       </c>
       <c r="H101" t="n">
         <v>1750</v>
@@ -3327,7 +3327,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G102" t="n">
-        <v>3.64033484458923</v>
+        <v>3.64033460617065</v>
       </c>
       <c r="H102" t="n">
         <v>9855</v>
@@ -3356,7 +3356,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G103" t="n">
-        <v>3.64033484458923</v>
+        <v>3.64033460617065</v>
       </c>
       <c r="H103" t="n">
         <v>40000</v>
@@ -3385,7 +3385,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>3.64033484458923</v>
+        <v>3.64033460617065</v>
       </c>
       <c r="H104" t="n">
         <v>505</v>
@@ -3414,7 +3414,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G105" t="n">
-        <v>3.64966893196106</v>
+        <v>3.64966869354248</v>
       </c>
       <c r="H105" t="n">
         <v>1680</v>
@@ -3501,7 +3501,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G108" t="n">
-        <v>3.81768465042114</v>
+        <v>3.81768441200256</v>
       </c>
       <c r="H108" t="n">
         <v>7940</v>
@@ -3559,7 +3559,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G110" t="n">
-        <v>3.81768465042114</v>
+        <v>3.81768441200256</v>
       </c>
       <c r="H110" t="n">
         <v>41689</v>
@@ -3588,7 +3588,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>3.80834984779358</v>
+        <v>3.80835032463074</v>
       </c>
       <c r="H111" t="n">
         <v>19699</v>
@@ -3617,7 +3617,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G112" t="n">
-        <v>3.80834984779358</v>
+        <v>3.80835032463074</v>
       </c>
       <c r="H112" t="n">
         <v>17603</v>
@@ -3733,7 +3733,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G116" t="n">
-        <v>3.76167917251587</v>
+        <v>3.76167941093445</v>
       </c>
       <c r="H116" t="n">
         <v>40346</v>
@@ -3907,7 +3907,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G122" t="n">
-        <v>3.86435532569885</v>
+        <v>3.86435484886169</v>
       </c>
       <c r="H122" t="n">
         <v>44816</v>
@@ -3936,7 +3936,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G123" t="n">
-        <v>3.85502123832703</v>
+        <v>3.85502099990845</v>
       </c>
       <c r="H123" t="n">
         <v>5193</v>
@@ -3965,7 +3965,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G124" t="n">
-        <v>3.86435532569885</v>
+        <v>3.86435484886169</v>
       </c>
       <c r="H124" t="n">
         <v>15805</v>
@@ -4023,7 +4023,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G126" t="n">
-        <v>3.80834984779358</v>
+        <v>3.80835032463074</v>
       </c>
       <c r="H126" t="n">
         <v>1562</v>
@@ -4226,7 +4226,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G133" t="n">
-        <v>3.87368941307068</v>
+        <v>3.87368965148926</v>
       </c>
       <c r="H133" t="n">
         <v>7109</v>
@@ -4284,7 +4284,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G135" t="n">
-        <v>3.92036032676697</v>
+        <v>3.92036008834839</v>
       </c>
       <c r="H135" t="n">
         <v>8125</v>
@@ -4313,7 +4313,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G136" t="n">
-        <v>3.92036032676697</v>
+        <v>3.92036008834839</v>
       </c>
       <c r="H136" t="n">
         <v>6440</v>
@@ -4342,7 +4342,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G137" t="n">
-        <v>3.92969465255737</v>
+        <v>3.92969489097595</v>
       </c>
       <c r="H137" t="n">
         <v>5529</v>
@@ -4371,7 +4371,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G138" t="n">
-        <v>3.92036032676697</v>
+        <v>3.92036008834839</v>
       </c>
       <c r="H138" t="n">
         <v>255</v>
@@ -4400,7 +4400,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G139" t="n">
-        <v>3.87368941307068</v>
+        <v>3.87368965148926</v>
       </c>
       <c r="H139" t="n">
         <v>2403</v>
@@ -4429,7 +4429,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G140" t="n">
-        <v>3.93902826309204</v>
+        <v>3.9390287399292</v>
       </c>
       <c r="H140" t="n">
         <v>3505</v>
@@ -4545,7 +4545,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G144" t="n">
-        <v>3.93902826309204</v>
+        <v>3.9390287399292</v>
       </c>
       <c r="H144" t="n">
         <v>3005</v>
@@ -4574,7 +4574,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G145" t="n">
-        <v>3.89235782623291</v>
+        <v>3.89235758781433</v>
       </c>
       <c r="H145" t="n">
         <v>14</v>
@@ -4603,7 +4603,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G146" t="n">
-        <v>3.87368941307068</v>
+        <v>3.87368965148926</v>
       </c>
       <c r="H146" t="n">
         <v>495</v>
@@ -4661,7 +4661,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G148" t="n">
-        <v>3.95769667625427</v>
+        <v>3.95769739151001</v>
       </c>
       <c r="H148" t="n">
         <v>228432</v>
@@ -4690,7 +4690,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G149" t="n">
-        <v>4.0417046546936</v>
+        <v>4.04170513153076</v>
       </c>
       <c r="H149" t="n">
         <v>42576</v>
@@ -4719,7 +4719,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G150" t="n">
-        <v>4.22838878631592</v>
+        <v>4.22838926315308</v>
       </c>
       <c r="H150" t="n">
         <v>26577</v>
@@ -4748,7 +4748,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G151" t="n">
-        <v>4.25639152526855</v>
+        <v>4.2563910484314</v>
       </c>
       <c r="H151" t="n">
         <v>8178</v>
@@ -4835,7 +4835,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G154" t="n">
-        <v>4.35906744003296</v>
+        <v>4.3590669631958</v>
       </c>
       <c r="H154" t="n">
         <v>15474</v>
@@ -4864,7 +4864,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G155" t="n">
-        <v>4.40573787689209</v>
+        <v>4.40573835372925</v>
       </c>
       <c r="H155" t="n">
         <v>10834</v>
@@ -4893,7 +4893,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G156" t="n">
-        <v>4.46174383163452</v>
+        <v>4.46174335479736</v>
       </c>
       <c r="H156" t="n">
         <v>4570</v>
@@ -4922,7 +4922,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G157" t="n">
-        <v>4.40573787689209</v>
+        <v>4.40573835372925</v>
       </c>
       <c r="H157" t="n">
         <v>4479</v>
@@ -4951,7 +4951,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G158" t="n">
-        <v>4.26572561264038</v>
+        <v>4.26572513580322</v>
       </c>
       <c r="H158" t="n">
         <v>10313</v>
@@ -5067,7 +5067,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G162" t="n">
-        <v>4.14438056945801</v>
+        <v>4.14438104629517</v>
       </c>
       <c r="H162" t="n">
         <v>5657</v>
@@ -5096,7 +5096,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G163" t="n">
-        <v>4.16304969787598</v>
+        <v>4.16304922103882</v>
       </c>
       <c r="H163" t="n">
         <v>656</v>
@@ -5183,7 +5183,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G166" t="n">
-        <v>4.16304969787598</v>
+        <v>4.16304922103882</v>
       </c>
       <c r="H166" t="n">
         <v>505</v>
@@ -5212,7 +5212,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G167" t="n">
-        <v>4.12571287155151</v>
+        <v>4.12571239471436</v>
       </c>
       <c r="H167" t="n">
         <v>1585</v>
@@ -5241,7 +5241,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>4.05103874206543</v>
+        <v>4.05103969573975</v>
       </c>
       <c r="H168" t="n">
         <v>499</v>
@@ -5270,7 +5270,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G169" t="n">
-        <v>4.14438056945801</v>
+        <v>4.14438104629517</v>
       </c>
       <c r="H169" t="n">
         <v>4433</v>
@@ -5299,7 +5299,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G170" t="n">
-        <v>4.13504648208618</v>
+        <v>4.13504695892334</v>
       </c>
       <c r="H170" t="n">
         <v>250</v>
@@ -5328,7 +5328,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G171" t="n">
-        <v>4.15371561050415</v>
+        <v>4.15371513366699</v>
       </c>
       <c r="H171" t="n">
         <v>3578</v>
@@ -5357,7 +5357,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G172" t="n">
-        <v>4.28439426422119</v>
+        <v>4.28439378738403</v>
       </c>
       <c r="H172" t="n">
         <v>1482</v>
@@ -5386,7 +5386,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G173" t="n">
-        <v>4.06037330627441</v>
+        <v>4.06037282943726</v>
       </c>
       <c r="H173" t="n">
         <v>6766</v>
@@ -5415,7 +5415,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G174" t="n">
-        <v>3.59366369247437</v>
+        <v>3.59366345405579</v>
       </c>
       <c r="H174" t="n">
         <v>11092</v>
@@ -5502,7 +5502,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G177" t="n">
-        <v>3.64966893196106</v>
+        <v>3.64966869354248</v>
       </c>
       <c r="H177" t="n">
         <v>15736</v>
@@ -5560,7 +5560,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G179" t="n">
-        <v>3.45365071296692</v>
+        <v>3.4536509513855</v>
       </c>
       <c r="H179" t="n">
         <v>1256</v>
@@ -5589,7 +5589,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G180" t="n">
-        <v>3.56566119194031</v>
+        <v>3.56566095352173</v>
       </c>
       <c r="H180" t="n">
         <v>6037</v>
@@ -5618,7 +5618,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G181" t="n">
-        <v>3.51899027824402</v>
+        <v>3.51899003982544</v>
       </c>
       <c r="H181" t="n">
         <v>1786</v>
@@ -5734,7 +5734,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G185" t="n">
-        <v>3.08961725234985</v>
+        <v>3.08961749076843</v>
       </c>
       <c r="H185" t="n">
         <v>4124</v>
@@ -5763,7 +5763,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G186" t="n">
-        <v>2.92160224914551</v>
+        <v>2.92160201072693</v>
       </c>
       <c r="H186" t="n">
         <v>2211</v>
@@ -5821,7 +5821,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G188" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H188" t="n">
         <v>6941</v>
@@ -5850,7 +5850,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G189" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G190" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H190" t="n">
         <v>500</v>
@@ -5908,7 +5908,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G191" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -5937,7 +5937,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G192" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -6169,7 +6169,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G200" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H200" t="n">
         <v>925</v>
@@ -6198,7 +6198,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G201" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H201" t="n">
         <v>93</v>
@@ -6401,7 +6401,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G208" t="n">
-        <v>2.91226744651794</v>
+        <v>2.91226768493652</v>
       </c>
       <c r="H208" t="n">
         <v>205</v>
@@ -6488,7 +6488,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G211" t="n">
-        <v>2.77225494384766</v>
+        <v>2.77225470542908</v>
       </c>
       <c r="H211" t="n">
         <v>5153</v>
@@ -6517,7 +6517,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>2.76292061805725</v>
+        <v>2.76292037963867</v>
       </c>
       <c r="H212" t="n">
         <v>1030</v>
@@ -6546,7 +6546,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G213" t="n">
-        <v>2.65091013908386</v>
+        <v>2.65091037750244</v>
       </c>
       <c r="H213" t="n">
         <v>760</v>
@@ -6691,7 +6691,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G218" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H218" t="n">
         <v>488</v>
@@ -6749,7 +6749,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G220" t="n">
-        <v>2.85626244544983</v>
+        <v>2.85626268386841</v>
       </c>
       <c r="H220" t="n">
         <v>4706</v>
@@ -6894,7 +6894,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G225" t="n">
-        <v>2.73491787910461</v>
+        <v>2.73491835594177</v>
       </c>
       <c r="H225" t="n">
         <v>823</v>
@@ -7097,7 +7097,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G232" t="n">
-        <v>2.65091013908386</v>
+        <v>2.65091037750244</v>
       </c>
       <c r="H232" t="n">
         <v>1146</v>
@@ -7126,7 +7126,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>2.76292061805725</v>
+        <v>2.76292037963867</v>
       </c>
       <c r="H233" t="n">
         <v>2100</v>
@@ -7213,7 +7213,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G236" t="n">
-        <v>2.753586769104</v>
+        <v>2.75358653068542</v>
       </c>
       <c r="H236" t="n">
         <v>2835</v>
@@ -7271,7 +7271,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G238" t="n">
-        <v>2.85626244544983</v>
+        <v>2.85626268386841</v>
       </c>
       <c r="H238" t="n">
         <v>3815</v>
@@ -7300,7 +7300,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G239" t="n">
-        <v>2.85626244544983</v>
+        <v>2.85626268386841</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G247" t="n">
-        <v>2.91226744651794</v>
+        <v>2.91226768493652</v>
       </c>
       <c r="H247" t="n">
         <v>1679</v>
@@ -7561,7 +7561,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G248" t="n">
-        <v>2.97760725021362</v>
+        <v>2.97760701179504</v>
       </c>
       <c r="H248" t="n">
         <v>6756</v>
@@ -7590,7 +7590,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G249" t="n">
-        <v>2.88426494598389</v>
+        <v>2.88426518440247</v>
       </c>
       <c r="H249" t="n">
         <v>3107</v>
@@ -8083,7 +8083,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G266" t="n">
-        <v>2.62290787696838</v>
+        <v>2.6229076385498</v>
       </c>
       <c r="H266" t="n">
         <v>2300</v>
@@ -8141,7 +8141,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G268" t="n">
-        <v>2.63224196434021</v>
+        <v>2.63224172592163</v>
       </c>
       <c r="H268" t="n">
         <v>1640</v>
@@ -8199,7 +8199,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G270" t="n">
-        <v>2.62290787696838</v>
+        <v>2.6229076385498</v>
       </c>
       <c r="H270" t="n">
         <v>626</v>
@@ -8286,7 +8286,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G273" t="n">
-        <v>2.52956604957581</v>
+        <v>2.52956581115723</v>
       </c>
       <c r="H273" t="n">
         <v>3807</v>
@@ -8315,7 +8315,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G274" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H274" t="n">
         <v>12686</v>
@@ -8344,7 +8344,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G275" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H275" t="n">
         <v>3412</v>
@@ -8402,7 +8402,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G277" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H277" t="n">
         <v>689</v>
@@ -8431,7 +8431,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G278" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H278" t="n">
         <v>0</v>
@@ -8460,7 +8460,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G279" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H279" t="n">
         <v>1890</v>
@@ -8489,7 +8489,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G280" t="n">
-        <v>2.52956604957581</v>
+        <v>2.52956581115723</v>
       </c>
       <c r="H280" t="n">
         <v>3085</v>
@@ -8547,7 +8547,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G282" t="n">
-        <v>2.48289513587952</v>
+        <v>2.48289489746094</v>
       </c>
       <c r="H282" t="n">
         <v>1691</v>
@@ -8605,7 +8605,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G284" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H284" t="n">
         <v>550</v>
@@ -8634,7 +8634,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G285" t="n">
-        <v>2.40822148323059</v>
+        <v>2.40822124481201</v>
       </c>
       <c r="H285" t="n">
         <v>437</v>
@@ -8663,7 +8663,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G286" t="n">
-        <v>2.40822148323059</v>
+        <v>2.40822124481201</v>
       </c>
       <c r="H286" t="n">
         <v>155</v>
@@ -8808,7 +8808,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G291" t="n">
-        <v>2.62290787696838</v>
+        <v>2.6229076385498</v>
       </c>
       <c r="H291" t="n">
         <v>32348</v>
@@ -8924,7 +8924,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G295" t="n">
-        <v>2.54823422431946</v>
+        <v>2.54823446273804</v>
       </c>
       <c r="H295" t="n">
         <v>1050</v>
@@ -8982,7 +8982,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G297" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H297" t="n">
         <v>238</v>
@@ -9011,7 +9011,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G298" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H298" t="n">
         <v>0</v>
@@ -9272,7 +9272,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G307" t="n">
-        <v>2.50156331062317</v>
+        <v>2.50156354904175</v>
       </c>
       <c r="H307" t="n">
         <v>7083</v>
@@ -9301,7 +9301,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G308" t="n">
-        <v>2.46422648429871</v>
+        <v>2.46422672271729</v>
       </c>
       <c r="H308" t="n">
         <v>982</v>
@@ -9388,7 +9388,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G311" t="n">
-        <v>2.48289513587952</v>
+        <v>2.48289489746094</v>
       </c>
       <c r="H311" t="n">
         <v>204</v>
@@ -9417,7 +9417,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G312" t="n">
-        <v>2.48289513587952</v>
+        <v>2.48289489746094</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G313" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H313" t="n">
         <v>350</v>
@@ -9504,7 +9504,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G315" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H315" t="n">
         <v>500</v>
@@ -9533,7 +9533,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G316" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H316" t="n">
         <v>2033</v>
@@ -9620,7 +9620,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G319" t="n">
-        <v>2.40822148323059</v>
+        <v>2.40822124481201</v>
       </c>
       <c r="H319" t="n">
         <v>50</v>
@@ -9649,7 +9649,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G320" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H320" t="n">
         <v>110</v>
@@ -9678,7 +9678,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G321" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H321" t="n">
         <v>3920</v>
@@ -9765,7 +9765,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G324" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H324" t="n">
         <v>1280</v>
@@ -9794,7 +9794,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G325" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G326" t="n">
-        <v>2.36155033111572</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H326" t="n">
         <v>4022</v>
@@ -9852,7 +9852,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H327" t="n">
         <v>7005</v>
@@ -9910,7 +9910,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G329" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H329" t="n">
         <v>2690</v>
@@ -9939,7 +9939,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G330" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -9968,7 +9968,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G331" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -9997,7 +9997,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G332" t="n">
-        <v>2.27754282951355</v>
+        <v>2.27754259109497</v>
       </c>
       <c r="H332" t="n">
         <v>2310</v>
@@ -10055,7 +10055,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G334" t="n">
-        <v>2.24020576477051</v>
+        <v>2.24020600318909</v>
       </c>
       <c r="H334" t="n">
         <v>4089</v>
@@ -10113,7 +10113,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G336" t="n">
-        <v>2.26820850372314</v>
+        <v>2.26820874214172</v>
       </c>
       <c r="H336" t="n">
         <v>12996</v>
@@ -10142,7 +10142,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G337" t="n">
-        <v>2.24020576477051</v>
+        <v>2.24020600318909</v>
       </c>
       <c r="H337" t="n">
         <v>15170</v>
@@ -10200,7 +10200,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G339" t="n">
-        <v>2.12819576263428</v>
+        <v>2.1281955242157</v>
       </c>
       <c r="H339" t="n">
         <v>35672</v>
@@ -10287,7 +10287,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>2.06285643577576</v>
+        <v>2.06285619735718</v>
       </c>
       <c r="H342" t="n">
         <v>15756</v>
@@ -10316,7 +10316,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G343" t="n">
-        <v>1.98818302154541</v>
+        <v>1.98818278312683</v>
       </c>
       <c r="H343" t="n">
         <v>9524</v>
@@ -10461,7 +10461,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G348" t="n">
-        <v>1.76416206359863</v>
+        <v>1.76416218280792</v>
       </c>
       <c r="H348" t="n">
         <v>3234</v>
@@ -10548,7 +10548,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G351" t="n">
-        <v>1.57747840881348</v>
+        <v>1.57747828960419</v>
       </c>
       <c r="H351" t="n">
         <v>44141</v>
@@ -10838,7 +10838,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G361" t="n">
-        <v>1.66148614883423</v>
+        <v>1.66148602962494</v>
       </c>
       <c r="H361" t="n">
         <v>186911</v>
@@ -10896,7 +10896,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G363" t="n">
-        <v>1.84817004203796</v>
+        <v>1.84816980361938</v>
       </c>
       <c r="H363" t="n">
         <v>74595</v>
@@ -10954,7 +10954,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G365" t="n">
-        <v>1.94151163101196</v>
+        <v>1.94151175022125</v>
       </c>
       <c r="H365" t="n">
         <v>38866</v>
@@ -10983,7 +10983,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G366" t="n">
-        <v>2.02551937103271</v>
+        <v>2.02551984786987</v>
       </c>
       <c r="H366" t="n">
         <v>41167</v>
@@ -11012,7 +11012,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G367" t="n">
-        <v>2.06285643577576</v>
+        <v>2.06285619735718</v>
       </c>
       <c r="H367" t="n">
         <v>65581</v>
@@ -11070,7 +11070,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G369" t="n">
-        <v>2.12819576263428</v>
+        <v>2.1281955242157</v>
       </c>
       <c r="H369" t="n">
         <v>27238</v>
@@ -11157,7 +11157,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G372" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H372" t="n">
         <v>100574</v>
@@ -11186,7 +11186,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G373" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H373" t="n">
         <v>50734</v>
@@ -11215,7 +11215,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G374" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H374" t="n">
         <v>32104</v>
@@ -11273,7 +11273,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G376" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H376" t="n">
         <v>260524</v>
@@ -11418,7 +11418,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G381" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H381" t="n">
         <v>13489</v>
@@ -11447,7 +11447,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G382" t="n">
-        <v>2.50156331062317</v>
+        <v>2.50156354904175</v>
       </c>
       <c r="H382" t="n">
         <v>22219</v>
@@ -11476,7 +11476,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G383" t="n">
-        <v>2.40822148323059</v>
+        <v>2.40822124481201</v>
       </c>
       <c r="H383" t="n">
         <v>19181</v>
@@ -11505,7 +11505,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G384" t="n">
-        <v>2.36155033111572</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H384" t="n">
         <v>46528</v>
@@ -11592,7 +11592,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G387" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H387" t="n">
         <v>20692</v>
@@ -11737,7 +11737,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G392" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H392" t="n">
         <v>78496</v>
@@ -11766,7 +11766,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G393" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H393" t="n">
         <v>2710</v>
@@ -11853,7 +11853,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G396" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H396" t="n">
         <v>3361</v>
@@ -11882,7 +11882,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G397" t="n">
-        <v>2.27754282951355</v>
+        <v>2.27754259109497</v>
       </c>
       <c r="H397" t="n">
         <v>70461</v>
@@ -11911,7 +11911,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H398" t="n">
         <v>4671</v>
@@ -11940,7 +11940,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G399" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H399" t="n">
         <v>20075</v>
@@ -11969,7 +11969,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G400" t="n">
-        <v>2.20286893844604</v>
+        <v>2.20286917686462</v>
       </c>
       <c r="H400" t="n">
         <v>35084</v>
@@ -11998,7 +11998,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G401" t="n">
-        <v>2.072190284729</v>
+        <v>2.07219052314758</v>
       </c>
       <c r="H401" t="n">
         <v>51398</v>
@@ -12201,7 +12201,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G408" t="n">
-        <v>2.20286893844604</v>
+        <v>2.20286917686462</v>
       </c>
       <c r="H408" t="n">
         <v>20357</v>
@@ -12375,7 +12375,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G414" t="n">
-        <v>2.08152484893799</v>
+        <v>2.08152461051941</v>
       </c>
       <c r="H414" t="n">
         <v>6065</v>
@@ -12462,7 +12462,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G417" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H417" t="n">
         <v>112741</v>
@@ -12491,7 +12491,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G418" t="n">
-        <v>2.40822148323059</v>
+        <v>2.40822124481201</v>
       </c>
       <c r="H418" t="n">
         <v>31183</v>
@@ -12520,7 +12520,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G419" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H419" t="n">
         <v>24246</v>
@@ -12607,7 +12607,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G422" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H422" t="n">
         <v>15411</v>
@@ -12665,7 +12665,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G424" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H424" t="n">
         <v>4139</v>
@@ -12723,7 +12723,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G426" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H426" t="n">
         <v>6863</v>
@@ -12752,7 +12752,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G427" t="n">
-        <v>2.26820850372314</v>
+        <v>2.26820874214172</v>
       </c>
       <c r="H427" t="n">
         <v>8209</v>
@@ -12781,7 +12781,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G428" t="n">
-        <v>2.27754282951355</v>
+        <v>2.27754259109497</v>
       </c>
       <c r="H428" t="n">
         <v>8879</v>
@@ -12810,7 +12810,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G429" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H429" t="n">
         <v>17663</v>
@@ -12839,7 +12839,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G430" t="n">
-        <v>2.2588746547699</v>
+        <v>2.25887441635132</v>
       </c>
       <c r="H430" t="n">
         <v>8648</v>
@@ -12868,7 +12868,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G431" t="n">
-        <v>2.2588746547699</v>
+        <v>2.25887441635132</v>
       </c>
       <c r="H431" t="n">
         <v>10630</v>
@@ -12897,7 +12897,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G432" t="n">
-        <v>2.27754282951355</v>
+        <v>2.27754259109497</v>
       </c>
       <c r="H432" t="n">
         <v>5782</v>
@@ -12926,7 +12926,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G433" t="n">
-        <v>2.2588746547699</v>
+        <v>2.25887441635132</v>
       </c>
       <c r="H433" t="n">
         <v>39250</v>
@@ -12955,7 +12955,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G434" t="n">
-        <v>2.24020576477051</v>
+        <v>2.24020600318909</v>
       </c>
       <c r="H434" t="n">
         <v>3580</v>
@@ -13013,7 +13013,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G436" t="n">
-        <v>2.27754282951355</v>
+        <v>2.27754259109497</v>
       </c>
       <c r="H436" t="n">
         <v>3250</v>
@@ -13042,7 +13042,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G437" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H437" t="n">
         <v>10145</v>
@@ -13071,7 +13071,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G438" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H438" t="n">
         <v>40576</v>
@@ -13100,7 +13100,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G439" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H439" t="n">
         <v>6378</v>
@@ -13158,7 +13158,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G441" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H441" t="n">
         <v>4745</v>
@@ -13216,7 +13216,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G443" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H443" t="n">
         <v>10240</v>
@@ -13274,7 +13274,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G445" t="n">
-        <v>2.23087191581726</v>
+        <v>2.23087167739868</v>
       </c>
       <c r="H445" t="n">
         <v>29277</v>
@@ -13303,7 +13303,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G446" t="n">
-        <v>2.23087191581726</v>
+        <v>2.23087167739868</v>
       </c>
       <c r="H446" t="n">
         <v>37961</v>
@@ -13332,7 +13332,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G447" t="n">
-        <v>2.27754282951355</v>
+        <v>2.27754259109497</v>
       </c>
       <c r="H447" t="n">
         <v>53947</v>
@@ -13361,7 +13361,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G448" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H448" t="n">
         <v>75506</v>
@@ -13419,7 +13419,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G450" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H450" t="n">
         <v>45849</v>
@@ -13738,7 +13738,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G461" t="n">
-        <v>2.73491787910461</v>
+        <v>2.73491835594177</v>
       </c>
       <c r="H461" t="n">
         <v>18508</v>
@@ -13854,7 +13854,7 @@
         <v>3.25</v>
       </c>
       <c r="G465" t="n">
-        <v>3.03361201286316</v>
+        <v>3.03361225128174</v>
       </c>
       <c r="H465" t="n">
         <v>83242</v>
@@ -13912,7 +13912,7 @@
         <v>3.25</v>
       </c>
       <c r="G467" t="n">
-        <v>3.03361201286316</v>
+        <v>3.03361225128174</v>
       </c>
       <c r="H467" t="n">
         <v>62595</v>
@@ -13941,7 +13941,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G468" t="n">
-        <v>3.08028292655945</v>
+        <v>3.08028316497803</v>
       </c>
       <c r="H468" t="n">
         <v>39566</v>
@@ -13970,7 +13970,7 @@
         <v>3.25</v>
       </c>
       <c r="G469" t="n">
-        <v>3.03361201286316</v>
+        <v>3.03361225128174</v>
       </c>
       <c r="H469" t="n">
         <v>22979</v>
@@ -14028,7 +14028,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G471" t="n">
-        <v>3.27630114555359</v>
+        <v>3.27630138397217</v>
       </c>
       <c r="H471" t="n">
         <v>27454</v>
@@ -14086,7 +14086,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G473" t="n">
-        <v>3.33230638504028</v>
+        <v>3.3323061466217</v>
       </c>
       <c r="H473" t="n">
         <v>14421</v>
@@ -14144,7 +14144,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G475" t="n">
-        <v>3.22962999343872</v>
+        <v>3.2296302318573</v>
       </c>
       <c r="H475" t="n">
         <v>13099</v>
@@ -14202,7 +14202,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G477" t="n">
-        <v>3.11761999130249</v>
+        <v>3.11761975288391</v>
       </c>
       <c r="H477" t="n">
         <v>29958</v>
@@ -14289,7 +14289,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G480" t="n">
-        <v>3.20162796974182</v>
+        <v>3.20162773132324</v>
       </c>
       <c r="H480" t="n">
         <v>55118</v>
@@ -14347,7 +14347,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G482" t="n">
-        <v>3.08961725234985</v>
+        <v>3.08961749076843</v>
       </c>
       <c r="H482" t="n">
         <v>34183</v>
@@ -14376,7 +14376,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G483" t="n">
-        <v>3.12695407867432</v>
+        <v>3.12695384025574</v>
       </c>
       <c r="H483" t="n">
         <v>32378</v>
@@ -14434,7 +14434,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G485" t="n">
-        <v>3.15495681762695</v>
+        <v>3.15495657920837</v>
       </c>
       <c r="H485" t="n">
         <v>12813</v>
@@ -14550,7 +14550,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G489" t="n">
-        <v>3.11761999130249</v>
+        <v>3.11761975288391</v>
       </c>
       <c r="H489" t="n">
         <v>17075</v>
@@ -14579,7 +14579,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G490" t="n">
-        <v>3.08028292655945</v>
+        <v>3.08028316497803</v>
       </c>
       <c r="H490" t="n">
         <v>17126</v>
@@ -14637,7 +14637,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G492" t="n">
-        <v>2.97760725021362</v>
+        <v>2.97760701179504</v>
       </c>
       <c r="H492" t="n">
         <v>12648</v>
@@ -14666,7 +14666,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G493" t="n">
-        <v>3.04294633865356</v>
+        <v>3.04294657707214</v>
       </c>
       <c r="H493" t="n">
         <v>3499</v>
@@ -14753,7 +14753,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G496" t="n">
-        <v>3.08028292655945</v>
+        <v>3.08028316497803</v>
       </c>
       <c r="H496" t="n">
         <v>39248</v>
@@ -14782,7 +14782,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G497" t="n">
-        <v>3.08028292655945</v>
+        <v>3.08028316497803</v>
       </c>
       <c r="H497" t="n">
         <v>17788</v>
@@ -14840,7 +14840,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G499" t="n">
-        <v>3.11761999130249</v>
+        <v>3.11761975288391</v>
       </c>
       <c r="H499" t="n">
         <v>21907</v>
@@ -14869,7 +14869,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G500" t="n">
-        <v>3.11761999130249</v>
+        <v>3.11761975288391</v>
       </c>
       <c r="H500" t="n">
         <v>17501</v>
@@ -14956,7 +14956,7 @@
         <v>3.25</v>
       </c>
       <c r="G503" t="n">
-        <v>3.03361201286316</v>
+        <v>3.03361225128174</v>
       </c>
       <c r="H503" t="n">
         <v>5248</v>
@@ -14985,7 +14985,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G504" t="n">
-        <v>3.02427816390991</v>
+        <v>3.02427792549133</v>
       </c>
       <c r="H504" t="n">
         <v>20370</v>
@@ -15130,7 +15130,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G509" t="n">
-        <v>2.9682731628418</v>
+        <v>2.96827292442322</v>
       </c>
       <c r="H509" t="n">
         <v>5868</v>
@@ -15391,7 +15391,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G518" t="n">
-        <v>2.73491787910461</v>
+        <v>2.73491835594177</v>
       </c>
       <c r="H518" t="n">
         <v>15415</v>
@@ -15478,7 +15478,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G521" t="n">
-        <v>2.753586769104</v>
+        <v>2.75358653068542</v>
       </c>
       <c r="H521" t="n">
         <v>5980</v>
@@ -15565,7 +15565,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G524" t="n">
-        <v>2.63224196434021</v>
+        <v>2.63224172592163</v>
       </c>
       <c r="H524" t="n">
         <v>10487</v>
@@ -15710,7 +15710,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G529" t="n">
-        <v>2.46422648429871</v>
+        <v>2.46422672271729</v>
       </c>
       <c r="H529" t="n">
         <v>31873</v>
@@ -15768,7 +15768,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G531" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H531" t="n">
         <v>29110</v>
@@ -15797,7 +15797,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G532" t="n">
-        <v>2.46422648429871</v>
+        <v>2.46422672271729</v>
       </c>
       <c r="H532" t="n">
         <v>14070</v>
@@ -15855,7 +15855,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G534" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H534" t="n">
         <v>58949</v>
@@ -15913,7 +15913,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G536" t="n">
-        <v>2.52956604957581</v>
+        <v>2.52956581115723</v>
       </c>
       <c r="H536" t="n">
         <v>18439</v>
@@ -15971,7 +15971,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G538" t="n">
-        <v>2.62290787696838</v>
+        <v>2.6229076385498</v>
       </c>
       <c r="H538" t="n">
         <v>65552</v>
@@ -16000,7 +16000,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G539" t="n">
-        <v>2.62290787696838</v>
+        <v>2.6229076385498</v>
       </c>
       <c r="H539" t="n">
         <v>55945</v>
@@ -16029,7 +16029,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G540" t="n">
-        <v>2.62290787696838</v>
+        <v>2.6229076385498</v>
       </c>
       <c r="H540" t="n">
         <v>32955</v>
@@ -16087,7 +16087,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G542" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H542" t="n">
         <v>34564</v>
@@ -16116,7 +16116,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G543" t="n">
-        <v>2.63224196434021</v>
+        <v>2.63224172592163</v>
       </c>
       <c r="H543" t="n">
         <v>7927</v>
@@ -16145,7 +16145,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G544" t="n">
-        <v>2.54823422431946</v>
+        <v>2.54823446273804</v>
       </c>
       <c r="H544" t="n">
         <v>22371</v>
@@ -16406,7 +16406,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G553" t="n">
-        <v>2.65091013908386</v>
+        <v>2.65091037750244</v>
       </c>
       <c r="H553" t="n">
         <v>17288</v>
@@ -16464,7 +16464,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G555" t="n">
-        <v>2.753586769104</v>
+        <v>2.75358653068542</v>
       </c>
       <c r="H555" t="n">
         <v>44001</v>
@@ -16493,7 +16493,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G556" t="n">
-        <v>2.77225494384766</v>
+        <v>2.77225470542908</v>
       </c>
       <c r="H556" t="n">
         <v>1552</v>
@@ -16522,7 +16522,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G557" t="n">
-        <v>2.77225494384766</v>
+        <v>2.77225470542908</v>
       </c>
       <c r="H557" t="n">
         <v>7892</v>
@@ -16551,7 +16551,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G558" t="n">
-        <v>2.65091013908386</v>
+        <v>2.65091037750244</v>
       </c>
       <c r="H558" t="n">
         <v>16646</v>
@@ -16580,7 +16580,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G559" t="n">
-        <v>2.65091013908386</v>
+        <v>2.65091037750244</v>
       </c>
       <c r="H559" t="n">
         <v>14560</v>
@@ -16638,7 +16638,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G561" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H561" t="n">
         <v>55511</v>
@@ -16899,7 +16899,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G570" t="n">
-        <v>2.77225494384766</v>
+        <v>2.77225470542908</v>
       </c>
       <c r="H570" t="n">
         <v>12140</v>
@@ -17102,7 +17102,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G577" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H577" t="n">
         <v>5655</v>
@@ -17218,7 +17218,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G581" t="n">
-        <v>2.77225494384766</v>
+        <v>2.77225470542908</v>
       </c>
       <c r="H581" t="n">
         <v>1650</v>
@@ -17276,7 +17276,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G583" t="n">
-        <v>2.76292061805725</v>
+        <v>2.76292037963867</v>
       </c>
       <c r="H583" t="n">
         <v>1500</v>
@@ -17450,7 +17450,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G589" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H589" t="n">
         <v>5281</v>
@@ -17508,7 +17508,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G591" t="n">
-        <v>2.77225494384766</v>
+        <v>2.77225470542908</v>
       </c>
       <c r="H591" t="n">
         <v>2450</v>
@@ -17537,7 +17537,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G592" t="n">
-        <v>2.77225494384766</v>
+        <v>2.77225470542908</v>
       </c>
       <c r="H592" t="n">
         <v>0</v>
@@ -17595,7 +17595,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G594" t="n">
-        <v>2.79092335700989</v>
+        <v>2.79092311859131</v>
       </c>
       <c r="H594" t="n">
         <v>3352</v>
@@ -17653,7 +17653,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G596" t="n">
-        <v>2.77225494384766</v>
+        <v>2.77225470542908</v>
       </c>
       <c r="H596" t="n">
         <v>850</v>
@@ -17711,7 +17711,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G598" t="n">
-        <v>2.753586769104</v>
+        <v>2.75358653068542</v>
       </c>
       <c r="H598" t="n">
         <v>47530</v>
@@ -17769,7 +17769,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G600" t="n">
-        <v>2.753586769104</v>
+        <v>2.75358653068542</v>
       </c>
       <c r="H600" t="n">
         <v>7623</v>
@@ -17856,7 +17856,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G603" t="n">
-        <v>2.73491787910461</v>
+        <v>2.73491835594177</v>
       </c>
       <c r="H603" t="n">
         <v>6297</v>
@@ -18030,7 +18030,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G609" t="n">
-        <v>2.76292061805725</v>
+        <v>2.76292037963867</v>
       </c>
       <c r="H609" t="n">
         <v>13444</v>
@@ -18059,7 +18059,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G610" t="n">
-        <v>2.77225494384766</v>
+        <v>2.77225470542908</v>
       </c>
       <c r="H610" t="n">
         <v>4440</v>
@@ -18175,7 +18175,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G614" t="n">
-        <v>2.77225494384766</v>
+        <v>2.77225470542908</v>
       </c>
       <c r="H614" t="n">
         <v>20031</v>
@@ -18407,7 +18407,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G622" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H622" t="n">
         <v>9853</v>
@@ -18494,7 +18494,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G625" t="n">
-        <v>2.48289513587952</v>
+        <v>2.48289489746094</v>
       </c>
       <c r="H625" t="n">
         <v>9305</v>
@@ -18523,7 +18523,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G626" t="n">
-        <v>2.50156331062317</v>
+        <v>2.50156354904175</v>
       </c>
       <c r="H626" t="n">
         <v>7546</v>
@@ -18552,7 +18552,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G627" t="n">
-        <v>2.48289513587952</v>
+        <v>2.48289489746094</v>
       </c>
       <c r="H627" t="n">
         <v>3175</v>
@@ -18610,7 +18610,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G629" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H629" t="n">
         <v>9381</v>
@@ -18639,7 +18639,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G630" t="n">
-        <v>2.52956604957581</v>
+        <v>2.52956581115723</v>
       </c>
       <c r="H630" t="n">
         <v>5890</v>
@@ -18784,7 +18784,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G635" t="n">
-        <v>2.65091013908386</v>
+        <v>2.65091037750244</v>
       </c>
       <c r="H635" t="n">
         <v>1700</v>
@@ -18871,7 +18871,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G638" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H638" t="n">
         <v>10004</v>
@@ -19045,7 +19045,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G644" t="n">
-        <v>2.50156331062317</v>
+        <v>2.50156354904175</v>
       </c>
       <c r="H644" t="n">
         <v>7248</v>
@@ -19074,7 +19074,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G645" t="n">
-        <v>2.40822148323059</v>
+        <v>2.40822124481201</v>
       </c>
       <c r="H645" t="n">
         <v>26536</v>
@@ -19248,7 +19248,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G651" t="n">
-        <v>2.54823422431946</v>
+        <v>2.54823446273804</v>
       </c>
       <c r="H651" t="n">
         <v>1402</v>
@@ -19277,7 +19277,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G652" t="n">
-        <v>2.52956604957581</v>
+        <v>2.52956581115723</v>
       </c>
       <c r="H652" t="n">
         <v>6533</v>
@@ -19306,7 +19306,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G653" t="n">
-        <v>2.52956604957581</v>
+        <v>2.52956581115723</v>
       </c>
       <c r="H653" t="n">
         <v>6896</v>
@@ -19335,7 +19335,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G654" t="n">
-        <v>2.50156331062317</v>
+        <v>2.50156354904175</v>
       </c>
       <c r="H654" t="n">
         <v>2900</v>
@@ -19393,7 +19393,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>2.52956604957581</v>
+        <v>2.52956581115723</v>
       </c>
       <c r="H656" t="n">
         <v>5573</v>
@@ -19654,7 +19654,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G665" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H665" t="n">
         <v>1580</v>
@@ -19828,7 +19828,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G671" t="n">
-        <v>2.52956604957581</v>
+        <v>2.52956581115723</v>
       </c>
       <c r="H671" t="n">
         <v>1055</v>
@@ -19915,7 +19915,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G674" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H674" t="n">
         <v>1004</v>
@@ -19944,7 +19944,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G675" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H675" t="n">
         <v>0</v>
@@ -20060,7 +20060,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G679" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H679" t="n">
         <v>6131</v>
@@ -20234,7 +20234,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G685" t="n">
-        <v>2.65091013908386</v>
+        <v>2.65091037750244</v>
       </c>
       <c r="H685" t="n">
         <v>3302</v>
@@ -20263,7 +20263,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G686" t="n">
-        <v>2.48289513587952</v>
+        <v>2.48289489746094</v>
       </c>
       <c r="H686" t="n">
         <v>18872</v>
@@ -20321,7 +20321,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G688" t="n">
-        <v>2.50156331062317</v>
+        <v>2.50156354904175</v>
       </c>
       <c r="H688" t="n">
         <v>5477</v>
@@ -20350,7 +20350,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G689" t="n">
-        <v>2.510897397995</v>
+        <v>2.51089763641357</v>
       </c>
       <c r="H689" t="n">
         <v>6459</v>
@@ -20524,7 +20524,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G695" t="n">
-        <v>2.23087191581726</v>
+        <v>2.23087167739868</v>
       </c>
       <c r="H695" t="n">
         <v>25461</v>
@@ -20582,7 +20582,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G697" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H697" t="n">
         <v>5477</v>
@@ -20611,7 +20611,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G698" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H698" t="n">
         <v>4617</v>
@@ -20669,7 +20669,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G700" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H700" t="n">
         <v>10078</v>
@@ -20698,7 +20698,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G701" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H701" t="n">
         <v>11679</v>
@@ -20727,7 +20727,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G702" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H702" t="n">
         <v>12282</v>
@@ -20814,7 +20814,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G705" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H705" t="n">
         <v>7231</v>
@@ -20843,7 +20843,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G706" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H706" t="n">
         <v>16794</v>
@@ -20901,7 +20901,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G708" t="n">
-        <v>2.40822148323059</v>
+        <v>2.40822124481201</v>
       </c>
       <c r="H708" t="n">
         <v>11650</v>
@@ -21046,7 +21046,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G713" t="n">
-        <v>2.36155033111572</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H713" t="n">
         <v>5601</v>
@@ -21075,7 +21075,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G714" t="n">
-        <v>2.40822148323059</v>
+        <v>2.40822124481201</v>
       </c>
       <c r="H714" t="n">
         <v>3865</v>
@@ -21249,7 +21249,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G720" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H720" t="n">
         <v>2110</v>
@@ -21307,7 +21307,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G722" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H722" t="n">
         <v>20</v>
@@ -21365,7 +21365,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G724" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H724" t="n">
         <v>3000</v>
@@ -21394,7 +21394,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G725" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H725" t="n">
         <v>2583</v>
@@ -21423,7 +21423,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G726" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H726" t="n">
         <v>2</v>
@@ -21452,7 +21452,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G727" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H727" t="n">
         <v>4770</v>
@@ -21481,7 +21481,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G728" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H728" t="n">
         <v>6795</v>
@@ -21539,7 +21539,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G730" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H730" t="n">
         <v>9829</v>
@@ -21655,7 +21655,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G734" t="n">
-        <v>2.36155033111572</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H734" t="n">
         <v>59751</v>
@@ -21713,7 +21713,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G736" t="n">
-        <v>2.24020576477051</v>
+        <v>2.24020600318909</v>
       </c>
       <c r="H736" t="n">
         <v>8673</v>
@@ -21800,7 +21800,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G739" t="n">
-        <v>2.23087191581726</v>
+        <v>2.23087167739868</v>
       </c>
       <c r="H739" t="n">
         <v>4337</v>
@@ -21887,7 +21887,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G742" t="n">
-        <v>2.23087191581726</v>
+        <v>2.23087167739868</v>
       </c>
       <c r="H742" t="n">
         <v>6415</v>
@@ -21974,7 +21974,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G745" t="n">
-        <v>2.20286893844604</v>
+        <v>2.20286917686462</v>
       </c>
       <c r="H745" t="n">
         <v>3400</v>
@@ -22061,7 +22061,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G748" t="n">
-        <v>2.12819576263428</v>
+        <v>2.1281955242157</v>
       </c>
       <c r="H748" t="n">
         <v>9244</v>
@@ -22090,7 +22090,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G749" t="n">
-        <v>2.12819576263428</v>
+        <v>2.1281955242157</v>
       </c>
       <c r="H749" t="n">
         <v>2187</v>
@@ -22322,7 +22322,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G757" t="n">
-        <v>2.15619802474976</v>
+        <v>2.15619826316833</v>
       </c>
       <c r="H757" t="n">
         <v>5</v>
@@ -22351,7 +22351,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G758" t="n">
-        <v>2.24020576477051</v>
+        <v>2.24020600318909</v>
       </c>
       <c r="H758" t="n">
         <v>3859</v>
@@ -22380,7 +22380,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G759" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H759" t="n">
         <v>6674</v>
@@ -22409,7 +22409,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G760" t="n">
-        <v>2.15619802474976</v>
+        <v>2.15619826316833</v>
       </c>
       <c r="H760" t="n">
         <v>9288</v>
@@ -22496,7 +22496,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G763" t="n">
-        <v>2.15619802474976</v>
+        <v>2.15619826316833</v>
       </c>
       <c r="H763" t="n">
         <v>74</v>
@@ -22670,7 +22670,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G769" t="n">
-        <v>2.08152484893799</v>
+        <v>2.08152461051941</v>
       </c>
       <c r="H769" t="n">
         <v>5355</v>
@@ -22699,7 +22699,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G770" t="n">
-        <v>2.08152484893799</v>
+        <v>2.08152461051941</v>
       </c>
       <c r="H770" t="n">
         <v>0</v>
@@ -22902,7 +22902,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G777" t="n">
-        <v>2.00685119628906</v>
+        <v>2.00685143470764</v>
       </c>
       <c r="H777" t="n">
         <v>6782</v>
@@ -22931,7 +22931,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G778" t="n">
-        <v>2.01618528366089</v>
+        <v>2.01618552207947</v>
       </c>
       <c r="H778" t="n">
         <v>3662</v>
@@ -22960,7 +22960,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G779" t="n">
-        <v>2.01618528366089</v>
+        <v>2.01618552207947</v>
       </c>
       <c r="H779" t="n">
         <v>5386</v>
@@ -22989,7 +22989,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G780" t="n">
-        <v>1.99751710891724</v>
+        <v>1.99751698970795</v>
       </c>
       <c r="H780" t="n">
         <v>923</v>
@@ -23018,7 +23018,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G781" t="n">
-        <v>2.02551937103271</v>
+        <v>2.02551984786987</v>
       </c>
       <c r="H781" t="n">
         <v>2701</v>
@@ -23047,7 +23047,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G782" t="n">
-        <v>1.96018016338348</v>
+        <v>1.96018004417419</v>
       </c>
       <c r="H782" t="n">
         <v>4798</v>
@@ -23076,7 +23076,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G783" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417516231537</v>
       </c>
       <c r="H783" t="n">
         <v>16989</v>
@@ -23192,7 +23192,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G787" t="n">
-        <v>1.76416206359863</v>
+        <v>1.76416218280792</v>
       </c>
       <c r="H787" t="n">
         <v>18464</v>
@@ -23221,7 +23221,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G788" t="n">
-        <v>1.76882922649384</v>
+        <v>1.76882934570312</v>
       </c>
       <c r="H788" t="n">
         <v>25213</v>
@@ -23366,7 +23366,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G793" t="n">
-        <v>1.79216468334198</v>
+        <v>1.79216480255127</v>
       </c>
       <c r="H793" t="n">
         <v>26069</v>
@@ -23424,7 +23424,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G795" t="n">
-        <v>1.84817004203796</v>
+        <v>1.84816980361938</v>
       </c>
       <c r="H795" t="n">
         <v>1870</v>
@@ -23569,7 +23569,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G800" t="n">
-        <v>1.82016742229462</v>
+        <v>1.82016730308533</v>
       </c>
       <c r="H800" t="n">
         <v>293</v>
@@ -23743,7 +23743,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417516231537</v>
       </c>
       <c r="H806" t="n">
         <v>2225</v>
@@ -23772,7 +23772,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G807" t="n">
-        <v>1.88550662994385</v>
+        <v>1.88550674915314</v>
       </c>
       <c r="H807" t="n">
         <v>530</v>
@@ -23975,7 +23975,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G814" t="n">
-        <v>1.98818302154541</v>
+        <v>1.98818278312683</v>
       </c>
       <c r="H814" t="n">
         <v>5130</v>
@@ -24004,7 +24004,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G815" t="n">
-        <v>1.98818302154541</v>
+        <v>1.98818278312683</v>
       </c>
       <c r="H815" t="n">
         <v>13633</v>
@@ -24033,7 +24033,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G816" t="n">
-        <v>1.97884833812714</v>
+        <v>1.978848695755</v>
       </c>
       <c r="H816" t="n">
         <v>18908</v>
@@ -24120,7 +24120,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G819" t="n">
-        <v>1.94151163101196</v>
+        <v>1.94151175022125</v>
       </c>
       <c r="H819" t="n">
         <v>4235</v>
@@ -24236,7 +24236,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G823" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417516231537</v>
       </c>
       <c r="H823" t="n">
         <v>2258</v>
@@ -24265,7 +24265,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G824" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417516231537</v>
       </c>
       <c r="H824" t="n">
         <v>0</v>
@@ -24323,7 +24323,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G826" t="n">
-        <v>2.02551937103271</v>
+        <v>2.02551984786987</v>
       </c>
       <c r="H826" t="n">
         <v>12498</v>
@@ -24352,7 +24352,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G827" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417516231537</v>
       </c>
       <c r="H827" t="n">
         <v>15383</v>
@@ -24381,7 +24381,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G828" t="n">
-        <v>1.88550662994385</v>
+        <v>1.88550674915314</v>
       </c>
       <c r="H828" t="n">
         <v>2410</v>
@@ -24410,7 +24410,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G829" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417516231537</v>
       </c>
       <c r="H829" t="n">
         <v>4980</v>
@@ -24468,7 +24468,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G831" t="n">
-        <v>1.84817004203796</v>
+        <v>1.84816980361938</v>
       </c>
       <c r="H831" t="n">
         <v>1282</v>
@@ -24526,7 +24526,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G833" t="n">
-        <v>1.88550662994385</v>
+        <v>1.88550674915314</v>
       </c>
       <c r="H833" t="n">
         <v>500</v>
@@ -24671,7 +24671,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G838" t="n">
-        <v>1.82016742229462</v>
+        <v>1.82016730308533</v>
       </c>
       <c r="H838" t="n">
         <v>2308</v>
@@ -24787,7 +24787,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G842" t="n">
-        <v>1.79216468334198</v>
+        <v>1.79216480255127</v>
       </c>
       <c r="H842" t="n">
         <v>5998</v>
@@ -24845,7 +24845,7 @@
         <v>1.875</v>
       </c>
       <c r="G844" t="n">
-        <v>1.75016093254089</v>
+        <v>1.7501608133316</v>
       </c>
       <c r="H844" t="n">
         <v>17976</v>
@@ -25048,7 +25048,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G851" t="n">
-        <v>1.79216468334198</v>
+        <v>1.79216480255127</v>
       </c>
       <c r="H851" t="n">
         <v>8829</v>
@@ -25106,7 +25106,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G853" t="n">
-        <v>1.82016742229462</v>
+        <v>1.82016730308533</v>
       </c>
       <c r="H853" t="n">
         <v>4615</v>
@@ -25251,7 +25251,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G858" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417516231537</v>
       </c>
       <c r="H858" t="n">
         <v>1659</v>
@@ -25309,7 +25309,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G860" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417516231537</v>
       </c>
       <c r="H860" t="n">
         <v>5149</v>
@@ -25425,7 +25425,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G864" t="n">
-        <v>1.84817004203796</v>
+        <v>1.84816980361938</v>
       </c>
       <c r="H864" t="n">
         <v>1500</v>
@@ -25570,7 +25570,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G869" t="n">
-        <v>1.88550662994385</v>
+        <v>1.88550674915314</v>
       </c>
       <c r="H869" t="n">
         <v>4311</v>
@@ -25599,7 +25599,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G870" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417516231537</v>
       </c>
       <c r="H870" t="n">
         <v>5440</v>
@@ -25628,7 +25628,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G871" t="n">
-        <v>1.94151163101196</v>
+        <v>1.94151175022125</v>
       </c>
       <c r="H871" t="n">
         <v>830</v>
@@ -25744,7 +25744,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G875" t="n">
-        <v>1.88550662994385</v>
+        <v>1.88550674915314</v>
       </c>
       <c r="H875" t="n">
         <v>7617</v>
@@ -25947,7 +25947,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G882" t="n">
-        <v>1.94151163101196</v>
+        <v>1.94151175022125</v>
       </c>
       <c r="H882" t="n">
         <v>5000</v>
@@ -25976,7 +25976,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G883" t="n">
-        <v>1.94151163101196</v>
+        <v>1.94151175022125</v>
       </c>
       <c r="H883" t="n">
         <v>1500</v>
@@ -26034,7 +26034,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417516231537</v>
       </c>
       <c r="H885" t="n">
         <v>6104</v>
@@ -26092,7 +26092,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G887" t="n">
-        <v>1.94151163101196</v>
+        <v>1.94151175022125</v>
       </c>
       <c r="H887" t="n">
         <v>3600</v>
@@ -26121,7 +26121,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G888" t="n">
-        <v>1.94151163101196</v>
+        <v>1.94151175022125</v>
       </c>
       <c r="H888" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G891" t="n">
-        <v>1.94151163101196</v>
+        <v>1.94151175022125</v>
       </c>
       <c r="H891" t="n">
         <v>3305</v>
@@ -26266,7 +26266,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G893" t="n">
-        <v>1.90417492389679</v>
+        <v>1.90417516231537</v>
       </c>
       <c r="H893" t="n">
         <v>2300</v>
@@ -26411,7 +26411,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G898" t="n">
-        <v>2.20286893844604</v>
+        <v>2.20286917686462</v>
       </c>
       <c r="H898" t="n">
         <v>36211</v>
@@ -26469,7 +26469,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G900" t="n">
-        <v>2.23087191581726</v>
+        <v>2.23087167739868</v>
       </c>
       <c r="H900" t="n">
         <v>18041</v>
@@ -26498,7 +26498,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G901" t="n">
-        <v>2.2588746547699</v>
+        <v>2.25887441635132</v>
       </c>
       <c r="H901" t="n">
         <v>13774</v>
@@ -26527,7 +26527,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G902" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H902" t="n">
         <v>9996</v>
@@ -26556,7 +26556,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G903" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H903" t="n">
         <v>12989</v>
@@ -26614,7 +26614,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G905" t="n">
-        <v>2.23087191581726</v>
+        <v>2.23087167739868</v>
       </c>
       <c r="H905" t="n">
         <v>12451</v>
@@ -26643,7 +26643,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G906" t="n">
-        <v>2.23087191581726</v>
+        <v>2.23087167739868</v>
       </c>
       <c r="H906" t="n">
         <v>1897</v>
@@ -26672,7 +26672,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G907" t="n">
-        <v>2.2588746547699</v>
+        <v>2.25887441635132</v>
       </c>
       <c r="H907" t="n">
         <v>2583</v>
@@ -26701,7 +26701,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G908" t="n">
-        <v>2.23087191581726</v>
+        <v>2.23087167739868</v>
       </c>
       <c r="H908" t="n">
         <v>1500</v>
@@ -26730,7 +26730,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G909" t="n">
-        <v>2.27754282951355</v>
+        <v>2.27754259109497</v>
       </c>
       <c r="H909" t="n">
         <v>4836</v>
@@ -26759,7 +26759,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G910" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H910" t="n">
         <v>2850</v>
@@ -26962,7 +26962,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G917" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H917" t="n">
         <v>3029</v>
@@ -27020,7 +27020,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G919" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H919" t="n">
         <v>3027</v>
@@ -27078,7 +27078,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G921" t="n">
-        <v>2.40822148323059</v>
+        <v>2.40822124481201</v>
       </c>
       <c r="H921" t="n">
         <v>2800</v>
@@ -27107,7 +27107,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G922" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H922" t="n">
         <v>2840</v>
@@ -27136,7 +27136,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G923" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H923" t="n">
         <v>2275</v>
@@ -27165,7 +27165,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G924" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H924" t="n">
         <v>2811</v>
@@ -27194,7 +27194,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G925" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H925" t="n">
         <v>10000</v>
@@ -27252,7 +27252,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G927" t="n">
-        <v>2.36155033111572</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H927" t="n">
         <v>13666</v>
@@ -27339,7 +27339,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G930" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H930" t="n">
         <v>2560</v>
@@ -27455,7 +27455,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G934" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H934" t="n">
         <v>18035</v>
@@ -27513,7 +27513,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G936" t="n">
-        <v>2.20286893844604</v>
+        <v>2.20286917686462</v>
       </c>
       <c r="H936" t="n">
         <v>6398</v>
@@ -27542,7 +27542,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G937" t="n">
-        <v>2.24020576477051</v>
+        <v>2.24020600318909</v>
       </c>
       <c r="H937" t="n">
         <v>5629</v>
@@ -27571,7 +27571,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G938" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H938" t="n">
         <v>36604</v>
@@ -27600,7 +27600,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G939" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H939" t="n">
         <v>14446</v>
@@ -27687,7 +27687,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G942" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H942" t="n">
         <v>24000</v>
@@ -27716,7 +27716,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G943" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H943" t="n">
         <v>10884</v>
@@ -27861,7 +27861,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G948" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H948" t="n">
         <v>2000</v>
@@ -27919,7 +27919,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G950" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H950" t="n">
         <v>2715</v>
@@ -27948,7 +27948,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G951" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H951" t="n">
         <v>3000</v>
@@ -28064,7 +28064,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G955" t="n">
-        <v>2.36155033111572</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H955" t="n">
         <v>1000</v>
@@ -28093,7 +28093,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G956" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H956" t="n">
         <v>4601</v>
@@ -28122,7 +28122,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G957" t="n">
-        <v>2.36155033111572</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H957" t="n">
         <v>2000</v>
@@ -28209,7 +28209,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G960" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H960" t="n">
         <v>8263</v>
@@ -28267,7 +28267,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G962" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H962" t="n">
         <v>1000</v>
@@ -28354,7 +28354,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G965" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H965" t="n">
         <v>21</v>
@@ -28383,7 +28383,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G966" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H966" t="n">
         <v>6028</v>
@@ -28644,7 +28644,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G975" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H975" t="n">
         <v>5517</v>
@@ -28702,7 +28702,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G977" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H977" t="n">
         <v>2500</v>
@@ -28731,7 +28731,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G978" t="n">
-        <v>2.40822148323059</v>
+        <v>2.40822124481201</v>
       </c>
       <c r="H978" t="n">
         <v>4636</v>
@@ -28818,7 +28818,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G981" t="n">
-        <v>2.36155033111572</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H981" t="n">
         <v>3499</v>
@@ -28905,7 +28905,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G984" t="n">
-        <v>2.36155033111572</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H984" t="n">
         <v>1677</v>
@@ -29427,7 +29427,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1002" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H1002" t="n">
         <v>3900</v>
@@ -29514,7 +29514,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1005" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H1005" t="n">
         <v>642</v>
@@ -29543,7 +29543,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.40822148323059</v>
+        <v>2.40822124481201</v>
       </c>
       <c r="H1006" t="n">
         <v>2020</v>
@@ -29630,7 +29630,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1009" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H1009" t="n">
         <v>1826</v>
@@ -29688,7 +29688,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1011" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H1011" t="n">
         <v>3388</v>
@@ -29978,7 +29978,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1021" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H1021" t="n">
         <v>942</v>
@@ -30065,7 +30065,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1024" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H1024" t="n">
         <v>1010</v>
@@ -30239,7 +30239,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1030" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H1030" t="n">
         <v>1301</v>
@@ -30268,7 +30268,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1031" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H1031" t="n">
         <v>2233</v>
@@ -30297,7 +30297,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1032" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H1032" t="n">
         <v>200</v>
@@ -30326,7 +30326,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1033" t="n">
-        <v>2.31487941741943</v>
+        <v>2.31487965583801</v>
       </c>
       <c r="H1033" t="n">
         <v>939</v>
@@ -30413,7 +30413,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1036" t="n">
-        <v>2.40822148323059</v>
+        <v>2.40822124481201</v>
       </c>
       <c r="H1036" t="n">
         <v>1101</v>
@@ -30558,7 +30558,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1041" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H1041" t="n">
         <v>15334</v>
@@ -30587,7 +30587,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1042" t="n">
-        <v>2.29621124267578</v>
+        <v>2.2962110042572</v>
       </c>
       <c r="H1042" t="n">
         <v>548</v>
@@ -30616,7 +30616,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1043" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H1043" t="n">
         <v>7200</v>
@@ -30645,7 +30645,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1044" t="n">
-        <v>2.32421374320984</v>
+        <v>2.32421350479126</v>
       </c>
       <c r="H1044" t="n">
         <v>0</v>
@@ -30877,7 +30877,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1052" t="n">
-        <v>2.36155033111572</v>
+        <v>2.3615505695343</v>
       </c>
       <c r="H1052" t="n">
         <v>6417</v>
@@ -31138,7 +31138,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1061" t="n">
-        <v>2.37088441848755</v>
+        <v>2.37088465690613</v>
       </c>
       <c r="H1061" t="n">
         <v>6</v>
@@ -31196,7 +31196,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1063" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H1063" t="n">
         <v>2460</v>
@@ -31225,7 +31225,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1064" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H1064" t="n">
         <v>0</v>
@@ -31254,7 +31254,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1065" t="n">
-        <v>2.41755533218384</v>
+        <v>2.41755557060242</v>
       </c>
       <c r="H1065" t="n">
         <v>7276</v>
@@ -31283,7 +31283,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H1066" t="n">
         <v>5691</v>
@@ -31312,7 +31312,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.42688965797424</v>
+        <v>2.42688941955566</v>
       </c>
       <c r="H1067" t="n">
         <v>400</v>
@@ -31457,7 +31457,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1072" t="n">
-        <v>2.65091013908386</v>
+        <v>2.65091037750244</v>
       </c>
       <c r="H1072" t="n">
         <v>188026</v>
@@ -32095,7 +32095,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.62290787696838</v>
+        <v>2.6229076385498</v>
       </c>
       <c r="H1094" t="n">
         <v>16861</v>
@@ -32124,7 +32124,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1095" t="n">
         <v>2654</v>
@@ -32443,7 +32443,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1106" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1106" t="n">
         <v>200</v>
@@ -32501,7 +32501,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1108" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1108" t="n">
         <v>1000</v>
@@ -32530,7 +32530,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1109" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1109" t="n">
         <v>1587</v>
@@ -32559,7 +32559,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1110" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1110" t="n">
         <v>2194</v>
@@ -32617,7 +32617,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1112" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1112" t="n">
         <v>3440</v>
@@ -32646,7 +32646,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1113" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1113" t="n">
         <v>0</v>
@@ -32675,7 +32675,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1114" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1114" t="n">
         <v>3456</v>
@@ -32704,7 +32704,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1115" t="n">
-        <v>2.57623696327209</v>
+        <v>2.57623672485352</v>
       </c>
       <c r="H1115" t="n">
         <v>0</v>
@@ -32849,7 +32849,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1120" t="n">
-        <v>2.63224196434021</v>
+        <v>2.63224172592163</v>
       </c>
       <c r="H1120" t="n">
         <v>3502</v>
@@ -33023,7 +33023,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1126" t="n">
-        <v>2.753586769104</v>
+        <v>2.75358653068542</v>
       </c>
       <c r="H1126" t="n">
         <v>11211</v>
@@ -33516,7 +33516,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1143" t="n">
-        <v>2.85626244544983</v>
+        <v>2.85626268386841</v>
       </c>
       <c r="H1143" t="n">
         <v>15530</v>
@@ -33661,7 +33661,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1148" t="n">
-        <v>2.91226744651794</v>
+        <v>2.91226768493652</v>
       </c>
       <c r="H1148" t="n">
         <v>1813</v>
@@ -33690,7 +33690,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1149" t="n">
-        <v>2.92160224914551</v>
+        <v>2.92160201072693</v>
       </c>
       <c r="H1149" t="n">
         <v>3909</v>
@@ -33835,7 +33835,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1154" t="n">
-        <v>2.85626244544983</v>
+        <v>2.85626268386841</v>
       </c>
       <c r="H1154" t="n">
         <v>3063</v>
@@ -33951,7 +33951,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1158" t="n">
-        <v>2.91226744651794</v>
+        <v>2.91226768493652</v>
       </c>
       <c r="H1158" t="n">
         <v>950</v>
@@ -34038,7 +34038,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1161" t="n">
-        <v>2.88426494598389</v>
+        <v>2.88426518440247</v>
       </c>
       <c r="H1161" t="n">
         <v>2639</v>
@@ -34096,7 +34096,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1163" t="n">
-        <v>2.9682731628418</v>
+        <v>2.96827292442322</v>
       </c>
       <c r="H1163" t="n">
         <v>21970</v>
@@ -34212,7 +34212,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.20162796974182</v>
+        <v>3.20162773132324</v>
       </c>
       <c r="H1167" t="n">
         <v>24299</v>
@@ -34241,7 +34241,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.18295907974243</v>
+        <v>3.18295931816101</v>
       </c>
       <c r="H1168" t="n">
         <v>4144</v>
@@ -34270,7 +34270,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.18295907974243</v>
+        <v>3.18295931816101</v>
       </c>
       <c r="H1169" t="n">
         <v>7563</v>
@@ -34299,7 +34299,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.22962999343872</v>
+        <v>3.2296302318573</v>
       </c>
       <c r="H1170" t="n">
         <v>8410</v>
@@ -34328,7 +34328,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.28563547134399</v>
+        <v>3.28563523292542</v>
       </c>
       <c r="H1171" t="n">
         <v>9302</v>
@@ -34444,7 +34444,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.44431662559509</v>
+        <v>3.44431686401367</v>
       </c>
       <c r="H1175" t="n">
         <v>13251</v>
@@ -34589,7 +34589,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1180" t="n">
-        <v>4.0043683052063</v>
+        <v>4.00436782836914</v>
       </c>
       <c r="H1180" t="n">
         <v>86548</v>
@@ -34618,7 +34618,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1181" t="n">
-        <v>4.26572561264038</v>
+        <v>4.26572513580322</v>
       </c>
       <c r="H1181" t="n">
         <v>61743</v>
@@ -34647,7 +34647,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1182" t="n">
-        <v>4.46174383163452</v>
+        <v>4.46174335479736</v>
       </c>
       <c r="H1182" t="n">
         <v>47140</v>
@@ -34763,7 +34763,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1186" t="n">
-        <v>4.85377931594849</v>
+        <v>4.85377883911133</v>
       </c>
       <c r="H1186" t="n">
         <v>39631</v>
@@ -34850,7 +34850,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1189" t="n">
-        <v>4.51774930953979</v>
+        <v>4.51774883270264</v>
       </c>
       <c r="H1189" t="n">
         <v>67215</v>
@@ -34908,7 +34908,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1191" t="n">
-        <v>4.50841426849365</v>
+        <v>4.50841474533081</v>
       </c>
       <c r="H1191" t="n">
         <v>16999</v>
@@ -34966,7 +34966,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1193" t="n">
-        <v>4.46174383163452</v>
+        <v>4.46174335479736</v>
       </c>
       <c r="H1193" t="n">
         <v>24861</v>
@@ -35024,7 +35024,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1195" t="n">
-        <v>4.46174383163452</v>
+        <v>4.46174335479736</v>
       </c>
       <c r="H1195" t="n">
         <v>12604</v>
@@ -35082,7 +35082,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1197" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1197" t="n">
         <v>37624</v>
@@ -35111,7 +35111,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1198" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1198" t="n">
         <v>17896</v>
@@ -35169,7 +35169,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1200" t="n">
-        <v>4.51774930953979</v>
+        <v>4.51774883270264</v>
       </c>
       <c r="H1200" t="n">
         <v>23594</v>
@@ -35198,7 +35198,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1201" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1201" t="n">
         <v>16723</v>
@@ -35401,7 +35401,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1208" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1208" t="n">
         <v>10200</v>
@@ -35488,7 +35488,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1211" t="n">
-        <v>4.46174383163452</v>
+        <v>4.46174335479736</v>
       </c>
       <c r="H1211" t="n">
         <v>10557</v>
@@ -35517,7 +35517,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1212" t="n">
-        <v>4.50841426849365</v>
+        <v>4.50841474533081</v>
       </c>
       <c r="H1212" t="n">
         <v>8520</v>
@@ -35575,7 +35575,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1214" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1214" t="n">
         <v>5950</v>
@@ -35604,7 +35604,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1215" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1215" t="n">
         <v>6941</v>
@@ -35720,7 +35720,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1219" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1219" t="n">
         <v>2891</v>
@@ -35749,7 +35749,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1220" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1220" t="n">
         <v>5384</v>
@@ -35778,7 +35778,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1221" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1221" t="n">
         <v>3060</v>
@@ -36474,7 +36474,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.40573787689209</v>
+        <v>4.40573835372925</v>
       </c>
       <c r="H1245" t="n">
         <v>1123</v>
@@ -36619,7 +36619,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1250" t="n">
-        <v>4.40573787689209</v>
+        <v>4.40573835372925</v>
       </c>
       <c r="H1250" t="n">
         <v>2487</v>
@@ -36648,7 +36648,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1251" t="n">
-        <v>4.48041152954102</v>
+        <v>4.48041200637817</v>
       </c>
       <c r="H1251" t="n">
         <v>39291</v>
@@ -36677,7 +36677,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1252" t="n">
-        <v>4.53641700744629</v>
+        <v>4.53641748428345</v>
       </c>
       <c r="H1252" t="n">
         <v>10852</v>
@@ -37315,7 +37315,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1274" t="n">
-        <v>4.99078130722046</v>
+        <v>4.9907808303833</v>
       </c>
       <c r="H1274" t="n">
         <v>24772</v>
@@ -37344,7 +37344,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1275" t="n">
-        <v>5.02917146682739</v>
+        <v>5.02917194366455</v>
       </c>
       <c r="H1275" t="n">
         <v>31385</v>
@@ -37431,7 +37431,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1278" t="n">
-        <v>5.48985958099365</v>
+        <v>5.48985910415649</v>
       </c>
       <c r="H1278" t="n">
         <v>70084</v>
@@ -37576,7 +37576,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1283" t="n">
-        <v>5.83537483215332</v>
+        <v>5.83537530899048</v>
       </c>
       <c r="H1283" t="n">
         <v>8786</v>
@@ -37634,7 +37634,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1285" t="n">
-        <v>6.39203929901123</v>
+        <v>6.39203882217407</v>
       </c>
       <c r="H1285" t="n">
         <v>35361</v>
@@ -37750,7 +37750,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1289" t="n">
-        <v>6.46882009506226</v>
+        <v>6.46882057189941</v>
       </c>
       <c r="H1289" t="n">
         <v>13104</v>
@@ -37866,7 +37866,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G1293" t="n">
-        <v>6.1808910369873</v>
+        <v>6.18089056015015</v>
       </c>
       <c r="H1293" t="n">
         <v>21462</v>
@@ -37895,7 +37895,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1294" t="n">
-        <v>6.12330532073975</v>
+        <v>6.12330484390259</v>
       </c>
       <c r="H1294" t="n">
         <v>21748</v>
@@ -37953,7 +37953,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1296" t="n">
-        <v>6.39203929901123</v>
+        <v>6.39203882217407</v>
       </c>
       <c r="H1296" t="n">
         <v>15861</v>
@@ -37982,7 +37982,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1297" t="n">
-        <v>6.48801612854004</v>
+        <v>6.48801565170288</v>
       </c>
       <c r="H1297" t="n">
         <v>2374</v>
@@ -38011,7 +38011,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1298" t="n">
-        <v>6.48801612854004</v>
+        <v>6.48801565170288</v>
       </c>
       <c r="H1298" t="n">
         <v>9827</v>
@@ -38156,7 +38156,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1303" t="n">
-        <v>6.48801612854004</v>
+        <v>6.48801565170288</v>
       </c>
       <c r="H1303" t="n">
         <v>11171</v>
@@ -38388,7 +38388,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1311" t="n">
-        <v>5.93135118484497</v>
+        <v>5.93135166168213</v>
       </c>
       <c r="H1311" t="n">
         <v>18885</v>
@@ -38446,7 +38446,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1313" t="n">
-        <v>5.93135118484497</v>
+        <v>5.93135166168213</v>
       </c>
       <c r="H1313" t="n">
         <v>34147</v>
@@ -38533,7 +38533,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1316" t="n">
-        <v>5.93135118484497</v>
+        <v>5.93135166168213</v>
       </c>
       <c r="H1316" t="n">
         <v>10376</v>
@@ -38939,7 +38939,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1330" t="n">
-        <v>5.68181276321411</v>
+        <v>5.68181228637695</v>
       </c>
       <c r="H1330" t="n">
         <v>4010</v>
@@ -39026,7 +39026,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1333" t="n">
-        <v>5.66261720657349</v>
+        <v>5.66261768341064</v>
       </c>
       <c r="H1333" t="n">
         <v>3167</v>
@@ -39055,7 +39055,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.56664085388184</v>
+        <v>5.56664133071899</v>
       </c>
       <c r="H1334" t="n">
         <v>13673</v>
@@ -39084,7 +39084,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1335" t="n">
-        <v>5.48985958099365</v>
+        <v>5.48985910415649</v>
       </c>
       <c r="H1335" t="n">
         <v>2565</v>
@@ -39142,7 +39142,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1337" t="n">
-        <v>5.56664085388184</v>
+        <v>5.56664133071899</v>
       </c>
       <c r="H1337" t="n">
         <v>2917</v>
@@ -39171,7 +39171,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1338" t="n">
-        <v>5.56664085388184</v>
+        <v>5.56664133071899</v>
       </c>
       <c r="H1338" t="n">
         <v>1312</v>
@@ -39258,7 +39258,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1341" t="n">
-        <v>5.66261720657349</v>
+        <v>5.66261768341064</v>
       </c>
       <c r="H1341" t="n">
         <v>1605</v>
@@ -39287,7 +39287,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1342" t="n">
-        <v>5.66261720657349</v>
+        <v>5.66261768341064</v>
       </c>
       <c r="H1342" t="n">
         <v>3220</v>
@@ -39403,7 +39403,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1346" t="n">
-        <v>5.56664085388184</v>
+        <v>5.56664133071899</v>
       </c>
       <c r="H1346" t="n">
         <v>2814</v>
@@ -39519,7 +39519,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1350" t="n">
-        <v>5.93135118484497</v>
+        <v>5.93135166168213</v>
       </c>
       <c r="H1350" t="n">
         <v>11182</v>
@@ -39548,7 +39548,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1351" t="n">
-        <v>5.93135118484497</v>
+        <v>5.93135166168213</v>
       </c>
       <c r="H1351" t="n">
         <v>17082</v>
@@ -39577,7 +39577,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1352" t="n">
-        <v>5.93135118484497</v>
+        <v>5.93135166168213</v>
       </c>
       <c r="H1352" t="n">
         <v>5027</v>
@@ -39606,7 +39606,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1353" t="n">
-        <v>6.12330532073975</v>
+        <v>6.12330484390259</v>
       </c>
       <c r="H1353" t="n">
         <v>15567</v>
@@ -39693,7 +39693,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1356" t="n">
-        <v>5.87376546859741</v>
+        <v>5.87376594543457</v>
       </c>
       <c r="H1356" t="n">
         <v>18468</v>
@@ -39896,7 +39896,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1363" t="n">
-        <v>5.96974182128906</v>
+        <v>5.96974229812622</v>
       </c>
       <c r="H1363" t="n">
         <v>14927</v>
@@ -40012,7 +40012,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1367" t="n">
-        <v>5.96974182128906</v>
+        <v>5.96974229812622</v>
       </c>
       <c r="H1367" t="n">
         <v>5383</v>
@@ -40041,7 +40041,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1368" t="n">
-        <v>5.83537483215332</v>
+        <v>5.83537530899048</v>
       </c>
       <c r="H1368" t="n">
         <v>3207</v>
@@ -40099,7 +40099,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1370" t="n">
-        <v>5.96974182128906</v>
+        <v>5.96974229812622</v>
       </c>
       <c r="H1370" t="n">
         <v>2420</v>
@@ -40128,7 +40128,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1371" t="n">
-        <v>5.87376546859741</v>
+        <v>5.87376594543457</v>
       </c>
       <c r="H1371" t="n">
         <v>5952</v>
@@ -40186,7 +40186,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1373" t="n">
-        <v>6.08491468429565</v>
+        <v>6.0849142074585</v>
       </c>
       <c r="H1373" t="n">
         <v>4048</v>
@@ -40244,7 +40244,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1375" t="n">
-        <v>5.87376546859741</v>
+        <v>5.87376594543457</v>
       </c>
       <c r="H1375" t="n">
         <v>6216</v>
@@ -40505,7 +40505,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1384" t="n">
-        <v>5.87376546859741</v>
+        <v>5.87376594543457</v>
       </c>
       <c r="H1384" t="n">
         <v>8532</v>
@@ -40534,7 +40534,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1385" t="n">
-        <v>5.96974182128906</v>
+        <v>5.96974229812622</v>
       </c>
       <c r="H1385" t="n">
         <v>4804</v>
@@ -40563,7 +40563,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1386" t="n">
-        <v>5.96974182128906</v>
+        <v>5.96974229812622</v>
       </c>
       <c r="H1386" t="n">
         <v>51315</v>
@@ -40592,7 +40592,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1387" t="n">
-        <v>5.96974182128906</v>
+        <v>5.96974229812622</v>
       </c>
       <c r="H1387" t="n">
         <v>3086</v>
@@ -40621,7 +40621,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1388" t="n">
-        <v>5.93135118484497</v>
+        <v>5.93135166168213</v>
       </c>
       <c r="H1388" t="n">
         <v>5083</v>
@@ -40679,7 +40679,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1390" t="n">
-        <v>5.93135118484497</v>
+        <v>5.93135166168213</v>
       </c>
       <c r="H1390" t="n">
         <v>3425</v>
@@ -40737,7 +40737,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1392" t="n">
-        <v>5.93135118484497</v>
+        <v>5.93135166168213</v>
       </c>
       <c r="H1392" t="n">
         <v>2371</v>
@@ -40766,7 +40766,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1393" t="n">
-        <v>5.87376546859741</v>
+        <v>5.87376594543457</v>
       </c>
       <c r="H1393" t="n">
         <v>4474</v>
@@ -41085,7 +41085,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1404" t="n">
-        <v>6.08491468429565</v>
+        <v>6.0849142074585</v>
       </c>
       <c r="H1404" t="n">
         <v>18941</v>
@@ -41143,7 +41143,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1406" t="n">
-        <v>6.12330532073975</v>
+        <v>6.12330484390259</v>
       </c>
       <c r="H1406" t="n">
         <v>40015</v>
@@ -41462,7 +41462,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1417" t="n">
-        <v>7.02548503875732</v>
+        <v>7.02548456192017</v>
       </c>
       <c r="H1417" t="n">
         <v>6334</v>
@@ -41839,7 +41839,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1430" t="n">
-        <v>7.02548503875732</v>
+        <v>7.02548456192017</v>
       </c>
       <c r="H1430" t="n">
         <v>15354</v>
@@ -41897,7 +41897,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1432" t="n">
-        <v>7.02548503875732</v>
+        <v>7.02548456192017</v>
       </c>
       <c r="H1432" t="n">
         <v>1260</v>
@@ -42129,7 +42129,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1440" t="n">
-        <v>7.06387519836426</v>
+        <v>7.06387567520142</v>
       </c>
       <c r="H1440" t="n">
         <v>1592</v>
@@ -42187,7 +42187,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G1442" t="n">
-        <v>7.12146139144897</v>
+        <v>7.12146091461182</v>
       </c>
       <c r="H1442" t="n">
         <v>9087</v>
@@ -42303,7 +42303,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1446" t="n">
-        <v>7.06387519836426</v>
+        <v>7.06387567520142</v>
       </c>
       <c r="H1446" t="n">
         <v>10440</v>
@@ -42361,7 +42361,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1448" t="n">
-        <v>7.06387519836426</v>
+        <v>7.06387567520142</v>
       </c>
       <c r="H1448" t="n">
         <v>6369</v>
@@ -42390,7 +42390,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1449" t="n">
-        <v>6.91031265258789</v>
+        <v>6.91031217575073</v>
       </c>
       <c r="H1449" t="n">
         <v>8416</v>
@@ -42419,7 +42419,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1450" t="n">
-        <v>7.02548503875732</v>
+        <v>7.02548456192017</v>
       </c>
       <c r="H1450" t="n">
         <v>5499</v>
@@ -42535,7 +42535,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1454" t="n">
-        <v>7.06387519836426</v>
+        <v>7.06387567520142</v>
       </c>
       <c r="H1454" t="n">
         <v>2894</v>
@@ -42680,7 +42680,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1459" t="n">
-        <v>6.91031265258789</v>
+        <v>6.91031217575073</v>
       </c>
       <c r="H1459" t="n">
         <v>3121</v>
@@ -42738,7 +42738,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1461" t="n">
-        <v>6.91031265258789</v>
+        <v>6.91031217575073</v>
       </c>
       <c r="H1461" t="n">
         <v>9076</v>
@@ -42767,7 +42767,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1462" t="n">
-        <v>7.06387519836426</v>
+        <v>7.06387567520142</v>
       </c>
       <c r="H1462" t="n">
         <v>300</v>
@@ -42883,7 +42883,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1466" t="n">
-        <v>7.02548503875732</v>
+        <v>7.02548456192017</v>
       </c>
       <c r="H1466" t="n">
         <v>501</v>
@@ -43173,7 +43173,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1476" t="n">
-        <v>6.91031265258789</v>
+        <v>6.91031217575073</v>
       </c>
       <c r="H1476" t="n">
         <v>7848</v>
@@ -43202,7 +43202,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1477" t="n">
-        <v>6.89111757278442</v>
+        <v>6.89111709594727</v>
       </c>
       <c r="H1477" t="n">
         <v>12560</v>
@@ -43260,7 +43260,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1479" t="n">
-        <v>6.91031265258789</v>
+        <v>6.91031217575073</v>
       </c>
       <c r="H1479" t="n">
         <v>16205</v>
@@ -43289,7 +43289,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1480" t="n">
-        <v>6.77594518661499</v>
+        <v>6.77594566345215</v>
       </c>
       <c r="H1480" t="n">
         <v>1973</v>
@@ -43318,7 +43318,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1481" t="n">
-        <v>6.98709440231323</v>
+        <v>6.98709392547607</v>
       </c>
       <c r="H1481" t="n">
         <v>4148</v>
@@ -43347,7 +43347,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1482" t="n">
-        <v>6.89111757278442</v>
+        <v>6.89111709594727</v>
       </c>
       <c r="H1482" t="n">
         <v>144</v>
@@ -43405,7 +43405,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G1484" t="n">
-        <v>6.79514026641846</v>
+        <v>6.79514074325562</v>
       </c>
       <c r="H1484" t="n">
         <v>10530</v>
@@ -43434,7 +43434,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1485" t="n">
-        <v>6.81433629989624</v>
+        <v>6.81433582305908</v>
       </c>
       <c r="H1485" t="n">
         <v>2742</v>
@@ -43463,7 +43463,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1486" t="n">
-        <v>6.91031265258789</v>
+        <v>6.91031217575073</v>
       </c>
       <c r="H1486" t="n">
         <v>1912</v>
@@ -43492,7 +43492,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1487" t="n">
-        <v>6.91031265258789</v>
+        <v>6.91031217575073</v>
       </c>
       <c r="H1487" t="n">
         <v>6267</v>
@@ -43521,7 +43521,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1488" t="n">
-        <v>6.98709440231323</v>
+        <v>6.98709392547607</v>
       </c>
       <c r="H1488" t="n">
         <v>8301</v>
@@ -43724,7 +43724,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1495" t="n">
-        <v>7.29421901702881</v>
+        <v>7.29421854019165</v>
       </c>
       <c r="H1495" t="n">
         <v>3213</v>
@@ -43753,7 +43753,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1496" t="n">
-        <v>7.42858552932739</v>
+        <v>7.42858600616455</v>
       </c>
       <c r="H1496" t="n">
         <v>9505</v>
@@ -43811,7 +43811,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1498" t="n">
-        <v>7.54375791549683</v>
+        <v>7.54375839233398</v>
       </c>
       <c r="H1498" t="n">
         <v>2199</v>
@@ -54692,6 +54692,35 @@
         <v>5613</v>
       </c>
       <c r="I1873" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1874">
+      <c r="A1874" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1874" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1874" t="n">
+        <v>13.9499998092651</v>
+      </c>
+      <c r="D1874" t="n">
+        <v>14.3500003814697</v>
+      </c>
+      <c r="E1874" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="F1874" t="n">
+        <v>14.1499996185303</v>
+      </c>
+      <c r="G1874" t="n">
+        <v>14.1499996185303</v>
+      </c>
+      <c r="H1874" t="n">
+        <v>16931</v>
+      </c>
+      <c r="I1874" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IEG.MI.xlsx
+++ b/data/IEG.MI.xlsx
@@ -485,7 +485,7 @@
         <v>3.73099994659424</v>
       </c>
       <c r="G4" t="n">
-        <v>3.48258686065674</v>
+        <v>3.48258662223816</v>
       </c>
       <c r="H4" t="n">
         <v>132269</v>
@@ -514,7 +514,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G5" t="n">
-        <v>3.52832436561584</v>
+        <v>3.52832412719727</v>
       </c>
       <c r="H5" t="n">
         <v>20727</v>
@@ -543,7 +543,7 @@
         <v>3.69749999046326</v>
       </c>
       <c r="G6" t="n">
-        <v>3.45131731033325</v>
+        <v>3.45131707191467</v>
       </c>
       <c r="H6" t="n">
         <v>5051</v>
@@ -572,7 +572,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G7" t="n">
-        <v>3.4536509513855</v>
+        <v>3.45365071296692</v>
       </c>
       <c r="H7" t="n">
         <v>13909</v>
@@ -601,7 +601,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>3.40698003768921</v>
+        <v>3.40697979927063</v>
       </c>
       <c r="H8" t="n">
         <v>31297</v>
@@ -630,7 +630,7 @@
         <v>3.67050004005432</v>
       </c>
       <c r="G9" t="n">
-        <v>3.42611479759216</v>
+        <v>3.42611503601074</v>
       </c>
       <c r="H9" t="n">
         <v>132</v>
@@ -659,7 +659,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G10" t="n">
-        <v>3.4536509513855</v>
+        <v>3.45365071296692</v>
       </c>
       <c r="H10" t="n">
         <v>5150</v>
@@ -688,7 +688,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G11" t="n">
-        <v>3.4536509513855</v>
+        <v>3.45365071296692</v>
       </c>
       <c r="H11" t="n">
         <v>2000</v>
@@ -717,7 +717,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G12" t="n">
-        <v>3.43498277664185</v>
+        <v>3.43498253822327</v>
       </c>
       <c r="H12" t="n">
         <v>3250</v>
@@ -746,7 +746,7 @@
         <v>3.64050006866455</v>
       </c>
       <c r="G13" t="n">
-        <v>3.39811253547668</v>
+        <v>3.39811229705811</v>
       </c>
       <c r="H13" t="n">
         <v>1311</v>
@@ -804,7 +804,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G15" t="n">
-        <v>3.42564845085144</v>
+        <v>3.42564821243286</v>
       </c>
       <c r="H15" t="n">
         <v>10175</v>
@@ -862,7 +862,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G17" t="n">
-        <v>3.47231912612915</v>
+        <v>3.47231936454773</v>
       </c>
       <c r="H17" t="n">
         <v>86899</v>
@@ -920,7 +920,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G19" t="n">
-        <v>3.69633960723877</v>
+        <v>3.69634008407593</v>
       </c>
       <c r="H19" t="n">
         <v>96525</v>
@@ -978,7 +978,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G21" t="n">
-        <v>3.80835032463074</v>
+        <v>3.80834984779358</v>
       </c>
       <c r="H21" t="n">
         <v>29979</v>
@@ -1065,7 +1065,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G24" t="n">
-        <v>3.85502099990845</v>
+        <v>3.85502123832703</v>
       </c>
       <c r="H24" t="n">
         <v>69970</v>
@@ -1094,7 +1094,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G25" t="n">
-        <v>3.81768441200256</v>
+        <v>3.81768465042114</v>
       </c>
       <c r="H25" t="n">
         <v>4963</v>
@@ -1181,7 +1181,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G28" t="n">
-        <v>3.95769739151001</v>
+        <v>3.95769667625427</v>
       </c>
       <c r="H28" t="n">
         <v>6052</v>
@@ -1210,7 +1210,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G29" t="n">
-        <v>3.97636556625366</v>
+        <v>3.97636604309082</v>
       </c>
       <c r="H29" t="n">
         <v>2457</v>
@@ -1239,7 +1239,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G30" t="n">
-        <v>4.05103969573975</v>
+        <v>4.05103874206543</v>
       </c>
       <c r="H30" t="n">
         <v>10363</v>
@@ -1268,7 +1268,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G31" t="n">
-        <v>4.03237104415894</v>
+        <v>4.03237056732178</v>
       </c>
       <c r="H31" t="n">
         <v>17060</v>
@@ -1297,7 +1297,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G32" t="n">
-        <v>3.9390287399292</v>
+        <v>3.93902826309204</v>
       </c>
       <c r="H32" t="n">
         <v>6284</v>
@@ -1326,7 +1326,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>4.01370286941528</v>
+        <v>4.01370239257812</v>
       </c>
       <c r="H33" t="n">
         <v>4871</v>
@@ -1355,7 +1355,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G34" t="n">
-        <v>4.01370286941528</v>
+        <v>4.01370239257812</v>
       </c>
       <c r="H34" t="n">
         <v>114</v>
@@ -1384,7 +1384,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G35" t="n">
-        <v>3.99503397941589</v>
+        <v>3.99503421783447</v>
       </c>
       <c r="H35" t="n">
         <v>922</v>
@@ -1413,7 +1413,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G36" t="n">
-        <v>3.99503397941589</v>
+        <v>3.99503421783447</v>
       </c>
       <c r="H36" t="n">
         <v>300</v>
@@ -1442,7 +1442,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G37" t="n">
-        <v>3.99503397941589</v>
+        <v>3.99503421783447</v>
       </c>
       <c r="H37" t="n">
         <v>4226</v>
@@ -1471,7 +1471,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G38" t="n">
-        <v>3.95769739151001</v>
+        <v>3.95769667625427</v>
       </c>
       <c r="H38" t="n">
         <v>4960</v>
@@ -1500,7 +1500,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G39" t="n">
-        <v>3.8830235004425</v>
+        <v>3.88302326202393</v>
       </c>
       <c r="H39" t="n">
         <v>592</v>
@@ -1529,7 +1529,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G40" t="n">
-        <v>3.8830235004425</v>
+        <v>3.88302326202393</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1558,7 +1558,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G41" t="n">
-        <v>3.95769739151001</v>
+        <v>3.95769667625427</v>
       </c>
       <c r="H41" t="n">
         <v>225</v>
@@ -1587,7 +1587,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G42" t="n">
-        <v>3.95769739151001</v>
+        <v>3.95769667625427</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>3.92036008834839</v>
+        <v>3.92036032676697</v>
       </c>
       <c r="H43" t="n">
         <v>148291</v>
@@ -1645,7 +1645,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G44" t="n">
-        <v>3.92036008834839</v>
+        <v>3.92036032676697</v>
       </c>
       <c r="H44" t="n">
         <v>59672</v>
@@ -1703,7 +1703,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G46" t="n">
-        <v>3.92036008834839</v>
+        <v>3.92036032676697</v>
       </c>
       <c r="H46" t="n">
         <v>4540</v>
@@ -1732,7 +1732,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G47" t="n">
-        <v>3.85502099990845</v>
+        <v>3.85502123832703</v>
       </c>
       <c r="H47" t="n">
         <v>125</v>
@@ -1819,7 +1819,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G50" t="n">
-        <v>3.92036008834839</v>
+        <v>3.92036032676697</v>
       </c>
       <c r="H50" t="n">
         <v>3900</v>
@@ -1848,7 +1848,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G51" t="n">
-        <v>3.64033460617065</v>
+        <v>3.64033484458923</v>
       </c>
       <c r="H51" t="n">
         <v>168018</v>
@@ -1877,7 +1877,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G52" t="n">
-        <v>3.59366345405579</v>
+        <v>3.59366369247437</v>
       </c>
       <c r="H52" t="n">
         <v>66112</v>
@@ -1906,7 +1906,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G53" t="n">
-        <v>3.63100075721741</v>
+        <v>3.63100051879883</v>
       </c>
       <c r="H53" t="n">
         <v>23073</v>
@@ -1935,7 +1935,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G54" t="n">
-        <v>3.53765869140625</v>
+        <v>3.53765845298767</v>
       </c>
       <c r="H54" t="n">
         <v>154944</v>
@@ -1964,7 +1964,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G55" t="n">
-        <v>3.42564845085144</v>
+        <v>3.42564821243286</v>
       </c>
       <c r="H55" t="n">
         <v>62162</v>
@@ -1993,7 +1993,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G56" t="n">
-        <v>3.40698003768921</v>
+        <v>3.40697979927063</v>
       </c>
       <c r="H56" t="n">
         <v>6594</v>
@@ -2022,7 +2022,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G57" t="n">
-        <v>3.4536509513855</v>
+        <v>3.45365071296692</v>
       </c>
       <c r="H57" t="n">
         <v>73464</v>
@@ -2051,7 +2051,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G58" t="n">
-        <v>3.4536509513855</v>
+        <v>3.45365071296692</v>
       </c>
       <c r="H58" t="n">
         <v>35821</v>
@@ -2109,7 +2109,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G60" t="n">
-        <v>3.47231912612915</v>
+        <v>3.47231936454773</v>
       </c>
       <c r="H60" t="n">
         <v>10849</v>
@@ -2167,7 +2167,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>3.59366345405579</v>
+        <v>3.59366369247437</v>
       </c>
       <c r="H62" t="n">
         <v>6367</v>
@@ -2225,7 +2225,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G64" t="n">
-        <v>3.56566095352173</v>
+        <v>3.56566119194031</v>
       </c>
       <c r="H64" t="n">
         <v>333</v>
@@ -2254,7 +2254,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G65" t="n">
-        <v>3.58432960510254</v>
+        <v>3.58432936668396</v>
       </c>
       <c r="H65" t="n">
         <v>6062</v>
@@ -2283,7 +2283,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G66" t="n">
-        <v>3.59366345405579</v>
+        <v>3.59366369247437</v>
       </c>
       <c r="H66" t="n">
         <v>2000</v>
@@ -2341,7 +2341,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G68" t="n">
-        <v>3.69633960723877</v>
+        <v>3.69634008407593</v>
       </c>
       <c r="H68" t="n">
         <v>6933</v>
@@ -2428,7 +2428,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G71" t="n">
-        <v>3.59366345405579</v>
+        <v>3.59366369247437</v>
       </c>
       <c r="H71" t="n">
         <v>700</v>
@@ -2457,7 +2457,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G72" t="n">
-        <v>3.53765869140625</v>
+        <v>3.53765845298767</v>
       </c>
       <c r="H72" t="n">
         <v>3200</v>
@@ -2486,7 +2486,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G73" t="n">
-        <v>3.53765869140625</v>
+        <v>3.53765845298767</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G74" t="n">
-        <v>3.53765869140625</v>
+        <v>3.53765845298767</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>3.5469925403595</v>
+        <v>3.54699277877808</v>
       </c>
       <c r="H75" t="n">
         <v>550</v>
@@ -2573,7 +2573,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G76" t="n">
-        <v>3.5469925403595</v>
+        <v>3.54699277877808</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>3.5469925403595</v>
+        <v>3.54699277877808</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -2660,7 +2660,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G79" t="n">
-        <v>3.56566095352173</v>
+        <v>3.56566119194031</v>
       </c>
       <c r="H79" t="n">
         <v>505</v>
@@ -2689,7 +2689,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G80" t="n">
-        <v>3.59366345405579</v>
+        <v>3.59366369247437</v>
       </c>
       <c r="H80" t="n">
         <v>320</v>
@@ -2718,7 +2718,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G81" t="n">
-        <v>3.59366345405579</v>
+        <v>3.59366369247437</v>
       </c>
       <c r="H81" t="n">
         <v>11</v>
@@ -2747,7 +2747,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G82" t="n">
-        <v>3.59366345405579</v>
+        <v>3.59366369247437</v>
       </c>
       <c r="H82" t="n">
         <v>659</v>
@@ -2776,7 +2776,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G83" t="n">
-        <v>3.6123321056366</v>
+        <v>3.61233186721802</v>
       </c>
       <c r="H83" t="n">
         <v>505</v>
@@ -2805,7 +2805,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G84" t="n">
-        <v>3.6123321056366</v>
+        <v>3.61233186721802</v>
       </c>
       <c r="H84" t="n">
         <v>10</v>
@@ -2834,7 +2834,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G85" t="n">
-        <v>3.56566095352173</v>
+        <v>3.56566119194031</v>
       </c>
       <c r="H85" t="n">
         <v>7252</v>
@@ -2863,7 +2863,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>3.57499527931213</v>
+        <v>3.57499504089355</v>
       </c>
       <c r="H86" t="n">
         <v>6205</v>
@@ -2892,7 +2892,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G87" t="n">
-        <v>3.63100075721741</v>
+        <v>3.63100051879883</v>
       </c>
       <c r="H87" t="n">
         <v>3367</v>
@@ -2950,7 +2950,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>3.59366345405579</v>
+        <v>3.59366369247437</v>
       </c>
       <c r="H89" t="n">
         <v>19</v>
@@ -3008,7 +3008,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G91" t="n">
-        <v>3.6123321056366</v>
+        <v>3.61233186721802</v>
       </c>
       <c r="H91" t="n">
         <v>5</v>
@@ -3037,7 +3037,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G92" t="n">
-        <v>3.5469925403595</v>
+        <v>3.54699277877808</v>
       </c>
       <c r="H92" t="n">
         <v>495</v>
@@ -3066,7 +3066,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G93" t="n">
-        <v>3.58432960510254</v>
+        <v>3.58432936668396</v>
       </c>
       <c r="H93" t="n">
         <v>410</v>
@@ -3269,7 +3269,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G100" t="n">
-        <v>3.69633960723877</v>
+        <v>3.69634008407593</v>
       </c>
       <c r="H100" t="n">
         <v>5164</v>
@@ -3298,7 +3298,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G101" t="n">
-        <v>3.69633960723877</v>
+        <v>3.69634008407593</v>
       </c>
       <c r="H101" t="n">
         <v>1750</v>
@@ -3327,7 +3327,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G102" t="n">
-        <v>3.64033460617065</v>
+        <v>3.64033484458923</v>
       </c>
       <c r="H102" t="n">
         <v>9855</v>
@@ -3356,7 +3356,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G103" t="n">
-        <v>3.64033460617065</v>
+        <v>3.64033484458923</v>
       </c>
       <c r="H103" t="n">
         <v>40000</v>
@@ -3385,7 +3385,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>3.64033460617065</v>
+        <v>3.64033484458923</v>
       </c>
       <c r="H104" t="n">
         <v>505</v>
@@ -3414,7 +3414,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G105" t="n">
-        <v>3.64966869354248</v>
+        <v>3.64966893196106</v>
       </c>
       <c r="H105" t="n">
         <v>1680</v>
@@ -3501,7 +3501,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G108" t="n">
-        <v>3.81768441200256</v>
+        <v>3.81768465042114</v>
       </c>
       <c r="H108" t="n">
         <v>7940</v>
@@ -3559,7 +3559,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G110" t="n">
-        <v>3.81768441200256</v>
+        <v>3.81768465042114</v>
       </c>
       <c r="H110" t="n">
         <v>41689</v>
@@ -3588,7 +3588,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>3.80835032463074</v>
+        <v>3.80834984779358</v>
       </c>
       <c r="H111" t="n">
         <v>19699</v>
@@ -3617,7 +3617,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G112" t="n">
-        <v>3.80835032463074</v>
+        <v>3.80834984779358</v>
       </c>
       <c r="H112" t="n">
         <v>17603</v>
@@ -3733,7 +3733,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G116" t="n">
-        <v>3.76167941093445</v>
+        <v>3.76167917251587</v>
       </c>
       <c r="H116" t="n">
         <v>40346</v>
@@ -3907,7 +3907,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G122" t="n">
-        <v>3.86435484886169</v>
+        <v>3.86435532569885</v>
       </c>
       <c r="H122" t="n">
         <v>44816</v>
@@ -3936,7 +3936,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G123" t="n">
-        <v>3.85502099990845</v>
+        <v>3.85502123832703</v>
       </c>
       <c r="H123" t="n">
         <v>5193</v>
@@ -3965,7 +3965,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G124" t="n">
-        <v>3.86435484886169</v>
+        <v>3.86435532569885</v>
       </c>
       <c r="H124" t="n">
         <v>15805</v>
@@ -4023,7 +4023,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G126" t="n">
-        <v>3.80835032463074</v>
+        <v>3.80834984779358</v>
       </c>
       <c r="H126" t="n">
         <v>1562</v>
@@ -4226,7 +4226,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G133" t="n">
-        <v>3.87368965148926</v>
+        <v>3.87368941307068</v>
       </c>
       <c r="H133" t="n">
         <v>7109</v>
@@ -4284,7 +4284,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G135" t="n">
-        <v>3.92036008834839</v>
+        <v>3.92036032676697</v>
       </c>
       <c r="H135" t="n">
         <v>8125</v>
@@ -4313,7 +4313,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G136" t="n">
-        <v>3.92036008834839</v>
+        <v>3.92036032676697</v>
       </c>
       <c r="H136" t="n">
         <v>6440</v>
@@ -4342,7 +4342,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G137" t="n">
-        <v>3.92969489097595</v>
+        <v>3.92969465255737</v>
       </c>
       <c r="H137" t="n">
         <v>5529</v>
@@ -4371,7 +4371,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G138" t="n">
-        <v>3.92036008834839</v>
+        <v>3.92036032676697</v>
       </c>
       <c r="H138" t="n">
         <v>255</v>
@@ -4400,7 +4400,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G139" t="n">
-        <v>3.87368965148926</v>
+        <v>3.87368941307068</v>
       </c>
       <c r="H139" t="n">
         <v>2403</v>
@@ -4429,7 +4429,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G140" t="n">
-        <v>3.9390287399292</v>
+        <v>3.93902826309204</v>
       </c>
       <c r="H140" t="n">
         <v>3505</v>
@@ -4545,7 +4545,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G144" t="n">
-        <v>3.9390287399292</v>
+        <v>3.93902826309204</v>
       </c>
       <c r="H144" t="n">
         <v>3005</v>
@@ -4574,7 +4574,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G145" t="n">
-        <v>3.89235758781433</v>
+        <v>3.89235782623291</v>
       </c>
       <c r="H145" t="n">
         <v>14</v>
@@ -4603,7 +4603,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G146" t="n">
-        <v>3.87368965148926</v>
+        <v>3.87368941307068</v>
       </c>
       <c r="H146" t="n">
         <v>495</v>
@@ -4661,7 +4661,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G148" t="n">
-        <v>3.95769739151001</v>
+        <v>3.95769667625427</v>
       </c>
       <c r="H148" t="n">
         <v>228432</v>
@@ -4690,7 +4690,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G149" t="n">
-        <v>4.04170513153076</v>
+        <v>4.0417046546936</v>
       </c>
       <c r="H149" t="n">
         <v>42576</v>
@@ -4719,7 +4719,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G150" t="n">
-        <v>4.22838926315308</v>
+        <v>4.22838878631592</v>
       </c>
       <c r="H150" t="n">
         <v>26577</v>
@@ -4748,7 +4748,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G151" t="n">
-        <v>4.2563910484314</v>
+        <v>4.25639152526855</v>
       </c>
       <c r="H151" t="n">
         <v>8178</v>
@@ -4835,7 +4835,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G154" t="n">
-        <v>4.3590669631958</v>
+        <v>4.35906744003296</v>
       </c>
       <c r="H154" t="n">
         <v>15474</v>
@@ -4864,7 +4864,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G155" t="n">
-        <v>4.40573835372925</v>
+        <v>4.40573787689209</v>
       </c>
       <c r="H155" t="n">
         <v>10834</v>
@@ -4893,7 +4893,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G156" t="n">
-        <v>4.46174335479736</v>
+        <v>4.46174383163452</v>
       </c>
       <c r="H156" t="n">
         <v>4570</v>
@@ -4922,7 +4922,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G157" t="n">
-        <v>4.40573835372925</v>
+        <v>4.40573787689209</v>
       </c>
       <c r="H157" t="n">
         <v>4479</v>
@@ -4951,7 +4951,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G158" t="n">
-        <v>4.26572513580322</v>
+        <v>4.26572561264038</v>
       </c>
       <c r="H158" t="n">
         <v>10313</v>
@@ -5067,7 +5067,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G162" t="n">
-        <v>4.14438104629517</v>
+        <v>4.14438056945801</v>
       </c>
       <c r="H162" t="n">
         <v>5657</v>
@@ -5096,7 +5096,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G163" t="n">
-        <v>4.16304922103882</v>
+        <v>4.16304969787598</v>
       </c>
       <c r="H163" t="n">
         <v>656</v>
@@ -5183,7 +5183,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G166" t="n">
-        <v>4.16304922103882</v>
+        <v>4.16304969787598</v>
       </c>
       <c r="H166" t="n">
         <v>505</v>
@@ -5212,7 +5212,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G167" t="n">
-        <v>4.12571239471436</v>
+        <v>4.12571287155151</v>
       </c>
       <c r="H167" t="n">
         <v>1585</v>
@@ -5241,7 +5241,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>4.05103969573975</v>
+        <v>4.05103874206543</v>
       </c>
       <c r="H168" t="n">
         <v>499</v>
@@ -5270,7 +5270,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G169" t="n">
-        <v>4.14438104629517</v>
+        <v>4.14438056945801</v>
       </c>
       <c r="H169" t="n">
         <v>4433</v>
@@ -5299,7 +5299,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G170" t="n">
-        <v>4.13504695892334</v>
+        <v>4.13504648208618</v>
       </c>
       <c r="H170" t="n">
         <v>250</v>
@@ -5328,7 +5328,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G171" t="n">
-        <v>4.15371513366699</v>
+        <v>4.15371561050415</v>
       </c>
       <c r="H171" t="n">
         <v>3578</v>
@@ -5357,7 +5357,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G172" t="n">
-        <v>4.28439378738403</v>
+        <v>4.28439426422119</v>
       </c>
       <c r="H172" t="n">
         <v>1482</v>
@@ -5386,7 +5386,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G173" t="n">
-        <v>4.06037282943726</v>
+        <v>4.06037330627441</v>
       </c>
       <c r="H173" t="n">
         <v>6766</v>
@@ -5415,7 +5415,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G174" t="n">
-        <v>3.59366345405579</v>
+        <v>3.59366369247437</v>
       </c>
       <c r="H174" t="n">
         <v>11092</v>
@@ -5502,7 +5502,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G177" t="n">
-        <v>3.64966869354248</v>
+        <v>3.64966893196106</v>
       </c>
       <c r="H177" t="n">
         <v>15736</v>
@@ -5560,7 +5560,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G179" t="n">
-        <v>3.4536509513855</v>
+        <v>3.45365071296692</v>
       </c>
       <c r="H179" t="n">
         <v>1256</v>
@@ -5589,7 +5589,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G180" t="n">
-        <v>3.56566095352173</v>
+        <v>3.56566119194031</v>
       </c>
       <c r="H180" t="n">
         <v>6037</v>
@@ -5618,7 +5618,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G181" t="n">
-        <v>3.51899003982544</v>
+        <v>3.51899027824402</v>
       </c>
       <c r="H181" t="n">
         <v>1786</v>
@@ -5734,7 +5734,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G185" t="n">
-        <v>3.08961749076843</v>
+        <v>3.08961725234985</v>
       </c>
       <c r="H185" t="n">
         <v>4124</v>
@@ -5763,7 +5763,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G186" t="n">
-        <v>2.92160201072693</v>
+        <v>2.92160224914551</v>
       </c>
       <c r="H186" t="n">
         <v>2211</v>
@@ -5821,7 +5821,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G188" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H188" t="n">
         <v>6941</v>
@@ -5850,7 +5850,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G189" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G190" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H190" t="n">
         <v>500</v>
@@ -5908,7 +5908,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G191" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -5937,7 +5937,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G192" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -6169,7 +6169,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G200" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H200" t="n">
         <v>925</v>
@@ -6198,7 +6198,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G201" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H201" t="n">
         <v>93</v>
@@ -6401,7 +6401,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G208" t="n">
-        <v>2.91226768493652</v>
+        <v>2.91226744651794</v>
       </c>
       <c r="H208" t="n">
         <v>205</v>
@@ -6488,7 +6488,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G211" t="n">
-        <v>2.77225470542908</v>
+        <v>2.77225494384766</v>
       </c>
       <c r="H211" t="n">
         <v>5153</v>
@@ -6517,7 +6517,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>2.76292037963867</v>
+        <v>2.76292061805725</v>
       </c>
       <c r="H212" t="n">
         <v>1030</v>
@@ -6546,7 +6546,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G213" t="n">
-        <v>2.65091037750244</v>
+        <v>2.65091013908386</v>
       </c>
       <c r="H213" t="n">
         <v>760</v>
@@ -6691,7 +6691,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G218" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H218" t="n">
         <v>488</v>
@@ -6749,7 +6749,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G220" t="n">
-        <v>2.85626268386841</v>
+        <v>2.85626244544983</v>
       </c>
       <c r="H220" t="n">
         <v>4706</v>
@@ -6894,7 +6894,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G225" t="n">
-        <v>2.73491835594177</v>
+        <v>2.73491787910461</v>
       </c>
       <c r="H225" t="n">
         <v>823</v>
@@ -7097,7 +7097,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G232" t="n">
-        <v>2.65091037750244</v>
+        <v>2.65091013908386</v>
       </c>
       <c r="H232" t="n">
         <v>1146</v>
@@ -7126,7 +7126,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>2.76292037963867</v>
+        <v>2.76292061805725</v>
       </c>
       <c r="H233" t="n">
         <v>2100</v>
@@ -7213,7 +7213,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G236" t="n">
-        <v>2.75358653068542</v>
+        <v>2.753586769104</v>
       </c>
       <c r="H236" t="n">
         <v>2835</v>
@@ -7271,7 +7271,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G238" t="n">
-        <v>2.85626268386841</v>
+        <v>2.85626244544983</v>
       </c>
       <c r="H238" t="n">
         <v>3815</v>
@@ -7300,7 +7300,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G239" t="n">
-        <v>2.85626268386841</v>
+        <v>2.85626244544983</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G247" t="n">
-        <v>2.91226768493652</v>
+        <v>2.91226744651794</v>
       </c>
       <c r="H247" t="n">
         <v>1679</v>
@@ -7561,7 +7561,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G248" t="n">
-        <v>2.97760701179504</v>
+        <v>2.97760725021362</v>
       </c>
       <c r="H248" t="n">
         <v>6756</v>
@@ -7590,7 +7590,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G249" t="n">
-        <v>2.88426518440247</v>
+        <v>2.88426494598389</v>
       </c>
       <c r="H249" t="n">
         <v>3107</v>
@@ -8083,7 +8083,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G266" t="n">
-        <v>2.6229076385498</v>
+        <v>2.62290787696838</v>
       </c>
       <c r="H266" t="n">
         <v>2300</v>
@@ -8141,7 +8141,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G268" t="n">
-        <v>2.63224172592163</v>
+        <v>2.63224196434021</v>
       </c>
       <c r="H268" t="n">
         <v>1640</v>
@@ -8199,7 +8199,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G270" t="n">
-        <v>2.6229076385498</v>
+        <v>2.62290787696838</v>
       </c>
       <c r="H270" t="n">
         <v>626</v>
@@ -8286,7 +8286,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G273" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H273" t="n">
         <v>3807</v>
@@ -8315,7 +8315,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G274" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H274" t="n">
         <v>12686</v>
@@ -8344,7 +8344,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G275" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H275" t="n">
         <v>3412</v>
@@ -8402,7 +8402,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G277" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H277" t="n">
         <v>689</v>
@@ -8431,7 +8431,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G278" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H278" t="n">
         <v>0</v>
@@ -8460,7 +8460,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G279" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H279" t="n">
         <v>1890</v>
@@ -8489,7 +8489,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G280" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H280" t="n">
         <v>3085</v>
@@ -8547,7 +8547,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G282" t="n">
-        <v>2.48289489746094</v>
+        <v>2.48289513587952</v>
       </c>
       <c r="H282" t="n">
         <v>1691</v>
@@ -8605,7 +8605,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G284" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H284" t="n">
         <v>550</v>
@@ -8634,7 +8634,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G285" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H285" t="n">
         <v>437</v>
@@ -8663,7 +8663,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G286" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H286" t="n">
         <v>155</v>
@@ -8808,7 +8808,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G291" t="n">
-        <v>2.6229076385498</v>
+        <v>2.62290787696838</v>
       </c>
       <c r="H291" t="n">
         <v>32348</v>
@@ -8924,7 +8924,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G295" t="n">
-        <v>2.54823446273804</v>
+        <v>2.54823422431946</v>
       </c>
       <c r="H295" t="n">
         <v>1050</v>
@@ -8982,7 +8982,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G297" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H297" t="n">
         <v>238</v>
@@ -9011,7 +9011,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G298" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H298" t="n">
         <v>0</v>
@@ -9272,7 +9272,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G307" t="n">
-        <v>2.50156354904175</v>
+        <v>2.50156331062317</v>
       </c>
       <c r="H307" t="n">
         <v>7083</v>
@@ -9301,7 +9301,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G308" t="n">
-        <v>2.46422672271729</v>
+        <v>2.46422648429871</v>
       </c>
       <c r="H308" t="n">
         <v>982</v>
@@ -9388,7 +9388,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G311" t="n">
-        <v>2.48289489746094</v>
+        <v>2.48289513587952</v>
       </c>
       <c r="H311" t="n">
         <v>204</v>
@@ -9417,7 +9417,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G312" t="n">
-        <v>2.48289489746094</v>
+        <v>2.48289513587952</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G313" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H313" t="n">
         <v>350</v>
@@ -9504,7 +9504,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G315" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H315" t="n">
         <v>500</v>
@@ -9533,7 +9533,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G316" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H316" t="n">
         <v>2033</v>
@@ -9620,7 +9620,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G319" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H319" t="n">
         <v>50</v>
@@ -9649,7 +9649,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G320" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H320" t="n">
         <v>110</v>
@@ -9678,7 +9678,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G321" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H321" t="n">
         <v>3920</v>
@@ -9765,7 +9765,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G324" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H324" t="n">
         <v>1280</v>
@@ -9794,7 +9794,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G325" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G326" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H326" t="n">
         <v>4022</v>
@@ -9852,7 +9852,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H327" t="n">
         <v>7005</v>
@@ -9910,7 +9910,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G329" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H329" t="n">
         <v>2690</v>
@@ -9939,7 +9939,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G330" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -9968,7 +9968,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G331" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -9997,7 +9997,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G332" t="n">
-        <v>2.27754259109497</v>
+        <v>2.27754282951355</v>
       </c>
       <c r="H332" t="n">
         <v>2310</v>
@@ -10055,7 +10055,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G334" t="n">
-        <v>2.24020600318909</v>
+        <v>2.24020576477051</v>
       </c>
       <c r="H334" t="n">
         <v>4089</v>
@@ -10113,7 +10113,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G336" t="n">
-        <v>2.26820874214172</v>
+        <v>2.26820850372314</v>
       </c>
       <c r="H336" t="n">
         <v>12996</v>
@@ -10142,7 +10142,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G337" t="n">
-        <v>2.24020600318909</v>
+        <v>2.24020576477051</v>
       </c>
       <c r="H337" t="n">
         <v>15170</v>
@@ -10200,7 +10200,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G339" t="n">
-        <v>2.1281955242157</v>
+        <v>2.12819576263428</v>
       </c>
       <c r="H339" t="n">
         <v>35672</v>
@@ -10287,7 +10287,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>2.06285619735718</v>
+        <v>2.06285643577576</v>
       </c>
       <c r="H342" t="n">
         <v>15756</v>
@@ -10316,7 +10316,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G343" t="n">
-        <v>1.98818278312683</v>
+        <v>1.98818302154541</v>
       </c>
       <c r="H343" t="n">
         <v>9524</v>
@@ -10461,7 +10461,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G348" t="n">
-        <v>1.76416218280792</v>
+        <v>1.76416206359863</v>
       </c>
       <c r="H348" t="n">
         <v>3234</v>
@@ -10548,7 +10548,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G351" t="n">
-        <v>1.57747828960419</v>
+        <v>1.57747840881348</v>
       </c>
       <c r="H351" t="n">
         <v>44141</v>
@@ -10838,7 +10838,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G361" t="n">
-        <v>1.66148602962494</v>
+        <v>1.66148614883423</v>
       </c>
       <c r="H361" t="n">
         <v>186911</v>
@@ -10896,7 +10896,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G363" t="n">
-        <v>1.84816980361938</v>
+        <v>1.84817004203796</v>
       </c>
       <c r="H363" t="n">
         <v>74595</v>
@@ -10954,7 +10954,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G365" t="n">
-        <v>1.94151175022125</v>
+        <v>1.94151163101196</v>
       </c>
       <c r="H365" t="n">
         <v>38866</v>
@@ -10983,7 +10983,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G366" t="n">
-        <v>2.02551984786987</v>
+        <v>2.02551937103271</v>
       </c>
       <c r="H366" t="n">
         <v>41167</v>
@@ -11012,7 +11012,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G367" t="n">
-        <v>2.06285619735718</v>
+        <v>2.06285643577576</v>
       </c>
       <c r="H367" t="n">
         <v>65581</v>
@@ -11070,7 +11070,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G369" t="n">
-        <v>2.1281955242157</v>
+        <v>2.12819576263428</v>
       </c>
       <c r="H369" t="n">
         <v>27238</v>
@@ -11157,7 +11157,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G372" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H372" t="n">
         <v>100574</v>
@@ -11186,7 +11186,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G373" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H373" t="n">
         <v>50734</v>
@@ -11215,7 +11215,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G374" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H374" t="n">
         <v>32104</v>
@@ -11273,7 +11273,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G376" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H376" t="n">
         <v>260524</v>
@@ -11418,7 +11418,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G381" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H381" t="n">
         <v>13489</v>
@@ -11447,7 +11447,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G382" t="n">
-        <v>2.50156354904175</v>
+        <v>2.50156331062317</v>
       </c>
       <c r="H382" t="n">
         <v>22219</v>
@@ -11476,7 +11476,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G383" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H383" t="n">
         <v>19181</v>
@@ -11505,7 +11505,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G384" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H384" t="n">
         <v>46528</v>
@@ -11592,7 +11592,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G387" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H387" t="n">
         <v>20692</v>
@@ -11737,7 +11737,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G392" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H392" t="n">
         <v>78496</v>
@@ -11766,7 +11766,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G393" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H393" t="n">
         <v>2710</v>
@@ -11853,7 +11853,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G396" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H396" t="n">
         <v>3361</v>
@@ -11882,7 +11882,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G397" t="n">
-        <v>2.27754259109497</v>
+        <v>2.27754282951355</v>
       </c>
       <c r="H397" t="n">
         <v>70461</v>
@@ -11911,7 +11911,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H398" t="n">
         <v>4671</v>
@@ -11940,7 +11940,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G399" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H399" t="n">
         <v>20075</v>
@@ -11969,7 +11969,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G400" t="n">
-        <v>2.20286917686462</v>
+        <v>2.20286893844604</v>
       </c>
       <c r="H400" t="n">
         <v>35084</v>
@@ -11998,7 +11998,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G401" t="n">
-        <v>2.07219052314758</v>
+        <v>2.072190284729</v>
       </c>
       <c r="H401" t="n">
         <v>51398</v>
@@ -12201,7 +12201,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G408" t="n">
-        <v>2.20286917686462</v>
+        <v>2.20286893844604</v>
       </c>
       <c r="H408" t="n">
         <v>20357</v>
@@ -12375,7 +12375,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G414" t="n">
-        <v>2.08152461051941</v>
+        <v>2.08152484893799</v>
       </c>
       <c r="H414" t="n">
         <v>6065</v>
@@ -12462,7 +12462,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G417" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H417" t="n">
         <v>112741</v>
@@ -12491,7 +12491,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G418" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H418" t="n">
         <v>31183</v>
@@ -12520,7 +12520,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G419" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H419" t="n">
         <v>24246</v>
@@ -12607,7 +12607,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G422" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H422" t="n">
         <v>15411</v>
@@ -12665,7 +12665,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G424" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H424" t="n">
         <v>4139</v>
@@ -12723,7 +12723,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G426" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H426" t="n">
         <v>6863</v>
@@ -12752,7 +12752,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G427" t="n">
-        <v>2.26820874214172</v>
+        <v>2.26820850372314</v>
       </c>
       <c r="H427" t="n">
         <v>8209</v>
@@ -12781,7 +12781,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G428" t="n">
-        <v>2.27754259109497</v>
+        <v>2.27754282951355</v>
       </c>
       <c r="H428" t="n">
         <v>8879</v>
@@ -12810,7 +12810,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G429" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H429" t="n">
         <v>17663</v>
@@ -12839,7 +12839,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G430" t="n">
-        <v>2.25887441635132</v>
+        <v>2.2588746547699</v>
       </c>
       <c r="H430" t="n">
         <v>8648</v>
@@ -12868,7 +12868,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G431" t="n">
-        <v>2.25887441635132</v>
+        <v>2.2588746547699</v>
       </c>
       <c r="H431" t="n">
         <v>10630</v>
@@ -12897,7 +12897,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G432" t="n">
-        <v>2.27754259109497</v>
+        <v>2.27754282951355</v>
       </c>
       <c r="H432" t="n">
         <v>5782</v>
@@ -12926,7 +12926,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G433" t="n">
-        <v>2.25887441635132</v>
+        <v>2.2588746547699</v>
       </c>
       <c r="H433" t="n">
         <v>39250</v>
@@ -12955,7 +12955,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G434" t="n">
-        <v>2.24020600318909</v>
+        <v>2.24020576477051</v>
       </c>
       <c r="H434" t="n">
         <v>3580</v>
@@ -13013,7 +13013,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G436" t="n">
-        <v>2.27754259109497</v>
+        <v>2.27754282951355</v>
       </c>
       <c r="H436" t="n">
         <v>3250</v>
@@ -13042,7 +13042,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G437" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H437" t="n">
         <v>10145</v>
@@ -13071,7 +13071,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G438" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H438" t="n">
         <v>40576</v>
@@ -13100,7 +13100,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G439" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H439" t="n">
         <v>6378</v>
@@ -13158,7 +13158,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G441" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H441" t="n">
         <v>4745</v>
@@ -13216,7 +13216,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G443" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H443" t="n">
         <v>10240</v>
@@ -13274,7 +13274,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G445" t="n">
-        <v>2.23087167739868</v>
+        <v>2.23087191581726</v>
       </c>
       <c r="H445" t="n">
         <v>29277</v>
@@ -13303,7 +13303,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G446" t="n">
-        <v>2.23087167739868</v>
+        <v>2.23087191581726</v>
       </c>
       <c r="H446" t="n">
         <v>37961</v>
@@ -13332,7 +13332,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G447" t="n">
-        <v>2.27754259109497</v>
+        <v>2.27754282951355</v>
       </c>
       <c r="H447" t="n">
         <v>53947</v>
@@ -13361,7 +13361,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G448" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H448" t="n">
         <v>75506</v>
@@ -13419,7 +13419,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G450" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H450" t="n">
         <v>45849</v>
@@ -13738,7 +13738,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G461" t="n">
-        <v>2.73491835594177</v>
+        <v>2.73491787910461</v>
       </c>
       <c r="H461" t="n">
         <v>18508</v>
@@ -13854,7 +13854,7 @@
         <v>3.25</v>
       </c>
       <c r="G465" t="n">
-        <v>3.03361225128174</v>
+        <v>3.03361201286316</v>
       </c>
       <c r="H465" t="n">
         <v>83242</v>
@@ -13912,7 +13912,7 @@
         <v>3.25</v>
       </c>
       <c r="G467" t="n">
-        <v>3.03361225128174</v>
+        <v>3.03361201286316</v>
       </c>
       <c r="H467" t="n">
         <v>62595</v>
@@ -13941,7 +13941,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G468" t="n">
-        <v>3.08028316497803</v>
+        <v>3.08028292655945</v>
       </c>
       <c r="H468" t="n">
         <v>39566</v>
@@ -13970,7 +13970,7 @@
         <v>3.25</v>
       </c>
       <c r="G469" t="n">
-        <v>3.03361225128174</v>
+        <v>3.03361201286316</v>
       </c>
       <c r="H469" t="n">
         <v>22979</v>
@@ -14028,7 +14028,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G471" t="n">
-        <v>3.27630138397217</v>
+        <v>3.27630114555359</v>
       </c>
       <c r="H471" t="n">
         <v>27454</v>
@@ -14086,7 +14086,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G473" t="n">
-        <v>3.3323061466217</v>
+        <v>3.33230638504028</v>
       </c>
       <c r="H473" t="n">
         <v>14421</v>
@@ -14144,7 +14144,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G475" t="n">
-        <v>3.2296302318573</v>
+        <v>3.22962999343872</v>
       </c>
       <c r="H475" t="n">
         <v>13099</v>
@@ -14202,7 +14202,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G477" t="n">
-        <v>3.11761975288391</v>
+        <v>3.11761999130249</v>
       </c>
       <c r="H477" t="n">
         <v>29958</v>
@@ -14289,7 +14289,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G480" t="n">
-        <v>3.20162773132324</v>
+        <v>3.20162796974182</v>
       </c>
       <c r="H480" t="n">
         <v>55118</v>
@@ -14347,7 +14347,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G482" t="n">
-        <v>3.08961749076843</v>
+        <v>3.08961725234985</v>
       </c>
       <c r="H482" t="n">
         <v>34183</v>
@@ -14376,7 +14376,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G483" t="n">
-        <v>3.12695384025574</v>
+        <v>3.12695407867432</v>
       </c>
       <c r="H483" t="n">
         <v>32378</v>
@@ -14434,7 +14434,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G485" t="n">
-        <v>3.15495657920837</v>
+        <v>3.15495681762695</v>
       </c>
       <c r="H485" t="n">
         <v>12813</v>
@@ -14550,7 +14550,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G489" t="n">
-        <v>3.11761975288391</v>
+        <v>3.11761999130249</v>
       </c>
       <c r="H489" t="n">
         <v>17075</v>
@@ -14579,7 +14579,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G490" t="n">
-        <v>3.08028316497803</v>
+        <v>3.08028292655945</v>
       </c>
       <c r="H490" t="n">
         <v>17126</v>
@@ -14637,7 +14637,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G492" t="n">
-        <v>2.97760701179504</v>
+        <v>2.97760725021362</v>
       </c>
       <c r="H492" t="n">
         <v>12648</v>
@@ -14666,7 +14666,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G493" t="n">
-        <v>3.04294657707214</v>
+        <v>3.04294633865356</v>
       </c>
       <c r="H493" t="n">
         <v>3499</v>
@@ -14753,7 +14753,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G496" t="n">
-        <v>3.08028316497803</v>
+        <v>3.08028292655945</v>
       </c>
       <c r="H496" t="n">
         <v>39248</v>
@@ -14782,7 +14782,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G497" t="n">
-        <v>3.08028316497803</v>
+        <v>3.08028292655945</v>
       </c>
       <c r="H497" t="n">
         <v>17788</v>
@@ -14840,7 +14840,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G499" t="n">
-        <v>3.11761975288391</v>
+        <v>3.11761999130249</v>
       </c>
       <c r="H499" t="n">
         <v>21907</v>
@@ -14869,7 +14869,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G500" t="n">
-        <v>3.11761975288391</v>
+        <v>3.11761999130249</v>
       </c>
       <c r="H500" t="n">
         <v>17501</v>
@@ -14956,7 +14956,7 @@
         <v>3.25</v>
       </c>
       <c r="G503" t="n">
-        <v>3.03361225128174</v>
+        <v>3.03361201286316</v>
       </c>
       <c r="H503" t="n">
         <v>5248</v>
@@ -14985,7 +14985,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G504" t="n">
-        <v>3.02427792549133</v>
+        <v>3.02427816390991</v>
       </c>
       <c r="H504" t="n">
         <v>20370</v>
@@ -15130,7 +15130,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G509" t="n">
-        <v>2.96827292442322</v>
+        <v>2.9682731628418</v>
       </c>
       <c r="H509" t="n">
         <v>5868</v>
@@ -15391,7 +15391,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G518" t="n">
-        <v>2.73491835594177</v>
+        <v>2.73491787910461</v>
       </c>
       <c r="H518" t="n">
         <v>15415</v>
@@ -15478,7 +15478,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G521" t="n">
-        <v>2.75358653068542</v>
+        <v>2.753586769104</v>
       </c>
       <c r="H521" t="n">
         <v>5980</v>
@@ -15565,7 +15565,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G524" t="n">
-        <v>2.63224172592163</v>
+        <v>2.63224196434021</v>
       </c>
       <c r="H524" t="n">
         <v>10487</v>
@@ -15710,7 +15710,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G529" t="n">
-        <v>2.46422672271729</v>
+        <v>2.46422648429871</v>
       </c>
       <c r="H529" t="n">
         <v>31873</v>
@@ -15768,7 +15768,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G531" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H531" t="n">
         <v>29110</v>
@@ -15797,7 +15797,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G532" t="n">
-        <v>2.46422672271729</v>
+        <v>2.46422648429871</v>
       </c>
       <c r="H532" t="n">
         <v>14070</v>
@@ -15855,7 +15855,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G534" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H534" t="n">
         <v>58949</v>
@@ -15913,7 +15913,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G536" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H536" t="n">
         <v>18439</v>
@@ -15971,7 +15971,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G538" t="n">
-        <v>2.6229076385498</v>
+        <v>2.62290787696838</v>
       </c>
       <c r="H538" t="n">
         <v>65552</v>
@@ -16000,7 +16000,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G539" t="n">
-        <v>2.6229076385498</v>
+        <v>2.62290787696838</v>
       </c>
       <c r="H539" t="n">
         <v>55945</v>
@@ -16029,7 +16029,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G540" t="n">
-        <v>2.6229076385498</v>
+        <v>2.62290787696838</v>
       </c>
       <c r="H540" t="n">
         <v>32955</v>
@@ -16087,7 +16087,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G542" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H542" t="n">
         <v>34564</v>
@@ -16116,7 +16116,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G543" t="n">
-        <v>2.63224172592163</v>
+        <v>2.63224196434021</v>
       </c>
       <c r="H543" t="n">
         <v>7927</v>
@@ -16145,7 +16145,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G544" t="n">
-        <v>2.54823446273804</v>
+        <v>2.54823422431946</v>
       </c>
       <c r="H544" t="n">
         <v>22371</v>
@@ -16406,7 +16406,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G553" t="n">
-        <v>2.65091037750244</v>
+        <v>2.65091013908386</v>
       </c>
       <c r="H553" t="n">
         <v>17288</v>
@@ -16464,7 +16464,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G555" t="n">
-        <v>2.75358653068542</v>
+        <v>2.753586769104</v>
       </c>
       <c r="H555" t="n">
         <v>44001</v>
@@ -16493,7 +16493,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G556" t="n">
-        <v>2.77225470542908</v>
+        <v>2.77225494384766</v>
       </c>
       <c r="H556" t="n">
         <v>1552</v>
@@ -16522,7 +16522,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G557" t="n">
-        <v>2.77225470542908</v>
+        <v>2.77225494384766</v>
       </c>
       <c r="H557" t="n">
         <v>7892</v>
@@ -16551,7 +16551,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G558" t="n">
-        <v>2.65091037750244</v>
+        <v>2.65091013908386</v>
       </c>
       <c r="H558" t="n">
         <v>16646</v>
@@ -16580,7 +16580,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G559" t="n">
-        <v>2.65091037750244</v>
+        <v>2.65091013908386</v>
       </c>
       <c r="H559" t="n">
         <v>14560</v>
@@ -16638,7 +16638,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G561" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H561" t="n">
         <v>55511</v>
@@ -16899,7 +16899,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G570" t="n">
-        <v>2.77225470542908</v>
+        <v>2.77225494384766</v>
       </c>
       <c r="H570" t="n">
         <v>12140</v>
@@ -17102,7 +17102,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G577" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H577" t="n">
         <v>5655</v>
@@ -17218,7 +17218,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G581" t="n">
-        <v>2.77225470542908</v>
+        <v>2.77225494384766</v>
       </c>
       <c r="H581" t="n">
         <v>1650</v>
@@ -17276,7 +17276,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G583" t="n">
-        <v>2.76292037963867</v>
+        <v>2.76292061805725</v>
       </c>
       <c r="H583" t="n">
         <v>1500</v>
@@ -17450,7 +17450,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G589" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H589" t="n">
         <v>5281</v>
@@ -17508,7 +17508,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G591" t="n">
-        <v>2.77225470542908</v>
+        <v>2.77225494384766</v>
       </c>
       <c r="H591" t="n">
         <v>2450</v>
@@ -17537,7 +17537,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G592" t="n">
-        <v>2.77225470542908</v>
+        <v>2.77225494384766</v>
       </c>
       <c r="H592" t="n">
         <v>0</v>
@@ -17595,7 +17595,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G594" t="n">
-        <v>2.79092311859131</v>
+        <v>2.79092335700989</v>
       </c>
       <c r="H594" t="n">
         <v>3352</v>
@@ -17653,7 +17653,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G596" t="n">
-        <v>2.77225470542908</v>
+        <v>2.77225494384766</v>
       </c>
       <c r="H596" t="n">
         <v>850</v>
@@ -17711,7 +17711,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G598" t="n">
-        <v>2.75358653068542</v>
+        <v>2.753586769104</v>
       </c>
       <c r="H598" t="n">
         <v>47530</v>
@@ -17769,7 +17769,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G600" t="n">
-        <v>2.75358653068542</v>
+        <v>2.753586769104</v>
       </c>
       <c r="H600" t="n">
         <v>7623</v>
@@ -17856,7 +17856,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G603" t="n">
-        <v>2.73491835594177</v>
+        <v>2.73491787910461</v>
       </c>
       <c r="H603" t="n">
         <v>6297</v>
@@ -18030,7 +18030,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G609" t="n">
-        <v>2.76292037963867</v>
+        <v>2.76292061805725</v>
       </c>
       <c r="H609" t="n">
         <v>13444</v>
@@ -18059,7 +18059,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G610" t="n">
-        <v>2.77225470542908</v>
+        <v>2.77225494384766</v>
       </c>
       <c r="H610" t="n">
         <v>4440</v>
@@ -18175,7 +18175,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G614" t="n">
-        <v>2.77225470542908</v>
+        <v>2.77225494384766</v>
       </c>
       <c r="H614" t="n">
         <v>20031</v>
@@ -18407,7 +18407,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G622" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H622" t="n">
         <v>9853</v>
@@ -18494,7 +18494,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G625" t="n">
-        <v>2.48289489746094</v>
+        <v>2.48289513587952</v>
       </c>
       <c r="H625" t="n">
         <v>9305</v>
@@ -18523,7 +18523,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G626" t="n">
-        <v>2.50156354904175</v>
+        <v>2.50156331062317</v>
       </c>
       <c r="H626" t="n">
         <v>7546</v>
@@ -18552,7 +18552,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G627" t="n">
-        <v>2.48289489746094</v>
+        <v>2.48289513587952</v>
       </c>
       <c r="H627" t="n">
         <v>3175</v>
@@ -18610,7 +18610,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G629" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H629" t="n">
         <v>9381</v>
@@ -18639,7 +18639,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G630" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H630" t="n">
         <v>5890</v>
@@ -18784,7 +18784,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G635" t="n">
-        <v>2.65091037750244</v>
+        <v>2.65091013908386</v>
       </c>
       <c r="H635" t="n">
         <v>1700</v>
@@ -18871,7 +18871,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G638" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H638" t="n">
         <v>10004</v>
@@ -19045,7 +19045,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G644" t="n">
-        <v>2.50156354904175</v>
+        <v>2.50156331062317</v>
       </c>
       <c r="H644" t="n">
         <v>7248</v>
@@ -19074,7 +19074,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G645" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H645" t="n">
         <v>26536</v>
@@ -19248,7 +19248,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G651" t="n">
-        <v>2.54823446273804</v>
+        <v>2.54823422431946</v>
       </c>
       <c r="H651" t="n">
         <v>1402</v>
@@ -19277,7 +19277,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G652" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H652" t="n">
         <v>6533</v>
@@ -19306,7 +19306,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G653" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H653" t="n">
         <v>6896</v>
@@ -19335,7 +19335,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G654" t="n">
-        <v>2.50156354904175</v>
+        <v>2.50156331062317</v>
       </c>
       <c r="H654" t="n">
         <v>2900</v>
@@ -19393,7 +19393,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H656" t="n">
         <v>5573</v>
@@ -19654,7 +19654,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G665" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H665" t="n">
         <v>1580</v>
@@ -19828,7 +19828,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G671" t="n">
-        <v>2.52956581115723</v>
+        <v>2.52956604957581</v>
       </c>
       <c r="H671" t="n">
         <v>1055</v>
@@ -19915,7 +19915,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G674" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H674" t="n">
         <v>1004</v>
@@ -19944,7 +19944,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G675" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H675" t="n">
         <v>0</v>
@@ -20060,7 +20060,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G679" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H679" t="n">
         <v>6131</v>
@@ -20234,7 +20234,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G685" t="n">
-        <v>2.65091037750244</v>
+        <v>2.65091013908386</v>
       </c>
       <c r="H685" t="n">
         <v>3302</v>
@@ -20263,7 +20263,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G686" t="n">
-        <v>2.48289489746094</v>
+        <v>2.48289513587952</v>
       </c>
       <c r="H686" t="n">
         <v>18872</v>
@@ -20321,7 +20321,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G688" t="n">
-        <v>2.50156354904175</v>
+        <v>2.50156331062317</v>
       </c>
       <c r="H688" t="n">
         <v>5477</v>
@@ -20350,7 +20350,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G689" t="n">
-        <v>2.51089763641357</v>
+        <v>2.510897397995</v>
       </c>
       <c r="H689" t="n">
         <v>6459</v>
@@ -20524,7 +20524,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G695" t="n">
-        <v>2.23087167739868</v>
+        <v>2.23087191581726</v>
       </c>
       <c r="H695" t="n">
         <v>25461</v>
@@ -20582,7 +20582,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G697" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H697" t="n">
         <v>5477</v>
@@ -20611,7 +20611,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G698" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H698" t="n">
         <v>4617</v>
@@ -20669,7 +20669,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G700" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H700" t="n">
         <v>10078</v>
@@ -20698,7 +20698,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G701" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H701" t="n">
         <v>11679</v>
@@ -20727,7 +20727,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G702" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H702" t="n">
         <v>12282</v>
@@ -20814,7 +20814,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G705" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H705" t="n">
         <v>7231</v>
@@ -20843,7 +20843,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G706" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H706" t="n">
         <v>16794</v>
@@ -20901,7 +20901,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G708" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H708" t="n">
         <v>11650</v>
@@ -21046,7 +21046,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G713" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H713" t="n">
         <v>5601</v>
@@ -21075,7 +21075,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G714" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H714" t="n">
         <v>3865</v>
@@ -21249,7 +21249,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G720" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H720" t="n">
         <v>2110</v>
@@ -21307,7 +21307,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G722" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H722" t="n">
         <v>20</v>
@@ -21365,7 +21365,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G724" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H724" t="n">
         <v>3000</v>
@@ -21394,7 +21394,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G725" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H725" t="n">
         <v>2583</v>
@@ -21423,7 +21423,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G726" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H726" t="n">
         <v>2</v>
@@ -21452,7 +21452,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G727" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H727" t="n">
         <v>4770</v>
@@ -21481,7 +21481,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G728" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H728" t="n">
         <v>6795</v>
@@ -21539,7 +21539,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G730" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H730" t="n">
         <v>9829</v>
@@ -21655,7 +21655,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G734" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H734" t="n">
         <v>59751</v>
@@ -21713,7 +21713,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G736" t="n">
-        <v>2.24020600318909</v>
+        <v>2.24020576477051</v>
       </c>
       <c r="H736" t="n">
         <v>8673</v>
@@ -21800,7 +21800,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G739" t="n">
-        <v>2.23087167739868</v>
+        <v>2.23087191581726</v>
       </c>
       <c r="H739" t="n">
         <v>4337</v>
@@ -21887,7 +21887,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G742" t="n">
-        <v>2.23087167739868</v>
+        <v>2.23087191581726</v>
       </c>
       <c r="H742" t="n">
         <v>6415</v>
@@ -21974,7 +21974,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G745" t="n">
-        <v>2.20286917686462</v>
+        <v>2.20286893844604</v>
       </c>
       <c r="H745" t="n">
         <v>3400</v>
@@ -22061,7 +22061,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G748" t="n">
-        <v>2.1281955242157</v>
+        <v>2.12819576263428</v>
       </c>
       <c r="H748" t="n">
         <v>9244</v>
@@ -22090,7 +22090,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G749" t="n">
-        <v>2.1281955242157</v>
+        <v>2.12819576263428</v>
       </c>
       <c r="H749" t="n">
         <v>2187</v>
@@ -22322,7 +22322,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G757" t="n">
-        <v>2.15619826316833</v>
+        <v>2.15619802474976</v>
       </c>
       <c r="H757" t="n">
         <v>5</v>
@@ -22351,7 +22351,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G758" t="n">
-        <v>2.24020600318909</v>
+        <v>2.24020576477051</v>
       </c>
       <c r="H758" t="n">
         <v>3859</v>
@@ -22380,7 +22380,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G759" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H759" t="n">
         <v>6674</v>
@@ -22409,7 +22409,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G760" t="n">
-        <v>2.15619826316833</v>
+        <v>2.15619802474976</v>
       </c>
       <c r="H760" t="n">
         <v>9288</v>
@@ -22496,7 +22496,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G763" t="n">
-        <v>2.15619826316833</v>
+        <v>2.15619802474976</v>
       </c>
       <c r="H763" t="n">
         <v>74</v>
@@ -22670,7 +22670,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G769" t="n">
-        <v>2.08152461051941</v>
+        <v>2.08152484893799</v>
       </c>
       <c r="H769" t="n">
         <v>5355</v>
@@ -22699,7 +22699,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G770" t="n">
-        <v>2.08152461051941</v>
+        <v>2.08152484893799</v>
       </c>
       <c r="H770" t="n">
         <v>0</v>
@@ -22902,7 +22902,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G777" t="n">
-        <v>2.00685143470764</v>
+        <v>2.00685119628906</v>
       </c>
       <c r="H777" t="n">
         <v>6782</v>
@@ -22931,7 +22931,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G778" t="n">
-        <v>2.01618552207947</v>
+        <v>2.01618528366089</v>
       </c>
       <c r="H778" t="n">
         <v>3662</v>
@@ -22960,7 +22960,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G779" t="n">
-        <v>2.01618552207947</v>
+        <v>2.01618528366089</v>
       </c>
       <c r="H779" t="n">
         <v>5386</v>
@@ -22989,7 +22989,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G780" t="n">
-        <v>1.99751698970795</v>
+        <v>1.99751710891724</v>
       </c>
       <c r="H780" t="n">
         <v>923</v>
@@ -23018,7 +23018,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G781" t="n">
-        <v>2.02551984786987</v>
+        <v>2.02551937103271</v>
       </c>
       <c r="H781" t="n">
         <v>2701</v>
@@ -23047,7 +23047,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G782" t="n">
-        <v>1.96018004417419</v>
+        <v>1.96018016338348</v>
       </c>
       <c r="H782" t="n">
         <v>4798</v>
@@ -23076,7 +23076,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G783" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H783" t="n">
         <v>16989</v>
@@ -23192,7 +23192,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G787" t="n">
-        <v>1.76416218280792</v>
+        <v>1.76416206359863</v>
       </c>
       <c r="H787" t="n">
         <v>18464</v>
@@ -23221,7 +23221,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G788" t="n">
-        <v>1.76882934570312</v>
+        <v>1.76882922649384</v>
       </c>
       <c r="H788" t="n">
         <v>25213</v>
@@ -23366,7 +23366,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G793" t="n">
-        <v>1.79216480255127</v>
+        <v>1.79216468334198</v>
       </c>
       <c r="H793" t="n">
         <v>26069</v>
@@ -23424,7 +23424,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G795" t="n">
-        <v>1.84816980361938</v>
+        <v>1.84817004203796</v>
       </c>
       <c r="H795" t="n">
         <v>1870</v>
@@ -23569,7 +23569,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G800" t="n">
-        <v>1.82016730308533</v>
+        <v>1.82016742229462</v>
       </c>
       <c r="H800" t="n">
         <v>293</v>
@@ -23743,7 +23743,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H806" t="n">
         <v>2225</v>
@@ -23772,7 +23772,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G807" t="n">
-        <v>1.88550674915314</v>
+        <v>1.88550662994385</v>
       </c>
       <c r="H807" t="n">
         <v>530</v>
@@ -23975,7 +23975,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G814" t="n">
-        <v>1.98818278312683</v>
+        <v>1.98818302154541</v>
       </c>
       <c r="H814" t="n">
         <v>5130</v>
@@ -24004,7 +24004,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G815" t="n">
-        <v>1.98818278312683</v>
+        <v>1.98818302154541</v>
       </c>
       <c r="H815" t="n">
         <v>13633</v>
@@ -24033,7 +24033,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G816" t="n">
-        <v>1.978848695755</v>
+        <v>1.97884833812714</v>
       </c>
       <c r="H816" t="n">
         <v>18908</v>
@@ -24120,7 +24120,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G819" t="n">
-        <v>1.94151175022125</v>
+        <v>1.94151163101196</v>
       </c>
       <c r="H819" t="n">
         <v>4235</v>
@@ -24236,7 +24236,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G823" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H823" t="n">
         <v>2258</v>
@@ -24265,7 +24265,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G824" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H824" t="n">
         <v>0</v>
@@ -24323,7 +24323,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G826" t="n">
-        <v>2.02551984786987</v>
+        <v>2.02551937103271</v>
       </c>
       <c r="H826" t="n">
         <v>12498</v>
@@ -24352,7 +24352,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G827" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H827" t="n">
         <v>15383</v>
@@ -24381,7 +24381,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G828" t="n">
-        <v>1.88550674915314</v>
+        <v>1.88550662994385</v>
       </c>
       <c r="H828" t="n">
         <v>2410</v>
@@ -24410,7 +24410,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G829" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H829" t="n">
         <v>4980</v>
@@ -24468,7 +24468,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G831" t="n">
-        <v>1.84816980361938</v>
+        <v>1.84817004203796</v>
       </c>
       <c r="H831" t="n">
         <v>1282</v>
@@ -24526,7 +24526,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G833" t="n">
-        <v>1.88550674915314</v>
+        <v>1.88550662994385</v>
       </c>
       <c r="H833" t="n">
         <v>500</v>
@@ -24671,7 +24671,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G838" t="n">
-        <v>1.82016730308533</v>
+        <v>1.82016742229462</v>
       </c>
       <c r="H838" t="n">
         <v>2308</v>
@@ -24787,7 +24787,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G842" t="n">
-        <v>1.79216480255127</v>
+        <v>1.79216468334198</v>
       </c>
       <c r="H842" t="n">
         <v>5998</v>
@@ -24845,7 +24845,7 @@
         <v>1.875</v>
       </c>
       <c r="G844" t="n">
-        <v>1.7501608133316</v>
+        <v>1.75016093254089</v>
       </c>
       <c r="H844" t="n">
         <v>17976</v>
@@ -25048,7 +25048,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G851" t="n">
-        <v>1.79216480255127</v>
+        <v>1.79216468334198</v>
       </c>
       <c r="H851" t="n">
         <v>8829</v>
@@ -25106,7 +25106,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G853" t="n">
-        <v>1.82016730308533</v>
+        <v>1.82016742229462</v>
       </c>
       <c r="H853" t="n">
         <v>4615</v>
@@ -25251,7 +25251,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G858" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H858" t="n">
         <v>1659</v>
@@ -25309,7 +25309,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G860" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H860" t="n">
         <v>5149</v>
@@ -25425,7 +25425,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G864" t="n">
-        <v>1.84816980361938</v>
+        <v>1.84817004203796</v>
       </c>
       <c r="H864" t="n">
         <v>1500</v>
@@ -25570,7 +25570,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G869" t="n">
-        <v>1.88550674915314</v>
+        <v>1.88550662994385</v>
       </c>
       <c r="H869" t="n">
         <v>4311</v>
@@ -25599,7 +25599,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G870" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H870" t="n">
         <v>5440</v>
@@ -25628,7 +25628,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G871" t="n">
-        <v>1.94151175022125</v>
+        <v>1.94151163101196</v>
       </c>
       <c r="H871" t="n">
         <v>830</v>
@@ -25744,7 +25744,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G875" t="n">
-        <v>1.88550674915314</v>
+        <v>1.88550662994385</v>
       </c>
       <c r="H875" t="n">
         <v>7617</v>
@@ -25947,7 +25947,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G882" t="n">
-        <v>1.94151175022125</v>
+        <v>1.94151163101196</v>
       </c>
       <c r="H882" t="n">
         <v>5000</v>
@@ -25976,7 +25976,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G883" t="n">
-        <v>1.94151175022125</v>
+        <v>1.94151163101196</v>
       </c>
       <c r="H883" t="n">
         <v>1500</v>
@@ -26034,7 +26034,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H885" t="n">
         <v>6104</v>
@@ -26092,7 +26092,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G887" t="n">
-        <v>1.94151175022125</v>
+        <v>1.94151163101196</v>
       </c>
       <c r="H887" t="n">
         <v>3600</v>
@@ -26121,7 +26121,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G888" t="n">
-        <v>1.94151175022125</v>
+        <v>1.94151163101196</v>
       </c>
       <c r="H888" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G891" t="n">
-        <v>1.94151175022125</v>
+        <v>1.94151163101196</v>
       </c>
       <c r="H891" t="n">
         <v>3305</v>
@@ -26266,7 +26266,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G893" t="n">
-        <v>1.90417516231537</v>
+        <v>1.90417492389679</v>
       </c>
       <c r="H893" t="n">
         <v>2300</v>
@@ -26411,7 +26411,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G898" t="n">
-        <v>2.20286917686462</v>
+        <v>2.20286893844604</v>
       </c>
       <c r="H898" t="n">
         <v>36211</v>
@@ -26469,7 +26469,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G900" t="n">
-        <v>2.23087167739868</v>
+        <v>2.23087191581726</v>
       </c>
       <c r="H900" t="n">
         <v>18041</v>
@@ -26498,7 +26498,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G901" t="n">
-        <v>2.25887441635132</v>
+        <v>2.2588746547699</v>
       </c>
       <c r="H901" t="n">
         <v>13774</v>
@@ -26527,7 +26527,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G902" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H902" t="n">
         <v>9996</v>
@@ -26556,7 +26556,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G903" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H903" t="n">
         <v>12989</v>
@@ -26614,7 +26614,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G905" t="n">
-        <v>2.23087167739868</v>
+        <v>2.23087191581726</v>
       </c>
       <c r="H905" t="n">
         <v>12451</v>
@@ -26643,7 +26643,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G906" t="n">
-        <v>2.23087167739868</v>
+        <v>2.23087191581726</v>
       </c>
       <c r="H906" t="n">
         <v>1897</v>
@@ -26672,7 +26672,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G907" t="n">
-        <v>2.25887441635132</v>
+        <v>2.2588746547699</v>
       </c>
       <c r="H907" t="n">
         <v>2583</v>
@@ -26701,7 +26701,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G908" t="n">
-        <v>2.23087167739868</v>
+        <v>2.23087191581726</v>
       </c>
       <c r="H908" t="n">
         <v>1500</v>
@@ -26730,7 +26730,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G909" t="n">
-        <v>2.27754259109497</v>
+        <v>2.27754282951355</v>
       </c>
       <c r="H909" t="n">
         <v>4836</v>
@@ -26759,7 +26759,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G910" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H910" t="n">
         <v>2850</v>
@@ -26962,7 +26962,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G917" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H917" t="n">
         <v>3029</v>
@@ -27020,7 +27020,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G919" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H919" t="n">
         <v>3027</v>
@@ -27078,7 +27078,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G921" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H921" t="n">
         <v>2800</v>
@@ -27107,7 +27107,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G922" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H922" t="n">
         <v>2840</v>
@@ -27136,7 +27136,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G923" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H923" t="n">
         <v>2275</v>
@@ -27165,7 +27165,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G924" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H924" t="n">
         <v>2811</v>
@@ -27194,7 +27194,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G925" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H925" t="n">
         <v>10000</v>
@@ -27252,7 +27252,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G927" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H927" t="n">
         <v>13666</v>
@@ -27339,7 +27339,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G930" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H930" t="n">
         <v>2560</v>
@@ -27455,7 +27455,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G934" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H934" t="n">
         <v>18035</v>
@@ -27513,7 +27513,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G936" t="n">
-        <v>2.20286917686462</v>
+        <v>2.20286893844604</v>
       </c>
       <c r="H936" t="n">
         <v>6398</v>
@@ -27542,7 +27542,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G937" t="n">
-        <v>2.24020600318909</v>
+        <v>2.24020576477051</v>
       </c>
       <c r="H937" t="n">
         <v>5629</v>
@@ -27571,7 +27571,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G938" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H938" t="n">
         <v>36604</v>
@@ -27600,7 +27600,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G939" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H939" t="n">
         <v>14446</v>
@@ -27687,7 +27687,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G942" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H942" t="n">
         <v>24000</v>
@@ -27716,7 +27716,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G943" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H943" t="n">
         <v>10884</v>
@@ -27861,7 +27861,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G948" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H948" t="n">
         <v>2000</v>
@@ -27919,7 +27919,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G950" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H950" t="n">
         <v>2715</v>
@@ -27948,7 +27948,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G951" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H951" t="n">
         <v>3000</v>
@@ -28064,7 +28064,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G955" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H955" t="n">
         <v>1000</v>
@@ -28093,7 +28093,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G956" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H956" t="n">
         <v>4601</v>
@@ -28122,7 +28122,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G957" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H957" t="n">
         <v>2000</v>
@@ -28209,7 +28209,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G960" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H960" t="n">
         <v>8263</v>
@@ -28267,7 +28267,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G962" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H962" t="n">
         <v>1000</v>
@@ -28354,7 +28354,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G965" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H965" t="n">
         <v>21</v>
@@ -28383,7 +28383,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G966" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H966" t="n">
         <v>6028</v>
@@ -28644,7 +28644,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G975" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H975" t="n">
         <v>5517</v>
@@ -28702,7 +28702,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G977" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H977" t="n">
         <v>2500</v>
@@ -28731,7 +28731,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G978" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H978" t="n">
         <v>4636</v>
@@ -28818,7 +28818,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G981" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H981" t="n">
         <v>3499</v>
@@ -28905,7 +28905,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G984" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H984" t="n">
         <v>1677</v>
@@ -29427,7 +29427,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1002" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H1002" t="n">
         <v>3900</v>
@@ -29514,7 +29514,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1005" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H1005" t="n">
         <v>642</v>
@@ -29543,7 +29543,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H1006" t="n">
         <v>2020</v>
@@ -29630,7 +29630,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1009" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H1009" t="n">
         <v>1826</v>
@@ -29688,7 +29688,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1011" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H1011" t="n">
         <v>3388</v>
@@ -29978,7 +29978,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1021" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H1021" t="n">
         <v>942</v>
@@ -30065,7 +30065,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1024" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H1024" t="n">
         <v>1010</v>
@@ -30239,7 +30239,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1030" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H1030" t="n">
         <v>1301</v>
@@ -30268,7 +30268,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1031" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H1031" t="n">
         <v>2233</v>
@@ -30297,7 +30297,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1032" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H1032" t="n">
         <v>200</v>
@@ -30326,7 +30326,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1033" t="n">
-        <v>2.31487965583801</v>
+        <v>2.31487941741943</v>
       </c>
       <c r="H1033" t="n">
         <v>939</v>
@@ -30413,7 +30413,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1036" t="n">
-        <v>2.40822124481201</v>
+        <v>2.40822148323059</v>
       </c>
       <c r="H1036" t="n">
         <v>1101</v>
@@ -30558,7 +30558,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1041" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H1041" t="n">
         <v>15334</v>
@@ -30587,7 +30587,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1042" t="n">
-        <v>2.2962110042572</v>
+        <v>2.29621124267578</v>
       </c>
       <c r="H1042" t="n">
         <v>548</v>
@@ -30616,7 +30616,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1043" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H1043" t="n">
         <v>7200</v>
@@ -30645,7 +30645,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1044" t="n">
-        <v>2.32421350479126</v>
+        <v>2.32421374320984</v>
       </c>
       <c r="H1044" t="n">
         <v>0</v>
@@ -30877,7 +30877,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1052" t="n">
-        <v>2.3615505695343</v>
+        <v>2.36155033111572</v>
       </c>
       <c r="H1052" t="n">
         <v>6417</v>
@@ -31138,7 +31138,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1061" t="n">
-        <v>2.37088465690613</v>
+        <v>2.37088441848755</v>
       </c>
       <c r="H1061" t="n">
         <v>6</v>
@@ -31196,7 +31196,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1063" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H1063" t="n">
         <v>2460</v>
@@ -31225,7 +31225,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1064" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H1064" t="n">
         <v>0</v>
@@ -31254,7 +31254,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1065" t="n">
-        <v>2.41755557060242</v>
+        <v>2.41755533218384</v>
       </c>
       <c r="H1065" t="n">
         <v>7276</v>
@@ -31283,7 +31283,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H1066" t="n">
         <v>5691</v>
@@ -31312,7 +31312,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.42688941955566</v>
+        <v>2.42688965797424</v>
       </c>
       <c r="H1067" t="n">
         <v>400</v>
@@ -31457,7 +31457,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1072" t="n">
-        <v>2.65091037750244</v>
+        <v>2.65091013908386</v>
       </c>
       <c r="H1072" t="n">
         <v>188026</v>
@@ -32095,7 +32095,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.6229076385498</v>
+        <v>2.62290787696838</v>
       </c>
       <c r="H1094" t="n">
         <v>16861</v>
@@ -32124,7 +32124,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1095" t="n">
         <v>2654</v>
@@ -32443,7 +32443,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1106" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1106" t="n">
         <v>200</v>
@@ -32501,7 +32501,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1108" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1108" t="n">
         <v>1000</v>
@@ -32530,7 +32530,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1109" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1109" t="n">
         <v>1587</v>
@@ -32559,7 +32559,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1110" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1110" t="n">
         <v>2194</v>
@@ -32617,7 +32617,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1112" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1112" t="n">
         <v>3440</v>
@@ -32646,7 +32646,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1113" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1113" t="n">
         <v>0</v>
@@ -32675,7 +32675,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1114" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1114" t="n">
         <v>3456</v>
@@ -32704,7 +32704,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1115" t="n">
-        <v>2.57623672485352</v>
+        <v>2.57623696327209</v>
       </c>
       <c r="H1115" t="n">
         <v>0</v>
@@ -32849,7 +32849,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1120" t="n">
-        <v>2.63224172592163</v>
+        <v>2.63224196434021</v>
       </c>
       <c r="H1120" t="n">
         <v>3502</v>
@@ -33023,7 +33023,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1126" t="n">
-        <v>2.75358653068542</v>
+        <v>2.753586769104</v>
       </c>
       <c r="H1126" t="n">
         <v>11211</v>
@@ -33516,7 +33516,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1143" t="n">
-        <v>2.85626268386841</v>
+        <v>2.85626244544983</v>
       </c>
       <c r="H1143" t="n">
         <v>15530</v>
@@ -33661,7 +33661,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1148" t="n">
-        <v>2.91226768493652</v>
+        <v>2.91226744651794</v>
       </c>
       <c r="H1148" t="n">
         <v>1813</v>
@@ -33690,7 +33690,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1149" t="n">
-        <v>2.92160201072693</v>
+        <v>2.92160224914551</v>
       </c>
       <c r="H1149" t="n">
         <v>3909</v>
@@ -33835,7 +33835,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1154" t="n">
-        <v>2.85626268386841</v>
+        <v>2.85626244544983</v>
       </c>
       <c r="H1154" t="n">
         <v>3063</v>
@@ -33951,7 +33951,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1158" t="n">
-        <v>2.91226768493652</v>
+        <v>2.91226744651794</v>
       </c>
       <c r="H1158" t="n">
         <v>950</v>
@@ -34038,7 +34038,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1161" t="n">
-        <v>2.88426518440247</v>
+        <v>2.88426494598389</v>
       </c>
       <c r="H1161" t="n">
         <v>2639</v>
@@ -34096,7 +34096,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1163" t="n">
-        <v>2.96827292442322</v>
+        <v>2.9682731628418</v>
       </c>
       <c r="H1163" t="n">
         <v>21970</v>
@@ -34212,7 +34212,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.20162773132324</v>
+        <v>3.20162796974182</v>
       </c>
       <c r="H1167" t="n">
         <v>24299</v>
@@ -34241,7 +34241,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.18295931816101</v>
+        <v>3.18295907974243</v>
       </c>
       <c r="H1168" t="n">
         <v>4144</v>
@@ -34270,7 +34270,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.18295931816101</v>
+        <v>3.18295907974243</v>
       </c>
       <c r="H1169" t="n">
         <v>7563</v>
@@ -34299,7 +34299,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.2296302318573</v>
+        <v>3.22962999343872</v>
       </c>
       <c r="H1170" t="n">
         <v>8410</v>
@@ -34328,7 +34328,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.28563523292542</v>
+        <v>3.28563547134399</v>
       </c>
       <c r="H1171" t="n">
         <v>9302</v>
@@ -34444,7 +34444,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.44431686401367</v>
+        <v>3.44431662559509</v>
       </c>
       <c r="H1175" t="n">
         <v>13251</v>
@@ -34589,7 +34589,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1180" t="n">
-        <v>4.00436782836914</v>
+        <v>4.0043683052063</v>
       </c>
       <c r="H1180" t="n">
         <v>86548</v>
@@ -34618,7 +34618,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1181" t="n">
-        <v>4.26572513580322</v>
+        <v>4.26572561264038</v>
       </c>
       <c r="H1181" t="n">
         <v>61743</v>
@@ -34647,7 +34647,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1182" t="n">
-        <v>4.46174335479736</v>
+        <v>4.46174383163452</v>
       </c>
       <c r="H1182" t="n">
         <v>47140</v>
@@ -34763,7 +34763,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1186" t="n">
-        <v>4.85377883911133</v>
+        <v>4.85377931594849</v>
       </c>
       <c r="H1186" t="n">
         <v>39631</v>
@@ -34850,7 +34850,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1189" t="n">
-        <v>4.51774883270264</v>
+        <v>4.51774930953979</v>
       </c>
       <c r="H1189" t="n">
         <v>67215</v>
@@ -34908,7 +34908,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1191" t="n">
-        <v>4.50841474533081</v>
+        <v>4.50841426849365</v>
       </c>
       <c r="H1191" t="n">
         <v>16999</v>
@@ -34966,7 +34966,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1193" t="n">
-        <v>4.46174335479736</v>
+        <v>4.46174383163452</v>
       </c>
       <c r="H1193" t="n">
         <v>24861</v>
@@ -35024,7 +35024,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1195" t="n">
-        <v>4.46174335479736</v>
+        <v>4.46174383163452</v>
       </c>
       <c r="H1195" t="n">
         <v>12604</v>
@@ -35082,7 +35082,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1197" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1197" t="n">
         <v>37624</v>
@@ -35111,7 +35111,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1198" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1198" t="n">
         <v>17896</v>
@@ -35169,7 +35169,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1200" t="n">
-        <v>4.51774883270264</v>
+        <v>4.51774930953979</v>
       </c>
       <c r="H1200" t="n">
         <v>23594</v>
@@ -35198,7 +35198,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1201" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1201" t="n">
         <v>16723</v>
@@ -35401,7 +35401,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1208" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1208" t="n">
         <v>10200</v>
@@ -35488,7 +35488,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1211" t="n">
-        <v>4.46174335479736</v>
+        <v>4.46174383163452</v>
       </c>
       <c r="H1211" t="n">
         <v>10557</v>
@@ -35517,7 +35517,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1212" t="n">
-        <v>4.50841474533081</v>
+        <v>4.50841426849365</v>
       </c>
       <c r="H1212" t="n">
         <v>8520</v>
@@ -35575,7 +35575,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1214" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1214" t="n">
         <v>5950</v>
@@ -35604,7 +35604,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1215" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1215" t="n">
         <v>6941</v>
@@ -35720,7 +35720,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1219" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1219" t="n">
         <v>2891</v>
@@ -35749,7 +35749,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1220" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1220" t="n">
         <v>5384</v>
@@ -35778,7 +35778,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1221" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1221" t="n">
         <v>3060</v>
@@ -36474,7 +36474,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.40573835372925</v>
+        <v>4.40573787689209</v>
       </c>
       <c r="H1245" t="n">
         <v>1123</v>
@@ -36619,7 +36619,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1250" t="n">
-        <v>4.40573835372925</v>
+        <v>4.40573787689209</v>
       </c>
       <c r="H1250" t="n">
         <v>2487</v>
@@ -36648,7 +36648,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1251" t="n">
-        <v>4.48041200637817</v>
+        <v>4.48041152954102</v>
       </c>
       <c r="H1251" t="n">
         <v>39291</v>
@@ -36677,7 +36677,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1252" t="n">
-        <v>4.53641748428345</v>
+        <v>4.53641700744629</v>
       </c>
       <c r="H1252" t="n">
         <v>10852</v>
@@ -37315,7 +37315,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1274" t="n">
-        <v>4.9907808303833</v>
+        <v>4.99078130722046</v>
       </c>
       <c r="H1274" t="n">
         <v>24772</v>
@@ -37344,7 +37344,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1275" t="n">
-        <v>5.02917194366455</v>
+        <v>5.02917146682739</v>
       </c>
       <c r="H1275" t="n">
         <v>31385</v>
@@ -37431,7 +37431,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1278" t="n">
-        <v>5.48985910415649</v>
+        <v>5.48985958099365</v>
       </c>
       <c r="H1278" t="n">
         <v>70084</v>
@@ -37576,7 +37576,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1283" t="n">
-        <v>5.83537530899048</v>
+        <v>5.83537483215332</v>
       </c>
       <c r="H1283" t="n">
         <v>8786</v>
@@ -37634,7 +37634,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1285" t="n">
-        <v>6.39203882217407</v>
+        <v>6.39203929901123</v>
       </c>
       <c r="H1285" t="n">
         <v>35361</v>
@@ -37750,7 +37750,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1289" t="n">
-        <v>6.46882057189941</v>
+        <v>6.46882009506226</v>
       </c>
       <c r="H1289" t="n">
         <v>13104</v>
@@ -37866,7 +37866,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G1293" t="n">
-        <v>6.18089056015015</v>
+        <v>6.1808910369873</v>
       </c>
       <c r="H1293" t="n">
         <v>21462</v>
@@ -37895,7 +37895,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1294" t="n">
-        <v>6.12330484390259</v>
+        <v>6.12330532073975</v>
       </c>
       <c r="H1294" t="n">
         <v>21748</v>
@@ -37953,7 +37953,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1296" t="n">
-        <v>6.39203882217407</v>
+        <v>6.39203929901123</v>
       </c>
       <c r="H1296" t="n">
         <v>15861</v>
@@ -37982,7 +37982,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1297" t="n">
-        <v>6.48801565170288</v>
+        <v>6.48801612854004</v>
       </c>
       <c r="H1297" t="n">
         <v>2374</v>
@@ -38011,7 +38011,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1298" t="n">
-        <v>6.48801565170288</v>
+        <v>6.48801612854004</v>
       </c>
       <c r="H1298" t="n">
         <v>9827</v>
@@ -38156,7 +38156,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1303" t="n">
-        <v>6.48801565170288</v>
+        <v>6.48801612854004</v>
       </c>
       <c r="H1303" t="n">
         <v>11171</v>
@@ -38388,7 +38388,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1311" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1311" t="n">
         <v>18885</v>
@@ -38446,7 +38446,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1313" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1313" t="n">
         <v>34147</v>
@@ -38533,7 +38533,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1316" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1316" t="n">
         <v>10376</v>
@@ -38939,7 +38939,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1330" t="n">
-        <v>5.68181228637695</v>
+        <v>5.68181276321411</v>
       </c>
       <c r="H1330" t="n">
         <v>4010</v>
@@ -39026,7 +39026,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1333" t="n">
-        <v>5.66261768341064</v>
+        <v>5.66261720657349</v>
       </c>
       <c r="H1333" t="n">
         <v>3167</v>
@@ -39055,7 +39055,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.56664133071899</v>
+        <v>5.56664085388184</v>
       </c>
       <c r="H1334" t="n">
         <v>13673</v>
@@ -39084,7 +39084,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1335" t="n">
-        <v>5.48985910415649</v>
+        <v>5.48985958099365</v>
       </c>
       <c r="H1335" t="n">
         <v>2565</v>
@@ -39142,7 +39142,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1337" t="n">
-        <v>5.56664133071899</v>
+        <v>5.56664085388184</v>
       </c>
       <c r="H1337" t="n">
         <v>2917</v>
@@ -39171,7 +39171,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1338" t="n">
-        <v>5.56664133071899</v>
+        <v>5.56664085388184</v>
       </c>
       <c r="H1338" t="n">
         <v>1312</v>
@@ -39258,7 +39258,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1341" t="n">
-        <v>5.66261768341064</v>
+        <v>5.66261720657349</v>
       </c>
       <c r="H1341" t="n">
         <v>1605</v>
@@ -39287,7 +39287,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1342" t="n">
-        <v>5.66261768341064</v>
+        <v>5.66261720657349</v>
       </c>
       <c r="H1342" t="n">
         <v>3220</v>
@@ -39403,7 +39403,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1346" t="n">
-        <v>5.56664133071899</v>
+        <v>5.56664085388184</v>
       </c>
       <c r="H1346" t="n">
         <v>2814</v>
@@ -39519,7 +39519,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1350" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1350" t="n">
         <v>11182</v>
@@ -39548,7 +39548,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1351" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1351" t="n">
         <v>17082</v>
@@ -39577,7 +39577,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1352" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1352" t="n">
         <v>5027</v>
@@ -39606,7 +39606,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1353" t="n">
-        <v>6.12330484390259</v>
+        <v>6.12330532073975</v>
       </c>
       <c r="H1353" t="n">
         <v>15567</v>
@@ -39693,7 +39693,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1356" t="n">
-        <v>5.87376594543457</v>
+        <v>5.87376546859741</v>
       </c>
       <c r="H1356" t="n">
         <v>18468</v>
@@ -39896,7 +39896,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1363" t="n">
-        <v>5.96974229812622</v>
+        <v>5.96974182128906</v>
       </c>
       <c r="H1363" t="n">
         <v>14927</v>
@@ -40012,7 +40012,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1367" t="n">
-        <v>5.96974229812622</v>
+        <v>5.96974182128906</v>
       </c>
       <c r="H1367" t="n">
         <v>5383</v>
@@ -40041,7 +40041,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1368" t="n">
-        <v>5.83537530899048</v>
+        <v>5.83537483215332</v>
       </c>
       <c r="H1368" t="n">
         <v>3207</v>
@@ -40099,7 +40099,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1370" t="n">
-        <v>5.96974229812622</v>
+        <v>5.96974182128906</v>
       </c>
       <c r="H1370" t="n">
         <v>2420</v>
@@ -40128,7 +40128,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1371" t="n">
-        <v>5.87376594543457</v>
+        <v>5.87376546859741</v>
       </c>
       <c r="H1371" t="n">
         <v>5952</v>
@@ -40186,7 +40186,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1373" t="n">
-        <v>6.0849142074585</v>
+        <v>6.08491468429565</v>
       </c>
       <c r="H1373" t="n">
         <v>4048</v>
@@ -40244,7 +40244,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1375" t="n">
-        <v>5.87376594543457</v>
+        <v>5.87376546859741</v>
       </c>
       <c r="H1375" t="n">
         <v>6216</v>
@@ -40505,7 +40505,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1384" t="n">
-        <v>5.87376594543457</v>
+        <v>5.87376546859741</v>
       </c>
       <c r="H1384" t="n">
         <v>8532</v>
@@ -40534,7 +40534,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1385" t="n">
-        <v>5.96974229812622</v>
+        <v>5.96974182128906</v>
       </c>
       <c r="H1385" t="n">
         <v>4804</v>
@@ -40563,7 +40563,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1386" t="n">
-        <v>5.96974229812622</v>
+        <v>5.96974182128906</v>
       </c>
       <c r="H1386" t="n">
         <v>51315</v>
@@ -40592,7 +40592,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1387" t="n">
-        <v>5.96974229812622</v>
+        <v>5.96974182128906</v>
       </c>
       <c r="H1387" t="n">
         <v>3086</v>
@@ -40621,7 +40621,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1388" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1388" t="n">
         <v>5083</v>
@@ -40679,7 +40679,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1390" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1390" t="n">
         <v>3425</v>
@@ -40737,7 +40737,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1392" t="n">
-        <v>5.93135166168213</v>
+        <v>5.93135118484497</v>
       </c>
       <c r="H1392" t="n">
         <v>2371</v>
@@ -40766,7 +40766,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1393" t="n">
-        <v>5.87376594543457</v>
+        <v>5.87376546859741</v>
       </c>
       <c r="H1393" t="n">
         <v>4474</v>
@@ -41085,7 +41085,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1404" t="n">
-        <v>6.0849142074585</v>
+        <v>6.08491468429565</v>
       </c>
       <c r="H1404" t="n">
         <v>18941</v>
@@ -41143,7 +41143,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1406" t="n">
-        <v>6.12330484390259</v>
+        <v>6.12330532073975</v>
       </c>
       <c r="H1406" t="n">
         <v>40015</v>
@@ -41462,7 +41462,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1417" t="n">
-        <v>7.02548456192017</v>
+        <v>7.02548503875732</v>
       </c>
       <c r="H1417" t="n">
         <v>6334</v>
@@ -41839,7 +41839,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1430" t="n">
-        <v>7.02548456192017</v>
+        <v>7.02548503875732</v>
       </c>
       <c r="H1430" t="n">
         <v>15354</v>
@@ -41897,7 +41897,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1432" t="n">
-        <v>7.02548456192017</v>
+        <v>7.02548503875732</v>
       </c>
       <c r="H1432" t="n">
         <v>1260</v>
@@ -42129,7 +42129,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1440" t="n">
-        <v>7.06387567520142</v>
+        <v>7.06387519836426</v>
       </c>
       <c r="H1440" t="n">
         <v>1592</v>
@@ -42187,7 +42187,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G1442" t="n">
-        <v>7.12146091461182</v>
+        <v>7.12146139144897</v>
       </c>
       <c r="H1442" t="n">
         <v>9087</v>
@@ -42303,7 +42303,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1446" t="n">
-        <v>7.06387567520142</v>
+        <v>7.06387519836426</v>
       </c>
       <c r="H1446" t="n">
         <v>10440</v>
@@ -42361,7 +42361,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1448" t="n">
-        <v>7.06387567520142</v>
+        <v>7.06387519836426</v>
       </c>
       <c r="H1448" t="n">
         <v>6369</v>
@@ -42390,7 +42390,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1449" t="n">
-        <v>6.91031217575073</v>
+        <v>6.91031265258789</v>
       </c>
       <c r="H1449" t="n">
         <v>8416</v>
@@ -42419,7 +42419,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1450" t="n">
-        <v>7.02548456192017</v>
+        <v>7.02548503875732</v>
       </c>
       <c r="H1450" t="n">
         <v>5499</v>
@@ -42535,7 +42535,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1454" t="n">
-        <v>7.06387567520142</v>
+        <v>7.06387519836426</v>
       </c>
       <c r="H1454" t="n">
         <v>2894</v>
@@ -42680,7 +42680,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1459" t="n">
-        <v>6.91031217575073</v>
+        <v>6.91031265258789</v>
       </c>
       <c r="H1459" t="n">
         <v>3121</v>
@@ -42738,7 +42738,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1461" t="n">
-        <v>6.91031217575073</v>
+        <v>6.91031265258789</v>
       </c>
       <c r="H1461" t="n">
         <v>9076</v>
@@ -42767,7 +42767,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1462" t="n">
-        <v>7.06387567520142</v>
+        <v>7.06387519836426</v>
       </c>
       <c r="H1462" t="n">
         <v>300</v>
@@ -42883,7 +42883,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1466" t="n">
-        <v>7.02548456192017</v>
+        <v>7.02548503875732</v>
       </c>
       <c r="H1466" t="n">
         <v>501</v>
@@ -43173,7 +43173,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1476" t="n">
-        <v>6.91031217575073</v>
+        <v>6.91031265258789</v>
       </c>
       <c r="H1476" t="n">
         <v>7848</v>
@@ -43202,7 +43202,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1477" t="n">
-        <v>6.89111709594727</v>
+        <v>6.89111757278442</v>
       </c>
       <c r="H1477" t="n">
         <v>12560</v>
@@ -43260,7 +43260,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1479" t="n">
-        <v>6.91031217575073</v>
+        <v>6.91031265258789</v>
       </c>
       <c r="H1479" t="n">
         <v>16205</v>
@@ -43289,7 +43289,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1480" t="n">
-        <v>6.77594566345215</v>
+        <v>6.77594518661499</v>
       </c>
       <c r="H1480" t="n">
         <v>1973</v>
@@ -43318,7 +43318,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1481" t="n">
-        <v>6.98709392547607</v>
+        <v>6.98709440231323</v>
       </c>
       <c r="H1481" t="n">
         <v>4148</v>
@@ -43347,7 +43347,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1482" t="n">
-        <v>6.89111709594727</v>
+        <v>6.89111757278442</v>
       </c>
       <c r="H1482" t="n">
         <v>144</v>
@@ -43405,7 +43405,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G1484" t="n">
-        <v>6.79514074325562</v>
+        <v>6.79514026641846</v>
       </c>
       <c r="H1484" t="n">
         <v>10530</v>
@@ -43434,7 +43434,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1485" t="n">
-        <v>6.81433582305908</v>
+        <v>6.81433629989624</v>
       </c>
       <c r="H1485" t="n">
         <v>2742</v>
@@ -43463,7 +43463,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1486" t="n">
-        <v>6.91031217575073</v>
+        <v>6.91031265258789</v>
       </c>
       <c r="H1486" t="n">
         <v>1912</v>
@@ -43492,7 +43492,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1487" t="n">
-        <v>6.91031217575073</v>
+        <v>6.91031265258789</v>
       </c>
       <c r="H1487" t="n">
         <v>6267</v>
@@ -43521,7 +43521,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1488" t="n">
-        <v>6.98709392547607</v>
+        <v>6.98709440231323</v>
       </c>
       <c r="H1488" t="n">
         <v>8301</v>
@@ -43724,7 +43724,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1495" t="n">
-        <v>7.29421854019165</v>
+        <v>7.29421901702881</v>
       </c>
       <c r="H1495" t="n">
         <v>3213</v>
@@ -43753,7 +43753,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1496" t="n">
-        <v>7.42858600616455</v>
+        <v>7.42858552932739</v>
       </c>
       <c r="H1496" t="n">
         <v>9505</v>
@@ -43811,7 +43811,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1498" t="n">
-        <v>7.54375839233398</v>
+        <v>7.54375791549683</v>
       </c>
       <c r="H1498" t="n">
         <v>2199</v>
@@ -54721,6 +54721,35 @@
         <v>16931</v>
       </c>
       <c r="I1874" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1875">
+      <c r="A1875" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1875" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1875" t="n">
+        <v>13.8500003814697</v>
+      </c>
+      <c r="D1875" t="n">
+        <v>14.1999998092651</v>
+      </c>
+      <c r="E1875" t="n">
+        <v>13.8500003814697</v>
+      </c>
+      <c r="F1875" t="n">
+        <v>13.8500003814697</v>
+      </c>
+      <c r="G1875" t="n">
+        <v>13.8500003814697</v>
+      </c>
+      <c r="H1875" t="n">
+        <v>13981</v>
+      </c>
+      <c r="I1875" t="s">
         <v>9</v>
       </c>
     </row>
